--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="88">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,58 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.3 → 65.0</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.3</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.8% → -9.0%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>-9.0%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>65.0 → 46.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>65.0</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.7 → 46.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>46.1</t>
-  </si>
-  <si>
-    <t>51.1 → 40.6</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>40.6</t>
+    <t>46.6</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>59.4 → 46.8</t>
+  </si>
+  <si>
+    <t>59.4</t>
+  </si>
+  <si>
+    <t>46.8</t>
+  </si>
+  <si>
+    <t>58.0 → 42.4</t>
+  </si>
+  <si>
+    <t>58.0</t>
+  </si>
+  <si>
+    <t>42.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -827,8 +842,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -968,10 +983,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>671.3</v>
+        <v>737.9</v>
       </c>
       <c r="D2">
-        <v>-0.89</v>
+        <v>9.92</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -980,46 +995,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.38</v>
+        <v>-26.77</v>
       </c>
       <c r="H2">
-        <v>82.81999999999999</v>
+        <v>100.95</v>
       </c>
       <c r="I2">
-        <v>-0.16</v>
+        <v>5.55</v>
       </c>
       <c r="J2">
-        <v>3.04</v>
+        <v>15.97</v>
       </c>
       <c r="K2">
-        <v>-9.210000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="L2">
-        <v>15.52</v>
+        <v>26.15</v>
       </c>
       <c r="M2">
-        <v>-7.17</v>
+        <v>-6.2</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>681.4400000000001</v>
+        <v>689.2</v>
       </c>
       <c r="Q2">
-        <v>659.9400000000001</v>
+        <v>663.55</v>
       </c>
       <c r="R2">
-        <v>652.86</v>
+        <v>655.0599999999999</v>
       </c>
       <c r="S2">
-        <v>627.1799999999999</v>
+        <v>628.23</v>
       </c>
       <c r="T2">
-        <v>7.04</v>
+        <v>17.46</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1034,34 +1049,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.4</v>
+        <v>67.92</v>
       </c>
       <c r="Z2">
-        <v>9.48</v>
+        <v>14.11</v>
       </c>
       <c r="AA2">
-        <v>7.48</v>
+        <v>8.81</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="AC2">
-        <v>47.8</v>
+        <v>64.5</v>
       </c>
       <c r="AD2">
-        <v>57.04</v>
+        <v>55.83</v>
       </c>
       <c r="AE2">
-        <v>25.22</v>
+        <v>28.59</v>
       </c>
       <c r="AF2">
-        <v>-61.91</v>
+        <v>1288.16</v>
       </c>
       <c r="AG2">
-        <v>705.91</v>
+        <v>721.27</v>
       </c>
       <c r="AH2">
-        <v>613.97</v>
+        <v>605.84</v>
       </c>
       <c r="AI2">
         <v>619.79</v>
@@ -1070,7 +1085,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>50.2</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1081,10 +1096,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>311.95</v>
+        <v>289</v>
       </c>
       <c r="D3">
-        <v>-1.75</v>
+        <v>-7.36</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1093,46 +1108,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-1.75</v>
+        <v>-8.98</v>
       </c>
       <c r="H3">
-        <v>103.58</v>
+        <v>88.61</v>
       </c>
       <c r="I3">
-        <v>2.18</v>
+        <v>-6.64</v>
       </c>
       <c r="J3">
-        <v>17.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K3">
-        <v>26.65</v>
+        <v>16.57</v>
       </c>
       <c r="L3">
-        <v>55.96</v>
+        <v>44.45</v>
       </c>
       <c r="M3">
-        <v>40.81</v>
+        <v>37.92</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>311.66</v>
+        <v>307.55</v>
       </c>
       <c r="Q3">
-        <v>297.96</v>
+        <v>299.05</v>
       </c>
       <c r="R3">
-        <v>277.5</v>
+        <v>278.08</v>
       </c>
       <c r="S3">
-        <v>219.47</v>
+        <v>220.08</v>
       </c>
       <c r="T3">
-        <v>42.14</v>
+        <v>31.31</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1147,34 +1162,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>64.98999999999999</v>
+        <v>46.64</v>
       </c>
       <c r="Z3">
-        <v>11.53</v>
+        <v>9.27</v>
       </c>
       <c r="AA3">
-        <v>11.33</v>
+        <v>10.92</v>
       </c>
       <c r="AB3">
-        <v>0.2</v>
+        <v>-1.65</v>
       </c>
       <c r="AC3">
-        <v>60.94</v>
+        <v>40.34</v>
       </c>
       <c r="AD3">
-        <v>64.59999999999999</v>
+        <v>56.58</v>
       </c>
       <c r="AE3">
-        <v>10.72</v>
+        <v>11.93</v>
       </c>
       <c r="AF3">
-        <v>-40.98</v>
+        <v>-19.95</v>
       </c>
       <c r="AG3">
-        <v>332.84</v>
+        <v>331.12</v>
       </c>
       <c r="AH3">
-        <v>263.08</v>
+        <v>266.99</v>
       </c>
       <c r="AI3">
         <v>282.53</v>
@@ -1183,7 +1198,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>37.32</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1194,10 +1209,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1120.5</v>
+        <v>1095</v>
       </c>
       <c r="D4">
-        <v>-1.45</v>
+        <v>-2.28</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1206,46 +1221,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-13.06</v>
+        <v>-15.04</v>
       </c>
       <c r="H4">
-        <v>13.64</v>
+        <v>11.05</v>
       </c>
       <c r="I4">
-        <v>-3.82</v>
+        <v>-4.61</v>
       </c>
       <c r="J4">
-        <v>1.87</v>
+        <v>0.32</v>
       </c>
       <c r="K4">
-        <v>-2.52</v>
+        <v>-3.93</v>
       </c>
       <c r="L4">
-        <v>8.359999999999999</v>
+        <v>5.33</v>
       </c>
       <c r="M4">
-        <v>23.04</v>
+        <v>22.54</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>1137.64</v>
+        <v>1127.06</v>
       </c>
       <c r="Q4">
-        <v>1144.65</v>
+        <v>1144.82</v>
       </c>
       <c r="R4">
-        <v>1098.6</v>
+        <v>1099.31</v>
       </c>
       <c r="S4">
-        <v>1130.78</v>
+        <v>1131.05</v>
       </c>
       <c r="T4">
-        <v>-0.91</v>
+        <v>-3.19</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1260,43 +1275,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>46.15</v>
+        <v>40.12</v>
       </c>
       <c r="Z4">
-        <v>9.07</v>
+        <v>4.54</v>
       </c>
       <c r="AA4">
-        <v>15.12</v>
+        <v>13</v>
       </c>
       <c r="AB4">
-        <v>-6.05</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="AC4">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>4.21</v>
+        <v>2.81</v>
       </c>
       <c r="AE4">
-        <v>31.04</v>
+        <v>30.96</v>
       </c>
       <c r="AF4">
-        <v>-27.64</v>
+        <v>5.7</v>
       </c>
       <c r="AG4">
-        <v>1197.61</v>
+        <v>1197.06</v>
       </c>
       <c r="AH4">
-        <v>1091.68</v>
+        <v>1092.58</v>
       </c>
       <c r="AI4">
-        <v>1106.3</v>
+        <v>1183.12</v>
       </c>
       <c r="AJ4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>27.73</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1307,10 +1322,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>756.1</v>
+        <v>723.55</v>
       </c>
       <c r="D5">
-        <v>-0.79</v>
+        <v>-4.3</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1319,49 +1334,49 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-12.55</v>
+        <v>-16.31</v>
       </c>
       <c r="H5">
-        <v>14.23</v>
+        <v>9.31</v>
       </c>
       <c r="I5">
-        <v>2.47</v>
+        <v>-1.8</v>
       </c>
       <c r="J5">
-        <v>2.81</v>
+        <v>-1.94</v>
       </c>
       <c r="K5">
-        <v>7.84</v>
+        <v>1.93</v>
       </c>
       <c r="L5">
-        <v>-1.56</v>
+        <v>-6.92</v>
       </c>
       <c r="M5">
-        <v>36.35</v>
+        <v>35.16</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>755.42</v>
+        <v>752.77</v>
       </c>
       <c r="Q5">
-        <v>728.27</v>
+        <v>727.55</v>
       </c>
       <c r="R5">
-        <v>727.3</v>
+        <v>727.72</v>
       </c>
       <c r="S5">
-        <v>748.9</v>
+        <v>748.7</v>
       </c>
       <c r="T5">
-        <v>0.96</v>
+        <v>-3.36</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V5" t="s">
         <v>48</v>
@@ -1370,37 +1385,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>59.43</v>
+        <v>46.81</v>
       </c>
       <c r="Z5">
-        <v>9.23</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>4.14</v>
+        <v>4.71</v>
       </c>
       <c r="AB5">
-        <v>5.08</v>
+        <v>2.28</v>
       </c>
       <c r="AC5">
-        <v>76.47</v>
+        <v>50.19</v>
       </c>
       <c r="AD5">
-        <v>88.08</v>
+        <v>72.03</v>
       </c>
       <c r="AE5">
-        <v>20.8</v>
+        <v>22.08</v>
       </c>
       <c r="AF5">
-        <v>108.15</v>
+        <v>-35.32</v>
       </c>
       <c r="AG5">
-        <v>773.54</v>
+        <v>772.64</v>
       </c>
       <c r="AH5">
-        <v>682.99</v>
+        <v>682.46</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1409,7 +1424,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>38.42</v>
+        <v>33.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1420,10 +1435,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>526.45</v>
+        <v>505</v>
       </c>
       <c r="D6">
-        <v>-0.75</v>
+        <v>-4.07</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1432,46 +1447,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-12.26</v>
+        <v>-15.83</v>
       </c>
       <c r="H6">
-        <v>20.04</v>
+        <v>15.15</v>
       </c>
       <c r="I6">
-        <v>-2.48</v>
+        <v>-4.72</v>
       </c>
       <c r="J6">
-        <v>-5.76</v>
+        <v>-9.82</v>
       </c>
       <c r="K6">
-        <v>-7.03</v>
+        <v>-10.15</v>
       </c>
       <c r="L6">
-        <v>4.38</v>
+        <v>-2.37</v>
       </c>
       <c r="M6">
-        <v>13.02</v>
+        <v>10.82</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>529.64</v>
+        <v>524.64</v>
       </c>
       <c r="Q6">
-        <v>537.71</v>
+        <v>535.1900000000001</v>
       </c>
       <c r="R6">
-        <v>548.1</v>
+        <v>547.25</v>
       </c>
       <c r="S6">
-        <v>521.16</v>
+        <v>521.26</v>
       </c>
       <c r="T6">
-        <v>1.02</v>
+        <v>-3.12</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1483,46 +1498,46 @@
         <v>48</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>40.47</v>
+        <v>31.4</v>
       </c>
       <c r="Z6">
-        <v>-6.57</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AA6">
-        <v>-6.18</v>
+        <v>-6.62</v>
       </c>
       <c r="AB6">
-        <v>-0.39</v>
+        <v>-1.75</v>
       </c>
       <c r="AC6">
-        <v>79.84999999999999</v>
+        <v>53.29</v>
       </c>
       <c r="AD6">
-        <v>76.56999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="AE6">
-        <v>11.92</v>
+        <v>12.6</v>
       </c>
       <c r="AF6">
-        <v>-70.95999999999999</v>
+        <v>-54.06</v>
       </c>
       <c r="AG6">
-        <v>557.34</v>
+        <v>557.92</v>
       </c>
       <c r="AH6">
-        <v>518.09</v>
+        <v>512.45</v>
       </c>
       <c r="AI6">
-        <v>555.41</v>
+        <v>553.53</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>17.65</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,10 +1548,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11449</v>
+        <v>10967</v>
       </c>
       <c r="D7">
-        <v>0.04</v>
+        <v>-4.21</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1545,46 +1560,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.35</v>
+        <v>-50.52</v>
       </c>
       <c r="H7">
-        <v>7.45</v>
+        <v>2.93</v>
       </c>
       <c r="I7">
-        <v>-0.2</v>
+        <v>-3.56</v>
       </c>
       <c r="J7">
-        <v>-1.89</v>
+        <v>-7.64</v>
       </c>
       <c r="K7">
-        <v>-7.83</v>
+        <v>-14.45</v>
       </c>
       <c r="L7">
-        <v>-39.05</v>
+        <v>-43.18</v>
       </c>
       <c r="M7">
-        <v>19.11</v>
+        <v>18.03</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>11415</v>
+        <v>11334</v>
       </c>
       <c r="Q7">
-        <v>11525.95</v>
+        <v>11480.6</v>
       </c>
       <c r="R7">
-        <v>11474.02</v>
+        <v>11450.28</v>
       </c>
       <c r="S7">
-        <v>14619.24</v>
+        <v>14577.41</v>
       </c>
       <c r="T7">
-        <v>-21.69</v>
+        <v>-24.77</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1599,43 +1614,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.67</v>
+        <v>39.01</v>
       </c>
       <c r="Z7">
-        <v>-49.96</v>
+        <v>-88.52</v>
       </c>
       <c r="AA7">
-        <v>-30.57</v>
+        <v>-42.16</v>
       </c>
       <c r="AB7">
-        <v>-19.39</v>
+        <v>-46.36</v>
       </c>
       <c r="AC7">
-        <v>29.55</v>
+        <v>20.09</v>
       </c>
       <c r="AD7">
-        <v>33.37</v>
+        <v>28.92</v>
       </c>
       <c r="AE7">
-        <v>389.05</v>
+        <v>415.26</v>
       </c>
       <c r="AF7">
-        <v>-33.79</v>
+        <v>1194.32</v>
       </c>
       <c r="AG7">
-        <v>11955.21</v>
+        <v>11945.22</v>
       </c>
       <c r="AH7">
-        <v>11096.69</v>
+        <v>11015.98</v>
       </c>
       <c r="AI7">
-        <v>12426.6</v>
+        <v>12410.78</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>19.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1646,10 +1661,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>343.15</v>
+        <v>325.85</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>-5.04</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1658,46 +1673,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.29</v>
+        <v>-7.22</v>
       </c>
       <c r="H8">
-        <v>46.45</v>
+        <v>39.07</v>
       </c>
       <c r="I8">
-        <v>3.05</v>
+        <v>-1.51</v>
       </c>
       <c r="J8">
-        <v>0.53</v>
+        <v>-3.92</v>
       </c>
       <c r="K8">
-        <v>16.54</v>
+        <v>10.91</v>
       </c>
       <c r="L8">
-        <v>9.619999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="M8">
-        <v>30.56</v>
+        <v>28.17</v>
       </c>
       <c r="N8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P8">
-        <v>337.97</v>
+        <v>336.97</v>
       </c>
       <c r="Q8">
-        <v>336.67</v>
+        <v>336.19</v>
       </c>
       <c r="R8">
-        <v>333.81</v>
+        <v>333.84</v>
       </c>
       <c r="S8">
-        <v>287.34</v>
+        <v>287.62</v>
       </c>
       <c r="T8">
-        <v>19.42</v>
+        <v>13.29</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1712,34 +1727,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.97</v>
+        <v>42.43</v>
       </c>
       <c r="Z8">
-        <v>1.99</v>
+        <v>0.89</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>0.12</v>
+        <v>-0.78</v>
       </c>
       <c r="AC8">
-        <v>77.41</v>
+        <v>53.47</v>
       </c>
       <c r="AD8">
-        <v>52.39</v>
+        <v>61.25</v>
       </c>
       <c r="AE8">
-        <v>8.77</v>
+        <v>9.9</v>
       </c>
       <c r="AF8">
-        <v>37.04</v>
+        <v>55.52</v>
       </c>
       <c r="AG8">
-        <v>347.36</v>
+        <v>347.93</v>
       </c>
       <c r="AH8">
-        <v>325.97</v>
+        <v>324.45</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1748,7 +1763,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>18.53</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1759,10 +1774,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="D9">
-        <v>-2.99</v>
+        <v>-2.83</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1771,46 +1786,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.67</v>
+        <v>-8.34</v>
       </c>
       <c r="H9">
-        <v>17.21</v>
+        <v>13.89</v>
       </c>
       <c r="I9">
-        <v>-4.53</v>
+        <v>-5.59</v>
       </c>
       <c r="J9">
-        <v>-0.78</v>
+        <v>-3.21</v>
       </c>
       <c r="K9">
-        <v>-2.43</v>
+        <v>-3.54</v>
       </c>
       <c r="L9">
-        <v>14.53</v>
+        <v>11.62</v>
       </c>
       <c r="M9">
-        <v>13.78</v>
+        <v>13.04</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9">
-        <v>1295.66</v>
+        <v>1281.1</v>
       </c>
       <c r="Q9">
-        <v>1306.19</v>
+        <v>1303.76</v>
       </c>
       <c r="R9">
-        <v>1279.83</v>
+        <v>1279.55</v>
       </c>
       <c r="S9">
-        <v>1229.39</v>
+        <v>1229.77</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>-0.05</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1822,46 +1837,46 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>40.61</v>
+        <v>33.75</v>
       </c>
       <c r="Z9">
-        <v>3.05</v>
+        <v>-2.96</v>
       </c>
       <c r="AA9">
-        <v>8.699999999999999</v>
+        <v>6.37</v>
       </c>
       <c r="AB9">
-        <v>-5.65</v>
+        <v>-9.32</v>
       </c>
       <c r="AC9">
-        <v>11.55</v>
+        <v>3.79</v>
       </c>
       <c r="AD9">
-        <v>10.29</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AE9">
-        <v>25.81</v>
+        <v>26.72</v>
       </c>
       <c r="AF9">
-        <v>-3.26</v>
+        <v>-36.76</v>
       </c>
       <c r="AG9">
-        <v>1349.19</v>
+        <v>1357.63</v>
       </c>
       <c r="AH9">
-        <v>1263.19</v>
+        <v>1249.89</v>
       </c>
       <c r="AI9">
-        <v>1264.89</v>
+        <v>1328.6</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK9">
-        <v>28.12</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1872,10 +1887,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>85.73</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="D10">
-        <v>0.34</v>
+        <v>-4.6</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1884,46 +1899,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-6.25</v>
+        <v>-10.56</v>
       </c>
       <c r="H10">
-        <v>137.61</v>
+        <v>126.69</v>
       </c>
       <c r="I10">
-        <v>0.3</v>
+        <v>-2.51</v>
       </c>
       <c r="J10">
-        <v>-1.51</v>
+        <v>-10.5</v>
       </c>
       <c r="K10">
-        <v>63.02</v>
+        <v>53.97</v>
       </c>
       <c r="L10">
-        <v>16.77</v>
+        <v>10.95</v>
       </c>
       <c r="M10">
-        <v>-2.39</v>
+        <v>-3.35</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>84.61</v>
+        <v>84.19</v>
       </c>
       <c r="Q10">
-        <v>82.98999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R10">
-        <v>73.81999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S10">
-        <v>60.26</v>
+        <v>60.33</v>
       </c>
       <c r="T10">
-        <v>42.27</v>
+        <v>35.57</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1938,34 +1953,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.72</v>
+        <v>51.71</v>
       </c>
       <c r="Z10">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AA10">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AB10">
-        <v>-0.29</v>
+        <v>-0.48</v>
       </c>
       <c r="AC10">
-        <v>84.63</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AD10">
-        <v>76.91</v>
+        <v>77.03</v>
       </c>
       <c r="AE10">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AF10">
-        <v>-27.03</v>
+        <v>-52.84</v>
       </c>
       <c r="AG10">
-        <v>89.38</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="AH10">
-        <v>76.59</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1974,7 +1989,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>13.47</v>
+        <v>14.28</v>
       </c>
     </row>
   </sheetData>
@@ -2115,7 +2130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2175,7 +2190,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>62</v>
@@ -2195,1005 +2210,1011 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.61</v>
-      </c>
-      <c r="D9" s="7">
-        <v>3.04</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>17.79</v>
-      </c>
-      <c r="D10" s="7">
-        <v>17.98</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.19</v>
+      <c r="B10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="D11" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-0.38</v>
+        <v>15.97</v>
+      </c>
+      <c r="E11" s="8">
+        <v>12.93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>3.29</v>
+        <v>17.98</v>
       </c>
       <c r="D12" s="7">
-        <v>2.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E12" s="9">
-        <v>-0.48</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-5.06</v>
+        <v>1.87</v>
       </c>
       <c r="D13" s="7">
-        <v>-5.76</v>
+        <v>0.32</v>
       </c>
       <c r="E13" s="9">
-        <v>-0.7</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-1.11</v>
+        <v>2.81</v>
       </c>
       <c r="D14" s="7">
-        <v>-1.89</v>
+        <v>-1.94</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.78</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-1.2</v>
+        <v>-5.76</v>
       </c>
       <c r="D15" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.73</v>
+        <v>-9.82</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-4.06</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>2.75</v>
+        <v>-1.89</v>
       </c>
       <c r="D16" s="7">
-        <v>-0.78</v>
+        <v>-7.64</v>
       </c>
       <c r="E16" s="9">
-        <v>-3.53</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>3.06</v>
+        <v>0.53</v>
       </c>
       <c r="D17" s="7">
-        <v>-1.51</v>
+        <v>-3.92</v>
       </c>
       <c r="E17" s="9">
-        <v>-4.57</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="D18" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.78</v>
+        <v>-3.21</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>2.14</v>
+        <v>-1.51</v>
       </c>
       <c r="D19" s="7">
-        <v>2.18</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.04</v>
+        <v>-10.5</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-8.99</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-0.7</v>
+        <v>-0.16</v>
       </c>
       <c r="D20" s="7">
-        <v>-3.82</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-3.12</v>
+        <v>5.55</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5.71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>3.22</v>
+        <v>2.18</v>
       </c>
       <c r="D21" s="7">
-        <v>2.47</v>
+        <v>-6.64</v>
       </c>
       <c r="E21" s="9">
-        <v>-0.75</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-1.68</v>
+        <v>-3.82</v>
       </c>
       <c r="D22" s="7">
-        <v>-2.48</v>
+        <v>-4.61</v>
       </c>
       <c r="E22" s="9">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-1.26</v>
+        <v>2.47</v>
       </c>
       <c r="D23" s="7">
-        <v>-0.2</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.06</v>
+        <v>-1.8</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>2.5</v>
+        <v>-2.48</v>
       </c>
       <c r="D24" s="7">
-        <v>3.05</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.55</v>
+        <v>-4.72</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="D25" s="7">
-        <v>-4.53</v>
+        <v>-3.56</v>
       </c>
       <c r="E25" s="9">
-        <v>-4.22</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>4.77</v>
+        <v>3.05</v>
       </c>
       <c r="D26" s="7">
-        <v>0.3</v>
+        <v>-1.51</v>
       </c>
       <c r="E26" s="9">
-        <v>-4.47</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>16.44</v>
+        <v>-4.53</v>
       </c>
       <c r="D27" s="7">
-        <v>15.52</v>
+        <v>-5.59</v>
       </c>
       <c r="E27" s="9">
-        <v>-0.92</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" s="7">
-        <v>58.2</v>
+        <v>0.3</v>
       </c>
       <c r="D28" s="7">
-        <v>55.96</v>
+        <v>-2.51</v>
       </c>
       <c r="E28" s="9">
-        <v>-2.24</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>9.16</v>
+        <v>15.52</v>
       </c>
       <c r="D29" s="7">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.8</v>
+        <v>26.15</v>
+      </c>
+      <c r="E29" s="8">
+        <v>10.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>1.92</v>
+        <v>55.96</v>
       </c>
       <c r="D30" s="7">
-        <v>-1.56</v>
+        <v>44.45</v>
       </c>
       <c r="E30" s="9">
-        <v>-3.48</v>
+        <v>-11.51</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>4.32</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D31" s="7">
-        <v>4.38</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.06</v>
+        <v>5.33</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-39.75</v>
+        <v>-1.56</v>
       </c>
       <c r="D32" s="7">
-        <v>-39.05</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.7</v>
+        <v>-6.92</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-5.36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>13.68</v>
+        <v>4.38</v>
       </c>
       <c r="D33" s="7">
-        <v>9.619999999999999</v>
+        <v>-2.37</v>
       </c>
       <c r="E33" s="9">
-        <v>-4.06</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>18.39</v>
+        <v>-39.05</v>
       </c>
       <c r="D34" s="7">
-        <v>14.53</v>
+        <v>-43.18</v>
       </c>
       <c r="E34" s="9">
-        <v>-3.86</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>17.36</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D35" s="7">
-        <v>16.77</v>
+        <v>3.82</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.59</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="7">
-        <v>-9.93</v>
+        <v>14.53</v>
       </c>
       <c r="D36" s="7">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.72</v>
+        <v>11.62</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="7">
-        <v>33.12</v>
+        <v>16.77</v>
       </c>
       <c r="D37" s="7">
-        <v>26.65</v>
+        <v>10.95</v>
       </c>
       <c r="E37" s="9">
-        <v>-6.47</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>-1</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D38" s="7">
-        <v>-2.52</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-1.52</v>
+        <v>2.54</v>
+      </c>
+      <c r="E38" s="8">
+        <v>11.75</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>9.73</v>
+        <v>26.65</v>
       </c>
       <c r="D39" s="7">
-        <v>7.84</v>
+        <v>16.57</v>
       </c>
       <c r="E39" s="9">
-        <v>-1.89</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-5.17</v>
+        <v>-2.52</v>
       </c>
       <c r="D40" s="7">
-        <v>-7.03</v>
+        <v>-3.93</v>
       </c>
       <c r="E40" s="9">
-        <v>-1.86</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-6.63</v>
+        <v>7.84</v>
       </c>
       <c r="D41" s="7">
-        <v>-7.83</v>
+        <v>1.93</v>
       </c>
       <c r="E41" s="9">
-        <v>-1.2</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>17.68</v>
+        <v>-7.03</v>
       </c>
       <c r="D42" s="7">
-        <v>16.54</v>
+        <v>-10.15</v>
       </c>
       <c r="E42" s="9">
-        <v>-1.14</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>0.49</v>
+        <v>-7.83</v>
       </c>
       <c r="D43" s="7">
-        <v>-2.43</v>
+        <v>-14.45</v>
       </c>
       <c r="E43" s="9">
-        <v>-2.92</v>
+        <v>-6.62</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>64.81</v>
+        <v>16.54</v>
       </c>
       <c r="D44" s="7">
-        <v>63.02</v>
+        <v>10.91</v>
       </c>
       <c r="E44" s="9">
-        <v>-1.79</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C45" s="7">
-        <v>-32.78</v>
+        <v>-2.43</v>
       </c>
       <c r="D45" s="7">
-        <v>-33.38</v>
+        <v>-3.54</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.6</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C46" s="7">
-        <v>0</v>
+        <v>63.02</v>
       </c>
       <c r="D46" s="7">
-        <v>-1.75</v>
+        <v>53.97</v>
       </c>
       <c r="E46" s="9">
-        <v>-1.75</v>
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-11.78</v>
+        <v>-33.38</v>
       </c>
       <c r="D47" s="7">
-        <v>-13.06</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.28</v>
+        <v>-26.77</v>
+      </c>
+      <c r="E47" s="8">
+        <v>6.61</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-11.85</v>
+        <v>-1.75</v>
       </c>
       <c r="D48" s="7">
-        <v>-12.55</v>
+        <v>-8.98</v>
       </c>
       <c r="E48" s="9">
-        <v>-0.7</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-11.59</v>
+        <v>-13.06</v>
       </c>
       <c r="D49" s="7">
-        <v>-12.26</v>
+        <v>-15.04</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.67</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-48.37</v>
+        <v>-12.55</v>
       </c>
       <c r="D50" s="7">
-        <v>-48.35</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.02</v>
+        <v>-16.31</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-3.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-2.49</v>
+        <v>-12.26</v>
       </c>
       <c r="D51" s="7">
-        <v>-2.29</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.2</v>
+        <v>-15.83</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-2.76</v>
+        <v>-48.35</v>
       </c>
       <c r="D52" s="7">
-        <v>-5.67</v>
+        <v>-50.52</v>
       </c>
       <c r="E52" s="9">
-        <v>-2.91</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>-6.57</v>
+        <v>-2.29</v>
       </c>
       <c r="D53" s="7">
-        <v>-6.25</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.32</v>
+        <v>-7.22</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-4.93</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" s="7">
-        <v>677.3</v>
+        <v>-5.67</v>
       </c>
       <c r="D54" s="7">
-        <v>671.3</v>
+        <v>-8.34</v>
       </c>
       <c r="E54" s="9">
-        <v>-6</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C55" s="7">
-        <v>317.5</v>
+        <v>-6.25</v>
       </c>
       <c r="D55" s="7">
-        <v>311.95</v>
+        <v>-10.56</v>
       </c>
       <c r="E55" s="9">
-        <v>-5.55</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>1137</v>
+        <v>671.3</v>
       </c>
       <c r="D56" s="7">
-        <v>1120.5</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-16.5</v>
+        <v>737.9</v>
+      </c>
+      <c r="E56" s="8">
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>762.15</v>
+        <v>311.95</v>
       </c>
       <c r="D57" s="7">
-        <v>756.1</v>
+        <v>289</v>
       </c>
       <c r="E57" s="9">
-        <v>-6.05</v>
+        <v>-22.95</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>530.45</v>
+        <v>1120.5</v>
       </c>
       <c r="D58" s="7">
-        <v>526.45</v>
+        <v>1095</v>
       </c>
       <c r="E58" s="9">
-        <v>-4</v>
+        <v>-25.5</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>11444</v>
+        <v>756.1</v>
       </c>
       <c r="D59" s="7">
-        <v>11449</v>
-      </c>
-      <c r="E59" s="8">
-        <v>5</v>
+        <v>723.55</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-32.55</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>342.45</v>
+        <v>526.45</v>
       </c>
       <c r="D60" s="7">
-        <v>343.15</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.7</v>
+        <v>505</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-21.45</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>1304</v>
+        <v>11449</v>
       </c>
       <c r="D61" s="7">
-        <v>1265</v>
+        <v>10967</v>
       </c>
       <c r="E61" s="9">
-        <v>-39</v>
+        <v>-482</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>85.44</v>
+        <v>343.15</v>
       </c>
       <c r="D62" s="7">
-        <v>85.73</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.29</v>
+        <v>325.85</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-17.3</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C63" s="7">
-        <v>34</v>
+        <v>1265</v>
       </c>
       <c r="D63" s="7">
-        <v>55</v>
-      </c>
-      <c r="E63" s="8">
-        <v>21</v>
+        <v>1229.2</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-35.8</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C64" s="7">
-        <v>45</v>
+        <v>85.73</v>
       </c>
       <c r="D64" s="7">
-        <v>34</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E64" s="9">
-        <v>-11</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>13</v>
@@ -3202,322 +3223,390 @@
         <v>55</v>
       </c>
       <c r="D65" s="7">
-        <v>45</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-10</v>
+        <v>77</v>
+      </c>
+      <c r="E65" s="8">
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="7">
-        <v>55.51</v>
+        <v>34</v>
       </c>
       <c r="D66" s="7">
-        <v>53.4</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-2.11</v>
+        <v>45</v>
+      </c>
+      <c r="E66" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C67" s="7">
-        <v>71.29000000000001</v>
+        <v>45</v>
       </c>
       <c r="D67" s="7">
-        <v>64.98999999999999</v>
+        <v>34</v>
       </c>
       <c r="E67" s="9">
-        <v>-6.3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C68" s="7">
-        <v>50.73</v>
+        <v>77</v>
       </c>
       <c r="D68" s="7">
-        <v>46.15</v>
+        <v>66</v>
       </c>
       <c r="E68" s="9">
-        <v>-4.58</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C69" s="7">
-        <v>62.33</v>
+        <v>66</v>
       </c>
       <c r="D69" s="7">
-        <v>59.43</v>
+        <v>55</v>
       </c>
       <c r="E69" s="9">
-        <v>-2.9</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>42.6</v>
+        <v>53.4</v>
       </c>
       <c r="D70" s="7">
-        <v>40.47</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-2.13</v>
+        <v>67.92</v>
+      </c>
+      <c r="E70" s="8">
+        <v>14.52</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>47.56</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D71" s="7">
-        <v>47.67</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.11</v>
+        <v>46.64</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-18.35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>57.39</v>
+        <v>46.15</v>
       </c>
       <c r="D72" s="7">
-        <v>57.97</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.58</v>
+        <v>40.12</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-6.03</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>51.11</v>
+        <v>59.43</v>
       </c>
       <c r="D73" s="7">
-        <v>40.61</v>
+        <v>46.81</v>
       </c>
       <c r="E73" s="9">
-        <v>-10.5</v>
+        <v>-12.62</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>59.28</v>
+        <v>40.47</v>
       </c>
       <c r="D74" s="7">
-        <v>59.72</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.44</v>
+        <v>31.4</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-9.07</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="7">
-        <v>-81.14</v>
+        <v>47.67</v>
       </c>
       <c r="D75" s="7">
-        <v>-61.91</v>
-      </c>
-      <c r="E75" s="8">
-        <v>19.23</v>
+        <v>39.01</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-8.66</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C76" s="7">
-        <v>10.01</v>
+        <v>57.97</v>
       </c>
       <c r="D76" s="7">
-        <v>-40.98</v>
+        <v>42.43</v>
       </c>
       <c r="E76" s="9">
-        <v>-50.99</v>
+        <v>-15.54</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C77" s="7">
-        <v>-26.32</v>
+        <v>40.61</v>
       </c>
       <c r="D77" s="7">
-        <v>-27.64</v>
+        <v>33.75</v>
       </c>
       <c r="E77" s="9">
-        <v>-1.32</v>
+        <v>-6.86</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C78" s="7">
-        <v>27.16</v>
+        <v>59.72</v>
       </c>
       <c r="D78" s="7">
-        <v>108.15</v>
-      </c>
-      <c r="E78" s="8">
-        <v>80.98999999999999</v>
+        <v>51.71</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-8.01</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-51.97</v>
+        <v>-61.91</v>
       </c>
       <c r="D79" s="7">
-        <v>-70.95999999999999</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-18.99</v>
+        <v>1288.16</v>
+      </c>
+      <c r="E79" s="8">
+        <v>1350.07</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>-1.96</v>
+        <v>-40.98</v>
       </c>
       <c r="D80" s="7">
-        <v>-33.79</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-31.83</v>
+        <v>-19.95</v>
+      </c>
+      <c r="E80" s="8">
+        <v>21.03</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>17.23</v>
+        <v>-27.64</v>
       </c>
       <c r="D81" s="7">
-        <v>37.04</v>
+        <v>5.7</v>
       </c>
       <c r="E81" s="8">
-        <v>19.81</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="7">
-        <v>-32.04</v>
+        <v>108.15</v>
       </c>
       <c r="D82" s="7">
-        <v>-3.26</v>
-      </c>
-      <c r="E82" s="8">
-        <v>28.78</v>
+        <v>-35.32</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-143.47</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C83" s="7">
-        <v>122.35</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="D83" s="7">
+        <v>-54.06</v>
+      </c>
+      <c r="E83" s="8">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-33.79</v>
+      </c>
+      <c r="D84" s="7">
+        <v>1194.32</v>
+      </c>
+      <c r="E84" s="8">
+        <v>1228.11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="7">
+        <v>37.04</v>
+      </c>
+      <c r="D85" s="7">
+        <v>55.52</v>
+      </c>
+      <c r="E85" s="8">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="7">
+        <v>-3.26</v>
+      </c>
+      <c r="D86" s="7">
+        <v>-36.76</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-33.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="7">
         <v>-27.03</v>
       </c>
-      <c r="E83" s="9">
-        <v>-149.38</v>
+      <c r="D87" s="7">
+        <v>-52.84</v>
+      </c>
+      <c r="E87" s="9">
+        <v>-25.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3541,28 +3630,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3570,22 +3659,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>64.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>52.3</v>
+        <v>44.4</v>
       </c>
       <c r="E2" s="12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="G2" s="12">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3722,31 +3811,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4081</v>
+        <v>0.3792</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3635</v>
+        <v>0.3516</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3056</v>
+        <v>0.2817</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2304</v>
+        <v>0.2254</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1911</v>
+        <v>0.1803</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1378</v>
+        <v>0.1304</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1302</v>
+        <v>0.1082</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0239</v>
+        <v>-0.0335</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0717</v>
+        <v>-0.062</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,73 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.8% → -9.0%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>-9.0%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>65.0 → 46.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>65.0</t>
-  </si>
-  <si>
-    <t>46.6</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>59.4 → 46.8</t>
-  </si>
-  <si>
-    <t>59.4</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>58.0 → 42.4</t>
-  </si>
-  <si>
-    <t>58.0</t>
-  </si>
-  <si>
-    <t>42.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -296,7 +230,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,13 +264,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,7 +277,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,12 +299,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,23 +380,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -484,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -842,15 +761,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -983,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>737.9</v>
+        <v>742.4</v>
       </c>
       <c r="D2">
-        <v>9.92</v>
+        <v>0.61</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -995,46 +914,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-26.77</v>
+        <v>-26.32</v>
       </c>
       <c r="H2">
-        <v>100.95</v>
+        <v>102.18</v>
       </c>
       <c r="I2">
-        <v>5.55</v>
+        <v>8.57</v>
       </c>
       <c r="J2">
-        <v>15.97</v>
+        <v>11.53</v>
       </c>
       <c r="K2">
-        <v>2.54</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L2">
-        <v>26.15</v>
+        <v>23.69</v>
       </c>
       <c r="M2">
-        <v>-6.2</v>
+        <v>-5.73</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>689.2</v>
+        <v>700.92</v>
       </c>
       <c r="Q2">
-        <v>663.55</v>
+        <v>668.34</v>
       </c>
       <c r="R2">
-        <v>655.0599999999999</v>
+        <v>657.5</v>
       </c>
       <c r="S2">
-        <v>628.23</v>
+        <v>629.33</v>
       </c>
       <c r="T2">
-        <v>17.46</v>
+        <v>17.97</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1049,43 +968,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>67.92</v>
+        <v>68.63</v>
       </c>
       <c r="Z2">
-        <v>14.11</v>
+        <v>17.93</v>
       </c>
       <c r="AA2">
-        <v>8.81</v>
+        <v>10.63</v>
       </c>
       <c r="AB2">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="AC2">
-        <v>64.5</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="AD2">
-        <v>55.83</v>
+        <v>64.25</v>
       </c>
       <c r="AE2">
-        <v>28.59</v>
+        <v>31.9</v>
       </c>
       <c r="AF2">
-        <v>1288.16</v>
+        <v>947.28</v>
       </c>
       <c r="AG2">
-        <v>721.27</v>
+        <v>735.3</v>
       </c>
       <c r="AH2">
-        <v>605.84</v>
+        <v>601.38</v>
       </c>
       <c r="AI2">
-        <v>619.79</v>
+        <v>666.86</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>52.36</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1096,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>289</v>
+        <v>281.25</v>
       </c>
       <c r="D3">
-        <v>-7.36</v>
+        <v>-2.68</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1108,46 +1027,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-8.98</v>
+        <v>-11.42</v>
       </c>
       <c r="H3">
-        <v>88.61</v>
+        <v>83.55</v>
       </c>
       <c r="I3">
-        <v>-6.64</v>
+        <v>-8.57</v>
       </c>
       <c r="J3">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>16.57</v>
+        <v>8.81</v>
       </c>
       <c r="L3">
-        <v>44.45</v>
+        <v>40.15</v>
       </c>
       <c r="M3">
-        <v>37.92</v>
+        <v>37.49</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>307.55</v>
+        <v>302.28</v>
       </c>
       <c r="Q3">
-        <v>299.05</v>
+        <v>299.68</v>
       </c>
       <c r="R3">
-        <v>278.08</v>
+        <v>278.48</v>
       </c>
       <c r="S3">
-        <v>220.08</v>
+        <v>220.66</v>
       </c>
       <c r="T3">
-        <v>31.31</v>
+        <v>27.46</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1162,43 +1081,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.64</v>
+        <v>42.29</v>
       </c>
       <c r="Z3">
-        <v>9.27</v>
+        <v>6.77</v>
       </c>
       <c r="AA3">
-        <v>10.92</v>
+        <v>10.09</v>
       </c>
       <c r="AB3">
-        <v>-1.65</v>
+        <v>-3.32</v>
       </c>
       <c r="AC3">
-        <v>40.34</v>
+        <v>11.98</v>
       </c>
       <c r="AD3">
-        <v>56.58</v>
+        <v>37.75</v>
       </c>
       <c r="AE3">
-        <v>11.93</v>
+        <v>12.23</v>
       </c>
       <c r="AF3">
-        <v>-19.95</v>
+        <v>-26.96</v>
       </c>
       <c r="AG3">
-        <v>331.12</v>
+        <v>329.66</v>
       </c>
       <c r="AH3">
-        <v>266.99</v>
+        <v>269.71</v>
       </c>
       <c r="AI3">
-        <v>282.53</v>
+        <v>320.41</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.24</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1209,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="D4">
-        <v>-2.28</v>
+        <v>0.73</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1221,46 +1140,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-15.04</v>
+        <v>-14.42</v>
       </c>
       <c r="H4">
-        <v>11.05</v>
+        <v>11.87</v>
       </c>
       <c r="I4">
-        <v>-4.61</v>
+        <v>-2.93</v>
       </c>
       <c r="J4">
-        <v>0.32</v>
+        <v>1.05</v>
       </c>
       <c r="K4">
-        <v>-3.93</v>
+        <v>-2.89</v>
       </c>
       <c r="L4">
-        <v>5.33</v>
+        <v>6.02</v>
       </c>
       <c r="M4">
-        <v>22.54</v>
+        <v>23.14</v>
       </c>
       <c r="N4">
         <v>45</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1127.06</v>
+        <v>1120.4</v>
       </c>
       <c r="Q4">
-        <v>1144.82</v>
+        <v>1144.9</v>
       </c>
       <c r="R4">
-        <v>1099.31</v>
+        <v>1100.66</v>
       </c>
       <c r="S4">
-        <v>1131.05</v>
+        <v>1131.36</v>
       </c>
       <c r="T4">
-        <v>-3.19</v>
+        <v>-2.51</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1275,34 +1194,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>40.12</v>
+        <v>42.65</v>
       </c>
       <c r="Z4">
-        <v>4.54</v>
+        <v>1.58</v>
       </c>
       <c r="AA4">
-        <v>13</v>
+        <v>10.72</v>
       </c>
       <c r="AB4">
-        <v>-8.460000000000001</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
       <c r="AE4">
-        <v>30.96</v>
+        <v>31.01</v>
       </c>
       <c r="AF4">
-        <v>5.7</v>
+        <v>-41.95</v>
       </c>
       <c r="AG4">
-        <v>1197.06</v>
+        <v>1196.88</v>
       </c>
       <c r="AH4">
-        <v>1092.58</v>
+        <v>1092.91</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1311,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>32.23</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1322,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>723.55</v>
+        <v>730.85</v>
       </c>
       <c r="D5">
-        <v>-4.3</v>
+        <v>1.01</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1334,46 +1253,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.31</v>
+        <v>-15.47</v>
       </c>
       <c r="H5">
-        <v>9.31</v>
+        <v>10.42</v>
       </c>
       <c r="I5">
-        <v>-1.8</v>
+        <v>-1.07</v>
       </c>
       <c r="J5">
-        <v>-1.94</v>
+        <v>-0.95</v>
       </c>
       <c r="K5">
-        <v>1.93</v>
+        <v>0.41</v>
       </c>
       <c r="L5">
-        <v>-6.92</v>
+        <v>-3.87</v>
       </c>
       <c r="M5">
-        <v>35.16</v>
+        <v>34.78</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>752.77</v>
+        <v>751.1900000000001</v>
       </c>
       <c r="Q5">
-        <v>727.55</v>
+        <v>727.47</v>
       </c>
       <c r="R5">
-        <v>727.72</v>
+        <v>728.4299999999999</v>
       </c>
       <c r="S5">
-        <v>748.7</v>
+        <v>748.5</v>
       </c>
       <c r="T5">
-        <v>-3.36</v>
+        <v>-2.36</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1388,34 +1307,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.81</v>
+        <v>49.4</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
-        <v>4.71</v>
+        <v>4.92</v>
       </c>
       <c r="AB5">
-        <v>2.28</v>
+        <v>0.83</v>
       </c>
       <c r="AC5">
-        <v>50.19</v>
+        <v>36.88</v>
       </c>
       <c r="AD5">
-        <v>72.03</v>
+        <v>54.51</v>
       </c>
       <c r="AE5">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="AF5">
-        <v>-35.32</v>
+        <v>59.68</v>
       </c>
       <c r="AG5">
-        <v>772.64</v>
+        <v>772.53</v>
       </c>
       <c r="AH5">
-        <v>682.46</v>
+        <v>682.41</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1424,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>33.83</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1435,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>505</v>
+        <v>504.7</v>
       </c>
       <c r="D6">
-        <v>-4.07</v>
+        <v>-0.06</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1447,25 +1366,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-15.83</v>
+        <v>-15.88</v>
       </c>
       <c r="H6">
-        <v>15.15</v>
+        <v>15.08</v>
       </c>
       <c r="I6">
-        <v>-4.72</v>
+        <v>-4.14</v>
       </c>
       <c r="J6">
-        <v>-9.82</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="K6">
-        <v>-10.15</v>
+        <v>-11.77</v>
       </c>
       <c r="L6">
-        <v>-2.37</v>
+        <v>-2.9</v>
       </c>
       <c r="M6">
-        <v>10.82</v>
+        <v>10.71</v>
       </c>
       <c r="N6">
         <v>23</v>
@@ -1474,19 +1393,19 @@
         <v>46</v>
       </c>
       <c r="P6">
-        <v>524.64</v>
+        <v>520.28</v>
       </c>
       <c r="Q6">
-        <v>535.1900000000001</v>
+        <v>533.02</v>
       </c>
       <c r="R6">
-        <v>547.25</v>
+        <v>546.46</v>
       </c>
       <c r="S6">
-        <v>521.26</v>
+        <v>521.35</v>
       </c>
       <c r="T6">
-        <v>-3.12</v>
+        <v>-3.19</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1501,43 +1420,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>31.4</v>
+        <v>31.29</v>
       </c>
       <c r="Z6">
-        <v>-8.369999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="AA6">
-        <v>-6.62</v>
+        <v>-7.23</v>
       </c>
       <c r="AB6">
-        <v>-1.75</v>
+        <v>-2.47</v>
       </c>
       <c r="AC6">
-        <v>53.29</v>
+        <v>31.19</v>
       </c>
       <c r="AD6">
-        <v>69.98</v>
+        <v>54.78</v>
       </c>
       <c r="AE6">
-        <v>12.6</v>
+        <v>12.27</v>
       </c>
       <c r="AF6">
-        <v>-54.06</v>
+        <v>0.71</v>
       </c>
       <c r="AG6">
-        <v>557.92</v>
+        <v>558.66</v>
       </c>
       <c r="AH6">
-        <v>512.45</v>
+        <v>507.37</v>
       </c>
       <c r="AI6">
-        <v>553.53</v>
+        <v>543.8</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.42</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1548,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>10967</v>
+        <v>10935</v>
       </c>
       <c r="D7">
-        <v>-4.21</v>
+        <v>-0.29</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1560,22 +1479,22 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-50.52</v>
+        <v>-50.67</v>
       </c>
       <c r="H7">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="I7">
-        <v>-3.56</v>
+        <v>-4.63</v>
       </c>
       <c r="J7">
-        <v>-7.64</v>
+        <v>-7.91</v>
       </c>
       <c r="K7">
-        <v>-14.45</v>
+        <v>-14.22</v>
       </c>
       <c r="L7">
-        <v>-43.18</v>
+        <v>-41.38</v>
       </c>
       <c r="M7">
         <v>18.03</v>
@@ -1584,22 +1503,22 @@
         <v>12</v>
       </c>
       <c r="O7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>11334</v>
+        <v>11227.8</v>
       </c>
       <c r="Q7">
-        <v>11480.6</v>
+        <v>11452.9</v>
       </c>
       <c r="R7">
-        <v>11450.28</v>
+        <v>11433.6</v>
       </c>
       <c r="S7">
-        <v>14577.41</v>
+        <v>14532.98</v>
       </c>
       <c r="T7">
-        <v>-24.77</v>
+        <v>-24.76</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1614,43 +1533,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>39.01</v>
+        <v>38.51</v>
       </c>
       <c r="Z7">
-        <v>-88.52</v>
+        <v>-120.27</v>
       </c>
       <c r="AA7">
-        <v>-42.16</v>
+        <v>-57.78</v>
       </c>
       <c r="AB7">
-        <v>-46.36</v>
+        <v>-62.49</v>
       </c>
       <c r="AC7">
-        <v>20.09</v>
+        <v>6.32</v>
       </c>
       <c r="AD7">
-        <v>28.92</v>
+        <v>18.65</v>
       </c>
       <c r="AE7">
-        <v>415.26</v>
+        <v>405.1</v>
       </c>
       <c r="AF7">
-        <v>1194.32</v>
+        <v>-59.07</v>
       </c>
       <c r="AG7">
-        <v>11945.22</v>
+        <v>11977.59</v>
       </c>
       <c r="AH7">
-        <v>11015.98</v>
+        <v>10928.21</v>
       </c>
       <c r="AI7">
-        <v>12410.78</v>
+        <v>12187.8</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>21.3</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1661,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>325.85</v>
+        <v>325.55</v>
       </c>
       <c r="D8">
-        <v>-5.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1673,46 +1592,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.22</v>
+        <v>-7.3</v>
       </c>
       <c r="H8">
-        <v>39.07</v>
+        <v>38.94</v>
       </c>
       <c r="I8">
-        <v>-1.51</v>
+        <v>-1.94</v>
       </c>
       <c r="J8">
-        <v>-3.92</v>
+        <v>-2.94</v>
       </c>
       <c r="K8">
-        <v>10.91</v>
+        <v>8.77</v>
       </c>
       <c r="L8">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="M8">
-        <v>28.17</v>
+        <v>28.1</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P8">
-        <v>336.97</v>
+        <v>335.68</v>
       </c>
       <c r="Q8">
-        <v>336.19</v>
+        <v>336.04</v>
       </c>
       <c r="R8">
-        <v>333.84</v>
+        <v>333.91</v>
       </c>
       <c r="S8">
-        <v>287.62</v>
+        <v>287.9</v>
       </c>
       <c r="T8">
-        <v>13.29</v>
+        <v>13.08</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1727,34 +1646,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>42.43</v>
+        <v>42.22</v>
       </c>
       <c r="Z8">
-        <v>0.89</v>
+        <v>-0.01</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AB8">
-        <v>-0.78</v>
+        <v>-1.34</v>
       </c>
       <c r="AC8">
-        <v>53.47</v>
+        <v>27.45</v>
       </c>
       <c r="AD8">
-        <v>61.25</v>
+        <v>52.78</v>
       </c>
       <c r="AE8">
-        <v>9.9</v>
+        <v>10.12</v>
       </c>
       <c r="AF8">
-        <v>55.52</v>
+        <v>17.84</v>
       </c>
       <c r="AG8">
-        <v>347.93</v>
+        <v>348.26</v>
       </c>
       <c r="AH8">
-        <v>324.45</v>
+        <v>323.81</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1763,7 +1682,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.22</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1774,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1229.2</v>
+        <v>1248.9</v>
       </c>
       <c r="D9">
-        <v>-2.83</v>
+        <v>1.6</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1786,46 +1705,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-8.34</v>
+        <v>-6.87</v>
       </c>
       <c r="H9">
-        <v>13.89</v>
+        <v>15.71</v>
       </c>
       <c r="I9">
-        <v>-5.59</v>
+        <v>-3.73</v>
       </c>
       <c r="J9">
-        <v>-3.21</v>
+        <v>-2.26</v>
       </c>
       <c r="K9">
-        <v>-3.54</v>
+        <v>-2.98</v>
       </c>
       <c r="L9">
-        <v>11.62</v>
+        <v>13.64</v>
       </c>
       <c r="M9">
-        <v>13.04</v>
+        <v>13.64</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1281.1</v>
+        <v>1271.42</v>
       </c>
       <c r="Q9">
-        <v>1303.76</v>
+        <v>1302.82</v>
       </c>
       <c r="R9">
-        <v>1279.55</v>
+        <v>1279.6</v>
       </c>
       <c r="S9">
-        <v>1229.77</v>
+        <v>1230.21</v>
       </c>
       <c r="T9">
-        <v>-0.05</v>
+        <v>1.52</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1837,46 +1756,46 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9">
-        <v>33.75</v>
+        <v>39.78</v>
       </c>
       <c r="Z9">
-        <v>-2.96</v>
+        <v>-6.05</v>
       </c>
       <c r="AA9">
-        <v>6.37</v>
+        <v>3.88</v>
       </c>
       <c r="AB9">
-        <v>-9.32</v>
+        <v>-9.94</v>
       </c>
       <c r="AC9">
-        <v>3.79</v>
+        <v>6.56</v>
       </c>
       <c r="AD9">
-        <v>8.960000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AE9">
-        <v>26.72</v>
+        <v>26.47</v>
       </c>
       <c r="AF9">
-        <v>-36.76</v>
+        <v>10.57</v>
       </c>
       <c r="AG9">
-        <v>1357.63</v>
+        <v>1359.9</v>
       </c>
       <c r="AH9">
-        <v>1249.89</v>
+        <v>1245.75</v>
       </c>
       <c r="AI9">
-        <v>1328.6</v>
+        <v>1318</v>
       </c>
       <c r="AJ9" t="s">
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>31.62</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1887,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.79000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="D10">
-        <v>-4.6</v>
+        <v>0.16</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1899,46 +1818,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.56</v>
+        <v>-10.42</v>
       </c>
       <c r="H10">
-        <v>126.69</v>
+        <v>127.05</v>
       </c>
       <c r="I10">
-        <v>-2.51</v>
+        <v>-2.62</v>
       </c>
       <c r="J10">
-        <v>-10.5</v>
+        <v>-10.42</v>
       </c>
       <c r="K10">
-        <v>53.97</v>
+        <v>57.87</v>
       </c>
       <c r="L10">
-        <v>10.95</v>
+        <v>11.11</v>
       </c>
       <c r="M10">
-        <v>-3.35</v>
+        <v>-3.33</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>84.19</v>
+        <v>83.75</v>
       </c>
       <c r="Q10">
-        <v>82.5</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="R10">
-        <v>74.40000000000001</v>
+        <v>74.98</v>
       </c>
       <c r="S10">
-        <v>60.33</v>
+        <v>60.41</v>
       </c>
       <c r="T10">
-        <v>35.57</v>
+        <v>35.61</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1953,34 +1872,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>51.71</v>
+        <v>51.94</v>
       </c>
       <c r="Z10">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AA10">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="AB10">
-        <v>-0.48</v>
+        <v>-0.59</v>
       </c>
       <c r="AC10">
-        <v>70.40000000000001</v>
+        <v>50.29</v>
       </c>
       <c r="AD10">
-        <v>77.03</v>
+        <v>68.44</v>
       </c>
       <c r="AE10">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="AF10">
-        <v>-52.84</v>
+        <v>-19.33</v>
       </c>
       <c r="AG10">
-        <v>87.51000000000001</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="AH10">
-        <v>77.48999999999999</v>
+        <v>77.69</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1989,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>14.28</v>
+        <v>17.37</v>
       </c>
     </row>
   </sheetData>
@@ -2130,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2150,1463 +2069,1297 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>15.97</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11.53</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>74</v>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5.3</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.73</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>79</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-1.94</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-9.82</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.64</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.91</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.92</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.94</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.21</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-10.5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-10.42</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3.04</v>
-      </c>
-      <c r="D11" s="7">
-        <v>15.97</v>
-      </c>
-      <c r="E11" s="8">
-        <v>12.93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5.55</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8.57</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>17.98</v>
-      </c>
-      <c r="D12" s="7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-9.779999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-6.64</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-8.57</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.93</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.81</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.07</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-4.72</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-4.14</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-3.56</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-4.63</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.51</v>
+      </c>
+      <c r="D22" s="5">
         <v>-1.94</v>
       </c>
-      <c r="E14" s="9">
-        <v>-4.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="E22" s="6">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-5.59</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-3.73</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-2.51</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-2.62</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>26.15</v>
+      </c>
+      <c r="D25" s="5">
+        <v>23.69</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>44.45</v>
+      </c>
+      <c r="D26" s="5">
+        <v>40.15</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>5.33</v>
+      </c>
+      <c r="D27" s="5">
+        <v>6.02</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-6.92</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-3.87</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-5.76</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-9.82</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-2.37</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-2.9</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.89</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-7.64</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-5.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-43.18</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-41.38</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.92</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="D31" s="5">
+        <v>3.68</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>11.62</v>
+      </c>
+      <c r="D32" s="5">
+        <v>13.64</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-10.5</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-8.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>10.95</v>
+      </c>
+      <c r="D33" s="5">
+        <v>11.11</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="D34" s="5">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="E34" s="7">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>16.57</v>
+      </c>
+      <c r="D35" s="5">
+        <v>8.81</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-7.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-3.93</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1.93</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-10.15</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-11.77</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-14.45</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-14.22</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>10.91</v>
+      </c>
+      <c r="D40" s="5">
+        <v>8.77</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-3.54</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-2.98</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>53.97</v>
+      </c>
+      <c r="D42" s="5">
+        <v>57.87</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-26.77</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-26.32</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-8.98</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-11.42</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-15.04</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-14.42</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-16.31</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.47</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-15.83</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-15.88</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-50.52</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-50.67</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-7.22</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-7.3</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-8.34</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-6.87</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-10.56</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-10.42</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>737.9</v>
+      </c>
+      <c r="D52" s="5">
+        <v>742.4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>289</v>
+      </c>
+      <c r="D53" s="5">
+        <v>281.25</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-7.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1095</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1103</v>
+      </c>
+      <c r="E54" s="7">
         <v>8</v>
       </c>
-      <c r="C20" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="D20" s="7">
-        <v>5.55</v>
-      </c>
-      <c r="E20" s="8">
-        <v>5.71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>723.55</v>
+      </c>
+      <c r="D55" s="5">
+        <v>730.85</v>
+      </c>
+      <c r="E55" s="7">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>505</v>
+      </c>
+      <c r="D56" s="5">
+        <v>504.7</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>10967</v>
+      </c>
+      <c r="D57" s="5">
+        <v>10935</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>325.85</v>
+      </c>
+      <c r="D58" s="5">
+        <v>325.55</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1229.2</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1248.9</v>
+      </c>
+      <c r="E59" s="7">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="D60" s="5">
+        <v>81.92</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2.18</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-6.64</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-8.82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>99</v>
+      </c>
+      <c r="D61" s="5">
+        <v>88</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>88</v>
+      </c>
+      <c r="D62" s="5">
+        <v>99</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>67.92</v>
+      </c>
+      <c r="D63" s="5">
+        <v>68.63</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46.64</v>
+      </c>
+      <c r="D64" s="5">
+        <v>42.29</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-3.82</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-4.61</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>40.12</v>
+      </c>
+      <c r="D65" s="5">
+        <v>42.65</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2.47</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-1.8</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>46.81</v>
+      </c>
+      <c r="D66" s="5">
+        <v>49.4</v>
+      </c>
+      <c r="E66" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-4.72</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>31.4</v>
+      </c>
+      <c r="D67" s="5">
+        <v>31.29</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.2</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.56</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-3.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>39.01</v>
+      </c>
+      <c r="D68" s="5">
+        <v>38.51</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>3.05</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-4.56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>42.43</v>
+      </c>
+      <c r="D69" s="5">
+        <v>42.22</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-5.59</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>33.75</v>
+      </c>
+      <c r="D70" s="5">
+        <v>39.78</v>
+      </c>
+      <c r="E70" s="7">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-2.51</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>51.71</v>
+      </c>
+      <c r="D71" s="5">
+        <v>51.94</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>15.52</v>
-      </c>
-      <c r="D29" s="7">
-        <v>26.15</v>
-      </c>
-      <c r="E29" s="8">
-        <v>10.63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>1288.16</v>
+      </c>
+      <c r="D72" s="5">
+        <v>947.28</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-340.88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>55.96</v>
-      </c>
-      <c r="D30" s="7">
-        <v>44.45</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-11.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-19.95</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-26.96</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-7.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="D31" s="7">
-        <v>5.33</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>5.7</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-41.95</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-47.65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-1.56</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-6.92</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-35.32</v>
+      </c>
+      <c r="D75" s="5">
+        <v>59.68</v>
+      </c>
+      <c r="E75" s="7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>4.38</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-2.37</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-6.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-54.06</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="E76" s="7">
+        <v>54.77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-39.05</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-43.18</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>1194.32</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-59.07</v>
+      </c>
+      <c r="E77" s="6">
+        <v>-1253.39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="D35" s="7">
-        <v>3.82</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>55.52</v>
+      </c>
+      <c r="D78" s="5">
+        <v>17.84</v>
+      </c>
+      <c r="E78" s="6">
+        <v>-37.68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>14.53</v>
-      </c>
-      <c r="D36" s="7">
-        <v>11.62</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-36.76</v>
+      </c>
+      <c r="D79" s="5">
+        <v>10.57</v>
+      </c>
+      <c r="E79" s="7">
+        <v>47.33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="7">
-        <v>16.77</v>
-      </c>
-      <c r="D37" s="7">
-        <v>10.95</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-5.82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D38" s="7">
-        <v>2.54</v>
-      </c>
-      <c r="E38" s="8">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>26.65</v>
-      </c>
-      <c r="D39" s="7">
-        <v>16.57</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-10.08</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-2.52</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>7.84</v>
-      </c>
-      <c r="D41" s="7">
-        <v>1.93</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-5.91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-7.03</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-10.15</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-7.83</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-14.45</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-6.62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>16.54</v>
-      </c>
-      <c r="D44" s="7">
-        <v>10.91</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-5.63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-2.43</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-3.54</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="7">
-        <v>63.02</v>
-      </c>
-      <c r="D46" s="7">
-        <v>53.97</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-9.050000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-33.38</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-26.77</v>
-      </c>
-      <c r="E47" s="8">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-1.75</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-8.98</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-7.23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-13.06</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-15.04</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-12.55</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-16.31</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-3.76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-12.26</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-15.83</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-3.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-48.35</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-50.52</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-2.29</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-7.22</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-4.93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-5.67</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-8.34</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-6.25</v>
-      </c>
-      <c r="D55" s="7">
-        <v>-10.56</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>671.3</v>
-      </c>
-      <c r="D56" s="7">
-        <v>737.9</v>
-      </c>
-      <c r="E56" s="8">
-        <v>66.59999999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>311.95</v>
-      </c>
-      <c r="D57" s="7">
-        <v>289</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-22.95</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1120.5</v>
-      </c>
-      <c r="D58" s="7">
-        <v>1095</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-25.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>756.1</v>
-      </c>
-      <c r="D59" s="7">
-        <v>723.55</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-32.55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>526.45</v>
-      </c>
-      <c r="D60" s="7">
-        <v>505</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-21.45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>11449</v>
-      </c>
-      <c r="D61" s="7">
-        <v>10967</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-482</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>343.15</v>
-      </c>
-      <c r="D62" s="7">
-        <v>325.85</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-17.3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>1265</v>
-      </c>
-      <c r="D63" s="7">
-        <v>1229.2</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-35.8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="7">
-        <v>85.73</v>
-      </c>
-      <c r="D64" s="7">
-        <v>81.79000000000001</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>55</v>
-      </c>
-      <c r="D65" s="7">
-        <v>77</v>
-      </c>
-      <c r="E65" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>34</v>
-      </c>
-      <c r="D66" s="7">
-        <v>45</v>
-      </c>
-      <c r="E66" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>45</v>
-      </c>
-      <c r="D67" s="7">
-        <v>34</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="7">
-        <v>77</v>
-      </c>
-      <c r="D68" s="7">
-        <v>66</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="7">
-        <v>66</v>
-      </c>
-      <c r="D69" s="7">
-        <v>55</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>53.4</v>
-      </c>
-      <c r="D70" s="7">
-        <v>67.92</v>
-      </c>
-      <c r="E70" s="8">
-        <v>14.52</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="D71" s="7">
-        <v>46.64</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-18.35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>46.15</v>
-      </c>
-      <c r="D72" s="7">
-        <v>40.12</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>59.43</v>
-      </c>
-      <c r="D73" s="7">
-        <v>46.81</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-12.62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>40.47</v>
-      </c>
-      <c r="D74" s="7">
-        <v>31.4</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-9.07</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>47.67</v>
-      </c>
-      <c r="D75" s="7">
-        <v>39.01</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-8.66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>57.97</v>
-      </c>
-      <c r="D76" s="7">
-        <v>42.43</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-15.54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="7">
-        <v>40.61</v>
-      </c>
-      <c r="D77" s="7">
-        <v>33.75</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-6.86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" s="7">
-        <v>59.72</v>
-      </c>
-      <c r="D78" s="7">
-        <v>51.71</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-8.01</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="6" t="s">
+      <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C79" s="7">
-        <v>-61.91</v>
-      </c>
-      <c r="D79" s="7">
-        <v>1288.16</v>
-      </c>
-      <c r="E79" s="8">
-        <v>1350.07</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-40.98</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-19.95</v>
-      </c>
-      <c r="E80" s="8">
-        <v>21.03</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-27.64</v>
-      </c>
-      <c r="D81" s="7">
-        <v>5.7</v>
-      </c>
-      <c r="E81" s="8">
-        <v>33.34</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>108.15</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-35.32</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-143.47</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-70.95999999999999</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-54.06</v>
-      </c>
-      <c r="E83" s="8">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-33.79</v>
-      </c>
-      <c r="D84" s="7">
-        <v>1194.32</v>
-      </c>
-      <c r="E84" s="8">
-        <v>1228.11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>37.04</v>
-      </c>
-      <c r="D85" s="7">
-        <v>55.52</v>
-      </c>
-      <c r="E85" s="8">
-        <v>18.48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="7">
-        <v>-3.26</v>
-      </c>
-      <c r="D86" s="7">
-        <v>-36.76</v>
-      </c>
-      <c r="E86" s="9">
-        <v>-33.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C87" s="7">
-        <v>-27.03</v>
-      </c>
-      <c r="D87" s="7">
+      <c r="C80" s="5">
         <v>-52.84</v>
       </c>
-      <c r="E87" s="9">
-        <v>-25.81</v>
+      <c r="D80" s="5">
+        <v>-19.33</v>
+      </c>
+      <c r="E80" s="7">
+        <v>33.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3626,60 +3379,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>87</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="10">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.4</v>
-      </c>
-      <c r="E2" s="12">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-1.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="10">
+        <v>45.2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3781,61 +3534,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3792</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3516</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2817</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2254</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="A2" s="13">
+        <v>0.3749</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3478</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.281</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2314</v>
+      </c>
+      <c r="E2" s="13">
         <v>0.1803</v>
       </c>
-      <c r="F2" s="15">
-        <v>0.1304</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1082</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0335</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.062</v>
+      <c r="F2" s="13">
+        <v>0.1364</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.1071</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0333</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.0573</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.9 → 49.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -761,8 +789,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -902,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>742.4</v>
+        <v>726</v>
       </c>
       <c r="D2">
-        <v>0.61</v>
+        <v>-2.21</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -914,46 +942,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-26.32</v>
+        <v>-27.95</v>
       </c>
       <c r="H2">
-        <v>102.18</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="I2">
-        <v>8.57</v>
+        <v>7.44</v>
       </c>
       <c r="J2">
-        <v>11.53</v>
+        <v>12.27</v>
       </c>
       <c r="K2">
-        <v>8.130000000000001</v>
+        <v>5.07</v>
       </c>
       <c r="L2">
-        <v>23.69</v>
+        <v>20.76</v>
       </c>
       <c r="M2">
-        <v>-5.73</v>
+        <v>-6.41</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>700.92</v>
+        <v>710.98</v>
       </c>
       <c r="Q2">
-        <v>668.34</v>
+        <v>672.72</v>
       </c>
       <c r="R2">
-        <v>657.5</v>
+        <v>658.99</v>
       </c>
       <c r="S2">
-        <v>629.33</v>
+        <v>630.36</v>
       </c>
       <c r="T2">
-        <v>17.97</v>
+        <v>15.17</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>68.63</v>
+        <v>63.14</v>
       </c>
       <c r="Z2">
-        <v>17.93</v>
+        <v>19.41</v>
       </c>
       <c r="AA2">
-        <v>10.63</v>
+        <v>12.39</v>
       </c>
       <c r="AB2">
-        <v>7.3</v>
+        <v>7.02</v>
       </c>
       <c r="AC2">
-        <v>80.45999999999999</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="AD2">
-        <v>64.25</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>31.9</v>
+        <v>31.43</v>
       </c>
       <c r="AF2">
-        <v>947.28</v>
+        <v>-46.11</v>
       </c>
       <c r="AG2">
-        <v>735.3</v>
+        <v>742.8099999999999</v>
       </c>
       <c r="AH2">
-        <v>601.38</v>
+        <v>602.63</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1004,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>56.05</v>
+        <v>57.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>281.25</v>
+        <v>291.2</v>
       </c>
       <c r="D3">
-        <v>-2.68</v>
+        <v>3.54</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1027,46 +1055,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-11.42</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="H3">
-        <v>83.55</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="I3">
-        <v>-8.57</v>
+        <v>-6.58</v>
       </c>
       <c r="J3">
-        <v>5.3</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K3">
-        <v>8.81</v>
+        <v>10.28</v>
       </c>
       <c r="L3">
-        <v>40.15</v>
+        <v>41.32</v>
       </c>
       <c r="M3">
-        <v>37.49</v>
+        <v>38.16</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3">
-        <v>302.28</v>
+        <v>298.18</v>
       </c>
       <c r="Q3">
-        <v>299.68</v>
+        <v>300.81</v>
       </c>
       <c r="R3">
-        <v>278.48</v>
+        <v>279.11</v>
       </c>
       <c r="S3">
-        <v>220.66</v>
+        <v>221.31</v>
       </c>
       <c r="T3">
-        <v>27.46</v>
+        <v>31.58</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>42.29</v>
+        <v>48.88</v>
       </c>
       <c r="Z3">
-        <v>6.77</v>
+        <v>5.53</v>
       </c>
       <c r="AA3">
-        <v>10.09</v>
+        <v>9.18</v>
       </c>
       <c r="AB3">
-        <v>-3.32</v>
+        <v>-3.65</v>
       </c>
       <c r="AC3">
-        <v>11.98</v>
+        <v>7.33</v>
       </c>
       <c r="AD3">
-        <v>37.75</v>
+        <v>19.88</v>
       </c>
       <c r="AE3">
-        <v>12.23</v>
+        <v>12.32</v>
       </c>
       <c r="AF3">
-        <v>-26.96</v>
+        <v>-47.99</v>
       </c>
       <c r="AG3">
-        <v>329.66</v>
+        <v>327.38</v>
       </c>
       <c r="AH3">
-        <v>269.71</v>
+        <v>274.23</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1117,7 +1145,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>37.24</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1103</v>
+        <v>1128.4</v>
       </c>
       <c r="D4">
-        <v>0.73</v>
+        <v>2.3</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1140,46 +1168,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-14.42</v>
+        <v>-12.45</v>
       </c>
       <c r="H4">
-        <v>11.87</v>
+        <v>14.44</v>
       </c>
       <c r="I4">
-        <v>-2.93</v>
+        <v>-1.58</v>
       </c>
       <c r="J4">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="K4">
-        <v>-2.89</v>
+        <v>-0.31</v>
       </c>
       <c r="L4">
-        <v>6.02</v>
+        <v>8.92</v>
       </c>
       <c r="M4">
-        <v>23.14</v>
+        <v>24.24</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1120.4</v>
+        <v>1116.78</v>
       </c>
       <c r="Q4">
-        <v>1144.9</v>
+        <v>1145.57</v>
       </c>
       <c r="R4">
-        <v>1100.66</v>
+        <v>1102.8</v>
       </c>
       <c r="S4">
-        <v>1131.36</v>
+        <v>1131.78</v>
       </c>
       <c r="T4">
-        <v>-2.51</v>
+        <v>-0.3</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1222,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>42.65</v>
+        <v>49.89</v>
       </c>
       <c r="Z4">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="AA4">
-        <v>10.72</v>
+        <v>8.83</v>
       </c>
       <c r="AB4">
-        <v>-9.140000000000001</v>
+        <v>-7.56</v>
       </c>
       <c r="AC4">
-        <v>2.6</v>
+        <v>12.64</v>
       </c>
       <c r="AD4">
-        <v>2.27</v>
+        <v>5.08</v>
       </c>
       <c r="AE4">
-        <v>31.01</v>
+        <v>31.05</v>
       </c>
       <c r="AF4">
-        <v>-41.95</v>
+        <v>-7.66</v>
       </c>
       <c r="AG4">
-        <v>1196.88</v>
+        <v>1196.26</v>
       </c>
       <c r="AH4">
-        <v>1092.91</v>
+        <v>1094.87</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1230,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>36.43</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>730.85</v>
+        <v>724.45</v>
       </c>
       <c r="D5">
-        <v>1.01</v>
+        <v>-0.88</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1253,46 +1281,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.47</v>
+        <v>-16.21</v>
       </c>
       <c r="H5">
-        <v>10.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I5">
-        <v>-1.07</v>
+        <v>-7.51</v>
       </c>
       <c r="J5">
-        <v>-0.95</v>
+        <v>-1.09</v>
       </c>
       <c r="K5">
-        <v>0.41</v>
+        <v>2.47</v>
       </c>
       <c r="L5">
-        <v>-3.87</v>
+        <v>-2.11</v>
       </c>
       <c r="M5">
-        <v>34.78</v>
+        <v>35.09</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>751.1900000000001</v>
+        <v>739.42</v>
       </c>
       <c r="Q5">
-        <v>727.47</v>
+        <v>727.5</v>
       </c>
       <c r="R5">
-        <v>728.4299999999999</v>
+        <v>729</v>
       </c>
       <c r="S5">
-        <v>748.5</v>
+        <v>748.27</v>
       </c>
       <c r="T5">
-        <v>-2.36</v>
+        <v>-3.18</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1335,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>49.4</v>
+        <v>47.23</v>
       </c>
       <c r="Z5">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
-        <v>4.92</v>
+        <v>4.78</v>
       </c>
       <c r="AB5">
-        <v>0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AC5">
-        <v>36.88</v>
+        <v>24.06</v>
       </c>
       <c r="AD5">
-        <v>54.51</v>
+        <v>37.04</v>
       </c>
       <c r="AE5">
-        <v>22.21</v>
+        <v>22.11</v>
       </c>
       <c r="AF5">
-        <v>59.68</v>
+        <v>41.81</v>
       </c>
       <c r="AG5">
-        <v>772.53</v>
+        <v>772.55</v>
       </c>
       <c r="AH5">
-        <v>682.41</v>
+        <v>682.4400000000001</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1343,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>29.81</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>504.7</v>
+        <v>512</v>
       </c>
       <c r="D6">
-        <v>-0.06</v>
+        <v>1.45</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1366,46 +1394,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-15.88</v>
+        <v>-14.67</v>
       </c>
       <c r="H6">
-        <v>15.08</v>
+        <v>16.75</v>
       </c>
       <c r="I6">
-        <v>-4.14</v>
+        <v>-4.26</v>
       </c>
       <c r="J6">
-        <v>-9.140000000000001</v>
+        <v>-6.59</v>
       </c>
       <c r="K6">
-        <v>-11.77</v>
+        <v>-11.04</v>
       </c>
       <c r="L6">
-        <v>-2.9</v>
+        <v>-2.28</v>
       </c>
       <c r="M6">
-        <v>10.71</v>
+        <v>10.19</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>520.28</v>
+        <v>515.72</v>
       </c>
       <c r="Q6">
-        <v>533.02</v>
+        <v>531.42</v>
       </c>
       <c r="R6">
-        <v>546.46</v>
+        <v>545.96</v>
       </c>
       <c r="S6">
-        <v>521.35</v>
+        <v>521.47</v>
       </c>
       <c r="T6">
-        <v>-3.19</v>
+        <v>-1.82</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,34 +1448,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>31.29</v>
+        <v>36.86</v>
       </c>
       <c r="Z6">
-        <v>-9.710000000000001</v>
+        <v>-10.07</v>
       </c>
       <c r="AA6">
-        <v>-7.23</v>
+        <v>-7.8</v>
       </c>
       <c r="AB6">
-        <v>-2.47</v>
+        <v>-2.27</v>
       </c>
       <c r="AC6">
-        <v>31.19</v>
+        <v>24.13</v>
       </c>
       <c r="AD6">
-        <v>54.78</v>
+        <v>36.2</v>
       </c>
       <c r="AE6">
-        <v>12.27</v>
+        <v>12.06</v>
       </c>
       <c r="AF6">
-        <v>0.71</v>
+        <v>-48.43</v>
       </c>
       <c r="AG6">
-        <v>558.66</v>
+        <v>558.16</v>
       </c>
       <c r="AH6">
-        <v>507.37</v>
+        <v>504.68</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1456,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.15</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>10935</v>
+        <v>11146</v>
       </c>
       <c r="D7">
-        <v>-0.29</v>
+        <v>1.93</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1479,46 +1507,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-50.67</v>
+        <v>-49.71</v>
       </c>
       <c r="H7">
-        <v>2.63</v>
+        <v>4.61</v>
       </c>
       <c r="I7">
-        <v>-4.63</v>
+        <v>-1.75</v>
       </c>
       <c r="J7">
-        <v>-7.91</v>
+        <v>-2.99</v>
       </c>
       <c r="K7">
-        <v>-14.22</v>
+        <v>-13.35</v>
       </c>
       <c r="L7">
-        <v>-41.38</v>
+        <v>-40.87</v>
       </c>
       <c r="M7">
-        <v>18.03</v>
+        <v>18.9</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>11227.8</v>
+        <v>11188.2</v>
       </c>
       <c r="Q7">
-        <v>11452.9</v>
+        <v>11443.75</v>
       </c>
       <c r="R7">
-        <v>11433.6</v>
+        <v>11430.24</v>
       </c>
       <c r="S7">
-        <v>14532.98</v>
+        <v>14487.56</v>
       </c>
       <c r="T7">
-        <v>-24.76</v>
+        <v>-23.07</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1561,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>38.51</v>
+        <v>43.64</v>
       </c>
       <c r="Z7">
-        <v>-120.27</v>
+        <v>-126.95</v>
       </c>
       <c r="AA7">
-        <v>-57.78</v>
+        <v>-71.62</v>
       </c>
       <c r="AB7">
-        <v>-62.49</v>
+        <v>-55.33</v>
       </c>
       <c r="AC7">
-        <v>6.32</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AD7">
-        <v>18.65</v>
+        <v>11.81</v>
       </c>
       <c r="AE7">
-        <v>405.1</v>
+        <v>409.45</v>
       </c>
       <c r="AF7">
-        <v>-59.07</v>
+        <v>-48.17</v>
       </c>
       <c r="AG7">
-        <v>11977.59</v>
+        <v>11983.7</v>
       </c>
       <c r="AH7">
-        <v>10928.21</v>
+        <v>10903.8</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1569,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>22.78</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>325.55</v>
+        <v>326.65</v>
       </c>
       <c r="D8">
-        <v>-0.09</v>
+        <v>0.34</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1592,46 +1620,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.3</v>
+        <v>-6.99</v>
       </c>
       <c r="H8">
-        <v>38.94</v>
+        <v>39.41</v>
       </c>
       <c r="I8">
-        <v>-1.94</v>
+        <v>-4.32</v>
       </c>
       <c r="J8">
-        <v>-2.94</v>
+        <v>-0.61</v>
       </c>
       <c r="K8">
-        <v>8.77</v>
+        <v>6.07</v>
       </c>
       <c r="L8">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="M8">
-        <v>28.1</v>
+        <v>28.22</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P8">
-        <v>335.68</v>
+        <v>332.73</v>
       </c>
       <c r="Q8">
-        <v>336.04</v>
+        <v>335.87</v>
       </c>
       <c r="R8">
-        <v>333.91</v>
+        <v>334.15</v>
       </c>
       <c r="S8">
-        <v>287.9</v>
+        <v>288.18</v>
       </c>
       <c r="T8">
-        <v>13.08</v>
+        <v>13.35</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>42.22</v>
+        <v>43.34</v>
       </c>
       <c r="Z8">
-        <v>-0.01</v>
+        <v>-0.62</v>
       </c>
       <c r="AA8">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="AB8">
-        <v>-1.34</v>
+        <v>-1.57</v>
       </c>
       <c r="AC8">
-        <v>27.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD8">
-        <v>52.78</v>
+        <v>27.76</v>
       </c>
       <c r="AE8">
-        <v>10.12</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AF8">
-        <v>17.84</v>
+        <v>-12.01</v>
       </c>
       <c r="AG8">
-        <v>348.26</v>
+        <v>348.52</v>
       </c>
       <c r="AH8">
-        <v>323.81</v>
+        <v>323.22</v>
       </c>
       <c r="AI8">
         <v>346.77</v>
@@ -1682,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>25.24</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1248.9</v>
+        <v>1253.4</v>
       </c>
       <c r="D9">
-        <v>1.6</v>
+        <v>0.36</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1705,46 +1733,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-6.87</v>
+        <v>-6.53</v>
       </c>
       <c r="H9">
-        <v>15.71</v>
+        <v>16.13</v>
       </c>
       <c r="I9">
-        <v>-3.73</v>
+        <v>-4.32</v>
       </c>
       <c r="J9">
-        <v>-2.26</v>
+        <v>-1.12</v>
       </c>
       <c r="K9">
-        <v>-2.98</v>
+        <v>-3.13</v>
       </c>
       <c r="L9">
-        <v>13.64</v>
+        <v>14.05</v>
       </c>
       <c r="M9">
-        <v>13.64</v>
+        <v>13.96</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O9">
         <v>67</v>
       </c>
       <c r="P9">
-        <v>1271.42</v>
+        <v>1260.1</v>
       </c>
       <c r="Q9">
-        <v>1302.82</v>
+        <v>1301.2</v>
       </c>
       <c r="R9">
-        <v>1279.6</v>
+        <v>1280.28</v>
       </c>
       <c r="S9">
-        <v>1230.21</v>
+        <v>1230.67</v>
       </c>
       <c r="T9">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1787,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>39.78</v>
+        <v>41.1</v>
       </c>
       <c r="Z9">
-        <v>-6.05</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="AA9">
-        <v>3.88</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>-9.94</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AC9">
-        <v>6.56</v>
+        <v>14.83</v>
       </c>
       <c r="AD9">
-        <v>7.3</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AE9">
-        <v>26.47</v>
+        <v>25.85</v>
       </c>
       <c r="AF9">
-        <v>10.57</v>
+        <v>-18.1</v>
       </c>
       <c r="AG9">
-        <v>1359.9</v>
+        <v>1362.03</v>
       </c>
       <c r="AH9">
-        <v>1245.75</v>
+        <v>1240.38</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1795,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>34.8</v>
+        <v>35.22</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.92</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="D10">
-        <v>0.16</v>
+        <v>-1.51</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1818,46 +1846,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.42</v>
+        <v>-11.78</v>
       </c>
       <c r="H10">
-        <v>127.05</v>
+        <v>123.61</v>
       </c>
       <c r="I10">
-        <v>-2.62</v>
+        <v>-3.79</v>
       </c>
       <c r="J10">
-        <v>-10.42</v>
+        <v>-7.14</v>
       </c>
       <c r="K10">
-        <v>57.87</v>
+        <v>56.3</v>
       </c>
       <c r="L10">
-        <v>11.11</v>
+        <v>10.66</v>
       </c>
       <c r="M10">
-        <v>-3.33</v>
+        <v>-3.38</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>83.75</v>
+        <v>83.11</v>
       </c>
       <c r="Q10">
-        <v>82.26000000000001</v>
+        <v>82.16</v>
       </c>
       <c r="R10">
-        <v>74.98</v>
+        <v>75.58</v>
       </c>
       <c r="S10">
-        <v>60.41</v>
+        <v>60.48</v>
       </c>
       <c r="T10">
-        <v>35.61</v>
+        <v>33.41</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1900,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>51.94</v>
+        <v>49.53</v>
       </c>
       <c r="Z10">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AA10">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="AB10">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="AC10">
-        <v>50.29</v>
+        <v>19.46</v>
       </c>
       <c r="AD10">
-        <v>68.44</v>
+        <v>46.72</v>
       </c>
       <c r="AE10">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="AF10">
-        <v>-19.33</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="AG10">
-        <v>86.81999999999999</v>
+        <v>86.78</v>
       </c>
       <c r="AH10">
-        <v>77.69</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1908,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>17.37</v>
+        <v>20.04</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1278 +2145,1295 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>11.53</v>
+      </c>
+      <c r="D7" s="6">
+        <v>12.27</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.59</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-7.91</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.94</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>8.57</v>
+      </c>
+      <c r="D16" s="6">
+        <v>7.44</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-8.57</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.58</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.93</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.07</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-7.51</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.14</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.26</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-4.63</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.75</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.94</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.62</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>23.69</v>
+      </c>
+      <c r="D25" s="6">
+        <v>20.76</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>40.15</v>
+      </c>
+      <c r="D26" s="6">
+        <v>41.32</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>6.02</v>
+      </c>
+      <c r="D27" s="6">
+        <v>8.92</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.87</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-2.9</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-2.28</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-41.38</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-40.87</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="D31" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>13.64</v>
+      </c>
+      <c r="D32" s="6">
+        <v>14.05</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>11.11</v>
+      </c>
+      <c r="D33" s="6">
+        <v>10.66</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="D34" s="6">
+        <v>5.07</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>8.81</v>
+      </c>
+      <c r="D35" s="6">
+        <v>10.28</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-2.89</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="D37" s="6">
+        <v>2.47</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-11.77</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-11.04</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-14.22</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-13.35</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>8.77</v>
+      </c>
+      <c r="D40" s="6">
+        <v>6.07</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-3.13</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>57.87</v>
+      </c>
+      <c r="D42" s="6">
+        <v>56.3</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-26.32</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-27.95</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-11.42</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-14.42</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-12.45</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-15.47</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-16.21</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-15.88</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-14.67</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-50.67</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-49.71</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-7.3</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-6.99</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-6.87</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-11.78</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>742.4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>726</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-16.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>281.25</v>
+      </c>
+      <c r="D53" s="6">
+        <v>291.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1103</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1128.4</v>
+      </c>
+      <c r="E54" s="7">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>730.85</v>
+      </c>
+      <c r="D55" s="6">
+        <v>724.45</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>504.7</v>
+      </c>
+      <c r="D56" s="6">
+        <v>512</v>
+      </c>
+      <c r="E56" s="7">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>10935</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11146</v>
+      </c>
+      <c r="E57" s="7">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>325.55</v>
+      </c>
+      <c r="D58" s="6">
+        <v>326.65</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1248.9</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1253.4</v>
+      </c>
+      <c r="E59" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>81.92</v>
+      </c>
+      <c r="D60" s="6">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45</v>
+      </c>
+      <c r="D61" s="6">
         <v>55</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="E61" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>66</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>66</v>
+      </c>
+      <c r="E63" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>15.97</v>
-      </c>
-      <c r="D7" s="5">
-        <v>11.53</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>68.63</v>
+      </c>
+      <c r="D64" s="6">
+        <v>63.14</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D8" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>42.29</v>
+      </c>
+      <c r="D65" s="6">
+        <v>48.88</v>
+      </c>
+      <c r="E65" s="7">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>42.65</v>
+      </c>
+      <c r="D66" s="6">
+        <v>49.89</v>
+      </c>
+      <c r="E66" s="7">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>49.4</v>
+      </c>
+      <c r="D67" s="6">
+        <v>47.23</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-9.82</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>31.29</v>
+      </c>
+      <c r="D68" s="6">
+        <v>36.86</v>
+      </c>
+      <c r="E68" s="7">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-7.64</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>38.51</v>
+      </c>
+      <c r="D69" s="6">
+        <v>43.64</v>
+      </c>
+      <c r="E69" s="7">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-3.92</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-2.94</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>42.22</v>
+      </c>
+      <c r="D70" s="6">
+        <v>43.34</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-3.21</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>39.78</v>
+      </c>
+      <c r="D71" s="6">
+        <v>41.1</v>
+      </c>
+      <c r="E71" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-10.5</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-10.42</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>51.94</v>
+      </c>
+      <c r="D72" s="6">
+        <v>49.53</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>5.55</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8.57</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>947.28</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-46.11</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-993.39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-6.64</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-8.57</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-26.96</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-47.99</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-21.03</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.61</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.93</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-41.95</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="E75" s="7">
+        <v>34.29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.8</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.07</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>59.68</v>
+      </c>
+      <c r="D76" s="6">
+        <v>41.81</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-17.87</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-4.72</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-48.43</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-49.14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-3.56</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-4.63</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-59.07</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-48.17</v>
+      </c>
+      <c r="E78" s="7">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>17.84</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-29.85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-5.59</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-3.73</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>10.57</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-18.1</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-28.67</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-2.51</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-2.62</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>26.15</v>
-      </c>
-      <c r="D25" s="5">
-        <v>23.69</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>44.45</v>
-      </c>
-      <c r="D26" s="5">
-        <v>40.15</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>5.33</v>
-      </c>
-      <c r="D27" s="5">
-        <v>6.02</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-6.92</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-2.37</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-2.9</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-43.18</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-41.38</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="D31" s="5">
-        <v>3.68</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>11.62</v>
-      </c>
-      <c r="D32" s="5">
-        <v>13.64</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>10.95</v>
-      </c>
-      <c r="D33" s="5">
-        <v>11.11</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="D34" s="5">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="E34" s="7">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>16.57</v>
-      </c>
-      <c r="D35" s="5">
-        <v>8.81</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-7.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-3.93</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-2.89</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>1.93</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-10.15</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-11.77</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-14.45</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-14.22</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>10.91</v>
-      </c>
-      <c r="D40" s="5">
-        <v>8.77</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-3.54</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-2.98</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>53.97</v>
-      </c>
-      <c r="D42" s="5">
-        <v>57.87</v>
-      </c>
-      <c r="E42" s="7">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-26.77</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-26.32</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-8.98</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-11.42</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-15.04</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-16.31</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-15.47</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-15.83</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-15.88</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-50.52</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-50.67</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-7.3</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-8.34</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-6.87</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-10.56</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-10.42</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>737.9</v>
-      </c>
-      <c r="D52" s="5">
-        <v>742.4</v>
-      </c>
-      <c r="E52" s="7">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>289</v>
-      </c>
-      <c r="D53" s="5">
-        <v>281.25</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-7.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1095</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1103</v>
-      </c>
-      <c r="E54" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>723.55</v>
-      </c>
-      <c r="D55" s="5">
-        <v>730.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>505</v>
-      </c>
-      <c r="D56" s="5">
-        <v>504.7</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>10967</v>
-      </c>
-      <c r="D57" s="5">
-        <v>10935</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>325.85</v>
-      </c>
-      <c r="D58" s="5">
-        <v>325.55</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1229.2</v>
-      </c>
-      <c r="D59" s="5">
-        <v>1248.9</v>
-      </c>
-      <c r="E59" s="7">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>81.79000000000001</v>
-      </c>
-      <c r="D60" s="5">
-        <v>81.92</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>99</v>
-      </c>
-      <c r="D61" s="5">
-        <v>88</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>88</v>
-      </c>
-      <c r="D62" s="5">
-        <v>99</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>67.92</v>
-      </c>
-      <c r="D63" s="5">
-        <v>68.63</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46.64</v>
-      </c>
-      <c r="D64" s="5">
-        <v>42.29</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>40.12</v>
-      </c>
-      <c r="D65" s="5">
-        <v>42.65</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46.81</v>
-      </c>
-      <c r="D66" s="5">
-        <v>49.4</v>
-      </c>
-      <c r="E66" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>31.4</v>
-      </c>
-      <c r="D67" s="5">
-        <v>31.29</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>39.01</v>
-      </c>
-      <c r="D68" s="5">
-        <v>38.51</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>42.43</v>
-      </c>
-      <c r="D69" s="5">
-        <v>42.22</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>33.75</v>
-      </c>
-      <c r="D70" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="E70" s="7">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>51.71</v>
-      </c>
-      <c r="D71" s="5">
-        <v>51.94</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="5">
-        <v>1288.16</v>
-      </c>
-      <c r="D72" s="5">
-        <v>947.28</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-340.88</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-7.01</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>5.7</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-41.95</v>
-      </c>
-      <c r="E74" s="6">
-        <v>-47.65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-35.32</v>
-      </c>
-      <c r="D75" s="5">
-        <v>59.68</v>
-      </c>
-      <c r="E75" s="7">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-54.06</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.71</v>
-      </c>
-      <c r="E76" s="7">
-        <v>54.77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>1194.32</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-59.07</v>
-      </c>
-      <c r="E77" s="6">
-        <v>-1253.39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>55.52</v>
-      </c>
-      <c r="D78" s="5">
-        <v>17.84</v>
-      </c>
-      <c r="E78" s="6">
-        <v>-37.68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-36.76</v>
-      </c>
-      <c r="D79" s="5">
-        <v>10.57</v>
-      </c>
-      <c r="E79" s="7">
-        <v>47.33</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-52.84</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C81" s="6">
         <v>-19.33</v>
       </c>
-      <c r="E80" s="7">
-        <v>33.51</v>
+      <c r="D81" s="6">
+        <v>-70.09999999999999</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-50.77</v>
       </c>
     </row>
   </sheetData>
@@ -3379,60 +3459,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>47.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10">
-        <v>45.2</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-1.7</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="11">
         <v>5.8</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3534,61 +3614,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3749</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3478</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.281</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2314</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1803</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1364</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.1071</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0333</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0573</v>
+      <c r="A2" s="14">
+        <v>0.3815999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3509</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2822</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2424</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.189</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1396</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1019</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0338</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0641</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,43 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-7.0% → -0.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-7.0%</t>
+  </si>
+  <si>
+    <t>-0.8%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.9 → 49.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>49.5</t>
+    <t>47.2 → 55.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>55.9</t>
+  </si>
+  <si>
+    <t>43.3 → 59.8</t>
+  </si>
+  <si>
+    <t>43.3</t>
+  </si>
+  <si>
+    <t>59.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +315,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +355,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,8 +441,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,8 +813,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -930,10 +954,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>726</v>
+        <v>718.45</v>
       </c>
       <c r="D2">
-        <v>-2.21</v>
+        <v>-1.04</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -942,46 +966,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-27.95</v>
+        <v>-28.7</v>
       </c>
       <c r="H2">
-        <v>97.70999999999999</v>
+        <v>95.66</v>
       </c>
       <c r="I2">
-        <v>7.44</v>
+        <v>6.08</v>
       </c>
       <c r="J2">
-        <v>12.27</v>
+        <v>12.55</v>
       </c>
       <c r="K2">
-        <v>5.07</v>
+        <v>4.59</v>
       </c>
       <c r="L2">
-        <v>20.76</v>
+        <v>19.73</v>
       </c>
       <c r="M2">
-        <v>-6.41</v>
+        <v>-5.87</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>710.98</v>
+        <v>719.21</v>
       </c>
       <c r="Q2">
-        <v>672.72</v>
+        <v>676.79</v>
       </c>
       <c r="R2">
-        <v>658.99</v>
+        <v>659.67</v>
       </c>
       <c r="S2">
-        <v>630.36</v>
+        <v>631.39</v>
       </c>
       <c r="T2">
-        <v>15.17</v>
+        <v>13.79</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1020,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>63.14</v>
+        <v>60.73</v>
       </c>
       <c r="Z2">
-        <v>19.41</v>
+        <v>19.75</v>
       </c>
       <c r="AA2">
-        <v>12.39</v>
+        <v>13.86</v>
       </c>
       <c r="AB2">
-        <v>7.02</v>
+        <v>5.89</v>
       </c>
       <c r="AC2">
-        <v>92.15000000000001</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="AD2">
-        <v>79.04000000000001</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="AE2">
-        <v>31.43</v>
+        <v>31.11</v>
       </c>
       <c r="AF2">
-        <v>-46.11</v>
+        <v>-71.52</v>
       </c>
       <c r="AG2">
-        <v>742.8099999999999</v>
+        <v>747.61</v>
       </c>
       <c r="AH2">
-        <v>602.63</v>
+        <v>605.98</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1032,7 +1056,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>57.87</v>
+        <v>58.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1067,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>291.2</v>
+        <v>289.5</v>
       </c>
       <c r="D3">
-        <v>3.54</v>
+        <v>-0.58</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1055,46 +1079,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-8.279999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="H3">
-        <v>90.04000000000001</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="I3">
-        <v>-6.58</v>
+        <v>-8.82</v>
       </c>
       <c r="J3">
-        <v>8.390000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="K3">
-        <v>10.28</v>
+        <v>10.97</v>
       </c>
       <c r="L3">
-        <v>41.32</v>
+        <v>38.1</v>
       </c>
       <c r="M3">
-        <v>38.16</v>
+        <v>39.9</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>298.18</v>
+        <v>292.58</v>
       </c>
       <c r="Q3">
-        <v>300.81</v>
+        <v>301.8</v>
       </c>
       <c r="R3">
-        <v>279.11</v>
+        <v>279.45</v>
       </c>
       <c r="S3">
-        <v>221.31</v>
+        <v>221.94</v>
       </c>
       <c r="T3">
-        <v>31.58</v>
+        <v>30.44</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1133,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.88</v>
+        <v>47.87</v>
       </c>
       <c r="Z3">
-        <v>5.53</v>
+        <v>4.36</v>
       </c>
       <c r="AA3">
-        <v>9.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AB3">
-        <v>-3.65</v>
+        <v>-3.86</v>
       </c>
       <c r="AC3">
-        <v>7.33</v>
+        <v>13.54</v>
       </c>
       <c r="AD3">
-        <v>19.88</v>
+        <v>10.95</v>
       </c>
       <c r="AE3">
-        <v>12.32</v>
+        <v>11.92</v>
       </c>
       <c r="AF3">
-        <v>-47.99</v>
+        <v>-40.18</v>
       </c>
       <c r="AG3">
-        <v>327.38</v>
+        <v>324.73</v>
       </c>
       <c r="AH3">
-        <v>274.23</v>
+        <v>278.86</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1145,7 +1169,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.88</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1180,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1128.4</v>
+        <v>1119.5</v>
       </c>
       <c r="D4">
-        <v>2.3</v>
+        <v>-0.79</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1168,46 +1192,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-12.45</v>
+        <v>-13.14</v>
       </c>
       <c r="H4">
-        <v>14.44</v>
+        <v>13.54</v>
       </c>
       <c r="I4">
-        <v>-1.58</v>
+        <v>-1.54</v>
       </c>
       <c r="J4">
-        <v>2.44</v>
+        <v>0.4</v>
       </c>
       <c r="K4">
-        <v>-0.31</v>
+        <v>-1.6</v>
       </c>
       <c r="L4">
-        <v>8.92</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>24.24</v>
+        <v>26.49</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>1116.78</v>
+        <v>1113.28</v>
       </c>
       <c r="Q4">
-        <v>1145.57</v>
+        <v>1145.6</v>
       </c>
       <c r="R4">
-        <v>1102.8</v>
+        <v>1104.59</v>
       </c>
       <c r="S4">
-        <v>1131.78</v>
+        <v>1132.13</v>
       </c>
       <c r="T4">
-        <v>-0.3</v>
+        <v>-1.12</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1246,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.89</v>
+        <v>47.63</v>
       </c>
       <c r="Z4">
-        <v>1.26</v>
+        <v>0.29</v>
       </c>
       <c r="AA4">
-        <v>8.83</v>
+        <v>7.12</v>
       </c>
       <c r="AB4">
-        <v>-7.56</v>
+        <v>-6.83</v>
       </c>
       <c r="AC4">
-        <v>12.64</v>
+        <v>20.34</v>
       </c>
       <c r="AD4">
-        <v>5.08</v>
+        <v>11.86</v>
       </c>
       <c r="AE4">
-        <v>31.05</v>
+        <v>30.31</v>
       </c>
       <c r="AF4">
-        <v>-7.66</v>
+        <v>34.42</v>
       </c>
       <c r="AG4">
-        <v>1196.26</v>
+        <v>1196.22</v>
       </c>
       <c r="AH4">
-        <v>1094.87</v>
+        <v>1094.97</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1258,7 +1282,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>36.04</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1293,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>724.45</v>
+        <v>750.95</v>
       </c>
       <c r="D5">
-        <v>-0.88</v>
+        <v>3.66</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1281,46 +1305,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.21</v>
+        <v>-13.14</v>
       </c>
       <c r="H5">
-        <v>9.449999999999999</v>
+        <v>13.45</v>
       </c>
       <c r="I5">
-        <v>-7.51</v>
+        <v>-1.47</v>
       </c>
       <c r="J5">
-        <v>-1.09</v>
+        <v>3.72</v>
       </c>
       <c r="K5">
-        <v>2.47</v>
+        <v>7.79</v>
       </c>
       <c r="L5">
-        <v>-2.11</v>
+        <v>0.22</v>
       </c>
       <c r="M5">
-        <v>35.09</v>
+        <v>37.6</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>739.42</v>
+        <v>737.1799999999999</v>
       </c>
       <c r="Q5">
-        <v>727.5</v>
+        <v>729.12</v>
       </c>
       <c r="R5">
-        <v>729</v>
+        <v>729.83</v>
       </c>
       <c r="S5">
-        <v>748.27</v>
+        <v>748.25</v>
       </c>
       <c r="T5">
-        <v>-3.18</v>
+        <v>0.36</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1332,37 +1356,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.23</v>
+        <v>55.89</v>
       </c>
       <c r="Z5">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="AA5">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="AB5">
-        <v>-0.58</v>
+        <v>0.22</v>
       </c>
       <c r="AC5">
-        <v>24.06</v>
+        <v>32.81</v>
       </c>
       <c r="AD5">
-        <v>37.04</v>
+        <v>31.25</v>
       </c>
       <c r="AE5">
-        <v>22.11</v>
+        <v>22.71</v>
       </c>
       <c r="AF5">
-        <v>41.81</v>
+        <v>184.99</v>
       </c>
       <c r="AG5">
-        <v>772.55</v>
+        <v>775.14</v>
       </c>
       <c r="AH5">
-        <v>682.4400000000001</v>
+        <v>683.11</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1371,7 +1395,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>26.04</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1406,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="D6">
-        <v>1.45</v>
+        <v>2.73</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1394,46 +1418,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-14.67</v>
+        <v>-12.33</v>
       </c>
       <c r="H6">
-        <v>16.75</v>
+        <v>19.94</v>
       </c>
       <c r="I6">
-        <v>-4.26</v>
+        <v>-0.84</v>
       </c>
       <c r="J6">
-        <v>-6.59</v>
+        <v>-3.3</v>
       </c>
       <c r="K6">
-        <v>-11.04</v>
+        <v>-7.74</v>
       </c>
       <c r="L6">
-        <v>-2.28</v>
+        <v>-0.79</v>
       </c>
       <c r="M6">
-        <v>10.19</v>
+        <v>10.3</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>515.72</v>
+        <v>514.83</v>
       </c>
       <c r="Q6">
-        <v>531.42</v>
+        <v>530.62</v>
       </c>
       <c r="R6">
-        <v>545.96</v>
+        <v>545.8099999999999</v>
       </c>
       <c r="S6">
-        <v>521.47</v>
+        <v>521.65</v>
       </c>
       <c r="T6">
-        <v>-1.82</v>
+        <v>0.83</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1445,37 +1469,37 @@
         <v>48</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>36.86</v>
+        <v>45.91</v>
       </c>
       <c r="Z6">
-        <v>-10.07</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="AA6">
-        <v>-7.8</v>
+        <v>-8.06</v>
       </c>
       <c r="AB6">
-        <v>-2.27</v>
+        <v>-1.05</v>
       </c>
       <c r="AC6">
-        <v>24.13</v>
+        <v>52.5</v>
       </c>
       <c r="AD6">
-        <v>36.2</v>
+        <v>35.94</v>
       </c>
       <c r="AE6">
-        <v>12.06</v>
+        <v>12.41</v>
       </c>
       <c r="AF6">
-        <v>-48.43</v>
+        <v>73.03</v>
       </c>
       <c r="AG6">
-        <v>558.16</v>
+        <v>556.98</v>
       </c>
       <c r="AH6">
-        <v>504.68</v>
+        <v>504.26</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1484,7 +1508,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.28</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1519,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11146</v>
+        <v>11282</v>
       </c>
       <c r="D7">
-        <v>1.93</v>
+        <v>1.22</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1507,46 +1531,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.71</v>
+        <v>-49.1</v>
       </c>
       <c r="H7">
-        <v>4.61</v>
+        <v>5.88</v>
       </c>
       <c r="I7">
-        <v>-1.75</v>
+        <v>-1.42</v>
       </c>
       <c r="J7">
-        <v>-2.99</v>
+        <v>-0.41</v>
       </c>
       <c r="K7">
-        <v>-13.35</v>
+        <v>-10.3</v>
       </c>
       <c r="L7">
-        <v>-40.87</v>
+        <v>-39.35</v>
       </c>
       <c r="M7">
-        <v>18.9</v>
+        <v>19.91</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>11188.2</v>
+        <v>11155.8</v>
       </c>
       <c r="Q7">
-        <v>11443.75</v>
+        <v>11434.6</v>
       </c>
       <c r="R7">
-        <v>11430.24</v>
+        <v>11433.38</v>
       </c>
       <c r="S7">
-        <v>14487.56</v>
+        <v>14438.35</v>
       </c>
       <c r="T7">
-        <v>-23.07</v>
+        <v>-21.86</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1585,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>43.64</v>
+        <v>46.73</v>
       </c>
       <c r="Z7">
-        <v>-126.95</v>
+        <v>-119.88</v>
       </c>
       <c r="AA7">
-        <v>-71.62</v>
+        <v>-81.27</v>
       </c>
       <c r="AB7">
-        <v>-55.33</v>
+        <v>-38.61</v>
       </c>
       <c r="AC7">
-        <v>9.039999999999999</v>
+        <v>23.51</v>
       </c>
       <c r="AD7">
-        <v>11.81</v>
+        <v>12.95</v>
       </c>
       <c r="AE7">
-        <v>409.45</v>
+        <v>421.13</v>
       </c>
       <c r="AF7">
-        <v>-48.17</v>
+        <v>-46.95</v>
       </c>
       <c r="AG7">
-        <v>11983.7</v>
+        <v>11979.21</v>
       </c>
       <c r="AH7">
-        <v>10903.8</v>
+        <v>10889.99</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1597,7 +1621,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>21.34</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1632,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>326.65</v>
+        <v>348.25</v>
       </c>
       <c r="D8">
-        <v>0.34</v>
+        <v>6.61</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1620,46 +1644,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-6.99</v>
+        <v>-0.84</v>
       </c>
       <c r="H8">
-        <v>39.41</v>
+        <v>48.63</v>
       </c>
       <c r="I8">
-        <v>-4.32</v>
+        <v>1.69</v>
       </c>
       <c r="J8">
-        <v>-0.61</v>
+        <v>5.56</v>
       </c>
       <c r="K8">
-        <v>6.07</v>
+        <v>13.01</v>
       </c>
       <c r="L8">
-        <v>3.62</v>
+        <v>10.59</v>
       </c>
       <c r="M8">
-        <v>28.22</v>
+        <v>30.99</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="P8">
-        <v>332.73</v>
+        <v>333.89</v>
       </c>
       <c r="Q8">
-        <v>335.87</v>
+        <v>336.79</v>
       </c>
       <c r="R8">
-        <v>334.15</v>
+        <v>334.64</v>
       </c>
       <c r="S8">
-        <v>288.18</v>
+        <v>288.57</v>
       </c>
       <c r="T8">
-        <v>13.35</v>
+        <v>20.68</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1698,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>43.34</v>
+        <v>59.75</v>
       </c>
       <c r="Z8">
-        <v>-0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AA8">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="AB8">
-        <v>-1.57</v>
+        <v>-0.25</v>
       </c>
       <c r="AC8">
-        <v>2.36</v>
+        <v>35.69</v>
       </c>
       <c r="AD8">
-        <v>27.76</v>
+        <v>21.83</v>
       </c>
       <c r="AE8">
-        <v>9.869999999999999</v>
+        <v>11.37</v>
       </c>
       <c r="AF8">
-        <v>-12.01</v>
+        <v>1021.34</v>
       </c>
       <c r="AG8">
-        <v>348.52</v>
+        <v>350.25</v>
       </c>
       <c r="AH8">
-        <v>323.22</v>
+        <v>323.34</v>
       </c>
       <c r="AI8">
-        <v>346.77</v>
+        <v>316.51</v>
       </c>
       <c r="AJ8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.72</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1745,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1253.4</v>
+        <v>1275.6</v>
       </c>
       <c r="D9">
-        <v>0.36</v>
+        <v>1.77</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1733,46 +1757,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-6.53</v>
+        <v>-4.88</v>
       </c>
       <c r="H9">
-        <v>16.13</v>
+        <v>18.19</v>
       </c>
       <c r="I9">
-        <v>-4.32</v>
+        <v>-2.18</v>
       </c>
       <c r="J9">
-        <v>-1.12</v>
+        <v>-0.79</v>
       </c>
       <c r="K9">
-        <v>-3.13</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L9">
-        <v>14.05</v>
+        <v>15.87</v>
       </c>
       <c r="M9">
-        <v>13.96</v>
+        <v>16.1</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1260.1</v>
+        <v>1254.42</v>
       </c>
       <c r="Q9">
-        <v>1301.2</v>
+        <v>1300</v>
       </c>
       <c r="R9">
-        <v>1280.28</v>
+        <v>1281.27</v>
       </c>
       <c r="S9">
-        <v>1230.67</v>
+        <v>1231.21</v>
       </c>
       <c r="T9">
-        <v>1.85</v>
+        <v>3.61</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1811,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>41.1</v>
+        <v>47.23</v>
       </c>
       <c r="Z9">
-        <v>-8.050000000000001</v>
+        <v>-7.76</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>-0.35</v>
       </c>
       <c r="AB9">
-        <v>-9.550000000000001</v>
+        <v>-7.4</v>
       </c>
       <c r="AC9">
-        <v>14.83</v>
+        <v>33.14</v>
       </c>
       <c r="AD9">
-        <v>8.390000000000001</v>
+        <v>18.18</v>
       </c>
       <c r="AE9">
-        <v>25.85</v>
+        <v>25.81</v>
       </c>
       <c r="AF9">
-        <v>-18.1</v>
+        <v>41.5</v>
       </c>
       <c r="AG9">
-        <v>1362.03</v>
+        <v>1361.89</v>
       </c>
       <c r="AH9">
-        <v>1240.38</v>
+        <v>1238.11</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1823,7 +1847,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>35.22</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1858,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.68000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D10">
-        <v>-1.51</v>
+        <v>0.27</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1846,46 +1870,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.78</v>
+        <v>-11.54</v>
       </c>
       <c r="H10">
-        <v>123.61</v>
+        <v>124.22</v>
       </c>
       <c r="I10">
-        <v>-3.79</v>
+        <v>-5.31</v>
       </c>
       <c r="J10">
-        <v>-7.14</v>
+        <v>-1.99</v>
       </c>
       <c r="K10">
-        <v>56.3</v>
+        <v>49.23</v>
       </c>
       <c r="L10">
-        <v>10.66</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M10">
-        <v>-3.38</v>
+        <v>-2.9</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>83.11</v>
+        <v>82.2</v>
       </c>
       <c r="Q10">
-        <v>82.16</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="R10">
-        <v>75.58</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="S10">
-        <v>60.48</v>
+        <v>60.55</v>
       </c>
       <c r="T10">
-        <v>33.41</v>
+        <v>33.61</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1924,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.53</v>
+        <v>49.97</v>
       </c>
       <c r="Z10">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AA10">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>-0.72</v>
+        <v>-0.78</v>
       </c>
       <c r="AC10">
-        <v>19.46</v>
+        <v>14.2</v>
       </c>
       <c r="AD10">
-        <v>46.72</v>
+        <v>27.98</v>
       </c>
       <c r="AE10">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="AF10">
-        <v>-70.09999999999999</v>
+        <v>-71.69</v>
       </c>
       <c r="AG10">
-        <v>86.78</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AH10">
-        <v>77.54000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1936,7 +1960,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.04</v>
+        <v>22.36</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2141,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,987 +2159,993 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>11.53</v>
-      </c>
-      <c r="D7" s="6">
-        <v>12.27</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5.3</v>
-      </c>
-      <c r="D8" s="6">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3.09</v>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>1.05</v>
+        <v>12.27</v>
       </c>
       <c r="D9" s="6">
-        <v>2.44</v>
+        <v>12.55</v>
       </c>
       <c r="E9" s="7">
-        <v>1.39</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-0.95</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.09</v>
+        <v>7.74</v>
       </c>
       <c r="E10" s="8">
-        <v>-0.14</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.140000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.59</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.55</v>
+        <v>0.4</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.91</v>
+        <v>-1.09</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.99</v>
+        <v>3.72</v>
       </c>
       <c r="E12" s="7">
-        <v>4.92</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.94</v>
+        <v>-6.59</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.61</v>
+        <v>-3.3</v>
       </c>
       <c r="E13" s="7">
-        <v>2.33</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.26</v>
+        <v>-2.99</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.12</v>
+        <v>-0.41</v>
       </c>
       <c r="E14" s="7">
-        <v>1.14</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-10.42</v>
+        <v>-0.61</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.14</v>
+        <v>5.56</v>
       </c>
       <c r="E15" s="7">
-        <v>3.28</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>8.57</v>
+        <v>-1.12</v>
       </c>
       <c r="D16" s="6">
-        <v>7.44</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.13</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.57</v>
+        <v>-7.14</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.58</v>
+        <v>-1.99</v>
       </c>
       <c r="E17" s="7">
-        <v>1.99</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.93</v>
+        <v>7.44</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.35</v>
+        <v>6.08</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.07</v>
+        <v>-6.58</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.51</v>
+        <v>-8.82</v>
       </c>
       <c r="E19" s="8">
-        <v>-6.44</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.14</v>
+        <v>-1.58</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.26</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.12</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.63</v>
+        <v>-7.51</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.75</v>
+        <v>-1.47</v>
       </c>
       <c r="E21" s="7">
-        <v>2.88</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.94</v>
+        <v>-4.26</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.38</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.42</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.73</v>
+        <v>-1.75</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.59</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.62</v>
+        <v>-4.32</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.17</v>
+        <v>1.69</v>
+      </c>
+      <c r="E24" s="7">
+        <v>6.01</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>23.69</v>
+        <v>-4.32</v>
       </c>
       <c r="D25" s="6">
-        <v>20.76</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.93</v>
+        <v>-2.18</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>40.15</v>
+        <v>-3.79</v>
       </c>
       <c r="D26" s="6">
-        <v>41.32</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.17</v>
+        <v>-5.31</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>6.02</v>
+        <v>20.76</v>
       </c>
       <c r="D27" s="6">
-        <v>8.92</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.9</v>
+        <v>19.73</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.87</v>
+        <v>41.32</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.76</v>
+        <v>38.1</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.9</v>
+        <v>8.92</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.28</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.62</v>
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-41.38</v>
+        <v>-2.11</v>
       </c>
       <c r="D30" s="6">
-        <v>-40.87</v>
+        <v>0.22</v>
       </c>
       <c r="E30" s="7">
-        <v>0.51</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>3.68</v>
+        <v>-2.28</v>
       </c>
       <c r="D31" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.06</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>13.64</v>
+        <v>-40.87</v>
       </c>
       <c r="D32" s="6">
-        <v>14.05</v>
+        <v>-39.35</v>
       </c>
       <c r="E32" s="7">
-        <v>0.41</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>11.11</v>
+        <v>3.62</v>
       </c>
       <c r="D33" s="6">
-        <v>10.66</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.45</v>
+        <v>10.59</v>
+      </c>
+      <c r="E33" s="7">
+        <v>6.97</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>8.130000000000001</v>
+        <v>14.05</v>
       </c>
       <c r="D34" s="6">
-        <v>5.07</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.06</v>
+        <v>15.87</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.82</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>8.81</v>
+        <v>10.66</v>
       </c>
       <c r="D35" s="6">
-        <v>10.28</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.47</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.89</v>
+        <v>5.07</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.58</v>
+        <v>4.59</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>0.41</v>
+        <v>10.28</v>
       </c>
       <c r="D37" s="6">
-        <v>2.47</v>
+        <v>10.97</v>
       </c>
       <c r="E37" s="7">
-        <v>2.06</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-11.77</v>
+        <v>-0.31</v>
       </c>
       <c r="D38" s="6">
-        <v>-11.04</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.73</v>
+        <v>-1.6</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-14.22</v>
+        <v>2.47</v>
       </c>
       <c r="D39" s="6">
-        <v>-13.35</v>
+        <v>7.79</v>
       </c>
       <c r="E39" s="7">
-        <v>0.87</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>8.77</v>
+        <v>-11.04</v>
       </c>
       <c r="D40" s="6">
-        <v>6.07</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.7</v>
+        <v>-7.74</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.3</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-2.98</v>
+        <v>-13.35</v>
       </c>
       <c r="D41" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.15</v>
+        <v>-10.3</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>57.87</v>
+        <v>6.07</v>
       </c>
       <c r="D42" s="6">
-        <v>56.3</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.57</v>
+        <v>13.01</v>
+      </c>
+      <c r="E42" s="7">
+        <v>6.94</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-26.32</v>
+        <v>-3.13</v>
       </c>
       <c r="D43" s="6">
-        <v>-27.95</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.63</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.42</v>
+        <v>56.3</v>
       </c>
       <c r="D44" s="6">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.14</v>
+        <v>49.23</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-7.07</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-14.42</v>
+        <v>-27.95</v>
       </c>
       <c r="D45" s="6">
-        <v>-12.45</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.97</v>
+        <v>-28.7</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-15.47</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D46" s="6">
-        <v>-16.21</v>
+        <v>-8.82</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.74</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-15.88</v>
+        <v>-12.45</v>
       </c>
       <c r="D47" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.21</v>
+        <v>-13.14</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-50.67</v>
+        <v>-16.21</v>
       </c>
       <c r="D48" s="6">
-        <v>-49.71</v>
+        <v>-13.14</v>
       </c>
       <c r="E48" s="7">
-        <v>0.96</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-7.3</v>
+        <v>-14.67</v>
       </c>
       <c r="D49" s="6">
-        <v>-6.99</v>
+        <v>-12.33</v>
       </c>
       <c r="E49" s="7">
-        <v>0.31</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-6.87</v>
+        <v>-49.71</v>
       </c>
       <c r="D50" s="6">
-        <v>-6.53</v>
+        <v>-49.1</v>
       </c>
       <c r="E50" s="7">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-10.42</v>
+        <v>-6.99</v>
       </c>
       <c r="D51" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.36</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E51" s="7">
+        <v>6.15</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>742.4</v>
+        <v>-6.53</v>
       </c>
       <c r="D52" s="6">
-        <v>726</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-16.4</v>
+        <v>-4.88</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.65</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6">
-        <v>281.25</v>
+        <v>-11.78</v>
       </c>
       <c r="D53" s="6">
-        <v>291.2</v>
+        <v>-11.54</v>
       </c>
       <c r="E53" s="7">
-        <v>9.949999999999999</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1103</v>
+        <v>726</v>
       </c>
       <c r="D54" s="6">
-        <v>1128.4</v>
-      </c>
-      <c r="E54" s="7">
-        <v>25.4</v>
+        <v>718.45</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-7.55</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>730.85</v>
+        <v>291.2</v>
       </c>
       <c r="D55" s="6">
-        <v>724.45</v>
+        <v>289.5</v>
       </c>
       <c r="E55" s="8">
-        <v>-6.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>504.7</v>
+        <v>1128.4</v>
       </c>
       <c r="D56" s="6">
-        <v>512</v>
-      </c>
-      <c r="E56" s="7">
-        <v>7.3</v>
+        <v>1119.5</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-8.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>10935</v>
+        <v>724.45</v>
       </c>
       <c r="D57" s="6">
-        <v>11146</v>
+        <v>750.95</v>
       </c>
       <c r="E57" s="7">
-        <v>211</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>325.55</v>
+        <v>512</v>
       </c>
       <c r="D58" s="6">
-        <v>326.65</v>
+        <v>526</v>
       </c>
       <c r="E58" s="7">
-        <v>1.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1248.9</v>
+        <v>11146</v>
       </c>
       <c r="D59" s="6">
-        <v>1253.4</v>
+        <v>11282</v>
       </c>
       <c r="E59" s="7">
-        <v>4.5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>81.92</v>
+        <v>326.65</v>
       </c>
       <c r="D60" s="6">
-        <v>80.68000000000001</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.24</v>
+        <v>348.25</v>
+      </c>
+      <c r="E60" s="7">
+        <v>21.6</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>45</v>
+        <v>1253.4</v>
       </c>
       <c r="D61" s="6">
-        <v>55</v>
+        <v>1275.6</v>
       </c>
       <c r="E61" s="7">
-        <v>10</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6">
-        <v>66</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-21</v>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
@@ -3124,322 +3154,373 @@
         <v>55</v>
       </c>
       <c r="D63" s="6">
-        <v>66</v>
-      </c>
-      <c r="E63" s="7">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-21</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>68.63</v>
+        <v>34</v>
       </c>
       <c r="D64" s="6">
-        <v>63.14</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-5.49</v>
+        <v>45</v>
+      </c>
+      <c r="E64" s="7">
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="6">
-        <v>42.29</v>
+        <v>45</v>
       </c>
       <c r="D65" s="6">
-        <v>48.88</v>
+        <v>66</v>
       </c>
       <c r="E65" s="7">
-        <v>6.59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="6">
-        <v>42.65</v>
+        <v>66</v>
       </c>
       <c r="D66" s="6">
-        <v>49.89</v>
-      </c>
-      <c r="E66" s="7">
-        <v>7.24</v>
+        <v>55</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>49.4</v>
+        <v>63.14</v>
       </c>
       <c r="D67" s="6">
-        <v>47.23</v>
+        <v>60.73</v>
       </c>
       <c r="E67" s="8">
-        <v>-2.17</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>31.29</v>
+        <v>48.88</v>
       </c>
       <c r="D68" s="6">
-        <v>36.86</v>
-      </c>
-      <c r="E68" s="7">
-        <v>5.57</v>
+        <v>47.87</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>38.51</v>
+        <v>49.89</v>
       </c>
       <c r="D69" s="6">
-        <v>43.64</v>
-      </c>
-      <c r="E69" s="7">
-        <v>5.13</v>
+        <v>47.63</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>42.22</v>
+        <v>47.23</v>
       </c>
       <c r="D70" s="6">
-        <v>43.34</v>
+        <v>55.89</v>
       </c>
       <c r="E70" s="7">
-        <v>1.12</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>39.78</v>
+        <v>36.86</v>
       </c>
       <c r="D71" s="6">
-        <v>41.1</v>
+        <v>45.91</v>
       </c>
       <c r="E71" s="7">
-        <v>1.32</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>51.94</v>
+        <v>43.64</v>
       </c>
       <c r="D72" s="6">
-        <v>49.53</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.41</v>
+        <v>46.73</v>
+      </c>
+      <c r="E72" s="7">
+        <v>3.09</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>947.28</v>
+        <v>43.34</v>
       </c>
       <c r="D73" s="6">
-        <v>-46.11</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-993.39</v>
+        <v>59.75</v>
+      </c>
+      <c r="E73" s="7">
+        <v>16.41</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="6">
-        <v>-26.96</v>
+        <v>41.1</v>
       </c>
       <c r="D74" s="6">
-        <v>-47.99</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-21.03</v>
+        <v>47.23</v>
+      </c>
+      <c r="E74" s="7">
+        <v>6.13</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="6">
-        <v>-41.95</v>
+        <v>49.53</v>
       </c>
       <c r="D75" s="6">
-        <v>-7.66</v>
+        <v>49.97</v>
       </c>
       <c r="E75" s="7">
-        <v>34.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>59.68</v>
+        <v>-46.11</v>
       </c>
       <c r="D76" s="6">
-        <v>41.81</v>
+        <v>-71.52</v>
       </c>
       <c r="E76" s="8">
-        <v>-17.87</v>
+        <v>-25.41</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>0.71</v>
+        <v>-47.99</v>
       </c>
       <c r="D77" s="6">
-        <v>-48.43</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-49.14</v>
+        <v>-40.18</v>
+      </c>
+      <c r="E77" s="7">
+        <v>7.81</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-59.07</v>
+        <v>-7.66</v>
       </c>
       <c r="D78" s="6">
-        <v>-48.17</v>
+        <v>34.42</v>
       </c>
       <c r="E78" s="7">
-        <v>10.9</v>
+        <v>42.08</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>17.84</v>
+        <v>41.81</v>
       </c>
       <c r="D79" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-29.85</v>
+        <v>184.99</v>
+      </c>
+      <c r="E79" s="7">
+        <v>143.18</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>10.57</v>
+        <v>-48.43</v>
       </c>
       <c r="D80" s="6">
-        <v>-18.1</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-28.67</v>
+        <v>73.03</v>
+      </c>
+      <c r="E80" s="7">
+        <v>121.46</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-19.33</v>
+        <v>-48.17</v>
       </c>
       <c r="D81" s="6">
+        <v>-46.95</v>
+      </c>
+      <c r="E81" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="D82" s="6">
+        <v>1021.34</v>
+      </c>
+      <c r="E82" s="7">
+        <v>1033.35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="6">
+        <v>-18.1</v>
+      </c>
+      <c r="D83" s="6">
+        <v>41.5</v>
+      </c>
+      <c r="E83" s="7">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6">
         <v>-70.09999999999999</v>
       </c>
-      <c r="E81" s="8">
-        <v>-50.77</v>
+      <c r="D84" s="6">
+        <v>-71.69</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-1.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,28 +3544,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3492,22 +3573,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>56.16</v>
+        <v>64.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>47.1</v>
+        <v>51.3</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="G2" s="11">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3644,31 +3725,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3815999999999999</v>
+        <v>0.399</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3509</v>
+        <v>0.376</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2822</v>
+        <v>0.3099</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2424</v>
+        <v>0.2649</v>
       </c>
       <c r="E2" s="14">
-        <v>0.189</v>
+        <v>0.1991</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1396</v>
+        <v>0.161</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1019</v>
+        <v>0.103</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0338</v>
+        <v>-0.029</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0641</v>
+        <v>-0.0587</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-7.0% → -0.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-7.0%</t>
-  </si>
-  <si>
-    <t>-0.8%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.2 → 55.9</t>
+    <t>47.9 → 50.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>47.2</t>
-  </si>
-  <si>
-    <t>55.9</t>
-  </si>
-  <si>
-    <t>43.3 → 59.8</t>
-  </si>
-  <si>
-    <t>43.3</t>
-  </si>
-  <si>
-    <t>59.8</t>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>47.6 → 50.6</t>
+  </si>
+  <si>
+    <t>47.6</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -431,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -439,6 +436,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -954,10 +952,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>718.45</v>
+        <v>741.5</v>
       </c>
       <c r="D2">
-        <v>-1.04</v>
+        <v>3.21</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -966,46 +964,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-28.7</v>
+        <v>-26.41</v>
       </c>
       <c r="H2">
-        <v>95.66</v>
+        <v>101.93</v>
       </c>
       <c r="I2">
-        <v>6.08</v>
+        <v>10.46</v>
       </c>
       <c r="J2">
-        <v>12.55</v>
+        <v>16.41</v>
       </c>
       <c r="K2">
-        <v>4.59</v>
+        <v>10.74</v>
       </c>
       <c r="L2">
-        <v>19.73</v>
+        <v>24.43</v>
       </c>
       <c r="M2">
-        <v>-5.87</v>
+        <v>-5.35</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>719.21</v>
+        <v>733.25</v>
       </c>
       <c r="Q2">
-        <v>676.79</v>
+        <v>681.99</v>
       </c>
       <c r="R2">
-        <v>659.67</v>
+        <v>660.14</v>
       </c>
       <c r="S2">
-        <v>631.39</v>
+        <v>632.52</v>
       </c>
       <c r="T2">
-        <v>13.79</v>
+        <v>17.23</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1020,34 +1018,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>60.73</v>
+        <v>65.11</v>
       </c>
       <c r="Z2">
-        <v>19.75</v>
+        <v>21.63</v>
       </c>
       <c r="AA2">
-        <v>13.86</v>
+        <v>15.41</v>
       </c>
       <c r="AB2">
-        <v>5.89</v>
+        <v>6.21</v>
       </c>
       <c r="AC2">
-        <v>80.84999999999999</v>
+        <v>73.14</v>
       </c>
       <c r="AD2">
-        <v>84.48999999999999</v>
+        <v>82.05</v>
       </c>
       <c r="AE2">
-        <v>31.11</v>
+        <v>32.36</v>
       </c>
       <c r="AF2">
-        <v>-71.52</v>
+        <v>-24.87</v>
       </c>
       <c r="AG2">
-        <v>747.61</v>
+        <v>755.87</v>
       </c>
       <c r="AH2">
-        <v>605.98</v>
+        <v>608.11</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1056,7 +1054,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>58.01</v>
+        <v>59.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1067,10 +1065,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>289.5</v>
+        <v>293.05</v>
       </c>
       <c r="D3">
-        <v>-0.58</v>
+        <v>1.23</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1079,46 +1077,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-8.82</v>
+        <v>-7.7</v>
       </c>
       <c r="H3">
-        <v>88.93000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="I3">
-        <v>-8.82</v>
+        <v>-6.06</v>
       </c>
       <c r="J3">
-        <v>7.74</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K3">
-        <v>10.97</v>
+        <v>14.6</v>
       </c>
       <c r="L3">
-        <v>38.1</v>
+        <v>40.8</v>
       </c>
       <c r="M3">
-        <v>39.9</v>
+        <v>40.47</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P3">
-        <v>292.58</v>
+        <v>288.8</v>
       </c>
       <c r="Q3">
-        <v>301.8</v>
+        <v>301.87</v>
       </c>
       <c r="R3">
-        <v>279.45</v>
+        <v>279.8</v>
       </c>
       <c r="S3">
-        <v>221.94</v>
+        <v>222.59</v>
       </c>
       <c r="T3">
-        <v>30.44</v>
+        <v>31.66</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1133,34 +1131,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>47.87</v>
+        <v>50.18</v>
       </c>
       <c r="Z3">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="AA3">
-        <v>8.210000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AB3">
-        <v>-3.86</v>
+        <v>-3.63</v>
       </c>
       <c r="AC3">
-        <v>13.54</v>
+        <v>22.32</v>
       </c>
       <c r="AD3">
-        <v>10.95</v>
+        <v>14.4</v>
       </c>
       <c r="AE3">
-        <v>11.92</v>
+        <v>11.53</v>
       </c>
       <c r="AF3">
-        <v>-40.18</v>
+        <v>-68.94</v>
       </c>
       <c r="AG3">
-        <v>324.73</v>
+        <v>324.68</v>
       </c>
       <c r="AH3">
-        <v>278.86</v>
+        <v>279.05</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1169,7 +1167,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.57</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1180,10 +1178,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1119.5</v>
+        <v>1130.6</v>
       </c>
       <c r="D4">
-        <v>-0.79</v>
+        <v>0.99</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1192,46 +1190,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-13.14</v>
+        <v>-12.27</v>
       </c>
       <c r="H4">
-        <v>13.54</v>
+        <v>14.67</v>
       </c>
       <c r="I4">
-        <v>-1.54</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
-        <v>0.4</v>
+        <v>1.05</v>
       </c>
       <c r="K4">
-        <v>-1.6</v>
+        <v>-0.12</v>
       </c>
       <c r="L4">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="M4">
-        <v>26.49</v>
+        <v>25.96</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1113.28</v>
+        <v>1115.3</v>
       </c>
       <c r="Q4">
-        <v>1145.6</v>
+        <v>1145.74</v>
       </c>
       <c r="R4">
-        <v>1104.59</v>
+        <v>1106.18</v>
       </c>
       <c r="S4">
-        <v>1132.13</v>
+        <v>1132.64</v>
       </c>
       <c r="T4">
-        <v>-1.12</v>
+        <v>-0.18</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1246,34 +1244,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.63</v>
+        <v>50.64</v>
       </c>
       <c r="Z4">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="AA4">
-        <v>7.12</v>
+        <v>5.78</v>
       </c>
       <c r="AB4">
-        <v>-6.83</v>
+        <v>-5.36</v>
       </c>
       <c r="AC4">
-        <v>20.34</v>
+        <v>35.56</v>
       </c>
       <c r="AD4">
-        <v>11.86</v>
+        <v>22.85</v>
       </c>
       <c r="AE4">
-        <v>30.31</v>
+        <v>29.86</v>
       </c>
       <c r="AF4">
-        <v>34.42</v>
+        <v>-9.44</v>
       </c>
       <c r="AG4">
-        <v>1196.22</v>
+        <v>1196.17</v>
       </c>
       <c r="AH4">
-        <v>1094.97</v>
+        <v>1095.3</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1282,7 +1280,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>34.58</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,10 +1291,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>750.95</v>
+        <v>751.45</v>
       </c>
       <c r="D5">
-        <v>3.66</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1305,49 +1303,49 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.14</v>
+        <v>-13.08</v>
       </c>
       <c r="H5">
-        <v>13.45</v>
+        <v>13.53</v>
       </c>
       <c r="I5">
-        <v>-1.47</v>
+        <v>-0.61</v>
       </c>
       <c r="J5">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>7.79</v>
+        <v>6.02</v>
       </c>
       <c r="L5">
-        <v>0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="M5">
-        <v>37.6</v>
+        <v>37.09</v>
       </c>
       <c r="N5">
         <v>45</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>737.1799999999999</v>
+        <v>736.25</v>
       </c>
       <c r="Q5">
-        <v>729.12</v>
+        <v>731.63</v>
       </c>
       <c r="R5">
-        <v>729.83</v>
+        <v>730.53</v>
       </c>
       <c r="S5">
-        <v>748.25</v>
+        <v>748.21</v>
       </c>
       <c r="T5">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="U5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V5" t="s">
         <v>48</v>
@@ -1356,37 +1354,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>55.89</v>
+        <v>56.04</v>
       </c>
       <c r="Z5">
-        <v>5.05</v>
+        <v>5.7</v>
       </c>
       <c r="AA5">
-        <v>4.83</v>
+        <v>5.01</v>
       </c>
       <c r="AB5">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="AC5">
-        <v>32.81</v>
+        <v>34.55</v>
       </c>
       <c r="AD5">
-        <v>31.25</v>
+        <v>30.47</v>
       </c>
       <c r="AE5">
-        <v>22.71</v>
+        <v>22.15</v>
       </c>
       <c r="AF5">
-        <v>184.99</v>
+        <v>-1.84</v>
       </c>
       <c r="AG5">
-        <v>775.14</v>
+        <v>776.72</v>
       </c>
       <c r="AH5">
-        <v>683.11</v>
+        <v>686.53</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1395,7 +1393,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.79</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1406,10 +1404,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="D6">
-        <v>2.73</v>
+        <v>-1.71</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1418,25 +1416,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-12.33</v>
+        <v>-13.83</v>
       </c>
       <c r="H6">
-        <v>19.94</v>
+        <v>17.89</v>
       </c>
       <c r="I6">
-        <v>-0.84</v>
+        <v>-1.8</v>
       </c>
       <c r="J6">
-        <v>-3.3</v>
+        <v>-4.61</v>
       </c>
       <c r="K6">
-        <v>-7.74</v>
+        <v>-11.18</v>
       </c>
       <c r="L6">
-        <v>-0.79</v>
+        <v>-3.94</v>
       </c>
       <c r="M6">
-        <v>10.3</v>
+        <v>9.43</v>
       </c>
       <c r="N6">
         <v>23</v>
@@ -1445,19 +1443,19 @@
         <v>49</v>
       </c>
       <c r="P6">
-        <v>514.83</v>
+        <v>512.9400000000001</v>
       </c>
       <c r="Q6">
-        <v>530.62</v>
+        <v>529.22</v>
       </c>
       <c r="R6">
-        <v>545.8099999999999</v>
+        <v>545.08</v>
       </c>
       <c r="S6">
-        <v>521.65</v>
+        <v>521.8200000000001</v>
       </c>
       <c r="T6">
-        <v>0.83</v>
+        <v>-0.92</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1469,37 +1467,37 @@
         <v>48</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.91</v>
+        <v>41.76</v>
       </c>
       <c r="Z6">
-        <v>-9.109999999999999</v>
+        <v>-8.98</v>
       </c>
       <c r="AA6">
-        <v>-8.06</v>
+        <v>-8.25</v>
       </c>
       <c r="AB6">
-        <v>-1.05</v>
+        <v>-0.73</v>
       </c>
       <c r="AC6">
-        <v>52.5</v>
+        <v>72.98</v>
       </c>
       <c r="AD6">
-        <v>35.94</v>
+        <v>49.87</v>
       </c>
       <c r="AE6">
-        <v>12.41</v>
+        <v>12.34</v>
       </c>
       <c r="AF6">
-        <v>73.03</v>
+        <v>-19.26</v>
       </c>
       <c r="AG6">
-        <v>556.98</v>
+        <v>555.34</v>
       </c>
       <c r="AH6">
-        <v>504.26</v>
+        <v>503.1</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1508,7 +1506,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.24</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1519,10 +1517,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11282</v>
+        <v>11205</v>
       </c>
       <c r="D7">
-        <v>1.22</v>
+        <v>-0.68</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1531,25 +1529,25 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.1</v>
+        <v>-49.45</v>
       </c>
       <c r="H7">
-        <v>5.88</v>
+        <v>5.16</v>
       </c>
       <c r="I7">
-        <v>-1.42</v>
+        <v>-2.13</v>
       </c>
       <c r="J7">
-        <v>-0.41</v>
+        <v>-2.27</v>
       </c>
       <c r="K7">
-        <v>-10.3</v>
+        <v>-11.09</v>
       </c>
       <c r="L7">
-        <v>-39.35</v>
+        <v>-39.55</v>
       </c>
       <c r="M7">
-        <v>19.91</v>
+        <v>18.56</v>
       </c>
       <c r="N7">
         <v>12</v>
@@ -1558,22 +1556,22 @@
         <v>17</v>
       </c>
       <c r="P7">
-        <v>11155.8</v>
+        <v>11107</v>
       </c>
       <c r="Q7">
-        <v>11434.6</v>
+        <v>11430.4</v>
       </c>
       <c r="R7">
-        <v>11433.38</v>
+        <v>11432.52</v>
       </c>
       <c r="S7">
-        <v>14438.35</v>
+        <v>14383.55</v>
       </c>
       <c r="T7">
-        <v>-21.86</v>
+        <v>-22.1</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
         <v>48</v>
@@ -1582,37 +1580,37 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>46.73</v>
+        <v>45.22</v>
       </c>
       <c r="Z7">
-        <v>-119.88</v>
+        <v>-119.12</v>
       </c>
       <c r="AA7">
-        <v>-81.27</v>
+        <v>-88.84</v>
       </c>
       <c r="AB7">
-        <v>-38.61</v>
+        <v>-30.28</v>
       </c>
       <c r="AC7">
-        <v>23.51</v>
+        <v>40.8</v>
       </c>
       <c r="AD7">
-        <v>12.95</v>
+        <v>24.45</v>
       </c>
       <c r="AE7">
-        <v>421.13</v>
+        <v>404.26</v>
       </c>
       <c r="AF7">
-        <v>-46.95</v>
+        <v>-85.13</v>
       </c>
       <c r="AG7">
-        <v>11979.21</v>
+        <v>11981</v>
       </c>
       <c r="AH7">
-        <v>10889.99</v>
+        <v>10879.8</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1621,7 +1619,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>19.99</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1632,10 +1630,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>348.25</v>
+        <v>349.6</v>
       </c>
       <c r="D8">
-        <v>6.61</v>
+        <v>0.39</v>
       </c>
       <c r="E8">
         <v>351.2</v>
@@ -1644,46 +1642,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-0.84</v>
+        <v>-0.46</v>
       </c>
       <c r="H8">
-        <v>48.63</v>
+        <v>49.2</v>
       </c>
       <c r="I8">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="J8">
-        <v>5.56</v>
+        <v>5.99</v>
       </c>
       <c r="K8">
-        <v>13.01</v>
+        <v>13.86</v>
       </c>
       <c r="L8">
-        <v>10.59</v>
+        <v>7.17</v>
       </c>
       <c r="M8">
-        <v>30.99</v>
+        <v>31.06</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>333.89</v>
+        <v>335.18</v>
       </c>
       <c r="Q8">
-        <v>336.79</v>
+        <v>337.49</v>
       </c>
       <c r="R8">
-        <v>334.64</v>
+        <v>335.03</v>
       </c>
       <c r="S8">
-        <v>288.57</v>
+        <v>288.95</v>
       </c>
       <c r="T8">
-        <v>20.68</v>
+        <v>20.99</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1698,34 +1696,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>59.75</v>
+        <v>60.52</v>
       </c>
       <c r="Z8">
-        <v>0.63</v>
+        <v>1.71</v>
       </c>
       <c r="AA8">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="AB8">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="AC8">
+        <v>69.03</v>
+      </c>
+      <c r="AD8">
         <v>35.69</v>
       </c>
-      <c r="AD8">
-        <v>21.83</v>
-      </c>
       <c r="AE8">
-        <v>11.37</v>
+        <v>10.92</v>
       </c>
       <c r="AF8">
-        <v>1021.34</v>
+        <v>26.3</v>
       </c>
       <c r="AG8">
-        <v>350.25</v>
+        <v>352.09</v>
       </c>
       <c r="AH8">
-        <v>323.34</v>
+        <v>322.88</v>
       </c>
       <c r="AI8">
         <v>316.51</v>
@@ -1734,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.78</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1745,10 +1743,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1275.6</v>
+        <v>1268.6</v>
       </c>
       <c r="D9">
-        <v>1.77</v>
+        <v>-0.55</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1757,46 +1755,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-4.88</v>
+        <v>-5.4</v>
       </c>
       <c r="H9">
-        <v>18.19</v>
+        <v>17.54</v>
       </c>
       <c r="I9">
-        <v>-2.18</v>
+        <v>0.28</v>
       </c>
       <c r="J9">
-        <v>-0.79</v>
+        <v>-2.39</v>
       </c>
       <c r="K9">
-        <v>-0.9399999999999999</v>
+        <v>-1.08</v>
       </c>
       <c r="L9">
-        <v>15.87</v>
+        <v>13.76</v>
       </c>
       <c r="M9">
-        <v>16.1</v>
+        <v>14.69</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P9">
-        <v>1254.42</v>
+        <v>1255.14</v>
       </c>
       <c r="Q9">
-        <v>1300</v>
+        <v>1298.75</v>
       </c>
       <c r="R9">
-        <v>1281.27</v>
+        <v>1281.74</v>
       </c>
       <c r="S9">
-        <v>1231.21</v>
+        <v>1231.74</v>
       </c>
       <c r="T9">
-        <v>3.61</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1811,34 +1809,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>47.23</v>
+        <v>45.62</v>
       </c>
       <c r="Z9">
-        <v>-7.76</v>
+        <v>-7.99</v>
       </c>
       <c r="AA9">
-        <v>-0.35</v>
+        <v>-1.88</v>
       </c>
       <c r="AB9">
-        <v>-7.4</v>
+        <v>-6.11</v>
       </c>
       <c r="AC9">
-        <v>33.14</v>
+        <v>42.69</v>
       </c>
       <c r="AD9">
-        <v>18.18</v>
+        <v>30.22</v>
       </c>
       <c r="AE9">
-        <v>25.81</v>
+        <v>25.29</v>
       </c>
       <c r="AF9">
-        <v>41.5</v>
+        <v>-46.01</v>
       </c>
       <c r="AG9">
-        <v>1361.89</v>
+        <v>1362.17</v>
       </c>
       <c r="AH9">
-        <v>1238.11</v>
+        <v>1235.32</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1847,7 +1845,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>31.92</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1858,10 +1856,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.90000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="D10">
-        <v>0.27</v>
+        <v>-0.91</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1870,46 +1868,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.54</v>
+        <v>-12.35</v>
       </c>
       <c r="H10">
-        <v>124.22</v>
+        <v>122.17</v>
       </c>
       <c r="I10">
-        <v>-5.31</v>
+        <v>-6.5</v>
       </c>
       <c r="J10">
-        <v>-1.99</v>
+        <v>-3.2</v>
       </c>
       <c r="K10">
-        <v>49.23</v>
+        <v>48.61</v>
       </c>
       <c r="L10">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="M10">
-        <v>-2.9</v>
+        <v>-2.37</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
         <v>85</v>
       </c>
       <c r="P10">
-        <v>82.2</v>
+        <v>81.09</v>
       </c>
       <c r="Q10">
-        <v>82.06999999999999</v>
+        <v>82.03</v>
       </c>
       <c r="R10">
-        <v>76.18000000000001</v>
+        <v>76.77</v>
       </c>
       <c r="S10">
-        <v>60.55</v>
+        <v>60.63</v>
       </c>
       <c r="T10">
-        <v>33.61</v>
+        <v>32.22</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1924,34 +1922,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.97</v>
+        <v>48.43</v>
       </c>
       <c r="Z10">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
-        <v>-0.78</v>
+        <v>-0.84</v>
       </c>
       <c r="AC10">
-        <v>14.2</v>
+        <v>5.05</v>
       </c>
       <c r="AD10">
-        <v>27.98</v>
+        <v>12.91</v>
       </c>
       <c r="AE10">
-        <v>4.11</v>
+        <v>4.03</v>
       </c>
       <c r="AF10">
-        <v>-71.69</v>
+        <v>-83.33</v>
       </c>
       <c r="AG10">
-        <v>86.70999999999999</v>
+        <v>86.72</v>
       </c>
       <c r="AH10">
-        <v>77.42</v>
+        <v>77.34</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1960,7 +1958,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>22.36</v>
+        <v>25.01</v>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2141,7 +2139,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2161,1366 +2159,1352 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>12.55</v>
+      </c>
+      <c r="D10" s="7">
+        <v>16.41</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>7.74</v>
+      </c>
+      <c r="D11" s="7">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3.72</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4.6</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-3.3</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-4.61</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-0.41</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-2.27</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>5.56</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.99</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.39</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1.99</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>12.27</v>
-      </c>
-      <c r="D9" s="6">
-        <v>12.55</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>6.08</v>
+      </c>
+      <c r="D19" s="7">
+        <v>10.46</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-8.82</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-6.06</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.54</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-1.47</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-0.84</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-1.8</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.42</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-2.13</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D26" s="7">
         <v>0.28</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="E26" s="8">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-5.31</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-6.5</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>19.73</v>
+      </c>
+      <c r="D28" s="7">
+        <v>24.43</v>
+      </c>
+      <c r="E28" s="8">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="D10" s="6">
-        <v>7.74</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>38.1</v>
+      </c>
+      <c r="D29" s="7">
+        <v>40.8</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>7</v>
+      </c>
+      <c r="D30" s="7">
+        <v>7.33</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D12" s="6">
-        <v>3.72</v>
-      </c>
-      <c r="E12" s="7">
-        <v>4.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-0.18</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-6.59</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-3.94</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-3.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.41</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-39.35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-39.55</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D15" s="6">
-        <v>5.56</v>
-      </c>
-      <c r="E15" s="7">
-        <v>6.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.59</v>
+      </c>
+      <c r="D34" s="7">
+        <v>7.17</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>15.87</v>
+      </c>
+      <c r="D35" s="7">
+        <v>13.76</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D36" s="7">
+        <v>9.57</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>4.59</v>
+      </c>
+      <c r="D37" s="7">
+        <v>10.74</v>
+      </c>
+      <c r="E37" s="8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>10.97</v>
+      </c>
+      <c r="D38" s="7">
+        <v>14.6</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-0.12</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>7.79</v>
+      </c>
+      <c r="D40" s="7">
+        <v>6.02</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-7.74</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-11.18</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-10.3</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-11.09</v>
+      </c>
+      <c r="E42" s="9">
         <v>-0.79</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>13.01</v>
+      </c>
+      <c r="D43" s="7">
+        <v>13.86</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-1.08</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-7.14</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.99</v>
-      </c>
-      <c r="E17" s="7">
-        <v>5.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>49.23</v>
+      </c>
+      <c r="D45" s="7">
+        <v>48.61</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>7.44</v>
-      </c>
-      <c r="D18" s="6">
-        <v>6.08</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-28.7</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-26.41</v>
+      </c>
+      <c r="E46" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-6.58</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
         <v>-8.82</v>
       </c>
-      <c r="E19" s="8">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D47" s="7">
+        <v>-7.7</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-13.14</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-12.27</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-13.14</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-13.08</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-12.33</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-13.83</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-49.1</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-49.45</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-0.84</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-0.46</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-4.88</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-5.4</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-11.54</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-12.35</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>718.45</v>
+      </c>
+      <c r="D55" s="7">
+        <v>741.5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>23.05</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>289.5</v>
+      </c>
+      <c r="D56" s="7">
+        <v>293.05</v>
+      </c>
+      <c r="E56" s="8">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1119.5</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1130.6</v>
+      </c>
+      <c r="E57" s="8">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>750.95</v>
+      </c>
+      <c r="D58" s="7">
+        <v>751.45</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>526</v>
+      </c>
+      <c r="D59" s="7">
+        <v>517</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>11282</v>
+      </c>
+      <c r="D60" s="7">
+        <v>11205</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>348.25</v>
+      </c>
+      <c r="D61" s="7">
+        <v>349.6</v>
+      </c>
+      <c r="E61" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1275.6</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1268.6</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D63" s="7">
+        <v>80.16</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>88</v>
+      </c>
+      <c r="D64" s="7">
+        <v>99</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>99</v>
+      </c>
+      <c r="D65" s="7">
+        <v>88</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>60.73</v>
+      </c>
+      <c r="D66" s="7">
+        <v>65.11</v>
+      </c>
+      <c r="E66" s="8">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>47.87</v>
+      </c>
+      <c r="D67" s="7">
+        <v>50.18</v>
+      </c>
+      <c r="E67" s="8">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>47.63</v>
+      </c>
+      <c r="D68" s="7">
+        <v>50.64</v>
+      </c>
+      <c r="E68" s="8">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>55.89</v>
+      </c>
+      <c r="D69" s="7">
+        <v>56.04</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>45.91</v>
+      </c>
+      <c r="D70" s="7">
+        <v>41.76</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46.73</v>
+      </c>
+      <c r="D71" s="7">
+        <v>45.22</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>59.75</v>
+      </c>
+      <c r="D72" s="7">
+        <v>60.52</v>
+      </c>
+      <c r="E72" s="8">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>47.23</v>
+      </c>
+      <c r="D73" s="7">
+        <v>45.62</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>49.97</v>
+      </c>
+      <c r="D74" s="7">
+        <v>48.43</v>
+      </c>
+      <c r="E74" s="9">
         <v>-1.54</v>
       </c>
-      <c r="E20" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-71.52</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-24.87</v>
+      </c>
+      <c r="E75" s="8">
+        <v>46.65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-40.18</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-68.94</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-28.76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>34.42</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-9.44</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-43.86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.47</v>
-      </c>
-      <c r="E21" s="7">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>184.99</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-1.84</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-186.83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.26</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>73.03</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-19.26</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-92.29000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-46.95</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-85.13</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-38.18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.69</v>
-      </c>
-      <c r="E24" s="7">
-        <v>6.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1021.34</v>
+      </c>
+      <c r="D81" s="7">
+        <v>26.3</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-995.04</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>41.5</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-46.01</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-87.51000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-5.31</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>20.76</v>
-      </c>
-      <c r="D27" s="6">
-        <v>19.73</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>41.32</v>
-      </c>
-      <c r="D28" s="6">
-        <v>38.1</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>8.92</v>
-      </c>
-      <c r="D29" s="6">
-        <v>7</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-2.28</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-40.87</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-39.35</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="D33" s="6">
-        <v>10.59</v>
-      </c>
-      <c r="E33" s="7">
-        <v>6.97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>14.05</v>
-      </c>
-      <c r="D34" s="6">
-        <v>15.87</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>10.66</v>
-      </c>
-      <c r="D35" s="6">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>5.07</v>
-      </c>
-      <c r="D36" s="6">
-        <v>4.59</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>10.28</v>
-      </c>
-      <c r="D37" s="6">
-        <v>10.97</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2.47</v>
-      </c>
-      <c r="D39" s="6">
-        <v>7.79</v>
-      </c>
-      <c r="E39" s="7">
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.04</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-7.74</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-13.35</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-10.3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>6.07</v>
-      </c>
-      <c r="D42" s="6">
-        <v>13.01</v>
-      </c>
-      <c r="E42" s="7">
-        <v>6.94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>56.3</v>
-      </c>
-      <c r="D44" s="6">
-        <v>49.23</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-7.07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-27.95</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-28.7</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-8.82</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-12.45</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-13.14</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-16.21</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-13.14</v>
-      </c>
-      <c r="E48" s="7">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-12.33</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-49.71</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-49.1</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-6.99</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E51" s="7">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-6.53</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-4.88</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-11.54</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>726</v>
-      </c>
-      <c r="D54" s="6">
-        <v>718.45</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-7.55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>291.2</v>
-      </c>
-      <c r="D55" s="6">
-        <v>289.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1128.4</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1119.5</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-8.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>724.45</v>
-      </c>
-      <c r="D57" s="6">
-        <v>750.95</v>
-      </c>
-      <c r="E57" s="7">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>512</v>
-      </c>
-      <c r="D58" s="6">
-        <v>526</v>
-      </c>
-      <c r="E58" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>11146</v>
-      </c>
-      <c r="D59" s="6">
-        <v>11282</v>
-      </c>
-      <c r="E59" s="7">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>326.65</v>
-      </c>
-      <c r="D60" s="6">
-        <v>348.25</v>
-      </c>
-      <c r="E60" s="7">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1253.4</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1275.6</v>
-      </c>
-      <c r="E61" s="7">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>80.68000000000001</v>
-      </c>
-      <c r="D62" s="6">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E62" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>34</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>34</v>
-      </c>
-      <c r="D64" s="6">
-        <v>45</v>
-      </c>
-      <c r="E64" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="6">
-        <v>45</v>
-      </c>
-      <c r="D65" s="6">
-        <v>66</v>
-      </c>
-      <c r="E65" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="6">
-        <v>66</v>
-      </c>
-      <c r="D66" s="6">
-        <v>55</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>63.14</v>
-      </c>
-      <c r="D67" s="6">
-        <v>60.73</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>48.88</v>
-      </c>
-      <c r="D68" s="6">
-        <v>47.87</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>49.89</v>
-      </c>
-      <c r="D69" s="6">
-        <v>47.63</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>47.23</v>
-      </c>
-      <c r="D70" s="6">
-        <v>55.89</v>
-      </c>
-      <c r="E70" s="7">
-        <v>8.66</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>36.86</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45.91</v>
-      </c>
-      <c r="E71" s="7">
-        <v>9.050000000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>43.64</v>
-      </c>
-      <c r="D72" s="6">
-        <v>46.73</v>
-      </c>
-      <c r="E72" s="7">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>43.34</v>
-      </c>
-      <c r="D73" s="6">
-        <v>59.75</v>
-      </c>
-      <c r="E73" s="7">
-        <v>16.41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="6">
-        <v>41.1</v>
-      </c>
-      <c r="D74" s="6">
-        <v>47.23</v>
-      </c>
-      <c r="E74" s="7">
-        <v>6.13</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="6">
-        <v>49.53</v>
-      </c>
-      <c r="D75" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="6">
-        <v>-46.11</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-71.52</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-25.41</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-47.99</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-40.18</v>
-      </c>
-      <c r="E77" s="7">
-        <v>7.81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="D78" s="6">
-        <v>34.42</v>
-      </c>
-      <c r="E78" s="7">
-        <v>42.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>41.81</v>
-      </c>
-      <c r="D79" s="6">
-        <v>184.99</v>
-      </c>
-      <c r="E79" s="7">
-        <v>143.18</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-48.43</v>
-      </c>
-      <c r="D80" s="6">
-        <v>73.03</v>
-      </c>
-      <c r="E80" s="7">
-        <v>121.46</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-48.17</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-46.95</v>
-      </c>
-      <c r="E81" s="7">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="D82" s="6">
-        <v>1021.34</v>
-      </c>
-      <c r="E82" s="7">
-        <v>1033.35</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>-18.1</v>
-      </c>
-      <c r="D83" s="6">
-        <v>41.5</v>
-      </c>
-      <c r="E83" s="7">
-        <v>59.6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="6">
-        <v>-70.09999999999999</v>
-      </c>
-      <c r="D84" s="6">
+      <c r="C83" s="7">
         <v>-71.69</v>
       </c>
-      <c r="E84" s="8">
-        <v>-1.59</v>
+      <c r="D83" s="7">
+        <v>-83.33</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-11.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3540,60 +3524,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>51.3</v>
-      </c>
-      <c r="E2" s="11">
-        <v>80</v>
-      </c>
-      <c r="F2" s="11">
-        <v>2.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>51.5</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="G2" s="12">
+        <v>7.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3695,61 +3679,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.399</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.376</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3099</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2649</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1991</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.161</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.103</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.029</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0587</v>
+      <c r="A2" s="15">
+        <v>0.4047</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3709</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3106</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2596</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1856</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1469</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0237</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0535</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,40 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.9 → 50.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.9</t>
+    <t>50.2 → 46.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.2</t>
   </si>
   <si>
-    <t>47.6 → 50.6</t>
-  </si>
-  <si>
-    <t>47.6</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>46.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -439,8 +427,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -811,8 +799,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -952,10 +940,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>741.5</v>
+        <v>721.9</v>
       </c>
       <c r="D2">
-        <v>3.21</v>
+        <v>-2.64</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -964,46 +952,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-26.41</v>
+        <v>-28.35</v>
       </c>
       <c r="H2">
-        <v>101.93</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I2">
-        <v>10.46</v>
+        <v>-2.17</v>
       </c>
       <c r="J2">
-        <v>16.41</v>
+        <v>13.22</v>
       </c>
       <c r="K2">
-        <v>10.74</v>
+        <v>12.93</v>
       </c>
       <c r="L2">
-        <v>24.43</v>
+        <v>20.02</v>
       </c>
       <c r="M2">
-        <v>-5.35</v>
+        <v>-5.91</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>733.25</v>
+        <v>730.05</v>
       </c>
       <c r="Q2">
-        <v>681.99</v>
+        <v>686.24</v>
       </c>
       <c r="R2">
-        <v>660.14</v>
+        <v>660.8200000000001</v>
       </c>
       <c r="S2">
-        <v>632.52</v>
+        <v>633.5599999999999</v>
       </c>
       <c r="T2">
-        <v>17.23</v>
+        <v>13.94</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1018,34 +1006,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>65.11</v>
+        <v>59.08</v>
       </c>
       <c r="Z2">
-        <v>21.63</v>
+        <v>21.29</v>
       </c>
       <c r="AA2">
-        <v>15.41</v>
+        <v>16.59</v>
       </c>
       <c r="AB2">
-        <v>6.21</v>
+        <v>4.7</v>
       </c>
       <c r="AC2">
-        <v>73.14</v>
+        <v>60.07</v>
       </c>
       <c r="AD2">
-        <v>82.05</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="AE2">
-        <v>32.36</v>
+        <v>32.61</v>
       </c>
       <c r="AF2">
-        <v>-24.87</v>
+        <v>-69.55</v>
       </c>
       <c r="AG2">
-        <v>755.87</v>
+        <v>758.97</v>
       </c>
       <c r="AH2">
-        <v>608.11</v>
+        <v>613.52</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1054,7 +1042,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>59.33</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1065,10 +1053,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>293.05</v>
+        <v>286.45</v>
       </c>
       <c r="D3">
-        <v>1.23</v>
+        <v>-2.25</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1077,46 +1065,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-7.7</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="H3">
-        <v>91.25</v>
+        <v>86.94</v>
       </c>
       <c r="I3">
-        <v>-6.06</v>
+        <v>-0.88</v>
       </c>
       <c r="J3">
-        <v>8.640000000000001</v>
+        <v>-1.78</v>
       </c>
       <c r="K3">
-        <v>14.6</v>
+        <v>11.11</v>
       </c>
       <c r="L3">
-        <v>40.8</v>
+        <v>37.21</v>
       </c>
       <c r="M3">
-        <v>40.47</v>
+        <v>39.14</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>288.8</v>
+        <v>288.29</v>
       </c>
       <c r="Q3">
-        <v>301.87</v>
+        <v>301.83</v>
       </c>
       <c r="R3">
-        <v>279.8</v>
+        <v>280.15</v>
       </c>
       <c r="S3">
-        <v>222.59</v>
+        <v>223.2</v>
       </c>
       <c r="T3">
-        <v>31.66</v>
+        <v>28.34</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1131,34 +1119,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.18</v>
+        <v>46.1</v>
       </c>
       <c r="Z3">
-        <v>3.67</v>
+        <v>2.57</v>
       </c>
       <c r="AA3">
-        <v>7.3</v>
+        <v>6.36</v>
       </c>
       <c r="AB3">
-        <v>-3.63</v>
+        <v>-3.79</v>
       </c>
       <c r="AC3">
-        <v>22.32</v>
+        <v>19.22</v>
       </c>
       <c r="AD3">
-        <v>14.4</v>
+        <v>18.36</v>
       </c>
       <c r="AE3">
-        <v>11.53</v>
+        <v>11.48</v>
       </c>
       <c r="AF3">
-        <v>-68.94</v>
+        <v>-75.39</v>
       </c>
       <c r="AG3">
-        <v>324.68</v>
+        <v>324.75</v>
       </c>
       <c r="AH3">
-        <v>279.05</v>
+        <v>278.9</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1167,7 +1155,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>35.81</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1178,10 +1166,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1130.6</v>
+        <v>1141</v>
       </c>
       <c r="D4">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1190,46 +1178,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-12.27</v>
+        <v>-11.47</v>
       </c>
       <c r="H4">
-        <v>14.67</v>
+        <v>15.72</v>
       </c>
       <c r="I4">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="K4">
-        <v>-0.12</v>
+        <v>5.39</v>
       </c>
       <c r="L4">
-        <v>7.33</v>
+        <v>10.39</v>
       </c>
       <c r="M4">
-        <v>25.96</v>
+        <v>25.89</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="O4">
         <v>68</v>
       </c>
       <c r="P4">
-        <v>1115.3</v>
+        <v>1124.5</v>
       </c>
       <c r="Q4">
-        <v>1145.74</v>
+        <v>1145.34</v>
       </c>
       <c r="R4">
-        <v>1106.18</v>
+        <v>1108.42</v>
       </c>
       <c r="S4">
-        <v>1132.64</v>
+        <v>1133.26</v>
       </c>
       <c r="T4">
-        <v>-0.18</v>
+        <v>0.68</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1241,37 +1229,37 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>50.64</v>
+        <v>53.35</v>
       </c>
       <c r="Z4">
-        <v>0.42</v>
+        <v>1.34</v>
       </c>
       <c r="AA4">
-        <v>5.78</v>
+        <v>4.89</v>
       </c>
       <c r="AB4">
-        <v>-5.36</v>
+        <v>-3.55</v>
       </c>
       <c r="AC4">
-        <v>35.56</v>
+        <v>48.1</v>
       </c>
       <c r="AD4">
-        <v>22.85</v>
+        <v>34.67</v>
       </c>
       <c r="AE4">
-        <v>29.86</v>
+        <v>28.94</v>
       </c>
       <c r="AF4">
-        <v>-9.44</v>
+        <v>15.91</v>
       </c>
       <c r="AG4">
-        <v>1196.17</v>
+        <v>1195.79</v>
       </c>
       <c r="AH4">
-        <v>1095.3</v>
+        <v>1094.88</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1280,7 +1268,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>32.63</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1291,10 +1279,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>751.45</v>
+        <v>743.45</v>
       </c>
       <c r="D5">
-        <v>0.07000000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1303,46 +1291,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.08</v>
+        <v>-14.01</v>
       </c>
       <c r="H5">
-        <v>13.53</v>
+        <v>12.32</v>
       </c>
       <c r="I5">
-        <v>-0.61</v>
+        <v>2.75</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>6.02</v>
+        <v>7.53</v>
       </c>
       <c r="L5">
-        <v>-0.18</v>
+        <v>-2.13</v>
       </c>
       <c r="M5">
-        <v>37.09</v>
+        <v>36.23</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>736.25</v>
+        <v>740.23</v>
       </c>
       <c r="Q5">
-        <v>731.63</v>
+        <v>733.6799999999999</v>
       </c>
       <c r="R5">
-        <v>730.53</v>
+        <v>731.33</v>
       </c>
       <c r="S5">
-        <v>748.21</v>
+        <v>748.1900000000001</v>
       </c>
       <c r="T5">
-        <v>0.43</v>
+        <v>-0.63</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1354,37 +1342,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>56.04</v>
+        <v>53</v>
       </c>
       <c r="Z5">
-        <v>5.7</v>
+        <v>5.51</v>
       </c>
       <c r="AA5">
-        <v>5.01</v>
+        <v>5.11</v>
       </c>
       <c r="AB5">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AC5">
-        <v>34.55</v>
+        <v>34.66</v>
       </c>
       <c r="AD5">
-        <v>30.47</v>
+        <v>34.01</v>
       </c>
       <c r="AE5">
-        <v>22.15</v>
+        <v>21.49</v>
       </c>
       <c r="AF5">
-        <v>-1.84</v>
+        <v>-18.63</v>
       </c>
       <c r="AG5">
-        <v>776.72</v>
+        <v>776.87</v>
       </c>
       <c r="AH5">
-        <v>686.53</v>
+        <v>690.49</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1393,7 +1381,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.71</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1404,10 +1392,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D6">
-        <v>-1.71</v>
+        <v>0.19</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1416,46 +1404,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-13.83</v>
+        <v>-13.67</v>
       </c>
       <c r="H6">
-        <v>17.89</v>
+        <v>18.11</v>
       </c>
       <c r="I6">
-        <v>-1.8</v>
+        <v>2.57</v>
       </c>
       <c r="J6">
-        <v>-4.61</v>
+        <v>-4.95</v>
       </c>
       <c r="K6">
-        <v>-11.18</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L6">
-        <v>-3.94</v>
+        <v>-2.85</v>
       </c>
       <c r="M6">
-        <v>9.43</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>512.9400000000001</v>
+        <v>515.54</v>
       </c>
       <c r="Q6">
-        <v>529.22</v>
+        <v>527.89</v>
       </c>
       <c r="R6">
-        <v>545.08</v>
+        <v>544.37</v>
       </c>
       <c r="S6">
-        <v>521.8200000000001</v>
+        <v>522.0700000000001</v>
       </c>
       <c r="T6">
-        <v>-0.92</v>
+        <v>-0.78</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1470,34 +1458,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.76</v>
+        <v>42.39</v>
       </c>
       <c r="Z6">
-        <v>-8.98</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AA6">
-        <v>-8.25</v>
+        <v>-8.34</v>
       </c>
       <c r="AB6">
-        <v>-0.73</v>
+        <v>-0.36</v>
       </c>
       <c r="AC6">
-        <v>72.98</v>
+        <v>82.69</v>
       </c>
       <c r="AD6">
-        <v>49.87</v>
+        <v>69.39</v>
       </c>
       <c r="AE6">
-        <v>12.34</v>
+        <v>11.94</v>
       </c>
       <c r="AF6">
-        <v>-19.26</v>
+        <v>-46.8</v>
       </c>
       <c r="AG6">
-        <v>555.34</v>
+        <v>553.4</v>
       </c>
       <c r="AH6">
-        <v>503.1</v>
+        <v>502.38</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1506,7 +1494,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.6</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,10 +1505,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11205</v>
+        <v>11219</v>
       </c>
       <c r="D7">
-        <v>-0.68</v>
+        <v>0.12</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1529,49 +1517,49 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.45</v>
+        <v>-49.38</v>
       </c>
       <c r="H7">
-        <v>5.16</v>
+        <v>5.29</v>
       </c>
       <c r="I7">
-        <v>-2.13</v>
+        <v>2.3</v>
       </c>
       <c r="J7">
-        <v>-2.27</v>
+        <v>-0.62</v>
       </c>
       <c r="K7">
-        <v>-11.09</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L7">
-        <v>-39.55</v>
+        <v>-40.08</v>
       </c>
       <c r="M7">
-        <v>18.56</v>
+        <v>18.75</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>11107</v>
+        <v>11157.4</v>
       </c>
       <c r="Q7">
-        <v>11430.4</v>
+        <v>11433.3</v>
       </c>
       <c r="R7">
-        <v>11432.52</v>
+        <v>11428.5</v>
       </c>
       <c r="S7">
-        <v>14383.55</v>
+        <v>14329.22</v>
       </c>
       <c r="T7">
-        <v>-22.1</v>
+        <v>-21.71</v>
       </c>
       <c r="U7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
         <v>48</v>
@@ -1580,37 +1568,37 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>45.22</v>
+        <v>45.56</v>
       </c>
       <c r="Z7">
-        <v>-119.12</v>
+        <v>-116.05</v>
       </c>
       <c r="AA7">
-        <v>-88.84</v>
+        <v>-94.28</v>
       </c>
       <c r="AB7">
-        <v>-30.28</v>
+        <v>-21.77</v>
       </c>
       <c r="AC7">
-        <v>40.8</v>
+        <v>53.26</v>
       </c>
       <c r="AD7">
-        <v>24.45</v>
+        <v>39.19</v>
       </c>
       <c r="AE7">
-        <v>404.26</v>
+        <v>402.96</v>
       </c>
       <c r="AF7">
-        <v>-85.13</v>
+        <v>-62.16</v>
       </c>
       <c r="AG7">
-        <v>11981</v>
+        <v>11978.51</v>
       </c>
       <c r="AH7">
-        <v>10879.8</v>
+        <v>10888.09</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1619,7 +1607,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>18.83</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1630,58 +1618,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>349.6</v>
+        <v>367.6</v>
       </c>
       <c r="D8">
-        <v>0.39</v>
+        <v>5.15</v>
       </c>
       <c r="E8">
-        <v>351.2</v>
+        <v>367.6</v>
       </c>
       <c r="F8">
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>49.2</v>
+        <v>56.89</v>
       </c>
       <c r="I8">
-        <v>1.88</v>
+        <v>12.81</v>
       </c>
       <c r="J8">
-        <v>5.99</v>
+        <v>9.5</v>
       </c>
       <c r="K8">
-        <v>13.86</v>
+        <v>16.72</v>
       </c>
       <c r="L8">
-        <v>7.17</v>
+        <v>11.82</v>
       </c>
       <c r="M8">
-        <v>31.06</v>
+        <v>33.26</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P8">
-        <v>335.18</v>
+        <v>343.53</v>
       </c>
       <c r="Q8">
-        <v>337.49</v>
+        <v>338.86</v>
       </c>
       <c r="R8">
-        <v>335.03</v>
+        <v>335.36</v>
       </c>
       <c r="S8">
-        <v>288.95</v>
+        <v>289.44</v>
       </c>
       <c r="T8">
-        <v>20.99</v>
+        <v>27.01</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1696,43 +1684,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>60.52</v>
+        <v>69.03</v>
       </c>
       <c r="Z8">
-        <v>1.71</v>
+        <v>3.97</v>
       </c>
       <c r="AA8">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="AB8">
-        <v>0.66</v>
+        <v>2.34</v>
       </c>
       <c r="AC8">
-        <v>69.03</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>35.69</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="AE8">
-        <v>10.92</v>
+        <v>11.99</v>
       </c>
       <c r="AF8">
-        <v>26.3</v>
+        <v>383.3</v>
       </c>
       <c r="AG8">
-        <v>352.09</v>
+        <v>358.73</v>
       </c>
       <c r="AH8">
-        <v>322.88</v>
+        <v>318.99</v>
       </c>
       <c r="AI8">
-        <v>316.51</v>
+        <v>327.44</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.83</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1731,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1268.6</v>
+        <v>1267</v>
       </c>
       <c r="D9">
-        <v>-0.55</v>
+        <v>-0.13</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1755,46 +1743,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.4</v>
+        <v>-5.52</v>
       </c>
       <c r="H9">
-        <v>17.54</v>
+        <v>17.39</v>
       </c>
       <c r="I9">
-        <v>0.28</v>
+        <v>3.08</v>
       </c>
       <c r="J9">
-        <v>-2.39</v>
+        <v>-2.06</v>
       </c>
       <c r="K9">
-        <v>-1.08</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>13.76</v>
+        <v>14.04</v>
       </c>
       <c r="M9">
-        <v>14.69</v>
+        <v>14.33</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1255.14</v>
+        <v>1262.7</v>
       </c>
       <c r="Q9">
-        <v>1298.75</v>
+        <v>1295.75</v>
       </c>
       <c r="R9">
-        <v>1281.74</v>
+        <v>1282.33</v>
       </c>
       <c r="S9">
-        <v>1231.74</v>
+        <v>1232.36</v>
       </c>
       <c r="T9">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1809,34 +1797,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>45.62</v>
+        <v>45.24</v>
       </c>
       <c r="Z9">
-        <v>-7.99</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="AA9">
-        <v>-1.88</v>
+        <v>-3.15</v>
       </c>
       <c r="AB9">
-        <v>-6.11</v>
+        <v>-5.07</v>
       </c>
       <c r="AC9">
-        <v>42.69</v>
+        <v>50.01</v>
       </c>
       <c r="AD9">
-        <v>30.22</v>
+        <v>41.94</v>
       </c>
       <c r="AE9">
-        <v>25.29</v>
+        <v>24.41</v>
       </c>
       <c r="AF9">
-        <v>-46.01</v>
+        <v>-46.28</v>
       </c>
       <c r="AG9">
-        <v>1362.17</v>
+        <v>1359.22</v>
       </c>
       <c r="AH9">
-        <v>1235.32</v>
+        <v>1232.27</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1845,7 +1833,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>27.7</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1856,10 +1844,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.16</v>
+        <v>77.64</v>
       </c>
       <c r="D10">
-        <v>-0.91</v>
+        <v>-3.14</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1868,46 +1856,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-12.35</v>
+        <v>-15.1</v>
       </c>
       <c r="H10">
-        <v>122.17</v>
+        <v>115.19</v>
       </c>
       <c r="I10">
-        <v>-6.5</v>
+        <v>-5.07</v>
       </c>
       <c r="J10">
-        <v>-3.2</v>
+        <v>-4.02</v>
       </c>
       <c r="K10">
-        <v>48.61</v>
+        <v>44.15</v>
       </c>
       <c r="L10">
-        <v>9.57</v>
+        <v>5.66</v>
       </c>
       <c r="M10">
-        <v>-2.37</v>
+        <v>-3.54</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P10">
-        <v>81.09</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="Q10">
-        <v>82.03</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="R10">
-        <v>76.77</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="S10">
-        <v>60.63</v>
+        <v>60.69</v>
       </c>
       <c r="T10">
-        <v>32.22</v>
+        <v>27.92</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1922,34 +1910,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>48.43</v>
+        <v>43.5</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="AA10">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>-0.84</v>
+        <v>-1.01</v>
       </c>
       <c r="AC10">
-        <v>5.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>12.91</v>
+        <v>7.48</v>
       </c>
       <c r="AE10">
-        <v>4.03</v>
+        <v>4.15</v>
       </c>
       <c r="AF10">
-        <v>-83.33</v>
+        <v>-65.45</v>
       </c>
       <c r="AG10">
-        <v>86.72</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="AH10">
-        <v>77.34</v>
+        <v>76.78</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1958,7 +1946,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>25.01</v>
+        <v>29.18</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2139,7 +2127,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2151,1360 +2139,1371 @@
         <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>48</v>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>16.41</v>
+      </c>
+      <c r="D8" s="7">
+        <v>13.22</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.19</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>73</v>
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-1.78</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-10.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>12.55</v>
+        <v>1.05</v>
       </c>
       <c r="D10" s="7">
-        <v>16.41</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.86</v>
+        <v>1.17</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>7.74</v>
+        <v>4.6</v>
       </c>
       <c r="D11" s="7">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.9</v>
+        <v>6</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>0.4</v>
+        <v>-4.61</v>
       </c>
       <c r="D12" s="7">
-        <v>1.05</v>
+        <v>-4.95</v>
       </c>
       <c r="E12" s="8">
-        <v>0.65</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>3.72</v>
+        <v>-2.27</v>
       </c>
       <c r="D13" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.88</v>
+        <v>-0.62</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-3.3</v>
+        <v>5.99</v>
       </c>
       <c r="D14" s="7">
-        <v>-4.61</v>
+        <v>9.5</v>
       </c>
       <c r="E14" s="9">
-        <v>-1.31</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-0.41</v>
+        <v>-2.39</v>
       </c>
       <c r="D15" s="7">
-        <v>-2.27</v>
+        <v>-2.06</v>
       </c>
       <c r="E15" s="9">
-        <v>-1.86</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>5.56</v>
+        <v>-3.2</v>
       </c>
       <c r="D16" s="7">
-        <v>5.99</v>
+        <v>-4.02</v>
       </c>
       <c r="E16" s="8">
-        <v>0.43</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-0.79</v>
+        <v>10.46</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.39</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.6</v>
+        <v>-2.17</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-12.63</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-1.99</v>
+        <v>-6.06</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.2</v>
+        <v>-0.88</v>
       </c>
       <c r="E18" s="9">
-        <v>-1.21</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>6.08</v>
+        <v>0.9</v>
       </c>
       <c r="D19" s="7">
-        <v>10.46</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4.38</v>
+        <v>4.2</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-8.82</v>
+        <v>-0.61</v>
       </c>
       <c r="D20" s="7">
-        <v>-6.06</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.76</v>
+        <v>2.75</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-1.54</v>
+        <v>-1.8</v>
       </c>
       <c r="D21" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.44</v>
+        <v>2.57</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-1.47</v>
+        <v>-2.13</v>
       </c>
       <c r="D22" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.86</v>
+        <v>2.3</v>
+      </c>
+      <c r="E22" s="9">
+        <v>4.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-0.84</v>
+        <v>1.88</v>
       </c>
       <c r="D23" s="7">
-        <v>-1.8</v>
+        <v>12.81</v>
       </c>
       <c r="E23" s="9">
-        <v>-0.96</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-1.42</v>
+        <v>0.28</v>
       </c>
       <c r="D24" s="7">
-        <v>-2.13</v>
+        <v>3.08</v>
       </c>
       <c r="E24" s="9">
-        <v>-0.71</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>1.69</v>
+        <v>-6.5</v>
       </c>
       <c r="D25" s="7">
-        <v>1.88</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.19</v>
+        <v>-5.07</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.43</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-2.18</v>
+        <v>24.43</v>
       </c>
       <c r="D26" s="7">
-        <v>0.28</v>
+        <v>20.02</v>
       </c>
       <c r="E26" s="8">
-        <v>2.46</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>-5.31</v>
+        <v>40.8</v>
       </c>
       <c r="D27" s="7">
-        <v>-6.5</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.19</v>
+        <v>37.21</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>19.73</v>
+        <v>7.33</v>
       </c>
       <c r="D28" s="7">
-        <v>24.43</v>
-      </c>
-      <c r="E28" s="8">
-        <v>4.7</v>
+        <v>10.39</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>38.1</v>
+        <v>-0.18</v>
       </c>
       <c r="D29" s="7">
-        <v>40.8</v>
+        <v>-2.13</v>
       </c>
       <c r="E29" s="8">
-        <v>2.7</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>7</v>
+        <v>-3.94</v>
       </c>
       <c r="D30" s="7">
-        <v>7.33</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.33</v>
+        <v>-2.85</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>0.22</v>
+        <v>-39.55</v>
       </c>
       <c r="D31" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.4</v>
+        <v>-40.08</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-0.79</v>
+        <v>7.17</v>
       </c>
       <c r="D32" s="7">
-        <v>-3.94</v>
+        <v>11.82</v>
       </c>
       <c r="E32" s="9">
-        <v>-3.15</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>-39.35</v>
+        <v>13.76</v>
       </c>
       <c r="D33" s="7">
-        <v>-39.55</v>
+        <v>14.04</v>
       </c>
       <c r="E33" s="9">
-        <v>-0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>10.59</v>
+        <v>9.57</v>
       </c>
       <c r="D34" s="7">
-        <v>7.17</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-3.42</v>
+        <v>5.66</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>15.87</v>
+        <v>10.74</v>
       </c>
       <c r="D35" s="7">
-        <v>13.76</v>
+        <v>12.93</v>
       </c>
       <c r="E35" s="9">
-        <v>-2.11</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>9.380000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="D36" s="7">
-        <v>9.57</v>
+        <v>11.11</v>
       </c>
       <c r="E36" s="8">
-        <v>0.19</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>4.59</v>
+        <v>-0.12</v>
       </c>
       <c r="D37" s="7">
-        <v>10.74</v>
-      </c>
-      <c r="E37" s="8">
-        <v>6.15</v>
+        <v>5.39</v>
+      </c>
+      <c r="E37" s="9">
+        <v>5.51</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>10.97</v>
+        <v>6.02</v>
       </c>
       <c r="D38" s="7">
-        <v>14.6</v>
-      </c>
-      <c r="E38" s="8">
-        <v>3.63</v>
+        <v>7.53</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.51</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-1.6</v>
+        <v>-11.18</v>
       </c>
       <c r="D39" s="7">
-        <v>-0.12</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.48</v>
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E39" s="9">
+        <v>2.23</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>7.79</v>
+        <v>-11.09</v>
       </c>
       <c r="D40" s="7">
-        <v>6.02</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="E40" s="9">
-        <v>-1.77</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-7.74</v>
+        <v>13.86</v>
       </c>
       <c r="D41" s="7">
-        <v>-11.18</v>
+        <v>16.72</v>
       </c>
       <c r="E41" s="9">
-        <v>-3.44</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>-10.3</v>
+        <v>-1.08</v>
       </c>
       <c r="D42" s="7">
-        <v>-11.09</v>
+        <v>2</v>
       </c>
       <c r="E42" s="9">
-        <v>-0.79</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>13.01</v>
+        <v>48.61</v>
       </c>
       <c r="D43" s="7">
-        <v>13.86</v>
+        <v>44.15</v>
       </c>
       <c r="E43" s="8">
-        <v>0.85</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-26.41</v>
       </c>
       <c r="D44" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.14</v>
+        <v>-28.35</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>49.23</v>
+        <v>-7.7</v>
       </c>
       <c r="D45" s="7">
-        <v>48.61</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.62</v>
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-28.7</v>
+        <v>-12.27</v>
       </c>
       <c r="D46" s="7">
-        <v>-26.41</v>
-      </c>
-      <c r="E46" s="8">
-        <v>2.29</v>
+        <v>-11.47</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-8.82</v>
+        <v>-13.08</v>
       </c>
       <c r="D47" s="7">
-        <v>-7.7</v>
+        <v>-14.01</v>
       </c>
       <c r="E47" s="8">
-        <v>1.12</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-13.14</v>
+        <v>-13.83</v>
       </c>
       <c r="D48" s="7">
-        <v>-12.27</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.87</v>
+        <v>-13.67</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.16</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-13.14</v>
+        <v>-49.45</v>
       </c>
       <c r="D49" s="7">
-        <v>-13.08</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.06</v>
+        <v>-49.38</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-12.33</v>
+        <v>-0.46</v>
       </c>
       <c r="D50" s="7">
-        <v>-13.83</v>
+        <v>0</v>
       </c>
       <c r="E50" s="9">
-        <v>-1.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-49.1</v>
+        <v>-5.4</v>
       </c>
       <c r="D51" s="7">
-        <v>-49.45</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.35</v>
+        <v>-5.52</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-0.84</v>
+        <v>-12.35</v>
       </c>
       <c r="D52" s="7">
-        <v>-0.46</v>
+        <v>-15.1</v>
       </c>
       <c r="E52" s="8">
-        <v>0.38</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>-4.88</v>
+        <v>741.5</v>
       </c>
       <c r="D53" s="7">
-        <v>-5.4</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.52</v>
+        <v>721.9</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-19.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>-11.54</v>
+        <v>293.05</v>
       </c>
       <c r="D54" s="7">
-        <v>-12.35</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-0.8100000000000001</v>
+        <v>286.45</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>718.45</v>
+        <v>1130.6</v>
       </c>
       <c r="D55" s="7">
-        <v>741.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>23.05</v>
+        <v>1141</v>
+      </c>
+      <c r="E55" s="9">
+        <v>10.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>289.5</v>
+        <v>751.45</v>
       </c>
       <c r="D56" s="7">
-        <v>293.05</v>
+        <v>743.45</v>
       </c>
       <c r="E56" s="8">
-        <v>3.55</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>1119.5</v>
+        <v>517</v>
       </c>
       <c r="D57" s="7">
-        <v>1130.6</v>
-      </c>
-      <c r="E57" s="8">
-        <v>11.1</v>
+        <v>518</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>750.95</v>
+        <v>11205</v>
       </c>
       <c r="D58" s="7">
-        <v>751.45</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.5</v>
+        <v>11219</v>
+      </c>
+      <c r="E58" s="9">
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>526</v>
+        <v>349.6</v>
       </c>
       <c r="D59" s="7">
-        <v>517</v>
+        <v>367.6</v>
       </c>
       <c r="E59" s="9">
-        <v>-9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>11282</v>
+        <v>1268.6</v>
       </c>
       <c r="D60" s="7">
-        <v>11205</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-77</v>
+        <v>1267</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>348.25</v>
+        <v>80.16</v>
       </c>
       <c r="D61" s="7">
-        <v>349.6</v>
+        <v>77.64</v>
       </c>
       <c r="E61" s="8">
-        <v>1.35</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C62" s="7">
-        <v>1275.6</v>
+        <v>99</v>
       </c>
       <c r="D62" s="7">
-        <v>1268.6</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-7</v>
+        <v>88</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C63" s="7">
-        <v>80.90000000000001</v>
+        <v>34</v>
       </c>
       <c r="D63" s="7">
-        <v>80.16</v>
+        <v>55</v>
       </c>
       <c r="E63" s="9">
-        <v>-0.74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D64" s="7">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E64" s="8">
-        <v>11</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="7">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D65" s="7">
-        <v>88</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-11</v>
+        <v>45</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="7">
-        <v>60.73</v>
+        <v>88</v>
       </c>
       <c r="D66" s="7">
-        <v>65.11</v>
-      </c>
-      <c r="E66" s="8">
-        <v>4.38</v>
+        <v>99</v>
+      </c>
+      <c r="E66" s="9">
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>47.87</v>
+        <v>65.11</v>
       </c>
       <c r="D67" s="7">
-        <v>50.18</v>
+        <v>59.08</v>
       </c>
       <c r="E67" s="8">
-        <v>2.31</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>47.63</v>
+        <v>50.18</v>
       </c>
       <c r="D68" s="7">
-        <v>50.64</v>
+        <v>46.1</v>
       </c>
       <c r="E68" s="8">
-        <v>3.01</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>55.89</v>
+        <v>50.64</v>
       </c>
       <c r="D69" s="7">
-        <v>56.04</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.15</v>
+        <v>53.35</v>
+      </c>
+      <c r="E69" s="9">
+        <v>2.71</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>45.91</v>
+        <v>56.04</v>
       </c>
       <c r="D70" s="7">
-        <v>41.76</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-4.15</v>
+        <v>53</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-3.04</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>46.73</v>
+        <v>41.76</v>
       </c>
       <c r="D71" s="7">
-        <v>45.22</v>
+        <v>42.39</v>
       </c>
       <c r="E71" s="9">
-        <v>-1.51</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>59.75</v>
+        <v>45.22</v>
       </c>
       <c r="D72" s="7">
-        <v>60.52</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.77</v>
+        <v>45.56</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.34</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>47.23</v>
+        <v>60.52</v>
       </c>
       <c r="D73" s="7">
-        <v>45.62</v>
+        <v>69.03</v>
       </c>
       <c r="E73" s="9">
-        <v>-1.61</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>49.97</v>
+        <v>45.62</v>
       </c>
       <c r="D74" s="7">
-        <v>48.43</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-1.54</v>
+        <v>45.24</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="7">
-        <v>-71.52</v>
+        <v>48.43</v>
       </c>
       <c r="D75" s="7">
-        <v>-24.87</v>
+        <v>43.5</v>
       </c>
       <c r="E75" s="8">
-        <v>46.65</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-40.18</v>
+        <v>-24.87</v>
       </c>
       <c r="D76" s="7">
-        <v>-68.94</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-28.76</v>
+        <v>-69.55</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-44.68</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>34.42</v>
+        <v>-68.94</v>
       </c>
       <c r="D77" s="7">
-        <v>-9.44</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-43.86</v>
+        <v>-75.39</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-6.45</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>184.99</v>
+        <v>-9.44</v>
       </c>
       <c r="D78" s="7">
-        <v>-1.84</v>
+        <v>15.91</v>
       </c>
       <c r="E78" s="9">
-        <v>-186.83</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>73.03</v>
+        <v>-1.84</v>
       </c>
       <c r="D79" s="7">
-        <v>-19.26</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-92.29000000000001</v>
+        <v>-18.63</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-16.79</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>-46.95</v>
+        <v>-19.26</v>
       </c>
       <c r="D80" s="7">
-        <v>-85.13</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-38.18</v>
+        <v>-46.8</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-27.54</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>1021.34</v>
+        <v>-85.13</v>
       </c>
       <c r="D81" s="7">
-        <v>26.3</v>
+        <v>-62.16</v>
       </c>
       <c r="E81" s="9">
-        <v>-995.04</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="7">
-        <v>41.5</v>
+        <v>26.3</v>
       </c>
       <c r="D82" s="7">
-        <v>-46.01</v>
+        <v>383.3</v>
       </c>
       <c r="E82" s="9">
-        <v>-87.51000000000001</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C83" s="7">
-        <v>-71.69</v>
+        <v>-46.01</v>
       </c>
       <c r="D83" s="7">
+        <v>-46.28</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
         <v>-83.33</v>
       </c>
-      <c r="E83" s="9">
-        <v>-11.64</v>
+      <c r="D84" s="7">
+        <v>-65.45</v>
+      </c>
+      <c r="E84" s="9">
+        <v>17.88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3528,28 +3527,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3563,16 +3562,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="E2" s="12">
         <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="G2" s="12">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3709,31 +3708,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.4047</v>
+        <v>0.3914</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3709</v>
+        <v>0.3623</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3106</v>
+        <v>0.3326</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2596</v>
+        <v>0.2589</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1856</v>
+        <v>0.1875</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1469</v>
+        <v>0.1433</v>
       </c>
       <c r="G2" s="15">
-        <v>0.09429999999999999</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0237</v>
+        <v>-0.0354</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0535</v>
+        <v>-0.0591</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,28 +193,37 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.1 → 50.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.1</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>45.2 → 53.3</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>53.3</t>
+  </si>
+  <si>
     <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.2 → 46.1</t>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>46.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -799,8 +808,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -940,10 +949,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>721.9</v>
+        <v>715.2</v>
       </c>
       <c r="D2">
-        <v>-2.64</v>
+        <v>-0.93</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -952,46 +961,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-28.35</v>
+        <v>-29.02</v>
       </c>
       <c r="H2">
-        <v>96.59999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="I2">
-        <v>-2.17</v>
+        <v>-3.66</v>
       </c>
       <c r="J2">
-        <v>13.22</v>
+        <v>12.3</v>
       </c>
       <c r="K2">
-        <v>12.93</v>
+        <v>8.65</v>
       </c>
       <c r="L2">
-        <v>20.02</v>
+        <v>18.08</v>
       </c>
       <c r="M2">
-        <v>-5.91</v>
+        <v>-6.34</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>730.05</v>
+        <v>724.61</v>
       </c>
       <c r="Q2">
-        <v>686.24</v>
+        <v>689.67</v>
       </c>
       <c r="R2">
-        <v>660.8200000000001</v>
+        <v>661.6799999999999</v>
       </c>
       <c r="S2">
-        <v>633.5599999999999</v>
+        <v>634.5700000000001</v>
       </c>
       <c r="T2">
-        <v>13.94</v>
+        <v>12.71</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1006,34 +1015,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.08</v>
+        <v>57.13</v>
       </c>
       <c r="Z2">
-        <v>21.29</v>
+        <v>20.25</v>
       </c>
       <c r="AA2">
-        <v>16.59</v>
+        <v>17.32</v>
       </c>
       <c r="AB2">
-        <v>4.7</v>
+        <v>2.93</v>
       </c>
       <c r="AC2">
-        <v>60.07</v>
+        <v>46.18</v>
       </c>
       <c r="AD2">
-        <v>71.34999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="AE2">
-        <v>32.61</v>
+        <v>32.03</v>
       </c>
       <c r="AF2">
-        <v>-69.55</v>
+        <v>-76.88</v>
       </c>
       <c r="AG2">
-        <v>758.97</v>
+        <v>760.98</v>
       </c>
       <c r="AH2">
-        <v>613.52</v>
+        <v>618.36</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1042,7 +1051,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>58.11</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,10 +1062,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>286.45</v>
+        <v>292.6</v>
       </c>
       <c r="D3">
-        <v>-2.25</v>
+        <v>2.15</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1065,46 +1074,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-9.779999999999999</v>
+        <v>-7.84</v>
       </c>
       <c r="H3">
-        <v>86.94</v>
+        <v>90.95</v>
       </c>
       <c r="I3">
-        <v>-0.88</v>
+        <v>4.04</v>
       </c>
       <c r="J3">
-        <v>-1.78</v>
+        <v>1.86</v>
       </c>
       <c r="K3">
-        <v>11.11</v>
+        <v>13.38</v>
       </c>
       <c r="L3">
-        <v>37.21</v>
+        <v>41.12</v>
       </c>
       <c r="M3">
-        <v>39.14</v>
+        <v>39.7</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>82</v>
       </c>
       <c r="P3">
-        <v>288.29</v>
+        <v>290.56</v>
       </c>
       <c r="Q3">
-        <v>301.83</v>
+        <v>302.37</v>
       </c>
       <c r="R3">
-        <v>280.15</v>
+        <v>280.83</v>
       </c>
       <c r="S3">
-        <v>223.2</v>
+        <v>223.85</v>
       </c>
       <c r="T3">
-        <v>28.34</v>
+        <v>30.71</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1119,34 +1128,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.1</v>
+        <v>50.16</v>
       </c>
       <c r="Z3">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="AA3">
-        <v>6.36</v>
+        <v>5.52</v>
       </c>
       <c r="AB3">
-        <v>-3.79</v>
+        <v>-3.35</v>
       </c>
       <c r="AC3">
-        <v>19.22</v>
+        <v>21.77</v>
       </c>
       <c r="AD3">
-        <v>18.36</v>
+        <v>21.1</v>
       </c>
       <c r="AE3">
-        <v>11.48</v>
+        <v>11.28</v>
       </c>
       <c r="AF3">
-        <v>-75.39</v>
+        <v>-56.36</v>
       </c>
       <c r="AG3">
-        <v>324.75</v>
+        <v>323.75</v>
       </c>
       <c r="AH3">
-        <v>278.9</v>
+        <v>280.98</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1155,7 +1164,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.11</v>
+        <v>36.37</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1175,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1141</v>
+        <v>1175.3</v>
       </c>
       <c r="D4">
-        <v>0.92</v>
+        <v>3.01</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1178,46 +1187,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.47</v>
+        <v>-8.81</v>
       </c>
       <c r="H4">
-        <v>15.72</v>
+        <v>19.2</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>6.55</v>
       </c>
       <c r="J4">
-        <v>1.17</v>
+        <v>2.29</v>
       </c>
       <c r="K4">
-        <v>5.39</v>
+        <v>7.86</v>
       </c>
       <c r="L4">
-        <v>10.39</v>
+        <v>12.18</v>
       </c>
       <c r="M4">
-        <v>25.89</v>
+        <v>26.29</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P4">
-        <v>1124.5</v>
+        <v>1138.96</v>
       </c>
       <c r="Q4">
-        <v>1145.34</v>
+        <v>1146.4</v>
       </c>
       <c r="R4">
-        <v>1108.42</v>
+        <v>1111.13</v>
       </c>
       <c r="S4">
-        <v>1133.26</v>
+        <v>1134.11</v>
       </c>
       <c r="T4">
-        <v>0.68</v>
+        <v>3.63</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1232,34 +1241,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>53.35</v>
+        <v>60.96</v>
       </c>
       <c r="Z4">
-        <v>1.34</v>
+        <v>4.78</v>
       </c>
       <c r="AA4">
-        <v>4.89</v>
+        <v>4.87</v>
       </c>
       <c r="AB4">
-        <v>-3.55</v>
+        <v>-0.09</v>
       </c>
       <c r="AC4">
-        <v>48.1</v>
+        <v>73.73</v>
       </c>
       <c r="AD4">
-        <v>34.67</v>
+        <v>52.46</v>
       </c>
       <c r="AE4">
-        <v>28.94</v>
+        <v>30.38</v>
       </c>
       <c r="AF4">
-        <v>15.91</v>
+        <v>30.25</v>
       </c>
       <c r="AG4">
-        <v>1195.79</v>
+        <v>1198.49</v>
       </c>
       <c r="AH4">
-        <v>1094.88</v>
+        <v>1094.3</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1268,7 +1277,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>30.06</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1288,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>743.45</v>
+        <v>758.55</v>
       </c>
       <c r="D5">
-        <v>-1.06</v>
+        <v>2.03</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1291,46 +1300,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.01</v>
+        <v>-12.26</v>
       </c>
       <c r="H5">
-        <v>12.32</v>
+        <v>14.6</v>
       </c>
       <c r="I5">
-        <v>2.75</v>
+        <v>3.79</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>7.99</v>
       </c>
       <c r="K5">
-        <v>7.53</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L5">
-        <v>-2.13</v>
+        <v>-0.36</v>
       </c>
       <c r="M5">
-        <v>36.23</v>
+        <v>36.5</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>740.23</v>
+        <v>745.77</v>
       </c>
       <c r="Q5">
-        <v>733.6799999999999</v>
+        <v>736.54</v>
       </c>
       <c r="R5">
-        <v>731.33</v>
+        <v>732.0700000000001</v>
       </c>
       <c r="S5">
-        <v>748.1900000000001</v>
+        <v>748.25</v>
       </c>
       <c r="T5">
-        <v>-0.63</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1342,37 +1351,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>53</v>
+        <v>57.66</v>
       </c>
       <c r="Z5">
-        <v>5.51</v>
+        <v>6.5</v>
       </c>
       <c r="AA5">
-        <v>5.11</v>
+        <v>5.39</v>
       </c>
       <c r="AB5">
-        <v>0.4</v>
+        <v>1.11</v>
       </c>
       <c r="AC5">
-        <v>34.66</v>
+        <v>32.13</v>
       </c>
       <c r="AD5">
-        <v>34.01</v>
+        <v>33.78</v>
       </c>
       <c r="AE5">
-        <v>21.49</v>
+        <v>21.63</v>
       </c>
       <c r="AF5">
-        <v>-18.63</v>
+        <v>-19.04</v>
       </c>
       <c r="AG5">
-        <v>776.87</v>
+        <v>778.27</v>
       </c>
       <c r="AH5">
-        <v>690.49</v>
+        <v>694.8</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1381,7 +1390,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.52</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1401,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D6">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1404,46 +1413,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-13.67</v>
+        <v>-13.17</v>
       </c>
       <c r="H6">
-        <v>18.11</v>
+        <v>18.8</v>
       </c>
       <c r="I6">
-        <v>2.57</v>
+        <v>3.23</v>
       </c>
       <c r="J6">
-        <v>-4.95</v>
+        <v>-4.35</v>
       </c>
       <c r="K6">
-        <v>-8.949999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L6">
-        <v>-2.85</v>
+        <v>-2.79</v>
       </c>
       <c r="M6">
-        <v>9.369999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>515.54</v>
+        <v>518.8</v>
       </c>
       <c r="Q6">
-        <v>527.89</v>
+        <v>526.52</v>
       </c>
       <c r="R6">
-        <v>544.37</v>
+        <v>543.65</v>
       </c>
       <c r="S6">
-        <v>522.0700000000001</v>
+        <v>522.39</v>
       </c>
       <c r="T6">
-        <v>-0.78</v>
+        <v>-0.27</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1458,34 +1467,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.39</v>
+        <v>44.31</v>
       </c>
       <c r="Z6">
-        <v>-8.699999999999999</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="AA6">
-        <v>-8.34</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AB6">
-        <v>-0.36</v>
+        <v>0.16</v>
       </c>
       <c r="AC6">
-        <v>82.69</v>
+        <v>79.03</v>
       </c>
       <c r="AD6">
-        <v>69.39</v>
+        <v>78.23</v>
       </c>
       <c r="AE6">
-        <v>11.94</v>
+        <v>11.79</v>
       </c>
       <c r="AF6">
-        <v>-46.8</v>
+        <v>-7.92</v>
       </c>
       <c r="AG6">
-        <v>553.4</v>
+        <v>550.27</v>
       </c>
       <c r="AH6">
-        <v>502.38</v>
+        <v>502.76</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1494,7 +1503,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>16.32</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1514,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11219</v>
+        <v>11333</v>
       </c>
       <c r="D7">
-        <v>0.12</v>
+        <v>1.02</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1517,25 +1526,25 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.38</v>
+        <v>-48.87</v>
       </c>
       <c r="H7">
-        <v>5.29</v>
+        <v>6.36</v>
       </c>
       <c r="I7">
-        <v>2.3</v>
+        <v>3.64</v>
       </c>
       <c r="J7">
-        <v>-0.62</v>
+        <v>1.54</v>
       </c>
       <c r="K7">
-        <v>-8.710000000000001</v>
+        <v>-7.16</v>
       </c>
       <c r="L7">
-        <v>-40.08</v>
+        <v>-38.66</v>
       </c>
       <c r="M7">
-        <v>18.75</v>
+        <v>19.08</v>
       </c>
       <c r="N7">
         <v>12</v>
@@ -1544,22 +1553,22 @@
         <v>19</v>
       </c>
       <c r="P7">
-        <v>11157.4</v>
+        <v>11237</v>
       </c>
       <c r="Q7">
-        <v>11433.3</v>
+        <v>11427.65</v>
       </c>
       <c r="R7">
-        <v>11428.5</v>
+        <v>11430.92</v>
       </c>
       <c r="S7">
-        <v>14329.22</v>
+        <v>14280.76</v>
       </c>
       <c r="T7">
-        <v>-21.71</v>
+        <v>-20.64</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
         <v>48</v>
@@ -1568,37 +1577,37 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>45.56</v>
+        <v>48.41</v>
       </c>
       <c r="Z7">
-        <v>-116.05</v>
+        <v>-103.23</v>
       </c>
       <c r="AA7">
-        <v>-94.28</v>
+        <v>-96.06999999999999</v>
       </c>
       <c r="AB7">
-        <v>-21.77</v>
+        <v>-7.16</v>
       </c>
       <c r="AC7">
-        <v>53.26</v>
+        <v>68.94</v>
       </c>
       <c r="AD7">
-        <v>39.19</v>
+        <v>54.33</v>
       </c>
       <c r="AE7">
-        <v>402.96</v>
+        <v>390.18</v>
       </c>
       <c r="AF7">
-        <v>-62.16</v>
+        <v>-80.25</v>
       </c>
       <c r="AG7">
-        <v>11978.51</v>
+        <v>11974.65</v>
       </c>
       <c r="AH7">
-        <v>10888.09</v>
+        <v>10880.65</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1607,7 +1616,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>16.42</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,10 +1627,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>367.6</v>
+        <v>363.6</v>
       </c>
       <c r="D8">
-        <v>5.15</v>
+        <v>-1.09</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1630,46 +1639,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="H8">
-        <v>56.89</v>
+        <v>55.18</v>
       </c>
       <c r="I8">
-        <v>12.81</v>
+        <v>11.69</v>
       </c>
       <c r="J8">
-        <v>9.5</v>
+        <v>6.88</v>
       </c>
       <c r="K8">
-        <v>16.72</v>
+        <v>7.45</v>
       </c>
       <c r="L8">
-        <v>11.82</v>
+        <v>10.96</v>
       </c>
       <c r="M8">
-        <v>33.26</v>
+        <v>32.74</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>343.53</v>
+        <v>351.14</v>
       </c>
       <c r="Q8">
-        <v>338.86</v>
+        <v>339.84</v>
       </c>
       <c r="R8">
-        <v>335.36</v>
+        <v>335.69</v>
       </c>
       <c r="S8">
-        <v>289.44</v>
+        <v>289.91</v>
       </c>
       <c r="T8">
-        <v>27.01</v>
+        <v>25.42</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1684,43 +1693,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>69.03</v>
+        <v>65.64</v>
       </c>
       <c r="Z8">
-        <v>3.97</v>
+        <v>5.38</v>
       </c>
       <c r="AA8">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AB8">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="AD8">
-        <v>68.23999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="AE8">
-        <v>11.99</v>
+        <v>11.7</v>
       </c>
       <c r="AF8">
-        <v>383.3</v>
+        <v>-22.18</v>
       </c>
       <c r="AG8">
-        <v>358.73</v>
+        <v>362.51</v>
       </c>
       <c r="AH8">
-        <v>318.99</v>
+        <v>317.17</v>
       </c>
       <c r="AI8">
-        <v>327.44</v>
+        <v>331.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>32.53</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1731,10 +1740,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1267</v>
+        <v>1297.8</v>
       </c>
       <c r="D9">
-        <v>-0.13</v>
+        <v>2.43</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1743,46 +1752,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.52</v>
+        <v>-3.22</v>
       </c>
       <c r="H9">
-        <v>17.39</v>
+        <v>20.24</v>
       </c>
       <c r="I9">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="J9">
-        <v>-2.06</v>
+        <v>-2.2</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>5.41</v>
       </c>
       <c r="L9">
-        <v>14.04</v>
+        <v>15.76</v>
       </c>
       <c r="M9">
-        <v>14.33</v>
+        <v>14.93</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P9">
-        <v>1262.7</v>
+        <v>1272.48</v>
       </c>
       <c r="Q9">
-        <v>1295.75</v>
+        <v>1294.62</v>
       </c>
       <c r="R9">
-        <v>1282.33</v>
+        <v>1283.33</v>
       </c>
       <c r="S9">
-        <v>1232.36</v>
+        <v>1233.1</v>
       </c>
       <c r="T9">
-        <v>2.81</v>
+        <v>5.25</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1797,34 +1806,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>45.24</v>
+        <v>53.31</v>
       </c>
       <c r="Z9">
-        <v>-8.220000000000001</v>
+        <v>-5.84</v>
       </c>
       <c r="AA9">
-        <v>-3.15</v>
+        <v>-3.69</v>
       </c>
       <c r="AB9">
-        <v>-5.07</v>
+        <v>-2.15</v>
       </c>
       <c r="AC9">
-        <v>50.01</v>
+        <v>58.26</v>
       </c>
       <c r="AD9">
-        <v>41.94</v>
+        <v>50.32</v>
       </c>
       <c r="AE9">
-        <v>24.41</v>
+        <v>25.31</v>
       </c>
       <c r="AF9">
-        <v>-46.28</v>
+        <v>-13.84</v>
       </c>
       <c r="AG9">
-        <v>1359.22</v>
+        <v>1357.05</v>
       </c>
       <c r="AH9">
-        <v>1232.27</v>
+        <v>1232.19</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1833,7 +1842,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>24.72</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1844,10 +1853,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>77.64</v>
+        <v>79.09</v>
       </c>
       <c r="D10">
-        <v>-3.14</v>
+        <v>1.87</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1856,46 +1865,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-15.1</v>
+        <v>-13.52</v>
       </c>
       <c r="H10">
-        <v>115.19</v>
+        <v>119.21</v>
       </c>
       <c r="I10">
-        <v>-5.07</v>
+        <v>-3.45</v>
       </c>
       <c r="J10">
-        <v>-4.02</v>
+        <v>-6.68</v>
       </c>
       <c r="K10">
-        <v>44.15</v>
+        <v>52.45</v>
       </c>
       <c r="L10">
-        <v>5.66</v>
+        <v>-6.29</v>
       </c>
       <c r="M10">
-        <v>-3.54</v>
+        <v>-3.2</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P10">
-        <v>80.26000000000001</v>
+        <v>79.69</v>
       </c>
       <c r="Q10">
-        <v>81.68000000000001</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="R10">
-        <v>77.26000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="S10">
-        <v>60.69</v>
+        <v>60.77</v>
       </c>
       <c r="T10">
-        <v>27.92</v>
+        <v>30.15</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1910,34 +1919,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>43.5</v>
+        <v>46.85</v>
       </c>
       <c r="Z10">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AB10">
-        <v>-1.01</v>
+        <v>-0.99</v>
       </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD10">
-        <v>7.48</v>
+        <v>5.01</v>
       </c>
       <c r="AE10">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AF10">
-        <v>-65.45</v>
+        <v>-71.69</v>
       </c>
       <c r="AG10">
         <v>86.56999999999999</v>
       </c>
       <c r="AH10">
-        <v>76.78</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1946,7 +1955,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>29.18</v>
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2127,7 +2136,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2139,1022 +2148,1025 @@
         <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>16.41</v>
-      </c>
-      <c r="D8" s="7">
-        <v>13.22</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.19</v>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>8.640000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="D9" s="7">
-        <v>-1.78</v>
+        <v>12.3</v>
       </c>
       <c r="E9" s="8">
-        <v>-10.42</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>1.05</v>
+        <v>-1.78</v>
       </c>
       <c r="D10" s="7">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="E10" s="9">
-        <v>0.12</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>4.6</v>
+        <v>1.17</v>
       </c>
       <c r="D11" s="7">
-        <v>6</v>
+        <v>2.29</v>
       </c>
       <c r="E11" s="9">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-4.61</v>
+        <v>6</v>
       </c>
       <c r="D12" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.34</v>
+        <v>7.99</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-2.27</v>
+        <v>-4.95</v>
       </c>
       <c r="D13" s="7">
-        <v>-0.62</v>
+        <v>-4.35</v>
       </c>
       <c r="E13" s="9">
-        <v>1.65</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>5.99</v>
+        <v>-0.62</v>
       </c>
       <c r="D14" s="7">
-        <v>9.5</v>
+        <v>1.54</v>
       </c>
       <c r="E14" s="9">
-        <v>3.51</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-2.39</v>
+        <v>9.5</v>
       </c>
       <c r="D15" s="7">
-        <v>-2.06</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.33</v>
+        <v>6.88</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.2</v>
+        <v>-2.06</v>
       </c>
       <c r="D16" s="7">
-        <v>-4.02</v>
+        <v>-2.2</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.82</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>10.46</v>
+        <v>-4.02</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.17</v>
+        <v>-6.68</v>
       </c>
       <c r="E17" s="8">
-        <v>-12.63</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-6.06</v>
+        <v>-2.17</v>
       </c>
       <c r="D18" s="7">
-        <v>-0.88</v>
-      </c>
-      <c r="E18" s="9">
-        <v>5.18</v>
+        <v>-3.66</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>0.9</v>
+        <v>-0.88</v>
       </c>
       <c r="D19" s="7">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="E19" s="9">
-        <v>3.3</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-0.61</v>
+        <v>4.2</v>
       </c>
       <c r="D20" s="7">
-        <v>2.75</v>
+        <v>6.55</v>
       </c>
       <c r="E20" s="9">
-        <v>3.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-1.8</v>
+        <v>2.75</v>
       </c>
       <c r="D21" s="7">
-        <v>2.57</v>
+        <v>3.79</v>
       </c>
       <c r="E21" s="9">
-        <v>4.37</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.13</v>
+        <v>2.57</v>
       </c>
       <c r="D22" s="7">
-        <v>2.3</v>
+        <v>3.23</v>
       </c>
       <c r="E22" s="9">
-        <v>4.43</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="D23" s="7">
-        <v>12.81</v>
+        <v>3.64</v>
       </c>
       <c r="E23" s="9">
-        <v>10.93</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>0.28</v>
+        <v>12.81</v>
       </c>
       <c r="D24" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.8</v>
+        <v>11.69</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-6.5</v>
+        <v>3.08</v>
       </c>
       <c r="D25" s="7">
-        <v>-5.07</v>
+        <v>3.92</v>
       </c>
       <c r="E25" s="9">
-        <v>1.43</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>24.43</v>
+        <v>-5.07</v>
       </c>
       <c r="D26" s="7">
-        <v>20.02</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-4.41</v>
+        <v>-3.45</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>40.8</v>
+        <v>20.02</v>
       </c>
       <c r="D27" s="7">
-        <v>37.21</v>
+        <v>18.08</v>
       </c>
       <c r="E27" s="8">
-        <v>-3.59</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>7.33</v>
+        <v>37.21</v>
       </c>
       <c r="D28" s="7">
-        <v>10.39</v>
+        <v>41.12</v>
       </c>
       <c r="E28" s="9">
-        <v>3.06</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>-0.18</v>
+        <v>10.39</v>
       </c>
       <c r="D29" s="7">
-        <v>-2.13</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.95</v>
+        <v>12.18</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>-3.94</v>
+        <v>-2.13</v>
       </c>
       <c r="D30" s="7">
-        <v>-2.85</v>
+        <v>-0.36</v>
       </c>
       <c r="E30" s="9">
-        <v>1.09</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-39.55</v>
+        <v>-2.85</v>
       </c>
       <c r="D31" s="7">
-        <v>-40.08</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.53</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>7.17</v>
+        <v>-40.08</v>
       </c>
       <c r="D32" s="7">
-        <v>11.82</v>
+        <v>-38.66</v>
       </c>
       <c r="E32" s="9">
-        <v>4.65</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>13.76</v>
+        <v>11.82</v>
       </c>
       <c r="D33" s="7">
-        <v>14.04</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.28</v>
+        <v>10.96</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>9.57</v>
+        <v>14.04</v>
       </c>
       <c r="D34" s="7">
-        <v>5.66</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.91</v>
+        <v>15.76</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.72</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>10.74</v>
+        <v>5.66</v>
       </c>
       <c r="D35" s="7">
-        <v>12.93</v>
-      </c>
-      <c r="E35" s="9">
-        <v>2.19</v>
+        <v>-6.29</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-11.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>14.6</v>
+        <v>12.93</v>
       </c>
       <c r="D36" s="7">
-        <v>11.11</v>
+        <v>8.65</v>
       </c>
       <c r="E36" s="8">
-        <v>-3.49</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-0.12</v>
+        <v>11.11</v>
       </c>
       <c r="D37" s="7">
-        <v>5.39</v>
+        <v>13.38</v>
       </c>
       <c r="E37" s="9">
-        <v>5.51</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>6.02</v>
+        <v>5.39</v>
       </c>
       <c r="D38" s="7">
-        <v>7.53</v>
+        <v>7.86</v>
       </c>
       <c r="E38" s="9">
-        <v>1.51</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-11.18</v>
+        <v>7.53</v>
       </c>
       <c r="D39" s="7">
-        <v>-8.949999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E39" s="9">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-11.09</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D40" s="7">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="E40" s="9">
-        <v>2.38</v>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>13.86</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="D41" s="7">
-        <v>16.72</v>
+        <v>-7.16</v>
       </c>
       <c r="E41" s="9">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.08</v>
+        <v>16.72</v>
       </c>
       <c r="D42" s="7">
-        <v>2</v>
-      </c>
-      <c r="E42" s="9">
-        <v>3.08</v>
+        <v>7.45</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-9.27</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>48.61</v>
+        <v>2</v>
       </c>
       <c r="D43" s="7">
-        <v>44.15</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-4.46</v>
+        <v>5.41</v>
+      </c>
+      <c r="E43" s="9">
+        <v>3.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>-26.41</v>
+        <v>44.15</v>
       </c>
       <c r="D44" s="7">
-        <v>-28.35</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.94</v>
+        <v>52.45</v>
+      </c>
+      <c r="E44" s="9">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-7.7</v>
+        <v>-28.35</v>
       </c>
       <c r="D45" s="7">
-        <v>-9.779999999999999</v>
+        <v>-29.02</v>
       </c>
       <c r="E45" s="8">
-        <v>-2.08</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-12.27</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="D46" s="7">
-        <v>-11.47</v>
+        <v>-7.84</v>
       </c>
       <c r="E46" s="9">
-        <v>0.8</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-13.08</v>
+        <v>-11.47</v>
       </c>
       <c r="D47" s="7">
-        <v>-14.01</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.93</v>
+        <v>-8.81</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.66</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-13.83</v>
+        <v>-14.01</v>
       </c>
       <c r="D48" s="7">
-        <v>-13.67</v>
+        <v>-12.26</v>
       </c>
       <c r="E48" s="9">
-        <v>0.16</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-49.45</v>
+        <v>-13.67</v>
       </c>
       <c r="D49" s="7">
-        <v>-49.38</v>
+        <v>-13.17</v>
       </c>
       <c r="E49" s="9">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-0.46</v>
+        <v>-49.38</v>
       </c>
       <c r="D50" s="7">
-        <v>0</v>
+        <v>-48.87</v>
       </c>
       <c r="E50" s="9">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="D51" s="7">
-        <v>-5.52</v>
+        <v>-1.09</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.12</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-12.35</v>
+        <v>-5.52</v>
       </c>
       <c r="D52" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-2.75</v>
+        <v>-3.22</v>
+      </c>
+      <c r="E52" s="9">
+        <v>2.3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>741.5</v>
+        <v>-15.1</v>
       </c>
       <c r="D53" s="7">
-        <v>721.9</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-19.6</v>
+        <v>-13.52</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1.58</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>293.05</v>
+        <v>721.9</v>
       </c>
       <c r="D54" s="7">
-        <v>286.45</v>
+        <v>715.2</v>
       </c>
       <c r="E54" s="8">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>1130.6</v>
+        <v>286.45</v>
       </c>
       <c r="D55" s="7">
-        <v>1141</v>
+        <v>292.6</v>
       </c>
       <c r="E55" s="9">
-        <v>10.4</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>751.45</v>
+        <v>1141</v>
       </c>
       <c r="D56" s="7">
-        <v>743.45</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-8</v>
+        <v>1175.3</v>
+      </c>
+      <c r="E56" s="9">
+        <v>34.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>517</v>
+        <v>743.45</v>
       </c>
       <c r="D57" s="7">
-        <v>518</v>
+        <v>758.55</v>
       </c>
       <c r="E57" s="9">
-        <v>1</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>11205</v>
+        <v>518</v>
       </c>
       <c r="D58" s="7">
-        <v>11219</v>
+        <v>521</v>
       </c>
       <c r="E58" s="9">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>349.6</v>
+        <v>11219</v>
       </c>
       <c r="D59" s="7">
-        <v>367.6</v>
+        <v>11333</v>
       </c>
       <c r="E59" s="9">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>1268.6</v>
+        <v>367.6</v>
       </c>
       <c r="D60" s="7">
-        <v>1267</v>
+        <v>363.6</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>80.16</v>
+        <v>1267</v>
       </c>
       <c r="D61" s="7">
-        <v>77.64</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-2.52</v>
+        <v>1297.8</v>
+      </c>
+      <c r="E61" s="9">
+        <v>30.8</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>99</v>
+        <v>77.64</v>
       </c>
       <c r="D62" s="7">
-        <v>88</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
+        <v>79.09</v>
+      </c>
+      <c r="E62" s="9">
+        <v>1.45</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="7">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="D63" s="7">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E63" s="9">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="D64" s="7">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="E64" s="8">
         <v>-11</v>
@@ -3162,348 +3174,314 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>55</v>
+        <v>59.08</v>
       </c>
       <c r="D65" s="7">
-        <v>45</v>
+        <v>57.13</v>
       </c>
       <c r="E65" s="8">
-        <v>-10</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>88</v>
+        <v>46.1</v>
       </c>
       <c r="D66" s="7">
-        <v>99</v>
+        <v>50.16</v>
       </c>
       <c r="E66" s="9">
-        <v>11</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>65.11</v>
+        <v>53.35</v>
       </c>
       <c r="D67" s="7">
-        <v>59.08</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-6.03</v>
+        <v>60.96</v>
+      </c>
+      <c r="E67" s="9">
+        <v>7.61</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>50.18</v>
+        <v>53</v>
       </c>
       <c r="D68" s="7">
-        <v>46.1</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-4.08</v>
+        <v>57.66</v>
+      </c>
+      <c r="E68" s="9">
+        <v>4.66</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>50.64</v>
+        <v>42.39</v>
       </c>
       <c r="D69" s="7">
-        <v>53.35</v>
+        <v>44.31</v>
       </c>
       <c r="E69" s="9">
-        <v>2.71</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>56.04</v>
+        <v>45.56</v>
       </c>
       <c r="D70" s="7">
-        <v>53</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-3.04</v>
+        <v>48.41</v>
+      </c>
+      <c r="E70" s="9">
+        <v>2.85</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>41.76</v>
+        <v>69.03</v>
       </c>
       <c r="D71" s="7">
-        <v>42.39</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0.63</v>
+        <v>65.64</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>45.22</v>
+        <v>45.24</v>
       </c>
       <c r="D72" s="7">
-        <v>45.56</v>
+        <v>53.31</v>
       </c>
       <c r="E72" s="9">
-        <v>0.34</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>60.52</v>
+        <v>43.5</v>
       </c>
       <c r="D73" s="7">
-        <v>69.03</v>
+        <v>46.85</v>
       </c>
       <c r="E73" s="9">
-        <v>8.51</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>45.62</v>
+        <v>-69.55</v>
       </c>
       <c r="D74" s="7">
-        <v>45.24</v>
+        <v>-76.88</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.38</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>48.43</v>
+        <v>-75.39</v>
       </c>
       <c r="D75" s="7">
-        <v>43.5</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-4.93</v>
+        <v>-56.36</v>
+      </c>
+      <c r="E75" s="9">
+        <v>19.03</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-24.87</v>
+        <v>15.91</v>
       </c>
       <c r="D76" s="7">
-        <v>-69.55</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-44.68</v>
+        <v>30.25</v>
+      </c>
+      <c r="E76" s="9">
+        <v>14.34</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-68.94</v>
+        <v>-18.63</v>
       </c>
       <c r="D77" s="7">
-        <v>-75.39</v>
+        <v>-19.04</v>
       </c>
       <c r="E77" s="8">
-        <v>-6.45</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-9.44</v>
+        <v>-46.8</v>
       </c>
       <c r="D78" s="7">
-        <v>15.91</v>
+        <v>-7.92</v>
       </c>
       <c r="E78" s="9">
-        <v>25.35</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-1.84</v>
+        <v>-62.16</v>
       </c>
       <c r="D79" s="7">
-        <v>-18.63</v>
+        <v>-80.25</v>
       </c>
       <c r="E79" s="8">
-        <v>-16.79</v>
+        <v>-18.09</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>-19.26</v>
+        <v>383.3</v>
       </c>
       <c r="D80" s="7">
-        <v>-46.8</v>
+        <v>-22.18</v>
       </c>
       <c r="E80" s="8">
-        <v>-27.54</v>
+        <v>-405.48</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>-85.13</v>
+        <v>-46.28</v>
       </c>
       <c r="D81" s="7">
-        <v>-62.16</v>
+        <v>-13.84</v>
       </c>
       <c r="E81" s="9">
-        <v>22.97</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="7">
-        <v>26.3</v>
+        <v>-65.45</v>
       </c>
       <c r="D82" s="7">
-        <v>383.3</v>
-      </c>
-      <c r="E82" s="9">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-46.01</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-46.28</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-83.33</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-65.45</v>
-      </c>
-      <c r="E84" s="9">
-        <v>17.88</v>
+        <v>-71.69</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-6.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3527,28 +3505,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3556,22 +3534,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>60.16</v>
+        <v>64.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>50.8</v>
+        <v>53.8</v>
       </c>
       <c r="E2" s="12">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F2" s="12">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G2" s="12">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3708,31 +3686,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3914</v>
+        <v>0.397</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3623</v>
+        <v>0.365</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3326</v>
+        <v>0.3274</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2589</v>
+        <v>0.2629</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1875</v>
+        <v>0.1908</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1433</v>
+        <v>0.1493</v>
       </c>
       <c r="G2" s="15">
-        <v>0.09369999999999999</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0354</v>
+        <v>-0.032</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.0591</v>
+        <v>-0.0634</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,34 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.1 → 50.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>50.2 → 44.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.2</t>
   </si>
   <si>
-    <t>45.2 → 53.3</t>
-  </si>
-  <si>
-    <t>45.2</t>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>53.3 → 47.3</t>
   </si>
   <si>
     <t>53.3</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>47.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -433,11 +424,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -949,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>715.2</v>
+        <v>699.8</v>
       </c>
       <c r="D2">
-        <v>-0.93</v>
+        <v>-2.15</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -961,22 +951,22 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-29.02</v>
+        <v>-30.55</v>
       </c>
       <c r="H2">
-        <v>94.77</v>
+        <v>90.58</v>
       </c>
       <c r="I2">
-        <v>-3.66</v>
+        <v>-3.61</v>
       </c>
       <c r="J2">
-        <v>12.3</v>
+        <v>8.23</v>
       </c>
       <c r="K2">
-        <v>8.65</v>
+        <v>8.77</v>
       </c>
       <c r="L2">
-        <v>18.08</v>
+        <v>15.53</v>
       </c>
       <c r="M2">
         <v>-6.34</v>
@@ -988,19 +978,19 @@
         <v>76</v>
       </c>
       <c r="P2">
-        <v>724.61</v>
+        <v>719.37</v>
       </c>
       <c r="Q2">
-        <v>689.67</v>
+        <v>692.59</v>
       </c>
       <c r="R2">
-        <v>661.6799999999999</v>
+        <v>662.16</v>
       </c>
       <c r="S2">
-        <v>634.5700000000001</v>
+        <v>635.52</v>
       </c>
       <c r="T2">
-        <v>12.71</v>
+        <v>10.11</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1015,34 +1005,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>57.13</v>
+        <v>52.82</v>
       </c>
       <c r="Z2">
-        <v>20.25</v>
+        <v>17.97</v>
       </c>
       <c r="AA2">
-        <v>17.32</v>
+        <v>17.45</v>
       </c>
       <c r="AB2">
-        <v>2.93</v>
+        <v>0.52</v>
       </c>
       <c r="AC2">
-        <v>46.18</v>
+        <v>20.56</v>
       </c>
       <c r="AD2">
-        <v>59.8</v>
+        <v>42.27</v>
       </c>
       <c r="AE2">
-        <v>32.03</v>
+        <v>31.19</v>
       </c>
       <c r="AF2">
-        <v>-76.88</v>
+        <v>-79.23</v>
       </c>
       <c r="AG2">
-        <v>760.98</v>
+        <v>760.27</v>
       </c>
       <c r="AH2">
-        <v>618.36</v>
+        <v>624.91</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1051,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>55.93</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1062,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>292.6</v>
+        <v>283.1</v>
       </c>
       <c r="D3">
-        <v>2.15</v>
+        <v>-3.25</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1074,46 +1064,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-7.84</v>
+        <v>-10.83</v>
       </c>
       <c r="H3">
-        <v>90.95</v>
+        <v>84.75</v>
       </c>
       <c r="I3">
-        <v>4.04</v>
+        <v>-2.78</v>
       </c>
       <c r="J3">
-        <v>1.86</v>
+        <v>0.48</v>
       </c>
       <c r="K3">
-        <v>13.38</v>
+        <v>8.58</v>
       </c>
       <c r="L3">
-        <v>41.12</v>
+        <v>34.46</v>
       </c>
       <c r="M3">
-        <v>39.7</v>
+        <v>39.47</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>290.56</v>
+        <v>288.94</v>
       </c>
       <c r="Q3">
-        <v>302.37</v>
+        <v>301.4</v>
       </c>
       <c r="R3">
-        <v>280.83</v>
+        <v>281.38</v>
       </c>
       <c r="S3">
-        <v>223.85</v>
+        <v>224.47</v>
       </c>
       <c r="T3">
-        <v>30.71</v>
+        <v>26.12</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1128,34 +1118,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.16</v>
+        <v>44.57</v>
       </c>
       <c r="Z3">
-        <v>2.16</v>
+        <v>1.06</v>
       </c>
       <c r="AA3">
-        <v>5.52</v>
+        <v>4.63</v>
       </c>
       <c r="AB3">
-        <v>-3.35</v>
+        <v>-3.56</v>
       </c>
       <c r="AC3">
-        <v>21.77</v>
+        <v>15.61</v>
       </c>
       <c r="AD3">
-        <v>21.1</v>
+        <v>18.87</v>
       </c>
       <c r="AE3">
-        <v>11.28</v>
+        <v>11.37</v>
       </c>
       <c r="AF3">
-        <v>-56.36</v>
+        <v>-68.86</v>
       </c>
       <c r="AG3">
-        <v>323.75</v>
+        <v>324.46</v>
       </c>
       <c r="AH3">
-        <v>280.98</v>
+        <v>278.34</v>
       </c>
       <c r="AI3">
         <v>320.41</v>
@@ -1164,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.37</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1175,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1175.3</v>
+        <v>1157.8</v>
       </c>
       <c r="D4">
-        <v>3.01</v>
+        <v>-1.49</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1187,46 +1177,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-8.81</v>
+        <v>-10.16</v>
       </c>
       <c r="H4">
-        <v>19.2</v>
+        <v>17.42</v>
       </c>
       <c r="I4">
-        <v>6.55</v>
+        <v>2.61</v>
       </c>
       <c r="J4">
-        <v>2.29</v>
+        <v>0.32</v>
       </c>
       <c r="K4">
-        <v>7.86</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L4">
-        <v>12.18</v>
+        <v>10.69</v>
       </c>
       <c r="M4">
-        <v>26.29</v>
+        <v>26.74</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>72</v>
       </c>
       <c r="P4">
-        <v>1138.96</v>
+        <v>1144.84</v>
       </c>
       <c r="Q4">
-        <v>1146.4</v>
+        <v>1145.52</v>
       </c>
       <c r="R4">
-        <v>1111.13</v>
+        <v>1113.44</v>
       </c>
       <c r="S4">
-        <v>1134.11</v>
+        <v>1134.86</v>
       </c>
       <c r="T4">
-        <v>3.63</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1241,34 +1231,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>60.96</v>
+        <v>55.95</v>
       </c>
       <c r="Z4">
-        <v>4.78</v>
+        <v>6.03</v>
       </c>
       <c r="AA4">
-        <v>4.87</v>
+        <v>5.1</v>
       </c>
       <c r="AB4">
-        <v>-0.09</v>
+        <v>0.93</v>
       </c>
       <c r="AC4">
-        <v>73.73</v>
+        <v>81.22</v>
       </c>
       <c r="AD4">
-        <v>52.46</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="AE4">
-        <v>30.38</v>
+        <v>29.86</v>
       </c>
       <c r="AF4">
-        <v>30.25</v>
+        <v>-22.05</v>
       </c>
       <c r="AG4">
-        <v>1198.49</v>
+        <v>1196.12</v>
       </c>
       <c r="AH4">
-        <v>1094.3</v>
+        <v>1094.91</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1277,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>30.1</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1288,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>758.55</v>
+        <v>738.95</v>
       </c>
       <c r="D5">
-        <v>2.03</v>
+        <v>-2.58</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1300,46 +1290,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-12.26</v>
+        <v>-14.53</v>
       </c>
       <c r="H5">
-        <v>14.6</v>
+        <v>11.64</v>
       </c>
       <c r="I5">
-        <v>3.79</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>7.99</v>
+        <v>5.35</v>
       </c>
       <c r="K5">
-        <v>9.140000000000001</v>
+        <v>6.32</v>
       </c>
       <c r="L5">
-        <v>-0.36</v>
+        <v>-5.02</v>
       </c>
       <c r="M5">
-        <v>36.5</v>
+        <v>36.22</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>745.77</v>
+        <v>748.67</v>
       </c>
       <c r="Q5">
-        <v>736.54</v>
+        <v>737.84</v>
       </c>
       <c r="R5">
-        <v>732.0700000000001</v>
+        <v>732.36</v>
       </c>
       <c r="S5">
-        <v>748.25</v>
+        <v>748.17</v>
       </c>
       <c r="T5">
-        <v>1.38</v>
+        <v>-1.23</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1351,37 +1341,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>57.66</v>
+        <v>50.64</v>
       </c>
       <c r="Z5">
-        <v>6.5</v>
+        <v>5.64</v>
       </c>
       <c r="AA5">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="AB5">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="AC5">
-        <v>32.13</v>
+        <v>25.53</v>
       </c>
       <c r="AD5">
-        <v>33.78</v>
+        <v>30.78</v>
       </c>
       <c r="AE5">
-        <v>21.63</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>-19.04</v>
+        <v>-35.53</v>
       </c>
       <c r="AG5">
-        <v>778.27</v>
+        <v>778.0700000000001</v>
       </c>
       <c r="AH5">
-        <v>694.8</v>
+        <v>697.61</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1390,7 +1380,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.22</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1401,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D6">
-        <v>0.58</v>
+        <v>-2.11</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1413,46 +1403,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-13.17</v>
+        <v>-15</v>
       </c>
       <c r="H6">
-        <v>18.8</v>
+        <v>16.29</v>
       </c>
       <c r="I6">
-        <v>3.23</v>
+        <v>-0.39</v>
       </c>
       <c r="J6">
-        <v>-4.35</v>
+        <v>-7</v>
       </c>
       <c r="K6">
-        <v>-9.300000000000001</v>
+        <v>-11.07</v>
       </c>
       <c r="L6">
-        <v>-2.79</v>
+        <v>-6.19</v>
       </c>
       <c r="M6">
-        <v>8.779999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>518.8</v>
+        <v>518.4</v>
       </c>
       <c r="Q6">
-        <v>526.52</v>
+        <v>524.84</v>
       </c>
       <c r="R6">
-        <v>543.65</v>
+        <v>542.85</v>
       </c>
       <c r="S6">
-        <v>522.39</v>
+        <v>522.63</v>
       </c>
       <c r="T6">
-        <v>-0.27</v>
+        <v>-2.42</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1467,34 +1457,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>44.31</v>
+        <v>39.15</v>
       </c>
       <c r="Z6">
-        <v>-8.130000000000001</v>
+        <v>-8.48</v>
       </c>
       <c r="AA6">
-        <v>-8.300000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="AB6">
-        <v>0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>79.03</v>
+        <v>71.88</v>
       </c>
       <c r="AD6">
-        <v>78.23</v>
+        <v>77.87</v>
       </c>
       <c r="AE6">
-        <v>11.79</v>
+        <v>11.87</v>
       </c>
       <c r="AF6">
-        <v>-7.92</v>
+        <v>-39.26</v>
       </c>
       <c r="AG6">
-        <v>550.27</v>
+        <v>548.28</v>
       </c>
       <c r="AH6">
-        <v>502.76</v>
+        <v>501.41</v>
       </c>
       <c r="AI6">
         <v>543.8</v>
@@ -1503,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>15.3</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1514,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11333</v>
+        <v>11116</v>
       </c>
       <c r="D7">
-        <v>1.02</v>
+        <v>-1.91</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1526,46 +1516,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.87</v>
+        <v>-49.85</v>
       </c>
       <c r="H7">
-        <v>6.36</v>
+        <v>4.33</v>
       </c>
       <c r="I7">
-        <v>3.64</v>
+        <v>-0.27</v>
       </c>
       <c r="J7">
-        <v>1.54</v>
+        <v>-2.88</v>
       </c>
       <c r="K7">
-        <v>-7.16</v>
+        <v>-8.51</v>
       </c>
       <c r="L7">
-        <v>-38.66</v>
+        <v>-39.94</v>
       </c>
       <c r="M7">
-        <v>19.08</v>
+        <v>18.48</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>11237</v>
+        <v>11231</v>
       </c>
       <c r="Q7">
-        <v>11427.65</v>
+        <v>11391.85</v>
       </c>
       <c r="R7">
-        <v>11430.92</v>
+        <v>11429.94</v>
       </c>
       <c r="S7">
-        <v>14280.76</v>
+        <v>14234.94</v>
       </c>
       <c r="T7">
-        <v>-20.64</v>
+        <v>-21.91</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1580,34 +1570,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.41</v>
+        <v>43.72</v>
       </c>
       <c r="Z7">
-        <v>-103.23</v>
+        <v>-109.32</v>
       </c>
       <c r="AA7">
-        <v>-96.06999999999999</v>
+        <v>-98.72</v>
       </c>
       <c r="AB7">
-        <v>-7.16</v>
+        <v>-10.6</v>
       </c>
       <c r="AC7">
-        <v>68.94</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="AD7">
-        <v>54.33</v>
+        <v>63.8</v>
       </c>
       <c r="AE7">
-        <v>390.18</v>
+        <v>382.45</v>
       </c>
       <c r="AF7">
-        <v>-80.25</v>
+        <v>-81.91</v>
       </c>
       <c r="AG7">
-        <v>11974.65</v>
+        <v>11920.85</v>
       </c>
       <c r="AH7">
-        <v>10880.65</v>
+        <v>10862.85</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1616,7 +1606,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>14.33</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1627,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>363.6</v>
+        <v>360.7</v>
       </c>
       <c r="D8">
-        <v>-1.09</v>
+        <v>-0.8</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1639,46 +1629,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.09</v>
+        <v>-1.88</v>
       </c>
       <c r="H8">
-        <v>55.18</v>
+        <v>53.94</v>
       </c>
       <c r="I8">
-        <v>11.69</v>
+        <v>10.42</v>
       </c>
       <c r="J8">
-        <v>6.88</v>
+        <v>4.87</v>
       </c>
       <c r="K8">
-        <v>7.45</v>
+        <v>9.34</v>
       </c>
       <c r="L8">
-        <v>10.96</v>
+        <v>7.42</v>
       </c>
       <c r="M8">
-        <v>32.74</v>
+        <v>32.35</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>351.14</v>
+        <v>357.95</v>
       </c>
       <c r="Q8">
-        <v>339.84</v>
+        <v>340.63</v>
       </c>
       <c r="R8">
-        <v>335.69</v>
+        <v>336.15</v>
       </c>
       <c r="S8">
-        <v>289.91</v>
+        <v>290.37</v>
       </c>
       <c r="T8">
-        <v>25.42</v>
+        <v>24.22</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1693,34 +1683,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>65.64</v>
+        <v>63.22</v>
       </c>
       <c r="Z8">
-        <v>5.38</v>
+        <v>6.19</v>
       </c>
       <c r="AA8">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AB8">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC8">
-        <v>95.79000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AD8">
-        <v>88.27</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="AE8">
-        <v>11.7</v>
+        <v>11.72</v>
       </c>
       <c r="AF8">
-        <v>-22.18</v>
+        <v>2.5</v>
       </c>
       <c r="AG8">
-        <v>362.51</v>
+        <v>365.07</v>
       </c>
       <c r="AH8">
-        <v>317.17</v>
+        <v>316.18</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1729,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.74</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1740,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1297.8</v>
+        <v>1273.2</v>
       </c>
       <c r="D9">
-        <v>2.43</v>
+        <v>-1.9</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1752,46 +1742,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-3.22</v>
+        <v>-5.06</v>
       </c>
       <c r="H9">
-        <v>20.24</v>
+        <v>17.97</v>
       </c>
       <c r="I9">
-        <v>3.92</v>
+        <v>1.58</v>
       </c>
       <c r="J9">
-        <v>-2.2</v>
+        <v>-3.57</v>
       </c>
       <c r="K9">
-        <v>5.41</v>
+        <v>3.43</v>
       </c>
       <c r="L9">
-        <v>15.76</v>
+        <v>13.4</v>
       </c>
       <c r="M9">
-        <v>14.93</v>
+        <v>15.11</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P9">
-        <v>1272.48</v>
+        <v>1276.44</v>
       </c>
       <c r="Q9">
-        <v>1294.62</v>
+        <v>1291.23</v>
       </c>
       <c r="R9">
-        <v>1283.33</v>
+        <v>1284.26</v>
       </c>
       <c r="S9">
-        <v>1233.1</v>
+        <v>1233.65</v>
       </c>
       <c r="T9">
-        <v>5.25</v>
+        <v>3.21</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1806,34 +1796,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>53.31</v>
+        <v>47.31</v>
       </c>
       <c r="Z9">
-        <v>-5.84</v>
+        <v>-5.87</v>
       </c>
       <c r="AA9">
-        <v>-3.69</v>
+        <v>-4.12</v>
       </c>
       <c r="AB9">
-        <v>-2.15</v>
+        <v>-1.75</v>
       </c>
       <c r="AC9">
-        <v>58.26</v>
+        <v>60.56</v>
       </c>
       <c r="AD9">
-        <v>50.32</v>
+        <v>56.28</v>
       </c>
       <c r="AE9">
-        <v>25.31</v>
+        <v>25.38</v>
       </c>
       <c r="AF9">
-        <v>-13.84</v>
+        <v>-42.87</v>
       </c>
       <c r="AG9">
-        <v>1357.05</v>
+        <v>1350.33</v>
       </c>
       <c r="AH9">
-        <v>1232.19</v>
+        <v>1232.13</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1842,7 +1832,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>24.53</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1853,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>79.09</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="D10">
-        <v>1.87</v>
+        <v>-3.09</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1865,46 +1855,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-13.52</v>
+        <v>-16.18</v>
       </c>
       <c r="H10">
-        <v>119.21</v>
+        <v>112.44</v>
       </c>
       <c r="I10">
-        <v>-3.45</v>
+        <v>-5</v>
       </c>
       <c r="J10">
-        <v>-6.68</v>
+        <v>-6.38</v>
       </c>
       <c r="K10">
-        <v>52.45</v>
+        <v>47.09</v>
       </c>
       <c r="L10">
-        <v>-6.29</v>
+        <v>-10.73</v>
       </c>
       <c r="M10">
-        <v>-3.2</v>
+        <v>-4.57</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P10">
-        <v>79.69</v>
+        <v>78.89</v>
       </c>
       <c r="Q10">
-        <v>81.54000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="R10">
-        <v>77.8</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="S10">
-        <v>60.77</v>
+        <v>60.84</v>
       </c>
       <c r="T10">
-        <v>30.15</v>
+        <v>25.98</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1919,34 +1909,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>46.85</v>
+        <v>42.3</v>
       </c>
       <c r="Z10">
-        <v>0.35</v>
+        <v>-0.02</v>
       </c>
       <c r="AA10">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AB10">
-        <v>-0.99</v>
+        <v>-1.09</v>
       </c>
       <c r="AC10">
         <v>6.8</v>
       </c>
       <c r="AD10">
-        <v>5.01</v>
+        <v>5.6</v>
       </c>
       <c r="AE10">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="AF10">
-        <v>-71.69</v>
+        <v>-38.46</v>
       </c>
       <c r="AG10">
-        <v>86.56999999999999</v>
+        <v>86.78</v>
       </c>
       <c r="AH10">
-        <v>76.51000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1955,7 +1945,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>32.8</v>
+        <v>36.81</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2174,1314 +2164,1294 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>12.3</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8.23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.86</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2.29</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>7.99</v>
+      </c>
+      <c r="D11" s="6">
+        <v>5.35</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.54</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>6.88</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4.87</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.2</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.57</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.68</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-6.38</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.66</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.61</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>4.04</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-6.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>6.55</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-3.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3.79</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3.23</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3.64</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-0.27</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>11.69</v>
+      </c>
+      <c r="D23" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3.92</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>18.08</v>
+      </c>
+      <c r="D26" s="6">
+        <v>15.53</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>41.12</v>
+      </c>
+      <c r="D27" s="6">
+        <v>34.46</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-6.66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.18</v>
+      </c>
+      <c r="D28" s="6">
+        <v>10.69</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-5.02</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-2.79</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.19</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-38.66</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-39.94</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>10.96</v>
+      </c>
+      <c r="D32" s="6">
+        <v>7.42</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>15.76</v>
+      </c>
+      <c r="D33" s="6">
+        <v>13.4</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-6.29</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>8.65</v>
+      </c>
+      <c r="D35" s="6">
+        <v>8.77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>13.38</v>
+      </c>
+      <c r="D36" s="6">
+        <v>8.58</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-4.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>7.86</v>
+      </c>
+      <c r="D37" s="6">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="D38" s="6">
+        <v>6.32</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-11.07</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-7.16</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="D41" s="6">
+        <v>9.34</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>5.41</v>
+      </c>
+      <c r="D42" s="6">
+        <v>3.43</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>52.45</v>
+      </c>
+      <c r="D43" s="6">
+        <v>47.09</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-5.36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-29.02</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-30.55</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-7.84</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-10.83</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-8.81</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-10.16</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-12.26</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-14.53</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-13.17</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-15</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-48.87</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-49.85</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-3.22</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-13.52</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-16.18</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>715.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>699.8</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-15.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>292.6</v>
+      </c>
+      <c r="D54" s="6">
+        <v>283.1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-9.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1175.3</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1157.8</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-17.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>758.55</v>
+      </c>
+      <c r="D56" s="6">
+        <v>738.95</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-19.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>521</v>
+      </c>
+      <c r="D57" s="6">
+        <v>510</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>11333</v>
+      </c>
+      <c r="D58" s="6">
+        <v>11116</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-217</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>363.6</v>
+      </c>
+      <c r="D59" s="6">
+        <v>360.7</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1297.8</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1273.2</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-24.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>79.09</v>
+      </c>
+      <c r="D61" s="6">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>55</v>
+      </c>
+      <c r="D62" s="6">
         <v>66</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="E62" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>66</v>
+      </c>
+      <c r="D63" s="6">
+        <v>55</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>13.22</v>
-      </c>
-      <c r="D9" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>57.13</v>
+      </c>
+      <c r="D64" s="6">
+        <v>52.82</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-1.78</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.86</v>
-      </c>
-      <c r="E10" s="9">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>50.16</v>
+      </c>
+      <c r="D65" s="6">
+        <v>44.57</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-5.59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1.17</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2.29</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>60.96</v>
+      </c>
+      <c r="D66" s="6">
+        <v>55.95</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>6</v>
-      </c>
-      <c r="D12" s="7">
-        <v>7.99</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>57.66</v>
+      </c>
+      <c r="D67" s="6">
+        <v>50.64</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-7.02</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-4.35</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>44.31</v>
+      </c>
+      <c r="D68" s="6">
+        <v>39.15</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-5.16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-0.62</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.54</v>
-      </c>
-      <c r="E14" s="9">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>48.41</v>
+      </c>
+      <c r="D69" s="6">
+        <v>43.72</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="D15" s="7">
-        <v>6.88</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>65.64</v>
+      </c>
+      <c r="D70" s="6">
+        <v>63.22</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.06</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>53.31</v>
+      </c>
+      <c r="D71" s="6">
+        <v>47.31</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.02</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-6.68</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>46.85</v>
+      </c>
+      <c r="D72" s="6">
+        <v>42.3</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-2.17</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.66</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-76.88</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-79.23</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.88</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4.04</v>
-      </c>
-      <c r="E19" s="9">
-        <v>4.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-56.36</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-68.86</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="D20" s="7">
-        <v>6.55</v>
-      </c>
-      <c r="E20" s="9">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>30.25</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-22.05</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-52.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3.79</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-19.04</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-35.53</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-16.49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.57</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3.23</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-7.92</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-39.26</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-31.34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2.3</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3.64</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-80.25</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-81.91</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>12.81</v>
-      </c>
-      <c r="D24" s="7">
-        <v>11.69</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-22.18</v>
+      </c>
+      <c r="D79" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E79" s="8">
+        <v>24.68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="D25" s="7">
-        <v>3.92</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-13.84</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-42.87</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-29.03</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-5.07</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-3.45</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>20.02</v>
-      </c>
-      <c r="D27" s="7">
-        <v>18.08</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>37.21</v>
-      </c>
-      <c r="D28" s="7">
-        <v>41.12</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>10.39</v>
-      </c>
-      <c r="D29" s="7">
-        <v>12.18</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-2.13</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E30" s="9">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-2.85</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-2.79</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-40.08</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-38.66</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>11.82</v>
-      </c>
-      <c r="D33" s="7">
-        <v>10.96</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>14.04</v>
-      </c>
-      <c r="D34" s="7">
-        <v>15.76</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>5.66</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-6.29</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-11.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>12.93</v>
-      </c>
-      <c r="D36" s="7">
-        <v>8.65</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-4.28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="D37" s="7">
-        <v>13.38</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>5.39</v>
-      </c>
-      <c r="D38" s="7">
-        <v>7.86</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>7.53</v>
-      </c>
-      <c r="D39" s="7">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-7.16</v>
-      </c>
-      <c r="E41" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>16.72</v>
-      </c>
-      <c r="D42" s="7">
-        <v>7.45</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-9.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>2</v>
-      </c>
-      <c r="D43" s="7">
-        <v>5.41</v>
-      </c>
-      <c r="E43" s="9">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>44.15</v>
-      </c>
-      <c r="D44" s="7">
-        <v>52.45</v>
-      </c>
-      <c r="E44" s="9">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-28.35</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-29.02</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-7.84</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-11.47</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-8.81</v>
-      </c>
-      <c r="E47" s="9">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-14.01</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-12.26</v>
-      </c>
-      <c r="E48" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-13.67</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-13.17</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-49.38</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-48.87</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>0</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-1.09</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-5.52</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-3.22</v>
-      </c>
-      <c r="E52" s="9">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-13.52</v>
-      </c>
-      <c r="E53" s="9">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>721.9</v>
-      </c>
-      <c r="D54" s="7">
-        <v>715.2</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>286.45</v>
-      </c>
-      <c r="D55" s="7">
-        <v>292.6</v>
-      </c>
-      <c r="E55" s="9">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1141</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1175.3</v>
-      </c>
-      <c r="E56" s="9">
-        <v>34.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>743.45</v>
-      </c>
-      <c r="D57" s="7">
-        <v>758.55</v>
-      </c>
-      <c r="E57" s="9">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>518</v>
-      </c>
-      <c r="D58" s="7">
-        <v>521</v>
-      </c>
-      <c r="E58" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>11219</v>
-      </c>
-      <c r="D59" s="7">
-        <v>11333</v>
-      </c>
-      <c r="E59" s="9">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>367.6</v>
-      </c>
-      <c r="D60" s="7">
-        <v>363.6</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>1267</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1297.8</v>
-      </c>
-      <c r="E61" s="9">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>77.64</v>
-      </c>
-      <c r="D62" s="7">
-        <v>79.09</v>
-      </c>
-      <c r="E62" s="9">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>88</v>
-      </c>
-      <c r="D63" s="7">
-        <v>99</v>
-      </c>
-      <c r="E63" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>99</v>
-      </c>
-      <c r="D64" s="7">
-        <v>88</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>59.08</v>
-      </c>
-      <c r="D65" s="7">
-        <v>57.13</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>46.1</v>
-      </c>
-      <c r="D66" s="7">
-        <v>50.16</v>
-      </c>
-      <c r="E66" s="9">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>53.35</v>
-      </c>
-      <c r="D67" s="7">
-        <v>60.96</v>
-      </c>
-      <c r="E67" s="9">
-        <v>7.61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>53</v>
-      </c>
-      <c r="D68" s="7">
-        <v>57.66</v>
-      </c>
-      <c r="E68" s="9">
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>42.39</v>
-      </c>
-      <c r="D69" s="7">
-        <v>44.31</v>
-      </c>
-      <c r="E69" s="9">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>45.56</v>
-      </c>
-      <c r="D70" s="7">
-        <v>48.41</v>
-      </c>
-      <c r="E70" s="9">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>69.03</v>
-      </c>
-      <c r="D71" s="7">
-        <v>65.64</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>45.24</v>
-      </c>
-      <c r="D72" s="7">
-        <v>53.31</v>
-      </c>
-      <c r="E72" s="9">
-        <v>8.07</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>43.5</v>
-      </c>
-      <c r="D73" s="7">
-        <v>46.85</v>
-      </c>
-      <c r="E73" s="9">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="7">
-        <v>-69.55</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-76.88</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-7.33</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-75.39</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-56.36</v>
-      </c>
-      <c r="E75" s="9">
-        <v>19.03</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>15.91</v>
-      </c>
-      <c r="D76" s="7">
-        <v>30.25</v>
-      </c>
-      <c r="E76" s="9">
-        <v>14.34</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-18.63</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-19.04</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-46.8</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-7.92</v>
-      </c>
-      <c r="E78" s="9">
-        <v>38.88</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-62.16</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-80.25</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-18.09</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>383.3</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-22.18</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-405.48</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-46.28</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-13.84</v>
-      </c>
-      <c r="E81" s="9">
-        <v>32.44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-65.45</v>
-      </c>
-      <c r="D82" s="7">
+      <c r="C81" s="6">
         <v>-71.69</v>
       </c>
-      <c r="E82" s="8">
-        <v>-6.24</v>
+      <c r="D81" s="6">
+        <v>-38.46</v>
+      </c>
+      <c r="E81" s="8">
+        <v>33.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3501,60 +3471,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>53.8</v>
-      </c>
-      <c r="E2" s="12">
-        <v>80</v>
-      </c>
-      <c r="F2" s="12">
-        <v>2.2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-0.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3656,60 +3626,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.397</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.365</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3274</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2629</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1908</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1493</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.08779999999999999</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.032</v>
-      </c>
-      <c r="I2" s="15">
+      <c r="A2" s="14">
+        <v>0.3947</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3622</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3235</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2674</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1848</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1511</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0837</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0457</v>
+      </c>
+      <c r="I2" s="14">
         <v>-0.0634</v>
       </c>
     </row>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,43 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.2 → 44.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>44.6</t>
-  </si>
-  <si>
-    <t>53.3 → 47.3</t>
-  </si>
-  <si>
-    <t>53.3</t>
-  </si>
-  <si>
-    <t>47.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -798,8 +761,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -939,10 +903,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>699.8</v>
+        <v>694.1</v>
       </c>
       <c r="D2">
-        <v>-2.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -951,46 +915,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-30.55</v>
+        <v>-31.11</v>
       </c>
       <c r="H2">
-        <v>90.58</v>
+        <v>89.03</v>
       </c>
       <c r="I2">
-        <v>-3.61</v>
+        <v>-3.39</v>
       </c>
       <c r="J2">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K2">
         <v>8.77</v>
       </c>
       <c r="L2">
-        <v>15.53</v>
+        <v>16.97</v>
       </c>
       <c r="M2">
-        <v>-6.34</v>
+        <v>-6.54</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>719.37</v>
+        <v>714.5</v>
       </c>
       <c r="Q2">
-        <v>692.59</v>
+        <v>695.42</v>
       </c>
       <c r="R2">
-        <v>662.16</v>
+        <v>662.42</v>
       </c>
       <c r="S2">
-        <v>635.52</v>
+        <v>636.53</v>
       </c>
       <c r="T2">
-        <v>10.11</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,34 +969,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.82</v>
+        <v>51.27</v>
       </c>
       <c r="Z2">
-        <v>17.97</v>
+        <v>15.53</v>
       </c>
       <c r="AA2">
-        <v>17.45</v>
+        <v>17.07</v>
       </c>
       <c r="AB2">
-        <v>0.52</v>
+        <v>-1.54</v>
       </c>
       <c r="AC2">
-        <v>20.56</v>
+        <v>8.15</v>
       </c>
       <c r="AD2">
-        <v>42.27</v>
+        <v>24.97</v>
       </c>
       <c r="AE2">
-        <v>31.19</v>
+        <v>31.74</v>
       </c>
       <c r="AF2">
-        <v>-79.23</v>
+        <v>-77.2</v>
       </c>
       <c r="AG2">
-        <v>760.27</v>
+        <v>757.95</v>
       </c>
       <c r="AH2">
-        <v>624.91</v>
+        <v>632.89</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1041,7 +1005,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>52.47</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1016,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>283.1</v>
+        <v>285.5</v>
       </c>
       <c r="D3">
-        <v>-3.25</v>
+        <v>0.85</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1064,46 +1028,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-10.83</v>
+        <v>-10.08</v>
       </c>
       <c r="H3">
-        <v>84.75</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="I3">
-        <v>-2.78</v>
+        <v>-1.38</v>
       </c>
       <c r="J3">
-        <v>0.48</v>
+        <v>-5.6</v>
       </c>
       <c r="K3">
-        <v>8.58</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L3">
-        <v>34.46</v>
+        <v>37.06</v>
       </c>
       <c r="M3">
-        <v>39.47</v>
+        <v>40.14</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>288.94</v>
+        <v>288.14</v>
       </c>
       <c r="Q3">
-        <v>301.4</v>
+        <v>300.16</v>
       </c>
       <c r="R3">
-        <v>281.38</v>
+        <v>281.73</v>
       </c>
       <c r="S3">
-        <v>224.47</v>
+        <v>225.12</v>
       </c>
       <c r="T3">
-        <v>26.12</v>
+        <v>26.82</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,43 +1082,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>44.57</v>
+        <v>46.2</v>
       </c>
       <c r="Z3">
-        <v>1.06</v>
+        <v>0.38</v>
       </c>
       <c r="AA3">
-        <v>4.63</v>
+        <v>3.78</v>
       </c>
       <c r="AB3">
-        <v>-3.56</v>
+        <v>-3.4</v>
       </c>
       <c r="AC3">
-        <v>15.61</v>
+        <v>15.87</v>
       </c>
       <c r="AD3">
-        <v>18.87</v>
+        <v>17.75</v>
       </c>
       <c r="AE3">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
       <c r="AF3">
-        <v>-68.86</v>
+        <v>-54.87</v>
       </c>
       <c r="AG3">
-        <v>324.46</v>
+        <v>323.87</v>
       </c>
       <c r="AH3">
-        <v>278.34</v>
+        <v>276.46</v>
       </c>
       <c r="AI3">
-        <v>320.41</v>
+        <v>319.77</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>37.88</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1129,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1157.8</v>
+        <v>1164.8</v>
       </c>
       <c r="D4">
-        <v>-1.49</v>
+        <v>0.6</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1177,46 +1141,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-10.16</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="H4">
-        <v>17.42</v>
+        <v>18.13</v>
       </c>
       <c r="I4">
-        <v>2.61</v>
+        <v>4.05</v>
       </c>
       <c r="J4">
-        <v>0.32</v>
+        <v>-0.9</v>
       </c>
       <c r="K4">
-        <v>9.279999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L4">
-        <v>10.69</v>
+        <v>12.82</v>
       </c>
       <c r="M4">
-        <v>26.74</v>
+        <v>27.02</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1144.84</v>
+        <v>1153.9</v>
       </c>
       <c r="Q4">
-        <v>1145.52</v>
+        <v>1145.26</v>
       </c>
       <c r="R4">
-        <v>1113.44</v>
+        <v>1116.18</v>
       </c>
       <c r="S4">
-        <v>1134.86</v>
+        <v>1135.7</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,34 +1195,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>55.95</v>
+        <v>57.45</v>
       </c>
       <c r="Z4">
-        <v>6.03</v>
+        <v>7.49</v>
       </c>
       <c r="AA4">
-        <v>5.1</v>
+        <v>5.58</v>
       </c>
       <c r="AB4">
-        <v>0.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>81.22</v>
+        <v>86.37</v>
       </c>
       <c r="AD4">
-        <v>67.68000000000001</v>
+        <v>80.44</v>
       </c>
       <c r="AE4">
-        <v>29.86</v>
+        <v>30</v>
       </c>
       <c r="AF4">
-        <v>-22.05</v>
+        <v>-44.66</v>
       </c>
       <c r="AG4">
-        <v>1196.12</v>
+        <v>1195.38</v>
       </c>
       <c r="AH4">
-        <v>1094.91</v>
+        <v>1095.13</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1267,7 +1231,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>30.14</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1242,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>738.95</v>
+        <v>748.25</v>
       </c>
       <c r="D5">
-        <v>-2.58</v>
+        <v>1.26</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1290,46 +1254,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.53</v>
+        <v>-13.46</v>
       </c>
       <c r="H5">
-        <v>11.64</v>
+        <v>13.05</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>-0.36</v>
       </c>
       <c r="J5">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="K5">
-        <v>6.32</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L5">
-        <v>-5.02</v>
+        <v>-4.87</v>
       </c>
       <c r="M5">
-        <v>36.22</v>
+        <v>37.22</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>748.67</v>
+        <v>748.13</v>
       </c>
       <c r="Q5">
-        <v>737.84</v>
+        <v>740</v>
       </c>
       <c r="R5">
-        <v>732.36</v>
+        <v>732.58</v>
       </c>
       <c r="S5">
-        <v>748.17</v>
+        <v>748.08</v>
       </c>
       <c r="T5">
-        <v>-1.23</v>
+        <v>0.02</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1341,37 +1305,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>50.64</v>
+        <v>53.53</v>
       </c>
       <c r="Z5">
         <v>5.64</v>
       </c>
       <c r="AA5">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="AB5">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AC5">
-        <v>25.53</v>
+        <v>26.18</v>
       </c>
       <c r="AD5">
-        <v>30.78</v>
+        <v>27.95</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>21.63</v>
       </c>
       <c r="AF5">
-        <v>-35.53</v>
+        <v>50.67</v>
       </c>
       <c r="AG5">
-        <v>778.0700000000001</v>
+        <v>777.35</v>
       </c>
       <c r="AH5">
-        <v>697.61</v>
+        <v>702.65</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1380,7 +1344,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.79</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1355,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>510</v>
+        <v>506.55</v>
       </c>
       <c r="D6">
-        <v>-2.11</v>
+        <v>-0.68</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1403,46 +1367,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-15</v>
+        <v>-15.58</v>
       </c>
       <c r="H6">
-        <v>16.29</v>
+        <v>15.5</v>
       </c>
       <c r="I6">
-        <v>-0.39</v>
+        <v>-3.7</v>
       </c>
       <c r="J6">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="K6">
-        <v>-11.07</v>
+        <v>-13.59</v>
       </c>
       <c r="L6">
-        <v>-6.19</v>
+        <v>-6.39</v>
       </c>
       <c r="M6">
-        <v>8.369999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P6">
-        <v>518.4</v>
+        <v>514.51</v>
       </c>
       <c r="Q6">
-        <v>524.84</v>
+        <v>523.0599999999999</v>
       </c>
       <c r="R6">
-        <v>542.85</v>
+        <v>542.11</v>
       </c>
       <c r="S6">
-        <v>522.63</v>
+        <v>522.9</v>
       </c>
       <c r="T6">
-        <v>-2.42</v>
+        <v>-3.13</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,43 +1421,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.15</v>
+        <v>37.67</v>
       </c>
       <c r="Z6">
-        <v>-8.48</v>
+        <v>-8.93</v>
       </c>
       <c r="AA6">
-        <v>-8.33</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.48</v>
       </c>
       <c r="AC6">
-        <v>71.88</v>
+        <v>61.48</v>
       </c>
       <c r="AD6">
-        <v>77.87</v>
+        <v>70.8</v>
       </c>
       <c r="AE6">
-        <v>11.87</v>
+        <v>11.73</v>
       </c>
       <c r="AF6">
-        <v>-39.26</v>
+        <v>-10.76</v>
       </c>
       <c r="AG6">
-        <v>548.28</v>
+        <v>546.38</v>
       </c>
       <c r="AH6">
-        <v>501.41</v>
+        <v>499.75</v>
       </c>
       <c r="AI6">
-        <v>543.8</v>
+        <v>543.33</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>14.91</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1468,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11116</v>
+        <v>11062</v>
       </c>
       <c r="D7">
-        <v>-1.91</v>
+        <v>-0.49</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1516,46 +1480,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.85</v>
+        <v>-50.09</v>
       </c>
       <c r="H7">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="I7">
-        <v>-0.27</v>
+        <v>-1.95</v>
       </c>
       <c r="J7">
-        <v>-2.88</v>
+        <v>-6.51</v>
       </c>
       <c r="K7">
-        <v>-8.51</v>
+        <v>-7.97</v>
       </c>
       <c r="L7">
-        <v>-39.94</v>
+        <v>-39.63</v>
       </c>
       <c r="M7">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P7">
-        <v>11231</v>
+        <v>11187</v>
       </c>
       <c r="Q7">
-        <v>11391.85</v>
+        <v>11358.2</v>
       </c>
       <c r="R7">
-        <v>11429.94</v>
+        <v>11427.24</v>
       </c>
       <c r="S7">
-        <v>14234.94</v>
+        <v>14188.3</v>
       </c>
       <c r="T7">
-        <v>-21.91</v>
+        <v>-22.03</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,34 +1534,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>43.72</v>
+        <v>42.62</v>
       </c>
       <c r="Z7">
-        <v>-109.32</v>
+        <v>-117.15</v>
       </c>
       <c r="AA7">
-        <v>-98.72</v>
+        <v>-102.41</v>
       </c>
       <c r="AB7">
-        <v>-10.6</v>
+        <v>-14.74</v>
       </c>
       <c r="AC7">
-        <v>69.20999999999999</v>
+        <v>61.56</v>
       </c>
       <c r="AD7">
-        <v>63.8</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="AE7">
-        <v>382.45</v>
+        <v>370.78</v>
       </c>
       <c r="AF7">
-        <v>-81.91</v>
+        <v>-80.15000000000001</v>
       </c>
       <c r="AG7">
-        <v>11920.85</v>
+        <v>11880.87</v>
       </c>
       <c r="AH7">
-        <v>10862.85</v>
+        <v>10835.53</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1606,7 +1570,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>14.54</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1581,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>360.7</v>
+        <v>362.05</v>
       </c>
       <c r="D8">
-        <v>-0.8</v>
+        <v>0.37</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1629,46 +1593,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.88</v>
+        <v>-1.51</v>
       </c>
       <c r="H8">
-        <v>53.94</v>
+        <v>54.52</v>
       </c>
       <c r="I8">
-        <v>10.42</v>
+        <v>3.96</v>
       </c>
       <c r="J8">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="K8">
-        <v>9.34</v>
+        <v>12.75</v>
       </c>
       <c r="L8">
-        <v>7.42</v>
+        <v>6.91</v>
       </c>
       <c r="M8">
-        <v>32.35</v>
+        <v>32.48</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>357.95</v>
+        <v>360.71</v>
       </c>
       <c r="Q8">
-        <v>340.63</v>
+        <v>341.83</v>
       </c>
       <c r="R8">
-        <v>336.15</v>
+        <v>336.61</v>
       </c>
       <c r="S8">
-        <v>290.37</v>
+        <v>290.86</v>
       </c>
       <c r="T8">
-        <v>24.22</v>
+        <v>24.47</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1647,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>63.22</v>
+        <v>63.89</v>
       </c>
       <c r="Z8">
-        <v>6.19</v>
+        <v>6.86</v>
       </c>
       <c r="AA8">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
       <c r="AB8">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AC8">
-        <v>88.56999999999999</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="AD8">
-        <v>94.79000000000001</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="AE8">
-        <v>11.72</v>
+        <v>11.29</v>
       </c>
       <c r="AF8">
-        <v>2.5</v>
+        <v>-12.02</v>
       </c>
       <c r="AG8">
-        <v>365.07</v>
+        <v>368.04</v>
       </c>
       <c r="AH8">
-        <v>316.18</v>
+        <v>315.63</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1719,7 +1683,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.83</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1694,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1273.2</v>
+        <v>1277</v>
       </c>
       <c r="D9">
-        <v>-1.9</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1742,46 +1706,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.06</v>
+        <v>-4.77</v>
       </c>
       <c r="H9">
-        <v>17.97</v>
+        <v>18.32</v>
       </c>
       <c r="I9">
-        <v>1.58</v>
+        <v>0.11</v>
       </c>
       <c r="J9">
-        <v>-3.57</v>
+        <v>-4.77</v>
       </c>
       <c r="K9">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="L9">
-        <v>13.4</v>
+        <v>14.32</v>
       </c>
       <c r="M9">
-        <v>15.11</v>
+        <v>15.57</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1276.44</v>
+        <v>1276.72</v>
       </c>
       <c r="Q9">
-        <v>1291.23</v>
+        <v>1288.2</v>
       </c>
       <c r="R9">
-        <v>1284.26</v>
+        <v>1285.38</v>
       </c>
       <c r="S9">
-        <v>1233.65</v>
+        <v>1234.44</v>
       </c>
       <c r="T9">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1760,34 @@
         <v>3</v>
       </c>
       <c r="Y9">
-        <v>47.31</v>
+        <v>48.28</v>
       </c>
       <c r="Z9">
-        <v>-5.87</v>
+        <v>-5.53</v>
       </c>
       <c r="AA9">
-        <v>-4.12</v>
+        <v>-4.41</v>
       </c>
       <c r="AB9">
-        <v>-1.75</v>
+        <v>-1.12</v>
       </c>
       <c r="AC9">
-        <v>60.56</v>
+        <v>69.73</v>
       </c>
       <c r="AD9">
-        <v>56.28</v>
+        <v>62.85</v>
       </c>
       <c r="AE9">
-        <v>25.38</v>
+        <v>25.16</v>
       </c>
       <c r="AF9">
-        <v>-42.87</v>
+        <v>-28.62</v>
       </c>
       <c r="AG9">
-        <v>1350.33</v>
+        <v>1343.4</v>
       </c>
       <c r="AH9">
-        <v>1232.13</v>
+        <v>1233.01</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1832,7 +1796,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>24.36</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1807,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.65000000000001</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="D10">
-        <v>-3.09</v>
+        <v>0.26</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1855,46 +1819,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-16.18</v>
+        <v>-15.97</v>
       </c>
       <c r="H10">
-        <v>112.44</v>
+        <v>113</v>
       </c>
       <c r="I10">
-        <v>-5</v>
+        <v>-5.01</v>
       </c>
       <c r="J10">
-        <v>-6.38</v>
+        <v>-5.76</v>
       </c>
       <c r="K10">
-        <v>47.09</v>
+        <v>50.22</v>
       </c>
       <c r="L10">
-        <v>-10.73</v>
+        <v>-6.76</v>
       </c>
       <c r="M10">
-        <v>-4.57</v>
+        <v>-3.97</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P10">
-        <v>78.89</v>
+        <v>78.08</v>
       </c>
       <c r="Q10">
-        <v>81.29000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="R10">
-        <v>78.31999999999999</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="S10">
-        <v>60.84</v>
+        <v>60.93</v>
       </c>
       <c r="T10">
-        <v>25.98</v>
+        <v>26.14</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,34 +1873,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>42.3</v>
+        <v>42.79</v>
       </c>
       <c r="Z10">
-        <v>-0.02</v>
+        <v>-0.29</v>
       </c>
       <c r="AA10">
-        <v>1.07</v>
+        <v>0.8</v>
       </c>
       <c r="AB10">
         <v>-1.09</v>
       </c>
       <c r="AC10">
-        <v>6.8</v>
+        <v>7.73</v>
       </c>
       <c r="AD10">
-        <v>5.6</v>
+        <v>7.11</v>
       </c>
       <c r="AE10">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="AF10">
-        <v>-38.46</v>
+        <v>-26.08</v>
       </c>
       <c r="AG10">
-        <v>86.78</v>
+        <v>86.94</v>
       </c>
       <c r="AH10">
-        <v>75.81</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="AI10">
         <v>76.45</v>
@@ -1945,7 +1909,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>36.81</v>
+        <v>41.15</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,1352 +2070,1280 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>8.23</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-5.6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-6.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>5.35</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4.95</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-6.8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.88</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-6.51</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4.87</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.96</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.57</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-4.77</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.38</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.76</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.61</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.38</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4.05</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.36</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-0.39</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-3.7</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>10.42</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3.96</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-6.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-5.01</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>15.53</v>
+      </c>
+      <c r="D25" s="5">
+        <v>16.97</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>34.46</v>
+      </c>
+      <c r="D26" s="5">
+        <v>37.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>10.69</v>
+      </c>
+      <c r="D27" s="5">
+        <v>12.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-5.02</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-4.87</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-6.19</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-6.39</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-39.94</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-39.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>7.42</v>
+      </c>
+      <c r="D31" s="5">
+        <v>6.91</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="D32" s="5">
+        <v>14.32</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-10.73</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>8.58</v>
+      </c>
+      <c r="D34" s="5">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="D35" s="5">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>6.32</v>
+      </c>
+      <c r="D36" s="5">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-11.07</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-13.59</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-8.51</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-7.97</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>9.34</v>
+      </c>
+      <c r="D39" s="5">
+        <v>12.75</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>3.43</v>
+      </c>
+      <c r="D40" s="5">
+        <v>3.62</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>47.09</v>
+      </c>
+      <c r="D41" s="5">
+        <v>50.22</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-30.55</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-31.11</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-10.83</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-10.08</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-10.16</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-14.53</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-13.46</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-15</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.58</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-49.85</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-50.09</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-1.88</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-1.51</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-4.77</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-16.18</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-15.97</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>699.8</v>
+      </c>
+      <c r="D51" s="5">
+        <v>694.1</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>283.1</v>
+      </c>
+      <c r="D52" s="5">
+        <v>285.5</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1157.8</v>
+      </c>
+      <c r="D53" s="5">
+        <v>1164.8</v>
+      </c>
+      <c r="E53" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>738.95</v>
+      </c>
+      <c r="D54" s="5">
+        <v>748.25</v>
+      </c>
+      <c r="E54" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>510</v>
+      </c>
+      <c r="D55" s="5">
+        <v>506.55</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>11116</v>
+      </c>
+      <c r="D56" s="5">
+        <v>11062</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>360.7</v>
+      </c>
+      <c r="D57" s="5">
+        <v>362.05</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1273.2</v>
+      </c>
+      <c r="D58" s="5">
+        <v>1277</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="D59" s="5">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="5">
         <v>66</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D60" s="5">
+        <v>55</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>55</v>
+      </c>
+      <c r="D61" s="5">
+        <v>66</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>12.3</v>
-      </c>
-      <c r="D8" s="6">
-        <v>8.23</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>52.82</v>
+      </c>
+      <c r="D62" s="5">
+        <v>51.27</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1.86</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>44.57</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46.2</v>
+      </c>
+      <c r="E63" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2.29</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>55.95</v>
+      </c>
+      <c r="D64" s="5">
+        <v>57.45</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>7.99</v>
-      </c>
-      <c r="D11" s="6">
-        <v>5.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>50.64</v>
+      </c>
+      <c r="D65" s="5">
+        <v>53.53</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>39.15</v>
+      </c>
+      <c r="D66" s="5">
+        <v>37.67</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.54</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-4.42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>43.72</v>
+      </c>
+      <c r="D67" s="5">
+        <v>42.62</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>6.88</v>
-      </c>
-      <c r="D14" s="6">
-        <v>4.87</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>63.22</v>
+      </c>
+      <c r="D68" s="5">
+        <v>63.89</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.57</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>47.31</v>
+      </c>
+      <c r="D69" s="5">
+        <v>48.28</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.68</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>42.3</v>
+      </c>
+      <c r="D70" s="5">
+        <v>42.79</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.66</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.61</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-79.23</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-77.2</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.04</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-6.82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-68.86</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-54.87</v>
+      </c>
+      <c r="E72" s="7">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6.55</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.61</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-22.05</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-44.66</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-22.61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-35.53</v>
+      </c>
+      <c r="D74" s="5">
+        <v>50.67</v>
+      </c>
+      <c r="E74" s="7">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3.23</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-39.26</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-10.76</v>
+      </c>
+      <c r="E75" s="7">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.64</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.27</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-81.91</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-80.15000000000001</v>
+      </c>
+      <c r="E76" s="7">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>11.69</v>
-      </c>
-      <c r="D23" s="6">
-        <v>10.42</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-12.02</v>
+      </c>
+      <c r="E77" s="6">
+        <v>-14.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3.92</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.58</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-42.87</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-28.62</v>
+      </c>
+      <c r="E78" s="7">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>18.08</v>
-      </c>
-      <c r="D26" s="6">
-        <v>15.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>41.12</v>
-      </c>
-      <c r="D27" s="6">
-        <v>34.46</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-6.66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>12.18</v>
-      </c>
-      <c r="D28" s="6">
-        <v>10.69</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.19</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-38.66</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-39.94</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>10.96</v>
-      </c>
-      <c r="D32" s="6">
-        <v>7.42</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>15.76</v>
-      </c>
-      <c r="D33" s="6">
-        <v>13.4</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-6.29</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-10.73</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>8.65</v>
-      </c>
-      <c r="D35" s="6">
-        <v>8.77</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>13.38</v>
-      </c>
-      <c r="D36" s="6">
-        <v>8.58</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>7.86</v>
-      </c>
-      <c r="D37" s="6">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="D38" s="6">
-        <v>6.32</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-11.07</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-7.16</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="D41" s="6">
-        <v>9.34</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>5.41</v>
-      </c>
-      <c r="D42" s="6">
-        <v>3.43</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>52.45</v>
-      </c>
-      <c r="D43" s="6">
-        <v>47.09</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-29.02</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-30.55</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-7.84</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-8.81</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-10.16</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-14.53</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-13.17</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-15</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-48.87</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-49.85</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-13.52</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-16.18</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>715.2</v>
-      </c>
-      <c r="D53" s="6">
-        <v>699.8</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-15.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>292.6</v>
-      </c>
-      <c r="D54" s="6">
-        <v>283.1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1175.3</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1157.8</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>758.55</v>
-      </c>
-      <c r="D56" s="6">
-        <v>738.95</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-19.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>521</v>
-      </c>
-      <c r="D57" s="6">
-        <v>510</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>11333</v>
-      </c>
-      <c r="D58" s="6">
-        <v>11116</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-217</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>363.6</v>
-      </c>
-      <c r="D59" s="6">
-        <v>360.7</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1297.8</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1273.2</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-24.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>79.09</v>
-      </c>
-      <c r="D61" s="6">
-        <v>76.65000000000001</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>55</v>
-      </c>
-      <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>66</v>
-      </c>
-      <c r="D63" s="6">
-        <v>55</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>57.13</v>
-      </c>
-      <c r="D64" s="6">
-        <v>52.82</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>50.16</v>
-      </c>
-      <c r="D65" s="6">
-        <v>44.57</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-5.59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>60.96</v>
-      </c>
-      <c r="D66" s="6">
-        <v>55.95</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>57.66</v>
-      </c>
-      <c r="D67" s="6">
-        <v>50.64</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-7.02</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>44.31</v>
-      </c>
-      <c r="D68" s="6">
-        <v>39.15</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-5.16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>48.41</v>
-      </c>
-      <c r="D69" s="6">
-        <v>43.72</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>65.64</v>
-      </c>
-      <c r="D70" s="6">
-        <v>63.22</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>53.31</v>
-      </c>
-      <c r="D71" s="6">
-        <v>47.31</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>46.85</v>
-      </c>
-      <c r="D72" s="6">
-        <v>42.3</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>-76.88</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-79.23</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-56.36</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-68.86</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-12.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>30.25</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-22.05</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-52.3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-19.04</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-35.53</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-16.49</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-7.92</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-39.26</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-31.34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-80.25</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-81.91</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-22.18</v>
-      </c>
-      <c r="D79" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="E79" s="8">
-        <v>24.68</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-13.84</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-42.87</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-29.03</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-71.69</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C79" s="5">
         <v>-38.46</v>
       </c>
-      <c r="E81" s="8">
-        <v>33.23</v>
+      <c r="D79" s="5">
+        <v>-26.08</v>
+      </c>
+      <c r="E79" s="7">
+        <v>12.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3471,60 +3363,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>64.16</v>
+      </c>
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.9</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-0.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>8.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>49.3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>80</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>9.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3626,61 +3518,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3947</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3622</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3235</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2674</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1848</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1511</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0837</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0457</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0634</v>
+      <c r="A2" s="13">
+        <v>0.4014</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3722</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.3248</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2702</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1843</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1557</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0823</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0397</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.0654</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,55 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.5% → -5.1%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.5%</t>
+  </si>
+  <si>
+    <t>-5.1%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.3 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +312,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -277,7 +332,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +441,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -762,8 +825,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -903,10 +965,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>694.1</v>
+        <v>679.65</v>
       </c>
       <c r="D2">
-        <v>-0.8100000000000001</v>
+        <v>-2.08</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -915,46 +977,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-31.11</v>
+        <v>-32.55</v>
       </c>
       <c r="H2">
-        <v>89.03</v>
+        <v>85.09</v>
       </c>
       <c r="I2">
-        <v>-3.39</v>
+        <v>-8.34</v>
       </c>
       <c r="J2">
-        <v>8.220000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="K2">
-        <v>8.77</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L2">
-        <v>16.97</v>
+        <v>14.14</v>
       </c>
       <c r="M2">
-        <v>-6.54</v>
+        <v>-7.02</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>714.5</v>
+        <v>702.13</v>
       </c>
       <c r="Q2">
-        <v>695.42</v>
+        <v>697.61</v>
       </c>
       <c r="R2">
-        <v>662.42</v>
+        <v>662.83</v>
       </c>
       <c r="S2">
-        <v>636.53</v>
+        <v>637.51</v>
       </c>
       <c r="T2">
-        <v>9.039999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -969,34 +1031,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.27</v>
+        <v>47.49</v>
       </c>
       <c r="Z2">
-        <v>15.53</v>
+        <v>12.28</v>
       </c>
       <c r="AA2">
-        <v>17.07</v>
+        <v>16.11</v>
       </c>
       <c r="AB2">
-        <v>-1.54</v>
+        <v>-3.82</v>
       </c>
       <c r="AC2">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>24.97</v>
+        <v>9.57</v>
       </c>
       <c r="AE2">
-        <v>31.74</v>
+        <v>31.55</v>
       </c>
       <c r="AF2">
-        <v>-77.2</v>
+        <v>-83.20999999999999</v>
       </c>
       <c r="AG2">
-        <v>757.95</v>
+        <v>754.13</v>
       </c>
       <c r="AH2">
-        <v>632.89</v>
+        <v>641.09</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1005,7 +1067,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>50.65</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1016,10 +1078,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>285.5</v>
+        <v>276.15</v>
       </c>
       <c r="D3">
-        <v>0.85</v>
+        <v>-3.27</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1028,46 +1090,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-10.08</v>
+        <v>-13.02</v>
       </c>
       <c r="H3">
-        <v>86.31999999999999</v>
+        <v>80.22</v>
       </c>
       <c r="I3">
-        <v>-1.38</v>
+        <v>-5.77</v>
       </c>
       <c r="J3">
-        <v>-5.6</v>
+        <v>-10.99</v>
       </c>
       <c r="K3">
-        <v>9.779999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="L3">
-        <v>37.06</v>
+        <v>29.46</v>
       </c>
       <c r="M3">
-        <v>40.14</v>
+        <v>39.33</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>288.14</v>
+        <v>284.76</v>
       </c>
       <c r="Q3">
-        <v>300.16</v>
+        <v>298.54</v>
       </c>
       <c r="R3">
-        <v>281.73</v>
+        <v>281.86</v>
       </c>
       <c r="S3">
-        <v>225.12</v>
+        <v>225.71</v>
       </c>
       <c r="T3">
-        <v>26.82</v>
+        <v>22.35</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1082,43 +1144,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.2</v>
+        <v>41.12</v>
       </c>
       <c r="Z3">
-        <v>0.38</v>
+        <v>-0.9</v>
       </c>
       <c r="AA3">
-        <v>3.78</v>
+        <v>2.84</v>
       </c>
       <c r="AB3">
-        <v>-3.4</v>
+        <v>-3.74</v>
       </c>
       <c r="AC3">
-        <v>15.87</v>
+        <v>7.11</v>
       </c>
       <c r="AD3">
-        <v>17.75</v>
+        <v>12.86</v>
       </c>
       <c r="AE3">
-        <v>11.36</v>
+        <v>11.28</v>
       </c>
       <c r="AF3">
-        <v>-54.87</v>
+        <v>-50.82</v>
       </c>
       <c r="AG3">
-        <v>323.87</v>
+        <v>324.18</v>
       </c>
       <c r="AH3">
-        <v>276.46</v>
+        <v>272.9</v>
       </c>
       <c r="AI3">
-        <v>319.77</v>
+        <v>313.25</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>39.64</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1129,10 +1191,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1164.8</v>
+        <v>1139.6</v>
       </c>
       <c r="D4">
-        <v>0.6</v>
+        <v>-2.16</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1141,46 +1203,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-9.619999999999999</v>
+        <v>-11.58</v>
       </c>
       <c r="H4">
-        <v>18.13</v>
+        <v>15.58</v>
       </c>
       <c r="I4">
-        <v>4.05</v>
+        <v>0.8</v>
       </c>
       <c r="J4">
-        <v>-0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="K4">
-        <v>9.050000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="L4">
-        <v>12.82</v>
+        <v>7.24</v>
       </c>
       <c r="M4">
-        <v>27.02</v>
+        <v>26.18</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>70</v>
       </c>
       <c r="P4">
-        <v>1153.9</v>
+        <v>1155.7</v>
       </c>
       <c r="Q4">
-        <v>1145.26</v>
+        <v>1143.28</v>
       </c>
       <c r="R4">
-        <v>1116.18</v>
+        <v>1118.47</v>
       </c>
       <c r="S4">
-        <v>1135.7</v>
+        <v>1136.38</v>
       </c>
       <c r="T4">
-        <v>2.56</v>
+        <v>0.28</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1195,34 +1257,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>57.45</v>
+        <v>50.72</v>
       </c>
       <c r="Z4">
-        <v>7.49</v>
+        <v>6.55</v>
       </c>
       <c r="AA4">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>0.77</v>
       </c>
       <c r="AC4">
-        <v>86.37</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>80.44</v>
+        <v>79.19</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>30.12</v>
       </c>
       <c r="AF4">
-        <v>-44.66</v>
+        <v>-3.75</v>
       </c>
       <c r="AG4">
-        <v>1195.38</v>
+        <v>1190.81</v>
       </c>
       <c r="AH4">
-        <v>1095.13</v>
+        <v>1095.74</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1231,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>27.31</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1242,10 +1304,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>748.25</v>
+        <v>745.7</v>
       </c>
       <c r="D5">
-        <v>1.26</v>
+        <v>-0.34</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1254,46 +1316,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.46</v>
+        <v>-13.75</v>
       </c>
       <c r="H5">
-        <v>13.05</v>
+        <v>12.66</v>
       </c>
       <c r="I5">
-        <v>-0.36</v>
+        <v>-0.77</v>
       </c>
       <c r="J5">
-        <v>4.95</v>
+        <v>5.77</v>
       </c>
       <c r="K5">
-        <v>9.529999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="L5">
-        <v>-4.87</v>
+        <v>-6.79</v>
       </c>
       <c r="M5">
-        <v>37.22</v>
+        <v>37.13</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>748.13</v>
+        <v>746.98</v>
       </c>
       <c r="Q5">
-        <v>740</v>
+        <v>742.03</v>
       </c>
       <c r="R5">
-        <v>732.58</v>
+        <v>732.74</v>
       </c>
       <c r="S5">
-        <v>748.08</v>
+        <v>747.95</v>
       </c>
       <c r="T5">
-        <v>0.02</v>
+        <v>-0.3</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1305,37 +1367,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>53.53</v>
+        <v>52.62</v>
       </c>
       <c r="Z5">
-        <v>5.64</v>
+        <v>5.37</v>
       </c>
       <c r="AA5">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="AB5">
-        <v>0.16</v>
+        <v>-0.08</v>
       </c>
       <c r="AC5">
-        <v>26.18</v>
+        <v>20.02</v>
       </c>
       <c r="AD5">
-        <v>27.95</v>
+        <v>23.91</v>
       </c>
       <c r="AE5">
-        <v>21.63</v>
+        <v>21.34</v>
       </c>
       <c r="AF5">
-        <v>50.67</v>
+        <v>2.56</v>
       </c>
       <c r="AG5">
-        <v>777.35</v>
+        <v>775.62</v>
       </c>
       <c r="AH5">
-        <v>702.65</v>
+        <v>708.4299999999999</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1344,7 +1406,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.16</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1355,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>506.55</v>
+        <v>495</v>
       </c>
       <c r="D6">
-        <v>-0.68</v>
+        <v>-2.28</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1367,46 +1429,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-15.58</v>
+        <v>-17.5</v>
       </c>
       <c r="H6">
-        <v>15.5</v>
+        <v>12.87</v>
       </c>
       <c r="I6">
-        <v>-3.7</v>
+        <v>-4.26</v>
       </c>
       <c r="J6">
-        <v>-6.8</v>
+        <v>-8.69</v>
       </c>
       <c r="K6">
-        <v>-13.59</v>
+        <v>-15.12</v>
       </c>
       <c r="L6">
-        <v>-6.39</v>
+        <v>-8.67</v>
       </c>
       <c r="M6">
-        <v>8.23</v>
+        <v>6.72</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P6">
-        <v>514.51</v>
+        <v>510.11</v>
       </c>
       <c r="Q6">
-        <v>523.0599999999999</v>
+        <v>521.05</v>
       </c>
       <c r="R6">
-        <v>542.11</v>
+        <v>541.1900000000001</v>
       </c>
       <c r="S6">
-        <v>522.9</v>
+        <v>523.13</v>
       </c>
       <c r="T6">
-        <v>-3.13</v>
+        <v>-5.38</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1421,43 +1483,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.67</v>
+        <v>33.15</v>
       </c>
       <c r="Z6">
-        <v>-8.93</v>
+        <v>-10.1</v>
       </c>
       <c r="AA6">
-        <v>-8.449999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.48</v>
+        <v>-1.32</v>
       </c>
       <c r="AC6">
-        <v>61.48</v>
+        <v>36.44</v>
       </c>
       <c r="AD6">
-        <v>70.8</v>
+        <v>56.6</v>
       </c>
       <c r="AE6">
-        <v>11.73</v>
+        <v>11.86</v>
       </c>
       <c r="AF6">
-        <v>-10.76</v>
+        <v>-24.02</v>
       </c>
       <c r="AG6">
-        <v>546.38</v>
+        <v>546.76</v>
       </c>
       <c r="AH6">
-        <v>499.75</v>
+        <v>495.34</v>
       </c>
       <c r="AI6">
-        <v>543.33</v>
+        <v>535.3099999999999</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>16.01</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1468,10 +1530,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11062</v>
+        <v>11026</v>
       </c>
       <c r="D7">
-        <v>-0.49</v>
+        <v>-0.33</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1480,43 +1542,43 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-50.09</v>
+        <v>-50.25</v>
       </c>
       <c r="H7">
-        <v>3.82</v>
+        <v>3.48</v>
       </c>
       <c r="I7">
-        <v>-1.95</v>
+        <v>-1.6</v>
       </c>
       <c r="J7">
-        <v>-6.51</v>
+        <v>-6.04</v>
       </c>
       <c r="K7">
-        <v>-7.97</v>
+        <v>-8.66</v>
       </c>
       <c r="L7">
-        <v>-39.63</v>
+        <v>-39.15</v>
       </c>
       <c r="M7">
-        <v>18.43</v>
+        <v>18.7</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P7">
-        <v>11187</v>
+        <v>11151.2</v>
       </c>
       <c r="Q7">
-        <v>11358.2</v>
+        <v>11330.6</v>
       </c>
       <c r="R7">
-        <v>11427.24</v>
+        <v>11428.14</v>
       </c>
       <c r="S7">
-        <v>14188.3</v>
+        <v>14142.08</v>
       </c>
       <c r="T7">
         <v>-22.03</v>
@@ -1534,34 +1596,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.62</v>
+        <v>41.86</v>
       </c>
       <c r="Z7">
-        <v>-117.15</v>
+        <v>-124.83</v>
       </c>
       <c r="AA7">
-        <v>-102.41</v>
+        <v>-106.89</v>
       </c>
       <c r="AB7">
-        <v>-14.74</v>
+        <v>-17.93</v>
       </c>
       <c r="AC7">
-        <v>61.56</v>
+        <v>42.68</v>
       </c>
       <c r="AD7">
-        <v>66.56999999999999</v>
+        <v>57.81</v>
       </c>
       <c r="AE7">
-        <v>370.78</v>
+        <v>369.43</v>
       </c>
       <c r="AF7">
-        <v>-80.15000000000001</v>
+        <v>-81.08</v>
       </c>
       <c r="AG7">
-        <v>11880.87</v>
+        <v>11862.62</v>
       </c>
       <c r="AH7">
-        <v>10835.53</v>
+        <v>10798.58</v>
       </c>
       <c r="AI7">
         <v>12187.8</v>
@@ -1570,7 +1632,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>15.45</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1581,10 +1643,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>362.05</v>
+        <v>348.75</v>
       </c>
       <c r="D8">
-        <v>0.37</v>
+        <v>-3.67</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1593,46 +1655,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.51</v>
+        <v>-5.13</v>
       </c>
       <c r="H8">
-        <v>54.52</v>
+        <v>48.84</v>
       </c>
       <c r="I8">
-        <v>3.96</v>
+        <v>-0.24</v>
       </c>
       <c r="J8">
-        <v>4.96</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>12.75</v>
+        <v>8.26</v>
       </c>
       <c r="L8">
-        <v>6.91</v>
+        <v>1.96</v>
       </c>
       <c r="M8">
-        <v>32.48</v>
+        <v>30.73</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P8">
-        <v>360.71</v>
+        <v>360.54</v>
       </c>
       <c r="Q8">
-        <v>341.83</v>
+        <v>342.12</v>
       </c>
       <c r="R8">
-        <v>336.61</v>
+        <v>336.74</v>
       </c>
       <c r="S8">
-        <v>290.86</v>
+        <v>291.28</v>
       </c>
       <c r="T8">
-        <v>24.47</v>
+        <v>19.73</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1647,34 +1709,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>63.89</v>
+        <v>53.57</v>
       </c>
       <c r="Z8">
-        <v>6.86</v>
+        <v>6.25</v>
       </c>
       <c r="AA8">
-        <v>3.89</v>
+        <v>4.36</v>
       </c>
       <c r="AB8">
-        <v>2.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC8">
-        <v>82.18000000000001</v>
+        <v>67.17</v>
       </c>
       <c r="AD8">
-        <v>88.84999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="AE8">
-        <v>11.29</v>
+        <v>11.65</v>
       </c>
       <c r="AF8">
-        <v>-12.02</v>
+        <v>-36.2</v>
       </c>
       <c r="AG8">
-        <v>368.04</v>
+        <v>368.51</v>
       </c>
       <c r="AH8">
-        <v>315.63</v>
+        <v>315.74</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1683,7 +1745,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>37.77</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1694,10 +1756,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1277</v>
+        <v>1264.1</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>-1.01</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1706,88 +1768,88 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-4.77</v>
+        <v>-5.73</v>
       </c>
       <c r="H9">
-        <v>18.32</v>
+        <v>17.12</v>
       </c>
       <c r="I9">
-        <v>0.11</v>
+        <v>-0.35</v>
       </c>
       <c r="J9">
-        <v>-4.77</v>
+        <v>-5.49</v>
       </c>
       <c r="K9">
-        <v>3.62</v>
+        <v>3.07</v>
       </c>
       <c r="L9">
-        <v>14.32</v>
+        <v>11.04</v>
       </c>
       <c r="M9">
-        <v>15.57</v>
+        <v>14.89</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1276.72</v>
+        <v>1275.82</v>
       </c>
       <c r="Q9">
-        <v>1288.2</v>
+        <v>1284.66</v>
       </c>
       <c r="R9">
-        <v>1285.38</v>
+        <v>1285.91</v>
       </c>
       <c r="S9">
-        <v>1234.44</v>
+        <v>1235.22</v>
       </c>
       <c r="T9">
-        <v>3.45</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V9" t="s">
         <v>47</v>
       </c>
       <c r="W9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>48.28</v>
+        <v>45.24</v>
       </c>
       <c r="Z9">
-        <v>-5.53</v>
+        <v>-6.23</v>
       </c>
       <c r="AA9">
-        <v>-4.41</v>
+        <v>-4.77</v>
       </c>
       <c r="AB9">
-        <v>-1.12</v>
+        <v>-1.46</v>
       </c>
       <c r="AC9">
-        <v>69.73</v>
+        <v>62.75</v>
       </c>
       <c r="AD9">
-        <v>62.85</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="AE9">
-        <v>25.16</v>
+        <v>25.1</v>
       </c>
       <c r="AF9">
-        <v>-28.62</v>
+        <v>-13.42</v>
       </c>
       <c r="AG9">
-        <v>1343.4</v>
+        <v>1336.21</v>
       </c>
       <c r="AH9">
-        <v>1233.01</v>
+        <v>1233.12</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1796,7 +1858,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>22.99</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1807,10 +1869,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.84999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D10">
-        <v>0.26</v>
+        <v>-3.19</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1819,46 +1881,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-15.97</v>
+        <v>-18.64</v>
       </c>
       <c r="H10">
-        <v>113</v>
+        <v>106.21</v>
       </c>
       <c r="I10">
-        <v>-5.01</v>
+        <v>-7.19</v>
       </c>
       <c r="J10">
-        <v>-5.76</v>
+        <v>-7.46</v>
       </c>
       <c r="K10">
-        <v>50.22</v>
+        <v>47.01</v>
       </c>
       <c r="L10">
-        <v>-6.76</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="M10">
-        <v>-3.97</v>
+        <v>-4.55</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
         <v>79</v>
       </c>
       <c r="P10">
-        <v>78.08</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="Q10">
-        <v>81.11</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R10">
-        <v>78.84999999999999</v>
+        <v>79.36</v>
       </c>
       <c r="S10">
-        <v>60.93</v>
+        <v>61</v>
       </c>
       <c r="T10">
-        <v>26.14</v>
+        <v>21.97</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1873,43 +1935,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>42.79</v>
+        <v>38.48</v>
       </c>
       <c r="Z10">
-        <v>-0.29</v>
+        <v>-0.7</v>
       </c>
       <c r="AA10">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AB10">
-        <v>-1.09</v>
+        <v>-1.2</v>
       </c>
       <c r="AC10">
-        <v>7.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD10">
-        <v>7.11</v>
+        <v>5.16</v>
       </c>
       <c r="AE10">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="AF10">
-        <v>-26.08</v>
+        <v>-47.56</v>
       </c>
       <c r="AG10">
-        <v>86.94</v>
+        <v>87.38</v>
       </c>
       <c r="AH10">
-        <v>75.29000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="AI10">
-        <v>76.45</v>
+        <v>89.36</v>
       </c>
       <c r="AJ10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK10">
-        <v>41.15</v>
+        <v>45.13</v>
       </c>
     </row>
   </sheetData>
@@ -2050,7 +2112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2070,1280 +2132,1426 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="D7" s="5">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.01</v>
+      <c r="A6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-5.6</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-6.08</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D10" s="7">
+        <v>6.6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-5.6</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-10.99</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-5.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="7">
         <v>-0.9</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-2.6</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>5.35</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="7">
         <v>4.95</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D13" s="7">
+        <v>5.77</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-7</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C14" s="7">
         <v>-6.8</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D14" s="7">
+        <v>-8.69</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.88</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C15" s="7">
         <v>-6.51</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D15" s="7">
+        <v>-6.04</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>4.87</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C16" s="7">
         <v>4.96</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D16" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.57</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C17" s="7">
         <v>-4.77</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-5.49</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C18" s="7">
         <v>-5.76</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D18" s="7">
+        <v>-7.46</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.61</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C19" s="7">
         <v>-3.39</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D19" s="7">
+        <v>-8.34</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-2.78</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C20" s="7">
         <v>-1.38</v>
       </c>
-      <c r="E17" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D20" s="7">
+        <v>-5.77</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-4.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>2.61</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C21" s="7">
         <v>4.05</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D21" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C22" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.77</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.26</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.95</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>3.96</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.24</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.35</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-5.01</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-7.19</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>16.97</v>
+      </c>
+      <c r="D28" s="7">
+        <v>14.14</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>37.06</v>
+      </c>
+      <c r="D29" s="7">
+        <v>29.46</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>12.82</v>
+      </c>
+      <c r="D30" s="7">
+        <v>7.24</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-4.87</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-6.79</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-6.39</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-8.67</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-39.63</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-39.15</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>6.91</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1.96</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>14.32</v>
+      </c>
+      <c r="D35" s="7">
+        <v>11.04</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-6.76</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>8.77</v>
+      </c>
+      <c r="D37" s="7">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D38" s="7">
+        <v>5.61</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="D39" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D40" s="7">
+        <v>7.66</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-13.59</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-15.12</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-7.97</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-8.66</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>12.75</v>
+      </c>
+      <c r="D43" s="7">
+        <v>8.26</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-4.49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3.62</v>
+      </c>
+      <c r="D44" s="7">
+        <v>3.07</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>50.22</v>
+      </c>
+      <c r="D45" s="7">
+        <v>47.01</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-31.11</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-32.55</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-10.08</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-13.02</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-11.58</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-13.46</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-13.75</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-15.58</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-17.5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-50.09</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-50.25</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-1.51</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-5.13</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-4.77</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-5.73</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-15.97</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-18.64</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="5">
-        <v>-0.36</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="C55" s="7">
+        <v>694.1</v>
+      </c>
+      <c r="D55" s="7">
+        <v>679.65</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-14.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>285.5</v>
+      </c>
+      <c r="D56" s="7">
+        <v>276.15</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-9.35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1164.8</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1139.6</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>748.25</v>
+      </c>
+      <c r="D58" s="7">
+        <v>745.7</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.39</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-3.7</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-3.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>506.55</v>
+      </c>
+      <c r="D59" s="7">
+        <v>495</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-11.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-0.27</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.95</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>11062</v>
+      </c>
+      <c r="D60" s="7">
+        <v>11026</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>10.42</v>
-      </c>
-      <c r="D22" s="5">
-        <v>3.96</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-6.46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>362.05</v>
+      </c>
+      <c r="D61" s="7">
+        <v>348.75</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-13.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1277</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1264.1</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-5.01</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="D63" s="7">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>99</v>
+      </c>
+      <c r="D64" s="7">
+        <v>88</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>55</v>
+      </c>
+      <c r="D65" s="7">
+        <v>66</v>
+      </c>
+      <c r="E65" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>66</v>
+      </c>
+      <c r="D66" s="7">
+        <v>55</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>88</v>
+      </c>
+      <c r="D67" s="7">
+        <v>99</v>
+      </c>
+      <c r="E67" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>15.53</v>
-      </c>
-      <c r="D25" s="5">
-        <v>16.97</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>51.27</v>
+      </c>
+      <c r="D68" s="7">
+        <v>47.49</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>34.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>37.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46.2</v>
+      </c>
+      <c r="D69" s="7">
+        <v>41.12</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-5.08</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>10.69</v>
-      </c>
-      <c r="D27" s="5">
-        <v>12.82</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>57.45</v>
+      </c>
+      <c r="D70" s="7">
+        <v>50.72</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-4.87</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>53.53</v>
+      </c>
+      <c r="D71" s="7">
+        <v>52.62</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-6.19</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-6.39</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>37.67</v>
+      </c>
+      <c r="D72" s="7">
+        <v>33.15</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-4.52</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-39.94</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-39.63</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>42.62</v>
+      </c>
+      <c r="D73" s="7">
+        <v>41.86</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>7.42</v>
-      </c>
-      <c r="D31" s="5">
-        <v>6.91</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>63.89</v>
+      </c>
+      <c r="D74" s="7">
+        <v>53.57</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-10.32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>13.4</v>
-      </c>
-      <c r="D32" s="5">
-        <v>14.32</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>48.28</v>
+      </c>
+      <c r="D75" s="7">
+        <v>45.24</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-10.73</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>42.79</v>
+      </c>
+      <c r="D76" s="7">
+        <v>38.48</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-77.2</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-6.01</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>8.58</v>
-      </c>
-      <c r="D34" s="5">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-54.87</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-50.82</v>
+      </c>
+      <c r="E78" s="9">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="D35" s="5">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-44.66</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-3.75</v>
+      </c>
+      <c r="E79" s="9">
+        <v>40.91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>6.32</v>
-      </c>
-      <c r="D36" s="5">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>50.67</v>
+      </c>
+      <c r="D80" s="7">
+        <v>2.56</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-48.11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-11.07</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-13.59</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-10.76</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-24.02</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-13.26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.97</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-80.15000000000001</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-81.08</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>9.34</v>
-      </c>
-      <c r="D39" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-12.02</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-36.2</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-24.18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>3.43</v>
-      </c>
-      <c r="D40" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-28.62</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-13.42</v>
+      </c>
+      <c r="E84" s="9">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>47.09</v>
-      </c>
-      <c r="D41" s="5">
-        <v>50.22</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-30.55</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-31.11</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-10.08</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-10.16</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-14.53</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-13.46</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-15</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-15.58</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-49.85</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-50.09</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-1.88</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-4.77</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-16.18</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-15.97</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>699.8</v>
-      </c>
-      <c r="D51" s="5">
-        <v>694.1</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>283.1</v>
-      </c>
-      <c r="D52" s="5">
-        <v>285.5</v>
-      </c>
-      <c r="E52" s="7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>1157.8</v>
-      </c>
-      <c r="D53" s="5">
-        <v>1164.8</v>
-      </c>
-      <c r="E53" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>738.95</v>
-      </c>
-      <c r="D54" s="5">
-        <v>748.25</v>
-      </c>
-      <c r="E54" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>510</v>
-      </c>
-      <c r="D55" s="5">
-        <v>506.55</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>11116</v>
-      </c>
-      <c r="D56" s="5">
-        <v>11062</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>360.7</v>
-      </c>
-      <c r="D57" s="5">
-        <v>362.05</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>1273.2</v>
-      </c>
-      <c r="D58" s="5">
-        <v>1277</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>76.65000000000001</v>
-      </c>
-      <c r="D59" s="5">
-        <v>76.84999999999999</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="5">
-        <v>66</v>
-      </c>
-      <c r="D60" s="5">
-        <v>55</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>55</v>
-      </c>
-      <c r="D61" s="5">
-        <v>66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>52.82</v>
-      </c>
-      <c r="D62" s="5">
-        <v>51.27</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>44.57</v>
-      </c>
-      <c r="D63" s="5">
-        <v>46.2</v>
-      </c>
-      <c r="E63" s="7">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>55.95</v>
-      </c>
-      <c r="D64" s="5">
-        <v>57.45</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>50.64</v>
-      </c>
-      <c r="D65" s="5">
-        <v>53.53</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>39.15</v>
-      </c>
-      <c r="D66" s="5">
-        <v>37.67</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>43.72</v>
-      </c>
-      <c r="D67" s="5">
-        <v>42.62</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>63.22</v>
-      </c>
-      <c r="D68" s="5">
-        <v>63.89</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>47.31</v>
-      </c>
-      <c r="D69" s="5">
-        <v>48.28</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>42.3</v>
-      </c>
-      <c r="D70" s="5">
-        <v>42.79</v>
-      </c>
-      <c r="E70" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="3" t="s">
+      <c r="B85" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="5">
-        <v>-79.23</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-77.2</v>
-      </c>
-      <c r="E71" s="7">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-68.86</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-54.87</v>
-      </c>
-      <c r="E72" s="7">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-22.05</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-44.66</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-22.61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-35.53</v>
-      </c>
-      <c r="D74" s="5">
-        <v>50.67</v>
-      </c>
-      <c r="E74" s="7">
-        <v>86.2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-39.26</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-10.76</v>
-      </c>
-      <c r="E75" s="7">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-81.91</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-80.15000000000001</v>
-      </c>
-      <c r="E76" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-12.02</v>
-      </c>
-      <c r="E77" s="6">
-        <v>-14.52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-42.87</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-28.62</v>
-      </c>
-      <c r="E78" s="7">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-38.46</v>
-      </c>
-      <c r="D79" s="5">
+      <c r="C85" s="7">
         <v>-26.08</v>
       </c>
-      <c r="E79" s="7">
-        <v>12.38</v>
+      <c r="D85" s="7">
+        <v>-47.56</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-21.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3363,61 +3571,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>64.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>49.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>80</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-1.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>9.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>44.9</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-2.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
-        <v>60</v>
+      <c r="I2" s="12">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3518,61 +3726,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.4014</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3722</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.3248</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2702</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1843</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1557</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0823</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0397</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0654</v>
+      <c r="A2" s="15">
+        <v>0.3933</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3713</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3073</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2618</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.187</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1489</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0672</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0455</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0702</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,40 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.5% → -5.1%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.5%</t>
-  </si>
-  <si>
-    <t>-5.1%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.3 → 47.5</t>
+    <t>50.7 → 48.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>47.5</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>52.6 → 50.0</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>50.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -278,7 +266,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,13 +300,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -332,7 +313,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,12 +335,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -449,15 +424,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -466,7 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -824,8 +798,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -965,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>679.65</v>
+        <v>675.3</v>
       </c>
       <c r="D2">
-        <v>-2.08</v>
+        <v>-0.64</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -977,46 +951,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.55</v>
+        <v>-32.98</v>
       </c>
       <c r="H2">
-        <v>85.09</v>
+        <v>83.91</v>
       </c>
       <c r="I2">
-        <v>-8.34</v>
+        <v>-6.46</v>
       </c>
       <c r="J2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="K2">
-        <v>9.289999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="L2">
-        <v>14.14</v>
+        <v>14.39</v>
       </c>
       <c r="M2">
-        <v>-7.02</v>
+        <v>-7.35</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>702.13</v>
+        <v>692.8099999999999</v>
       </c>
       <c r="Q2">
-        <v>697.61</v>
+        <v>699.8099999999999</v>
       </c>
       <c r="R2">
-        <v>662.83</v>
+        <v>663.01</v>
       </c>
       <c r="S2">
-        <v>637.51</v>
+        <v>638.4400000000001</v>
       </c>
       <c r="T2">
-        <v>6.61</v>
+        <v>5.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1031,34 +1005,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.49</v>
+        <v>46.38</v>
       </c>
       <c r="Z2">
-        <v>12.28</v>
+        <v>9.26</v>
       </c>
       <c r="AA2">
-        <v>16.11</v>
+        <v>14.74</v>
       </c>
       <c r="AB2">
-        <v>-3.82</v>
+        <v>-5.48</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.57</v>
+        <v>2.72</v>
       </c>
       <c r="AE2">
-        <v>31.55</v>
+        <v>30.6</v>
       </c>
       <c r="AF2">
-        <v>-83.20999999999999</v>
+        <v>-83.27</v>
       </c>
       <c r="AG2">
-        <v>754.13</v>
+        <v>748.33</v>
       </c>
       <c r="AH2">
-        <v>641.09</v>
+        <v>651.28</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1067,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>46.73</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1078,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>276.15</v>
+        <v>277.7</v>
       </c>
       <c r="D3">
-        <v>-3.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1090,46 +1064,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-13.02</v>
+        <v>-12.54</v>
       </c>
       <c r="H3">
-        <v>80.22</v>
+        <v>81.23</v>
       </c>
       <c r="I3">
-        <v>-5.77</v>
+        <v>-3.05</v>
       </c>
       <c r="J3">
-        <v>-10.99</v>
+        <v>-10.01</v>
       </c>
       <c r="K3">
-        <v>5.61</v>
+        <v>6.71</v>
       </c>
       <c r="L3">
-        <v>29.46</v>
+        <v>28.96</v>
       </c>
       <c r="M3">
-        <v>39.33</v>
+        <v>39.18</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>284.76</v>
+        <v>283.01</v>
       </c>
       <c r="Q3">
-        <v>298.54</v>
+        <v>296.94</v>
       </c>
       <c r="R3">
-        <v>281.86</v>
+        <v>282.1</v>
       </c>
       <c r="S3">
-        <v>225.71</v>
+        <v>226.31</v>
       </c>
       <c r="T3">
-        <v>22.35</v>
+        <v>22.71</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1144,43 +1118,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>41.12</v>
+        <v>42.26</v>
       </c>
       <c r="Z3">
-        <v>-0.9</v>
+        <v>-1.77</v>
       </c>
       <c r="AA3">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>-3.74</v>
+        <v>-3.69</v>
       </c>
       <c r="AC3">
-        <v>7.11</v>
+        <v>5.75</v>
       </c>
       <c r="AD3">
-        <v>12.86</v>
+        <v>9.58</v>
       </c>
       <c r="AE3">
-        <v>11.28</v>
+        <v>11.02</v>
       </c>
       <c r="AF3">
-        <v>-50.82</v>
+        <v>-51.78</v>
       </c>
       <c r="AG3">
-        <v>324.18</v>
+        <v>323.62</v>
       </c>
       <c r="AH3">
-        <v>272.9</v>
+        <v>270.26</v>
       </c>
       <c r="AI3">
-        <v>313.25</v>
+        <v>309.16</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>42.2</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1191,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1139.6</v>
+        <v>1130</v>
       </c>
       <c r="D4">
-        <v>-2.16</v>
+        <v>-0.84</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1203,46 +1177,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.58</v>
+        <v>-12.32</v>
       </c>
       <c r="H4">
-        <v>15.58</v>
+        <v>14.6</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>-0.96</v>
       </c>
       <c r="J4">
-        <v>-2.6</v>
+        <v>-4.17</v>
       </c>
       <c r="K4">
-        <v>7.5</v>
+        <v>9.84</v>
       </c>
       <c r="L4">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M4">
-        <v>26.18</v>
+        <v>24.54</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1155.7</v>
+        <v>1153.5</v>
       </c>
       <c r="Q4">
-        <v>1143.28</v>
+        <v>1140.13</v>
       </c>
       <c r="R4">
-        <v>1118.47</v>
+        <v>1120.4</v>
       </c>
       <c r="S4">
-        <v>1136.38</v>
+        <v>1136.99</v>
       </c>
       <c r="T4">
-        <v>0.28</v>
+        <v>-0.61</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1254,37 +1228,37 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.72</v>
+        <v>48.4</v>
       </c>
       <c r="Z4">
-        <v>6.55</v>
+        <v>4.96</v>
       </c>
       <c r="AA4">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="AB4">
-        <v>0.77</v>
+        <v>-0.65</v>
       </c>
       <c r="AC4">
-        <v>69.98999999999999</v>
+        <v>57.91</v>
       </c>
       <c r="AD4">
-        <v>79.19</v>
+        <v>71.42</v>
       </c>
       <c r="AE4">
-        <v>30.12</v>
+        <v>29.54</v>
       </c>
       <c r="AF4">
-        <v>-3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AG4">
-        <v>1190.81</v>
+        <v>1181.81</v>
       </c>
       <c r="AH4">
-        <v>1095.74</v>
+        <v>1098.45</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1293,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>24.2</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1304,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>745.7</v>
+        <v>738.3</v>
       </c>
       <c r="D5">
-        <v>-0.34</v>
+        <v>-0.99</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1316,46 +1290,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.75</v>
+        <v>-14.61</v>
       </c>
       <c r="H5">
-        <v>12.66</v>
+        <v>11.54</v>
       </c>
       <c r="I5">
-        <v>-0.77</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J5">
-        <v>5.77</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
-        <v>7.66</v>
+        <v>8.27</v>
       </c>
       <c r="L5">
-        <v>-6.79</v>
+        <v>-7.53</v>
       </c>
       <c r="M5">
-        <v>37.13</v>
+        <v>36.2</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>746.98</v>
+        <v>745.95</v>
       </c>
       <c r="Q5">
-        <v>742.03</v>
+        <v>743.84</v>
       </c>
       <c r="R5">
-        <v>732.74</v>
+        <v>732.89</v>
       </c>
       <c r="S5">
-        <v>747.95</v>
+        <v>747.72</v>
       </c>
       <c r="T5">
-        <v>-0.3</v>
+        <v>-1.26</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1370,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>52.62</v>
+        <v>49.97</v>
       </c>
       <c r="Z5">
-        <v>5.37</v>
+        <v>4.51</v>
       </c>
       <c r="AA5">
-        <v>5.46</v>
+        <v>5.27</v>
       </c>
       <c r="AB5">
-        <v>-0.08</v>
+        <v>-0.76</v>
       </c>
       <c r="AC5">
-        <v>20.02</v>
+        <v>19.19</v>
       </c>
       <c r="AD5">
-        <v>23.91</v>
+        <v>21.8</v>
       </c>
       <c r="AE5">
-        <v>21.34</v>
+        <v>21.53</v>
       </c>
       <c r="AF5">
-        <v>2.56</v>
+        <v>-52.54</v>
       </c>
       <c r="AG5">
-        <v>775.62</v>
+        <v>771.8200000000001</v>
       </c>
       <c r="AH5">
-        <v>708.4299999999999</v>
+        <v>715.85</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1406,7 +1380,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.22</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1417,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>495</v>
+        <v>501.15</v>
       </c>
       <c r="D6">
-        <v>-2.28</v>
+        <v>1.24</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1429,46 +1403,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-17.5</v>
+        <v>-16.48</v>
       </c>
       <c r="H6">
-        <v>12.87</v>
+        <v>14.27</v>
       </c>
       <c r="I6">
-        <v>-4.26</v>
+        <v>-3.25</v>
       </c>
       <c r="J6">
-        <v>-8.69</v>
+        <v>-6.38</v>
       </c>
       <c r="K6">
-        <v>-15.12</v>
+        <v>-11.99</v>
       </c>
       <c r="L6">
-        <v>-8.67</v>
+        <v>-6.04</v>
       </c>
       <c r="M6">
-        <v>6.72</v>
+        <v>5.95</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>510.11</v>
+        <v>506.74</v>
       </c>
       <c r="Q6">
-        <v>521.05</v>
+        <v>520.09</v>
       </c>
       <c r="R6">
-        <v>541.1900000000001</v>
+        <v>539.86</v>
       </c>
       <c r="S6">
-        <v>523.13</v>
+        <v>523.39</v>
       </c>
       <c r="T6">
-        <v>-5.38</v>
+        <v>-4.25</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1483,43 +1457,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>33.15</v>
+        <v>37.45</v>
       </c>
       <c r="Z6">
-        <v>-10.1</v>
+        <v>-10.41</v>
       </c>
       <c r="AA6">
-        <v>-8.779999999999999</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="AB6">
-        <v>-1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="AC6">
-        <v>36.44</v>
+        <v>32.82</v>
       </c>
       <c r="AD6">
-        <v>56.6</v>
+        <v>43.58</v>
       </c>
       <c r="AE6">
-        <v>11.86</v>
+        <v>11.87</v>
       </c>
       <c r="AF6">
-        <v>-24.02</v>
+        <v>-18.95</v>
       </c>
       <c r="AG6">
-        <v>546.76</v>
+        <v>547.3</v>
       </c>
       <c r="AH6">
-        <v>495.34</v>
+        <v>492.88</v>
       </c>
       <c r="AI6">
-        <v>535.3099999999999</v>
+        <v>530.75</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>19.26</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11026</v>
+        <v>11000</v>
       </c>
       <c r="D7">
-        <v>-0.33</v>
+        <v>-0.24</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1542,46 +1516,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-50.25</v>
+        <v>-50.37</v>
       </c>
       <c r="H7">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="I7">
-        <v>-1.6</v>
+        <v>-1.95</v>
       </c>
       <c r="J7">
-        <v>-6.04</v>
+        <v>-4.99</v>
       </c>
       <c r="K7">
-        <v>-8.66</v>
+        <v>-8.84</v>
       </c>
       <c r="L7">
-        <v>-39.15</v>
+        <v>-41.31</v>
       </c>
       <c r="M7">
-        <v>18.7</v>
+        <v>18.65</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>11151.2</v>
+        <v>11107.4</v>
       </c>
       <c r="Q7">
-        <v>11330.6</v>
+        <v>11279.25</v>
       </c>
       <c r="R7">
-        <v>11428.14</v>
+        <v>11427.12</v>
       </c>
       <c r="S7">
-        <v>14142.08</v>
+        <v>14093.58</v>
       </c>
       <c r="T7">
-        <v>-22.03</v>
+        <v>-21.95</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1596,43 +1570,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>41.86</v>
+        <v>41.29</v>
       </c>
       <c r="Z7">
-        <v>-124.83</v>
+        <v>-131.49</v>
       </c>
       <c r="AA7">
-        <v>-106.89</v>
+        <v>-111.81</v>
       </c>
       <c r="AB7">
-        <v>-17.93</v>
+        <v>-19.68</v>
       </c>
       <c r="AC7">
-        <v>42.68</v>
+        <v>34.47</v>
       </c>
       <c r="AD7">
-        <v>57.81</v>
+        <v>46.24</v>
       </c>
       <c r="AE7">
-        <v>369.43</v>
+        <v>363.62</v>
       </c>
       <c r="AF7">
-        <v>-81.08</v>
+        <v>-73.36</v>
       </c>
       <c r="AG7">
-        <v>11862.62</v>
+        <v>11718.39</v>
       </c>
       <c r="AH7">
-        <v>10798.58</v>
+        <v>10840.11</v>
       </c>
       <c r="AI7">
-        <v>12187.8</v>
+        <v>12115.85</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>17.42</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1643,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>348.75</v>
+        <v>350</v>
       </c>
       <c r="D8">
-        <v>-3.67</v>
+        <v>0.36</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1655,46 +1629,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-5.13</v>
+        <v>-4.79</v>
       </c>
       <c r="H8">
-        <v>48.84</v>
+        <v>49.37</v>
       </c>
       <c r="I8">
-        <v>-0.24</v>
+        <v>-4.79</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="K8">
-        <v>8.26</v>
+        <v>5.92</v>
       </c>
       <c r="L8">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="M8">
-        <v>30.73</v>
+        <v>30.85</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
         <v>68</v>
       </c>
       <c r="P8">
-        <v>360.54</v>
+        <v>357.02</v>
       </c>
       <c r="Q8">
-        <v>342.12</v>
+        <v>342.62</v>
       </c>
       <c r="R8">
-        <v>336.74</v>
+        <v>336.77</v>
       </c>
       <c r="S8">
-        <v>291.28</v>
+        <v>291.7</v>
       </c>
       <c r="T8">
-        <v>19.73</v>
+        <v>19.99</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1709,34 +1683,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>53.57</v>
+        <v>54.32</v>
       </c>
       <c r="Z8">
-        <v>6.25</v>
+        <v>5.79</v>
       </c>
       <c r="AA8">
-        <v>4.36</v>
+        <v>4.64</v>
       </c>
       <c r="AB8">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="AC8">
-        <v>67.17</v>
+        <v>56.1</v>
       </c>
       <c r="AD8">
-        <v>79.31</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="AE8">
-        <v>11.65</v>
+        <v>11.62</v>
       </c>
       <c r="AF8">
-        <v>-36.2</v>
+        <v>-45.85</v>
       </c>
       <c r="AG8">
-        <v>368.51</v>
+        <v>369.21</v>
       </c>
       <c r="AH8">
-        <v>315.74</v>
+        <v>316.03</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1745,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.71</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1756,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1264.1</v>
+        <v>1272.4</v>
       </c>
       <c r="D9">
-        <v>-1.01</v>
+        <v>0.66</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1768,46 +1742,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.73</v>
+        <v>-5.12</v>
       </c>
       <c r="H9">
-        <v>17.12</v>
+        <v>17.89</v>
       </c>
       <c r="I9">
-        <v>-0.35</v>
+        <v>0.43</v>
       </c>
       <c r="J9">
-        <v>-5.49</v>
+        <v>-4.68</v>
       </c>
       <c r="K9">
-        <v>3.07</v>
+        <v>4.62</v>
       </c>
       <c r="L9">
-        <v>11.04</v>
+        <v>10.73</v>
       </c>
       <c r="M9">
-        <v>14.89</v>
+        <v>14.39</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P9">
-        <v>1275.82</v>
+        <v>1276.9</v>
       </c>
       <c r="Q9">
-        <v>1284.66</v>
+        <v>1282.9</v>
       </c>
       <c r="R9">
-        <v>1285.91</v>
+        <v>1286.22</v>
       </c>
       <c r="S9">
-        <v>1235.22</v>
+        <v>1236.1</v>
       </c>
       <c r="T9">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1822,34 +1796,34 @@
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>45.24</v>
+        <v>47.53</v>
       </c>
       <c r="Z9">
-        <v>-6.23</v>
+        <v>-6.04</v>
       </c>
       <c r="AA9">
-        <v>-4.77</v>
+        <v>-5.02</v>
       </c>
       <c r="AB9">
-        <v>-1.46</v>
+        <v>-1.02</v>
       </c>
       <c r="AC9">
-        <v>62.75</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="AD9">
-        <v>64.34999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="AE9">
-        <v>25.1</v>
+        <v>25.15</v>
       </c>
       <c r="AF9">
-        <v>-13.42</v>
+        <v>86.92</v>
       </c>
       <c r="AG9">
-        <v>1336.21</v>
+        <v>1333.54</v>
       </c>
       <c r="AH9">
-        <v>1233.12</v>
+        <v>1232.26</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1858,7 +1832,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>20.34</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1869,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>74.40000000000001</v>
+        <v>78.09</v>
       </c>
       <c r="D10">
-        <v>-3.19</v>
+        <v>4.96</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1881,46 +1855,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-18.64</v>
+        <v>-14.61</v>
       </c>
       <c r="H10">
-        <v>106.21</v>
+        <v>116.44</v>
       </c>
       <c r="I10">
-        <v>-7.19</v>
+        <v>0.58</v>
       </c>
       <c r="J10">
-        <v>-7.46</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K10">
-        <v>47.01</v>
+        <v>49.71</v>
       </c>
       <c r="L10">
-        <v>-8.130000000000001</v>
+        <v>-2</v>
       </c>
       <c r="M10">
-        <v>-4.55</v>
+        <v>-3.47</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P10">
-        <v>76.93000000000001</v>
+        <v>77.02</v>
       </c>
       <c r="Q10">
-        <v>80.90000000000001</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="R10">
-        <v>79.36</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="S10">
-        <v>61</v>
+        <v>61.09</v>
       </c>
       <c r="T10">
-        <v>21.97</v>
+        <v>27.83</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1935,43 +1909,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>38.48</v>
+        <v>47.12</v>
       </c>
       <c r="Z10">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="AA10">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AB10">
-        <v>-1.2</v>
+        <v>-0.97</v>
       </c>
       <c r="AC10">
-        <v>0.9399999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AD10">
-        <v>5.16</v>
+        <v>7.73</v>
       </c>
       <c r="AE10">
-        <v>4.29</v>
+        <v>4.48</v>
       </c>
       <c r="AF10">
-        <v>-47.56</v>
+        <v>14.84</v>
       </c>
       <c r="AG10">
-        <v>87.38</v>
+        <v>87.36</v>
       </c>
       <c r="AH10">
-        <v>74.43000000000001</v>
+        <v>74.17</v>
       </c>
       <c r="AI10">
-        <v>89.36</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="AJ10" t="s">
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>45.13</v>
+        <v>49.58</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2152,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2171,1387 +2145,1313 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>6.6</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-10.99</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-10.01</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.17</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5.77</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-8.69</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-6.38</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-6.04</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.06</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.49</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.46</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E16" s="8">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-8.34</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.05</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.96</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-4.26</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-3.25</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.95</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.24</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-7.19</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.58</v>
+      </c>
+      <c r="E25" s="8">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D10" s="7">
-        <v>6.6</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>14.14</v>
+      </c>
+      <c r="D26" s="6">
+        <v>14.39</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-5.6</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-10.99</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-5.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>29.46</v>
+      </c>
+      <c r="D27" s="6">
+        <v>28.96</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.6</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>7.24</v>
+      </c>
+      <c r="D28" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>4.95</v>
-      </c>
-      <c r="D13" s="7">
-        <v>5.77</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.79</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-7.53</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-6.8</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-8.67</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.04</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-6.51</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-6.04</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-39.15</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-41.31</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>4.96</v>
-      </c>
-      <c r="D16" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.96</v>
+      </c>
+      <c r="D32" s="6">
+        <v>2.12</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.77</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.49</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>11.04</v>
+      </c>
+      <c r="D33" s="6">
+        <v>10.73</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-5.76</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-7.46</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-2</v>
+      </c>
+      <c r="E34" s="8">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-3.39</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-8.34</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="D35" s="6">
+        <v>10.28</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-5.77</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>5.61</v>
+      </c>
+      <c r="D36" s="6">
+        <v>6.71</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4.05</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="D37" s="6">
+        <v>9.84</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>7.66</v>
+      </c>
+      <c r="D38" s="6">
+        <v>8.27</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.26</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-15.12</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-11.99</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-1.95</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-8.84</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>3.96</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.24</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>8.26</v>
+      </c>
+      <c r="D41" s="6">
+        <v>5.92</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.35</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="D42" s="6">
+        <v>4.62</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-5.01</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-7.19</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>47.01</v>
+      </c>
+      <c r="D43" s="6">
+        <v>49.71</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>16.97</v>
-      </c>
-      <c r="D28" s="7">
-        <v>14.14</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-32.55</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-32.98</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>37.06</v>
-      </c>
-      <c r="D29" s="7">
-        <v>29.46</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-13.02</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-12.54</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>12.82</v>
-      </c>
-      <c r="D30" s="7">
-        <v>7.24</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-11.58</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-12.32</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-4.87</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-6.79</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-14.61</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-6.39</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-8.67</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-17.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-16.48</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-39.63</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-39.15</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-50.25</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-50.37</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>6.91</v>
-      </c>
-      <c r="D34" s="7">
-        <v>1.96</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-5.13</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>14.32</v>
-      </c>
-      <c r="D35" s="7">
-        <v>11.04</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-5.73</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-6.76</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-18.64</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-14.61</v>
+      </c>
+      <c r="E52" s="8">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>679.65</v>
+      </c>
+      <c r="D53" s="6">
+        <v>675.3</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>276.15</v>
+      </c>
+      <c r="D54" s="6">
+        <v>277.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1139.6</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1130</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>745.7</v>
+      </c>
+      <c r="D56" s="6">
+        <v>738.3</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-7.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>495</v>
+      </c>
+      <c r="D57" s="6">
+        <v>501.15</v>
+      </c>
+      <c r="E57" s="8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>11026</v>
+      </c>
+      <c r="D58" s="6">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>348.75</v>
+      </c>
+      <c r="D59" s="6">
+        <v>350</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1264.1</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1272.4</v>
+      </c>
+      <c r="E60" s="8">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D61" s="6">
+        <v>78.09</v>
+      </c>
+      <c r="E61" s="8">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>55</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>45</v>
+      </c>
+      <c r="D63" s="6">
+        <v>55</v>
+      </c>
+      <c r="E63" s="8">
         <v>10</v>
       </c>
-      <c r="C37" s="7">
-        <v>8.77</v>
-      </c>
-      <c r="D37" s="7">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>47.49</v>
+      </c>
+      <c r="D64" s="6">
+        <v>46.38</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="D38" s="7">
-        <v>5.61</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-4.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>41.12</v>
+      </c>
+      <c r="D65" s="6">
+        <v>42.26</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="D39" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>50.72</v>
+      </c>
+      <c r="D66" s="6">
+        <v>48.4</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="D40" s="7">
-        <v>7.66</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>52.62</v>
+      </c>
+      <c r="D67" s="6">
+        <v>49.97</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-13.59</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-15.12</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>33.15</v>
+      </c>
+      <c r="D68" s="6">
+        <v>37.45</v>
+      </c>
+      <c r="E68" s="8">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-7.97</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.66</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>41.86</v>
+      </c>
+      <c r="D69" s="6">
+        <v>41.29</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>12.75</v>
-      </c>
-      <c r="D43" s="7">
-        <v>8.26</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-4.49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>53.57</v>
+      </c>
+      <c r="D70" s="6">
+        <v>54.32</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>3.62</v>
-      </c>
-      <c r="D44" s="7">
-        <v>3.07</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>45.24</v>
+      </c>
+      <c r="D71" s="6">
+        <v>47.53</v>
+      </c>
+      <c r="E71" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>50.22</v>
-      </c>
-      <c r="D45" s="7">
-        <v>47.01</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>38.48</v>
+      </c>
+      <c r="D72" s="6">
+        <v>47.12</v>
+      </c>
+      <c r="E72" s="8">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-31.11</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-32.55</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-83.27</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-10.08</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-13.02</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-50.82</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-51.78</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-11.58</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-3.75</v>
+      </c>
+      <c r="D75" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="E75" s="8">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-13.46</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-13.75</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>2.56</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-52.54</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-55.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-15.58</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-17.5</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-24.02</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-18.95</v>
+      </c>
+      <c r="E77" s="8">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-50.09</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-50.25</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-81.08</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-73.36</v>
+      </c>
+      <c r="E78" s="8">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-1.51</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-5.13</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-36.2</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-45.85</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-9.65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-4.77</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-5.73</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-13.42</v>
+      </c>
+      <c r="D80" s="6">
+        <v>86.92</v>
+      </c>
+      <c r="E80" s="8">
+        <v>100.34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-15.97</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-18.64</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>694.1</v>
-      </c>
-      <c r="D55" s="7">
-        <v>679.65</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-14.45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>285.5</v>
-      </c>
-      <c r="D56" s="7">
-        <v>276.15</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-9.35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1164.8</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1139.6</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-25.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>748.25</v>
-      </c>
-      <c r="D58" s="7">
-        <v>745.7</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>506.55</v>
-      </c>
-      <c r="D59" s="7">
-        <v>495</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-11.55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>11062</v>
-      </c>
-      <c r="D60" s="7">
-        <v>11026</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>362.05</v>
-      </c>
-      <c r="D61" s="7">
-        <v>348.75</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-13.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1277</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1264.1</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-12.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>76.84999999999999</v>
-      </c>
-      <c r="D63" s="7">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>99</v>
-      </c>
-      <c r="D64" s="7">
-        <v>88</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>55</v>
-      </c>
-      <c r="D65" s="7">
-        <v>66</v>
-      </c>
-      <c r="E65" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>66</v>
-      </c>
-      <c r="D66" s="7">
-        <v>55</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>88</v>
-      </c>
-      <c r="D67" s="7">
-        <v>99</v>
-      </c>
-      <c r="E67" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>51.27</v>
-      </c>
-      <c r="D68" s="7">
-        <v>47.49</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>46.2</v>
-      </c>
-      <c r="D69" s="7">
-        <v>41.12</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-5.08</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>57.45</v>
-      </c>
-      <c r="D70" s="7">
-        <v>50.72</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.73</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>53.53</v>
-      </c>
-      <c r="D71" s="7">
-        <v>52.62</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>37.67</v>
-      </c>
-      <c r="D72" s="7">
-        <v>33.15</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-4.52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>42.62</v>
-      </c>
-      <c r="D73" s="7">
-        <v>41.86</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>63.89</v>
-      </c>
-      <c r="D74" s="7">
-        <v>53.57</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-10.32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>48.28</v>
-      </c>
-      <c r="D75" s="7">
-        <v>45.24</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>42.79</v>
-      </c>
-      <c r="D76" s="7">
-        <v>38.48</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="7">
-        <v>-77.2</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-83.20999999999999</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-6.01</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-54.87</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-50.82</v>
-      </c>
-      <c r="E78" s="9">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-44.66</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E79" s="9">
-        <v>40.91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>50.67</v>
-      </c>
-      <c r="D80" s="7">
-        <v>2.56</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-48.11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-10.76</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-24.02</v>
+      <c r="C81" s="6">
+        <v>-47.56</v>
+      </c>
+      <c r="D81" s="6">
+        <v>14.84</v>
       </c>
       <c r="E81" s="8">
-        <v>-13.26</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-80.15000000000001</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-81.08</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-12.02</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-36.2</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-24.18</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-28.62</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-13.42</v>
-      </c>
-      <c r="E84" s="9">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-26.08</v>
-      </c>
-      <c r="D85" s="7">
-        <v>-47.56</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-21.48</v>
+        <v>62.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3571,60 +3471,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.9</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-2.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>7.2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>46.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3726,61 +3626,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3933</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3713</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3073</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2618</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.187</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1489</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0672</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0455</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0702</v>
+      <c r="A2" s="14">
+        <v>0.3918</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.362</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3085</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2454</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1865</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1439</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0595</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0347</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0735</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.7 → 48.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>52.6 → 50.0</t>
-  </si>
-  <si>
-    <t>52.6</t>
+    <t>50.0 → 53.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>50.0</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>41.3 → 50.9</t>
+  </si>
+  <si>
+    <t>41.3</t>
+  </si>
+  <si>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>47.1 → 52.1</t>
+  </si>
+  <si>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>52.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -939,10 +948,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>675.3</v>
+        <v>672.55</v>
       </c>
       <c r="D2">
-        <v>-0.64</v>
+        <v>-0.41</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -951,25 +960,25 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-32.98</v>
+        <v>-33.25</v>
       </c>
       <c r="H2">
-        <v>83.91</v>
+        <v>83.16</v>
       </c>
       <c r="I2">
-        <v>-6.46</v>
+        <v>-5.96</v>
       </c>
       <c r="J2">
-        <v>6.2</v>
+        <v>6.53</v>
       </c>
       <c r="K2">
-        <v>10.28</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L2">
-        <v>14.39</v>
+        <v>16.66</v>
       </c>
       <c r="M2">
-        <v>-7.35</v>
+        <v>-7.57</v>
       </c>
       <c r="N2">
         <v>77</v>
@@ -978,19 +987,19 @@
         <v>77</v>
       </c>
       <c r="P2">
-        <v>692.8099999999999</v>
+        <v>684.28</v>
       </c>
       <c r="Q2">
-        <v>699.8099999999999</v>
+        <v>698.71</v>
       </c>
       <c r="R2">
-        <v>663.01</v>
+        <v>663.0700000000001</v>
       </c>
       <c r="S2">
-        <v>638.4400000000001</v>
+        <v>639.3200000000001</v>
       </c>
       <c r="T2">
-        <v>5.77</v>
+        <v>5.2</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,34 +1014,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>46.38</v>
+        <v>45.65</v>
       </c>
       <c r="Z2">
-        <v>9.26</v>
+        <v>6.56</v>
       </c>
       <c r="AA2">
-        <v>14.74</v>
+        <v>13.1</v>
       </c>
       <c r="AB2">
-        <v>-5.48</v>
+        <v>-6.54</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>30.6</v>
+        <v>29.74</v>
       </c>
       <c r="AF2">
-        <v>-83.27</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="AG2">
-        <v>748.33</v>
+        <v>748.71</v>
       </c>
       <c r="AH2">
-        <v>651.28</v>
+        <v>648.71</v>
       </c>
       <c r="AI2">
         <v>666.86</v>
@@ -1041,7 +1050,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>42.16</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,7 +1064,7 @@
         <v>277.7</v>
       </c>
       <c r="D3">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1070,40 +1079,40 @@
         <v>81.23</v>
       </c>
       <c r="I3">
-        <v>-3.05</v>
+        <v>-5.09</v>
       </c>
       <c r="J3">
-        <v>-10.01</v>
+        <v>-10.32</v>
       </c>
       <c r="K3">
-        <v>6.71</v>
+        <v>5.63</v>
       </c>
       <c r="L3">
-        <v>28.96</v>
+        <v>32.91</v>
       </c>
       <c r="M3">
-        <v>39.18</v>
+        <v>38.93</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>283.01</v>
+        <v>280.03</v>
       </c>
       <c r="Q3">
-        <v>296.94</v>
+        <v>295.34</v>
       </c>
       <c r="R3">
-        <v>282.1</v>
+        <v>282.41</v>
       </c>
       <c r="S3">
-        <v>226.31</v>
+        <v>226.91</v>
       </c>
       <c r="T3">
-        <v>22.71</v>
+        <v>22.39</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1121,31 +1130,31 @@
         <v>42.26</v>
       </c>
       <c r="Z3">
-        <v>-1.77</v>
+        <v>-2.44</v>
       </c>
       <c r="AA3">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="AB3">
-        <v>-3.69</v>
+        <v>-3.49</v>
       </c>
       <c r="AC3">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>9.58</v>
+        <v>5.12</v>
       </c>
       <c r="AE3">
-        <v>11.02</v>
+        <v>10.78</v>
       </c>
       <c r="AF3">
-        <v>-51.78</v>
+        <v>-34.36</v>
       </c>
       <c r="AG3">
-        <v>323.62</v>
+        <v>322.63</v>
       </c>
       <c r="AH3">
-        <v>270.26</v>
+        <v>268.05</v>
       </c>
       <c r="AI3">
         <v>309.16</v>
@@ -1154,7 +1163,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>44.98</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1174,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1130</v>
+        <v>1134.9</v>
       </c>
       <c r="D4">
-        <v>-0.84</v>
+        <v>0.43</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1177,46 +1186,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-12.32</v>
+        <v>-11.94</v>
       </c>
       <c r="H4">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="I4">
-        <v>-0.96</v>
+        <v>-3.44</v>
       </c>
       <c r="J4">
-        <v>-4.17</v>
+        <v>-4.86</v>
       </c>
       <c r="K4">
-        <v>9.84</v>
+        <v>8.73</v>
       </c>
       <c r="L4">
-        <v>7.35</v>
+        <v>7.91</v>
       </c>
       <c r="M4">
-        <v>24.54</v>
+        <v>24.22</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O4">
         <v>71</v>
       </c>
       <c r="P4">
-        <v>1153.5</v>
+        <v>1145.42</v>
       </c>
       <c r="Q4">
-        <v>1140.13</v>
+        <v>1138.88</v>
       </c>
       <c r="R4">
-        <v>1120.4</v>
+        <v>1122.21</v>
       </c>
       <c r="S4">
-        <v>1136.99</v>
+        <v>1137.6</v>
       </c>
       <c r="T4">
-        <v>-0.61</v>
+        <v>-0.24</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,34 +1240,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>48.4</v>
+        <v>49.67</v>
       </c>
       <c r="Z4">
-        <v>4.96</v>
+        <v>4.06</v>
       </c>
       <c r="AA4">
-        <v>5.61</v>
+        <v>5.3</v>
       </c>
       <c r="AB4">
-        <v>-0.65</v>
+        <v>-1.24</v>
       </c>
       <c r="AC4">
-        <v>57.91</v>
+        <v>45.45</v>
       </c>
       <c r="AD4">
-        <v>71.42</v>
+        <v>57.79</v>
       </c>
       <c r="AE4">
-        <v>29.54</v>
+        <v>28.84</v>
       </c>
       <c r="AF4">
-        <v>5.2</v>
+        <v>117.27</v>
       </c>
       <c r="AG4">
-        <v>1181.81</v>
+        <v>1179.53</v>
       </c>
       <c r="AH4">
-        <v>1098.45</v>
+        <v>1098.22</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1267,7 +1276,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>21.54</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1287,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>738.3</v>
+        <v>747.4</v>
       </c>
       <c r="D5">
-        <v>-0.99</v>
+        <v>1.23</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1290,46 +1299,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.61</v>
+        <v>-13.55</v>
       </c>
       <c r="H5">
-        <v>11.54</v>
+        <v>12.92</v>
       </c>
       <c r="I5">
-        <v>-0.6899999999999999</v>
+        <v>-1.47</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>6.44</v>
       </c>
       <c r="K5">
-        <v>8.27</v>
+        <v>8.09</v>
       </c>
       <c r="L5">
-        <v>-7.53</v>
+        <v>-4.61</v>
       </c>
       <c r="M5">
-        <v>36.2</v>
+        <v>36.23</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>745.95</v>
+        <v>743.72</v>
       </c>
       <c r="Q5">
-        <v>743.84</v>
+        <v>744.51</v>
       </c>
       <c r="R5">
-        <v>732.89</v>
+        <v>733.0599999999999</v>
       </c>
       <c r="S5">
-        <v>747.72</v>
+        <v>747.5700000000001</v>
       </c>
       <c r="T5">
-        <v>-1.26</v>
+        <v>-0.02</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1344,34 +1353,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>49.97</v>
+        <v>53.1</v>
       </c>
       <c r="Z5">
         <v>4.51</v>
       </c>
       <c r="AA5">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="AB5">
-        <v>-0.76</v>
+        <v>-0.6</v>
       </c>
       <c r="AC5">
-        <v>19.19</v>
+        <v>24.48</v>
       </c>
       <c r="AD5">
-        <v>21.8</v>
+        <v>21.23</v>
       </c>
       <c r="AE5">
-        <v>21.53</v>
+        <v>21.19</v>
       </c>
       <c r="AF5">
-        <v>-52.54</v>
+        <v>-34.26</v>
       </c>
       <c r="AG5">
-        <v>771.8200000000001</v>
+        <v>772.14</v>
       </c>
       <c r="AH5">
-        <v>715.85</v>
+        <v>716.87</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1380,7 +1389,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>20.42</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1400,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>501.15</v>
+        <v>494.7</v>
       </c>
       <c r="D6">
-        <v>1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1403,25 +1412,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-16.48</v>
+        <v>-17.55</v>
       </c>
       <c r="H6">
-        <v>14.27</v>
+        <v>12.8</v>
       </c>
       <c r="I6">
-        <v>-3.25</v>
+        <v>-5.05</v>
       </c>
       <c r="J6">
-        <v>-6.38</v>
+        <v>-4.94</v>
       </c>
       <c r="K6">
-        <v>-11.99</v>
+        <v>-12.5</v>
       </c>
       <c r="L6">
-        <v>-6.04</v>
+        <v>-6.1</v>
       </c>
       <c r="M6">
-        <v>5.95</v>
+        <v>5.42</v>
       </c>
       <c r="N6">
         <v>23</v>
@@ -1430,19 +1439,19 @@
         <v>47</v>
       </c>
       <c r="P6">
-        <v>506.74</v>
+        <v>501.48</v>
       </c>
       <c r="Q6">
-        <v>520.09</v>
+        <v>518.92</v>
       </c>
       <c r="R6">
-        <v>539.86</v>
+        <v>538.4299999999999</v>
       </c>
       <c r="S6">
-        <v>523.39</v>
+        <v>523.58</v>
       </c>
       <c r="T6">
-        <v>-4.25</v>
+        <v>-5.52</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,43 +1466,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.45</v>
+        <v>34.91</v>
       </c>
       <c r="Z6">
-        <v>-10.41</v>
+        <v>-11.05</v>
       </c>
       <c r="AA6">
-        <v>-9.109999999999999</v>
+        <v>-9.5</v>
       </c>
       <c r="AB6">
-        <v>-1.3</v>
+        <v>-1.55</v>
       </c>
       <c r="AC6">
-        <v>32.82</v>
+        <v>26.54</v>
       </c>
       <c r="AD6">
-        <v>43.58</v>
+        <v>31.93</v>
       </c>
       <c r="AE6">
-        <v>11.87</v>
+        <v>11.86</v>
       </c>
       <c r="AF6">
-        <v>-18.95</v>
+        <v>-12.37</v>
       </c>
       <c r="AG6">
-        <v>547.3</v>
+        <v>548.41</v>
       </c>
       <c r="AH6">
-        <v>492.88</v>
+        <v>489.44</v>
       </c>
       <c r="AI6">
-        <v>530.75</v>
+        <v>530.55</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.81</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1513,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11000</v>
+        <v>11346</v>
       </c>
       <c r="D7">
-        <v>-0.24</v>
+        <v>3.15</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1516,46 +1525,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-50.37</v>
+        <v>-48.81</v>
       </c>
       <c r="H7">
-        <v>3.24</v>
+        <v>6.49</v>
       </c>
       <c r="I7">
-        <v>-1.95</v>
+        <v>0.11</v>
       </c>
       <c r="J7">
-        <v>-4.99</v>
+        <v>-5.66</v>
       </c>
       <c r="K7">
-        <v>-8.84</v>
+        <v>-8.33</v>
       </c>
       <c r="L7">
-        <v>-41.31</v>
+        <v>-38.44</v>
       </c>
       <c r="M7">
-        <v>18.65</v>
+        <v>19.32</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>11107.4</v>
+        <v>11110</v>
       </c>
       <c r="Q7">
-        <v>11279.25</v>
+        <v>11260.75</v>
       </c>
       <c r="R7">
-        <v>11427.12</v>
+        <v>11434.42</v>
       </c>
       <c r="S7">
-        <v>14093.58</v>
+        <v>14041.64</v>
       </c>
       <c r="T7">
-        <v>-21.95</v>
+        <v>-19.2</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,34 +1579,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>41.29</v>
+        <v>50.91</v>
       </c>
       <c r="Z7">
-        <v>-131.49</v>
+        <v>-107.61</v>
       </c>
       <c r="AA7">
-        <v>-111.81</v>
+        <v>-110.97</v>
       </c>
       <c r="AB7">
-        <v>-19.68</v>
+        <v>3.36</v>
       </c>
       <c r="AC7">
-        <v>34.47</v>
+        <v>53.97</v>
       </c>
       <c r="AD7">
-        <v>46.24</v>
+        <v>43.71</v>
       </c>
       <c r="AE7">
-        <v>363.62</v>
+        <v>366.86</v>
       </c>
       <c r="AF7">
-        <v>-73.36</v>
+        <v>658.54</v>
       </c>
       <c r="AG7">
-        <v>11718.39</v>
+        <v>11650.86</v>
       </c>
       <c r="AH7">
-        <v>10840.11</v>
+        <v>10870.64</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1606,7 +1615,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>19.57</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>350</v>
+        <v>356.6</v>
       </c>
       <c r="D8">
-        <v>0.36</v>
+        <v>1.89</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1629,46 +1638,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-4.79</v>
+        <v>-2.99</v>
       </c>
       <c r="H8">
-        <v>49.37</v>
+        <v>52.19</v>
       </c>
       <c r="I8">
-        <v>-4.79</v>
+        <v>-1.93</v>
       </c>
       <c r="J8">
-        <v>2.06</v>
+        <v>4.88</v>
       </c>
       <c r="K8">
-        <v>5.92</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L8">
-        <v>2.12</v>
+        <v>5.42</v>
       </c>
       <c r="M8">
-        <v>30.85</v>
+        <v>31.64</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P8">
-        <v>357.02</v>
+        <v>355.62</v>
       </c>
       <c r="Q8">
-        <v>342.62</v>
+        <v>343.71</v>
       </c>
       <c r="R8">
-        <v>336.77</v>
+        <v>337.01</v>
       </c>
       <c r="S8">
-        <v>291.7</v>
+        <v>292.15</v>
       </c>
       <c r="T8">
-        <v>19.99</v>
+        <v>22.06</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1692,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>54.32</v>
+        <v>58.15</v>
       </c>
       <c r="Z8">
-        <v>5.79</v>
+        <v>5.9</v>
       </c>
       <c r="AA8">
-        <v>4.64</v>
+        <v>4.9</v>
       </c>
       <c r="AB8">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>56.1</v>
+        <v>48.96</v>
       </c>
       <c r="AD8">
-        <v>68.48999999999999</v>
+        <v>57.41</v>
       </c>
       <c r="AE8">
-        <v>11.62</v>
+        <v>11.49</v>
       </c>
       <c r="AF8">
-        <v>-45.85</v>
+        <v>-52.49</v>
       </c>
       <c r="AG8">
-        <v>369.21</v>
+        <v>370.74</v>
       </c>
       <c r="AH8">
-        <v>316.03</v>
+        <v>316.69</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1719,7 +1728,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.65</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1739,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1272.4</v>
+        <v>1253.4</v>
       </c>
       <c r="D9">
-        <v>0.66</v>
+        <v>-1.49</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1742,46 +1751,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-5.12</v>
+        <v>-6.53</v>
       </c>
       <c r="H9">
-        <v>17.89</v>
+        <v>16.13</v>
       </c>
       <c r="I9">
-        <v>0.43</v>
+        <v>-3.42</v>
       </c>
       <c r="J9">
-        <v>-4.68</v>
+        <v>-4.15</v>
       </c>
       <c r="K9">
-        <v>4.62</v>
+        <v>2.42</v>
       </c>
       <c r="L9">
-        <v>10.73</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M9">
-        <v>14.39</v>
+        <v>14.43</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P9">
-        <v>1276.9</v>
+        <v>1268.02</v>
       </c>
       <c r="Q9">
-        <v>1282.9</v>
+        <v>1279.9</v>
       </c>
       <c r="R9">
-        <v>1286.22</v>
+        <v>1285.94</v>
       </c>
       <c r="S9">
-        <v>1236.1</v>
+        <v>1236.84</v>
       </c>
       <c r="T9">
-        <v>2.94</v>
+        <v>1.34</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1796,34 +1805,34 @@
         <v>2</v>
       </c>
       <c r="Y9">
-        <v>47.53</v>
+        <v>43.09</v>
       </c>
       <c r="Z9">
-        <v>-6.04</v>
+        <v>-7.34</v>
       </c>
       <c r="AA9">
-        <v>-5.02</v>
+        <v>-5.49</v>
       </c>
       <c r="AB9">
-        <v>-1.02</v>
+        <v>-1.85</v>
       </c>
       <c r="AC9">
-        <v>67.81999999999999</v>
+        <v>58.98</v>
       </c>
       <c r="AD9">
-        <v>66.77</v>
+        <v>63.18</v>
       </c>
       <c r="AE9">
-        <v>25.15</v>
+        <v>24.96</v>
       </c>
       <c r="AF9">
-        <v>86.92</v>
+        <v>-4.32</v>
       </c>
       <c r="AG9">
-        <v>1333.54</v>
+        <v>1330.02</v>
       </c>
       <c r="AH9">
-        <v>1232.26</v>
+        <v>1229.77</v>
       </c>
       <c r="AI9">
         <v>1318</v>
@@ -1832,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>19.3</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1852,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>78.09</v>
+        <v>80.62</v>
       </c>
       <c r="D10">
-        <v>4.96</v>
+        <v>3.24</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1855,46 +1864,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-14.61</v>
+        <v>-11.84</v>
       </c>
       <c r="H10">
-        <v>116.44</v>
+        <v>123.45</v>
       </c>
       <c r="I10">
-        <v>0.58</v>
+        <v>1.93</v>
       </c>
       <c r="J10">
-        <v>-0.6899999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="K10">
-        <v>49.71</v>
+        <v>54.77</v>
       </c>
       <c r="L10">
-        <v>-2</v>
+        <v>3.07</v>
       </c>
       <c r="M10">
-        <v>-3.47</v>
+        <v>-2.8</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>77.02</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="Q10">
-        <v>80.76000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="R10">
-        <v>79.73999999999999</v>
+        <v>79.97</v>
       </c>
       <c r="S10">
-        <v>61.09</v>
+        <v>61.19</v>
       </c>
       <c r="T10">
-        <v>27.83</v>
+        <v>31.76</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,34 +1918,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>47.12</v>
+        <v>52.09</v>
       </c>
       <c r="Z10">
-        <v>-0.72</v>
+        <v>-0.52</v>
       </c>
       <c r="AA10">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AB10">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="AC10">
-        <v>14.5</v>
+        <v>34.93</v>
       </c>
       <c r="AD10">
-        <v>7.73</v>
+        <v>16.79</v>
       </c>
       <c r="AE10">
-        <v>4.48</v>
+        <v>4.44</v>
       </c>
       <c r="AF10">
-        <v>14.84</v>
+        <v>-10.52</v>
       </c>
       <c r="AG10">
-        <v>87.36</v>
+        <v>87.39</v>
       </c>
       <c r="AH10">
-        <v>74.17</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1945,7 +1954,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>49.58</v>
+        <v>46.57</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2135,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2146,7 +2155,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>57</v>
@@ -2164,676 +2173,679 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>6.6</v>
-      </c>
-      <c r="D8" s="6">
-        <v>6.2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.4</v>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-10.99</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="6">
-        <v>-10.01</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.98</v>
+        <v>6.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.6</v>
+        <v>-10.01</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.17</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.57</v>
+        <v>-10.32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>5.77</v>
+        <v>-4.17</v>
       </c>
       <c r="D11" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.07</v>
+        <v>-4.86</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.69</v>
+        <v>4.7</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.31</v>
+        <v>6.44</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.04</v>
+        <v>-6.38</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.05</v>
+        <v>-4.94</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>3.2</v>
+        <v>-4.99</v>
       </c>
       <c r="D14" s="6">
-        <v>2.06</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.14</v>
+        <v>-5.66</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.49</v>
+        <v>2.06</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.68</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.8100000000000001</v>
+        <v>4.88</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.46</v>
+        <v>-4.68</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E16" s="8">
-        <v>6.77</v>
+        <v>-4.15</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.34</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.46</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.88</v>
+        <v>-0.27</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.77</v>
+        <v>-6.46</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.72</v>
+        <v>-5.96</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>0.8</v>
+        <v>-3.05</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.76</v>
+        <v>-5.09</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.77</v>
+        <v>-0.96</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-3.44</v>
       </c>
       <c r="E20" s="8">
-        <v>0.08</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.26</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.25</v>
+        <v>-1.47</v>
       </c>
       <c r="E21" s="8">
-        <v>1.01</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.6</v>
+        <v>-3.25</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.35</v>
+        <v>-5.05</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.24</v>
+        <v>-1.95</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.79</v>
+        <v>0.11</v>
       </c>
       <c r="E23" s="7">
-        <v>-4.55</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.35</v>
+        <v>-4.79</v>
       </c>
       <c r="D24" s="6">
-        <v>0.43</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.78</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.86</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-7.19</v>
+        <v>0.43</v>
       </c>
       <c r="D25" s="6">
-        <v>0.58</v>
+        <v>-3.42</v>
       </c>
       <c r="E25" s="8">
-        <v>7.77</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>14.14</v>
+        <v>0.58</v>
       </c>
       <c r="D26" s="6">
-        <v>14.39</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.25</v>
+        <v>1.93</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>29.46</v>
+        <v>14.39</v>
       </c>
       <c r="D27" s="6">
-        <v>28.96</v>
+        <v>16.66</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.5</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>7.24</v>
+        <v>28.96</v>
       </c>
       <c r="D28" s="6">
-        <v>7.35</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.11</v>
+        <v>32.91</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-6.79</v>
+        <v>7.35</v>
       </c>
       <c r="D29" s="6">
-        <v>-7.53</v>
+        <v>7.91</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.74</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.67</v>
+        <v>-7.53</v>
       </c>
       <c r="D30" s="6">
-        <v>-6.04</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.63</v>
+        <v>-4.61</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.92</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-39.15</v>
+        <v>-6.04</v>
       </c>
       <c r="D31" s="6">
-        <v>-41.31</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.16</v>
+        <v>-6.1</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>1.96</v>
+        <v>-41.31</v>
       </c>
       <c r="D32" s="6">
-        <v>2.12</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.16</v>
+        <v>-38.44</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.87</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>11.04</v>
+        <v>2.12</v>
       </c>
       <c r="D33" s="6">
-        <v>10.73</v>
+        <v>5.42</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.31</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-8.130000000000001</v>
+        <v>10.73</v>
       </c>
       <c r="D34" s="6">
-        <v>-2</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E34" s="8">
-        <v>6.13</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>9.289999999999999</v>
+        <v>-2</v>
       </c>
       <c r="D35" s="6">
-        <v>10.28</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.99</v>
+        <v>3.07</v>
+      </c>
+      <c r="E35" s="7">
+        <v>5.07</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>5.61</v>
+        <v>10.28</v>
       </c>
       <c r="D36" s="6">
-        <v>6.71</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E36" s="8">
-        <v>1.1</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>7.5</v>
+        <v>6.71</v>
       </c>
       <c r="D37" s="6">
-        <v>9.84</v>
+        <v>5.63</v>
       </c>
       <c r="E37" s="8">
-        <v>2.34</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>7.66</v>
+        <v>9.84</v>
       </c>
       <c r="D38" s="6">
-        <v>8.27</v>
+        <v>8.73</v>
       </c>
       <c r="E38" s="8">
-        <v>0.61</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-15.12</v>
+        <v>8.27</v>
       </c>
       <c r="D39" s="6">
-        <v>-11.99</v>
+        <v>8.09</v>
       </c>
       <c r="E39" s="8">
-        <v>3.13</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-8.66</v>
+        <v>-11.99</v>
       </c>
       <c r="D40" s="6">
-        <v>-8.84</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.18</v>
+        <v>-12.5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>8.26</v>
+        <v>-8.84</v>
       </c>
       <c r="D41" s="6">
-        <v>5.92</v>
+        <v>-8.33</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.34</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>3.07</v>
+        <v>5.92</v>
       </c>
       <c r="D42" s="6">
-        <v>4.62</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.55</v>
+        <v>8.890000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>2.97</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>47.01</v>
+        <v>4.62</v>
       </c>
       <c r="D43" s="6">
-        <v>49.71</v>
+        <v>2.42</v>
       </c>
       <c r="E43" s="8">
-        <v>2.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>-32.55</v>
+        <v>49.71</v>
       </c>
       <c r="D44" s="6">
-        <v>-32.98</v>
+        <v>54.77</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.43</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-13.02</v>
+        <v>-32.98</v>
       </c>
       <c r="D45" s="6">
-        <v>-12.54</v>
+        <v>-33.25</v>
       </c>
       <c r="E45" s="8">
-        <v>0.48</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2844,13 +2856,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-11.58</v>
+        <v>-12.32</v>
       </c>
       <c r="D46" s="6">
-        <v>-12.32</v>
+        <v>-11.94</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.74</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2861,13 +2873,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-13.75</v>
+        <v>-14.61</v>
       </c>
       <c r="D47" s="6">
-        <v>-14.61</v>
+        <v>-13.55</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.86</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2878,13 +2890,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-17.5</v>
+        <v>-16.48</v>
       </c>
       <c r="D48" s="6">
-        <v>-16.48</v>
+        <v>-17.55</v>
       </c>
       <c r="E48" s="8">
-        <v>1.02</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2895,13 +2907,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-50.25</v>
+        <v>-50.37</v>
       </c>
       <c r="D49" s="6">
-        <v>-50.37</v>
+        <v>-48.81</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.12</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2912,13 +2924,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-5.13</v>
+        <v>-4.79</v>
       </c>
       <c r="D50" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.34</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.8</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2929,13 +2941,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-5.73</v>
+        <v>-5.12</v>
       </c>
       <c r="D51" s="6">
-        <v>-5.12</v>
+        <v>-6.53</v>
       </c>
       <c r="E51" s="8">
-        <v>0.61</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2946,13 +2958,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-18.64</v>
+        <v>-14.61</v>
       </c>
       <c r="D52" s="6">
-        <v>-14.61</v>
-      </c>
-      <c r="E52" s="8">
-        <v>4.03</v>
+        <v>-11.84</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2963,149 +2975,149 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>679.65</v>
+        <v>675.3</v>
       </c>
       <c r="D53" s="6">
-        <v>675.3</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-4.35</v>
+        <v>672.55</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>276.15</v>
+        <v>1130</v>
       </c>
       <c r="D54" s="6">
-        <v>277.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.55</v>
+        <v>1134.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>4.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1139.6</v>
+        <v>738.3</v>
       </c>
       <c r="D55" s="6">
-        <v>1130</v>
+        <v>747.4</v>
       </c>
       <c r="E55" s="7">
-        <v>-9.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>745.7</v>
+        <v>501.15</v>
       </c>
       <c r="D56" s="6">
-        <v>738.3</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-7.4</v>
+        <v>494.7</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-6.45</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>495</v>
+        <v>11000</v>
       </c>
       <c r="D57" s="6">
-        <v>501.15</v>
-      </c>
-      <c r="E57" s="8">
-        <v>6.15</v>
+        <v>11346</v>
+      </c>
+      <c r="E57" s="7">
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>11026</v>
+        <v>350</v>
       </c>
       <c r="D58" s="6">
-        <v>11000</v>
+        <v>356.6</v>
       </c>
       <c r="E58" s="7">
-        <v>-26</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>348.75</v>
+        <v>1272.4</v>
       </c>
       <c r="D59" s="6">
-        <v>350</v>
+        <v>1253.4</v>
       </c>
       <c r="E59" s="8">
-        <v>1.25</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1264.1</v>
+        <v>78.09</v>
       </c>
       <c r="D60" s="6">
-        <v>1272.4</v>
-      </c>
-      <c r="E60" s="8">
-        <v>8.300000000000001</v>
+        <v>80.62</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2.53</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>74.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="D61" s="6">
-        <v>78.09</v>
+        <v>55</v>
       </c>
       <c r="E61" s="8">
-        <v>3.69</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3116,13 +3128,13 @@
         <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D62" s="6">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E62" s="7">
-        <v>-10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3133,13 +3145,13 @@
         <v>13</v>
       </c>
       <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
         <v>45</v>
       </c>
-      <c r="D63" s="6">
-        <v>55</v>
-      </c>
       <c r="E63" s="8">
-        <v>10</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3150,308 +3162,291 @@
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>47.49</v>
+        <v>46.38</v>
       </c>
       <c r="D64" s="6">
-        <v>46.38</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.11</v>
+        <v>45.65</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>41.12</v>
+        <v>48.4</v>
       </c>
       <c r="D65" s="6">
-        <v>42.26</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.14</v>
+        <v>49.67</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.27</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>50.72</v>
+        <v>49.97</v>
       </c>
       <c r="D66" s="6">
-        <v>48.4</v>
+        <v>53.1</v>
       </c>
       <c r="E66" s="7">
-        <v>-2.32</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>52.62</v>
+        <v>37.45</v>
       </c>
       <c r="D67" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.65</v>
+        <v>34.91</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>33.15</v>
+        <v>41.29</v>
       </c>
       <c r="D68" s="6">
-        <v>37.45</v>
-      </c>
-      <c r="E68" s="8">
-        <v>4.3</v>
+        <v>50.91</v>
+      </c>
+      <c r="E68" s="7">
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>41.86</v>
+        <v>54.32</v>
       </c>
       <c r="D69" s="6">
-        <v>41.29</v>
+        <v>58.15</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.57</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>53.57</v>
+        <v>47.53</v>
       </c>
       <c r="D70" s="6">
-        <v>54.32</v>
+        <v>43.09</v>
       </c>
       <c r="E70" s="8">
-        <v>0.75</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>45.24</v>
+        <v>47.12</v>
       </c>
       <c r="D71" s="6">
-        <v>47.53</v>
-      </c>
-      <c r="E71" s="8">
-        <v>2.29</v>
+        <v>52.09</v>
+      </c>
+      <c r="E71" s="7">
+        <v>4.97</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>38.48</v>
+        <v>-83.27</v>
       </c>
       <c r="D72" s="6">
-        <v>47.12</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="E72" s="8">
-        <v>8.640000000000001</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-83.20999999999999</v>
+        <v>-51.78</v>
       </c>
       <c r="D73" s="6">
-        <v>-83.27</v>
+        <v>-34.36</v>
       </c>
       <c r="E73" s="7">
-        <v>-0.06</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-50.82</v>
+        <v>5.2</v>
       </c>
       <c r="D74" s="6">
-        <v>-51.78</v>
+        <v>117.27</v>
       </c>
       <c r="E74" s="7">
-        <v>-0.96</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-3.75</v>
+        <v>-52.54</v>
       </c>
       <c r="D75" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="E75" s="8">
-        <v>8.949999999999999</v>
+        <v>-34.26</v>
+      </c>
+      <c r="E75" s="7">
+        <v>18.28</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>2.56</v>
+        <v>-18.95</v>
       </c>
       <c r="D76" s="6">
-        <v>-52.54</v>
+        <v>-12.37</v>
       </c>
       <c r="E76" s="7">
-        <v>-55.1</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-24.02</v>
+        <v>-73.36</v>
       </c>
       <c r="D77" s="6">
-        <v>-18.95</v>
-      </c>
-      <c r="E77" s="8">
-        <v>5.07</v>
+        <v>658.54</v>
+      </c>
+      <c r="E77" s="7">
+        <v>731.9</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-81.08</v>
+        <v>-45.85</v>
       </c>
       <c r="D78" s="6">
-        <v>-73.36</v>
+        <v>-52.49</v>
       </c>
       <c r="E78" s="8">
-        <v>7.72</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-36.2</v>
+        <v>86.92</v>
       </c>
       <c r="D79" s="6">
-        <v>-45.85</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-9.65</v>
+        <v>-4.32</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-91.23999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-13.42</v>
+        <v>14.84</v>
       </c>
       <c r="D80" s="6">
-        <v>86.92</v>
+        <v>-10.52</v>
       </c>
       <c r="E80" s="8">
-        <v>100.34</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-47.56</v>
-      </c>
-      <c r="D81" s="6">
-        <v>14.84</v>
-      </c>
-      <c r="E81" s="8">
-        <v>62.4</v>
+        <v>-25.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3475,28 +3470,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3510,16 +3505,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>46.1</v>
+        <v>47.8</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="G2" s="11">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3656,31 +3651,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3918</v>
+        <v>0.3893</v>
       </c>
       <c r="B2" s="14">
-        <v>0.362</v>
+        <v>0.3623</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3085</v>
+        <v>0.3164</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2454</v>
+        <v>0.2422</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1865</v>
+        <v>0.1932</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1439</v>
+        <v>0.1443</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0595</v>
+        <v>0.0542</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0347</v>
+        <v>-0.028</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0735</v>
+        <v>-0.0757</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,12 +169,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -196,34 +196,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 53.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>50.0</t>
+    <t>53.1 → 47.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>53.1</t>
   </si>
   <si>
-    <t>41.3 → 50.9</t>
-  </si>
-  <si>
-    <t>41.3</t>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>50.9 → 48.7</t>
   </si>
   <si>
     <t>50.9</t>
   </si>
   <si>
-    <t>47.1 → 52.1</t>
-  </si>
-  <si>
-    <t>47.1</t>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>52.1 → 47.7</t>
   </si>
   <si>
     <t>52.1</t>
+  </si>
+  <si>
+    <t>47.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -807,15 +807,16 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -948,10 +949,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>672.55</v>
+        <v>653.7</v>
       </c>
       <c r="D2">
-        <v>-0.41</v>
+        <v>-2.8</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -960,46 +961,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.25</v>
+        <v>-35.12</v>
       </c>
       <c r="H2">
-        <v>83.16</v>
+        <v>78.02</v>
       </c>
       <c r="I2">
-        <v>-5.96</v>
+        <v>-6.59</v>
       </c>
       <c r="J2">
-        <v>6.53</v>
+        <v>-5.87</v>
       </c>
       <c r="K2">
-        <v>8.890000000000001</v>
+        <v>5.36</v>
       </c>
       <c r="L2">
-        <v>16.66</v>
+        <v>15.46</v>
       </c>
       <c r="M2">
-        <v>-7.57</v>
+        <v>-7.88</v>
       </c>
       <c r="N2">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>684.28</v>
+        <v>675.0599999999999</v>
       </c>
       <c r="Q2">
-        <v>698.71</v>
+        <v>697.09</v>
       </c>
       <c r="R2">
-        <v>663.0700000000001</v>
+        <v>663.1900000000001</v>
       </c>
       <c r="S2">
-        <v>639.3200000000001</v>
+        <v>640.12</v>
       </c>
       <c r="T2">
-        <v>5.2</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1014,16 +1015,16 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>45.65</v>
+        <v>40.92</v>
       </c>
       <c r="Z2">
-        <v>6.56</v>
+        <v>2.87</v>
       </c>
       <c r="AA2">
-        <v>13.1</v>
+        <v>11.06</v>
       </c>
       <c r="AB2">
-        <v>-6.54</v>
+        <v>-8.19</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1032,25 +1033,25 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>29.74</v>
+        <v>30.19</v>
       </c>
       <c r="AF2">
-        <v>-90.81999999999999</v>
+        <v>-75.53</v>
       </c>
       <c r="AG2">
-        <v>748.71</v>
+        <v>750.78</v>
       </c>
       <c r="AH2">
-        <v>648.71</v>
+        <v>643.39</v>
       </c>
       <c r="AI2">
-        <v>666.86</v>
+        <v>745.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>38.58</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1061,10 +1062,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>277.7</v>
+        <v>270.3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-2.66</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1073,46 +1074,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-12.54</v>
+        <v>-14.87</v>
       </c>
       <c r="H3">
-        <v>81.23</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I3">
-        <v>-5.09</v>
+        <v>-4.52</v>
       </c>
       <c r="J3">
-        <v>-10.32</v>
+        <v>-12.74</v>
       </c>
       <c r="K3">
-        <v>5.63</v>
+        <v>3.58</v>
       </c>
       <c r="L3">
-        <v>32.91</v>
+        <v>32.21</v>
       </c>
       <c r="M3">
-        <v>38.93</v>
+        <v>38.3</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>280.03</v>
+        <v>277.47</v>
       </c>
       <c r="Q3">
-        <v>295.34</v>
+        <v>293.4</v>
       </c>
       <c r="R3">
-        <v>282.41</v>
+        <v>282.51</v>
       </c>
       <c r="S3">
-        <v>226.91</v>
+        <v>227.46</v>
       </c>
       <c r="T3">
-        <v>22.39</v>
+        <v>18.83</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1127,43 +1128,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>42.26</v>
+        <v>38.19</v>
       </c>
       <c r="Z3">
-        <v>-2.44</v>
+        <v>-3.52</v>
       </c>
       <c r="AA3">
-        <v>1.05</v>
+        <v>0.13</v>
       </c>
       <c r="AB3">
-        <v>-3.49</v>
+        <v>-3.65</v>
       </c>
       <c r="AC3">
         <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>5.12</v>
+        <v>3.58</v>
       </c>
       <c r="AE3">
-        <v>10.78</v>
+        <v>11.24</v>
       </c>
       <c r="AF3">
-        <v>-34.36</v>
+        <v>19.54</v>
       </c>
       <c r="AG3">
-        <v>322.63</v>
+        <v>322.04</v>
       </c>
       <c r="AH3">
-        <v>268.05</v>
+        <v>264.75</v>
       </c>
       <c r="AI3">
-        <v>309.16</v>
+        <v>301.41</v>
       </c>
       <c r="AJ3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>45.68</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1174,10 +1175,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1134.9</v>
+        <v>1100.5</v>
       </c>
       <c r="D4">
-        <v>0.43</v>
+        <v>-3.03</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1186,46 +1187,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-11.94</v>
+        <v>-14.61</v>
       </c>
       <c r="H4">
-        <v>15.1</v>
+        <v>11.61</v>
       </c>
       <c r="I4">
-        <v>-3.44</v>
+        <v>-4.95</v>
       </c>
       <c r="J4">
-        <v>-4.86</v>
+        <v>-5.13</v>
       </c>
       <c r="K4">
-        <v>8.73</v>
+        <v>4.41</v>
       </c>
       <c r="L4">
-        <v>7.91</v>
+        <v>6.9</v>
       </c>
       <c r="M4">
-        <v>24.22</v>
+        <v>22.68</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1145.42</v>
+        <v>1133.96</v>
       </c>
       <c r="Q4">
-        <v>1138.88</v>
+        <v>1135.93</v>
       </c>
       <c r="R4">
-        <v>1122.21</v>
+        <v>1123.32</v>
       </c>
       <c r="S4">
-        <v>1137.6</v>
+        <v>1137.95</v>
       </c>
       <c r="T4">
-        <v>-0.24</v>
+        <v>-3.29</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1240,43 +1241,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.67</v>
+        <v>41.88</v>
       </c>
       <c r="Z4">
-        <v>4.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AA4">
-        <v>5.3</v>
+        <v>4.35</v>
       </c>
       <c r="AB4">
-        <v>-1.24</v>
+        <v>-3.79</v>
       </c>
       <c r="AC4">
-        <v>45.45</v>
+        <v>31.31</v>
       </c>
       <c r="AD4">
-        <v>57.79</v>
+        <v>44.89</v>
       </c>
       <c r="AE4">
-        <v>28.84</v>
+        <v>30.77</v>
       </c>
       <c r="AF4">
-        <v>117.27</v>
+        <v>16.08</v>
       </c>
       <c r="AG4">
-        <v>1179.53</v>
+        <v>1178.8</v>
       </c>
       <c r="AH4">
-        <v>1098.22</v>
+        <v>1093.06</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
       </c>
       <c r="AJ4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.64</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1287,10 +1288,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>747.4</v>
+        <v>732.7</v>
       </c>
       <c r="D5">
-        <v>1.23</v>
+        <v>-1.97</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1299,25 +1300,25 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.55</v>
+        <v>-15.25</v>
       </c>
       <c r="H5">
-        <v>12.92</v>
+        <v>10.7</v>
       </c>
       <c r="I5">
-        <v>-1.47</v>
+        <v>-0.85</v>
       </c>
       <c r="J5">
-        <v>6.44</v>
+        <v>-0.18</v>
       </c>
       <c r="K5">
-        <v>8.09</v>
+        <v>4.95</v>
       </c>
       <c r="L5">
-        <v>-4.61</v>
+        <v>-7.04</v>
       </c>
       <c r="M5">
-        <v>36.23</v>
+        <v>34.65</v>
       </c>
       <c r="N5">
         <v>34</v>
@@ -1326,19 +1327,19 @@
         <v>66</v>
       </c>
       <c r="P5">
-        <v>743.72</v>
+        <v>742.47</v>
       </c>
       <c r="Q5">
-        <v>744.51</v>
+        <v>744.4</v>
       </c>
       <c r="R5">
-        <v>733.0599999999999</v>
+        <v>732.95</v>
       </c>
       <c r="S5">
-        <v>747.5700000000001</v>
+        <v>747.3099999999999</v>
       </c>
       <c r="T5">
-        <v>-0.02</v>
+        <v>-1.96</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1353,43 +1354,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>53.1</v>
+        <v>47.88</v>
       </c>
       <c r="Z5">
-        <v>4.51</v>
+        <v>3.29</v>
       </c>
       <c r="AA5">
-        <v>5.12</v>
+        <v>4.75</v>
       </c>
       <c r="AB5">
-        <v>-0.6</v>
+        <v>-1.46</v>
       </c>
       <c r="AC5">
-        <v>24.48</v>
+        <v>20.21</v>
       </c>
       <c r="AD5">
-        <v>21.23</v>
+        <v>21.3</v>
       </c>
       <c r="AE5">
-        <v>21.19</v>
+        <v>21.04</v>
       </c>
       <c r="AF5">
-        <v>-34.26</v>
+        <v>-41.29</v>
       </c>
       <c r="AG5">
-        <v>772.14</v>
+        <v>772.2</v>
       </c>
       <c r="AH5">
-        <v>716.87</v>
+        <v>716.59</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
       </c>
       <c r="AJ5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>17.98</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1400,10 +1401,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>494.7</v>
+        <v>485</v>
       </c>
       <c r="D6">
-        <v>-1.29</v>
+        <v>-1.96</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1412,46 +1413,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-17.55</v>
+        <v>-19.17</v>
       </c>
       <c r="H6">
-        <v>12.8</v>
+        <v>10.59</v>
       </c>
       <c r="I6">
-        <v>-5.05</v>
+        <v>-4.9</v>
       </c>
       <c r="J6">
-        <v>-4.94</v>
+        <v>-6.37</v>
       </c>
       <c r="K6">
-        <v>-12.5</v>
+        <v>-11.85</v>
       </c>
       <c r="L6">
-        <v>-6.1</v>
+        <v>-6.43</v>
       </c>
       <c r="M6">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>501.48</v>
+        <v>496.48</v>
       </c>
       <c r="Q6">
-        <v>518.92</v>
+        <v>516.1799999999999</v>
       </c>
       <c r="R6">
-        <v>538.4299999999999</v>
+        <v>536.89</v>
       </c>
       <c r="S6">
-        <v>523.58</v>
+        <v>523.6</v>
       </c>
       <c r="T6">
-        <v>-5.52</v>
+        <v>-7.37</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1466,43 +1467,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.91</v>
+        <v>31.46</v>
       </c>
       <c r="Z6">
-        <v>-11.05</v>
+        <v>-12.2</v>
       </c>
       <c r="AA6">
-        <v>-9.5</v>
+        <v>-10.04</v>
       </c>
       <c r="AB6">
-        <v>-1.55</v>
+        <v>-2.16</v>
       </c>
       <c r="AC6">
-        <v>26.54</v>
+        <v>22.68</v>
       </c>
       <c r="AD6">
-        <v>31.93</v>
+        <v>27.35</v>
       </c>
       <c r="AE6">
-        <v>11.86</v>
+        <v>12.41</v>
       </c>
       <c r="AF6">
-        <v>-12.37</v>
+        <v>-0.15</v>
       </c>
       <c r="AG6">
-        <v>548.41</v>
+        <v>547.62</v>
       </c>
       <c r="AH6">
-        <v>489.44</v>
+        <v>484.75</v>
       </c>
       <c r="AI6">
-        <v>530.55</v>
+        <v>521.28</v>
       </c>
       <c r="AJ6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK6">
-        <v>25.89</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,10 +1514,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11346</v>
+        <v>11258</v>
       </c>
       <c r="D7">
-        <v>3.15</v>
+        <v>-0.78</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1525,46 +1526,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.81</v>
+        <v>-49.21</v>
       </c>
       <c r="H7">
-        <v>6.49</v>
+        <v>5.66</v>
       </c>
       <c r="I7">
-        <v>0.11</v>
+        <v>1.28</v>
       </c>
       <c r="J7">
-        <v>-5.66</v>
+        <v>-3.91</v>
       </c>
       <c r="K7">
-        <v>-8.33</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L7">
-        <v>-38.44</v>
+        <v>-37.7</v>
       </c>
       <c r="M7">
-        <v>19.32</v>
+        <v>18.98</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P7">
-        <v>11110</v>
+        <v>11138.4</v>
       </c>
       <c r="Q7">
-        <v>11260.75</v>
+        <v>11251.6</v>
       </c>
       <c r="R7">
-        <v>11434.42</v>
+        <v>11441.28</v>
       </c>
       <c r="S7">
-        <v>14041.64</v>
+        <v>13987.1</v>
       </c>
       <c r="T7">
-        <v>-19.2</v>
+        <v>-19.51</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1579,43 +1580,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.91</v>
+        <v>48.72</v>
       </c>
       <c r="Z7">
-        <v>-107.61</v>
+        <v>-94.69</v>
       </c>
       <c r="AA7">
-        <v>-110.97</v>
+        <v>-107.72</v>
       </c>
       <c r="AB7">
-        <v>3.36</v>
+        <v>13.02</v>
       </c>
       <c r="AC7">
-        <v>53.97</v>
+        <v>70.14</v>
       </c>
       <c r="AD7">
-        <v>43.71</v>
+        <v>52.86</v>
       </c>
       <c r="AE7">
-        <v>366.86</v>
+        <v>357.15</v>
       </c>
       <c r="AF7">
-        <v>658.54</v>
+        <v>-63.4</v>
       </c>
       <c r="AG7">
-        <v>11650.86</v>
+        <v>11632.38</v>
       </c>
       <c r="AH7">
-        <v>10870.64</v>
+        <v>10870.82</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
       </c>
       <c r="AJ7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>17.56</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1626,10 +1627,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>356.6</v>
+        <v>357.45</v>
       </c>
       <c r="D8">
-        <v>1.89</v>
+        <v>0.24</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1638,46 +1639,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.99</v>
+        <v>-2.76</v>
       </c>
       <c r="H8">
-        <v>52.19</v>
+        <v>52.55</v>
       </c>
       <c r="I8">
-        <v>-1.93</v>
+        <v>-0.9</v>
       </c>
       <c r="J8">
-        <v>4.88</v>
+        <v>6.77</v>
       </c>
       <c r="K8">
-        <v>8.890000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L8">
-        <v>5.42</v>
+        <v>10.79</v>
       </c>
       <c r="M8">
-        <v>31.64</v>
+        <v>31.71</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P8">
-        <v>355.62</v>
+        <v>354.97</v>
       </c>
       <c r="Q8">
-        <v>343.71</v>
+        <v>344.98</v>
       </c>
       <c r="R8">
-        <v>337.01</v>
+        <v>337.56</v>
       </c>
       <c r="S8">
-        <v>292.15</v>
+        <v>292.56</v>
       </c>
       <c r="T8">
-        <v>22.06</v>
+        <v>22.18</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1692,43 +1693,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.15</v>
+        <v>58.63</v>
       </c>
       <c r="Z8">
-        <v>5.9</v>
+        <v>5.99</v>
       </c>
       <c r="AA8">
-        <v>4.9</v>
+        <v>5.11</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="AC8">
-        <v>48.96</v>
+        <v>55.25</v>
       </c>
       <c r="AD8">
-        <v>57.41</v>
+        <v>53.44</v>
       </c>
       <c r="AE8">
-        <v>11.49</v>
+        <v>12.14</v>
       </c>
       <c r="AF8">
-        <v>-52.49</v>
+        <v>-26.65</v>
       </c>
       <c r="AG8">
-        <v>370.74</v>
+        <v>372.09</v>
       </c>
       <c r="AH8">
-        <v>316.69</v>
+        <v>317.87</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.74</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1739,10 +1740,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1253.4</v>
+        <v>1233</v>
       </c>
       <c r="D9">
-        <v>-1.49</v>
+        <v>-1.63</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1751,25 +1752,25 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-6.53</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="H9">
-        <v>16.13</v>
+        <v>14.24</v>
       </c>
       <c r="I9">
-        <v>-3.42</v>
+        <v>-3.16</v>
       </c>
       <c r="J9">
-        <v>-4.15</v>
+        <v>-6.13</v>
       </c>
       <c r="K9">
-        <v>2.42</v>
+        <v>0.23</v>
       </c>
       <c r="L9">
-        <v>9.130000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M9">
-        <v>14.43</v>
+        <v>13.86</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -1778,19 +1779,19 @@
         <v>68</v>
       </c>
       <c r="P9">
-        <v>1268.02</v>
+        <v>1259.98</v>
       </c>
       <c r="Q9">
-        <v>1279.9</v>
+        <v>1276.25</v>
       </c>
       <c r="R9">
-        <v>1285.94</v>
+        <v>1285.26</v>
       </c>
       <c r="S9">
-        <v>1236.84</v>
+        <v>1237.38</v>
       </c>
       <c r="T9">
-        <v>1.34</v>
+        <v>-0.35</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1802,46 +1803,46 @@
         <v>48</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>43.09</v>
+        <v>38.89</v>
       </c>
       <c r="Z9">
-        <v>-7.34</v>
+        <v>-9.9</v>
       </c>
       <c r="AA9">
-        <v>-5.49</v>
+        <v>-6.37</v>
       </c>
       <c r="AB9">
-        <v>-1.85</v>
+        <v>-3.53</v>
       </c>
       <c r="AC9">
-        <v>58.98</v>
+        <v>48.15</v>
       </c>
       <c r="AD9">
-        <v>63.18</v>
+        <v>58.32</v>
       </c>
       <c r="AE9">
-        <v>24.96</v>
+        <v>26.15</v>
       </c>
       <c r="AF9">
-        <v>-4.32</v>
+        <v>132.55</v>
       </c>
       <c r="AG9">
-        <v>1330.02</v>
+        <v>1328.93</v>
       </c>
       <c r="AH9">
-        <v>1229.77</v>
+        <v>1223.56</v>
       </c>
       <c r="AI9">
-        <v>1318</v>
+        <v>1314.04</v>
       </c>
       <c r="AJ9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>17.65</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1852,10 +1853,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.62</v>
+        <v>78.34</v>
       </c>
       <c r="D10">
-        <v>3.24</v>
+        <v>-2.83</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1864,46 +1865,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.84</v>
+        <v>-14.34</v>
       </c>
       <c r="H10">
-        <v>123.45</v>
+        <v>117.13</v>
       </c>
       <c r="I10">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="J10">
-        <v>-0.27</v>
+        <v>-1.31</v>
       </c>
       <c r="K10">
-        <v>54.77</v>
+        <v>51.18</v>
       </c>
       <c r="L10">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="M10">
-        <v>-2.8</v>
+        <v>-3.51</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P10">
-        <v>77.31999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="Q10">
-        <v>80.83</v>
+        <v>80.86</v>
       </c>
       <c r="R10">
-        <v>79.97</v>
+        <v>80.2</v>
       </c>
       <c r="S10">
-        <v>61.19</v>
+        <v>61.28</v>
       </c>
       <c r="T10">
-        <v>31.76</v>
+        <v>27.85</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1918,43 +1919,43 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>52.09</v>
+        <v>47.74</v>
       </c>
       <c r="Z10">
+        <v>-0.55</v>
+      </c>
+      <c r="AA10">
+        <v>-0.03</v>
+      </c>
+      <c r="AB10">
         <v>-0.52</v>
       </c>
-      <c r="AA10">
-        <v>0.1</v>
-      </c>
-      <c r="AB10">
-        <v>-0.62</v>
-      </c>
       <c r="AC10">
-        <v>34.93</v>
+        <v>49.46</v>
       </c>
       <c r="AD10">
-        <v>16.79</v>
+        <v>32.96</v>
       </c>
       <c r="AE10">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="AF10">
-        <v>-10.52</v>
+        <v>-37.97</v>
       </c>
       <c r="AG10">
-        <v>87.39</v>
+        <v>87.36</v>
       </c>
       <c r="AH10">
-        <v>74.26000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
       </c>
       <c r="AJ10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK10">
-        <v>46.57</v>
+        <v>44.28</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2227,13 +2228,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>6.2</v>
+        <v>6.53</v>
       </c>
       <c r="D9" s="6">
-        <v>6.53</v>
+        <v>-5.87</v>
       </c>
       <c r="E9" s="7">
-        <v>0.33</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2244,13 +2245,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.01</v>
+        <v>-10.32</v>
       </c>
       <c r="D10" s="6">
-        <v>-10.32</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.31</v>
+        <v>-12.74</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2261,13 +2262,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.17</v>
+        <v>-4.86</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.86</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-5.13</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2278,13 +2279,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>4.7</v>
+        <v>6.44</v>
       </c>
       <c r="D12" s="6">
-        <v>6.44</v>
+        <v>-0.18</v>
       </c>
       <c r="E12" s="7">
-        <v>1.74</v>
+        <v>-6.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2295,13 +2296,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.38</v>
+        <v>-4.94</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.94</v>
+        <v>-6.37</v>
       </c>
       <c r="E13" s="7">
-        <v>1.44</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2312,13 +2313,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.99</v>
+        <v>-5.66</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.66</v>
+        <v>-3.91</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.67</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2329,13 +2330,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>2.06</v>
+        <v>4.88</v>
       </c>
       <c r="D15" s="6">
-        <v>4.88</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.82</v>
+        <v>6.77</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2346,13 +2347,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.68</v>
+        <v>-4.15</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.15</v>
+        <v>-6.13</v>
       </c>
       <c r="E16" s="7">
-        <v>0.53</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2363,13 +2364,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.27</v>
+        <v>-1.31</v>
       </c>
       <c r="E17" s="7">
-        <v>0.42</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2380,13 +2381,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.46</v>
+        <v>-5.96</v>
       </c>
       <c r="D18" s="6">
-        <v>-5.96</v>
+        <v>-6.59</v>
       </c>
       <c r="E18" s="7">
-        <v>0.5</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2397,13 +2398,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.05</v>
+        <v>-5.09</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.09</v>
+        <v>-4.52</v>
       </c>
       <c r="E19" s="8">
-        <v>-2.04</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2414,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.96</v>
+        <v>-3.44</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.48</v>
+        <v>-4.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2431,13 +2432,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-1.47</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.47</v>
+        <v>-0.85</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.78</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2448,13 +2449,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.25</v>
+        <v>-5.05</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.05</v>
+        <v>-4.9</v>
       </c>
       <c r="E22" s="8">
-        <v>-1.8</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2465,13 +2466,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.95</v>
+        <v>0.11</v>
       </c>
       <c r="D23" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.06</v>
+        <v>1.28</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2482,13 +2483,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.79</v>
+        <v>-1.93</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.86</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.03</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2499,13 +2500,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>0.43</v>
+        <v>-3.42</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.42</v>
+        <v>-3.16</v>
       </c>
       <c r="E25" s="8">
-        <v>-3.85</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2516,13 +2517,13 @@
         <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>0.58</v>
+        <v>1.93</v>
       </c>
       <c r="D26" s="6">
-        <v>1.93</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.35</v>
+        <v>2.2</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2533,13 +2534,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>14.39</v>
+        <v>16.66</v>
       </c>
       <c r="D27" s="6">
-        <v>16.66</v>
+        <v>15.46</v>
       </c>
       <c r="E27" s="7">
-        <v>2.27</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2550,13 +2551,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.96</v>
+        <v>32.91</v>
       </c>
       <c r="D28" s="6">
-        <v>32.91</v>
+        <v>32.21</v>
       </c>
       <c r="E28" s="7">
-        <v>3.95</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2567,13 +2568,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>7.35</v>
+        <v>7.91</v>
       </c>
       <c r="D29" s="6">
-        <v>7.91</v>
+        <v>6.9</v>
       </c>
       <c r="E29" s="7">
-        <v>0.5600000000000001</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2584,13 +2585,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-7.53</v>
+        <v>-4.61</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.61</v>
+        <v>-7.04</v>
       </c>
       <c r="E30" s="7">
-        <v>2.92</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2601,13 +2602,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-6.04</v>
+        <v>-6.1</v>
       </c>
       <c r="D31" s="6">
-        <v>-6.1</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.06</v>
+        <v>-6.43</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2618,13 +2619,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-41.31</v>
+        <v>-38.44</v>
       </c>
       <c r="D32" s="6">
-        <v>-38.44</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.87</v>
+        <v>-37.7</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2635,13 +2636,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>2.12</v>
+        <v>5.42</v>
       </c>
       <c r="D33" s="6">
-        <v>5.42</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.3</v>
+        <v>10.79</v>
+      </c>
+      <c r="E33" s="8">
+        <v>5.37</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2652,13 +2653,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>10.73</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D34" s="6">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.6</v>
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2669,13 +2670,13 @@
         <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>-2</v>
+        <v>3.07</v>
       </c>
       <c r="D35" s="6">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="E35" s="7">
-        <v>5.07</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2686,13 +2687,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>10.28</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D36" s="6">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.39</v>
+        <v>5.36</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.53</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2703,13 +2704,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>6.71</v>
+        <v>5.63</v>
       </c>
       <c r="D37" s="6">
-        <v>5.63</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.08</v>
+        <v>3.58</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2720,13 +2721,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>9.84</v>
+        <v>8.73</v>
       </c>
       <c r="D38" s="6">
-        <v>8.73</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.11</v>
+        <v>4.41</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.32</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2737,13 +2738,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>8.27</v>
+        <v>8.09</v>
       </c>
       <c r="D39" s="6">
-        <v>8.09</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.18</v>
+        <v>4.95</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.14</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2754,13 +2755,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-11.99</v>
+        <v>-12.5</v>
       </c>
       <c r="D40" s="6">
-        <v>-12.5</v>
+        <v>-11.85</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.51</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2771,13 +2772,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-8.84</v>
+        <v>-8.33</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.33</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="E41" s="7">
-        <v>0.51</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2788,13 +2789,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>5.92</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D42" s="6">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.97</v>
+        <v>9.630000000000001</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2805,13 +2806,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>4.62</v>
+        <v>2.42</v>
       </c>
       <c r="D43" s="6">
-        <v>2.42</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.2</v>
+        <v>0.23</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2822,13 +2823,13 @@
         <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>49.71</v>
+        <v>54.77</v>
       </c>
       <c r="D44" s="6">
-        <v>54.77</v>
+        <v>51.18</v>
       </c>
       <c r="E44" s="7">
-        <v>5.06</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2839,608 +2840,642 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-32.98</v>
+        <v>-33.25</v>
       </c>
       <c r="D45" s="6">
-        <v>-33.25</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.27</v>
+        <v>-35.12</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-12.32</v>
+        <v>-12.54</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.94</v>
+        <v>-14.87</v>
       </c>
       <c r="E46" s="7">
-        <v>0.38</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
+        <v>-11.94</v>
+      </c>
+      <c r="D47" s="6">
         <v>-14.61</v>
       </c>
-      <c r="D47" s="6">
-        <v>-13.55</v>
-      </c>
       <c r="E47" s="7">
-        <v>1.06</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-16.48</v>
+        <v>-13.55</v>
       </c>
       <c r="D48" s="6">
-        <v>-17.55</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.07</v>
+        <v>-15.25</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-50.37</v>
+        <v>-17.55</v>
       </c>
       <c r="D49" s="6">
-        <v>-48.81</v>
+        <v>-19.17</v>
       </c>
       <c r="E49" s="7">
-        <v>1.56</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-4.79</v>
+        <v>-48.81</v>
       </c>
       <c r="D50" s="6">
-        <v>-2.99</v>
+        <v>-49.21</v>
       </c>
       <c r="E50" s="7">
-        <v>1.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-5.12</v>
+        <v>-2.99</v>
       </c>
       <c r="D51" s="6">
-        <v>-6.53</v>
+        <v>-2.76</v>
       </c>
       <c r="E51" s="8">
-        <v>-1.41</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-14.61</v>
+        <v>-6.53</v>
       </c>
       <c r="D52" s="6">
-        <v>-11.84</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="E52" s="7">
-        <v>2.77</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6">
-        <v>675.3</v>
+        <v>-11.84</v>
       </c>
       <c r="D53" s="6">
-        <v>672.55</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.75</v>
+        <v>-14.34</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1130</v>
+        <v>672.55</v>
       </c>
       <c r="D54" s="6">
-        <v>1134.9</v>
+        <v>653.7</v>
       </c>
       <c r="E54" s="7">
-        <v>4.9</v>
+        <v>-18.85</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>738.3</v>
+        <v>277.7</v>
       </c>
       <c r="D55" s="6">
-        <v>747.4</v>
+        <v>270.3</v>
       </c>
       <c r="E55" s="7">
-        <v>9.1</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>501.15</v>
+        <v>1134.9</v>
       </c>
       <c r="D56" s="6">
-        <v>494.7</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-6.45</v>
+        <v>1100.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-34.4</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>11000</v>
+        <v>747.4</v>
       </c>
       <c r="D57" s="6">
-        <v>11346</v>
+        <v>732.7</v>
       </c>
       <c r="E57" s="7">
-        <v>346</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>350</v>
+        <v>494.7</v>
       </c>
       <c r="D58" s="6">
-        <v>356.6</v>
+        <v>485</v>
       </c>
       <c r="E58" s="7">
-        <v>6.6</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1272.4</v>
+        <v>11346</v>
       </c>
       <c r="D59" s="6">
-        <v>1253.4</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-19</v>
+        <v>11258</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-88</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>78.09</v>
+        <v>356.6</v>
       </c>
       <c r="D60" s="6">
-        <v>80.62</v>
-      </c>
-      <c r="E60" s="7">
-        <v>2.53</v>
+        <v>357.45</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.85</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>66</v>
+        <v>1253.4</v>
       </c>
       <c r="D61" s="6">
-        <v>55</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
+        <v>1233</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-20.4</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6">
-        <v>45</v>
+        <v>80.62</v>
       </c>
       <c r="D62" s="6">
-        <v>66</v>
+        <v>78.34</v>
       </c>
       <c r="E62" s="7">
-        <v>21</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-10</v>
+        <v>66</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>46.38</v>
+        <v>66</v>
       </c>
       <c r="D64" s="6">
-        <v>45.65</v>
+        <v>77</v>
       </c>
       <c r="E64" s="8">
-        <v>-0.73</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>48.4</v>
+        <v>45.65</v>
       </c>
       <c r="D65" s="6">
-        <v>49.67</v>
+        <v>40.92</v>
       </c>
       <c r="E65" s="7">
-        <v>1.27</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>49.97</v>
+        <v>42.26</v>
       </c>
       <c r="D66" s="6">
-        <v>53.1</v>
+        <v>38.19</v>
       </c>
       <c r="E66" s="7">
-        <v>3.13</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>37.45</v>
+        <v>49.67</v>
       </c>
       <c r="D67" s="6">
-        <v>34.91</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.54</v>
+        <v>41.88</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-7.79</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>41.29</v>
+        <v>53.1</v>
       </c>
       <c r="D68" s="6">
-        <v>50.91</v>
+        <v>47.88</v>
       </c>
       <c r="E68" s="7">
-        <v>9.619999999999999</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>54.32</v>
+        <v>34.91</v>
       </c>
       <c r="D69" s="6">
-        <v>58.15</v>
+        <v>31.46</v>
       </c>
       <c r="E69" s="7">
-        <v>3.83</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>47.53</v>
+        <v>50.91</v>
       </c>
       <c r="D70" s="6">
-        <v>43.09</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-4.44</v>
+        <v>48.72</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>47.12</v>
+        <v>58.15</v>
       </c>
       <c r="D71" s="6">
-        <v>52.09</v>
-      </c>
-      <c r="E71" s="7">
-        <v>4.97</v>
+        <v>58.63</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-83.27</v>
+        <v>43.09</v>
       </c>
       <c r="D72" s="6">
-        <v>-90.81999999999999</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-7.55</v>
+        <v>38.89</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.2</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>-51.78</v>
+        <v>52.09</v>
       </c>
       <c r="D73" s="6">
-        <v>-34.36</v>
+        <v>47.74</v>
       </c>
       <c r="E73" s="7">
-        <v>17.42</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>5.2</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="D74" s="6">
-        <v>117.27</v>
-      </c>
-      <c r="E74" s="7">
-        <v>112.07</v>
+        <v>-75.53</v>
+      </c>
+      <c r="E74" s="8">
+        <v>15.29</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-52.54</v>
+        <v>-34.36</v>
       </c>
       <c r="D75" s="6">
-        <v>-34.26</v>
-      </c>
-      <c r="E75" s="7">
-        <v>18.28</v>
+        <v>19.54</v>
+      </c>
+      <c r="E75" s="8">
+        <v>53.9</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-18.95</v>
+        <v>117.27</v>
       </c>
       <c r="D76" s="6">
-        <v>-12.37</v>
+        <v>16.08</v>
       </c>
       <c r="E76" s="7">
-        <v>6.58</v>
+        <v>-101.19</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-73.36</v>
+        <v>-34.26</v>
       </c>
       <c r="D77" s="6">
-        <v>658.54</v>
+        <v>-41.29</v>
       </c>
       <c r="E77" s="7">
-        <v>731.9</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-45.85</v>
+        <v>-12.37</v>
       </c>
       <c r="D78" s="6">
-        <v>-52.49</v>
+        <v>-0.15</v>
       </c>
       <c r="E78" s="8">
-        <v>-6.64</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>86.92</v>
+        <v>658.54</v>
       </c>
       <c r="D79" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-91.23999999999999</v>
+        <v>-63.4</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-721.9400000000001</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>14.84</v>
+        <v>-52.49</v>
       </c>
       <c r="D80" s="6">
+        <v>-26.65</v>
+      </c>
+      <c r="E80" s="8">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="D81" s="6">
+        <v>132.55</v>
+      </c>
+      <c r="E81" s="8">
+        <v>136.87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
         <v>-10.52</v>
       </c>
-      <c r="E80" s="8">
-        <v>-25.36</v>
+      <c r="D82" s="6">
+        <v>-37.97</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-27.45</v>
       </c>
     </row>
   </sheetData>
@@ -3499,22 +3534,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>56.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>47.8</v>
+        <v>43.8</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.4</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3651,31 +3686,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3893</v>
+        <v>0.383</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3623</v>
+        <v>0.3465</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3164</v>
+        <v>0.3171</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2422</v>
+        <v>0.2268</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1932</v>
+        <v>0.1898</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1443</v>
+        <v>0.1386</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0542</v>
+        <v>0.0525</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.028</v>
+        <v>-0.0351</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0757</v>
+        <v>-0.0788</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,34 +196,22 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.1 → 47.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>47.9 → 51.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>47.9</t>
   </si>
   <si>
-    <t>50.9 → 48.7</t>
-  </si>
-  <si>
-    <t>50.9</t>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>48.7 → 51.1</t>
   </si>
   <si>
     <t>48.7</t>
-  </si>
-  <si>
-    <t>52.1 → 47.7</t>
-  </si>
-  <si>
-    <t>52.1</t>
-  </si>
-  <si>
-    <t>47.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +297,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,8 +423,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -808,8 +796,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -949,10 +936,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>653.7</v>
+        <v>641.6</v>
       </c>
       <c r="D2">
-        <v>-2.8</v>
+        <v>-1.85</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -961,46 +948,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.12</v>
+        <v>-36.32</v>
       </c>
       <c r="H2">
-        <v>78.02</v>
+        <v>74.73</v>
       </c>
       <c r="I2">
-        <v>-6.59</v>
+        <v>-7.56</v>
       </c>
       <c r="J2">
-        <v>-5.87</v>
+        <v>-6.51</v>
       </c>
       <c r="K2">
-        <v>5.36</v>
+        <v>2.17</v>
       </c>
       <c r="L2">
-        <v>15.46</v>
+        <v>14.18</v>
       </c>
       <c r="M2">
-        <v>-7.88</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>675.0599999999999</v>
+        <v>664.5599999999999</v>
       </c>
       <c r="Q2">
-        <v>697.09</v>
+        <v>694.98</v>
       </c>
       <c r="R2">
-        <v>663.1900000000001</v>
+        <v>663.26</v>
       </c>
       <c r="S2">
-        <v>640.12</v>
+        <v>640.86</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1015,16 +1002,16 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>40.92</v>
+        <v>38.18</v>
       </c>
       <c r="Z2">
-        <v>2.87</v>
+        <v>-1.02</v>
       </c>
       <c r="AA2">
-        <v>11.06</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB2">
-        <v>-8.19</v>
+        <v>-9.66</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1033,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>30.19</v>
+        <v>30.1</v>
       </c>
       <c r="AF2">
-        <v>-75.53</v>
+        <v>-74.06</v>
       </c>
       <c r="AG2">
-        <v>750.78</v>
+        <v>753.92</v>
       </c>
       <c r="AH2">
-        <v>643.39</v>
+        <v>636.04</v>
       </c>
       <c r="AI2">
-        <v>745.63</v>
+        <v>740.75</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>35.67</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1062,10 +1049,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>270.3</v>
+        <v>275</v>
       </c>
       <c r="D3">
-        <v>-2.66</v>
+        <v>1.74</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1074,46 +1061,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-14.87</v>
+        <v>-13.39</v>
       </c>
       <c r="H3">
-        <v>76.40000000000001</v>
+        <v>79.47</v>
       </c>
       <c r="I3">
-        <v>-4.52</v>
+        <v>-3.68</v>
       </c>
       <c r="J3">
-        <v>-12.74</v>
+        <v>-11.05</v>
       </c>
       <c r="K3">
-        <v>3.58</v>
+        <v>5.87</v>
       </c>
       <c r="L3">
-        <v>32.21</v>
+        <v>36.73</v>
       </c>
       <c r="M3">
-        <v>38.3</v>
+        <v>37.77</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>277.47</v>
+        <v>275.37</v>
       </c>
       <c r="Q3">
-        <v>293.4</v>
+        <v>291.61</v>
       </c>
       <c r="R3">
-        <v>282.51</v>
+        <v>282.79</v>
       </c>
       <c r="S3">
-        <v>227.46</v>
+        <v>228.02</v>
       </c>
       <c r="T3">
-        <v>18.83</v>
+        <v>20.6</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1128,34 +1115,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>38.19</v>
+        <v>42.01</v>
       </c>
       <c r="Z3">
-        <v>-3.52</v>
+        <v>-3.95</v>
       </c>
       <c r="AA3">
-        <v>0.13</v>
+        <v>-0.68</v>
       </c>
       <c r="AB3">
-        <v>-3.65</v>
+        <v>-3.27</v>
       </c>
       <c r="AC3">
-        <v>2.5</v>
+        <v>11.87</v>
       </c>
       <c r="AD3">
-        <v>3.58</v>
+        <v>5.63</v>
       </c>
       <c r="AE3">
-        <v>11.24</v>
+        <v>10.96</v>
       </c>
       <c r="AF3">
-        <v>19.54</v>
+        <v>-23.8</v>
       </c>
       <c r="AG3">
-        <v>322.04</v>
+        <v>320.14</v>
       </c>
       <c r="AH3">
-        <v>264.75</v>
+        <v>263.07</v>
       </c>
       <c r="AI3">
         <v>301.41</v>
@@ -1164,7 +1151,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>48.72</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1175,10 +1162,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1100.5</v>
+        <v>1097.3</v>
       </c>
       <c r="D4">
-        <v>-3.03</v>
+        <v>-0.29</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1187,46 +1174,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-14.61</v>
+        <v>-14.86</v>
       </c>
       <c r="H4">
-        <v>11.61</v>
+        <v>11.29</v>
       </c>
       <c r="I4">
-        <v>-4.95</v>
+        <v>-5.79</v>
       </c>
       <c r="J4">
-        <v>-5.13</v>
+        <v>-5.36</v>
       </c>
       <c r="K4">
-        <v>4.41</v>
+        <v>3.57</v>
       </c>
       <c r="L4">
-        <v>6.9</v>
+        <v>5.17</v>
       </c>
       <c r="M4">
-        <v>22.68</v>
+        <v>21.45</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1133.96</v>
+        <v>1120.46</v>
       </c>
       <c r="Q4">
-        <v>1135.93</v>
+        <v>1133.55</v>
       </c>
       <c r="R4">
-        <v>1123.32</v>
+        <v>1124.42</v>
       </c>
       <c r="S4">
-        <v>1137.95</v>
+        <v>1138.27</v>
       </c>
       <c r="T4">
-        <v>-3.29</v>
+        <v>-3.6</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1241,34 +1228,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.88</v>
+        <v>41.23</v>
       </c>
       <c r="Z4">
-        <v>0.5600000000000001</v>
+        <v>-2.44</v>
       </c>
       <c r="AA4">
-        <v>4.35</v>
+        <v>2.99</v>
       </c>
       <c r="AB4">
-        <v>-3.79</v>
+        <v>-5.44</v>
       </c>
       <c r="AC4">
-        <v>31.31</v>
+        <v>19.85</v>
       </c>
       <c r="AD4">
-        <v>44.89</v>
+        <v>32.2</v>
       </c>
       <c r="AE4">
-        <v>30.77</v>
+        <v>30.65</v>
       </c>
       <c r="AF4">
-        <v>16.08</v>
+        <v>-41.57</v>
       </c>
       <c r="AG4">
-        <v>1178.8</v>
+        <v>1179.49</v>
       </c>
       <c r="AH4">
-        <v>1093.06</v>
+        <v>1087.6</v>
       </c>
       <c r="AI4">
         <v>1183.12</v>
@@ -1277,7 +1264,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>23.26</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1288,10 +1275,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>732.7</v>
+        <v>742</v>
       </c>
       <c r="D5">
-        <v>-1.97</v>
+        <v>1.27</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1300,46 +1287,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.25</v>
+        <v>-14.18</v>
       </c>
       <c r="H5">
-        <v>10.7</v>
+        <v>12.1</v>
       </c>
       <c r="I5">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="J5">
-        <v>-0.18</v>
+        <v>0.97</v>
       </c>
       <c r="K5">
-        <v>4.95</v>
+        <v>5.66</v>
       </c>
       <c r="L5">
-        <v>-7.04</v>
+        <v>0.71</v>
       </c>
       <c r="M5">
-        <v>34.65</v>
+        <v>33.63</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>742.47</v>
+        <v>741.22</v>
       </c>
       <c r="Q5">
-        <v>744.4</v>
+        <v>744.58</v>
       </c>
       <c r="R5">
-        <v>732.95</v>
+        <v>733.0700000000001</v>
       </c>
       <c r="S5">
-        <v>747.3099999999999</v>
+        <v>747.04</v>
       </c>
       <c r="T5">
-        <v>-1.96</v>
+        <v>-0.67</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1354,34 +1341,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.88</v>
+        <v>51.15</v>
       </c>
       <c r="Z5">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AA5">
-        <v>4.75</v>
+        <v>4.41</v>
       </c>
       <c r="AB5">
-        <v>-1.46</v>
+        <v>-1.37</v>
       </c>
       <c r="AC5">
-        <v>20.21</v>
+        <v>29.69</v>
       </c>
       <c r="AD5">
-        <v>21.3</v>
+        <v>24.8</v>
       </c>
       <c r="AE5">
-        <v>21.04</v>
+        <v>20.83</v>
       </c>
       <c r="AF5">
-        <v>-41.29</v>
+        <v>-69.42</v>
       </c>
       <c r="AG5">
-        <v>772.2</v>
+        <v>772.27</v>
       </c>
       <c r="AH5">
-        <v>716.59</v>
+        <v>716.88</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1390,7 +1377,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>17.1</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1401,10 +1388,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>485</v>
+        <v>491.8</v>
       </c>
       <c r="D6">
-        <v>-1.96</v>
+        <v>1.4</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1413,46 +1400,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-19.17</v>
+        <v>-18.03</v>
       </c>
       <c r="H6">
-        <v>10.59</v>
+        <v>12.14</v>
       </c>
       <c r="I6">
-        <v>-4.9</v>
+        <v>-2.91</v>
       </c>
       <c r="J6">
-        <v>-6.37</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="K6">
-        <v>-11.85</v>
+        <v>-10.16</v>
       </c>
       <c r="L6">
-        <v>-6.43</v>
+        <v>-6.64</v>
       </c>
       <c r="M6">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>496.48</v>
+        <v>493.53</v>
       </c>
       <c r="Q6">
-        <v>516.1799999999999</v>
+        <v>513.8</v>
       </c>
       <c r="R6">
-        <v>536.89</v>
+        <v>535.58</v>
       </c>
       <c r="S6">
-        <v>523.6</v>
+        <v>523.64</v>
       </c>
       <c r="T6">
-        <v>-7.37</v>
+        <v>-6.08</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1467,34 +1454,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>31.46</v>
+        <v>36.22</v>
       </c>
       <c r="Z6">
-        <v>-12.2</v>
+        <v>-12.42</v>
       </c>
       <c r="AA6">
-        <v>-10.04</v>
+        <v>-10.51</v>
       </c>
       <c r="AB6">
-        <v>-2.16</v>
+        <v>-1.91</v>
       </c>
       <c r="AC6">
-        <v>22.68</v>
+        <v>19.88</v>
       </c>
       <c r="AD6">
-        <v>27.35</v>
+        <v>23.03</v>
       </c>
       <c r="AE6">
-        <v>12.41</v>
+        <v>12.14</v>
       </c>
       <c r="AF6">
-        <v>-0.15</v>
+        <v>-44.67</v>
       </c>
       <c r="AG6">
-        <v>547.62</v>
+        <v>545.02</v>
       </c>
       <c r="AH6">
-        <v>484.75</v>
+        <v>482.57</v>
       </c>
       <c r="AI6">
         <v>521.28</v>
@@ -1503,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>30.78</v>
+        <v>35.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1514,10 +1501,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11258</v>
+        <v>11350</v>
       </c>
       <c r="D7">
-        <v>-0.78</v>
+        <v>0.82</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1526,46 +1513,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.21</v>
+        <v>-48.79</v>
       </c>
       <c r="H7">
-        <v>5.66</v>
+        <v>6.52</v>
       </c>
       <c r="I7">
-        <v>1.28</v>
+        <v>2.6</v>
       </c>
       <c r="J7">
-        <v>-3.91</v>
+        <v>-0.8</v>
       </c>
       <c r="K7">
-        <v>-8.779999999999999</v>
+        <v>-6.62</v>
       </c>
       <c r="L7">
-        <v>-37.7</v>
+        <v>-33.88</v>
       </c>
       <c r="M7">
-        <v>18.98</v>
+        <v>19.07</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P7">
-        <v>11138.4</v>
+        <v>11196</v>
       </c>
       <c r="Q7">
-        <v>11251.6</v>
+        <v>11239.6</v>
       </c>
       <c r="R7">
-        <v>11441.28</v>
+        <v>11455.18</v>
       </c>
       <c r="S7">
-        <v>13987.1</v>
+        <v>13936.78</v>
       </c>
       <c r="T7">
-        <v>-19.51</v>
+        <v>-18.56</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1580,34 +1567,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.72</v>
+        <v>51.09</v>
       </c>
       <c r="Z7">
-        <v>-94.69</v>
+        <v>-76.16</v>
       </c>
       <c r="AA7">
-        <v>-107.72</v>
+        <v>-101.4</v>
       </c>
       <c r="AB7">
-        <v>13.02</v>
+        <v>25.25</v>
       </c>
       <c r="AC7">
-        <v>70.14</v>
+        <v>94.12</v>
       </c>
       <c r="AD7">
-        <v>52.86</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="AE7">
-        <v>357.15</v>
+        <v>353.72</v>
       </c>
       <c r="AF7">
-        <v>-63.4</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="AG7">
-        <v>11632.38</v>
+        <v>11589.34</v>
       </c>
       <c r="AH7">
-        <v>10870.82</v>
+        <v>10889.86</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1616,7 +1603,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>15.82</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1627,10 +1614,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>357.45</v>
+        <v>359.4</v>
       </c>
       <c r="D8">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1639,46 +1626,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.76</v>
+        <v>-2.23</v>
       </c>
       <c r="H8">
-        <v>52.55</v>
+        <v>53.39</v>
       </c>
       <c r="I8">
-        <v>-0.9</v>
+        <v>-0.73</v>
       </c>
       <c r="J8">
-        <v>6.77</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K8">
-        <v>9.630000000000001</v>
+        <v>10.93</v>
       </c>
       <c r="L8">
-        <v>10.79</v>
+        <v>11.36</v>
       </c>
       <c r="M8">
-        <v>31.71</v>
+        <v>31.82</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P8">
-        <v>354.97</v>
+        <v>354.44</v>
       </c>
       <c r="Q8">
-        <v>344.98</v>
+        <v>346.25</v>
       </c>
       <c r="R8">
-        <v>337.56</v>
+        <v>338.26</v>
       </c>
       <c r="S8">
-        <v>292.56</v>
+        <v>292.99</v>
       </c>
       <c r="T8">
-        <v>22.18</v>
+        <v>22.66</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1693,34 +1680,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.63</v>
+        <v>59.77</v>
       </c>
       <c r="Z8">
-        <v>5.99</v>
+        <v>6.14</v>
       </c>
       <c r="AA8">
-        <v>5.11</v>
+        <v>5.32</v>
       </c>
       <c r="AB8">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="AC8">
-        <v>55.25</v>
+        <v>62.02</v>
       </c>
       <c r="AD8">
-        <v>53.44</v>
+        <v>55.41</v>
       </c>
       <c r="AE8">
-        <v>12.14</v>
+        <v>11.84</v>
       </c>
       <c r="AF8">
-        <v>-26.65</v>
+        <v>-50.23</v>
       </c>
       <c r="AG8">
-        <v>372.09</v>
+        <v>373.58</v>
       </c>
       <c r="AH8">
-        <v>317.87</v>
+        <v>318.91</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1729,7 +1716,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>24.36</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1740,10 +1727,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1233</v>
+        <v>1235.3</v>
       </c>
       <c r="D9">
-        <v>-1.63</v>
+        <v>0.19</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1752,46 +1739,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-8.050000000000001</v>
+        <v>-7.88</v>
       </c>
       <c r="H9">
-        <v>14.24</v>
+        <v>14.45</v>
       </c>
       <c r="I9">
-        <v>-3.16</v>
+        <v>-3.27</v>
       </c>
       <c r="J9">
-        <v>-6.13</v>
+        <v>-5.41</v>
       </c>
       <c r="K9">
-        <v>0.23</v>
+        <v>-0.64</v>
       </c>
       <c r="L9">
-        <v>9.039999999999999</v>
+        <v>10.08</v>
       </c>
       <c r="M9">
-        <v>13.86</v>
+        <v>13.73</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P9">
-        <v>1259.98</v>
+        <v>1251.64</v>
       </c>
       <c r="Q9">
-        <v>1276.25</v>
+        <v>1272.61</v>
       </c>
       <c r="R9">
-        <v>1285.26</v>
+        <v>1285.03</v>
       </c>
       <c r="S9">
-        <v>1237.38</v>
+        <v>1237.98</v>
       </c>
       <c r="T9">
-        <v>-0.35</v>
+        <v>-0.22</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1806,34 +1793,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>38.89</v>
+        <v>39.6</v>
       </c>
       <c r="Z9">
-        <v>-9.9</v>
+        <v>-11.61</v>
       </c>
       <c r="AA9">
-        <v>-6.37</v>
+        <v>-7.42</v>
       </c>
       <c r="AB9">
-        <v>-3.53</v>
+        <v>-4.2</v>
       </c>
       <c r="AC9">
-        <v>48.15</v>
+        <v>34.65</v>
       </c>
       <c r="AD9">
-        <v>58.32</v>
+        <v>47.26</v>
       </c>
       <c r="AE9">
-        <v>26.15</v>
+        <v>25.97</v>
       </c>
       <c r="AF9">
-        <v>132.55</v>
+        <v>-28</v>
       </c>
       <c r="AG9">
-        <v>1328.93</v>
+        <v>1326.1</v>
       </c>
       <c r="AH9">
-        <v>1223.56</v>
+        <v>1219.12</v>
       </c>
       <c r="AI9">
         <v>1314.04</v>
@@ -1842,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>21.02</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1853,10 +1840,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>78.34</v>
+        <v>75.17</v>
       </c>
       <c r="D10">
-        <v>-2.83</v>
+        <v>-4.05</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1865,46 +1852,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-14.34</v>
+        <v>-17.8</v>
       </c>
       <c r="H10">
-        <v>117.13</v>
+        <v>108.34</v>
       </c>
       <c r="I10">
-        <v>2.2</v>
+        <v>-2.19</v>
       </c>
       <c r="J10">
-        <v>-1.31</v>
+        <v>-3.22</v>
       </c>
       <c r="K10">
-        <v>51.18</v>
+        <v>42.77</v>
       </c>
       <c r="L10">
-        <v>2.84</v>
+        <v>-9.85</v>
       </c>
       <c r="M10">
-        <v>-3.51</v>
+        <v>-4.93</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="P10">
-        <v>77.66</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="Q10">
-        <v>80.86</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="R10">
-        <v>80.2</v>
+        <v>80.45</v>
       </c>
       <c r="S10">
-        <v>61.28</v>
+        <v>61.36</v>
       </c>
       <c r="T10">
-        <v>27.85</v>
+        <v>22.51</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1919,34 +1906,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>47.74</v>
+        <v>42.43</v>
       </c>
       <c r="Z10">
-        <v>-0.55</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA10">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="AB10">
-        <v>-0.52</v>
+        <v>-0.62</v>
       </c>
       <c r="AC10">
-        <v>49.46</v>
+        <v>45.56</v>
       </c>
       <c r="AD10">
-        <v>32.96</v>
+        <v>43.32</v>
       </c>
       <c r="AE10">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="AF10">
-        <v>-37.97</v>
+        <v>28.05</v>
       </c>
       <c r="AG10">
-        <v>87.36</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="AH10">
-        <v>74.36</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1955,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>44.28</v>
+        <v>44.31</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2171,1317 +2158,1331 @@
         <v>63</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.87</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-6.51</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>6.53</v>
+        <v>-12.74</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.87</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-12.4</v>
+        <v>-11.05</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.69</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.32</v>
+        <v>-5.13</v>
       </c>
       <c r="D10" s="6">
-        <v>-12.74</v>
+        <v>-5.36</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.42</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.86</v>
+        <v>-0.18</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.13</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.27</v>
+        <v>0.97</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>6.44</v>
+        <v>-6.37</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.18</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E12" s="7">
-        <v>-6.62</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.94</v>
+        <v>-3.91</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.43</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.66</v>
+        <v>6.77</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.91</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E14" s="8">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>4.88</v>
+        <v>-6.13</v>
       </c>
       <c r="D15" s="6">
-        <v>6.77</v>
+        <v>-5.41</v>
       </c>
       <c r="E15" s="8">
-        <v>1.89</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.15</v>
+        <v>-1.31</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.13</v>
+        <v>-3.22</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.98</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.27</v>
+        <v>-6.59</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.31</v>
+        <v>-7.56</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.04</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.96</v>
+        <v>-4.52</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.59</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.63</v>
+        <v>-3.68</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.84</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-5.09</v>
+        <v>-4.95</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.52</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.57</v>
+        <v>-5.79</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.44</v>
+        <v>-0.85</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.51</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.47</v>
+        <v>-4.9</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.85</v>
+        <v>-2.91</v>
       </c>
       <c r="E21" s="8">
-        <v>0.62</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.05</v>
+        <v>1.28</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.9</v>
+        <v>2.6</v>
       </c>
       <c r="E22" s="8">
-        <v>0.15</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>0.11</v>
+        <v>-0.9</v>
       </c>
       <c r="D23" s="6">
-        <v>1.28</v>
+        <v>-0.73</v>
       </c>
       <c r="E23" s="8">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.93</v>
+        <v>-3.16</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.03</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.42</v>
+        <v>2.2</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.26</v>
+        <v>-2.19</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-4.39</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>1.93</v>
+        <v>15.46</v>
       </c>
       <c r="D26" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.27</v>
+        <v>14.18</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>16.66</v>
+        <v>32.21</v>
       </c>
       <c r="D27" s="6">
-        <v>15.46</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.2</v>
+        <v>36.73</v>
+      </c>
+      <c r="E27" s="8">
+        <v>4.52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>32.91</v>
+        <v>6.9</v>
       </c>
       <c r="D28" s="6">
-        <v>32.21</v>
+        <v>5.17</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.7</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>7.91</v>
+        <v>-7.04</v>
       </c>
       <c r="D29" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.01</v>
+        <v>0.71</v>
+      </c>
+      <c r="E29" s="8">
+        <v>7.75</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.61</v>
+        <v>-6.43</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.04</v>
+        <v>-6.64</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.43</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-6.1</v>
+        <v>-37.7</v>
       </c>
       <c r="D31" s="6">
-        <v>-6.43</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.33</v>
+        <v>-33.88</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.82</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-38.44</v>
+        <v>10.79</v>
       </c>
       <c r="D32" s="6">
-        <v>-37.7</v>
+        <v>11.36</v>
       </c>
       <c r="E32" s="8">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>5.42</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="D33" s="6">
-        <v>10.79</v>
+        <v>10.08</v>
       </c>
       <c r="E33" s="8">
-        <v>5.37</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>9.130000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="D34" s="6">
-        <v>9.039999999999999</v>
+        <v>-9.85</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.09</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>3.07</v>
+        <v>5.36</v>
       </c>
       <c r="D35" s="6">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.23</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>8.890000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="D36" s="6">
-        <v>5.36</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.53</v>
+        <v>5.87</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>5.63</v>
+        <v>4.41</v>
       </c>
       <c r="D37" s="6">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.05</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>8.73</v>
+        <v>4.95</v>
       </c>
       <c r="D38" s="6">
-        <v>4.41</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.32</v>
+        <v>5.66</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>8.09</v>
+        <v>-11.85</v>
       </c>
       <c r="D39" s="6">
-        <v>4.95</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.14</v>
+        <v>-10.16</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.69</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-12.5</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="D40" s="6">
-        <v>-11.85</v>
+        <v>-6.62</v>
       </c>
       <c r="E40" s="8">
-        <v>0.65</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-8.33</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.45</v>
+        <v>10.93</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>8.890000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="D42" s="6">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.74</v>
+        <v>-0.64</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>2.42</v>
+        <v>51.18</v>
       </c>
       <c r="D43" s="6">
-        <v>0.23</v>
+        <v>42.77</v>
       </c>
       <c r="E43" s="7">
-        <v>-2.19</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>54.77</v>
+        <v>-35.12</v>
       </c>
       <c r="D44" s="6">
-        <v>51.18</v>
+        <v>-36.32</v>
       </c>
       <c r="E44" s="7">
-        <v>-3.59</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-33.25</v>
+        <v>-14.87</v>
       </c>
       <c r="D45" s="6">
-        <v>-35.12</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.87</v>
+        <v>-13.39</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-12.54</v>
+        <v>-14.61</v>
       </c>
       <c r="D46" s="6">
-        <v>-14.87</v>
+        <v>-14.86</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.33</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-11.94</v>
+        <v>-15.25</v>
       </c>
       <c r="D47" s="6">
-        <v>-14.61</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.67</v>
+        <v>-14.18</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-13.55</v>
+        <v>-19.17</v>
       </c>
       <c r="D48" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.7</v>
+        <v>-18.03</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.14</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-17.55</v>
+        <v>-49.21</v>
       </c>
       <c r="D49" s="6">
-        <v>-19.17</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.62</v>
+        <v>-48.79</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-48.81</v>
+        <v>-2.76</v>
       </c>
       <c r="D50" s="6">
-        <v>-49.21</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.4</v>
+        <v>-2.23</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-2.99</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D51" s="6">
-        <v>-2.76</v>
+        <v>-7.88</v>
       </c>
       <c r="E51" s="8">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-6.53</v>
+        <v>-14.34</v>
       </c>
       <c r="D52" s="6">
-        <v>-8.050000000000001</v>
+        <v>-17.8</v>
       </c>
       <c r="E52" s="7">
-        <v>-1.52</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-11.84</v>
+        <v>653.7</v>
       </c>
       <c r="D53" s="6">
-        <v>-14.34</v>
+        <v>641.6</v>
       </c>
       <c r="E53" s="7">
-        <v>-2.5</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>672.55</v>
+        <v>270.3</v>
       </c>
       <c r="D54" s="6">
-        <v>653.7</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-18.85</v>
+        <v>275</v>
+      </c>
+      <c r="E54" s="8">
+        <v>4.7</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>277.7</v>
+        <v>1100.5</v>
       </c>
       <c r="D55" s="6">
-        <v>270.3</v>
+        <v>1097.3</v>
       </c>
       <c r="E55" s="7">
-        <v>-7.4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1134.9</v>
+        <v>732.7</v>
       </c>
       <c r="D56" s="6">
-        <v>1100.5</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-34.4</v>
+        <v>742</v>
+      </c>
+      <c r="E56" s="8">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>747.4</v>
+        <v>485</v>
       </c>
       <c r="D57" s="6">
-        <v>732.7</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-14.7</v>
+        <v>491.8</v>
+      </c>
+      <c r="E57" s="8">
+        <v>6.8</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>494.7</v>
+        <v>11258</v>
       </c>
       <c r="D58" s="6">
-        <v>485</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-9.699999999999999</v>
+        <v>11350</v>
+      </c>
+      <c r="E58" s="8">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>11346</v>
+        <v>357.45</v>
       </c>
       <c r="D59" s="6">
-        <v>11258</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-88</v>
+        <v>359.4</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.95</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>356.6</v>
+        <v>1233</v>
       </c>
       <c r="D60" s="6">
-        <v>357.45</v>
+        <v>1235.3</v>
       </c>
       <c r="E60" s="8">
-        <v>0.85</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>1253.4</v>
+        <v>78.34</v>
       </c>
       <c r="D61" s="6">
-        <v>1233</v>
+        <v>75.17</v>
       </c>
       <c r="E61" s="7">
-        <v>-20.4</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>80.62</v>
+        <v>88</v>
       </c>
       <c r="D62" s="6">
-        <v>78.34</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.28</v>
+        <v>99</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D63" s="6">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="E63" s="7">
-        <v>-11</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D64" s="6">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E64" s="8">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="6">
-        <v>45.65</v>
+        <v>99</v>
       </c>
       <c r="D65" s="6">
-        <v>40.92</v>
+        <v>88</v>
       </c>
       <c r="E65" s="7">
-        <v>-4.73</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>42.26</v>
+        <v>40.92</v>
       </c>
       <c r="D66" s="6">
-        <v>38.19</v>
+        <v>38.18</v>
       </c>
       <c r="E66" s="7">
-        <v>-4.07</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>49.67</v>
+        <v>38.19</v>
       </c>
       <c r="D67" s="6">
-        <v>41.88</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-7.79</v>
+        <v>42.01</v>
+      </c>
+      <c r="E67" s="8">
+        <v>3.82</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>53.1</v>
+        <v>41.88</v>
       </c>
       <c r="D68" s="6">
-        <v>47.88</v>
+        <v>41.23</v>
       </c>
       <c r="E68" s="7">
-        <v>-5.22</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>34.91</v>
+        <v>47.88</v>
       </c>
       <c r="D69" s="6">
-        <v>31.46</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.45</v>
+        <v>51.15</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3.27</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>50.91</v>
+        <v>31.46</v>
       </c>
       <c r="D70" s="6">
-        <v>48.72</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-2.19</v>
+        <v>36.22</v>
+      </c>
+      <c r="E70" s="8">
+        <v>4.76</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>58.15</v>
+        <v>48.72</v>
       </c>
       <c r="D71" s="6">
-        <v>58.63</v>
+        <v>51.09</v>
       </c>
       <c r="E71" s="8">
-        <v>0.48</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>43.09</v>
+        <v>58.63</v>
       </c>
       <c r="D72" s="6">
-        <v>38.89</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-4.2</v>
+        <v>59.77</v>
+      </c>
+      <c r="E72" s="8">
+        <v>1.14</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>52.09</v>
+        <v>38.89</v>
       </c>
       <c r="D73" s="6">
-        <v>47.74</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-4.35</v>
+        <v>39.6</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="6">
-        <v>-90.81999999999999</v>
+        <v>47.74</v>
       </c>
       <c r="D74" s="6">
-        <v>-75.53</v>
-      </c>
-      <c r="E74" s="8">
-        <v>15.29</v>
+        <v>42.43</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-5.31</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-34.36</v>
+        <v>-75.53</v>
       </c>
       <c r="D75" s="6">
-        <v>19.54</v>
+        <v>-74.06</v>
       </c>
       <c r="E75" s="8">
-        <v>53.9</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>117.27</v>
+        <v>19.54</v>
       </c>
       <c r="D76" s="6">
-        <v>16.08</v>
+        <v>-23.8</v>
       </c>
       <c r="E76" s="7">
-        <v>-101.19</v>
+        <v>-43.34</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-34.26</v>
+        <v>16.08</v>
       </c>
       <c r="D77" s="6">
-        <v>-41.29</v>
+        <v>-41.57</v>
       </c>
       <c r="E77" s="7">
-        <v>-7.03</v>
+        <v>-57.65</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-12.37</v>
+        <v>-41.29</v>
       </c>
       <c r="D78" s="6">
-        <v>-0.15</v>
-      </c>
-      <c r="E78" s="8">
-        <v>12.22</v>
+        <v>-69.42</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-28.13</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>658.54</v>
+        <v>-0.15</v>
       </c>
       <c r="D79" s="6">
-        <v>-63.4</v>
+        <v>-44.67</v>
       </c>
       <c r="E79" s="7">
-        <v>-721.9400000000001</v>
+        <v>-44.52</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-52.49</v>
+        <v>-63.4</v>
       </c>
       <c r="D80" s="6">
-        <v>-26.65</v>
-      </c>
-      <c r="E80" s="8">
-        <v>25.84</v>
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-17.2</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-4.32</v>
+        <v>-26.65</v>
       </c>
       <c r="D81" s="6">
-        <v>132.55</v>
-      </c>
-      <c r="E81" s="8">
-        <v>136.87</v>
+        <v>-50.23</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-23.58</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="6">
-        <v>-10.52</v>
+        <v>132.55</v>
       </c>
       <c r="D82" s="6">
+        <v>-28</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-160.55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="6">
         <v>-37.97</v>
       </c>
-      <c r="E82" s="7">
-        <v>-27.45</v>
+      <c r="D83" s="6">
+        <v>28.05</v>
+      </c>
+      <c r="E83" s="8">
+        <v>66.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3505,28 +3506,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3540,16 +3541,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>43.8</v>
+        <v>44.6</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
       <c r="G2" s="11">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3686,31 +3687,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.383</v>
+        <v>0.3777</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3465</v>
+        <v>0.3363</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3171</v>
+        <v>0.3182</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2268</v>
+        <v>0.2145</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1898</v>
+        <v>0.1907</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1386</v>
+        <v>0.1373</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0525</v>
+        <v>0.0535</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0351</v>
+        <v>-0.0493</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0788</v>
+        <v>-0.08460000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,25 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.9 → 51.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>48.7 → 51.1</t>
-  </si>
-  <si>
-    <t>48.7</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.2% → -1.2%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>-1.2%</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,10 +424,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -795,8 +799,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -936,10 +940,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>641.6</v>
+        <v>658.35</v>
       </c>
       <c r="D2">
-        <v>-1.85</v>
+        <v>2.61</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -948,46 +952,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.32</v>
+        <v>-34.66</v>
       </c>
       <c r="H2">
-        <v>74.73</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="I2">
-        <v>-7.56</v>
+        <v>-3.13</v>
       </c>
       <c r="J2">
-        <v>-6.51</v>
+        <v>-3.71</v>
       </c>
       <c r="K2">
-        <v>2.17</v>
+        <v>6.08</v>
       </c>
       <c r="L2">
-        <v>14.18</v>
+        <v>20.15</v>
       </c>
       <c r="M2">
-        <v>-8.460000000000001</v>
+        <v>-7.53</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>664.5599999999999</v>
+        <v>660.3</v>
       </c>
       <c r="Q2">
-        <v>694.98</v>
+        <v>694.28</v>
       </c>
       <c r="R2">
-        <v>663.26</v>
+        <v>663.6799999999999</v>
       </c>
       <c r="S2">
-        <v>640.86</v>
+        <v>641.7</v>
       </c>
       <c r="T2">
-        <v>0.12</v>
+        <v>2.6</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1002,34 +1006,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>38.18</v>
+        <v>43.79</v>
       </c>
       <c r="Z2">
-        <v>-1.02</v>
+        <v>-2.72</v>
       </c>
       <c r="AA2">
-        <v>8.640000000000001</v>
+        <v>6.37</v>
       </c>
       <c r="AB2">
-        <v>-9.66</v>
+        <v>-9.09</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE2">
-        <v>30.1</v>
+        <v>29.98</v>
       </c>
       <c r="AF2">
-        <v>-74.06</v>
+        <v>-73.33</v>
       </c>
       <c r="AG2">
-        <v>753.92</v>
+        <v>754.67</v>
       </c>
       <c r="AH2">
-        <v>636.04</v>
+        <v>633.89</v>
       </c>
       <c r="AI2">
         <v>740.75</v>
@@ -1038,7 +1042,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.25</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1053,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>275</v>
+        <v>282.4</v>
       </c>
       <c r="D3">
-        <v>1.74</v>
+        <v>2.69</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1061,25 +1065,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-13.39</v>
+        <v>-11.06</v>
       </c>
       <c r="H3">
-        <v>79.47</v>
+        <v>84.3</v>
       </c>
       <c r="I3">
-        <v>-3.68</v>
+        <v>2.26</v>
       </c>
       <c r="J3">
-        <v>-11.05</v>
+        <v>-9.15</v>
       </c>
       <c r="K3">
-        <v>5.87</v>
+        <v>7.97</v>
       </c>
       <c r="L3">
-        <v>36.73</v>
+        <v>40.52</v>
       </c>
       <c r="M3">
-        <v>37.77</v>
+        <v>38.88</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1088,19 +1092,19 @@
         <v>80</v>
       </c>
       <c r="P3">
-        <v>275.37</v>
+        <v>276.62</v>
       </c>
       <c r="Q3">
-        <v>291.61</v>
+        <v>290.46</v>
       </c>
       <c r="R3">
-        <v>282.79</v>
+        <v>283.33</v>
       </c>
       <c r="S3">
-        <v>228.02</v>
+        <v>228.63</v>
       </c>
       <c r="T3">
-        <v>20.6</v>
+        <v>23.52</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1115,34 +1119,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>42.01</v>
+        <v>47.51</v>
       </c>
       <c r="Z3">
-        <v>-3.95</v>
+        <v>-3.66</v>
       </c>
       <c r="AA3">
-        <v>-0.68</v>
+        <v>-1.28</v>
       </c>
       <c r="AB3">
-        <v>-3.27</v>
+        <v>-2.38</v>
       </c>
       <c r="AC3">
-        <v>11.87</v>
+        <v>36.54</v>
       </c>
       <c r="AD3">
-        <v>5.63</v>
+        <v>16.97</v>
       </c>
       <c r="AE3">
-        <v>10.96</v>
+        <v>10.81</v>
       </c>
       <c r="AF3">
-        <v>-23.8</v>
+        <v>-37.18</v>
       </c>
       <c r="AG3">
-        <v>320.14</v>
+        <v>318.51</v>
       </c>
       <c r="AH3">
-        <v>263.07</v>
+        <v>262.41</v>
       </c>
       <c r="AI3">
         <v>301.41</v>
@@ -1151,7 +1155,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>49.69</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1166,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1097.3</v>
+        <v>1085.9</v>
       </c>
       <c r="D4">
-        <v>-0.29</v>
+        <v>-1.04</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1174,46 +1178,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-14.86</v>
+        <v>-15.74</v>
       </c>
       <c r="H4">
-        <v>11.29</v>
+        <v>10.13</v>
       </c>
       <c r="I4">
-        <v>-5.79</v>
+        <v>-4.71</v>
       </c>
       <c r="J4">
-        <v>-5.36</v>
+        <v>-5.16</v>
       </c>
       <c r="K4">
-        <v>3.57</v>
+        <v>4.88</v>
       </c>
       <c r="L4">
-        <v>5.17</v>
+        <v>2.08</v>
       </c>
       <c r="M4">
-        <v>21.45</v>
+        <v>21.87</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1120.46</v>
+        <v>1109.72</v>
       </c>
       <c r="Q4">
-        <v>1133.55</v>
+        <v>1129.59</v>
       </c>
       <c r="R4">
-        <v>1124.42</v>
+        <v>1125.43</v>
       </c>
       <c r="S4">
-        <v>1138.27</v>
+        <v>1138.64</v>
       </c>
       <c r="T4">
-        <v>-3.6</v>
+        <v>-4.63</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1228,43 +1232,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.23</v>
+        <v>38.92</v>
       </c>
       <c r="Z4">
-        <v>-2.44</v>
+        <v>-5.68</v>
       </c>
       <c r="AA4">
-        <v>2.99</v>
+        <v>1.26</v>
       </c>
       <c r="AB4">
-        <v>-5.44</v>
+        <v>-6.94</v>
       </c>
       <c r="AC4">
-        <v>19.85</v>
+        <v>4.59</v>
       </c>
       <c r="AD4">
-        <v>32.2</v>
+        <v>18.58</v>
       </c>
       <c r="AE4">
-        <v>30.65</v>
+        <v>32.93</v>
       </c>
       <c r="AF4">
-        <v>-41.57</v>
+        <v>494.44</v>
       </c>
       <c r="AG4">
-        <v>1179.49</v>
+        <v>1177.7</v>
       </c>
       <c r="AH4">
-        <v>1087.6</v>
+        <v>1081.48</v>
       </c>
       <c r="AI4">
-        <v>1183.12</v>
+        <v>1161.19</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>26.39</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1279,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>742</v>
+        <v>750.95</v>
       </c>
       <c r="D5">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1287,46 +1291,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.18</v>
+        <v>-13.14</v>
       </c>
       <c r="H5">
-        <v>12.1</v>
+        <v>13.45</v>
       </c>
       <c r="I5">
-        <v>-0.84</v>
+        <v>0.7</v>
       </c>
       <c r="J5">
-        <v>0.97</v>
+        <v>1.7</v>
       </c>
       <c r="K5">
-        <v>5.66</v>
+        <v>7.98</v>
       </c>
       <c r="L5">
-        <v>0.71</v>
+        <v>1.91</v>
       </c>
       <c r="M5">
-        <v>33.63</v>
+        <v>35.04</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>741.22</v>
+        <v>742.27</v>
       </c>
       <c r="Q5">
-        <v>744.58</v>
+        <v>745.23</v>
       </c>
       <c r="R5">
-        <v>733.0700000000001</v>
+        <v>733.8</v>
       </c>
       <c r="S5">
-        <v>747.04</v>
+        <v>746.8</v>
       </c>
       <c r="T5">
-        <v>-0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1338,37 +1342,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.15</v>
+        <v>54.14</v>
       </c>
       <c r="Z5">
-        <v>3.03</v>
+        <v>3.51</v>
       </c>
       <c r="AA5">
-        <v>4.41</v>
+        <v>4.23</v>
       </c>
       <c r="AB5">
-        <v>-1.37</v>
+        <v>-0.71</v>
       </c>
       <c r="AC5">
-        <v>29.69</v>
+        <v>38.25</v>
       </c>
       <c r="AD5">
-        <v>24.8</v>
+        <v>29.38</v>
       </c>
       <c r="AE5">
-        <v>20.83</v>
+        <v>20.6</v>
       </c>
       <c r="AF5">
-        <v>-69.42</v>
+        <v>-62.87</v>
       </c>
       <c r="AG5">
-        <v>772.27</v>
+        <v>772.87</v>
       </c>
       <c r="AH5">
-        <v>716.88</v>
+        <v>717.59</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1377,7 +1381,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>15.8</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1392,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>491.8</v>
+        <v>494.9</v>
       </c>
       <c r="D6">
-        <v>1.4</v>
+        <v>0.63</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1400,46 +1404,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-18.03</v>
+        <v>-17.52</v>
       </c>
       <c r="H6">
-        <v>12.14</v>
+        <v>12.85</v>
       </c>
       <c r="I6">
-        <v>-2.91</v>
+        <v>-0.02</v>
       </c>
       <c r="J6">
-        <v>-8.890000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="K6">
-        <v>-10.16</v>
+        <v>-9.06</v>
       </c>
       <c r="L6">
-        <v>-6.64</v>
+        <v>-6.45</v>
       </c>
       <c r="M6">
-        <v>5.35</v>
+        <v>5.93</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P6">
-        <v>493.53</v>
+        <v>493.51</v>
       </c>
       <c r="Q6">
-        <v>513.8</v>
+        <v>511.55</v>
       </c>
       <c r="R6">
-        <v>535.58</v>
+        <v>534.45</v>
       </c>
       <c r="S6">
-        <v>523.64</v>
+        <v>523.73</v>
       </c>
       <c r="T6">
-        <v>-6.08</v>
+        <v>-5.5</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1454,34 +1458,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>36.22</v>
+        <v>38.33</v>
       </c>
       <c r="Z6">
-        <v>-12.42</v>
+        <v>-12.2</v>
       </c>
       <c r="AA6">
-        <v>-10.51</v>
+        <v>-10.85</v>
       </c>
       <c r="AB6">
-        <v>-1.91</v>
+        <v>-1.35</v>
       </c>
       <c r="AC6">
-        <v>19.88</v>
+        <v>27.67</v>
       </c>
       <c r="AD6">
-        <v>23.03</v>
+        <v>23.41</v>
       </c>
       <c r="AE6">
-        <v>12.14</v>
+        <v>12.31</v>
       </c>
       <c r="AF6">
-        <v>-44.67</v>
+        <v>131.31</v>
       </c>
       <c r="AG6">
-        <v>545.02</v>
+        <v>541.3200000000001</v>
       </c>
       <c r="AH6">
-        <v>482.57</v>
+        <v>481.78</v>
       </c>
       <c r="AI6">
         <v>521.28</v>
@@ -1490,7 +1494,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>35.02</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1505,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11350</v>
+        <v>11313</v>
       </c>
       <c r="D7">
-        <v>0.82</v>
+        <v>-0.33</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1513,22 +1517,22 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.79</v>
+        <v>-48.96</v>
       </c>
       <c r="H7">
-        <v>6.52</v>
+        <v>6.18</v>
       </c>
       <c r="I7">
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>-0.8</v>
+        <v>-2.39</v>
       </c>
       <c r="K7">
-        <v>-6.62</v>
+        <v>-3.87</v>
       </c>
       <c r="L7">
-        <v>-33.88</v>
+        <v>-30.63</v>
       </c>
       <c r="M7">
         <v>19.07</v>
@@ -1537,22 +1541,22 @@
         <v>12</v>
       </c>
       <c r="O7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P7">
-        <v>11196</v>
+        <v>11253.4</v>
       </c>
       <c r="Q7">
-        <v>11239.6</v>
+        <v>11231.65</v>
       </c>
       <c r="R7">
-        <v>11455.18</v>
+        <v>11464.14</v>
       </c>
       <c r="S7">
-        <v>13936.78</v>
+        <v>13887.94</v>
       </c>
       <c r="T7">
-        <v>-18.56</v>
+        <v>-18.54</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1567,34 +1571,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>51.09</v>
+        <v>50.09</v>
       </c>
       <c r="Z7">
-        <v>-76.16</v>
+        <v>-63.72</v>
       </c>
       <c r="AA7">
-        <v>-101.4</v>
+        <v>-93.87</v>
       </c>
       <c r="AB7">
-        <v>25.25</v>
+        <v>30.15</v>
       </c>
       <c r="AC7">
-        <v>94.12</v>
+        <v>91.47</v>
       </c>
       <c r="AD7">
-        <v>72.73999999999999</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="AE7">
-        <v>353.72</v>
+        <v>341.31</v>
       </c>
       <c r="AF7">
-        <v>-80.59999999999999</v>
+        <v>-71.09</v>
       </c>
       <c r="AG7">
-        <v>11589.34</v>
+        <v>11566.04</v>
       </c>
       <c r="AH7">
-        <v>10889.86</v>
+        <v>10897.26</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1603,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>15.34</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,10 +1618,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>359.4</v>
+        <v>363.05</v>
       </c>
       <c r="D8">
-        <v>0.55</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1626,46 +1630,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-2.23</v>
+        <v>-1.24</v>
       </c>
       <c r="H8">
-        <v>53.39</v>
+        <v>54.94</v>
       </c>
       <c r="I8">
-        <v>-0.73</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
-        <v>8.220000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="K8">
-        <v>10.93</v>
+        <v>12.59</v>
       </c>
       <c r="L8">
-        <v>11.36</v>
+        <v>15.16</v>
       </c>
       <c r="M8">
-        <v>31.82</v>
+        <v>32.23</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P8">
-        <v>354.44</v>
+        <v>357.3</v>
       </c>
       <c r="Q8">
-        <v>346.25</v>
+        <v>347.75</v>
       </c>
       <c r="R8">
-        <v>338.26</v>
+        <v>339.07</v>
       </c>
       <c r="S8">
-        <v>292.99</v>
+        <v>293.44</v>
       </c>
       <c r="T8">
-        <v>22.66</v>
+        <v>23.72</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1680,34 +1684,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>59.77</v>
+        <v>61.89</v>
       </c>
       <c r="Z8">
-        <v>6.14</v>
+        <v>6.48</v>
       </c>
       <c r="AA8">
-        <v>5.32</v>
+        <v>5.55</v>
       </c>
       <c r="AB8">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="AC8">
-        <v>62.02</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="AD8">
-        <v>55.41</v>
+        <v>61.32</v>
       </c>
       <c r="AE8">
-        <v>11.84</v>
+        <v>11.54</v>
       </c>
       <c r="AF8">
-        <v>-50.23</v>
+        <v>-51.22</v>
       </c>
       <c r="AG8">
-        <v>373.58</v>
+        <v>375.32</v>
       </c>
       <c r="AH8">
-        <v>318.91</v>
+        <v>320.18</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1716,7 +1720,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.52</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1727,10 +1731,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1235.3</v>
+        <v>1259.6</v>
       </c>
       <c r="D9">
-        <v>0.19</v>
+        <v>1.97</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1739,25 +1743,25 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-7.88</v>
+        <v>-6.07</v>
       </c>
       <c r="H9">
-        <v>14.45</v>
+        <v>16.71</v>
       </c>
       <c r="I9">
-        <v>-3.27</v>
+        <v>-0.36</v>
       </c>
       <c r="J9">
-        <v>-5.41</v>
+        <v>-3.7</v>
       </c>
       <c r="K9">
-        <v>-0.64</v>
+        <v>1.06</v>
       </c>
       <c r="L9">
-        <v>10.08</v>
+        <v>10.23</v>
       </c>
       <c r="M9">
-        <v>13.73</v>
+        <v>14.86</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -1766,19 +1770,19 @@
         <v>67</v>
       </c>
       <c r="P9">
-        <v>1251.64</v>
+        <v>1250.74</v>
       </c>
       <c r="Q9">
-        <v>1272.61</v>
+        <v>1269.34</v>
       </c>
       <c r="R9">
-        <v>1285.03</v>
+        <v>1285.41</v>
       </c>
       <c r="S9">
-        <v>1237.98</v>
+        <v>1238.87</v>
       </c>
       <c r="T9">
-        <v>-0.22</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1790,37 +1794,37 @@
         <v>48</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>39.6</v>
+        <v>46.7</v>
       </c>
       <c r="Z9">
-        <v>-11.61</v>
+        <v>-10.88</v>
       </c>
       <c r="AA9">
-        <v>-7.42</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="AB9">
-        <v>-4.2</v>
+        <v>-2.77</v>
       </c>
       <c r="AC9">
-        <v>34.65</v>
+        <v>36.78</v>
       </c>
       <c r="AD9">
-        <v>47.26</v>
+        <v>39.86</v>
       </c>
       <c r="AE9">
-        <v>25.97</v>
+        <v>26.12</v>
       </c>
       <c r="AF9">
-        <v>-28</v>
+        <v>-7.26</v>
       </c>
       <c r="AG9">
-        <v>1326.1</v>
+        <v>1317.02</v>
       </c>
       <c r="AH9">
-        <v>1219.12</v>
+        <v>1221.66</v>
       </c>
       <c r="AI9">
         <v>1314.04</v>
@@ -1829,7 +1833,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.94</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1840,10 +1844,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>75.17</v>
+        <v>77.64</v>
       </c>
       <c r="D10">
-        <v>-4.05</v>
+        <v>3.29</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1852,88 +1856,88 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-17.8</v>
+        <v>-15.1</v>
       </c>
       <c r="H10">
-        <v>108.34</v>
+        <v>115.19</v>
       </c>
       <c r="I10">
-        <v>-2.19</v>
+        <v>4.35</v>
       </c>
       <c r="J10">
-        <v>-3.22</v>
+        <v>-4.79</v>
       </c>
       <c r="K10">
-        <v>42.77</v>
+        <v>46.85</v>
       </c>
       <c r="L10">
-        <v>-9.85</v>
+        <v>-9.93</v>
       </c>
       <c r="M10">
-        <v>-4.93</v>
+        <v>-4.33</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P10">
-        <v>77.31999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="Q10">
-        <v>80.54000000000001</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="R10">
-        <v>80.45</v>
+        <v>80.62</v>
       </c>
       <c r="S10">
-        <v>61.36</v>
+        <v>61.46</v>
       </c>
       <c r="T10">
-        <v>22.51</v>
+        <v>26.33</v>
       </c>
       <c r="U10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V10" t="s">
         <v>47</v>
       </c>
       <c r="W10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>42.43</v>
+        <v>47.34</v>
       </c>
       <c r="Z10">
         <v>-0.8100000000000001</v>
       </c>
       <c r="AA10">
-        <v>-0.19</v>
+        <v>-0.31</v>
       </c>
       <c r="AB10">
-        <v>-0.62</v>
+        <v>-0.5</v>
       </c>
       <c r="AC10">
-        <v>45.56</v>
+        <v>45.9</v>
       </c>
       <c r="AD10">
-        <v>43.32</v>
+        <v>46.97</v>
       </c>
       <c r="AE10">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="AF10">
-        <v>28.05</v>
+        <v>-54.3</v>
       </c>
       <c r="AG10">
-        <v>87.51000000000001</v>
+        <v>86.83</v>
       </c>
       <c r="AH10">
-        <v>73.56999999999999</v>
+        <v>73.47</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1942,7 +1946,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>44.31</v>
+        <v>44.33</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2123,7 +2127,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2142,1347 +2146,1282 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-6.51</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-11.05</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-9.15</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-5.36</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5.16</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-8.27</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-0.8</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.39</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D15" s="7">
+        <v>8.67</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-5.41</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.22</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-4.79</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.87</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-6.51</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-7.56</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.13</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-3.68</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2.26</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-5.79</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.71</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.84</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.91</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.02</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-0.73</v>
+      </c>
+      <c r="D23" s="7">
+        <v>4.1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-3.27</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-2.19</v>
+      </c>
+      <c r="D25" s="7">
+        <v>4.35</v>
+      </c>
+      <c r="E25" s="8">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>14.18</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20.15</v>
+      </c>
+      <c r="E26" s="8">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>36.73</v>
+      </c>
+      <c r="D27" s="7">
+        <v>40.52</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>5.17</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2.08</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-6.64</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-6.45</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-33.88</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-30.63</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>11.36</v>
+      </c>
+      <c r="D32" s="7">
+        <v>15.16</v>
+      </c>
+      <c r="E32" s="8">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>10.08</v>
+      </c>
+      <c r="D33" s="7">
+        <v>10.23</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-9.85</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-9.93</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2.17</v>
+      </c>
+      <c r="D35" s="7">
+        <v>6.08</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5.87</v>
+      </c>
+      <c r="D36" s="7">
+        <v>7.97</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>3.57</v>
+      </c>
+      <c r="D37" s="7">
+        <v>4.88</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>5.66</v>
+      </c>
+      <c r="D38" s="7">
+        <v>7.98</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-10.16</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-9.06</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-6.62</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-3.87</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>10.93</v>
+      </c>
+      <c r="D41" s="7">
+        <v>12.59</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
         <v>-0.64</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D42" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>42.77</v>
+      </c>
+      <c r="D43" s="7">
+        <v>46.85</v>
+      </c>
+      <c r="E43" s="8">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-36.32</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-34.66</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-12.74</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-11.05</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-13.39</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-11.06</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.13</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.36</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-14.86</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-15.74</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-14.18</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-13.14</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-8.890000000000001</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-18.03</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-17.52</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-48.79</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-48.96</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>6.77</v>
-      </c>
-      <c r="D14" s="6">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-2.23</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-1.24</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-6.13</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-7.88</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-6.07</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-17.8</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-15.1</v>
+      </c>
+      <c r="E52" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.59</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>641.6</v>
+      </c>
+      <c r="D53" s="7">
+        <v>658.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.52</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>275</v>
+      </c>
+      <c r="D54" s="7">
+        <v>282.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-5.79</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1097.3</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1085.9</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.85</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>742</v>
+      </c>
+      <c r="D56" s="7">
+        <v>750.95</v>
+      </c>
+      <c r="E56" s="8">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-4.9</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>491.8</v>
+      </c>
+      <c r="D57" s="7">
+        <v>494.9</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11350</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11313</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.73</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>359.4</v>
+      </c>
+      <c r="D59" s="7">
+        <v>363.05</v>
+      </c>
+      <c r="E59" s="8">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1235.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1259.6</v>
+      </c>
+      <c r="E60" s="8">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.19</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>75.17</v>
+      </c>
+      <c r="D61" s="7">
+        <v>77.64</v>
+      </c>
+      <c r="E61" s="8">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>15.46</v>
-      </c>
-      <c r="D26" s="6">
-        <v>14.18</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>38.18</v>
+      </c>
+      <c r="D62" s="7">
+        <v>43.79</v>
+      </c>
+      <c r="E62" s="8">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>32.21</v>
-      </c>
-      <c r="D27" s="6">
-        <v>36.73</v>
-      </c>
-      <c r="E27" s="8">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>42.01</v>
+      </c>
+      <c r="D63" s="7">
+        <v>47.51</v>
+      </c>
+      <c r="E63" s="8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="D28" s="6">
-        <v>5.17</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>41.23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>38.92</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0.71</v>
-      </c>
-      <c r="E29" s="8">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>51.15</v>
+      </c>
+      <c r="D65" s="7">
+        <v>54.14</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-6.43</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.64</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>36.22</v>
+      </c>
+      <c r="D66" s="7">
+        <v>38.33</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-37.7</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.88</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>51.09</v>
+      </c>
+      <c r="D67" s="7">
+        <v>50.09</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>10.79</v>
-      </c>
-      <c r="D32" s="6">
-        <v>11.36</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>59.77</v>
+      </c>
+      <c r="D68" s="7">
+        <v>61.89</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="D33" s="6">
-        <v>10.08</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>39.6</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46.7</v>
+      </c>
+      <c r="E69" s="8">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>2.84</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-9.85</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-12.69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>42.43</v>
+      </c>
+      <c r="D70" s="7">
+        <v>47.34</v>
+      </c>
+      <c r="E70" s="8">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>5.36</v>
-      </c>
-      <c r="D35" s="6">
-        <v>2.17</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-74.06</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-73.33</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.58</v>
-      </c>
-      <c r="D36" s="6">
-        <v>5.87</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-23.8</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-37.18</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-13.38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4.41</v>
-      </c>
-      <c r="D37" s="6">
-        <v>3.57</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-41.57</v>
+      </c>
+      <c r="D73" s="7">
+        <v>494.44</v>
+      </c>
+      <c r="E73" s="8">
+        <v>536.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>4.95</v>
-      </c>
-      <c r="D38" s="6">
-        <v>5.66</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-69.42</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-62.87</v>
+      </c>
+      <c r="E74" s="8">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-11.85</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-10.16</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-44.67</v>
+      </c>
+      <c r="D75" s="7">
+        <v>131.31</v>
+      </c>
+      <c r="E75" s="8">
+        <v>175.98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-6.62</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-71.09</v>
+      </c>
+      <c r="E76" s="8">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="D41" s="6">
-        <v>10.93</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-50.23</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-51.22</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-28</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-7.26</v>
+      </c>
+      <c r="E78" s="8">
+        <v>20.74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>51.18</v>
-      </c>
-      <c r="D43" s="6">
-        <v>42.77</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-8.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-35.12</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-36.32</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-14.87</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-13.39</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-14.61</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.86</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-14.18</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-19.17</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-18.03</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-49.21</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-48.79</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-2.76</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-7.88</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-14.34</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-17.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>653.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>641.6</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-12.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>270.3</v>
-      </c>
-      <c r="D54" s="6">
-        <v>275</v>
-      </c>
-      <c r="E54" s="8">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1100.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1097.3</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>732.7</v>
-      </c>
-      <c r="D56" s="6">
-        <v>742</v>
-      </c>
-      <c r="E56" s="8">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>485</v>
-      </c>
-      <c r="D57" s="6">
-        <v>491.8</v>
-      </c>
-      <c r="E57" s="8">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>11258</v>
-      </c>
-      <c r="D58" s="6">
-        <v>11350</v>
-      </c>
-      <c r="E58" s="8">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>357.45</v>
-      </c>
-      <c r="D59" s="6">
-        <v>359.4</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1233</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1235.3</v>
-      </c>
-      <c r="E60" s="8">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>78.34</v>
-      </c>
-      <c r="D61" s="6">
-        <v>75.17</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>88</v>
-      </c>
-      <c r="D62" s="6">
-        <v>99</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>34</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>34</v>
-      </c>
-      <c r="D64" s="6">
-        <v>55</v>
-      </c>
-      <c r="E64" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="6">
-        <v>99</v>
-      </c>
-      <c r="D65" s="6">
-        <v>88</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>40.92</v>
-      </c>
-      <c r="D66" s="6">
-        <v>38.18</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>38.19</v>
-      </c>
-      <c r="D67" s="6">
-        <v>42.01</v>
-      </c>
-      <c r="E67" s="8">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.88</v>
-      </c>
-      <c r="D68" s="6">
-        <v>41.23</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>47.88</v>
-      </c>
-      <c r="D69" s="6">
-        <v>51.15</v>
-      </c>
-      <c r="E69" s="8">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>31.46</v>
-      </c>
-      <c r="D70" s="6">
-        <v>36.22</v>
-      </c>
-      <c r="E70" s="8">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>48.72</v>
-      </c>
-      <c r="D71" s="6">
-        <v>51.09</v>
-      </c>
-      <c r="E71" s="8">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>58.63</v>
-      </c>
-      <c r="D72" s="6">
-        <v>59.77</v>
-      </c>
-      <c r="E72" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>38.89</v>
-      </c>
-      <c r="D73" s="6">
-        <v>39.6</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="6">
-        <v>47.74</v>
-      </c>
-      <c r="D74" s="6">
-        <v>42.43</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-5.31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="6">
-        <v>-75.53</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-74.06</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>19.54</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-23.8</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-43.34</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>16.08</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-41.57</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-57.65</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-41.29</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-69.42</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-28.13</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-0.15</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-44.67</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-44.52</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-63.4</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-80.59999999999999</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-17.2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-26.65</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-50.23</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-23.58</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>132.55</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-28</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-160.55</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>-37.97</v>
-      </c>
-      <c r="D83" s="6">
+      <c r="C79" s="7">
         <v>28.05</v>
       </c>
-      <c r="E83" s="8">
-        <v>66.02</v>
+      <c r="D79" s="7">
+        <v>-54.3</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-82.34999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3502,61 +3441,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>76</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.6</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-3.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>47.6</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
-        <v>40</v>
+      <c r="I2" s="12">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3657,61 +3596,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3777</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3363</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3182</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2145</v>
-      </c>
-      <c r="E2" s="14">
+      <c r="A2" s="15">
+        <v>0.3888</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3504</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3223</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2187</v>
+      </c>
+      <c r="E2" s="15">
         <v>0.1907</v>
       </c>
-      <c r="F2" s="14">
-        <v>0.1373</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0535</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0493</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.08460000000000001</v>
+      <c r="F2" s="15">
+        <v>0.1486</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0593</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0433</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.07530000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,28 +193,49 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.2% → -1.2%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.2% → -3.7%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.2%</t>
   </si>
   <si>
+    <t>-3.7%</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>54.1 → 47.6</t>
+  </si>
+  <si>
+    <t>54.1</t>
+  </si>
+  <si>
+    <t>47.6</t>
+  </si>
+  <si>
+    <t>50.1 → 48.9</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -266,7 +287,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,7 +321,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -312,8 +333,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,13 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,12 +461,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -441,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -800,7 +834,9 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -940,10 +976,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>658.35</v>
+        <v>653.25</v>
       </c>
       <c r="D2">
-        <v>2.61</v>
+        <v>-0.77</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -952,46 +988,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-34.66</v>
+        <v>-35.17</v>
       </c>
       <c r="H2">
-        <v>79.29000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I2">
-        <v>-3.13</v>
+        <v>-3.27</v>
       </c>
       <c r="J2">
-        <v>-3.71</v>
+        <v>-2.84</v>
       </c>
       <c r="K2">
-        <v>6.08</v>
+        <v>0.26</v>
       </c>
       <c r="L2">
-        <v>20.15</v>
+        <v>17.26</v>
       </c>
       <c r="M2">
-        <v>-7.53</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>660.3</v>
+        <v>655.89</v>
       </c>
       <c r="Q2">
-        <v>694.28</v>
+        <v>691.99</v>
       </c>
       <c r="R2">
-        <v>663.6799999999999</v>
+        <v>664.04</v>
       </c>
       <c r="S2">
-        <v>641.7</v>
+        <v>642.55</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1006,34 +1042,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>43.79</v>
+        <v>42.52</v>
       </c>
       <c r="Z2">
-        <v>-2.72</v>
+        <v>-4.43</v>
       </c>
       <c r="AA2">
-        <v>6.37</v>
+        <v>4.21</v>
       </c>
       <c r="AB2">
-        <v>-9.09</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="AC2">
-        <v>6.13</v>
+        <v>11.51</v>
       </c>
       <c r="AD2">
-        <v>2.04</v>
+        <v>5.88</v>
       </c>
       <c r="AE2">
-        <v>29.98</v>
+        <v>29.8</v>
       </c>
       <c r="AF2">
-        <v>-73.33</v>
+        <v>-86.62</v>
       </c>
       <c r="AG2">
-        <v>754.67</v>
+        <v>755.03</v>
       </c>
       <c r="AH2">
-        <v>633.89</v>
+        <v>628.9400000000001</v>
       </c>
       <c r="AI2">
         <v>740.75</v>
@@ -1042,7 +1078,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.31</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,10 +1089,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>282.4</v>
+        <v>281.9</v>
       </c>
       <c r="D3">
-        <v>2.69</v>
+        <v>-0.18</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1065,46 +1101,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-11.06</v>
+        <v>-11.21</v>
       </c>
       <c r="H3">
-        <v>84.3</v>
+        <v>83.97</v>
       </c>
       <c r="I3">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="J3">
-        <v>-9.15</v>
+        <v>-7.66</v>
       </c>
       <c r="K3">
-        <v>7.97</v>
+        <v>8.57</v>
       </c>
       <c r="L3">
-        <v>40.52</v>
+        <v>39.13</v>
       </c>
       <c r="M3">
-        <v>38.88</v>
+        <v>38.73</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>276.62</v>
+        <v>277.46</v>
       </c>
       <c r="Q3">
-        <v>290.46</v>
+        <v>289.08</v>
       </c>
       <c r="R3">
-        <v>283.33</v>
+        <v>283.95</v>
       </c>
       <c r="S3">
-        <v>228.63</v>
+        <v>229.24</v>
       </c>
       <c r="T3">
-        <v>23.52</v>
+        <v>22.97</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1119,34 +1155,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>47.51</v>
+        <v>47.18</v>
       </c>
       <c r="Z3">
-        <v>-3.66</v>
+        <v>-3.42</v>
       </c>
       <c r="AA3">
-        <v>-1.28</v>
+        <v>-1.71</v>
       </c>
       <c r="AB3">
-        <v>-2.38</v>
+        <v>-1.72</v>
       </c>
       <c r="AC3">
-        <v>36.54</v>
+        <v>61.55</v>
       </c>
       <c r="AD3">
-        <v>16.97</v>
+        <v>36.65</v>
       </c>
       <c r="AE3">
-        <v>10.81</v>
+        <v>10.42</v>
       </c>
       <c r="AF3">
-        <v>-37.18</v>
+        <v>-57.64</v>
       </c>
       <c r="AG3">
-        <v>318.51</v>
+        <v>315.86</v>
       </c>
       <c r="AH3">
-        <v>262.41</v>
+        <v>262.29</v>
       </c>
       <c r="AI3">
         <v>301.41</v>
@@ -1155,7 +1191,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>46.96</v>
+        <v>44.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1202,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1085.9</v>
+        <v>1061</v>
       </c>
       <c r="D4">
-        <v>-1.04</v>
+        <v>-2.29</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1178,49 +1214,49 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-15.74</v>
+        <v>-17.68</v>
       </c>
       <c r="H4">
-        <v>10.13</v>
+        <v>7.61</v>
       </c>
       <c r="I4">
-        <v>-4.71</v>
+        <v>-6.11</v>
       </c>
       <c r="J4">
-        <v>-5.16</v>
+        <v>-8.93</v>
       </c>
       <c r="K4">
-        <v>4.88</v>
+        <v>3.87</v>
       </c>
       <c r="L4">
-        <v>2.08</v>
+        <v>-0.38</v>
       </c>
       <c r="M4">
-        <v>21.87</v>
+        <v>21.43</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>1109.72</v>
+        <v>1095.92</v>
       </c>
       <c r="Q4">
-        <v>1129.59</v>
+        <v>1125.25</v>
       </c>
       <c r="R4">
-        <v>1125.43</v>
+        <v>1125.33</v>
       </c>
       <c r="S4">
-        <v>1138.64</v>
+        <v>1138.94</v>
       </c>
       <c r="T4">
-        <v>-4.63</v>
+        <v>-6.84</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V4" t="s">
         <v>48</v>
@@ -1229,37 +1265,37 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.92</v>
+        <v>34.39</v>
       </c>
       <c r="Z4">
-        <v>-5.68</v>
+        <v>-10.13</v>
       </c>
       <c r="AA4">
-        <v>1.26</v>
+        <v>-1.02</v>
       </c>
       <c r="AB4">
-        <v>-6.94</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="AC4">
-        <v>4.59</v>
+        <v>1.78</v>
       </c>
       <c r="AD4">
-        <v>18.58</v>
+        <v>8.74</v>
       </c>
       <c r="AE4">
-        <v>32.93</v>
+        <v>32.74</v>
       </c>
       <c r="AF4">
-        <v>494.44</v>
+        <v>-1.04</v>
       </c>
       <c r="AG4">
-        <v>1177.7</v>
+        <v>1181.41</v>
       </c>
       <c r="AH4">
-        <v>1081.48</v>
+        <v>1069.08</v>
       </c>
       <c r="AI4">
         <v>1161.19</v>
@@ -1268,7 +1304,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.88</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1315,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>750.95</v>
+        <v>732.15</v>
       </c>
       <c r="D5">
-        <v>1.21</v>
+        <v>-2.5</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1291,46 +1327,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-13.14</v>
+        <v>-15.32</v>
       </c>
       <c r="H5">
-        <v>13.45</v>
+        <v>10.61</v>
       </c>
       <c r="I5">
-        <v>0.7</v>
+        <v>-0.83</v>
       </c>
       <c r="J5">
-        <v>1.7</v>
+        <v>-0.77</v>
       </c>
       <c r="K5">
-        <v>7.98</v>
+        <v>5.23</v>
       </c>
       <c r="L5">
-        <v>1.91</v>
+        <v>-3.85</v>
       </c>
       <c r="M5">
-        <v>35.04</v>
+        <v>34.72</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>742.27</v>
+        <v>741.04</v>
       </c>
       <c r="Q5">
-        <v>745.23</v>
+        <v>745</v>
       </c>
       <c r="R5">
-        <v>733.8</v>
+        <v>733.97</v>
       </c>
       <c r="S5">
-        <v>746.8</v>
+        <v>746.52</v>
       </c>
       <c r="T5">
-        <v>0.5600000000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1342,37 +1378,37 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>54.14</v>
+        <v>47.57</v>
       </c>
       <c r="Z5">
-        <v>3.51</v>
+        <v>2.35</v>
       </c>
       <c r="AA5">
-        <v>4.23</v>
+        <v>3.85</v>
       </c>
       <c r="AB5">
-        <v>-0.71</v>
+        <v>-1.5</v>
       </c>
       <c r="AC5">
-        <v>38.25</v>
+        <v>36.49</v>
       </c>
       <c r="AD5">
-        <v>29.38</v>
+        <v>34.81</v>
       </c>
       <c r="AE5">
-        <v>20.6</v>
+        <v>20.88</v>
       </c>
       <c r="AF5">
-        <v>-62.87</v>
+        <v>-56.39</v>
       </c>
       <c r="AG5">
-        <v>772.87</v>
+        <v>773.01</v>
       </c>
       <c r="AH5">
-        <v>717.59</v>
+        <v>716.98</v>
       </c>
       <c r="AI5">
         <v>713.98</v>
@@ -1381,7 +1417,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>16.23</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1428,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>494.9</v>
+        <v>485.45</v>
       </c>
       <c r="D6">
-        <v>0.63</v>
+        <v>-1.91</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1404,46 +1440,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-17.52</v>
+        <v>-19.09</v>
       </c>
       <c r="H6">
-        <v>12.85</v>
+        <v>10.69</v>
       </c>
       <c r="I6">
-        <v>-0.02</v>
+        <v>-3.13</v>
       </c>
       <c r="J6">
-        <v>-8.27</v>
+        <v>-10.08</v>
       </c>
       <c r="K6">
-        <v>-9.06</v>
+        <v>-9.59</v>
       </c>
       <c r="L6">
-        <v>-6.45</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M6">
-        <v>5.93</v>
+        <v>5.61</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>493.51</v>
+        <v>490.37</v>
       </c>
       <c r="Q6">
-        <v>511.55</v>
+        <v>509.32</v>
       </c>
       <c r="R6">
-        <v>534.45</v>
+        <v>533.16</v>
       </c>
       <c r="S6">
-        <v>523.73</v>
+        <v>523.79</v>
       </c>
       <c r="T6">
-        <v>-5.5</v>
+        <v>-7.32</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1458,34 +1494,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>38.33</v>
+        <v>34.58</v>
       </c>
       <c r="Z6">
-        <v>-12.2</v>
+        <v>-12.65</v>
       </c>
       <c r="AA6">
-        <v>-10.85</v>
+        <v>-11.21</v>
       </c>
       <c r="AB6">
-        <v>-1.35</v>
+        <v>-1.44</v>
       </c>
       <c r="AC6">
-        <v>27.67</v>
+        <v>34.49</v>
       </c>
       <c r="AD6">
-        <v>23.41</v>
+        <v>27.35</v>
       </c>
       <c r="AE6">
-        <v>12.31</v>
+        <v>12.39</v>
       </c>
       <c r="AF6">
-        <v>131.31</v>
+        <v>29.15</v>
       </c>
       <c r="AG6">
-        <v>541.3200000000001</v>
+        <v>539.9299999999999</v>
       </c>
       <c r="AH6">
-        <v>481.78</v>
+        <v>478.71</v>
       </c>
       <c r="AI6">
         <v>521.28</v>
@@ -1494,7 +1530,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>32.7</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1541,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11313</v>
+        <v>11272</v>
       </c>
       <c r="D7">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1517,46 +1553,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.96</v>
+        <v>-49.15</v>
       </c>
       <c r="H7">
-        <v>6.18</v>
+        <v>5.79</v>
       </c>
       <c r="I7">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="J7">
-        <v>-2.39</v>
+        <v>-1.74</v>
       </c>
       <c r="K7">
-        <v>-3.87</v>
+        <v>-0.37</v>
       </c>
       <c r="L7">
-        <v>-30.63</v>
+        <v>-27.25</v>
       </c>
       <c r="M7">
-        <v>19.07</v>
+        <v>19.06</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P7">
-        <v>11253.4</v>
+        <v>11307.8</v>
       </c>
       <c r="Q7">
-        <v>11231.65</v>
+        <v>11226.65</v>
       </c>
       <c r="R7">
-        <v>11464.14</v>
+        <v>11469.6</v>
       </c>
       <c r="S7">
-        <v>13887.94</v>
+        <v>13842.08</v>
       </c>
       <c r="T7">
-        <v>-18.54</v>
+        <v>-18.57</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1571,34 +1607,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.09</v>
+        <v>48.94</v>
       </c>
       <c r="Z7">
-        <v>-63.72</v>
+        <v>-56.52</v>
       </c>
       <c r="AA7">
-        <v>-93.87</v>
+        <v>-86.40000000000001</v>
       </c>
       <c r="AB7">
-        <v>30.15</v>
+        <v>29.88</v>
       </c>
       <c r="AC7">
-        <v>91.47</v>
+        <v>90.05</v>
       </c>
       <c r="AD7">
-        <v>85.23999999999999</v>
+        <v>91.88</v>
       </c>
       <c r="AE7">
-        <v>341.31</v>
+        <v>330.28</v>
       </c>
       <c r="AF7">
-        <v>-71.09</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="AG7">
-        <v>11566.04</v>
+        <v>11555.14</v>
       </c>
       <c r="AH7">
-        <v>10897.26</v>
+        <v>10898.16</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1607,7 +1643,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>15.46</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,10 +1654,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>363.05</v>
+        <v>353.9</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>-2.52</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1630,25 +1666,25 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-1.24</v>
+        <v>-3.73</v>
       </c>
       <c r="H8">
-        <v>54.94</v>
+        <v>51.04</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>1.11</v>
       </c>
       <c r="J8">
-        <v>8.67</v>
+        <v>6.28</v>
       </c>
       <c r="K8">
-        <v>12.59</v>
+        <v>12.62</v>
       </c>
       <c r="L8">
-        <v>15.16</v>
+        <v>11.64</v>
       </c>
       <c r="M8">
-        <v>32.23</v>
+        <v>31.08</v>
       </c>
       <c r="N8">
         <v>77</v>
@@ -1657,19 +1693,19 @@
         <v>76</v>
       </c>
       <c r="P8">
-        <v>357.3</v>
+        <v>358.08</v>
       </c>
       <c r="Q8">
-        <v>347.75</v>
+        <v>348.9</v>
       </c>
       <c r="R8">
-        <v>339.07</v>
+        <v>339.71</v>
       </c>
       <c r="S8">
-        <v>293.44</v>
+        <v>293.87</v>
       </c>
       <c r="T8">
-        <v>23.72</v>
+        <v>20.43</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1684,34 +1720,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>61.89</v>
+        <v>54.18</v>
       </c>
       <c r="Z8">
-        <v>6.48</v>
+        <v>5.94</v>
       </c>
       <c r="AA8">
-        <v>5.55</v>
+        <v>5.63</v>
       </c>
       <c r="AB8">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="AC8">
-        <v>66.68000000000001</v>
+        <v>60.35</v>
       </c>
       <c r="AD8">
-        <v>61.32</v>
+        <v>63.02</v>
       </c>
       <c r="AE8">
-        <v>11.54</v>
+        <v>11.76</v>
       </c>
       <c r="AF8">
-        <v>-51.22</v>
+        <v>-4.36</v>
       </c>
       <c r="AG8">
-        <v>375.32</v>
+        <v>375.4</v>
       </c>
       <c r="AH8">
-        <v>320.18</v>
+        <v>322.4</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1720,7 +1756,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>19.2</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1731,10 +1767,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1259.6</v>
+        <v>1230</v>
       </c>
       <c r="D9">
-        <v>1.97</v>
+        <v>-2.35</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1743,46 +1779,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-6.07</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="H9">
-        <v>16.71</v>
+        <v>13.96</v>
       </c>
       <c r="I9">
-        <v>-0.36</v>
+        <v>-3.33</v>
       </c>
       <c r="J9">
-        <v>-3.7</v>
+        <v>-7.17</v>
       </c>
       <c r="K9">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="L9">
-        <v>10.23</v>
+        <v>7.32</v>
       </c>
       <c r="M9">
-        <v>14.86</v>
+        <v>14.06</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P9">
-        <v>1250.74</v>
+        <v>1242.26</v>
       </c>
       <c r="Q9">
-        <v>1269.34</v>
+        <v>1265.74</v>
       </c>
       <c r="R9">
-        <v>1285.41</v>
+        <v>1285.12</v>
       </c>
       <c r="S9">
-        <v>1238.87</v>
+        <v>1239.62</v>
       </c>
       <c r="T9">
-        <v>1.67</v>
+        <v>-0.78</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1794,37 +1830,37 @@
         <v>48</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>46.7</v>
+        <v>40.46</v>
       </c>
       <c r="Z9">
-        <v>-10.88</v>
+        <v>-12.55</v>
       </c>
       <c r="AA9">
-        <v>-8.109999999999999</v>
+        <v>-9</v>
       </c>
       <c r="AB9">
-        <v>-2.77</v>
+        <v>-3.55</v>
       </c>
       <c r="AC9">
-        <v>36.78</v>
+        <v>31.66</v>
       </c>
       <c r="AD9">
-        <v>39.86</v>
+        <v>34.36</v>
       </c>
       <c r="AE9">
-        <v>26.12</v>
+        <v>26.66</v>
       </c>
       <c r="AF9">
-        <v>-7.26</v>
+        <v>27.86</v>
       </c>
       <c r="AG9">
-        <v>1317.02</v>
+        <v>1313.91</v>
       </c>
       <c r="AH9">
-        <v>1221.66</v>
+        <v>1217.57</v>
       </c>
       <c r="AI9">
         <v>1314.04</v>
@@ -1833,7 +1869,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>24.41</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1844,10 +1880,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>77.64</v>
+        <v>77.08</v>
       </c>
       <c r="D10">
-        <v>3.29</v>
+        <v>-0.72</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1856,46 +1892,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-15.1</v>
+        <v>-15.71</v>
       </c>
       <c r="H10">
-        <v>115.19</v>
+        <v>113.64</v>
       </c>
       <c r="I10">
-        <v>4.35</v>
+        <v>-1.29</v>
       </c>
       <c r="J10">
-        <v>-4.79</v>
+        <v>-9.82</v>
       </c>
       <c r="K10">
-        <v>46.85</v>
+        <v>51.4</v>
       </c>
       <c r="L10">
-        <v>-9.93</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="M10">
-        <v>-4.33</v>
+        <v>-4.6</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P10">
-        <v>77.97</v>
+        <v>77.77</v>
       </c>
       <c r="Q10">
-        <v>80.15000000000001</v>
+        <v>79.81</v>
       </c>
       <c r="R10">
-        <v>80.62</v>
+        <v>80.77</v>
       </c>
       <c r="S10">
-        <v>61.46</v>
+        <v>61.57</v>
       </c>
       <c r="T10">
-        <v>26.33</v>
+        <v>25.19</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1910,34 +1946,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>47.34</v>
+        <v>46.38</v>
       </c>
       <c r="Z10">
-        <v>-0.8100000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="AA10">
-        <v>-0.31</v>
+        <v>-0.42</v>
       </c>
       <c r="AB10">
-        <v>-0.5</v>
+        <v>-0.43</v>
       </c>
       <c r="AC10">
-        <v>45.9</v>
+        <v>50.7</v>
       </c>
       <c r="AD10">
-        <v>46.97</v>
+        <v>47.39</v>
       </c>
       <c r="AE10">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="AF10">
-        <v>-54.3</v>
+        <v>17.29</v>
       </c>
       <c r="AG10">
-        <v>86.83</v>
+        <v>86.38</v>
       </c>
       <c r="AH10">
-        <v>73.47</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1946,7 +1982,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>44.33</v>
+        <v>41.83</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2147,16 +2183,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>47</v>
@@ -2167,1261 +2203,1332 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="C6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-6.51</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.8</v>
+      <c r="B9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-11.05</v>
+        <v>-3.71</v>
       </c>
       <c r="D10" s="7">
-        <v>-9.15</v>
+        <v>-2.84</v>
       </c>
       <c r="E10" s="8">
-        <v>1.9</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-5.36</v>
+        <v>-9.15</v>
       </c>
       <c r="D11" s="7">
-        <v>-5.16</v>
+        <v>-7.66</v>
       </c>
       <c r="E11" s="8">
-        <v>0.2</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>0.97</v>
+        <v>-5.16</v>
       </c>
       <c r="D12" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.73</v>
+        <v>-8.93</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-3.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-8.890000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="D13" s="7">
-        <v>-8.27</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.62</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-0.8</v>
+        <v>-8.27</v>
       </c>
       <c r="D14" s="7">
-        <v>-2.39</v>
+        <v>-10.08</v>
       </c>
       <c r="E14" s="9">
-        <v>-1.59</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>8.220000000000001</v>
+        <v>-2.39</v>
       </c>
       <c r="D15" s="7">
-        <v>8.67</v>
+        <v>-1.74</v>
       </c>
       <c r="E15" s="8">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-5.41</v>
+        <v>8.67</v>
       </c>
       <c r="D16" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.71</v>
+        <v>6.28</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-3.22</v>
+        <v>-3.7</v>
       </c>
       <c r="D17" s="7">
-        <v>-4.79</v>
+        <v>-7.17</v>
       </c>
       <c r="E17" s="9">
-        <v>-1.57</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-7.56</v>
+        <v>-4.79</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.13</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.43</v>
+        <v>-9.82</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-5.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.68</v>
+        <v>-3.13</v>
       </c>
       <c r="D19" s="7">
-        <v>2.26</v>
-      </c>
-      <c r="E19" s="8">
-        <v>5.94</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-5.79</v>
+        <v>2.26</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.71</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.08</v>
+        <v>1.51</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-0.84</v>
+        <v>-4.71</v>
       </c>
       <c r="D21" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.54</v>
+        <v>-6.11</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.91</v>
+        <v>0.7</v>
       </c>
       <c r="D22" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.89</v>
+        <v>-0.83</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-0.73</v>
+        <v>-0.02</v>
       </c>
       <c r="D23" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="E23" s="8">
-        <v>4.83</v>
+        <v>-3.13</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-3.27</v>
+        <v>2.6</v>
       </c>
       <c r="D24" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.91</v>
+        <v>2.47</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.19</v>
+        <v>4.1</v>
       </c>
       <c r="D25" s="7">
-        <v>4.35</v>
-      </c>
-      <c r="E25" s="8">
-        <v>6.54</v>
+        <v>1.11</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>14.18</v>
+        <v>-0.36</v>
       </c>
       <c r="D26" s="7">
-        <v>20.15</v>
-      </c>
-      <c r="E26" s="8">
-        <v>5.97</v>
+        <v>-3.33</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>36.73</v>
+        <v>4.35</v>
       </c>
       <c r="D27" s="7">
-        <v>40.52</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.79</v>
+        <v>-1.29</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-5.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>5.17</v>
+        <v>20.15</v>
       </c>
       <c r="D28" s="7">
-        <v>2.08</v>
+        <v>17.26</v>
       </c>
       <c r="E28" s="9">
-        <v>-3.09</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>0.71</v>
+        <v>40.52</v>
       </c>
       <c r="D29" s="7">
-        <v>1.91</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.2</v>
+        <v>39.13</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>-6.64</v>
+        <v>2.08</v>
       </c>
       <c r="D30" s="7">
-        <v>-6.45</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.19</v>
+        <v>-0.38</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-33.88</v>
+        <v>1.91</v>
       </c>
       <c r="D31" s="7">
-        <v>-30.63</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.25</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-5.76</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>11.36</v>
+        <v>-6.45</v>
       </c>
       <c r="D32" s="7">
-        <v>15.16</v>
-      </c>
-      <c r="E32" s="8">
-        <v>3.8</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>10.08</v>
+        <v>-30.63</v>
       </c>
       <c r="D33" s="7">
-        <v>10.23</v>
+        <v>-27.25</v>
       </c>
       <c r="E33" s="8">
-        <v>0.15</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>-9.85</v>
+        <v>15.16</v>
       </c>
       <c r="D34" s="7">
-        <v>-9.93</v>
+        <v>11.64</v>
       </c>
       <c r="E34" s="9">
-        <v>-0.08</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>2.17</v>
+        <v>10.23</v>
       </c>
       <c r="D35" s="7">
-        <v>6.08</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.91</v>
+        <v>7.32</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="7">
-        <v>5.87</v>
+        <v>-9.93</v>
       </c>
       <c r="D36" s="7">
-        <v>7.97</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E36" s="8">
-        <v>2.1</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>3.57</v>
+        <v>6.08</v>
       </c>
       <c r="D37" s="7">
-        <v>4.88</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.31</v>
+        <v>0.26</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-5.82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>5.66</v>
+        <v>7.97</v>
       </c>
       <c r="D38" s="7">
-        <v>7.98</v>
+        <v>8.57</v>
       </c>
       <c r="E38" s="8">
-        <v>2.32</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>-10.16</v>
+        <v>4.88</v>
       </c>
       <c r="D39" s="7">
-        <v>-9.06</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.1</v>
+        <v>3.87</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>-6.62</v>
+        <v>7.98</v>
       </c>
       <c r="D40" s="7">
-        <v>-3.87</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.75</v>
+        <v>5.23</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>10.93</v>
+        <v>-9.06</v>
       </c>
       <c r="D41" s="7">
-        <v>12.59</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.66</v>
+        <v>-9.59</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>-0.64</v>
+        <v>-3.87</v>
       </c>
       <c r="D42" s="7">
-        <v>1.06</v>
+        <v>-0.37</v>
       </c>
       <c r="E42" s="8">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>42.77</v>
+        <v>12.59</v>
       </c>
       <c r="D43" s="7">
-        <v>46.85</v>
+        <v>12.62</v>
       </c>
       <c r="E43" s="8">
-        <v>4.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>-36.32</v>
+        <v>1.06</v>
       </c>
       <c r="D44" s="7">
-        <v>-34.66</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.66</v>
+        <v>0.86</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C45" s="7">
-        <v>-13.39</v>
+        <v>46.85</v>
       </c>
       <c r="D45" s="7">
-        <v>-11.06</v>
+        <v>51.4</v>
       </c>
       <c r="E45" s="8">
-        <v>2.33</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-14.86</v>
+        <v>-34.66</v>
       </c>
       <c r="D46" s="7">
-        <v>-15.74</v>
+        <v>-35.17</v>
       </c>
       <c r="E46" s="9">
-        <v>-0.88</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-14.18</v>
+        <v>-11.06</v>
       </c>
       <c r="D47" s="7">
-        <v>-13.14</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.04</v>
+        <v>-11.21</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-18.03</v>
+        <v>-15.74</v>
       </c>
       <c r="D48" s="7">
-        <v>-17.52</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.51</v>
+        <v>-17.68</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-48.79</v>
+        <v>-13.14</v>
       </c>
       <c r="D49" s="7">
-        <v>-48.96</v>
+        <v>-15.32</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.17</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-2.23</v>
+        <v>-17.52</v>
       </c>
       <c r="D50" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.99</v>
+        <v>-19.09</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-7.88</v>
+        <v>-48.96</v>
       </c>
       <c r="D51" s="7">
-        <v>-6.07</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.81</v>
+        <v>-49.15</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-17.8</v>
+        <v>-1.24</v>
       </c>
       <c r="D52" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="E52" s="8">
-        <v>2.7</v>
+        <v>-3.73</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>641.6</v>
+        <v>-6.07</v>
       </c>
       <c r="D53" s="7">
-        <v>658.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>16.75</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" s="7">
-        <v>275</v>
+        <v>-15.1</v>
       </c>
       <c r="D54" s="7">
-        <v>282.4</v>
-      </c>
-      <c r="E54" s="8">
-        <v>7.4</v>
+        <v>-15.71</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>1097.3</v>
+        <v>658.35</v>
       </c>
       <c r="D55" s="7">
-        <v>1085.9</v>
+        <v>653.25</v>
       </c>
       <c r="E55" s="9">
-        <v>-11.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>742</v>
+        <v>282.4</v>
       </c>
       <c r="D56" s="7">
-        <v>750.95</v>
-      </c>
-      <c r="E56" s="8">
-        <v>8.949999999999999</v>
+        <v>281.9</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>491.8</v>
+        <v>1085.9</v>
       </c>
       <c r="D57" s="7">
-        <v>494.9</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.1</v>
+        <v>1061</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-24.9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>11350</v>
+        <v>750.95</v>
       </c>
       <c r="D58" s="7">
-        <v>11313</v>
+        <v>732.15</v>
       </c>
       <c r="E58" s="9">
-        <v>-37</v>
+        <v>-18.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>359.4</v>
+        <v>494.9</v>
       </c>
       <c r="D59" s="7">
-        <v>363.05</v>
-      </c>
-      <c r="E59" s="8">
-        <v>3.65</v>
+        <v>485.45</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>1235.3</v>
+        <v>11313</v>
       </c>
       <c r="D60" s="7">
-        <v>1259.6</v>
-      </c>
-      <c r="E60" s="8">
-        <v>24.3</v>
+        <v>11272</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-41</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>75.17</v>
+        <v>363.05</v>
       </c>
       <c r="D61" s="7">
-        <v>77.64</v>
-      </c>
-      <c r="E61" s="8">
-        <v>2.47</v>
+        <v>353.9</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-9.15</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>38.18</v>
+        <v>1259.6</v>
       </c>
       <c r="D62" s="7">
-        <v>43.79</v>
-      </c>
-      <c r="E62" s="8">
-        <v>5.61</v>
+        <v>1230</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-29.6</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C63" s="7">
-        <v>42.01</v>
+        <v>77.64</v>
       </c>
       <c r="D63" s="7">
-        <v>47.51</v>
-      </c>
-      <c r="E63" s="8">
-        <v>5.5</v>
+        <v>77.08</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>41.23</v>
+        <v>55</v>
       </c>
       <c r="D64" s="7">
-        <v>38.92</v>
+        <v>45</v>
       </c>
       <c r="E64" s="9">
-        <v>-2.31</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="7">
-        <v>51.15</v>
+        <v>45</v>
       </c>
       <c r="D65" s="7">
-        <v>54.14</v>
+        <v>55</v>
       </c>
       <c r="E65" s="8">
-        <v>2.99</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>36.22</v>
+        <v>43.79</v>
       </c>
       <c r="D66" s="7">
-        <v>38.33</v>
-      </c>
-      <c r="E66" s="8">
-        <v>2.11</v>
+        <v>42.52</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>51.09</v>
+        <v>47.51</v>
       </c>
       <c r="D67" s="7">
-        <v>50.09</v>
+        <v>47.18</v>
       </c>
       <c r="E67" s="9">
-        <v>-1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>59.77</v>
+        <v>38.92</v>
       </c>
       <c r="D68" s="7">
-        <v>61.89</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.12</v>
+        <v>34.39</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>39.6</v>
+        <v>54.14</v>
       </c>
       <c r="D69" s="7">
-        <v>46.7</v>
-      </c>
-      <c r="E69" s="8">
-        <v>7.1</v>
+        <v>47.57</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-6.57</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>42.43</v>
+        <v>38.33</v>
       </c>
       <c r="D70" s="7">
-        <v>47.34</v>
-      </c>
-      <c r="E70" s="8">
-        <v>4.91</v>
+        <v>34.58</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>-74.06</v>
+        <v>50.09</v>
       </c>
       <c r="D71" s="7">
-        <v>-73.33</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.73</v>
+        <v>48.94</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>-23.8</v>
+        <v>61.89</v>
       </c>
       <c r="D72" s="7">
-        <v>-37.18</v>
+        <v>54.18</v>
       </c>
       <c r="E72" s="9">
-        <v>-13.38</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>-41.57</v>
+        <v>46.7</v>
       </c>
       <c r="D73" s="7">
-        <v>494.44</v>
-      </c>
-      <c r="E73" s="8">
-        <v>536.01</v>
+        <v>40.46</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-6.24</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>-69.42</v>
+        <v>47.34</v>
       </c>
       <c r="D74" s="7">
-        <v>-62.87</v>
-      </c>
-      <c r="E74" s="8">
-        <v>6.55</v>
+        <v>46.38</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-44.67</v>
+        <v>-73.33</v>
       </c>
       <c r="D75" s="7">
-        <v>131.31</v>
-      </c>
-      <c r="E75" s="8">
-        <v>175.98</v>
+        <v>-86.62</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-13.29</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-80.59999999999999</v>
+        <v>-37.18</v>
       </c>
       <c r="D76" s="7">
-        <v>-71.09</v>
-      </c>
-      <c r="E76" s="8">
-        <v>9.51</v>
+        <v>-57.64</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-20.46</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-50.23</v>
+        <v>494.44</v>
       </c>
       <c r="D77" s="7">
-        <v>-51.22</v>
+        <v>-1.04</v>
       </c>
       <c r="E77" s="9">
-        <v>-0.99</v>
+        <v>-495.48</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-28</v>
+        <v>-62.87</v>
       </c>
       <c r="D78" s="7">
-        <v>-7.26</v>
+        <v>-56.39</v>
       </c>
       <c r="E78" s="8">
-        <v>20.74</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>28.05</v>
+        <v>131.31</v>
       </c>
       <c r="D79" s="7">
+        <v>29.15</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-102.16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-71.09</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-82.40000000000001</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-11.31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-51.22</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-4.36</v>
+      </c>
+      <c r="E81" s="8">
+        <v>46.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-7.26</v>
+      </c>
+      <c r="D82" s="7">
+        <v>27.86</v>
+      </c>
+      <c r="E82" s="8">
+        <v>35.12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
         <v>-54.3</v>
       </c>
-      <c r="E79" s="9">
-        <v>-82.34999999999999</v>
+      <c r="D83" s="7">
+        <v>17.29</v>
+      </c>
+      <c r="E83" s="8">
+        <v>71.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3445,28 +3552,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3474,22 +3581,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="12">
-        <v>60.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="13">
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>47.6</v>
+        <v>44</v>
       </c>
       <c r="E2" s="12">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>-3</v>
+        <v>-4.7</v>
       </c>
       <c r="G2" s="12">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3626,31 +3733,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3888</v>
+        <v>0.3873</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3504</v>
+        <v>0.3472</v>
       </c>
       <c r="C2" s="15">
-        <v>0.3223</v>
+        <v>0.3108</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2187</v>
+        <v>0.2143</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1907</v>
+        <v>0.1906</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1486</v>
+        <v>0.1406</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0593</v>
+        <v>0.0561</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0433</v>
+        <v>-0.046</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.07530000000000001</v>
+        <v>-0.0805</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,49 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.2% → -3.7%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.2%</t>
-  </si>
-  <si>
-    <t>-3.7%</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>54.2 → 41.8</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.1 → 47.6</t>
-  </si>
-  <si>
-    <t>54.1</t>
-  </si>
-  <si>
-    <t>47.6</t>
-  </si>
-  <si>
-    <t>50.1 → 48.9</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>54.2</t>
+  </si>
+  <si>
+    <t>41.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -287,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,13 +291,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -341,7 +304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -458,15 +415,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -475,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -834,9 +790,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -976,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>653.25</v>
+        <v>635.05</v>
       </c>
       <c r="D2">
-        <v>-0.77</v>
+        <v>-2.79</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -988,46 +942,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.17</v>
+        <v>-36.97</v>
       </c>
       <c r="H2">
-        <v>77.90000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="I2">
-        <v>-3.27</v>
+        <v>-5.58</v>
       </c>
       <c r="J2">
-        <v>-2.84</v>
+        <v>-9.16</v>
       </c>
       <c r="K2">
-        <v>0.26</v>
+        <v>-7.17</v>
       </c>
       <c r="L2">
-        <v>17.26</v>
+        <v>11.78</v>
       </c>
       <c r="M2">
-        <v>-8.050000000000001</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>655.89</v>
+        <v>648.39</v>
       </c>
       <c r="Q2">
-        <v>691.99</v>
+        <v>689.55</v>
       </c>
       <c r="R2">
-        <v>664.04</v>
+        <v>664.14</v>
       </c>
       <c r="S2">
-        <v>642.55</v>
+        <v>643.3200000000001</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>-1.29</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1039,46 +993,46 @@
         <v>47</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.52</v>
+        <v>38.27</v>
       </c>
       <c r="Z2">
-        <v>-4.43</v>
+        <v>-7.17</v>
       </c>
       <c r="AA2">
-        <v>4.21</v>
+        <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>-8.640000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="AC2">
-        <v>11.51</v>
+        <v>11.62</v>
       </c>
       <c r="AD2">
-        <v>5.88</v>
+        <v>9.76</v>
       </c>
       <c r="AE2">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="AF2">
-        <v>-86.62</v>
+        <v>-80.86</v>
       </c>
       <c r="AG2">
-        <v>755.03</v>
+        <v>757.5</v>
       </c>
       <c r="AH2">
-        <v>628.9400000000001</v>
+        <v>621.6</v>
       </c>
       <c r="AI2">
-        <v>740.75</v>
+        <v>739.46</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.26</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1089,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>281.9</v>
+        <v>270.2</v>
       </c>
       <c r="D3">
-        <v>-0.18</v>
+        <v>-4.15</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1101,46 +1055,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-11.21</v>
+        <v>-14.9</v>
       </c>
       <c r="H3">
-        <v>83.97</v>
+        <v>76.34</v>
       </c>
       <c r="I3">
-        <v>1.51</v>
+        <v>-2.7</v>
       </c>
       <c r="J3">
-        <v>-7.66</v>
+        <v>-12.71</v>
       </c>
       <c r="K3">
-        <v>8.57</v>
+        <v>-0.77</v>
       </c>
       <c r="L3">
-        <v>39.13</v>
+        <v>32.06</v>
       </c>
       <c r="M3">
-        <v>38.73</v>
+        <v>37.79</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>277.46</v>
+        <v>275.96</v>
       </c>
       <c r="Q3">
-        <v>289.08</v>
+        <v>287.21</v>
       </c>
       <c r="R3">
-        <v>283.95</v>
+        <v>284.21</v>
       </c>
       <c r="S3">
-        <v>229.24</v>
+        <v>229.78</v>
       </c>
       <c r="T3">
-        <v>22.97</v>
+        <v>17.59</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1155,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>47.18</v>
+        <v>40.23</v>
       </c>
       <c r="Z3">
-        <v>-3.42</v>
+        <v>-4.13</v>
       </c>
       <c r="AA3">
-        <v>-1.71</v>
+        <v>-2.19</v>
       </c>
       <c r="AB3">
-        <v>-1.72</v>
+        <v>-1.94</v>
       </c>
       <c r="AC3">
-        <v>61.55</v>
+        <v>56.61</v>
       </c>
       <c r="AD3">
-        <v>36.65</v>
+        <v>51.57</v>
       </c>
       <c r="AE3">
-        <v>10.42</v>
+        <v>10.72</v>
       </c>
       <c r="AF3">
-        <v>-57.64</v>
+        <v>-34.04</v>
       </c>
       <c r="AG3">
-        <v>315.86</v>
+        <v>313.77</v>
       </c>
       <c r="AH3">
-        <v>262.29</v>
+        <v>260.64</v>
       </c>
       <c r="AI3">
         <v>301.41</v>
@@ -1191,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>44.59</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1202,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1061</v>
+        <v>1010</v>
       </c>
       <c r="D4">
-        <v>-2.29</v>
+        <v>-4.81</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1214,46 +1168,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-17.68</v>
+        <v>-21.63</v>
       </c>
       <c r="H4">
-        <v>7.61</v>
+        <v>2.43</v>
       </c>
       <c r="I4">
-        <v>-6.11</v>
+        <v>-11.01</v>
       </c>
       <c r="J4">
-        <v>-8.93</v>
+        <v>-12.01</v>
       </c>
       <c r="K4">
-        <v>3.87</v>
+        <v>-1.92</v>
       </c>
       <c r="L4">
-        <v>-0.38</v>
+        <v>-6.18</v>
       </c>
       <c r="M4">
-        <v>21.43</v>
+        <v>19.76</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P4">
-        <v>1095.92</v>
+        <v>1070.94</v>
       </c>
       <c r="Q4">
-        <v>1125.25</v>
+        <v>1118.93</v>
       </c>
       <c r="R4">
-        <v>1125.33</v>
+        <v>1124.44</v>
       </c>
       <c r="S4">
-        <v>1138.94</v>
+        <v>1139.06</v>
       </c>
       <c r="T4">
-        <v>-6.84</v>
+        <v>-11.33</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1268,43 +1222,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.39</v>
+        <v>27.37</v>
       </c>
       <c r="Z4">
-        <v>-10.13</v>
+        <v>-17.58</v>
       </c>
       <c r="AA4">
-        <v>-1.02</v>
+        <v>-4.33</v>
       </c>
       <c r="AB4">
-        <v>-9.109999999999999</v>
+        <v>-13.25</v>
       </c>
       <c r="AC4">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>8.74</v>
+        <v>2.12</v>
       </c>
       <c r="AE4">
-        <v>32.74</v>
+        <v>34.95</v>
       </c>
       <c r="AF4">
-        <v>-1.04</v>
+        <v>134.56</v>
       </c>
       <c r="AG4">
-        <v>1181.41</v>
+        <v>1194.81</v>
       </c>
       <c r="AH4">
-        <v>1069.08</v>
+        <v>1043.05</v>
       </c>
       <c r="AI4">
-        <v>1161.19</v>
+        <v>1137.81</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>36.65</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1315,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>732.15</v>
+        <v>705.6</v>
       </c>
       <c r="D5">
-        <v>-2.5</v>
+        <v>-3.63</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1327,25 +1281,25 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.32</v>
+        <v>-18.39</v>
       </c>
       <c r="H5">
-        <v>10.61</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>-0.83</v>
+        <v>-5.59</v>
       </c>
       <c r="J5">
-        <v>-0.77</v>
+        <v>-4.23</v>
       </c>
       <c r="K5">
-        <v>5.23</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L5">
-        <v>-3.85</v>
+        <v>-10.37</v>
       </c>
       <c r="M5">
-        <v>34.72</v>
+        <v>33.64</v>
       </c>
       <c r="N5">
         <v>45</v>
@@ -1354,19 +1308,19 @@
         <v>61</v>
       </c>
       <c r="P5">
-        <v>741.04</v>
+        <v>732.6799999999999</v>
       </c>
       <c r="Q5">
-        <v>745</v>
+        <v>743.34</v>
       </c>
       <c r="R5">
-        <v>733.97</v>
+        <v>733.59</v>
       </c>
       <c r="S5">
-        <v>746.52</v>
+        <v>746.0599999999999</v>
       </c>
       <c r="T5">
-        <v>-1.92</v>
+        <v>-5.42</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1381,43 +1335,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.57</v>
+        <v>40.15</v>
       </c>
       <c r="Z5">
-        <v>2.35</v>
+        <v>-0.71</v>
       </c>
       <c r="AA5">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="AB5">
-        <v>-1.5</v>
+        <v>-3.65</v>
       </c>
       <c r="AC5">
-        <v>36.49</v>
+        <v>23.14</v>
       </c>
       <c r="AD5">
-        <v>34.81</v>
+        <v>32.63</v>
       </c>
       <c r="AE5">
-        <v>20.88</v>
+        <v>21.7</v>
       </c>
       <c r="AF5">
-        <v>-56.39</v>
+        <v>-41.84</v>
       </c>
       <c r="AG5">
-        <v>773.01</v>
+        <v>776.38</v>
       </c>
       <c r="AH5">
-        <v>716.98</v>
+        <v>710.3</v>
       </c>
       <c r="AI5">
-        <v>713.98</v>
+        <v>783.51</v>
       </c>
       <c r="AJ5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK5">
-        <v>14.9</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1428,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>485.45</v>
+        <v>466.85</v>
       </c>
       <c r="D6">
-        <v>-1.91</v>
+        <v>-3.83</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1440,46 +1394,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-19.09</v>
+        <v>-22.19</v>
       </c>
       <c r="H6">
-        <v>10.69</v>
+        <v>6.45</v>
       </c>
       <c r="I6">
-        <v>-3.13</v>
+        <v>-5.63</v>
       </c>
       <c r="J6">
-        <v>-10.08</v>
+        <v>-11.92</v>
       </c>
       <c r="K6">
-        <v>-9.59</v>
+        <v>-12.48</v>
       </c>
       <c r="L6">
-        <v>-9.199999999999999</v>
+        <v>-13.24</v>
       </c>
       <c r="M6">
-        <v>5.61</v>
+        <v>4.64</v>
       </c>
       <c r="N6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P6">
-        <v>490.37</v>
+        <v>484.8</v>
       </c>
       <c r="Q6">
-        <v>509.32</v>
+        <v>506.34</v>
       </c>
       <c r="R6">
-        <v>533.16</v>
+        <v>531.61</v>
       </c>
       <c r="S6">
-        <v>523.79</v>
+        <v>523.77</v>
       </c>
       <c r="T6">
-        <v>-7.32</v>
+        <v>-10.87</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1494,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.58</v>
+        <v>28.65</v>
       </c>
       <c r="Z6">
-        <v>-12.65</v>
+        <v>-14.33</v>
       </c>
       <c r="AA6">
-        <v>-11.21</v>
+        <v>-11.83</v>
       </c>
       <c r="AB6">
-        <v>-1.44</v>
+        <v>-2.5</v>
       </c>
       <c r="AC6">
-        <v>34.49</v>
+        <v>23.25</v>
       </c>
       <c r="AD6">
-        <v>27.35</v>
+        <v>28.47</v>
       </c>
       <c r="AE6">
-        <v>12.39</v>
+        <v>12.96</v>
       </c>
       <c r="AF6">
-        <v>29.15</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="AG6">
-        <v>539.9299999999999</v>
+        <v>541.23</v>
       </c>
       <c r="AH6">
-        <v>478.71</v>
+        <v>471.45</v>
       </c>
       <c r="AI6">
-        <v>521.28</v>
+        <v>513.64</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>32.66</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1541,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11272</v>
+        <v>11158</v>
       </c>
       <c r="D7">
-        <v>-0.36</v>
+        <v>-1.01</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1553,46 +1507,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.15</v>
+        <v>-49.66</v>
       </c>
       <c r="H7">
-        <v>5.79</v>
+        <v>4.72</v>
       </c>
       <c r="I7">
-        <v>2.47</v>
+        <v>-1.66</v>
       </c>
       <c r="J7">
-        <v>-1.74</v>
+        <v>-1.88</v>
       </c>
       <c r="K7">
-        <v>-0.37</v>
+        <v>0.3</v>
       </c>
       <c r="L7">
-        <v>-27.25</v>
+        <v>-29.75</v>
       </c>
       <c r="M7">
-        <v>19.06</v>
+        <v>18.84</v>
       </c>
       <c r="N7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>11307.8</v>
+        <v>11270.2</v>
       </c>
       <c r="Q7">
-        <v>11226.65</v>
+        <v>11211.25</v>
       </c>
       <c r="R7">
-        <v>11469.6</v>
+        <v>11473.14</v>
       </c>
       <c r="S7">
-        <v>13842.08</v>
+        <v>13797.62</v>
       </c>
       <c r="T7">
-        <v>-18.57</v>
+        <v>-19.13</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1607,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.94</v>
+        <v>45.81</v>
       </c>
       <c r="Z7">
-        <v>-56.52</v>
+        <v>-59.32</v>
       </c>
       <c r="AA7">
-        <v>-86.40000000000001</v>
+        <v>-80.98</v>
       </c>
       <c r="AB7">
-        <v>29.88</v>
+        <v>21.66</v>
       </c>
       <c r="AC7">
-        <v>90.05</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AD7">
-        <v>91.88</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="AE7">
-        <v>330.28</v>
+        <v>318.76</v>
       </c>
       <c r="AF7">
-        <v>-82.40000000000001</v>
+        <v>-76.98999999999999</v>
       </c>
       <c r="AG7">
-        <v>11555.14</v>
+        <v>11520.83</v>
       </c>
       <c r="AH7">
-        <v>10898.16</v>
+        <v>10901.67</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1643,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>14.27</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1654,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>353.9</v>
+        <v>333.75</v>
       </c>
       <c r="D8">
-        <v>-2.52</v>
+        <v>-5.69</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1666,46 +1620,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-3.73</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H8">
-        <v>51.04</v>
+        <v>42.44</v>
       </c>
       <c r="I8">
-        <v>1.11</v>
+        <v>-6.41</v>
       </c>
       <c r="J8">
-        <v>6.28</v>
+        <v>0.88</v>
       </c>
       <c r="K8">
-        <v>12.62</v>
+        <v>3.04</v>
       </c>
       <c r="L8">
-        <v>11.64</v>
+        <v>5.7</v>
       </c>
       <c r="M8">
-        <v>31.08</v>
+        <v>28.52</v>
       </c>
       <c r="N8">
         <v>77</v>
       </c>
       <c r="O8">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P8">
-        <v>358.08</v>
+        <v>353.51</v>
       </c>
       <c r="Q8">
-        <v>348.9</v>
+        <v>348.99</v>
       </c>
       <c r="R8">
-        <v>339.71</v>
+        <v>340.02</v>
       </c>
       <c r="S8">
-        <v>293.87</v>
+        <v>294.17</v>
       </c>
       <c r="T8">
-        <v>20.43</v>
+        <v>13.46</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1720,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>54.18</v>
+        <v>41.83</v>
       </c>
       <c r="Z8">
-        <v>5.94</v>
+        <v>3.85</v>
       </c>
       <c r="AA8">
-        <v>5.63</v>
+        <v>5.27</v>
       </c>
       <c r="AB8">
-        <v>0.31</v>
+        <v>-1.43</v>
       </c>
       <c r="AC8">
-        <v>60.35</v>
+        <v>38.53</v>
       </c>
       <c r="AD8">
-        <v>63.02</v>
+        <v>55.18</v>
       </c>
       <c r="AE8">
-        <v>11.76</v>
+        <v>12.52</v>
       </c>
       <c r="AF8">
-        <v>-4.36</v>
+        <v>-0.61</v>
       </c>
       <c r="AG8">
-        <v>375.4</v>
+        <v>375.26</v>
       </c>
       <c r="AH8">
-        <v>322.4</v>
+        <v>322.71</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1756,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>18.65</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1767,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1230</v>
+        <v>1175.2</v>
       </c>
       <c r="D9">
-        <v>-2.35</v>
+        <v>-4.46</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1779,46 +1733,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-8.279999999999999</v>
+        <v>-12.36</v>
       </c>
       <c r="H9">
-        <v>13.96</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I9">
-        <v>-3.33</v>
+        <v>-6.24</v>
       </c>
       <c r="J9">
-        <v>-7.17</v>
+        <v>-9.74</v>
       </c>
       <c r="K9">
-        <v>0.86</v>
+        <v>-4.13</v>
       </c>
       <c r="L9">
-        <v>7.32</v>
+        <v>1.16</v>
       </c>
       <c r="M9">
-        <v>14.06</v>
+        <v>13.05</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P9">
-        <v>1242.26</v>
+        <v>1226.62</v>
       </c>
       <c r="Q9">
-        <v>1265.74</v>
+        <v>1259.63</v>
       </c>
       <c r="R9">
-        <v>1285.12</v>
+        <v>1283.68</v>
       </c>
       <c r="S9">
-        <v>1239.62</v>
+        <v>1240.08</v>
       </c>
       <c r="T9">
-        <v>-0.78</v>
+        <v>-5.23</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1833,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>40.46</v>
+        <v>31.96</v>
       </c>
       <c r="Z9">
-        <v>-12.55</v>
+        <v>-18.08</v>
       </c>
       <c r="AA9">
-        <v>-9</v>
+        <v>-10.82</v>
       </c>
       <c r="AB9">
-        <v>-3.55</v>
+        <v>-7.27</v>
       </c>
       <c r="AC9">
-        <v>31.66</v>
+        <v>21.69</v>
       </c>
       <c r="AD9">
-        <v>34.36</v>
+        <v>30.05</v>
       </c>
       <c r="AE9">
-        <v>26.66</v>
+        <v>28.96</v>
       </c>
       <c r="AF9">
-        <v>27.86</v>
+        <v>161.1</v>
       </c>
       <c r="AG9">
-        <v>1313.91</v>
+        <v>1320.29</v>
       </c>
       <c r="AH9">
-        <v>1217.57</v>
+        <v>1198.98</v>
       </c>
       <c r="AI9">
-        <v>1314.04</v>
+        <v>1287.23</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.73</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1880,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>77.08</v>
+        <v>76.16</v>
       </c>
       <c r="D10">
-        <v>-0.72</v>
+        <v>-1.19</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1892,46 +1846,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-15.71</v>
+        <v>-16.72</v>
       </c>
       <c r="H10">
-        <v>113.64</v>
+        <v>111.09</v>
       </c>
       <c r="I10">
-        <v>-1.29</v>
+        <v>-5.53</v>
       </c>
       <c r="J10">
-        <v>-9.82</v>
+        <v>-9.23</v>
       </c>
       <c r="K10">
-        <v>51.4</v>
+        <v>50.39</v>
       </c>
       <c r="L10">
-        <v>-9.380000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="M10">
-        <v>-4.6</v>
+        <v>-4.83</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P10">
-        <v>77.77</v>
+        <v>76.88</v>
       </c>
       <c r="Q10">
-        <v>79.81</v>
+        <v>79.41</v>
       </c>
       <c r="R10">
-        <v>80.77</v>
+        <v>80.94</v>
       </c>
       <c r="S10">
-        <v>61.57</v>
+        <v>61.68</v>
       </c>
       <c r="T10">
-        <v>25.19</v>
+        <v>23.48</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1946,34 +1900,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>46.38</v>
+        <v>44.76</v>
       </c>
       <c r="Z10">
-        <v>-0.85</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AA10">
+        <v>-0.52</v>
+      </c>
+      <c r="AB10">
         <v>-0.42</v>
       </c>
-      <c r="AB10">
-        <v>-0.43</v>
-      </c>
       <c r="AC10">
-        <v>50.7</v>
+        <v>56.41</v>
       </c>
       <c r="AD10">
-        <v>47.39</v>
+        <v>51</v>
       </c>
       <c r="AE10">
-        <v>4.37</v>
+        <v>4.44</v>
       </c>
       <c r="AF10">
-        <v>17.29</v>
+        <v>51.23</v>
       </c>
       <c r="AG10">
-        <v>86.38</v>
+        <v>85.84</v>
       </c>
       <c r="AH10">
-        <v>73.23999999999999</v>
+        <v>72.98</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1982,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>41.83</v>
+        <v>41.32</v>
       </c>
     </row>
   </sheetData>
@@ -2123,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2181,1354 +2135,1328 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-2.84</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-9.16</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-6.32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-12.71</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-8.93</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.23</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-11.92</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-1.74</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6.28</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.74</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-9.82</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-2.84</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-9.15</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-7.66</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.7</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-5.16</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-8.93</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-6.11</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-11.01</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.83</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-5.59</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.13</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.63</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.47</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-4.13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1.11</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-7.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-5.53</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>17.26</v>
+      </c>
+      <c r="D25" s="6">
+        <v>11.78</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-5.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>39.13</v>
+      </c>
+      <c r="D26" s="6">
+        <v>32.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-7.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-0.38</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-6.18</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-6.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-13.24</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-27.25</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-29.75</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>11.64</v>
+      </c>
+      <c r="D31" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-5.94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>7.32</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1.16</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-6.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-7.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>8.57</v>
+      </c>
+      <c r="D35" s="6">
         <v>-0.77</v>
       </c>
-      <c r="E13" s="9">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="E35" s="7">
+        <v>-9.34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3.87</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-1.92</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-5.79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>5.23</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-5.79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-8.27</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-10.08</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-9.59</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-12.48</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.39</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-1.74</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-0.37</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>8.67</v>
-      </c>
-      <c r="D16" s="7">
-        <v>6.28</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>12.62</v>
+      </c>
+      <c r="D40" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-9.58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-7.17</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-4.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-4.79</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-9.82</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-5.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>51.4</v>
+      </c>
+      <c r="D42" s="6">
+        <v>50.39</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-35.17</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-36.97</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-11.21</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-14.9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-17.68</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-21.63</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-15.32</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-18.39</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-19.09</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-22.19</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-49.15</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-49.66</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-5.48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-12.36</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-4.08</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-15.71</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-16.72</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>653.25</v>
+      </c>
+      <c r="D52" s="6">
+        <v>635.05</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-18.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>281.9</v>
+      </c>
+      <c r="D53" s="6">
+        <v>270.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-11.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1061</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1010</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>732.15</v>
+      </c>
+      <c r="D55" s="6">
+        <v>705.6</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-26.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>485.45</v>
+      </c>
+      <c r="D56" s="6">
+        <v>466.85</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-18.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11272</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11158</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>353.9</v>
+      </c>
+      <c r="D58" s="6">
+        <v>333.75</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-20.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1230</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1175.2</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-54.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>77.08</v>
+      </c>
+      <c r="D60" s="6">
+        <v>76.16</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>99</v>
+      </c>
+      <c r="D61" s="6">
+        <v>88</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>23</v>
+      </c>
+      <c r="D62" s="6">
+        <v>12</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>12</v>
+      </c>
+      <c r="D63" s="6">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>88</v>
+      </c>
+      <c r="D64" s="6">
+        <v>99</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>42.52</v>
+      </c>
+      <c r="D65" s="6">
+        <v>38.27</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>47.18</v>
+      </c>
+      <c r="D66" s="6">
+        <v>40.23</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>34.39</v>
+      </c>
+      <c r="D67" s="6">
+        <v>27.37</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-7.02</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>47.57</v>
+      </c>
+      <c r="D68" s="6">
+        <v>40.15</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-7.42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>34.58</v>
+      </c>
+      <c r="D69" s="6">
+        <v>28.65</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-5.93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>48.94</v>
+      </c>
+      <c r="D70" s="6">
+        <v>45.81</v>
+      </c>
+      <c r="E70" s="7">
         <v>-3.13</v>
       </c>
-      <c r="D19" s="7">
-        <v>-3.27</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>54.18</v>
+      </c>
+      <c r="D71" s="6">
+        <v>41.83</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-12.35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>40.46</v>
+      </c>
+      <c r="D72" s="6">
+        <v>31.96</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>46.38</v>
+      </c>
+      <c r="D73" s="6">
+        <v>44.76</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-86.62</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-80.86</v>
+      </c>
+      <c r="E74" s="8">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>2.26</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.51</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-57.64</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-34.04</v>
+      </c>
+      <c r="E75" s="8">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-4.71</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-6.11</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-1.04</v>
+      </c>
+      <c r="D76" s="6">
+        <v>134.56</v>
+      </c>
+      <c r="E76" s="8">
+        <v>135.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.83</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-56.39</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-41.84</v>
+      </c>
+      <c r="E77" s="8">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-3.13</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>29.15</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-38.01</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2.47</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-82.40000000000001</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-76.98999999999999</v>
+      </c>
+      <c r="E79" s="8">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1.11</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-3.33</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>27.86</v>
+      </c>
+      <c r="D81" s="6">
+        <v>161.1</v>
+      </c>
+      <c r="E81" s="8">
+        <v>133.24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>4.35</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-5.64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>20.15</v>
-      </c>
-      <c r="D28" s="7">
-        <v>17.26</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>40.52</v>
-      </c>
-      <c r="D29" s="7">
-        <v>39.13</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>2.08</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-0.38</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>1.91</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-3.85</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-5.76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-6.45</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-30.63</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-27.25</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>15.16</v>
-      </c>
-      <c r="D34" s="7">
-        <v>11.64</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>10.23</v>
-      </c>
-      <c r="D35" s="7">
-        <v>7.32</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-9.93</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>6.08</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0.26</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-5.82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>7.97</v>
-      </c>
-      <c r="D38" s="7">
-        <v>8.57</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>4.88</v>
-      </c>
-      <c r="D39" s="7">
-        <v>3.87</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>7.98</v>
-      </c>
-      <c r="D40" s="7">
-        <v>5.23</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-9.06</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-9.59</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-3.87</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>12.59</v>
-      </c>
-      <c r="D43" s="7">
-        <v>12.62</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1.06</v>
-      </c>
-      <c r="D44" s="7">
-        <v>0.86</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>46.85</v>
-      </c>
-      <c r="D45" s="7">
-        <v>51.4</v>
-      </c>
-      <c r="E45" s="8">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-34.66</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-35.17</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-11.06</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-11.21</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-15.74</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-17.68</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-13.14</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-15.32</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-17.52</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-19.09</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-48.96</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-49.15</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-3.73</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-6.07</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-15.71</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>658.35</v>
-      </c>
-      <c r="D55" s="7">
-        <v>653.25</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>282.4</v>
-      </c>
-      <c r="D56" s="7">
-        <v>281.9</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1085.9</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1061</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-24.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>750.95</v>
-      </c>
-      <c r="D58" s="7">
-        <v>732.15</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-18.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>494.9</v>
-      </c>
-      <c r="D59" s="7">
-        <v>485.45</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-9.449999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>11313</v>
-      </c>
-      <c r="D60" s="7">
-        <v>11272</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>363.05</v>
-      </c>
-      <c r="D61" s="7">
-        <v>353.9</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-9.15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1259.6</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1230</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-29.6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>77.64</v>
-      </c>
-      <c r="D63" s="7">
-        <v>77.08</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>55</v>
-      </c>
-      <c r="D64" s="7">
-        <v>45</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>45</v>
-      </c>
-      <c r="D65" s="7">
-        <v>55</v>
-      </c>
-      <c r="E65" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>43.79</v>
-      </c>
-      <c r="D66" s="7">
-        <v>42.52</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>47.51</v>
-      </c>
-      <c r="D67" s="7">
-        <v>47.18</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>38.92</v>
-      </c>
-      <c r="D68" s="7">
-        <v>34.39</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-4.53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>54.14</v>
-      </c>
-      <c r="D69" s="7">
-        <v>47.57</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>38.33</v>
-      </c>
-      <c r="D70" s="7">
-        <v>34.58</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>50.09</v>
-      </c>
-      <c r="D71" s="7">
-        <v>48.94</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>61.89</v>
-      </c>
-      <c r="D72" s="7">
-        <v>54.18</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-7.71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>46.7</v>
-      </c>
-      <c r="D73" s="7">
-        <v>40.46</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-6.24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>47.34</v>
-      </c>
-      <c r="D74" s="7">
-        <v>46.38</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="7">
-        <v>-73.33</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-86.62</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-13.29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-37.18</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-57.64</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-20.46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>494.44</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-1.04</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-495.48</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-62.87</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-56.39</v>
-      </c>
-      <c r="E78" s="8">
-        <v>6.48</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>131.31</v>
-      </c>
-      <c r="D79" s="7">
-        <v>29.15</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-102.16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-71.09</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-82.40000000000001</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-11.31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-51.22</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-4.36</v>
-      </c>
-      <c r="E81" s="8">
-        <v>46.86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-7.26</v>
-      </c>
-      <c r="D82" s="7">
-        <v>27.86</v>
+      <c r="C82" s="6">
+        <v>17.29</v>
+      </c>
+      <c r="D82" s="6">
+        <v>51.23</v>
       </c>
       <c r="E82" s="8">
-        <v>35.12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-54.3</v>
-      </c>
-      <c r="D83" s="7">
-        <v>17.29</v>
-      </c>
-      <c r="E83" s="8">
-        <v>71.59</v>
+        <v>33.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3548,60 +3476,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>84</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>44.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>44</v>
-      </c>
-      <c r="E2" s="12">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-4.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>8.1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>37.7</v>
+      </c>
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-7.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3703,61 +3631,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3873</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3472</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3108</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2143</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1906</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1406</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0561</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.046</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0805</v>
+      <c r="A2" s="14">
+        <v>0.3779</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3364</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2852</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1976</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1884</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1305</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0464</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0483</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0839</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,49 +178,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.2 → 41.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.2</t>
-  </si>
-  <si>
-    <t>41.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -251,13 +215,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,22 +251,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,24 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,34 +337,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2077,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2097,47 +2020,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2146,1311 +2034,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-2.84</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-9.16</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-6.32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-12.71</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-8.93</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.92</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>6.28</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-9.74</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.7</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-6.11</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-11.01</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-5.59</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.63</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2.47</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-6.41</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-7.52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-5.53</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>17.26</v>
-      </c>
-      <c r="D25" s="6">
-        <v>11.78</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>39.13</v>
-      </c>
-      <c r="D26" s="6">
-        <v>32.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-7.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-0.38</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-10.37</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-6.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-27.25</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.75</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>11.64</v>
-      </c>
-      <c r="D31" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-5.94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>7.32</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-6.16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-7.43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>8.57</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-9.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.87</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>5.23</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-5.79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-9.59</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-12.48</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="D39" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>12.62</v>
-      </c>
-      <c r="D40" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-9.58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-4.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>51.4</v>
-      </c>
-      <c r="D42" s="6">
-        <v>50.39</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-35.17</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-36.97</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-11.21</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-17.68</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-21.63</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-15.32</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.39</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-19.09</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-22.19</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-49.15</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-49.66</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-12.36</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-4.08</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-15.71</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-16.72</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>653.25</v>
-      </c>
-      <c r="D52" s="6">
-        <v>635.05</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-18.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>281.9</v>
-      </c>
-      <c r="D53" s="6">
-        <v>270.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-11.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1061</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1010</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>732.15</v>
-      </c>
-      <c r="D55" s="6">
-        <v>705.6</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-26.55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>485.45</v>
-      </c>
-      <c r="D56" s="6">
-        <v>466.85</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-18.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11272</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11158</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>353.9</v>
-      </c>
-      <c r="D58" s="6">
-        <v>333.75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-20.15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1230</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1175.2</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-54.8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>77.08</v>
-      </c>
-      <c r="D60" s="6">
-        <v>76.16</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>99</v>
-      </c>
-      <c r="D61" s="6">
-        <v>88</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>23</v>
-      </c>
-      <c r="D62" s="6">
-        <v>12</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>12</v>
-      </c>
-      <c r="D63" s="6">
-        <v>23</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>88</v>
-      </c>
-      <c r="D64" s="6">
-        <v>99</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>42.52</v>
-      </c>
-      <c r="D65" s="6">
-        <v>38.27</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-4.25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>47.18</v>
-      </c>
-      <c r="D66" s="6">
-        <v>40.23</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-6.95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>34.39</v>
-      </c>
-      <c r="D67" s="6">
-        <v>27.37</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-7.02</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>47.57</v>
-      </c>
-      <c r="D68" s="6">
-        <v>40.15</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-7.42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>34.58</v>
-      </c>
-      <c r="D69" s="6">
-        <v>28.65</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-5.93</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>48.94</v>
-      </c>
-      <c r="D70" s="6">
-        <v>45.81</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>54.18</v>
-      </c>
-      <c r="D71" s="6">
-        <v>41.83</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-12.35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>40.46</v>
-      </c>
-      <c r="D72" s="6">
-        <v>31.96</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-8.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>46.38</v>
-      </c>
-      <c r="D73" s="6">
-        <v>44.76</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-86.62</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-80.86</v>
-      </c>
-      <c r="E74" s="8">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-57.64</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-34.04</v>
-      </c>
-      <c r="E75" s="8">
-        <v>23.6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="D76" s="6">
-        <v>134.56</v>
-      </c>
-      <c r="E76" s="8">
-        <v>135.6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-56.39</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-41.84</v>
-      </c>
-      <c r="E77" s="8">
-        <v>14.55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>29.15</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-38.01</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-82.40000000000001</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-76.98999999999999</v>
-      </c>
-      <c r="E79" s="8">
-        <v>5.41</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E80" s="8">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>27.86</v>
-      </c>
-      <c r="D81" s="6">
-        <v>161.1</v>
-      </c>
-      <c r="E81" s="8">
-        <v>133.24</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>17.29</v>
-      </c>
-      <c r="D82" s="6">
-        <v>51.23</v>
-      </c>
-      <c r="E82" s="8">
-        <v>33.94</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3476,60 +2060,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>44.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>37.7</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-7.8</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>3</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>30</v>
       </c>
     </row>
@@ -3631,60 +2215,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.3779</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.3364</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.2852</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1976</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.1884</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.1305</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>0.0464</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>-0.0483</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="9">
         <v>-0.0839</v>
       </c>
     </row>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,13 +178,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.8 → 51.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>51.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -215,11 +251,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +289,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +320,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,27 +407,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -713,7 +790,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -853,10 +931,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>635.05</v>
+        <v>646.8</v>
       </c>
       <c r="D2">
-        <v>-2.79</v>
+        <v>1.85</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -865,25 +943,25 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.97</v>
+        <v>-35.81</v>
       </c>
       <c r="H2">
-        <v>72.94</v>
+        <v>76.14</v>
       </c>
       <c r="I2">
-        <v>-5.58</v>
+        <v>-1.06</v>
       </c>
       <c r="J2">
-        <v>-9.16</v>
+        <v>-5.41</v>
       </c>
       <c r="K2">
-        <v>-7.17</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L2">
-        <v>11.78</v>
+        <v>15.38</v>
       </c>
       <c r="M2">
-        <v>-8.390000000000001</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -892,19 +970,19 @@
         <v>67</v>
       </c>
       <c r="P2">
-        <v>648.39</v>
+        <v>647.01</v>
       </c>
       <c r="Q2">
-        <v>689.55</v>
+        <v>688.1</v>
       </c>
       <c r="R2">
-        <v>664.14</v>
+        <v>664.33</v>
       </c>
       <c r="S2">
-        <v>643.3200000000001</v>
+        <v>644.16</v>
       </c>
       <c r="T2">
-        <v>-1.29</v>
+        <v>0.41</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -916,46 +994,46 @@
         <v>47</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>38.27</v>
+        <v>42.28</v>
       </c>
       <c r="Z2">
-        <v>-7.17</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AA2">
-        <v>1.93</v>
+        <v>-0.11</v>
       </c>
       <c r="AB2">
-        <v>-9.1</v>
+        <v>-8.18</v>
       </c>
       <c r="AC2">
-        <v>11.62</v>
+        <v>10.57</v>
       </c>
       <c r="AD2">
-        <v>9.76</v>
+        <v>11.23</v>
       </c>
       <c r="AE2">
-        <v>30.3</v>
+        <v>30.06</v>
       </c>
       <c r="AF2">
-        <v>-80.86</v>
+        <v>-83.79000000000001</v>
       </c>
       <c r="AG2">
-        <v>757.5</v>
+        <v>758.49</v>
       </c>
       <c r="AH2">
-        <v>621.6</v>
+        <v>617.72</v>
       </c>
       <c r="AI2">
-        <v>739.46</v>
+        <v>734.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.22</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -966,10 +1044,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>270.2</v>
+        <v>269.6</v>
       </c>
       <c r="D3">
-        <v>-4.15</v>
+        <v>-0.22</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -978,25 +1056,25 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-14.9</v>
+        <v>-15.09</v>
       </c>
       <c r="H3">
-        <v>76.34</v>
+        <v>75.94</v>
       </c>
       <c r="I3">
-        <v>-2.7</v>
+        <v>-0.26</v>
       </c>
       <c r="J3">
-        <v>-12.71</v>
+        <v>-12.35</v>
       </c>
       <c r="K3">
-        <v>-0.77</v>
+        <v>-2.25</v>
       </c>
       <c r="L3">
-        <v>32.06</v>
+        <v>33.46</v>
       </c>
       <c r="M3">
-        <v>37.79</v>
+        <v>37.65</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1005,19 +1083,19 @@
         <v>79</v>
       </c>
       <c r="P3">
-        <v>275.96</v>
+        <v>275.82</v>
       </c>
       <c r="Q3">
-        <v>287.21</v>
+        <v>285.1</v>
       </c>
       <c r="R3">
-        <v>284.21</v>
+        <v>284.45</v>
       </c>
       <c r="S3">
-        <v>229.78</v>
+        <v>230.33</v>
       </c>
       <c r="T3">
-        <v>17.59</v>
+        <v>17.05</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1032,43 +1110,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.23</v>
+        <v>39.91</v>
       </c>
       <c r="Z3">
-        <v>-4.13</v>
+        <v>-4.69</v>
       </c>
       <c r="AA3">
-        <v>-2.19</v>
+        <v>-2.69</v>
       </c>
       <c r="AB3">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="AC3">
-        <v>56.61</v>
+        <v>35.48</v>
       </c>
       <c r="AD3">
-        <v>51.57</v>
+        <v>51.21</v>
       </c>
       <c r="AE3">
-        <v>10.72</v>
+        <v>10.51</v>
       </c>
       <c r="AF3">
-        <v>-34.04</v>
+        <v>-20.48</v>
       </c>
       <c r="AG3">
-        <v>313.77</v>
+        <v>310.12</v>
       </c>
       <c r="AH3">
-        <v>260.64</v>
+        <v>260.08</v>
       </c>
       <c r="AI3">
-        <v>301.41</v>
+        <v>300.1</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>45.22</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1079,10 +1157,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1010</v>
+        <v>1016.7</v>
       </c>
       <c r="D4">
-        <v>-4.81</v>
+        <v>0.66</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1091,25 +1169,25 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-21.63</v>
+        <v>-21.11</v>
       </c>
       <c r="H4">
-        <v>2.43</v>
+        <v>3.11</v>
       </c>
       <c r="I4">
-        <v>-11.01</v>
+        <v>-7.61</v>
       </c>
       <c r="J4">
-        <v>-12.01</v>
+        <v>-10.53</v>
       </c>
       <c r="K4">
-        <v>-1.92</v>
+        <v>-3.29</v>
       </c>
       <c r="L4">
-        <v>-6.18</v>
+        <v>-3.71</v>
       </c>
       <c r="M4">
-        <v>19.76</v>
+        <v>20.11</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1118,19 +1196,19 @@
         <v>59</v>
       </c>
       <c r="P4">
-        <v>1070.94</v>
+        <v>1054.18</v>
       </c>
       <c r="Q4">
-        <v>1118.93</v>
+        <v>1112.44</v>
       </c>
       <c r="R4">
-        <v>1124.44</v>
+        <v>1123</v>
       </c>
       <c r="S4">
-        <v>1139.06</v>
+        <v>1139.18</v>
       </c>
       <c r="T4">
-        <v>-11.33</v>
+        <v>-10.75</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1145,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.37</v>
+        <v>29.41</v>
       </c>
       <c r="Z4">
-        <v>-17.58</v>
+        <v>-22.68</v>
       </c>
       <c r="AA4">
-        <v>-4.33</v>
+        <v>-8</v>
       </c>
       <c r="AB4">
-        <v>-13.25</v>
+        <v>-14.68</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD4">
-        <v>2.12</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
-        <v>34.95</v>
+        <v>34.11</v>
       </c>
       <c r="AF4">
-        <v>134.56</v>
+        <v>41.58</v>
       </c>
       <c r="AG4">
-        <v>1194.81</v>
+        <v>1199.73</v>
       </c>
       <c r="AH4">
-        <v>1043.05</v>
+        <v>1025.15</v>
       </c>
       <c r="AI4">
-        <v>1137.81</v>
+        <v>1119.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>42.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1192,10 +1270,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>705.6</v>
+        <v>709.05</v>
       </c>
       <c r="D5">
-        <v>-3.63</v>
+        <v>0.49</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1204,46 +1282,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.39</v>
+        <v>-17.99</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.12</v>
       </c>
       <c r="I5">
-        <v>-5.59</v>
+        <v>-3.23</v>
       </c>
       <c r="J5">
-        <v>-4.23</v>
+        <v>-4.02</v>
       </c>
       <c r="K5">
-        <v>-0.5600000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="L5">
-        <v>-10.37</v>
+        <v>-6.71</v>
       </c>
       <c r="M5">
-        <v>33.64</v>
+        <v>33.93</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O5">
         <v>61</v>
       </c>
       <c r="P5">
-        <v>732.6799999999999</v>
+        <v>727.95</v>
       </c>
       <c r="Q5">
-        <v>743.34</v>
+        <v>739.63</v>
       </c>
       <c r="R5">
-        <v>733.59</v>
+        <v>733.2</v>
       </c>
       <c r="S5">
-        <v>746.0599999999999</v>
+        <v>745.6</v>
       </c>
       <c r="T5">
-        <v>-5.42</v>
+        <v>-4.9</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1258,43 +1336,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.15</v>
+        <v>41.43</v>
       </c>
       <c r="Z5">
-        <v>-0.71</v>
+        <v>-2.82</v>
       </c>
       <c r="AA5">
-        <v>2.94</v>
+        <v>1.79</v>
       </c>
       <c r="AB5">
-        <v>-3.65</v>
+        <v>-4.61</v>
       </c>
       <c r="AC5">
-        <v>23.14</v>
+        <v>3.51</v>
       </c>
       <c r="AD5">
-        <v>32.63</v>
+        <v>21.05</v>
       </c>
       <c r="AE5">
-        <v>21.7</v>
+        <v>20.98</v>
       </c>
       <c r="AF5">
-        <v>-41.84</v>
+        <v>-79.18000000000001</v>
       </c>
       <c r="AG5">
-        <v>776.38</v>
+        <v>770.37</v>
       </c>
       <c r="AH5">
-        <v>710.3</v>
+        <v>708.88</v>
       </c>
       <c r="AI5">
-        <v>783.51</v>
+        <v>771.61</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>18.29</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1305,10 +1383,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>466.85</v>
+        <v>462.3</v>
       </c>
       <c r="D6">
-        <v>-3.83</v>
+        <v>-0.97</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1317,25 +1395,25 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-22.19</v>
+        <v>-22.95</v>
       </c>
       <c r="H6">
-        <v>6.45</v>
+        <v>5.41</v>
       </c>
       <c r="I6">
-        <v>-5.63</v>
+        <v>-4.68</v>
       </c>
       <c r="J6">
-        <v>-11.92</v>
+        <v>-12.19</v>
       </c>
       <c r="K6">
-        <v>-12.48</v>
+        <v>-16.47</v>
       </c>
       <c r="L6">
-        <v>-13.24</v>
+        <v>-14.26</v>
       </c>
       <c r="M6">
-        <v>4.64</v>
+        <v>4.05</v>
       </c>
       <c r="N6">
         <v>12</v>
@@ -1344,19 +1422,19 @@
         <v>41</v>
       </c>
       <c r="P6">
-        <v>484.8</v>
+        <v>480.26</v>
       </c>
       <c r="Q6">
-        <v>506.34</v>
+        <v>502.72</v>
       </c>
       <c r="R6">
-        <v>531.61</v>
+        <v>529.95</v>
       </c>
       <c r="S6">
-        <v>523.77</v>
+        <v>523.7</v>
       </c>
       <c r="T6">
-        <v>-10.87</v>
+        <v>-11.72</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1371,43 +1449,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>28.65</v>
+        <v>27.41</v>
       </c>
       <c r="Z6">
-        <v>-14.33</v>
+        <v>-15.86</v>
       </c>
       <c r="AA6">
-        <v>-11.83</v>
+        <v>-12.64</v>
       </c>
       <c r="AB6">
-        <v>-2.5</v>
+        <v>-3.22</v>
       </c>
       <c r="AC6">
-        <v>23.25</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>28.47</v>
+        <v>21.65</v>
       </c>
       <c r="AE6">
-        <v>12.96</v>
+        <v>12.6</v>
       </c>
       <c r="AF6">
-        <v>-8.859999999999999</v>
+        <v>-41.77</v>
       </c>
       <c r="AG6">
-        <v>541.23</v>
+        <v>540.13</v>
       </c>
       <c r="AH6">
-        <v>471.45</v>
+        <v>465.3</v>
       </c>
       <c r="AI6">
-        <v>513.64</v>
+        <v>502.76</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>35.07</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1418,10 +1496,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11158</v>
+        <v>11346</v>
       </c>
       <c r="D7">
-        <v>-1.01</v>
+        <v>1.68</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1430,25 +1508,25 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.66</v>
+        <v>-48.81</v>
       </c>
       <c r="H7">
-        <v>4.72</v>
+        <v>6.49</v>
       </c>
       <c r="I7">
-        <v>-1.66</v>
+        <v>0.78</v>
       </c>
       <c r="J7">
-        <v>-1.88</v>
+        <v>-1.05</v>
       </c>
       <c r="K7">
-        <v>0.3</v>
+        <v>0.87</v>
       </c>
       <c r="L7">
-        <v>-29.75</v>
+        <v>-29.79</v>
       </c>
       <c r="M7">
-        <v>18.84</v>
+        <v>19.49</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1457,19 +1535,19 @@
         <v>41</v>
       </c>
       <c r="P7">
-        <v>11270.2</v>
+        <v>11287.8</v>
       </c>
       <c r="Q7">
-        <v>11211.25</v>
+        <v>11211.35</v>
       </c>
       <c r="R7">
-        <v>11473.14</v>
+        <v>11476.8</v>
       </c>
       <c r="S7">
-        <v>13797.62</v>
+        <v>13754.5</v>
       </c>
       <c r="T7">
-        <v>-19.13</v>
+        <v>-17.51</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1484,34 +1562,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>45.81</v>
+        <v>51.34</v>
       </c>
       <c r="Z7">
-        <v>-59.32</v>
+        <v>-45.85</v>
       </c>
       <c r="AA7">
-        <v>-80.98</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="AB7">
-        <v>21.66</v>
+        <v>28.1</v>
       </c>
       <c r="AC7">
-        <v>72.09999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="AD7">
-        <v>84.54000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="AE7">
-        <v>318.76</v>
+        <v>314.5</v>
       </c>
       <c r="AF7">
-        <v>-76.98999999999999</v>
+        <v>426.61</v>
       </c>
       <c r="AG7">
-        <v>11520.83</v>
+        <v>11521.11</v>
       </c>
       <c r="AH7">
-        <v>10901.67</v>
+        <v>10901.59</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1520,7 +1598,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>13.53</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1531,10 +1609,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>333.75</v>
+        <v>338.75</v>
       </c>
       <c r="D8">
-        <v>-5.69</v>
+        <v>1.5</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1543,25 +1621,25 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-9.210000000000001</v>
+        <v>-7.85</v>
       </c>
       <c r="H8">
-        <v>42.44</v>
+        <v>44.57</v>
       </c>
       <c r="I8">
-        <v>-6.41</v>
+        <v>-5.23</v>
       </c>
       <c r="J8">
-        <v>0.88</v>
+        <v>2.03</v>
       </c>
       <c r="K8">
-        <v>3.04</v>
+        <v>2.64</v>
       </c>
       <c r="L8">
-        <v>5.7</v>
+        <v>9.66</v>
       </c>
       <c r="M8">
-        <v>28.52</v>
+        <v>29.13</v>
       </c>
       <c r="N8">
         <v>77</v>
@@ -1570,19 +1648,19 @@
         <v>72</v>
       </c>
       <c r="P8">
-        <v>353.51</v>
+        <v>349.77</v>
       </c>
       <c r="Q8">
-        <v>348.99</v>
+        <v>348.86</v>
       </c>
       <c r="R8">
-        <v>340.02</v>
+        <v>340.46</v>
       </c>
       <c r="S8">
-        <v>294.17</v>
+        <v>294.47</v>
       </c>
       <c r="T8">
-        <v>13.46</v>
+        <v>15.04</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1597,34 +1675,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.83</v>
+        <v>45.17</v>
       </c>
       <c r="Z8">
-        <v>3.85</v>
+        <v>2.56</v>
       </c>
       <c r="AA8">
-        <v>5.27</v>
+        <v>4.73</v>
       </c>
       <c r="AB8">
-        <v>-1.43</v>
+        <v>-2.17</v>
       </c>
       <c r="AC8">
-        <v>38.53</v>
+        <v>18.17</v>
       </c>
       <c r="AD8">
-        <v>55.18</v>
+        <v>39.01</v>
       </c>
       <c r="AE8">
-        <v>12.52</v>
+        <v>12.31</v>
       </c>
       <c r="AF8">
-        <v>-0.61</v>
+        <v>-29.1</v>
       </c>
       <c r="AG8">
-        <v>375.26</v>
+        <v>375.32</v>
       </c>
       <c r="AH8">
-        <v>322.71</v>
+        <v>322.39</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1633,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>21.94</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1644,10 +1722,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1175.2</v>
+        <v>1168</v>
       </c>
       <c r="D9">
-        <v>-4.46</v>
+        <v>-0.61</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1656,46 +1734,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-12.36</v>
+        <v>-12.9</v>
       </c>
       <c r="H9">
-        <v>8.890000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I9">
-        <v>-6.24</v>
+        <v>-5.27</v>
       </c>
       <c r="J9">
-        <v>-9.74</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K9">
-        <v>-4.13</v>
+        <v>-6.21</v>
       </c>
       <c r="L9">
-        <v>1.16</v>
+        <v>0.7</v>
       </c>
       <c r="M9">
-        <v>13.05</v>
+        <v>12.71</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>62</v>
       </c>
       <c r="P9">
-        <v>1226.62</v>
+        <v>1213.62</v>
       </c>
       <c r="Q9">
-        <v>1259.63</v>
+        <v>1252.53</v>
       </c>
       <c r="R9">
-        <v>1283.68</v>
+        <v>1281.51</v>
       </c>
       <c r="S9">
-        <v>1240.08</v>
+        <v>1240.53</v>
       </c>
       <c r="T9">
-        <v>-5.23</v>
+        <v>-5.85</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1710,43 +1788,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>31.96</v>
+        <v>31.03</v>
       </c>
       <c r="Z9">
-        <v>-18.08</v>
+        <v>-22.79</v>
       </c>
       <c r="AA9">
-        <v>-10.82</v>
+        <v>-13.21</v>
       </c>
       <c r="AB9">
-        <v>-7.27</v>
+        <v>-9.58</v>
       </c>
       <c r="AC9">
-        <v>21.69</v>
+        <v>3.64</v>
       </c>
       <c r="AD9">
-        <v>30.05</v>
+        <v>19</v>
       </c>
       <c r="AE9">
-        <v>28.96</v>
+        <v>28.94</v>
       </c>
       <c r="AF9">
-        <v>161.1</v>
+        <v>-31.75</v>
       </c>
       <c r="AG9">
-        <v>1320.29</v>
+        <v>1321.1</v>
       </c>
       <c r="AH9">
-        <v>1198.98</v>
+        <v>1183.97</v>
       </c>
       <c r="AI9">
-        <v>1287.23</v>
+        <v>1264.48</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>30.72</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1757,10 +1835,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.16</v>
+        <v>76.3</v>
       </c>
       <c r="D10">
-        <v>-1.19</v>
+        <v>0.18</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1769,25 +1847,25 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-16.72</v>
+        <v>-16.57</v>
       </c>
       <c r="H10">
-        <v>111.09</v>
+        <v>111.47</v>
       </c>
       <c r="I10">
-        <v>-5.53</v>
+        <v>-2.6</v>
       </c>
       <c r="J10">
-        <v>-9.23</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="K10">
-        <v>50.39</v>
+        <v>49.87</v>
       </c>
       <c r="L10">
-        <v>-9.65</v>
+        <v>-7.59</v>
       </c>
       <c r="M10">
-        <v>-4.83</v>
+        <v>-4.7</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1796,19 +1874,19 @@
         <v>82</v>
       </c>
       <c r="P10">
-        <v>76.88</v>
+        <v>76.47</v>
       </c>
       <c r="Q10">
-        <v>79.41</v>
+        <v>79.03</v>
       </c>
       <c r="R10">
-        <v>80.94</v>
+        <v>81.08</v>
       </c>
       <c r="S10">
-        <v>61.68</v>
+        <v>61.78</v>
       </c>
       <c r="T10">
-        <v>23.48</v>
+        <v>23.5</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1823,34 +1901,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>44.76</v>
+        <v>45.07</v>
       </c>
       <c r="Z10">
-        <v>-0.9399999999999999</v>
+        <v>-0.99</v>
       </c>
       <c r="AA10">
-        <v>-0.52</v>
+        <v>-0.62</v>
       </c>
       <c r="AB10">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="AC10">
-        <v>56.41</v>
+        <v>50.85</v>
       </c>
       <c r="AD10">
-        <v>51</v>
+        <v>52.65</v>
       </c>
       <c r="AE10">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="AF10">
-        <v>51.23</v>
+        <v>-35.25</v>
       </c>
       <c r="AG10">
-        <v>85.84</v>
+        <v>85.25</v>
       </c>
       <c r="AH10">
-        <v>72.98</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1859,7 +1937,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>41.32</v>
+        <v>40.87</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +2078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2020,12 +2098,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2034,7 +2147,1277 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.16</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-12.71</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-12.35</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-10.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-4.23</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.02</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-11.92</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.19</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.03</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-9.74</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-11.01</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-5.59</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.63</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-5.23</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-5.27</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-5.53</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>11.78</v>
+      </c>
+      <c r="D25" s="6">
+        <v>15.38</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>32.06</v>
+      </c>
+      <c r="D26" s="6">
+        <v>33.46</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-6.18</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-6.71</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-13.24</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-14.26</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-29.75</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-29.79</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="D31" s="6">
+        <v>9.66</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.16</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-7.59</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-1.92</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-3.29</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-1.03</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-12.48</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-16.47</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="D40" s="6">
+        <v>2.64</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>50.39</v>
+      </c>
+      <c r="D42" s="6">
+        <v>49.87</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-36.97</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-35.81</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-14.9</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-15.09</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-21.63</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-21.11</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-18.39</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-17.99</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-22.19</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-22.95</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-49.66</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-48.81</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-7.85</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-12.36</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-12.9</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-16.72</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-16.57</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>635.05</v>
+      </c>
+      <c r="D52" s="6">
+        <v>646.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>270.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>269.6</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1010</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1016.7</v>
+      </c>
+      <c r="E54" s="7">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>705.6</v>
+      </c>
+      <c r="D55" s="6">
+        <v>709.05</v>
+      </c>
+      <c r="E55" s="7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>466.85</v>
+      </c>
+      <c r="D56" s="6">
+        <v>462.3</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11158</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11346</v>
+      </c>
+      <c r="E57" s="7">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>333.75</v>
+      </c>
+      <c r="D58" s="6">
+        <v>338.75</v>
+      </c>
+      <c r="E58" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1175.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1168</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-7.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>76.16</v>
+      </c>
+      <c r="D60" s="6">
+        <v>76.3</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>55</v>
+      </c>
+      <c r="E61" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>55</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>38.27</v>
+      </c>
+      <c r="D63" s="6">
+        <v>42.28</v>
+      </c>
+      <c r="E63" s="7">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>40.23</v>
+      </c>
+      <c r="D64" s="6">
+        <v>39.91</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>27.37</v>
+      </c>
+      <c r="D65" s="6">
+        <v>29.41</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>40.15</v>
+      </c>
+      <c r="D66" s="6">
+        <v>41.43</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>28.65</v>
+      </c>
+      <c r="D67" s="6">
+        <v>27.41</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>45.81</v>
+      </c>
+      <c r="D68" s="6">
+        <v>51.34</v>
+      </c>
+      <c r="E68" s="7">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>41.83</v>
+      </c>
+      <c r="D69" s="6">
+        <v>45.17</v>
+      </c>
+      <c r="E69" s="7">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>31.96</v>
+      </c>
+      <c r="D70" s="6">
+        <v>31.03</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>44.76</v>
+      </c>
+      <c r="D71" s="6">
+        <v>45.07</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-80.86</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-83.79000000000001</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-34.04</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-20.48</v>
+      </c>
+      <c r="E73" s="7">
+        <v>13.56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>134.56</v>
+      </c>
+      <c r="D74" s="6">
+        <v>41.58</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-92.98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-41.84</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-37.34</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-41.77</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-32.91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-76.98999999999999</v>
+      </c>
+      <c r="D77" s="6">
+        <v>426.61</v>
+      </c>
+      <c r="E77" s="7">
+        <v>503.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-29.1</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-28.49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>161.1</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-31.75</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-192.85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>51.23</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-35.25</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-86.48</v>
       </c>
     </row>
   </sheetData>
@@ -2060,60 +3443,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="6">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="11">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
-        <v>37.7</v>
-      </c>
-      <c r="E2" s="6">
-        <v>30</v>
-      </c>
-      <c r="F2" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="G2" s="6">
-        <v>3</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="D2" s="11">
+        <v>39.2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -2215,61 +3598,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9">
-        <v>0.3779</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.3364</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.2852</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.1976</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.1884</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.1305</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.0464</v>
-      </c>
-      <c r="H2" s="9">
-        <v>-0.0483</v>
-      </c>
-      <c r="I2" s="9">
-        <v>-0.0839</v>
+      <c r="A2" s="14">
+        <v>0.3765</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3393</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2913</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2011</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1949</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1271</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0405</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.047</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.08039999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -967,7 +967,7 @@
         <v>66</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P2">
         <v>647.01</v>
@@ -1193,7 +1193,7 @@
         <v>34</v>
       </c>
       <c r="O4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P4">
         <v>1054.18</v>
@@ -1419,7 +1419,7 @@
         <v>12</v>
       </c>
       <c r="O6">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="P6">
         <v>480.26</v>
@@ -1532,7 +1532,7 @@
         <v>23</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P7">
         <v>11287.8</v>
@@ -1645,7 +1645,7 @@
         <v>77</v>
       </c>
       <c r="O8">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P8">
         <v>349.77</v>
@@ -1758,7 +1758,7 @@
         <v>45</v>
       </c>
       <c r="O9">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P9">
         <v>1213.62</v>
@@ -1871,7 +1871,7 @@
         <v>99</v>
       </c>
       <c r="O10">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P10">
         <v>76.47</v>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.4 → 31.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.8 → 51.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.8</t>
-  </si>
-  <si>
-    <t>51.3</t>
+    <t>45.1 → 50.1</t>
+  </si>
+  <si>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +436,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -790,8 +812,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -931,10 +952,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>646.8</v>
+        <v>644.9</v>
       </c>
       <c r="D2">
-        <v>1.85</v>
+        <v>-0.29</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -943,46 +964,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-35.81</v>
+        <v>-36</v>
       </c>
       <c r="H2">
-        <v>76.14</v>
+        <v>75.63</v>
       </c>
       <c r="I2">
-        <v>-1.06</v>
+        <v>0.51</v>
       </c>
       <c r="J2">
-        <v>-5.41</v>
+        <v>-4.56</v>
       </c>
       <c r="K2">
-        <v>-9.949999999999999</v>
+        <v>-6.21</v>
       </c>
       <c r="L2">
-        <v>15.38</v>
+        <v>15.23</v>
       </c>
       <c r="M2">
-        <v>-8.039999999999999</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>647.01</v>
+        <v>647.67</v>
       </c>
       <c r="Q2">
-        <v>688.1</v>
+        <v>686.49</v>
       </c>
       <c r="R2">
-        <v>664.33</v>
+        <v>664.64</v>
       </c>
       <c r="S2">
-        <v>644.16</v>
+        <v>644.9400000000001</v>
       </c>
       <c r="T2">
-        <v>0.41</v>
+        <v>-0.01</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -994,46 +1015,46 @@
         <v>47</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.28</v>
+        <v>41.81</v>
       </c>
       <c r="Z2">
-        <v>-8.300000000000001</v>
+        <v>-9.24</v>
       </c>
       <c r="AA2">
-        <v>-0.11</v>
+        <v>-1.94</v>
       </c>
       <c r="AB2">
-        <v>-8.18</v>
+        <v>-7.3</v>
       </c>
       <c r="AC2">
-        <v>10.57</v>
+        <v>10.98</v>
       </c>
       <c r="AD2">
-        <v>11.23</v>
+        <v>11.06</v>
       </c>
       <c r="AE2">
-        <v>30.06</v>
+        <v>28.93</v>
       </c>
       <c r="AF2">
-        <v>-83.79000000000001</v>
+        <v>-91.16</v>
       </c>
       <c r="AG2">
-        <v>758.49</v>
+        <v>759.36</v>
       </c>
       <c r="AH2">
-        <v>617.72</v>
+        <v>613.61</v>
       </c>
       <c r="AI2">
-        <v>734.71</v>
+        <v>732.39</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.18</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1065,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>269.6</v>
+        <v>281.1</v>
       </c>
       <c r="D3">
-        <v>-0.22</v>
+        <v>4.27</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1056,88 +1077,88 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-15.09</v>
+        <v>-11.46</v>
       </c>
       <c r="H3">
-        <v>75.94</v>
+        <v>83.45</v>
       </c>
       <c r="I3">
-        <v>-0.26</v>
+        <v>2.22</v>
       </c>
       <c r="J3">
-        <v>-12.35</v>
+        <v>-9.82</v>
       </c>
       <c r="K3">
-        <v>-2.25</v>
+        <v>4.65</v>
       </c>
       <c r="L3">
-        <v>33.46</v>
+        <v>40.29</v>
       </c>
       <c r="M3">
-        <v>37.65</v>
+        <v>38.81</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>275.82</v>
+        <v>277.04</v>
       </c>
       <c r="Q3">
-        <v>285.1</v>
+        <v>283.28</v>
       </c>
       <c r="R3">
-        <v>284.45</v>
+        <v>284.99</v>
       </c>
       <c r="S3">
-        <v>230.33</v>
+        <v>230.92</v>
       </c>
       <c r="T3">
-        <v>17.05</v>
+        <v>21.73</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V3" t="s">
         <v>47</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.91</v>
+        <v>48.49</v>
       </c>
       <c r="Z3">
-        <v>-4.69</v>
+        <v>-4.16</v>
       </c>
       <c r="AA3">
-        <v>-2.69</v>
+        <v>-2.98</v>
       </c>
       <c r="AB3">
-        <v>-2</v>
+        <v>-1.17</v>
       </c>
       <c r="AC3">
-        <v>35.48</v>
+        <v>39.14</v>
       </c>
       <c r="AD3">
-        <v>51.21</v>
+        <v>43.75</v>
       </c>
       <c r="AE3">
-        <v>10.51</v>
+        <v>10.67</v>
       </c>
       <c r="AF3">
-        <v>-20.48</v>
+        <v>11.95</v>
       </c>
       <c r="AG3">
-        <v>310.12</v>
+        <v>303.14</v>
       </c>
       <c r="AH3">
-        <v>260.08</v>
+        <v>263.42</v>
       </c>
       <c r="AI3">
         <v>300.1</v>
@@ -1146,7 +1167,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>46.24</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,10 +1178,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1016.7</v>
+        <v>1012.5</v>
       </c>
       <c r="D4">
-        <v>0.66</v>
+        <v>-0.41</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1169,46 +1190,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-21.11</v>
+        <v>-21.44</v>
       </c>
       <c r="H4">
-        <v>3.11</v>
+        <v>2.69</v>
       </c>
       <c r="I4">
-        <v>-7.61</v>
+        <v>-7.73</v>
       </c>
       <c r="J4">
-        <v>-10.53</v>
+        <v>-11.69</v>
       </c>
       <c r="K4">
-        <v>-3.29</v>
+        <v>-1.58</v>
       </c>
       <c r="L4">
-        <v>-3.71</v>
+        <v>-2.05</v>
       </c>
       <c r="M4">
-        <v>20.11</v>
+        <v>19.65</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>1054.18</v>
+        <v>1037.22</v>
       </c>
       <c r="Q4">
-        <v>1112.44</v>
+        <v>1106.22</v>
       </c>
       <c r="R4">
-        <v>1123</v>
+        <v>1121.38</v>
       </c>
       <c r="S4">
-        <v>1139.18</v>
+        <v>1139.23</v>
       </c>
       <c r="T4">
-        <v>-10.75</v>
+        <v>-11.12</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1223,34 +1244,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.41</v>
+        <v>28.86</v>
       </c>
       <c r="Z4">
-        <v>-22.68</v>
+        <v>-26.75</v>
       </c>
       <c r="AA4">
-        <v>-8</v>
+        <v>-11.75</v>
       </c>
       <c r="AB4">
-        <v>-14.68</v>
+        <v>-15</v>
       </c>
       <c r="AC4">
-        <v>2.02</v>
+        <v>3.51</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="AE4">
-        <v>34.11</v>
+        <v>34.14</v>
       </c>
       <c r="AF4">
-        <v>41.58</v>
+        <v>24.22</v>
       </c>
       <c r="AG4">
-        <v>1199.73</v>
+        <v>1203.34</v>
       </c>
       <c r="AH4">
-        <v>1025.15</v>
+        <v>1009.09</v>
       </c>
       <c r="AI4">
         <v>1119.97</v>
@@ -1259,7 +1280,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>47.2</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1291,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>709.05</v>
+        <v>706.9</v>
       </c>
       <c r="D5">
-        <v>0.49</v>
+        <v>-0.3</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1282,46 +1303,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-17.99</v>
+        <v>-18.24</v>
       </c>
       <c r="H5">
-        <v>7.12</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>-3.23</v>
+        <v>-4.73</v>
       </c>
       <c r="J5">
-        <v>-4.02</v>
+        <v>-9.75</v>
       </c>
       <c r="K5">
-        <v>-1.03</v>
+        <v>0.5</v>
       </c>
       <c r="L5">
-        <v>-6.71</v>
+        <v>-6.63</v>
       </c>
       <c r="M5">
-        <v>33.93</v>
+        <v>33.97</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>727.95</v>
+        <v>720.9299999999999</v>
       </c>
       <c r="Q5">
-        <v>739.63</v>
+        <v>736.87</v>
       </c>
       <c r="R5">
-        <v>733.2</v>
+        <v>732.59</v>
       </c>
       <c r="S5">
-        <v>745.6</v>
+        <v>745.1799999999999</v>
       </c>
       <c r="T5">
-        <v>-4.9</v>
+        <v>-5.14</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1336,34 +1357,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.43</v>
+        <v>40.85</v>
       </c>
       <c r="Z5">
-        <v>-2.82</v>
+        <v>-4.61</v>
       </c>
       <c r="AA5">
-        <v>1.79</v>
+        <v>0.51</v>
       </c>
       <c r="AB5">
-        <v>-4.61</v>
+        <v>-5.12</v>
       </c>
       <c r="AC5">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="AD5">
-        <v>21.05</v>
+        <v>10.13</v>
       </c>
       <c r="AE5">
-        <v>20.98</v>
+        <v>20.75</v>
       </c>
       <c r="AF5">
-        <v>-79.18000000000001</v>
+        <v>-73.38</v>
       </c>
       <c r="AG5">
-        <v>770.37</v>
+        <v>768.99</v>
       </c>
       <c r="AH5">
-        <v>708.88</v>
+        <v>704.74</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1372,7 +1393,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>21.22</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1404,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>462.3</v>
+        <v>467.35</v>
       </c>
       <c r="D6">
-        <v>-0.97</v>
+        <v>1.09</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1395,46 +1416,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-22.95</v>
+        <v>-22.11</v>
       </c>
       <c r="H6">
-        <v>5.41</v>
+        <v>6.56</v>
       </c>
       <c r="I6">
-        <v>-4.68</v>
+        <v>-4.97</v>
       </c>
       <c r="J6">
-        <v>-12.19</v>
+        <v>-12.61</v>
       </c>
       <c r="K6">
-        <v>-16.47</v>
+        <v>-15.59</v>
       </c>
       <c r="L6">
-        <v>-14.26</v>
+        <v>-14.43</v>
       </c>
       <c r="M6">
-        <v>4.05</v>
+        <v>4.77</v>
       </c>
       <c r="N6">
         <v>12</v>
       </c>
       <c r="O6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P6">
-        <v>480.26</v>
+        <v>475.37</v>
       </c>
       <c r="Q6">
-        <v>502.72</v>
+        <v>499.56</v>
       </c>
       <c r="R6">
-        <v>529.95</v>
+        <v>528.42</v>
       </c>
       <c r="S6">
-        <v>523.7</v>
+        <v>523.65</v>
       </c>
       <c r="T6">
-        <v>-11.72</v>
+        <v>-10.75</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1449,34 +1470,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>27.41</v>
+        <v>30.98</v>
       </c>
       <c r="Z6">
-        <v>-15.86</v>
+        <v>-16.46</v>
       </c>
       <c r="AA6">
-        <v>-12.64</v>
+        <v>-13.4</v>
       </c>
       <c r="AB6">
-        <v>-3.22</v>
+        <v>-3.06</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.04</v>
       </c>
       <c r="AD6">
-        <v>21.65</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>12.6</v>
+        <v>12.46</v>
       </c>
       <c r="AF6">
-        <v>-41.77</v>
+        <v>-8.52</v>
       </c>
       <c r="AG6">
-        <v>540.13</v>
+        <v>537.76</v>
       </c>
       <c r="AH6">
-        <v>465.3</v>
+        <v>461.36</v>
       </c>
       <c r="AI6">
         <v>502.76</v>
@@ -1485,7 +1506,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>37.62</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1496,10 +1517,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11346</v>
+        <v>11314</v>
       </c>
       <c r="D7">
-        <v>1.68</v>
+        <v>-0.28</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1508,46 +1529,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.81</v>
+        <v>-48.96</v>
       </c>
       <c r="H7">
-        <v>6.49</v>
+        <v>6.18</v>
       </c>
       <c r="I7">
-        <v>0.78</v>
+        <v>-0.32</v>
       </c>
       <c r="J7">
-        <v>-1.05</v>
+        <v>-0.26</v>
       </c>
       <c r="K7">
-        <v>0.87</v>
+        <v>-0.93</v>
       </c>
       <c r="L7">
-        <v>-29.79</v>
+        <v>-29.01</v>
       </c>
       <c r="M7">
-        <v>19.49</v>
+        <v>19.27</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>11287.8</v>
+        <v>11280.6</v>
       </c>
       <c r="Q7">
-        <v>11211.35</v>
+        <v>11204.85</v>
       </c>
       <c r="R7">
-        <v>11476.8</v>
+        <v>11479.16</v>
       </c>
       <c r="S7">
-        <v>13754.5</v>
+        <v>13708.16</v>
       </c>
       <c r="T7">
-        <v>-17.51</v>
+        <v>-17.47</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1562,34 +1583,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>51.34</v>
+        <v>50.4</v>
       </c>
       <c r="Z7">
-        <v>-45.85</v>
+        <v>-37.33</v>
       </c>
       <c r="AA7">
-        <v>-73.95999999999999</v>
+        <v>-66.63</v>
       </c>
       <c r="AB7">
-        <v>28.1</v>
+        <v>29.3</v>
       </c>
       <c r="AC7">
-        <v>74.75</v>
+        <v>78.92</v>
       </c>
       <c r="AD7">
-        <v>78.97</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="AE7">
-        <v>314.5</v>
+        <v>309.17</v>
       </c>
       <c r="AF7">
-        <v>426.61</v>
+        <v>-87.62</v>
       </c>
       <c r="AG7">
-        <v>11521.11</v>
+        <v>11499.13</v>
       </c>
       <c r="AH7">
-        <v>10901.59</v>
+        <v>10910.57</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1598,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>12.5</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1609,10 +1630,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>338.75</v>
+        <v>339.35</v>
       </c>
       <c r="D8">
-        <v>1.5</v>
+        <v>0.18</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1621,46 +1642,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.85</v>
+        <v>-7.68</v>
       </c>
       <c r="H8">
-        <v>44.57</v>
+        <v>44.83</v>
       </c>
       <c r="I8">
-        <v>-5.23</v>
+        <v>-5.58</v>
       </c>
       <c r="J8">
-        <v>2.03</v>
+        <v>-0.6</v>
       </c>
       <c r="K8">
-        <v>2.64</v>
+        <v>-3.37</v>
       </c>
       <c r="L8">
-        <v>9.66</v>
+        <v>10.34</v>
       </c>
       <c r="M8">
-        <v>29.13</v>
+        <v>29.12</v>
       </c>
       <c r="N8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P8">
-        <v>349.77</v>
+        <v>345.76</v>
       </c>
       <c r="Q8">
-        <v>348.86</v>
+        <v>348.7</v>
       </c>
       <c r="R8">
-        <v>340.46</v>
+        <v>340.87</v>
       </c>
       <c r="S8">
-        <v>294.47</v>
+        <v>294.78</v>
       </c>
       <c r="T8">
-        <v>15.04</v>
+        <v>15.12</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1675,34 +1696,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>45.17</v>
+        <v>45.57</v>
       </c>
       <c r="Z8">
-        <v>2.56</v>
+        <v>1.57</v>
       </c>
       <c r="AA8">
-        <v>4.73</v>
+        <v>4.1</v>
       </c>
       <c r="AB8">
-        <v>-2.17</v>
+        <v>-2.53</v>
       </c>
       <c r="AC8">
-        <v>18.17</v>
+        <v>8.68</v>
       </c>
       <c r="AD8">
-        <v>39.01</v>
+        <v>21.79</v>
       </c>
       <c r="AE8">
-        <v>12.31</v>
+        <v>12.17</v>
       </c>
       <c r="AF8">
-        <v>-29.1</v>
+        <v>-56.86</v>
       </c>
       <c r="AG8">
-        <v>375.32</v>
+        <v>375.36</v>
       </c>
       <c r="AH8">
-        <v>322.39</v>
+        <v>322.04</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1711,7 +1732,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>24.8</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1722,10 +1743,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="D9">
-        <v>-0.61</v>
+        <v>0.43</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1734,46 +1755,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-12.9</v>
+        <v>-12.53</v>
       </c>
       <c r="H9">
-        <v>8.220000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="I9">
-        <v>-5.27</v>
+        <v>-5.04</v>
       </c>
       <c r="J9">
-        <v>-9.970000000000001</v>
+        <v>-10.46</v>
       </c>
       <c r="K9">
-        <v>-6.21</v>
+        <v>-5.2</v>
       </c>
       <c r="L9">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
-        <v>12.71</v>
+        <v>12.74</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P9">
-        <v>1213.62</v>
+        <v>1201.16</v>
       </c>
       <c r="Q9">
-        <v>1252.53</v>
+        <v>1245.98</v>
       </c>
       <c r="R9">
-        <v>1281.51</v>
+        <v>1279.55</v>
       </c>
       <c r="S9">
-        <v>1240.53</v>
+        <v>1240.92</v>
       </c>
       <c r="T9">
-        <v>-5.85</v>
+        <v>-5.47</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1788,43 +1809,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>31.03</v>
+        <v>32.49</v>
       </c>
       <c r="Z9">
-        <v>-22.79</v>
+        <v>-25.81</v>
       </c>
       <c r="AA9">
-        <v>-13.21</v>
+        <v>-15.73</v>
       </c>
       <c r="AB9">
-        <v>-9.58</v>
+        <v>-10.08</v>
       </c>
       <c r="AC9">
-        <v>3.64</v>
+        <v>2.18</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>9.17</v>
       </c>
       <c r="AE9">
-        <v>28.94</v>
+        <v>28.59</v>
       </c>
       <c r="AF9">
-        <v>-31.75</v>
+        <v>-38.27</v>
       </c>
       <c r="AG9">
-        <v>1321.1</v>
+        <v>1318.75</v>
       </c>
       <c r="AH9">
-        <v>1183.97</v>
+        <v>1173.22</v>
       </c>
       <c r="AI9">
-        <v>1264.48</v>
+        <v>1261.37</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>35.39</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1835,10 +1856,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D10">
-        <v>0.18</v>
+        <v>3.01</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1847,46 +1868,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-16.57</v>
+        <v>-14.05</v>
       </c>
       <c r="H10">
-        <v>111.47</v>
+        <v>117.85</v>
       </c>
       <c r="I10">
-        <v>-2.6</v>
+        <v>4.56</v>
       </c>
       <c r="J10">
-        <v>-9.300000000000001</v>
+        <v>-6.27</v>
       </c>
       <c r="K10">
-        <v>49.87</v>
+        <v>48.44</v>
       </c>
       <c r="L10">
-        <v>-7.59</v>
+        <v>-5</v>
       </c>
       <c r="M10">
-        <v>-4.7</v>
+        <v>-4.1</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P10">
-        <v>76.47</v>
+        <v>77.16</v>
       </c>
       <c r="Q10">
-        <v>79.03</v>
+        <v>78.69</v>
       </c>
       <c r="R10">
-        <v>81.08</v>
+        <v>81.31</v>
       </c>
       <c r="S10">
-        <v>61.78</v>
+        <v>61.89</v>
       </c>
       <c r="T10">
-        <v>23.5</v>
+        <v>27.01</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1901,34 +1922,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>45.07</v>
+        <v>50.09</v>
       </c>
       <c r="Z10">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="AA10">
-        <v>-0.62</v>
+        <v>-0.66</v>
       </c>
       <c r="AB10">
-        <v>-0.37</v>
+        <v>-0.17</v>
       </c>
       <c r="AC10">
-        <v>50.85</v>
+        <v>59.95</v>
       </c>
       <c r="AD10">
-        <v>52.65</v>
+        <v>55.74</v>
       </c>
       <c r="AE10">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="AF10">
-        <v>-35.25</v>
+        <v>82.3</v>
       </c>
       <c r="AG10">
-        <v>85.25</v>
+        <v>84.12</v>
       </c>
       <c r="AH10">
-        <v>72.81999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1937,7 +1958,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>40.87</v>
+        <v>37.1</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2118,7 +2139,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2136,1294 +2157,1405 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-5.41</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-4.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-12.35</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-9.82</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-10.53</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-11.69</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-4.02</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-9.75</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-5.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-12.19</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-12.61</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-1.05</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>2.03</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-10.46</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-6.27</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.06</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2.22</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-7.61</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-7.73</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-3.23</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-4.73</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-4.68</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.97</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-0.32</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-5.23</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-5.58</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-5.27</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-5.04</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-2.6</v>
+      </c>
+      <c r="D27" s="7">
+        <v>4.56</v>
+      </c>
+      <c r="E27" s="8">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>15.38</v>
+      </c>
+      <c r="D28" s="7">
+        <v>15.23</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>33.46</v>
+      </c>
+      <c r="D29" s="7">
+        <v>40.29</v>
+      </c>
+      <c r="E29" s="8">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-2.05</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-6.71</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-6.63</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-14.26</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-14.43</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.79</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-29.01</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>9.66</v>
+      </c>
+      <c r="D34" s="7">
+        <v>10.34</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-7.59</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-6.21</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-2.25</v>
+      </c>
+      <c r="D38" s="7">
+        <v>4.65</v>
+      </c>
+      <c r="E38" s="8">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-3.29</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-1.58</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-1.03</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-16.47</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-15.59</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-0.93</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>2.64</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-3.37</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-6.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-6.21</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-5.2</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>49.87</v>
+      </c>
+      <c r="D45" s="7">
+        <v>48.44</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-35.81</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-36</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-15.09</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-11.46</v>
+      </c>
+      <c r="E47" s="8">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-21.11</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-21.44</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-17.99</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-18.24</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-22.95</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-22.11</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-48.81</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-48.96</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-7.85</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-7.68</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-12.9</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-12.53</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-16.57</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-14.05</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>646.8</v>
+      </c>
+      <c r="D55" s="7">
+        <v>644.9</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>269.6</v>
+      </c>
+      <c r="D56" s="7">
+        <v>281.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1016.7</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1012.5</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>709.05</v>
+      </c>
+      <c r="D58" s="7">
+        <v>706.9</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>462.3</v>
+      </c>
+      <c r="D59" s="7">
+        <v>467.35</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>11346</v>
+      </c>
+      <c r="D60" s="7">
+        <v>11314</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>338.75</v>
+      </c>
+      <c r="D61" s="7">
+        <v>339.35</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1168</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1173</v>
+      </c>
+      <c r="E62" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>76.3</v>
+      </c>
+      <c r="D63" s="7">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D64" s="7">
+        <v>77</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>34</v>
+      </c>
+      <c r="D65" s="7">
+        <v>45</v>
+      </c>
+      <c r="E65" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>55</v>
+      </c>
+      <c r="D66" s="7">
+        <v>34</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>77</v>
+      </c>
+      <c r="D67" s="7">
+        <v>66</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="7">
+        <v>45</v>
+      </c>
+      <c r="D68" s="7">
+        <v>55</v>
+      </c>
+      <c r="E68" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-9.16</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E7" s="7">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>42.28</v>
+      </c>
+      <c r="D69" s="7">
+        <v>41.81</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-12.71</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-12.35</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>39.91</v>
+      </c>
+      <c r="D70" s="7">
+        <v>48.49</v>
+      </c>
+      <c r="E70" s="8">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-10.53</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>29.41</v>
+      </c>
+      <c r="D71" s="7">
+        <v>28.86</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>41.43</v>
+      </c>
+      <c r="D72" s="7">
+        <v>40.85</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-11.92</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-12.19</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>27.41</v>
+      </c>
+      <c r="D73" s="7">
+        <v>30.98</v>
+      </c>
+      <c r="E73" s="8">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>51.34</v>
+      </c>
+      <c r="D74" s="7">
+        <v>50.4</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.03</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>45.17</v>
+      </c>
+      <c r="D75" s="7">
+        <v>45.57</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-9.74</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>31.03</v>
+      </c>
+      <c r="D76" s="7">
+        <v>32.49</v>
+      </c>
+      <c r="E76" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="7">
+        <v>45.07</v>
+      </c>
+      <c r="D77" s="7">
+        <v>50.09</v>
+      </c>
+      <c r="E77" s="8">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.06</v>
-      </c>
-      <c r="E16" s="7">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-83.79000000000001</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-91.16</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-7.37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.7</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-20.48</v>
+      </c>
+      <c r="D79" s="7">
+        <v>11.95</v>
+      </c>
+      <c r="E79" s="8">
+        <v>32.43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-11.01</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>41.58</v>
+      </c>
+      <c r="D80" s="7">
+        <v>24.22</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-17.36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-5.59</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-79.18000000000001</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-73.38</v>
+      </c>
+      <c r="E81" s="8">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.63</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4.68</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-41.77</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-8.52</v>
+      </c>
+      <c r="E82" s="8">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>426.61</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-87.62</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-514.23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-6.41</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-5.23</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-29.1</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-56.86</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-27.76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-5.27</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B85" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="7">
+        <v>-31.75</v>
+      </c>
+      <c r="D85" s="7">
+        <v>-38.27</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-6.52</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-5.53</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.6</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>11.78</v>
-      </c>
-      <c r="D25" s="6">
-        <v>15.38</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>32.06</v>
-      </c>
-      <c r="D26" s="6">
-        <v>33.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-10.37</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-13.24</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-14.26</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-29.75</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.79</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="D31" s="6">
-        <v>9.66</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-7.59</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-2.25</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-3.29</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-12.48</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-16.47</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="D39" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="D40" s="6">
-        <v>2.64</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>50.39</v>
-      </c>
-      <c r="D42" s="6">
-        <v>49.87</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-36.97</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-35.81</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-15.09</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-21.63</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-21.11</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-18.39</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-17.99</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-22.19</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-22.95</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-49.66</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-48.81</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-7.85</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-12.36</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-12.9</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-16.72</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-16.57</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>635.05</v>
-      </c>
-      <c r="D52" s="6">
-        <v>646.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>270.2</v>
-      </c>
-      <c r="D53" s="6">
-        <v>269.6</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1010</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1016.7</v>
-      </c>
-      <c r="E54" s="7">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>705.6</v>
-      </c>
-      <c r="D55" s="6">
-        <v>709.05</v>
-      </c>
-      <c r="E55" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>466.85</v>
-      </c>
-      <c r="D56" s="6">
-        <v>462.3</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>11158</v>
-      </c>
-      <c r="D57" s="6">
-        <v>11346</v>
-      </c>
-      <c r="E57" s="7">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>333.75</v>
-      </c>
-      <c r="D58" s="6">
-        <v>338.75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1175.2</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1168</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-7.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>76.16</v>
-      </c>
-      <c r="D60" s="6">
-        <v>76.3</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>55</v>
-      </c>
-      <c r="E61" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>55</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>38.27</v>
-      </c>
-      <c r="D63" s="6">
-        <v>42.28</v>
-      </c>
-      <c r="E63" s="7">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>40.23</v>
-      </c>
-      <c r="D64" s="6">
-        <v>39.91</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>27.37</v>
-      </c>
-      <c r="D65" s="6">
-        <v>29.41</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>40.15</v>
-      </c>
-      <c r="D66" s="6">
-        <v>41.43</v>
-      </c>
-      <c r="E66" s="7">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>28.65</v>
-      </c>
-      <c r="D67" s="6">
-        <v>27.41</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>45.81</v>
-      </c>
-      <c r="D68" s="6">
-        <v>51.34</v>
-      </c>
-      <c r="E68" s="7">
-        <v>5.53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>41.83</v>
-      </c>
-      <c r="D69" s="6">
-        <v>45.17</v>
-      </c>
-      <c r="E69" s="7">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>31.96</v>
-      </c>
-      <c r="D70" s="6">
-        <v>31.03</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>44.76</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45.07</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-80.86</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-83.79000000000001</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-34.04</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-20.48</v>
-      </c>
-      <c r="E73" s="7">
-        <v>13.56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>134.56</v>
-      </c>
-      <c r="D74" s="6">
-        <v>41.58</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-92.98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-41.84</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-79.18000000000001</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-37.34</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-41.77</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-32.91</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-76.98999999999999</v>
-      </c>
-      <c r="D77" s="6">
-        <v>426.61</v>
-      </c>
-      <c r="E77" s="7">
-        <v>503.6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-29.1</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-28.49</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>161.1</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-31.75</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-192.85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>51.23</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C86" s="7">
         <v>-35.25</v>
       </c>
-      <c r="E80" s="8">
-        <v>-86.48</v>
+      <c r="D86" s="7">
+        <v>82.3</v>
+      </c>
+      <c r="E86" s="8">
+        <v>117.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3443,61 +3575,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>44.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.2</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>41.1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>30</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-7.3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
-        <v>30</v>
+      <c r="I2" s="12">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3598,61 +3730,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3765</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3393</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2913</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2011</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1949</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1271</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0405</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.047</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.08039999999999999</v>
+      <c r="A2" s="15">
+        <v>0.3881</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3397</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2912</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1965</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1927</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1274</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.04769999999999999</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0814</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>27.4 → 31.0</t>
+    <t>28.9 → 34.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.4</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.1 → 50.1</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>34.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -428,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -436,11 +415,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -811,8 +789,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -952,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>644.9</v>
+        <v>643.85</v>
       </c>
       <c r="D2">
-        <v>-0.29</v>
+        <v>-0.16</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -964,46 +942,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36</v>
+        <v>-36.1</v>
       </c>
       <c r="H2">
-        <v>75.63</v>
+        <v>75.34</v>
       </c>
       <c r="I2">
-        <v>0.51</v>
+        <v>-2.2</v>
       </c>
       <c r="J2">
-        <v>-4.56</v>
+        <v>-4.94</v>
       </c>
       <c r="K2">
-        <v>-6.21</v>
+        <v>-4.25</v>
       </c>
       <c r="L2">
-        <v>15.23</v>
+        <v>15.33</v>
       </c>
       <c r="M2">
-        <v>-8.140000000000001</v>
+        <v>-8.01</v>
       </c>
       <c r="N2">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>647.67</v>
+        <v>644.77</v>
       </c>
       <c r="Q2">
-        <v>686.49</v>
+        <v>685.11</v>
       </c>
       <c r="R2">
-        <v>664.64</v>
+        <v>664.85</v>
       </c>
       <c r="S2">
-        <v>644.9400000000001</v>
+        <v>645.67</v>
       </c>
       <c r="T2">
-        <v>-0.01</v>
+        <v>-0.28</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1018,43 +996,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.81</v>
+        <v>41.53</v>
       </c>
       <c r="Z2">
-        <v>-9.24</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AA2">
-        <v>-1.94</v>
+        <v>-3.54</v>
       </c>
       <c r="AB2">
-        <v>-7.3</v>
+        <v>-6.41</v>
       </c>
       <c r="AC2">
-        <v>10.98</v>
+        <v>16.76</v>
       </c>
       <c r="AD2">
-        <v>11.06</v>
+        <v>12.77</v>
       </c>
       <c r="AE2">
-        <v>28.93</v>
+        <v>27.82</v>
       </c>
       <c r="AF2">
-        <v>-91.16</v>
+        <v>-90.23999999999999</v>
       </c>
       <c r="AG2">
-        <v>759.36</v>
+        <v>760.1900000000001</v>
       </c>
       <c r="AH2">
-        <v>613.61</v>
+        <v>610.03</v>
       </c>
       <c r="AI2">
-        <v>732.39</v>
+        <v>725.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.15</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1065,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>281.1</v>
+        <v>283.05</v>
       </c>
       <c r="D3">
-        <v>4.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1077,46 +1055,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-11.46</v>
+        <v>-10.85</v>
       </c>
       <c r="H3">
-        <v>83.45</v>
+        <v>84.72</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>0.23</v>
       </c>
       <c r="J3">
-        <v>-9.82</v>
+        <v>-10.85</v>
       </c>
       <c r="K3">
-        <v>4.65</v>
+        <v>9.35</v>
       </c>
       <c r="L3">
-        <v>40.29</v>
+        <v>41.09</v>
       </c>
       <c r="M3">
-        <v>38.81</v>
+        <v>38.66</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>277.04</v>
+        <v>277.17</v>
       </c>
       <c r="Q3">
-        <v>283.28</v>
+        <v>281.84</v>
       </c>
       <c r="R3">
-        <v>284.99</v>
+        <v>285.51</v>
       </c>
       <c r="S3">
-        <v>230.92</v>
+        <v>231.5</v>
       </c>
       <c r="T3">
-        <v>21.73</v>
+        <v>22.27</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1131,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.49</v>
+        <v>49.8</v>
       </c>
       <c r="Z3">
-        <v>-4.16</v>
+        <v>-3.54</v>
       </c>
       <c r="AA3">
-        <v>-2.98</v>
+        <v>-3.1</v>
       </c>
       <c r="AB3">
-        <v>-1.17</v>
+        <v>-0.44</v>
       </c>
       <c r="AC3">
-        <v>39.14</v>
+        <v>65.77</v>
       </c>
       <c r="AD3">
-        <v>43.75</v>
+        <v>46.8</v>
       </c>
       <c r="AE3">
-        <v>10.67</v>
+        <v>10.51</v>
       </c>
       <c r="AF3">
-        <v>11.95</v>
+        <v>-37.53</v>
       </c>
       <c r="AG3">
-        <v>303.14</v>
+        <v>296.42</v>
       </c>
       <c r="AH3">
-        <v>263.42</v>
+        <v>267.26</v>
       </c>
       <c r="AI3">
         <v>300.1</v>
@@ -1167,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>42.17</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1178,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1012.5</v>
+        <v>1031.7</v>
       </c>
       <c r="D4">
-        <v>-0.41</v>
+        <v>1.9</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1190,46 +1168,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-21.44</v>
+        <v>-19.95</v>
       </c>
       <c r="H4">
-        <v>2.69</v>
+        <v>4.63</v>
       </c>
       <c r="I4">
-        <v>-7.73</v>
+        <v>-4.99</v>
       </c>
       <c r="J4">
-        <v>-11.69</v>
+        <v>-9.26</v>
       </c>
       <c r="K4">
-        <v>-1.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L4">
-        <v>-2.05</v>
+        <v>1.23</v>
       </c>
       <c r="M4">
-        <v>19.65</v>
+        <v>19.32</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P4">
-        <v>1037.22</v>
+        <v>1026.38</v>
       </c>
       <c r="Q4">
-        <v>1106.22</v>
+        <v>1101.78</v>
       </c>
       <c r="R4">
-        <v>1121.38</v>
+        <v>1119.97</v>
       </c>
       <c r="S4">
-        <v>1139.23</v>
+        <v>1139.33</v>
       </c>
       <c r="T4">
-        <v>-11.12</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1244,43 +1222,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.86</v>
+        <v>34.83</v>
       </c>
       <c r="Z4">
-        <v>-26.75</v>
+        <v>-28.1</v>
       </c>
       <c r="AA4">
-        <v>-11.75</v>
+        <v>-15.02</v>
       </c>
       <c r="AB4">
-        <v>-15</v>
+        <v>-13.08</v>
       </c>
       <c r="AC4">
-        <v>3.51</v>
+        <v>10.91</v>
       </c>
       <c r="AD4">
-        <v>1.84</v>
+        <v>5.48</v>
       </c>
       <c r="AE4">
-        <v>34.14</v>
+        <v>33.72</v>
       </c>
       <c r="AF4">
-        <v>24.22</v>
+        <v>-48.23</v>
       </c>
       <c r="AG4">
-        <v>1203.34</v>
+        <v>1204.12</v>
       </c>
       <c r="AH4">
-        <v>1009.09</v>
+        <v>999.4299999999999</v>
       </c>
       <c r="AI4">
-        <v>1119.97</v>
+        <v>1118.75</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>49.41</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1291,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>706.9</v>
+        <v>720.55</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>1.93</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1303,46 +1281,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-18.24</v>
+        <v>-16.66</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I5">
-        <v>-4.73</v>
+        <v>-4.05</v>
       </c>
       <c r="J5">
-        <v>-9.75</v>
+        <v>-5.46</v>
       </c>
       <c r="K5">
-        <v>0.5</v>
+        <v>-0.17</v>
       </c>
       <c r="L5">
-        <v>-6.63</v>
+        <v>-4.27</v>
       </c>
       <c r="M5">
-        <v>33.97</v>
+        <v>33.62</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>720.9299999999999</v>
+        <v>714.85</v>
       </c>
       <c r="Q5">
-        <v>736.87</v>
+        <v>735.09</v>
       </c>
       <c r="R5">
-        <v>732.59</v>
+        <v>732.3</v>
       </c>
       <c r="S5">
-        <v>745.1799999999999</v>
+        <v>744.8</v>
       </c>
       <c r="T5">
-        <v>-5.14</v>
+        <v>-3.26</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1357,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.85</v>
+        <v>46.05</v>
       </c>
       <c r="Z5">
-        <v>-4.61</v>
+        <v>-4.87</v>
       </c>
       <c r="AA5">
-        <v>0.51</v>
+        <v>-0.57</v>
       </c>
       <c r="AB5">
-        <v>-5.12</v>
+        <v>-4.31</v>
       </c>
       <c r="AC5">
-        <v>3.75</v>
+        <v>14.98</v>
       </c>
       <c r="AD5">
-        <v>10.13</v>
+        <v>7.41</v>
       </c>
       <c r="AE5">
-        <v>20.75</v>
+        <v>20.87</v>
       </c>
       <c r="AF5">
-        <v>-73.38</v>
+        <v>-52.96</v>
       </c>
       <c r="AG5">
-        <v>768.99</v>
+        <v>766.66</v>
       </c>
       <c r="AH5">
-        <v>704.74</v>
+        <v>703.52</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1393,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>21.87</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1404,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>467.35</v>
+        <v>460.5</v>
       </c>
       <c r="D6">
-        <v>1.09</v>
+        <v>-1.47</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1416,46 +1394,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-22.11</v>
+        <v>-23.25</v>
       </c>
       <c r="H6">
-        <v>6.56</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-4.97</v>
+        <v>-6.95</v>
       </c>
       <c r="J6">
-        <v>-12.61</v>
+        <v>-13.19</v>
       </c>
       <c r="K6">
-        <v>-15.59</v>
+        <v>-17.36</v>
       </c>
       <c r="L6">
-        <v>-14.43</v>
+        <v>-13.54</v>
       </c>
       <c r="M6">
-        <v>4.77</v>
+        <v>3.45</v>
       </c>
       <c r="N6">
         <v>12</v>
       </c>
       <c r="O6">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P6">
-        <v>475.37</v>
+        <v>468.49</v>
       </c>
       <c r="Q6">
-        <v>499.56</v>
+        <v>496.26</v>
       </c>
       <c r="R6">
-        <v>528.42</v>
+        <v>526.54</v>
       </c>
       <c r="S6">
-        <v>523.65</v>
+        <v>523.53</v>
       </c>
       <c r="T6">
-        <v>-10.75</v>
+        <v>-12.04</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1470,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>30.98</v>
+        <v>28.9</v>
       </c>
       <c r="Z6">
-        <v>-16.46</v>
+        <v>-17.3</v>
       </c>
       <c r="AA6">
-        <v>-13.4</v>
+        <v>-14.18</v>
       </c>
       <c r="AB6">
-        <v>-3.06</v>
+        <v>-3.12</v>
       </c>
       <c r="AC6">
-        <v>7.04</v>
+        <v>9.98</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>8.08</v>
       </c>
       <c r="AE6">
-        <v>12.46</v>
+        <v>12.43</v>
       </c>
       <c r="AF6">
-        <v>-8.52</v>
+        <v>61.55</v>
       </c>
       <c r="AG6">
-        <v>537.76</v>
+        <v>536.04</v>
       </c>
       <c r="AH6">
-        <v>461.36</v>
+        <v>456.49</v>
       </c>
       <c r="AI6">
-        <v>502.76</v>
+        <v>500.78</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>38.31</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11314</v>
+        <v>11320</v>
       </c>
       <c r="D7">
-        <v>-0.28</v>
+        <v>0.05</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1529,46 +1507,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.96</v>
+        <v>-48.93</v>
       </c>
       <c r="H7">
-        <v>6.18</v>
+        <v>6.24</v>
       </c>
       <c r="I7">
-        <v>-0.32</v>
+        <v>0.06</v>
       </c>
       <c r="J7">
-        <v>-0.26</v>
+        <v>-1.08</v>
       </c>
       <c r="K7">
-        <v>-0.93</v>
+        <v>0.96</v>
       </c>
       <c r="L7">
-        <v>-29.01</v>
+        <v>-28.15</v>
       </c>
       <c r="M7">
-        <v>19.27</v>
+        <v>19.07</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P7">
-        <v>11280.6</v>
+        <v>11282</v>
       </c>
       <c r="Q7">
-        <v>11204.85</v>
+        <v>11198.4</v>
       </c>
       <c r="R7">
-        <v>11479.16</v>
+        <v>11480.42</v>
       </c>
       <c r="S7">
-        <v>13708.16</v>
+        <v>13662.56</v>
       </c>
       <c r="T7">
-        <v>-17.47</v>
+        <v>-17.15</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1583,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.4</v>
+        <v>50.58</v>
       </c>
       <c r="Z7">
-        <v>-37.33</v>
+        <v>-29.74</v>
       </c>
       <c r="AA7">
-        <v>-66.63</v>
+        <v>-59.25</v>
       </c>
       <c r="AB7">
-        <v>29.3</v>
+        <v>29.51</v>
       </c>
       <c r="AC7">
-        <v>78.92</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="AD7">
-        <v>75.26000000000001</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="AE7">
-        <v>309.17</v>
+        <v>308.16</v>
       </c>
       <c r="AF7">
-        <v>-87.62</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="AG7">
-        <v>11499.13</v>
+        <v>11475.29</v>
       </c>
       <c r="AH7">
-        <v>10910.57</v>
+        <v>10921.51</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1619,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>13.98</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1630,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>339.35</v>
+        <v>343.3</v>
       </c>
       <c r="D8">
-        <v>0.18</v>
+        <v>1.16</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1642,46 +1620,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.68</v>
+        <v>-6.61</v>
       </c>
       <c r="H8">
-        <v>44.83</v>
+        <v>46.52</v>
       </c>
       <c r="I8">
-        <v>-5.58</v>
+        <v>-5.44</v>
       </c>
       <c r="J8">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="K8">
-        <v>-3.37</v>
+        <v>-1.14</v>
       </c>
       <c r="L8">
-        <v>10.34</v>
+        <v>11.77</v>
       </c>
       <c r="M8">
-        <v>29.12</v>
+        <v>29.58</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O8">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>345.76</v>
+        <v>341.81</v>
       </c>
       <c r="Q8">
-        <v>348.7</v>
+        <v>348.71</v>
       </c>
       <c r="R8">
-        <v>340.87</v>
+        <v>341.49</v>
       </c>
       <c r="S8">
-        <v>294.78</v>
+        <v>295.06</v>
       </c>
       <c r="T8">
-        <v>15.12</v>
+        <v>16.35</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1696,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>45.57</v>
+        <v>48.27</v>
       </c>
       <c r="Z8">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AA8">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB8">
-        <v>-2.53</v>
+        <v>-2.4</v>
       </c>
       <c r="AC8">
-        <v>8.68</v>
+        <v>17.71</v>
       </c>
       <c r="AD8">
-        <v>21.79</v>
+        <v>14.85</v>
       </c>
       <c r="AE8">
-        <v>12.17</v>
+        <v>11.95</v>
       </c>
       <c r="AF8">
-        <v>-56.86</v>
+        <v>-65.83</v>
       </c>
       <c r="AG8">
         <v>375.36</v>
       </c>
       <c r="AH8">
-        <v>322.04</v>
+        <v>322.06</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1732,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>25.21</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1173</v>
+        <v>1176.6</v>
       </c>
       <c r="D9">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1755,46 +1733,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-12.53</v>
+        <v>-12.26</v>
       </c>
       <c r="H9">
-        <v>8.68</v>
+        <v>9.02</v>
       </c>
       <c r="I9">
-        <v>-5.04</v>
+        <v>-6.59</v>
       </c>
       <c r="J9">
-        <v>-10.46</v>
+        <v>-9.77</v>
       </c>
       <c r="K9">
-        <v>-5.2</v>
+        <v>-5.7</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>2.74</v>
       </c>
       <c r="M9">
-        <v>12.74</v>
+        <v>12.56</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="O9">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P9">
-        <v>1201.16</v>
+        <v>1184.56</v>
       </c>
       <c r="Q9">
-        <v>1245.98</v>
+        <v>1241.56</v>
       </c>
       <c r="R9">
-        <v>1279.55</v>
+        <v>1277.69</v>
       </c>
       <c r="S9">
-        <v>1240.92</v>
+        <v>1241.32</v>
       </c>
       <c r="T9">
-        <v>-5.47</v>
+        <v>-5.21</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1809,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>32.49</v>
+        <v>33.58</v>
       </c>
       <c r="Z9">
-        <v>-25.81</v>
+        <v>-27.6</v>
       </c>
       <c r="AA9">
-        <v>-15.73</v>
+        <v>-18.11</v>
       </c>
       <c r="AB9">
-        <v>-10.08</v>
+        <v>-9.5</v>
       </c>
       <c r="AC9">
-        <v>2.18</v>
+        <v>5.99</v>
       </c>
       <c r="AD9">
-        <v>9.17</v>
+        <v>3.94</v>
       </c>
       <c r="AE9">
-        <v>28.59</v>
+        <v>27.55</v>
       </c>
       <c r="AF9">
-        <v>-38.27</v>
+        <v>-50.59</v>
       </c>
       <c r="AG9">
-        <v>1318.75</v>
+        <v>1319.98</v>
       </c>
       <c r="AH9">
-        <v>1173.22</v>
+        <v>1163.15</v>
       </c>
       <c r="AI9">
-        <v>1261.37</v>
+        <v>1254.71</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>39.43</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1856,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>78.59999999999999</v>
+        <v>81.63</v>
       </c>
       <c r="D10">
-        <v>3.01</v>
+        <v>3.85</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1868,46 +1846,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-14.05</v>
+        <v>-10.74</v>
       </c>
       <c r="H10">
-        <v>117.85</v>
+        <v>126.25</v>
       </c>
       <c r="I10">
-        <v>4.56</v>
+        <v>5.14</v>
       </c>
       <c r="J10">
-        <v>-6.27</v>
+        <v>-4.46</v>
       </c>
       <c r="K10">
-        <v>48.44</v>
+        <v>57.28</v>
       </c>
       <c r="L10">
-        <v>-5</v>
+        <v>-1.4</v>
       </c>
       <c r="M10">
-        <v>-4.1</v>
+        <v>-3.45</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>77.16</v>
+        <v>77.95</v>
       </c>
       <c r="Q10">
-        <v>78.69</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="R10">
-        <v>81.31</v>
+        <v>81.61</v>
       </c>
       <c r="S10">
-        <v>61.89</v>
+        <v>62.01</v>
       </c>
       <c r="T10">
-        <v>27.01</v>
+        <v>31.65</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1922,34 +1900,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>50.09</v>
+        <v>55.81</v>
       </c>
       <c r="Z10">
-        <v>-0.83</v>
+        <v>-0.46</v>
       </c>
       <c r="AA10">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="AB10">
-        <v>-0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AC10">
-        <v>59.95</v>
+        <v>77.91</v>
       </c>
       <c r="AD10">
-        <v>55.74</v>
+        <v>62.9</v>
       </c>
       <c r="AE10">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="AF10">
-        <v>82.3</v>
+        <v>44.64</v>
       </c>
       <c r="AG10">
-        <v>84.12</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="AH10">
-        <v>73.26000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1958,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>37.1</v>
+        <v>33.19</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2139,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2157,1021 +2135,1012 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-4.56</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-9.82</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10.85</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-11.69</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-9.26</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-9.75</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.46</v>
+      </c>
+      <c r="E10" s="8">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-12.61</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-13.19</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.08</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-10.46</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.77</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-6.27</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.46</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.2</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2.22</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-7.73</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.97</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-6.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.32</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-5.44</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-6.59</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="D24" s="6">
+        <v>5.14</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>15.23</v>
+      </c>
+      <c r="D25" s="6">
+        <v>15.33</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>40.29</v>
+      </c>
+      <c r="D26" s="6">
+        <v>41.09</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1.23</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-6.63</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-4.27</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-14.43</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-13.54</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-29.01</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-28.15</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>10.34</v>
+      </c>
+      <c r="D31" s="6">
+        <v>11.77</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="D32" s="6">
+        <v>2.74</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-1.4</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-4.25</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>4.65</v>
+      </c>
+      <c r="D35" s="6">
+        <v>9.35</v>
+      </c>
+      <c r="E35" s="8">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.17</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.59</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-17.36</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-0.93</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.37</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-5.2</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>48.44</v>
+      </c>
+      <c r="D42" s="6">
+        <v>57.28</v>
+      </c>
+      <c r="E42" s="8">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-36</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-36.1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-11.46</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-10.85</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-21.44</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-19.95</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-18.24</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-16.66</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-22.11</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-23.25</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-48.96</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-48.93</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-7.68</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-6.61</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-12.53</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-12.26</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-14.05</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-10.74</v>
+      </c>
+      <c r="E51" s="8">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>644.9</v>
+      </c>
+      <c r="D52" s="6">
+        <v>643.85</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>281.1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>283.05</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1012.5</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1031.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>706.9</v>
+      </c>
+      <c r="D55" s="6">
+        <v>720.55</v>
+      </c>
+      <c r="E55" s="8">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>467.35</v>
+      </c>
+      <c r="D56" s="6">
+        <v>460.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>11314</v>
+      </c>
+      <c r="D57" s="6">
+        <v>11320</v>
+      </c>
+      <c r="E57" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>339.35</v>
+      </c>
+      <c r="D58" s="6">
+        <v>343.3</v>
+      </c>
+      <c r="E58" s="8">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1173</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1176.6</v>
+      </c>
+      <c r="E59" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>81.63</v>
+      </c>
+      <c r="E60" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>77</v>
+      </c>
+      <c r="D61" s="6">
         <v>66</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>45</v>
+      </c>
+      <c r="D62" s="6">
+        <v>55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>34</v>
+      </c>
+      <c r="D63" s="6">
+        <v>45</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
         <v>66</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.41</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-4.56</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-12.35</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-9.82</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-10.53</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-11.69</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-4.02</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-9.75</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-5.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-12.19</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-12.61</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.26</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>2.03</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-10.46</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.27</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.06</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-0.26</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2.22</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-7.61</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-7.73</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-4.73</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.97</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.78</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-5.23</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-5.58</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-5.27</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-5.04</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-2.6</v>
-      </c>
-      <c r="D27" s="7">
-        <v>4.56</v>
-      </c>
-      <c r="E27" s="8">
-        <v>7.16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>15.38</v>
-      </c>
-      <c r="D28" s="7">
-        <v>15.23</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>33.46</v>
-      </c>
-      <c r="D29" s="7">
-        <v>40.29</v>
-      </c>
-      <c r="E29" s="8">
-        <v>6.83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-6.71</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-6.63</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-14.26</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-14.43</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.79</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-29.01</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>9.66</v>
-      </c>
-      <c r="D34" s="7">
-        <v>10.34</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-7.59</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-6.21</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-2.25</v>
-      </c>
-      <c r="D38" s="7">
-        <v>4.65</v>
-      </c>
-      <c r="E38" s="8">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-3.29</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-1.58</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-1.03</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-16.47</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-15.59</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>0.87</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-0.93</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>2.64</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-3.37</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-6.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-6.21</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-5.2</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>49.87</v>
-      </c>
-      <c r="D45" s="7">
-        <v>48.44</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-35.81</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-36</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-15.09</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-11.46</v>
-      </c>
-      <c r="E47" s="8">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-21.11</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-21.44</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-17.99</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-18.24</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-22.95</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-22.11</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-48.81</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-48.96</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-7.85</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-7.68</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-12.9</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-12.53</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-16.57</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-14.05</v>
-      </c>
-      <c r="E54" s="8">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>646.8</v>
-      </c>
-      <c r="D55" s="7">
-        <v>644.9</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>269.6</v>
-      </c>
-      <c r="D56" s="7">
-        <v>281.1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1016.7</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1012.5</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>709.05</v>
-      </c>
-      <c r="D58" s="7">
-        <v>706.9</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>462.3</v>
-      </c>
-      <c r="D59" s="7">
-        <v>467.35</v>
-      </c>
-      <c r="E59" s="8">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>11346</v>
-      </c>
-      <c r="D60" s="7">
-        <v>11314</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>338.75</v>
-      </c>
-      <c r="D61" s="7">
-        <v>339.35</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1168</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1173</v>
-      </c>
-      <c r="E62" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>76.3</v>
-      </c>
-      <c r="D63" s="7">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="E63" s="8">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>66</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="D64" s="6">
         <v>77</v>
       </c>
       <c r="E64" s="8">
@@ -3179,383 +3148,332 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6">
+        <v>55</v>
+      </c>
+      <c r="D65" s="6">
+        <v>34</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>41.81</v>
+      </c>
+      <c r="D66" s="6">
+        <v>41.53</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>48.49</v>
+      </c>
+      <c r="D67" s="6">
+        <v>49.8</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>34</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>28.86</v>
+      </c>
+      <c r="D68" s="6">
+        <v>34.83</v>
+      </c>
+      <c r="E68" s="8">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>40.85</v>
+      </c>
+      <c r="D69" s="6">
+        <v>46.05</v>
+      </c>
+      <c r="E69" s="8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>30.98</v>
+      </c>
+      <c r="D70" s="6">
+        <v>28.9</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>50.4</v>
+      </c>
+      <c r="D71" s="6">
+        <v>50.58</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>45.57</v>
+      </c>
+      <c r="D72" s="6">
+        <v>48.27</v>
+      </c>
+      <c r="E72" s="8">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>32.49</v>
+      </c>
+      <c r="D73" s="6">
+        <v>33.58</v>
+      </c>
+      <c r="E73" s="8">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E65" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="6">
+        <v>50.09</v>
+      </c>
+      <c r="D74" s="6">
+        <v>55.81</v>
+      </c>
+      <c r="E74" s="8">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-91.16</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-90.23999999999999</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>11.95</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-37.53</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-49.48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>24.22</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-48.23</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-72.45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>55</v>
-      </c>
-      <c r="D66" s="7">
-        <v>34</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-73.38</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-52.96</v>
+      </c>
+      <c r="E78" s="8">
+        <v>20.42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-8.52</v>
+      </c>
+      <c r="D79" s="6">
+        <v>61.55</v>
+      </c>
+      <c r="E79" s="8">
+        <v>70.06999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-87.62</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-79.90000000000001</v>
+      </c>
+      <c r="E80" s="8">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>77</v>
-      </c>
-      <c r="D67" s="7">
-        <v>66</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-56.86</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-65.83</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-8.970000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="7">
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-38.27</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-50.59</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-12.32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="7">
-        <v>55</v>
-      </c>
-      <c r="E68" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>42.28</v>
-      </c>
-      <c r="D69" s="7">
-        <v>41.81</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>39.91</v>
-      </c>
-      <c r="D70" s="7">
-        <v>48.49</v>
-      </c>
-      <c r="E70" s="8">
-        <v>8.58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>29.41</v>
-      </c>
-      <c r="D71" s="7">
-        <v>28.86</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>41.43</v>
-      </c>
-      <c r="D72" s="7">
-        <v>40.85</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>27.41</v>
-      </c>
-      <c r="D73" s="7">
-        <v>30.98</v>
-      </c>
-      <c r="E73" s="8">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>51.34</v>
-      </c>
-      <c r="D74" s="7">
-        <v>50.4</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>45.17</v>
-      </c>
-      <c r="D75" s="7">
-        <v>45.57</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>31.03</v>
-      </c>
-      <c r="D76" s="7">
-        <v>32.49</v>
-      </c>
-      <c r="E76" s="8">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="7">
-        <v>45.07</v>
-      </c>
-      <c r="D77" s="7">
-        <v>50.09</v>
-      </c>
-      <c r="E77" s="8">
-        <v>5.02</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="7">
-        <v>-83.79000000000001</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-91.16</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-7.37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-20.48</v>
-      </c>
-      <c r="D79" s="7">
-        <v>11.95</v>
-      </c>
-      <c r="E79" s="8">
-        <v>32.43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>41.58</v>
-      </c>
-      <c r="D80" s="7">
-        <v>24.22</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-17.36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-79.18000000000001</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-73.38</v>
-      </c>
-      <c r="E81" s="8">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-41.77</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-8.52</v>
-      </c>
-      <c r="E82" s="8">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>426.61</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-87.62</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-514.23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-29.1</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-56.86</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-27.76</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-31.75</v>
-      </c>
-      <c r="D85" s="7">
-        <v>-38.27</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-6.52</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="7">
-        <v>-35.25</v>
-      </c>
-      <c r="D86" s="7">
+      <c r="C83" s="6">
         <v>82.3</v>
       </c>
-      <c r="E86" s="8">
-        <v>117.55</v>
+      <c r="D83" s="6">
+        <v>44.64</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-37.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3575,60 +3493,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>44.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>41.1</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>43.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="12">
-        <v>-7.3</v>
-      </c>
-      <c r="G2" s="12">
-        <v>2.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -3730,61 +3648,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3881</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3397</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2912</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1965</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1927</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1274</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.04769999999999999</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.04099999999999999</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0814</v>
+      <c r="A2" s="14">
+        <v>0.3865999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3362</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2958</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1932</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1907</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1256</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0345</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0345</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0801</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,12 +169,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -193,19 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>41.5 → 62.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>41.5</t>
+  </si>
+  <si>
+    <t>62.5</t>
+  </si>
+  <si>
+    <t>49.8 → 58.1</t>
+  </si>
+  <si>
+    <t>49.8</t>
+  </si>
+  <si>
+    <t>58.1</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.9 → 34.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>28.9 → 45.9</t>
   </si>
   <si>
     <t>28.9</t>
   </si>
   <si>
-    <t>34.8</t>
+    <t>45.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +438,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,8 +810,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -930,10 +951,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>643.85</v>
+        <v>726.3</v>
       </c>
       <c r="D2">
-        <v>-0.16</v>
+        <v>12.81</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -942,46 +963,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-36.1</v>
+        <v>-27.92</v>
       </c>
       <c r="H2">
-        <v>75.34</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="I2">
-        <v>-2.2</v>
+        <v>11.18</v>
       </c>
       <c r="J2">
-        <v>-4.94</v>
+        <v>8.19</v>
       </c>
       <c r="K2">
-        <v>-4.25</v>
+        <v>7.5</v>
       </c>
       <c r="L2">
-        <v>15.33</v>
+        <v>23.74</v>
       </c>
       <c r="M2">
-        <v>-8.01</v>
+        <v>-6.03</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>644.77</v>
+        <v>659.38</v>
       </c>
       <c r="Q2">
-        <v>685.11</v>
+        <v>684.53</v>
       </c>
       <c r="R2">
-        <v>664.85</v>
+        <v>666.87</v>
       </c>
       <c r="S2">
-        <v>645.67</v>
+        <v>646.86</v>
       </c>
       <c r="T2">
-        <v>-0.28</v>
+        <v>12.28</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -993,46 +1014,46 @@
         <v>47</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>41.53</v>
+        <v>62.5</v>
       </c>
       <c r="Z2">
-        <v>-9.949999999999999</v>
+        <v>-3.82</v>
       </c>
       <c r="AA2">
-        <v>-3.54</v>
+        <v>-3.6</v>
       </c>
       <c r="AB2">
-        <v>-6.41</v>
+        <v>-0.22</v>
       </c>
       <c r="AC2">
-        <v>16.76</v>
+        <v>45.02</v>
       </c>
       <c r="AD2">
-        <v>12.77</v>
+        <v>24.26</v>
       </c>
       <c r="AE2">
-        <v>27.82</v>
+        <v>34.54</v>
       </c>
       <c r="AF2">
-        <v>-90.23999999999999</v>
+        <v>1162.56</v>
       </c>
       <c r="AG2">
-        <v>760.1900000000001</v>
+        <v>758.0599999999999</v>
       </c>
       <c r="AH2">
-        <v>610.03</v>
+        <v>611.01</v>
       </c>
       <c r="AI2">
-        <v>725.3</v>
+        <v>599.79</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.65</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1064,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>283.05</v>
+        <v>297.1</v>
       </c>
       <c r="D3">
-        <v>0.6899999999999999</v>
+        <v>4.96</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1055,46 +1076,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-10.85</v>
+        <v>-6.43</v>
       </c>
       <c r="H3">
-        <v>84.72</v>
+        <v>93.89</v>
       </c>
       <c r="I3">
-        <v>0.23</v>
+        <v>5.39</v>
       </c>
       <c r="J3">
-        <v>-10.85</v>
+        <v>-4.76</v>
       </c>
       <c r="K3">
-        <v>9.35</v>
+        <v>16.26</v>
       </c>
       <c r="L3">
-        <v>41.09</v>
+        <v>47.44</v>
       </c>
       <c r="M3">
-        <v>38.66</v>
+        <v>38.97</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>277.17</v>
+        <v>280.21</v>
       </c>
       <c r="Q3">
-        <v>281.84</v>
+        <v>282.24</v>
       </c>
       <c r="R3">
-        <v>285.51</v>
+        <v>286.27</v>
       </c>
       <c r="S3">
-        <v>231.5</v>
+        <v>232.16</v>
       </c>
       <c r="T3">
-        <v>22.27</v>
+        <v>27.97</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1109,43 +1130,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>49.8</v>
+        <v>58.06</v>
       </c>
       <c r="Z3">
-        <v>-3.54</v>
+        <v>-1.89</v>
       </c>
       <c r="AA3">
-        <v>-3.1</v>
+        <v>-2.85</v>
       </c>
       <c r="AB3">
-        <v>-0.44</v>
+        <v>0.97</v>
       </c>
       <c r="AC3">
-        <v>65.77</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="AD3">
-        <v>46.8</v>
+        <v>66.41</v>
       </c>
       <c r="AE3">
-        <v>10.51</v>
+        <v>10.99</v>
       </c>
       <c r="AF3">
-        <v>-37.53</v>
+        <v>103.49</v>
       </c>
       <c r="AG3">
-        <v>296.42</v>
+        <v>298.06</v>
       </c>
       <c r="AH3">
-        <v>267.26</v>
+        <v>266.43</v>
       </c>
       <c r="AI3">
         <v>300.1</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>38.03</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1177,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1031.7</v>
+        <v>1029.2</v>
       </c>
       <c r="D4">
-        <v>1.9</v>
+        <v>-0.24</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1168,46 +1189,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-19.95</v>
+        <v>-20.14</v>
       </c>
       <c r="H4">
-        <v>4.63</v>
+        <v>4.38</v>
       </c>
       <c r="I4">
-        <v>-4.99</v>
+        <v>-3</v>
       </c>
       <c r="J4">
-        <v>-9.26</v>
+        <v>-8.15</v>
       </c>
       <c r="K4">
-        <v>-0.8100000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="L4">
-        <v>1.23</v>
+        <v>-1.07</v>
       </c>
       <c r="M4">
-        <v>19.32</v>
+        <v>18.51</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>1026.38</v>
+        <v>1020.02</v>
       </c>
       <c r="Q4">
-        <v>1101.78</v>
+        <v>1098.49</v>
       </c>
       <c r="R4">
-        <v>1119.97</v>
+        <v>1118.45</v>
       </c>
       <c r="S4">
-        <v>1139.33</v>
+        <v>1139.48</v>
       </c>
       <c r="T4">
-        <v>-9.449999999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,43 +1243,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.83</v>
+        <v>34.43</v>
       </c>
       <c r="Z4">
-        <v>-28.1</v>
+        <v>-29.04</v>
       </c>
       <c r="AA4">
-        <v>-15.02</v>
+        <v>-17.82</v>
       </c>
       <c r="AB4">
-        <v>-13.08</v>
+        <v>-11.21</v>
       </c>
       <c r="AC4">
-        <v>10.91</v>
+        <v>16.71</v>
       </c>
       <c r="AD4">
-        <v>5.48</v>
+        <v>10.37</v>
       </c>
       <c r="AE4">
-        <v>33.72</v>
+        <v>32.41</v>
       </c>
       <c r="AF4">
-        <v>-48.23</v>
+        <v>-51.25</v>
       </c>
       <c r="AG4">
-        <v>1204.12</v>
+        <v>1205.86</v>
       </c>
       <c r="AH4">
-        <v>999.4299999999999</v>
+        <v>991.11</v>
       </c>
       <c r="AI4">
         <v>1118.75</v>
       </c>
       <c r="AJ4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>51.41</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1290,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>720.55</v>
+        <v>714.05</v>
       </c>
       <c r="D5">
-        <v>1.93</v>
+        <v>-0.9</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1281,46 +1302,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.66</v>
+        <v>-17.41</v>
       </c>
       <c r="H5">
-        <v>8.859999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="I5">
-        <v>-4.05</v>
+        <v>-2.47</v>
       </c>
       <c r="J5">
-        <v>-5.46</v>
+        <v>-5.56</v>
       </c>
       <c r="K5">
-        <v>-0.17</v>
+        <v>-1.41</v>
       </c>
       <c r="L5">
-        <v>-4.27</v>
+        <v>-7.17</v>
       </c>
       <c r="M5">
-        <v>33.62</v>
+        <v>33.38</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>714.85</v>
+        <v>711.23</v>
       </c>
       <c r="Q5">
-        <v>735.09</v>
+        <v>734.61</v>
       </c>
       <c r="R5">
-        <v>732.3</v>
+        <v>731.95</v>
       </c>
       <c r="S5">
-        <v>744.8</v>
+        <v>744.4</v>
       </c>
       <c r="T5">
-        <v>-3.26</v>
+        <v>-4.08</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,43 +1356,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>46.05</v>
+        <v>44.06</v>
       </c>
       <c r="Z5">
-        <v>-4.87</v>
+        <v>-5.54</v>
       </c>
       <c r="AA5">
-        <v>-0.57</v>
+        <v>-1.56</v>
       </c>
       <c r="AB5">
-        <v>-4.31</v>
+        <v>-3.98</v>
       </c>
       <c r="AC5">
-        <v>14.98</v>
+        <v>21.87</v>
       </c>
       <c r="AD5">
-        <v>7.41</v>
+        <v>13.53</v>
       </c>
       <c r="AE5">
-        <v>20.87</v>
+        <v>20.95</v>
       </c>
       <c r="AF5">
-        <v>-52.96</v>
+        <v>-23.56</v>
       </c>
       <c r="AG5">
-        <v>766.66</v>
+        <v>767.1799999999999</v>
       </c>
       <c r="AH5">
-        <v>703.52</v>
+        <v>702.04</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
       </c>
       <c r="AJ5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>22.87</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1403,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>460.5</v>
+        <v>490.3</v>
       </c>
       <c r="D6">
-        <v>-1.47</v>
+        <v>6.47</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1394,46 +1415,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-23.25</v>
+        <v>-18.28</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="I6">
-        <v>-6.95</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>-13.19</v>
+        <v>-6.87</v>
       </c>
       <c r="K6">
-        <v>-17.36</v>
+        <v>-10.84</v>
       </c>
       <c r="L6">
-        <v>-13.54</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M6">
-        <v>3.45</v>
+        <v>5.01</v>
       </c>
       <c r="N6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O6">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>468.49</v>
+        <v>469.46</v>
       </c>
       <c r="Q6">
-        <v>496.26</v>
+        <v>495.53</v>
       </c>
       <c r="R6">
-        <v>526.54</v>
+        <v>524.96</v>
       </c>
       <c r="S6">
-        <v>523.53</v>
+        <v>523.5700000000001</v>
       </c>
       <c r="T6">
-        <v>-12.04</v>
+        <v>-6.35</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,43 +1469,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>28.9</v>
+        <v>45.89</v>
       </c>
       <c r="Z6">
-        <v>-17.3</v>
+        <v>-15.38</v>
       </c>
       <c r="AA6">
-        <v>-14.18</v>
+        <v>-14.42</v>
       </c>
       <c r="AB6">
-        <v>-3.12</v>
+        <v>-0.96</v>
       </c>
       <c r="AC6">
-        <v>9.98</v>
+        <v>43.32</v>
       </c>
       <c r="AD6">
-        <v>8.08</v>
+        <v>20.11</v>
       </c>
       <c r="AE6">
-        <v>12.43</v>
+        <v>13.68</v>
       </c>
       <c r="AF6">
-        <v>61.55</v>
+        <v>358.46</v>
       </c>
       <c r="AG6">
-        <v>536.04</v>
+        <v>535.17</v>
       </c>
       <c r="AH6">
-        <v>456.49</v>
+        <v>455.89</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
       </c>
       <c r="AJ6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK6">
-        <v>39.62</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1516,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11320</v>
+        <v>11324</v>
       </c>
       <c r="D7">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1507,46 +1528,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.93</v>
+        <v>-48.91</v>
       </c>
       <c r="H7">
-        <v>6.24</v>
+        <v>6.28</v>
       </c>
       <c r="I7">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="J7">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="K7">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="L7">
-        <v>-28.15</v>
+        <v>-30.66</v>
       </c>
       <c r="M7">
-        <v>19.07</v>
+        <v>19.24</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O7">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="P7">
-        <v>11282</v>
+        <v>11292.4</v>
       </c>
       <c r="Q7">
-        <v>11198.4</v>
+        <v>11216.25</v>
       </c>
       <c r="R7">
-        <v>11480.42</v>
+        <v>11466.58</v>
       </c>
       <c r="S7">
-        <v>13662.56</v>
+        <v>13617.71</v>
       </c>
       <c r="T7">
-        <v>-17.15</v>
+        <v>-16.84</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,43 +1582,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.58</v>
+        <v>50.71</v>
       </c>
       <c r="Z7">
-        <v>-29.74</v>
+        <v>-23.14</v>
       </c>
       <c r="AA7">
-        <v>-59.25</v>
+        <v>-52.03</v>
       </c>
       <c r="AB7">
-        <v>29.51</v>
+        <v>28.89</v>
       </c>
       <c r="AC7">
-        <v>94.34999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="AD7">
-        <v>82.68000000000001</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="AE7">
-        <v>308.16</v>
+        <v>299.22</v>
       </c>
       <c r="AF7">
-        <v>-79.90000000000001</v>
+        <v>-90.27</v>
       </c>
       <c r="AG7">
-        <v>11475.29</v>
+        <v>11475.81</v>
       </c>
       <c r="AH7">
-        <v>10921.51</v>
+        <v>10956.69</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK7">
-        <v>12.22</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1629,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>343.3</v>
+        <v>341.8</v>
       </c>
       <c r="D8">
-        <v>1.16</v>
+        <v>-0.44</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1620,46 +1641,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-6.61</v>
+        <v>-7.02</v>
       </c>
       <c r="H8">
-        <v>46.52</v>
+        <v>45.88</v>
       </c>
       <c r="I8">
-        <v>-5.44</v>
+        <v>-3.42</v>
       </c>
       <c r="J8">
-        <v>0.25</v>
+        <v>-0.39</v>
       </c>
       <c r="K8">
-        <v>-1.14</v>
+        <v>1.32</v>
       </c>
       <c r="L8">
-        <v>11.77</v>
+        <v>11.32</v>
       </c>
       <c r="M8">
-        <v>29.58</v>
+        <v>29.36</v>
       </c>
       <c r="N8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>341.81</v>
+        <v>339.39</v>
       </c>
       <c r="Q8">
-        <v>348.71</v>
+        <v>349.5</v>
       </c>
       <c r="R8">
-        <v>341.49</v>
+        <v>341.74</v>
       </c>
       <c r="S8">
-        <v>295.06</v>
+        <v>295.32</v>
       </c>
       <c r="T8">
-        <v>16.35</v>
+        <v>15.74</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1695,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>48.27</v>
+        <v>47.31</v>
       </c>
       <c r="Z8">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="AA8">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AB8">
-        <v>-2.4</v>
+        <v>-2.33</v>
       </c>
       <c r="AC8">
-        <v>17.71</v>
+        <v>21.9</v>
       </c>
       <c r="AD8">
-        <v>14.85</v>
+        <v>16.1</v>
       </c>
       <c r="AE8">
-        <v>11.95</v>
+        <v>11.76</v>
       </c>
       <c r="AF8">
-        <v>-65.83</v>
+        <v>-61.81</v>
       </c>
       <c r="AG8">
-        <v>375.36</v>
+        <v>374.16</v>
       </c>
       <c r="AH8">
-        <v>322.06</v>
+        <v>324.85</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.03</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1742,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1176.6</v>
+        <v>1176.2</v>
       </c>
       <c r="D9">
-        <v>0.31</v>
+        <v>-0.03</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1733,46 +1754,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-12.26</v>
+        <v>-12.29</v>
       </c>
       <c r="H9">
-        <v>9.02</v>
+        <v>8.98</v>
       </c>
       <c r="I9">
-        <v>-6.59</v>
+        <v>-4.37</v>
       </c>
       <c r="J9">
-        <v>-9.77</v>
+        <v>-7.02</v>
       </c>
       <c r="K9">
-        <v>-5.7</v>
+        <v>-4.13</v>
       </c>
       <c r="L9">
-        <v>2.74</v>
+        <v>0.09</v>
       </c>
       <c r="M9">
-        <v>12.56</v>
+        <v>12.17</v>
       </c>
       <c r="N9">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P9">
-        <v>1184.56</v>
+        <v>1173.8</v>
       </c>
       <c r="Q9">
-        <v>1241.56</v>
+        <v>1238.91</v>
       </c>
       <c r="R9">
-        <v>1277.69</v>
+        <v>1275.36</v>
       </c>
       <c r="S9">
-        <v>1241.32</v>
+        <v>1241.74</v>
       </c>
       <c r="T9">
-        <v>-5.21</v>
+        <v>-5.28</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,43 +1808,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>33.58</v>
+        <v>33.52</v>
       </c>
       <c r="Z9">
-        <v>-27.6</v>
+        <v>-28.72</v>
       </c>
       <c r="AA9">
-        <v>-18.11</v>
+        <v>-20.23</v>
       </c>
       <c r="AB9">
-        <v>-9.5</v>
+        <v>-8.49</v>
       </c>
       <c r="AC9">
-        <v>5.99</v>
+        <v>10.79</v>
       </c>
       <c r="AD9">
-        <v>3.94</v>
+        <v>6.32</v>
       </c>
       <c r="AE9">
-        <v>27.55</v>
+        <v>27.47</v>
       </c>
       <c r="AF9">
-        <v>-50.59</v>
+        <v>92.12</v>
       </c>
       <c r="AG9">
-        <v>1319.98</v>
+        <v>1322.5</v>
       </c>
       <c r="AH9">
-        <v>1163.15</v>
+        <v>1155.33</v>
       </c>
       <c r="AI9">
-        <v>1254.71</v>
+        <v>1253.62</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK9">
-        <v>42.93</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1855,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.63</v>
+        <v>83.25</v>
       </c>
       <c r="D10">
-        <v>3.85</v>
+        <v>1.98</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1846,46 +1867,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.74</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="H10">
-        <v>126.25</v>
+        <v>130.74</v>
       </c>
       <c r="I10">
-        <v>5.14</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-4.46</v>
+        <v>-2.89</v>
       </c>
       <c r="K10">
-        <v>57.28</v>
+        <v>63.4</v>
       </c>
       <c r="L10">
-        <v>-1.4</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
-        <v>-3.45</v>
+        <v>-3.02</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P10">
-        <v>77.95</v>
+        <v>79.19</v>
       </c>
       <c r="Q10">
-        <v>78.48999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="R10">
-        <v>81.61</v>
+        <v>81.67</v>
       </c>
       <c r="S10">
-        <v>62.01</v>
+        <v>62.14</v>
       </c>
       <c r="T10">
-        <v>31.65</v>
+        <v>33.96</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1900,43 +1921,43 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>55.81</v>
+        <v>58.55</v>
       </c>
       <c r="Z10">
-        <v>-0.46</v>
+        <v>-0.03</v>
       </c>
       <c r="AA10">
-        <v>-0.62</v>
+        <v>-0.5</v>
       </c>
       <c r="AB10">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="AC10">
-        <v>77.91</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AD10">
-        <v>62.9</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AE10">
-        <v>4.23</v>
+        <v>4.32</v>
       </c>
       <c r="AF10">
-        <v>44.64</v>
+        <v>133.59</v>
       </c>
       <c r="AG10">
-        <v>83.04000000000001</v>
+        <v>83.37</v>
       </c>
       <c r="AH10">
-        <v>73.93000000000001</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
       </c>
       <c r="AJ10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK10">
-        <v>33.19</v>
+        <v>31.76</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2138,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1345 +2156,1402 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-4.56</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-10.85</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.03</v>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.69</v>
+        <v>-4.94</v>
       </c>
       <c r="D9" s="6">
-        <v>-9.26</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.43</v>
+        <v>8.19</v>
+      </c>
+      <c r="E9" s="7">
+        <v>13.13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.75</v>
+        <v>-10.85</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.46</v>
-      </c>
-      <c r="E10" s="8">
-        <v>4.29</v>
+        <v>-4.76</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6.09</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-12.61</v>
+        <v>-9.26</v>
       </c>
       <c r="D11" s="6">
-        <v>-13.19</v>
+        <v>-8.15</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.58</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.26</v>
+        <v>-5.46</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.82</v>
+        <v>-5.56</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.6</v>
+        <v>-13.19</v>
       </c>
       <c r="D13" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.85</v>
+        <v>-6.87</v>
+      </c>
+      <c r="E13" s="7">
+        <v>6.32</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-10.46</v>
+        <v>-1.08</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.77</v>
+        <v>-1.09</v>
       </c>
       <c r="E14" s="8">
-        <v>0.6899999999999999</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.27</v>
+        <v>0.25</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.46</v>
+        <v>-0.39</v>
       </c>
       <c r="E15" s="8">
-        <v>1.81</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>0.51</v>
+        <v>-9.77</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.2</v>
+        <v>-7.02</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.71</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>2.22</v>
+        <v>-4.46</v>
       </c>
       <c r="D17" s="6">
-        <v>0.23</v>
+        <v>-2.89</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.99</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.73</v>
+        <v>-2.2</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.74</v>
+        <v>11.18</v>
+      </c>
+      <c r="E18" s="7">
+        <v>13.38</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.73</v>
+        <v>0.23</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.05</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.68</v>
+        <v>5.39</v>
+      </c>
+      <c r="E19" s="7">
+        <v>5.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.97</v>
+        <v>-4.99</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.95</v>
+        <v>-3</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.98</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.32</v>
+        <v>-4.05</v>
       </c>
       <c r="D21" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.38</v>
+        <v>-2.47</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.58</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.58</v>
+        <v>-6.95</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.14</v>
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>7.95</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-5.04</v>
+        <v>0.06</v>
       </c>
       <c r="D23" s="6">
-        <v>-6.59</v>
+        <v>0.46</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.55</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>4.56</v>
+        <v>-5.44</v>
       </c>
       <c r="D24" s="6">
-        <v>5.14</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.58</v>
+        <v>-3.42</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.02</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>15.23</v>
+        <v>-6.59</v>
       </c>
       <c r="D25" s="6">
-        <v>15.33</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.1</v>
+        <v>-4.37</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>40.29</v>
+        <v>5.14</v>
       </c>
       <c r="D26" s="6">
-        <v>41.09</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.8</v>
+        <v>8</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.86</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-2.05</v>
+        <v>15.33</v>
       </c>
       <c r="D27" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.28</v>
+        <v>23.74</v>
+      </c>
+      <c r="E27" s="7">
+        <v>8.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.63</v>
+        <v>41.09</v>
       </c>
       <c r="D28" s="6">
-        <v>-4.27</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.36</v>
+        <v>47.44</v>
+      </c>
+      <c r="E28" s="7">
+        <v>6.35</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-14.43</v>
+        <v>1.23</v>
       </c>
       <c r="D29" s="6">
-        <v>-13.54</v>
+        <v>-1.07</v>
       </c>
       <c r="E29" s="8">
-        <v>0.89</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-29.01</v>
+        <v>-4.27</v>
       </c>
       <c r="D30" s="6">
-        <v>-28.15</v>
+        <v>-7.17</v>
       </c>
       <c r="E30" s="8">
-        <v>0.86</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>10.34</v>
+        <v>-13.54</v>
       </c>
       <c r="D31" s="6">
-        <v>11.77</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.43</v>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>4.18</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>1.4</v>
+        <v>-28.15</v>
       </c>
       <c r="D32" s="6">
-        <v>2.74</v>
+        <v>-30.66</v>
       </c>
       <c r="E32" s="8">
-        <v>1.34</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-5</v>
+        <v>11.77</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.4</v>
+        <v>11.32</v>
       </c>
       <c r="E33" s="8">
-        <v>3.6</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-6.21</v>
+        <v>2.74</v>
       </c>
       <c r="D34" s="6">
-        <v>-4.25</v>
+        <v>0.09</v>
       </c>
       <c r="E34" s="8">
-        <v>1.96</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>4.65</v>
+        <v>-1.4</v>
       </c>
       <c r="D35" s="6">
-        <v>9.35</v>
-      </c>
-      <c r="E35" s="8">
-        <v>4.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.58</v>
+        <v>-4.25</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.77</v>
+        <v>7.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>11.75</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>0.5</v>
+        <v>9.35</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.17</v>
+        <v>16.26</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.67</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-15.59</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D38" s="6">
-        <v>-17.36</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.77</v>
+        <v>-1.25</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.93</v>
+        <v>-0.17</v>
       </c>
       <c r="D39" s="6">
-        <v>0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="E39" s="8">
-        <v>1.89</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-3.37</v>
+        <v>-17.36</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.23</v>
+        <v>-10.84</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-5.2</v>
+        <v>0.96</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.7</v>
+        <v>1.42</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>48.44</v>
+        <v>-1.14</v>
       </c>
       <c r="D42" s="6">
-        <v>57.28</v>
-      </c>
-      <c r="E42" s="8">
-        <v>8.84</v>
+        <v>1.32</v>
+      </c>
+      <c r="E42" s="7">
+        <v>2.46</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-36</v>
+        <v>-5.7</v>
       </c>
       <c r="D43" s="6">
-        <v>-36.1</v>
+        <v>-4.13</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.1</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.46</v>
+        <v>57.28</v>
       </c>
       <c r="D44" s="6">
-        <v>-10.85</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.61</v>
+        <v>63.4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>6.12</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-21.44</v>
+        <v>-36.1</v>
       </c>
       <c r="D45" s="6">
-        <v>-19.95</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.49</v>
+        <v>-27.92</v>
+      </c>
+      <c r="E45" s="7">
+        <v>8.18</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-18.24</v>
+        <v>-10.85</v>
       </c>
       <c r="D46" s="6">
-        <v>-16.66</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.58</v>
+        <v>-6.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>4.42</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-22.11</v>
+        <v>-19.95</v>
       </c>
       <c r="D47" s="6">
-        <v>-23.25</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.14</v>
+        <v>-20.14</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-48.96</v>
+        <v>-16.66</v>
       </c>
       <c r="D48" s="6">
-        <v>-48.93</v>
+        <v>-17.41</v>
       </c>
       <c r="E48" s="8">
-        <v>0.03</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-7.68</v>
+        <v>-23.25</v>
       </c>
       <c r="D49" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.07</v>
+        <v>-18.28</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4.97</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-12.53</v>
+        <v>-48.93</v>
       </c>
       <c r="D50" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.27</v>
+        <v>-48.91</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-14.05</v>
+        <v>-6.61</v>
       </c>
       <c r="D51" s="6">
-        <v>-10.74</v>
+        <v>-7.02</v>
       </c>
       <c r="E51" s="8">
-        <v>3.31</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>644.9</v>
+        <v>-12.26</v>
       </c>
       <c r="D52" s="6">
-        <v>643.85</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.05</v>
+        <v>-12.29</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6">
-        <v>281.1</v>
+        <v>-10.74</v>
       </c>
       <c r="D53" s="6">
-        <v>283.05</v>
-      </c>
-      <c r="E53" s="8">
-        <v>1.95</v>
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1012.5</v>
+        <v>643.85</v>
       </c>
       <c r="D54" s="6">
-        <v>1031.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>19.2</v>
+        <v>726.3</v>
+      </c>
+      <c r="E54" s="7">
+        <v>82.45</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>706.9</v>
+        <v>283.05</v>
       </c>
       <c r="D55" s="6">
-        <v>720.55</v>
-      </c>
-      <c r="E55" s="8">
-        <v>13.65</v>
+        <v>297.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>14.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>467.35</v>
+        <v>1031.7</v>
       </c>
       <c r="D56" s="6">
-        <v>460.5</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-6.85</v>
+        <v>1029.2</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>11314</v>
+        <v>720.55</v>
       </c>
       <c r="D57" s="6">
-        <v>11320</v>
+        <v>714.05</v>
       </c>
       <c r="E57" s="8">
-        <v>6</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>339.35</v>
+        <v>460.5</v>
       </c>
       <c r="D58" s="6">
-        <v>343.3</v>
-      </c>
-      <c r="E58" s="8">
-        <v>3.95</v>
+        <v>490.3</v>
+      </c>
+      <c r="E58" s="7">
+        <v>29.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1173</v>
+        <v>11320</v>
       </c>
       <c r="D59" s="6">
-        <v>1176.6</v>
-      </c>
-      <c r="E59" s="8">
-        <v>3.6</v>
+        <v>11324</v>
+      </c>
+      <c r="E59" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>78.59999999999999</v>
+        <v>343.3</v>
       </c>
       <c r="D60" s="6">
-        <v>81.63</v>
+        <v>341.8</v>
       </c>
       <c r="E60" s="8">
-        <v>3.03</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>77</v>
+        <v>1176.6</v>
       </c>
       <c r="D61" s="6">
-        <v>66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
+        <v>1176.2</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6">
-        <v>45</v>
+        <v>81.63</v>
       </c>
       <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>10</v>
+        <v>83.25</v>
+      </c>
+      <c r="E62" s="7">
+        <v>1.62</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="8">
+        <v>77</v>
+      </c>
+      <c r="E63" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D64" s="6">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="E64" s="8">
-        <v>11</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="6">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D65" s="6">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E65" s="7">
-        <v>-21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="6">
-        <v>41.81</v>
+        <v>23</v>
       </c>
       <c r="D66" s="6">
-        <v>41.53</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-0.28</v>
+        <v>12</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C67" s="6">
-        <v>48.49</v>
+        <v>77</v>
       </c>
       <c r="D67" s="6">
-        <v>49.8</v>
+        <v>66</v>
       </c>
       <c r="E67" s="8">
-        <v>1.31</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C68" s="6">
-        <v>28.86</v>
+        <v>34</v>
       </c>
       <c r="D68" s="6">
-        <v>34.83</v>
-      </c>
-      <c r="E68" s="8">
-        <v>5.97</v>
+        <v>45</v>
+      </c>
+      <c r="E68" s="7">
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>40.85</v>
+        <v>41.53</v>
       </c>
       <c r="D69" s="6">
-        <v>46.05</v>
-      </c>
-      <c r="E69" s="8">
-        <v>5.2</v>
+        <v>62.5</v>
+      </c>
+      <c r="E69" s="7">
+        <v>20.97</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>30.98</v>
+        <v>49.8</v>
       </c>
       <c r="D70" s="6">
-        <v>28.9</v>
+        <v>58.06</v>
       </c>
       <c r="E70" s="7">
-        <v>-2.08</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>50.4</v>
+        <v>34.83</v>
       </c>
       <c r="D71" s="6">
-        <v>50.58</v>
+        <v>34.43</v>
       </c>
       <c r="E71" s="8">
-        <v>0.18</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>45.57</v>
+        <v>46.05</v>
       </c>
       <c r="D72" s="6">
-        <v>48.27</v>
+        <v>44.06</v>
       </c>
       <c r="E72" s="8">
-        <v>2.7</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>32.49</v>
+        <v>28.9</v>
       </c>
       <c r="D73" s="6">
-        <v>33.58</v>
-      </c>
-      <c r="E73" s="8">
-        <v>1.09</v>
+        <v>45.89</v>
+      </c>
+      <c r="E73" s="7">
+        <v>16.99</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="6">
-        <v>50.09</v>
+        <v>50.58</v>
       </c>
       <c r="D74" s="6">
-        <v>55.81</v>
-      </c>
-      <c r="E74" s="8">
-        <v>5.72</v>
+        <v>50.71</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="6">
-        <v>-91.16</v>
+        <v>48.27</v>
       </c>
       <c r="D75" s="6">
-        <v>-90.23999999999999</v>
+        <v>47.31</v>
       </c>
       <c r="E75" s="8">
-        <v>0.92</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C76" s="6">
-        <v>11.95</v>
+        <v>33.58</v>
       </c>
       <c r="D76" s="6">
-        <v>-37.53</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-49.48</v>
+        <v>33.52</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C77" s="6">
-        <v>24.22</v>
+        <v>55.81</v>
       </c>
       <c r="D77" s="6">
-        <v>-48.23</v>
+        <v>58.55</v>
       </c>
       <c r="E77" s="7">
-        <v>-72.45</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-73.38</v>
+        <v>-90.23999999999999</v>
       </c>
       <c r="D78" s="6">
-        <v>-52.96</v>
-      </c>
-      <c r="E78" s="8">
-        <v>20.42</v>
+        <v>1162.56</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1252.8</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-8.52</v>
+        <v>-37.53</v>
       </c>
       <c r="D79" s="6">
-        <v>61.55</v>
-      </c>
-      <c r="E79" s="8">
-        <v>70.06999999999999</v>
+        <v>103.49</v>
+      </c>
+      <c r="E79" s="7">
+        <v>141.02</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-87.62</v>
+        <v>-48.23</v>
       </c>
       <c r="D80" s="6">
-        <v>-79.90000000000001</v>
+        <v>-51.25</v>
       </c>
       <c r="E80" s="8">
-        <v>7.72</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-56.86</v>
+        <v>-52.96</v>
       </c>
       <c r="D81" s="6">
-        <v>-65.83</v>
+        <v>-23.56</v>
       </c>
       <c r="E81" s="7">
-        <v>-8.970000000000001</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="6">
-        <v>-38.27</v>
+        <v>61.55</v>
       </c>
       <c r="D82" s="6">
-        <v>-50.59</v>
+        <v>358.46</v>
       </c>
       <c r="E82" s="7">
-        <v>-12.32</v>
+        <v>296.91</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C83" s="6">
-        <v>82.3</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="D83" s="6">
+        <v>-90.27</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-10.37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6">
+        <v>-65.83</v>
+      </c>
+      <c r="D84" s="6">
+        <v>-61.81</v>
+      </c>
+      <c r="E84" s="7">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="6">
+        <v>-50.59</v>
+      </c>
+      <c r="D85" s="6">
+        <v>92.12</v>
+      </c>
+      <c r="E85" s="7">
+        <v>142.71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="6">
         <v>44.64</v>
       </c>
-      <c r="E83" s="7">
-        <v>-37.66</v>
+      <c r="D86" s="6">
+        <v>133.59</v>
+      </c>
+      <c r="E86" s="7">
+        <v>88.95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3497,28 +3575,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3526,22 +3604,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>44.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>43.3</v>
+        <v>48.3</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.5</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="11">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3658,10 +3736,10 @@
         <v>43</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>44</v>
@@ -3678,31 +3756,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3865999999999999</v>
+        <v>0.3897</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3362</v>
+        <v>0.3338</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2958</v>
+        <v>0.2936</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1932</v>
+        <v>0.1924</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1907</v>
+        <v>0.1851</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1256</v>
+        <v>0.1217</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0345</v>
+        <v>0.0501</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0345</v>
+        <v>-0.0302</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0801</v>
+        <v>-0.0603</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>41.5 → 62.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>41.5</t>
-  </si>
-  <si>
-    <t>62.5</t>
-  </si>
-  <si>
-    <t>49.8 → 58.1</t>
-  </si>
-  <si>
-    <t>49.8</t>
-  </si>
-  <si>
-    <t>58.1</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.9 → 45.9</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>45.9</t>
+    <t>50.7 → 47.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,8 +798,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -951,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>726.3</v>
+        <v>700.75</v>
       </c>
       <c r="D2">
-        <v>12.81</v>
+        <v>-3.52</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -963,46 +951,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-27.92</v>
+        <v>-30.45</v>
       </c>
       <c r="H2">
-        <v>97.79000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="I2">
-        <v>11.18</v>
+        <v>10.35</v>
       </c>
       <c r="J2">
-        <v>8.19</v>
+        <v>-5.03</v>
       </c>
       <c r="K2">
-        <v>7.5</v>
+        <v>2.85</v>
       </c>
       <c r="L2">
-        <v>23.74</v>
+        <v>21.02</v>
       </c>
       <c r="M2">
-        <v>-6.03</v>
+        <v>-7.28</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>659.38</v>
+        <v>672.52</v>
       </c>
       <c r="Q2">
-        <v>684.53</v>
+        <v>682.45</v>
       </c>
       <c r="R2">
-        <v>666.87</v>
+        <v>668.39</v>
       </c>
       <c r="S2">
-        <v>646.86</v>
+        <v>647.95</v>
       </c>
       <c r="T2">
-        <v>12.28</v>
+        <v>8.15</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1017,43 +1005,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.5</v>
+        <v>55.82</v>
       </c>
       <c r="Z2">
-        <v>-3.82</v>
+        <v>-1.01</v>
       </c>
       <c r="AA2">
-        <v>-3.6</v>
+        <v>-3.08</v>
       </c>
       <c r="AB2">
-        <v>-0.22</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>45.02</v>
+        <v>63.41</v>
       </c>
       <c r="AD2">
-        <v>24.26</v>
+        <v>41.73</v>
       </c>
       <c r="AE2">
-        <v>34.54</v>
+        <v>34.8</v>
       </c>
       <c r="AF2">
-        <v>1162.56</v>
+        <v>107.69</v>
       </c>
       <c r="AG2">
-        <v>758.0599999999999</v>
+        <v>751.28</v>
       </c>
       <c r="AH2">
-        <v>611.01</v>
+        <v>613.62</v>
       </c>
       <c r="AI2">
-        <v>599.79</v>
+        <v>603.87</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.67</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>297.1</v>
+        <v>299.2</v>
       </c>
       <c r="D3">
-        <v>4.96</v>
+        <v>0.71</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1076,46 +1064,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-6.43</v>
+        <v>-5.76</v>
       </c>
       <c r="H3">
-        <v>93.89</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="I3">
-        <v>5.39</v>
+        <v>10.73</v>
       </c>
       <c r="J3">
-        <v>-4.76</v>
+        <v>3.53</v>
       </c>
       <c r="K3">
-        <v>16.26</v>
+        <v>11.62</v>
       </c>
       <c r="L3">
-        <v>47.44</v>
+        <v>46.36</v>
       </c>
       <c r="M3">
-        <v>38.97</v>
+        <v>38.58</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>280.21</v>
+        <v>286.01</v>
       </c>
       <c r="Q3">
-        <v>282.24</v>
+        <v>283.14</v>
       </c>
       <c r="R3">
-        <v>286.27</v>
+        <v>286.96</v>
       </c>
       <c r="S3">
-        <v>232.16</v>
+        <v>232.83</v>
       </c>
       <c r="T3">
-        <v>27.97</v>
+        <v>28.5</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1130,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.06</v>
+        <v>59.15</v>
       </c>
       <c r="Z3">
-        <v>-1.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AA3">
-        <v>-2.85</v>
+        <v>-2.36</v>
       </c>
       <c r="AB3">
-        <v>0.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>94.31999999999999</v>
+        <v>98.98</v>
       </c>
       <c r="AD3">
-        <v>66.41</v>
+        <v>86.36</v>
       </c>
       <c r="AE3">
-        <v>10.99</v>
+        <v>10.94</v>
       </c>
       <c r="AF3">
-        <v>103.49</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="AG3">
-        <v>298.06</v>
+        <v>300.66</v>
       </c>
       <c r="AH3">
-        <v>266.43</v>
+        <v>265.62</v>
       </c>
       <c r="AI3">
         <v>300.1</v>
@@ -1166,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.31</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1029.2</v>
+        <v>1030</v>
       </c>
       <c r="D4">
-        <v>-0.24</v>
+        <v>0.08</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1189,46 +1177,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-20.14</v>
+        <v>-20.08</v>
       </c>
       <c r="H4">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="I4">
-        <v>-3</v>
+        <v>1.98</v>
       </c>
       <c r="J4">
-        <v>-8.15</v>
+        <v>-5.94</v>
       </c>
       <c r="K4">
-        <v>-1.25</v>
+        <v>0.19</v>
       </c>
       <c r="L4">
-        <v>-1.07</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
-        <v>18.51</v>
+        <v>18.27</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>1020.02</v>
+        <v>1024.02</v>
       </c>
       <c r="Q4">
-        <v>1098.49</v>
+        <v>1094.84</v>
       </c>
       <c r="R4">
-        <v>1118.45</v>
+        <v>1116.57</v>
       </c>
       <c r="S4">
-        <v>1139.48</v>
+        <v>1139.7</v>
       </c>
       <c r="T4">
-        <v>-9.68</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1243,34 +1231,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.43</v>
+        <v>34.69</v>
       </c>
       <c r="Z4">
-        <v>-29.04</v>
+        <v>-29.38</v>
       </c>
       <c r="AA4">
-        <v>-17.82</v>
+        <v>-20.13</v>
       </c>
       <c r="AB4">
-        <v>-11.21</v>
+        <v>-9.24</v>
       </c>
       <c r="AC4">
-        <v>16.71</v>
+        <v>23.34</v>
       </c>
       <c r="AD4">
-        <v>10.37</v>
+        <v>16.98</v>
       </c>
       <c r="AE4">
-        <v>32.41</v>
+        <v>31.69</v>
       </c>
       <c r="AF4">
-        <v>-51.25</v>
+        <v>-12.3</v>
       </c>
       <c r="AG4">
-        <v>1205.86</v>
+        <v>1206.44</v>
       </c>
       <c r="AH4">
-        <v>991.11</v>
+        <v>983.23</v>
       </c>
       <c r="AI4">
         <v>1118.75</v>
@@ -1279,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>52.33</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>714.05</v>
+        <v>724.65</v>
       </c>
       <c r="D5">
-        <v>-0.9</v>
+        <v>1.48</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1302,46 +1290,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-17.41</v>
+        <v>-16.18</v>
       </c>
       <c r="H5">
-        <v>7.88</v>
+        <v>9.48</v>
       </c>
       <c r="I5">
-        <v>-2.47</v>
+        <v>2.7</v>
       </c>
       <c r="J5">
-        <v>-5.56</v>
+        <v>0.15</v>
       </c>
       <c r="K5">
-        <v>-1.41</v>
+        <v>-1.74</v>
       </c>
       <c r="L5">
-        <v>-7.17</v>
+        <v>-6.1</v>
       </c>
       <c r="M5">
-        <v>33.38</v>
+        <v>31.84</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>711.23</v>
+        <v>715.04</v>
       </c>
       <c r="Q5">
-        <v>734.61</v>
+        <v>734.3</v>
       </c>
       <c r="R5">
-        <v>731.95</v>
+        <v>731.73</v>
       </c>
       <c r="S5">
-        <v>744.4</v>
+        <v>744.0700000000001</v>
       </c>
       <c r="T5">
-        <v>-4.08</v>
+        <v>-2.61</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1356,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.06</v>
+        <v>48.01</v>
       </c>
       <c r="Z5">
-        <v>-5.54</v>
+        <v>-5.16</v>
       </c>
       <c r="AA5">
-        <v>-1.56</v>
+        <v>-2.28</v>
       </c>
       <c r="AB5">
-        <v>-3.98</v>
+        <v>-2.88</v>
       </c>
       <c r="AC5">
-        <v>21.87</v>
+        <v>39.28</v>
       </c>
       <c r="AD5">
-        <v>13.53</v>
+        <v>25.38</v>
       </c>
       <c r="AE5">
         <v>20.95</v>
       </c>
       <c r="AF5">
-        <v>-23.56</v>
+        <v>-43.95</v>
       </c>
       <c r="AG5">
-        <v>767.1799999999999</v>
+        <v>767.14</v>
       </c>
       <c r="AH5">
-        <v>702.04</v>
+        <v>701.47</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1392,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>21.91</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>490.3</v>
+        <v>478.95</v>
       </c>
       <c r="D6">
-        <v>6.47</v>
+        <v>-2.31</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1415,88 +1403,88 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-18.28</v>
+        <v>-20.18</v>
       </c>
       <c r="H6">
-        <v>11.8</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2.59</v>
       </c>
       <c r="J6">
-        <v>-6.87</v>
+        <v>-5.16</v>
       </c>
       <c r="K6">
-        <v>-10.84</v>
+        <v>-11.86</v>
       </c>
       <c r="L6">
-        <v>-9.359999999999999</v>
+        <v>-11.98</v>
       </c>
       <c r="M6">
-        <v>5.01</v>
+        <v>4.64</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P6">
-        <v>469.46</v>
+        <v>471.88</v>
       </c>
       <c r="Q6">
-        <v>495.53</v>
+        <v>494.24</v>
       </c>
       <c r="R6">
-        <v>524.96</v>
+        <v>523.1799999999999</v>
       </c>
       <c r="S6">
         <v>523.5700000000001</v>
       </c>
       <c r="T6">
-        <v>-6.35</v>
+        <v>-8.52</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
       </c>
       <c r="V6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W6" t="s">
         <v>48</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>45.89</v>
+        <v>41.79</v>
       </c>
       <c r="Z6">
-        <v>-15.38</v>
+        <v>-14.61</v>
       </c>
       <c r="AA6">
-        <v>-14.42</v>
+        <v>-14.46</v>
       </c>
       <c r="AB6">
-        <v>-0.96</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>43.32</v>
+        <v>62.23</v>
       </c>
       <c r="AD6">
-        <v>20.11</v>
+        <v>38.51</v>
       </c>
       <c r="AE6">
-        <v>13.68</v>
+        <v>13.71</v>
       </c>
       <c r="AF6">
-        <v>358.46</v>
+        <v>20.76</v>
       </c>
       <c r="AG6">
-        <v>535.17</v>
+        <v>534.3</v>
       </c>
       <c r="AH6">
-        <v>455.89</v>
+        <v>454.18</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
@@ -1505,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>34.37</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11324</v>
+        <v>11222</v>
       </c>
       <c r="D7">
-        <v>0.04</v>
+        <v>-0.9</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1528,46 +1516,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.91</v>
+        <v>-49.37</v>
       </c>
       <c r="H7">
-        <v>6.28</v>
+        <v>5.32</v>
       </c>
       <c r="I7">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="J7">
-        <v>-1.09</v>
+        <v>2.33</v>
       </c>
       <c r="K7">
-        <v>1.42</v>
+        <v>0.22</v>
       </c>
       <c r="L7">
-        <v>-30.66</v>
+        <v>-34.56</v>
       </c>
       <c r="M7">
-        <v>19.24</v>
+        <v>18.87</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P7">
-        <v>11292.4</v>
+        <v>11305.2</v>
       </c>
       <c r="Q7">
-        <v>11216.25</v>
+        <v>11230.6</v>
       </c>
       <c r="R7">
-        <v>11466.58</v>
+        <v>11447.52</v>
       </c>
       <c r="S7">
-        <v>13617.71</v>
+        <v>13576.72</v>
       </c>
       <c r="T7">
-        <v>-16.84</v>
+        <v>-17.34</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1582,34 +1570,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.71</v>
+        <v>47.28</v>
       </c>
       <c r="Z7">
-        <v>-23.14</v>
+        <v>-25.84</v>
       </c>
       <c r="AA7">
-        <v>-52.03</v>
+        <v>-46.79</v>
       </c>
       <c r="AB7">
-        <v>28.89</v>
+        <v>20.95</v>
       </c>
       <c r="AC7">
-        <v>92.27</v>
+        <v>81.92</v>
       </c>
       <c r="AD7">
-        <v>88.51000000000001</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="AE7">
-        <v>299.22</v>
+        <v>291.85</v>
       </c>
       <c r="AF7">
-        <v>-90.27</v>
+        <v>-77.34</v>
       </c>
       <c r="AG7">
-        <v>11475.81</v>
+        <v>11453.89</v>
       </c>
       <c r="AH7">
-        <v>10956.69</v>
+        <v>11007.31</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1618,7 +1606,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>11.11</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>341.8</v>
+        <v>334.65</v>
       </c>
       <c r="D8">
-        <v>-0.44</v>
+        <v>-2.09</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1641,46 +1629,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.02</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H8">
-        <v>45.88</v>
+        <v>42.82</v>
       </c>
       <c r="I8">
-        <v>-3.42</v>
+        <v>0.27</v>
       </c>
       <c r="J8">
-        <v>-0.39</v>
+        <v>2.7</v>
       </c>
       <c r="K8">
-        <v>1.32</v>
+        <v>-1.37</v>
       </c>
       <c r="L8">
-        <v>11.32</v>
+        <v>9.01</v>
       </c>
       <c r="M8">
-        <v>29.36</v>
+        <v>28.43</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P8">
-        <v>339.39</v>
+        <v>339.57</v>
       </c>
       <c r="Q8">
-        <v>349.5</v>
+        <v>349.96</v>
       </c>
       <c r="R8">
-        <v>341.74</v>
+        <v>341.85</v>
       </c>
       <c r="S8">
-        <v>295.32</v>
+        <v>295.57</v>
       </c>
       <c r="T8">
-        <v>15.74</v>
+        <v>13.22</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1695,34 +1683,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>47.31</v>
+        <v>42.93</v>
       </c>
       <c r="Z8">
-        <v>0.59</v>
+        <v>-0.39</v>
       </c>
       <c r="AA8">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="AB8">
-        <v>-2.33</v>
+        <v>-2.64</v>
       </c>
       <c r="AC8">
-        <v>21.9</v>
+        <v>18.98</v>
       </c>
       <c r="AD8">
-        <v>16.1</v>
+        <v>19.53</v>
       </c>
       <c r="AE8">
-        <v>11.76</v>
+        <v>11.67</v>
       </c>
       <c r="AF8">
-        <v>-61.81</v>
+        <v>-44.91</v>
       </c>
       <c r="AG8">
-        <v>374.16</v>
+        <v>373.03</v>
       </c>
       <c r="AH8">
-        <v>324.85</v>
+        <v>326.89</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1731,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>24.98</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1176.2</v>
+        <v>1200.4</v>
       </c>
       <c r="D9">
-        <v>-0.03</v>
+        <v>2.06</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1754,46 +1742,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-12.29</v>
+        <v>-10.48</v>
       </c>
       <c r="H9">
-        <v>8.98</v>
+        <v>11.22</v>
       </c>
       <c r="I9">
-        <v>-4.37</v>
+        <v>2.14</v>
       </c>
       <c r="J9">
-        <v>-7.02</v>
+        <v>-2.34</v>
       </c>
       <c r="K9">
-        <v>-4.13</v>
+        <v>-1.69</v>
       </c>
       <c r="L9">
-        <v>0.09</v>
+        <v>2.79</v>
       </c>
       <c r="M9">
-        <v>12.17</v>
+        <v>11.92</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P9">
-        <v>1173.8</v>
+        <v>1178.84</v>
       </c>
       <c r="Q9">
-        <v>1238.91</v>
+        <v>1236.49</v>
       </c>
       <c r="R9">
-        <v>1275.36</v>
+        <v>1273.37</v>
       </c>
       <c r="S9">
-        <v>1241.74</v>
+        <v>1242.27</v>
       </c>
       <c r="T9">
-        <v>-5.28</v>
+        <v>-3.37</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1808,34 +1796,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>33.52</v>
+        <v>40.93</v>
       </c>
       <c r="Z9">
-        <v>-28.72</v>
+        <v>-27.34</v>
       </c>
       <c r="AA9">
-        <v>-20.23</v>
+        <v>-21.65</v>
       </c>
       <c r="AB9">
-        <v>-8.49</v>
+        <v>-5.69</v>
       </c>
       <c r="AC9">
-        <v>10.79</v>
+        <v>27.74</v>
       </c>
       <c r="AD9">
-        <v>6.32</v>
+        <v>14.84</v>
       </c>
       <c r="AE9">
-        <v>27.47</v>
+        <v>28.39</v>
       </c>
       <c r="AF9">
-        <v>92.12</v>
+        <v>-3.31</v>
       </c>
       <c r="AG9">
-        <v>1322.5</v>
+        <v>1321.66</v>
       </c>
       <c r="AH9">
-        <v>1155.33</v>
+        <v>1151.32</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1844,7 +1832,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>46.35</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>83.25</v>
+        <v>81.47</v>
       </c>
       <c r="D10">
-        <v>1.98</v>
+        <v>-2.14</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1867,46 +1855,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-8.970000000000001</v>
+        <v>-10.91</v>
       </c>
       <c r="H10">
-        <v>130.74</v>
+        <v>125.8</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>6.97</v>
       </c>
       <c r="J10">
-        <v>-2.89</v>
+        <v>-0.39</v>
       </c>
       <c r="K10">
-        <v>63.4</v>
+        <v>61.68</v>
       </c>
       <c r="L10">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="M10">
-        <v>-3.02</v>
+        <v>-3.31</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P10">
-        <v>79.19</v>
+        <v>80.25</v>
       </c>
       <c r="Q10">
-        <v>78.56</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="R10">
-        <v>81.67</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="S10">
-        <v>62.14</v>
+        <v>62.26</v>
       </c>
       <c r="T10">
-        <v>33.96</v>
+        <v>30.85</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1921,34 +1909,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>58.55</v>
+        <v>54.55</v>
       </c>
       <c r="Z10">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AA10">
-        <v>-0.5</v>
+        <v>-0.37</v>
       </c>
       <c r="AB10">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="AC10">
-        <v>95.09999999999999</v>
+        <v>93.36</v>
       </c>
       <c r="AD10">
-        <v>77.65000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="AE10">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="AF10">
-        <v>133.59</v>
+        <v>-53.42</v>
       </c>
       <c r="AG10">
-        <v>83.37</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="AH10">
-        <v>73.73999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1957,7 +1945,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>31.76</v>
+        <v>30.51</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2138,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2158,1400 +2146,1312 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>8.19</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-5.03</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-13.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.94</v>
+        <v>-4.76</v>
       </c>
       <c r="D9" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="E9" s="7">
-        <v>13.13</v>
+        <v>3.53</v>
+      </c>
+      <c r="E9" s="8">
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.85</v>
+        <v>-8.15</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.76</v>
-      </c>
-      <c r="E10" s="7">
-        <v>6.09</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.26</v>
+        <v>-5.56</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.11</v>
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="8">
+        <v>5.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.46</v>
+        <v>-6.87</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.56</v>
+        <v>-5.16</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.1</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-13.19</v>
+        <v>-1.09</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.87</v>
-      </c>
-      <c r="E13" s="7">
-        <v>6.32</v>
+        <v>2.33</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.08</v>
+        <v>-0.39</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.09</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.01</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>0.25</v>
+        <v>-7.02</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.39</v>
+        <v>-2.34</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.64</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-9.77</v>
+        <v>-2.89</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.02</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.75</v>
+        <v>-0.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.46</v>
+        <v>11.18</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.89</v>
+        <v>10.35</v>
       </c>
       <c r="E17" s="7">
-        <v>1.57</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.2</v>
+        <v>5.39</v>
       </c>
       <c r="D18" s="6">
-        <v>11.18</v>
-      </c>
-      <c r="E18" s="7">
-        <v>13.38</v>
+        <v>10.73</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>0.23</v>
+        <v>-3</v>
       </c>
       <c r="D19" s="6">
-        <v>5.39</v>
-      </c>
-      <c r="E19" s="7">
-        <v>5.16</v>
+        <v>1.98</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.98</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.99</v>
+        <v>-2.47</v>
       </c>
       <c r="D20" s="6">
-        <v>-3</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.99</v>
+        <v>2.7</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5.17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.05</v>
+        <v>1</v>
       </c>
       <c r="D21" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.58</v>
+        <v>2.59</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-6.95</v>
+        <v>0.46</v>
       </c>
       <c r="D22" s="6">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7">
-        <v>7.95</v>
+        <v>0.57</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>0.06</v>
+        <v>-3.42</v>
       </c>
       <c r="D23" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.4</v>
+        <v>0.27</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.69</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-5.44</v>
+        <v>-4.37</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.02</v>
+        <v>2.14</v>
+      </c>
+      <c r="E24" s="8">
+        <v>6.51</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-6.59</v>
+        <v>8</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.37</v>
+        <v>6.97</v>
       </c>
       <c r="E25" s="7">
-        <v>2.22</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>5.14</v>
+        <v>23.74</v>
       </c>
       <c r="D26" s="6">
-        <v>8</v>
+        <v>21.02</v>
       </c>
       <c r="E26" s="7">
-        <v>2.86</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>15.33</v>
+        <v>47.44</v>
       </c>
       <c r="D27" s="6">
-        <v>23.74</v>
+        <v>46.36</v>
       </c>
       <c r="E27" s="7">
-        <v>8.41</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>41.09</v>
+        <v>-1.07</v>
       </c>
       <c r="D28" s="6">
-        <v>47.44</v>
-      </c>
-      <c r="E28" s="7">
-        <v>6.35</v>
+        <v>1.46</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.53</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>1.23</v>
+        <v>-7.17</v>
       </c>
       <c r="D29" s="6">
-        <v>-1.07</v>
+        <v>-6.1</v>
       </c>
       <c r="E29" s="8">
-        <v>-2.3</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.27</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.9</v>
+        <v>-11.98</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-13.54</v>
+        <v>-30.66</v>
       </c>
       <c r="D31" s="6">
-        <v>-9.359999999999999</v>
+        <v>-34.56</v>
       </c>
       <c r="E31" s="7">
-        <v>4.18</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.15</v>
+        <v>11.32</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.66</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.51</v>
+        <v>9.01</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>11.77</v>
+        <v>0.09</v>
       </c>
       <c r="D33" s="6">
-        <v>11.32</v>
+        <v>2.79</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.45</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="D34" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.65</v>
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.4</v>
+        <v>7.5</v>
       </c>
       <c r="D35" s="6">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="E35" s="7">
-        <v>2.8</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-4.25</v>
+        <v>16.26</v>
       </c>
       <c r="D36" s="6">
-        <v>7.5</v>
+        <v>11.62</v>
       </c>
       <c r="E36" s="7">
-        <v>11.75</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>9.35</v>
+        <v>-1.25</v>
       </c>
       <c r="D37" s="6">
-        <v>16.26</v>
-      </c>
-      <c r="E37" s="7">
-        <v>6.91</v>
+        <v>0.19</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.44</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.8100000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.44</v>
+        <v>-1.74</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.17</v>
+        <v>-10.84</v>
       </c>
       <c r="D39" s="6">
-        <v>-1.41</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.24</v>
+        <v>-11.86</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-17.36</v>
+        <v>1.42</v>
       </c>
       <c r="D40" s="6">
-        <v>-10.84</v>
+        <v>0.22</v>
       </c>
       <c r="E40" s="7">
-        <v>6.52</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>0.96</v>
+        <v>1.32</v>
       </c>
       <c r="D41" s="6">
-        <v>1.42</v>
+        <v>-1.37</v>
       </c>
       <c r="E41" s="7">
-        <v>0.46</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-1.14</v>
+        <v>-4.13</v>
       </c>
       <c r="D42" s="6">
-        <v>1.32</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.46</v>
+        <v>-1.69</v>
+      </c>
+      <c r="E42" s="8">
+        <v>2.44</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-5.7</v>
+        <v>63.4</v>
       </c>
       <c r="D43" s="6">
-        <v>-4.13</v>
+        <v>61.68</v>
       </c>
       <c r="E43" s="7">
-        <v>1.57</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>57.28</v>
+        <v>-27.92</v>
       </c>
       <c r="D44" s="6">
-        <v>63.4</v>
+        <v>-30.45</v>
       </c>
       <c r="E44" s="7">
-        <v>6.12</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-36.1</v>
+        <v>-6.43</v>
       </c>
       <c r="D45" s="6">
-        <v>-27.92</v>
-      </c>
-      <c r="E45" s="7">
-        <v>8.18</v>
+        <v>-5.76</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-10.85</v>
+        <v>-20.14</v>
       </c>
       <c r="D46" s="6">
-        <v>-6.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>4.42</v>
+        <v>-20.08</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-19.95</v>
+        <v>-17.41</v>
       </c>
       <c r="D47" s="6">
-        <v>-20.14</v>
+        <v>-16.18</v>
       </c>
       <c r="E47" s="8">
-        <v>-0.19</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-16.66</v>
+        <v>-18.28</v>
       </c>
       <c r="D48" s="6">
-        <v>-17.41</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.75</v>
+        <v>-20.18</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-23.25</v>
+        <v>-48.91</v>
       </c>
       <c r="D49" s="6">
-        <v>-18.28</v>
+        <v>-49.37</v>
       </c>
       <c r="E49" s="7">
-        <v>4.97</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-48.93</v>
+        <v>-7.02</v>
       </c>
       <c r="D50" s="6">
-        <v>-48.91</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="E50" s="7">
-        <v>0.02</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-6.61</v>
+        <v>-12.29</v>
       </c>
       <c r="D51" s="6">
-        <v>-7.02</v>
+        <v>-10.48</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.41</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-12.26</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="D52" s="6">
-        <v>-12.29</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.03</v>
+        <v>-10.91</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-10.74</v>
+        <v>726.3</v>
       </c>
       <c r="D53" s="6">
-        <v>-8.970000000000001</v>
+        <v>700.75</v>
       </c>
       <c r="E53" s="7">
-        <v>1.77</v>
+        <v>-25.55</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>643.85</v>
+        <v>297.1</v>
       </c>
       <c r="D54" s="6">
-        <v>726.3</v>
-      </c>
-      <c r="E54" s="7">
-        <v>82.45</v>
+        <v>299.2</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>283.05</v>
+        <v>1029.2</v>
       </c>
       <c r="D55" s="6">
-        <v>297.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>14.05</v>
+        <v>1030</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.8</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1031.7</v>
+        <v>714.05</v>
       </c>
       <c r="D56" s="6">
-        <v>1029.2</v>
+        <v>724.65</v>
       </c>
       <c r="E56" s="8">
-        <v>-2.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>720.55</v>
+        <v>490.3</v>
       </c>
       <c r="D57" s="6">
-        <v>714.05</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-6.5</v>
+        <v>478.95</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>460.5</v>
+        <v>11324</v>
       </c>
       <c r="D58" s="6">
-        <v>490.3</v>
+        <v>11222</v>
       </c>
       <c r="E58" s="7">
-        <v>29.8</v>
+        <v>-102</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>11320</v>
+        <v>341.8</v>
       </c>
       <c r="D59" s="6">
-        <v>11324</v>
+        <v>334.65</v>
       </c>
       <c r="E59" s="7">
-        <v>4</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>343.3</v>
+        <v>1176.2</v>
       </c>
       <c r="D60" s="6">
-        <v>341.8</v>
+        <v>1200.4</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.5</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>1176.6</v>
+        <v>83.25</v>
       </c>
       <c r="D61" s="6">
-        <v>1176.2</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.4</v>
+        <v>81.47</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>55</v>
+      </c>
+      <c r="D62" s="6">
         <v>45</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>81.63</v>
-      </c>
-      <c r="D62" s="6">
-        <v>83.25</v>
-      </c>
       <c r="E62" s="7">
-        <v>1.62</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D63" s="6">
-        <v>77</v>
-      </c>
-      <c r="E63" s="7">
-        <v>11</v>
+        <v>55</v>
+      </c>
+      <c r="E63" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>45</v>
+        <v>62.5</v>
       </c>
       <c r="D64" s="6">
-        <v>34</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11</v>
+        <v>55.82</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-6.68</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>12</v>
+        <v>58.06</v>
       </c>
       <c r="D65" s="6">
-        <v>23</v>
-      </c>
-      <c r="E65" s="7">
-        <v>11</v>
+        <v>59.15</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>23</v>
+        <v>34.43</v>
       </c>
       <c r="D66" s="6">
-        <v>12</v>
+        <v>34.69</v>
       </c>
       <c r="E66" s="8">
-        <v>-11</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>77</v>
+        <v>44.06</v>
       </c>
       <c r="D67" s="6">
-        <v>66</v>
+        <v>48.01</v>
       </c>
       <c r="E67" s="8">
-        <v>-11</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>34</v>
+        <v>45.89</v>
       </c>
       <c r="D68" s="6">
-        <v>45</v>
+        <v>41.79</v>
       </c>
       <c r="E68" s="7">
-        <v>11</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>41.53</v>
+        <v>50.71</v>
       </c>
       <c r="D69" s="6">
-        <v>62.5</v>
+        <v>47.28</v>
       </c>
       <c r="E69" s="7">
-        <v>20.97</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>49.8</v>
+        <v>47.31</v>
       </c>
       <c r="D70" s="6">
-        <v>58.06</v>
+        <v>42.93</v>
       </c>
       <c r="E70" s="7">
-        <v>8.26</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>34.83</v>
+        <v>33.52</v>
       </c>
       <c r="D71" s="6">
-        <v>34.43</v>
+        <v>40.93</v>
       </c>
       <c r="E71" s="8">
-        <v>-0.4</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>46.05</v>
+        <v>58.55</v>
       </c>
       <c r="D72" s="6">
-        <v>44.06</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1.99</v>
+        <v>54.55</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>28.9</v>
+        <v>1162.56</v>
       </c>
       <c r="D73" s="6">
-        <v>45.89</v>
+        <v>107.69</v>
       </c>
       <c r="E73" s="7">
-        <v>16.99</v>
+        <v>-1054.87</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>50.58</v>
+        <v>103.49</v>
       </c>
       <c r="D74" s="6">
-        <v>50.71</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="E74" s="7">
-        <v>0.13</v>
+        <v>-23.42</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>48.27</v>
+        <v>-51.25</v>
       </c>
       <c r="D75" s="6">
-        <v>47.31</v>
+        <v>-12.3</v>
       </c>
       <c r="E75" s="8">
-        <v>-0.96</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>33.58</v>
+        <v>-23.56</v>
       </c>
       <c r="D76" s="6">
-        <v>33.52</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.06</v>
+        <v>-43.95</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-20.39</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>55.81</v>
+        <v>358.46</v>
       </c>
       <c r="D77" s="6">
-        <v>58.55</v>
+        <v>20.76</v>
       </c>
       <c r="E77" s="7">
-        <v>2.74</v>
+        <v>-337.7</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-90.23999999999999</v>
+        <v>-90.27</v>
       </c>
       <c r="D78" s="6">
-        <v>1162.56</v>
-      </c>
-      <c r="E78" s="7">
-        <v>1252.8</v>
+        <v>-77.34</v>
+      </c>
+      <c r="E78" s="8">
+        <v>12.93</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-37.53</v>
+        <v>-61.81</v>
       </c>
       <c r="D79" s="6">
-        <v>103.49</v>
-      </c>
-      <c r="E79" s="7">
-        <v>141.02</v>
+        <v>-44.91</v>
+      </c>
+      <c r="E79" s="8">
+        <v>16.9</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-48.23</v>
+        <v>92.12</v>
       </c>
       <c r="D80" s="6">
-        <v>-51.25</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-3.02</v>
+        <v>-3.31</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-95.43000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-52.96</v>
+        <v>133.59</v>
       </c>
       <c r="D81" s="6">
-        <v>-23.56</v>
+        <v>-53.42</v>
       </c>
       <c r="E81" s="7">
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>61.55</v>
-      </c>
-      <c r="D82" s="6">
-        <v>358.46</v>
-      </c>
-      <c r="E82" s="7">
-        <v>296.91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>-79.90000000000001</v>
-      </c>
-      <c r="D83" s="6">
-        <v>-90.27</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-10.37</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="6">
-        <v>-65.83</v>
-      </c>
-      <c r="D84" s="6">
-        <v>-61.81</v>
-      </c>
-      <c r="E84" s="7">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="6">
-        <v>-50.59</v>
-      </c>
-      <c r="D85" s="6">
-        <v>92.12</v>
-      </c>
-      <c r="E85" s="7">
-        <v>142.71</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="6">
-        <v>44.64</v>
-      </c>
-      <c r="D86" s="6">
-        <v>133.59</v>
-      </c>
-      <c r="E86" s="7">
-        <v>88.95</v>
+        <v>-187.01</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3575,28 +3475,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3610,16 +3510,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>48.3</v>
+        <v>47.2</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G2" s="11">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3756,31 +3656,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3897</v>
+        <v>0.3858</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3338</v>
+        <v>0.3184</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2936</v>
+        <v>0.2843</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1924</v>
+        <v>0.1887</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1851</v>
+        <v>0.1827</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1217</v>
+        <v>0.1192</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0501</v>
+        <v>0.0464</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0302</v>
+        <v>-0.0331</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0603</v>
+        <v>-0.0728</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -196,25 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.7 → 47.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.7</t>
+    <t>48.0 → 52.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>47.3 → 50.6</t>
   </si>
   <si>
     <t>47.3</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>50.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -798,8 +798,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -939,10 +938,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>700.75</v>
+        <v>698.75</v>
       </c>
       <c r="D2">
-        <v>-3.52</v>
+        <v>-0.29</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -951,46 +950,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-30.45</v>
+        <v>-30.65</v>
       </c>
       <c r="H2">
-        <v>90.84</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="I2">
-        <v>10.35</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J2">
-        <v>-5.03</v>
+        <v>-5.88</v>
       </c>
       <c r="K2">
-        <v>2.85</v>
+        <v>6.02</v>
       </c>
       <c r="L2">
-        <v>21.02</v>
+        <v>21.99</v>
       </c>
       <c r="M2">
-        <v>-7.28</v>
+        <v>-7.33</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>672.52</v>
+        <v>682.91</v>
       </c>
       <c r="Q2">
-        <v>682.45</v>
+        <v>681.09</v>
       </c>
       <c r="R2">
-        <v>668.39</v>
+        <v>669.84</v>
       </c>
       <c r="S2">
-        <v>647.95</v>
+        <v>649.04</v>
       </c>
       <c r="T2">
-        <v>8.15</v>
+        <v>7.66</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,34 +1004,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>55.82</v>
+        <v>55.32</v>
       </c>
       <c r="Z2">
-        <v>-1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AA2">
-        <v>-3.08</v>
+        <v>-2.26</v>
       </c>
       <c r="AB2">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="AC2">
-        <v>63.41</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="AD2">
-        <v>41.73</v>
+        <v>63.14</v>
       </c>
       <c r="AE2">
-        <v>34.8</v>
+        <v>34.14</v>
       </c>
       <c r="AF2">
-        <v>107.69</v>
+        <v>-82</v>
       </c>
       <c r="AG2">
-        <v>751.28</v>
+        <v>747.3200000000001</v>
       </c>
       <c r="AH2">
-        <v>613.62</v>
+        <v>614.85</v>
       </c>
       <c r="AI2">
         <v>603.87</v>
@@ -1041,7 +1040,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>36.15</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1051,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>299.2</v>
+        <v>301.55</v>
       </c>
       <c r="D3">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1064,46 +1063,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-5.76</v>
+        <v>-5.02</v>
       </c>
       <c r="H3">
-        <v>95.26000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="I3">
-        <v>10.73</v>
+        <v>11.85</v>
       </c>
       <c r="J3">
-        <v>3.53</v>
+        <v>7.22</v>
       </c>
       <c r="K3">
-        <v>11.62</v>
+        <v>11.91</v>
       </c>
       <c r="L3">
-        <v>46.36</v>
+        <v>48.46</v>
       </c>
       <c r="M3">
-        <v>38.58</v>
+        <v>38.77</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>286.01</v>
+        <v>292.4</v>
       </c>
       <c r="Q3">
-        <v>283.14</v>
+        <v>283.66</v>
       </c>
       <c r="R3">
-        <v>286.96</v>
+        <v>287.68</v>
       </c>
       <c r="S3">
-        <v>232.83</v>
+        <v>233.52</v>
       </c>
       <c r="T3">
-        <v>28.5</v>
+        <v>29.13</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1118,43 +1117,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>59.15</v>
+        <v>60.38</v>
       </c>
       <c r="Z3">
-        <v>-0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA3">
-        <v>-2.36</v>
+        <v>-1.7</v>
       </c>
       <c r="AB3">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="AC3">
-        <v>98.98</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>86.36</v>
+        <v>97.77</v>
       </c>
       <c r="AE3">
-        <v>10.94</v>
+        <v>11.48</v>
       </c>
       <c r="AF3">
-        <v>80.06999999999999</v>
+        <v>147.59</v>
       </c>
       <c r="AG3">
-        <v>300.66</v>
+        <v>302.73</v>
       </c>
       <c r="AH3">
-        <v>265.62</v>
+        <v>264.59</v>
       </c>
       <c r="AI3">
-        <v>300.1</v>
+        <v>268.82</v>
       </c>
       <c r="AJ3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.46</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1164,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1030</v>
+        <v>1045.2</v>
       </c>
       <c r="D4">
-        <v>0.08</v>
+        <v>1.48</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1177,46 +1176,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-20.08</v>
+        <v>-18.9</v>
       </c>
       <c r="H4">
-        <v>4.46</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
-        <v>-5.94</v>
+        <v>-5.24</v>
       </c>
       <c r="K4">
-        <v>0.19</v>
+        <v>1.97</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>3.73</v>
       </c>
       <c r="M4">
-        <v>18.27</v>
+        <v>18.61</v>
       </c>
       <c r="N4">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>1024.02</v>
+        <v>1029.72</v>
       </c>
       <c r="Q4">
-        <v>1094.84</v>
+        <v>1090.68</v>
       </c>
       <c r="R4">
-        <v>1116.57</v>
+        <v>1115.2</v>
       </c>
       <c r="S4">
-        <v>1139.7</v>
+        <v>1139.97</v>
       </c>
       <c r="T4">
-        <v>-9.630000000000001</v>
+        <v>-8.31</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1231,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.69</v>
+        <v>39.62</v>
       </c>
       <c r="Z4">
-        <v>-29.38</v>
+        <v>-28.1</v>
       </c>
       <c r="AA4">
-        <v>-20.13</v>
+        <v>-21.73</v>
       </c>
       <c r="AB4">
-        <v>-9.24</v>
+        <v>-6.37</v>
       </c>
       <c r="AC4">
-        <v>23.34</v>
+        <v>33.42</v>
       </c>
       <c r="AD4">
-        <v>16.98</v>
+        <v>24.49</v>
       </c>
       <c r="AE4">
-        <v>31.69</v>
+        <v>31.27</v>
       </c>
       <c r="AF4">
-        <v>-12.3</v>
+        <v>4.05</v>
       </c>
       <c r="AG4">
-        <v>1206.44</v>
+        <v>1203.21</v>
       </c>
       <c r="AH4">
-        <v>983.23</v>
+        <v>978.14</v>
       </c>
       <c r="AI4">
         <v>1118.75</v>
@@ -1267,7 +1266,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>53.44</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1277,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>724.65</v>
+        <v>736.55</v>
       </c>
       <c r="D5">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1290,46 +1289,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-16.18</v>
+        <v>-14.81</v>
       </c>
       <c r="H5">
-        <v>9.48</v>
+        <v>11.28</v>
       </c>
       <c r="I5">
-        <v>2.7</v>
+        <v>3.88</v>
       </c>
       <c r="J5">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="K5">
-        <v>-1.74</v>
+        <v>-0.13</v>
       </c>
       <c r="L5">
-        <v>-6.1</v>
+        <v>-4.72</v>
       </c>
       <c r="M5">
-        <v>31.84</v>
+        <v>32.25</v>
       </c>
       <c r="N5">
         <v>34</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>715.04</v>
+        <v>720.54</v>
       </c>
       <c r="Q5">
-        <v>734.3</v>
+        <v>734.91</v>
       </c>
       <c r="R5">
-        <v>731.73</v>
+        <v>731.5700000000001</v>
       </c>
       <c r="S5">
-        <v>744.0700000000001</v>
+        <v>743.78</v>
       </c>
       <c r="T5">
-        <v>-2.61</v>
+        <v>-0.97</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1344,34 +1343,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>48.01</v>
+        <v>52.09</v>
       </c>
       <c r="Z5">
-        <v>-5.16</v>
+        <v>-3.85</v>
       </c>
       <c r="AA5">
-        <v>-2.28</v>
+        <v>-2.6</v>
       </c>
       <c r="AB5">
-        <v>-2.88</v>
+        <v>-1.25</v>
       </c>
       <c r="AC5">
-        <v>39.28</v>
+        <v>56.51</v>
       </c>
       <c r="AD5">
-        <v>25.38</v>
+        <v>39.22</v>
       </c>
       <c r="AE5">
-        <v>20.95</v>
+        <v>21.05</v>
       </c>
       <c r="AF5">
-        <v>-43.95</v>
+        <v>-49.98</v>
       </c>
       <c r="AG5">
-        <v>767.14</v>
+        <v>767.42</v>
       </c>
       <c r="AH5">
-        <v>701.47</v>
+        <v>702.39</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1380,7 +1379,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>20.76</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1390,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>478.95</v>
+        <v>482.6</v>
       </c>
       <c r="D6">
-        <v>-2.31</v>
+        <v>0.76</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1403,46 +1402,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-20.18</v>
+        <v>-19.57</v>
       </c>
       <c r="H6">
-        <v>9.210000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="I6">
-        <v>2.59</v>
+        <v>4.39</v>
       </c>
       <c r="J6">
-        <v>-5.16</v>
+        <v>-4.38</v>
       </c>
       <c r="K6">
-        <v>-11.86</v>
+        <v>-10.83</v>
       </c>
       <c r="L6">
-        <v>-11.98</v>
+        <v>-11.06</v>
       </c>
       <c r="M6">
-        <v>4.64</v>
+        <v>4.8</v>
       </c>
       <c r="N6">
         <v>23</v>
       </c>
       <c r="O6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>471.88</v>
+        <v>475.94</v>
       </c>
       <c r="Q6">
-        <v>494.24</v>
+        <v>492.77</v>
       </c>
       <c r="R6">
-        <v>523.1799999999999</v>
+        <v>521.51</v>
       </c>
       <c r="S6">
-        <v>523.5700000000001</v>
+        <v>523.64</v>
       </c>
       <c r="T6">
-        <v>-8.52</v>
+        <v>-7.84</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,34 +1456,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.79</v>
+        <v>43.54</v>
       </c>
       <c r="Z6">
-        <v>-14.61</v>
+        <v>-13.54</v>
       </c>
       <c r="AA6">
-        <v>-14.46</v>
+        <v>-14.28</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>0.73</v>
       </c>
       <c r="AC6">
-        <v>62.23</v>
+        <v>88.37</v>
       </c>
       <c r="AD6">
-        <v>38.51</v>
+        <v>64.64</v>
       </c>
       <c r="AE6">
-        <v>13.71</v>
+        <v>13.7</v>
       </c>
       <c r="AF6">
-        <v>20.76</v>
+        <v>-45.36</v>
       </c>
       <c r="AG6">
-        <v>534.3</v>
+        <v>532.24</v>
       </c>
       <c r="AH6">
-        <v>454.18</v>
+        <v>453.3</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
@@ -1493,7 +1492,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>29.82</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1503,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11222</v>
+        <v>11316</v>
       </c>
       <c r="D7">
-        <v>-0.9</v>
+        <v>0.84</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1516,46 +1515,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.37</v>
+        <v>-48.95</v>
       </c>
       <c r="H7">
-        <v>5.32</v>
+        <v>6.2</v>
       </c>
       <c r="I7">
-        <v>0.57</v>
+        <v>-0.26</v>
       </c>
       <c r="J7">
-        <v>2.33</v>
+        <v>3.48</v>
       </c>
       <c r="K7">
-        <v>0.22</v>
+        <v>3.05</v>
       </c>
       <c r="L7">
-        <v>-34.56</v>
+        <v>-32.75</v>
       </c>
       <c r="M7">
-        <v>18.87</v>
+        <v>19.05</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P7">
-        <v>11305.2</v>
+        <v>11299.2</v>
       </c>
       <c r="Q7">
-        <v>11230.6</v>
+        <v>11239.1</v>
       </c>
       <c r="R7">
-        <v>11447.52</v>
+        <v>11427.3</v>
       </c>
       <c r="S7">
-        <v>13576.72</v>
+        <v>13534.7</v>
       </c>
       <c r="T7">
-        <v>-17.34</v>
+        <v>-16.39</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,34 +1569,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>47.28</v>
+        <v>50.6</v>
       </c>
       <c r="Z7">
-        <v>-25.84</v>
+        <v>-20.17</v>
       </c>
       <c r="AA7">
-        <v>-46.79</v>
+        <v>-41.47</v>
       </c>
       <c r="AB7">
-        <v>20.95</v>
+        <v>21.3</v>
       </c>
       <c r="AC7">
-        <v>81.92</v>
+        <v>81.98</v>
       </c>
       <c r="AD7">
-        <v>89.51000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="AE7">
-        <v>291.85</v>
+        <v>287.5</v>
       </c>
       <c r="AF7">
-        <v>-77.34</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="AG7">
-        <v>11453.89</v>
+        <v>11461.77</v>
       </c>
       <c r="AH7">
-        <v>11007.31</v>
+        <v>11016.43</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1606,7 +1605,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>10.56</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1616,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>334.65</v>
+        <v>340.1</v>
       </c>
       <c r="D8">
-        <v>-2.09</v>
+        <v>1.63</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1629,46 +1628,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-8.960000000000001</v>
+        <v>-7.48</v>
       </c>
       <c r="H8">
-        <v>42.82</v>
+        <v>45.15</v>
       </c>
       <c r="I8">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="J8">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="K8">
-        <v>-1.37</v>
+        <v>-0.6</v>
       </c>
       <c r="L8">
-        <v>9.01</v>
+        <v>11.29</v>
       </c>
       <c r="M8">
-        <v>28.43</v>
+        <v>29.09</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P8">
-        <v>339.57</v>
+        <v>339.84</v>
       </c>
       <c r="Q8">
-        <v>349.96</v>
+        <v>350.63</v>
       </c>
       <c r="R8">
-        <v>341.85</v>
+        <v>341.97</v>
       </c>
       <c r="S8">
-        <v>295.57</v>
+        <v>295.86</v>
       </c>
       <c r="T8">
-        <v>13.22</v>
+        <v>14.95</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1682,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>42.93</v>
+        <v>46.96</v>
       </c>
       <c r="Z8">
-        <v>-0.39</v>
+        <v>-0.71</v>
       </c>
       <c r="AA8">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="AB8">
-        <v>-2.64</v>
+        <v>-2.37</v>
       </c>
       <c r="AC8">
-        <v>18.98</v>
+        <v>18.49</v>
       </c>
       <c r="AD8">
-        <v>19.53</v>
+        <v>19.79</v>
       </c>
       <c r="AE8">
-        <v>11.67</v>
+        <v>11.39</v>
       </c>
       <c r="AF8">
-        <v>-44.91</v>
+        <v>-58.35</v>
       </c>
       <c r="AG8">
-        <v>373.03</v>
+        <v>371.53</v>
       </c>
       <c r="AH8">
-        <v>326.89</v>
+        <v>329.74</v>
       </c>
       <c r="AI8">
         <v>331.1</v>
@@ -1719,7 +1718,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>25.87</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1729,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1200.4</v>
+        <v>1216.3</v>
       </c>
       <c r="D9">
-        <v>2.06</v>
+        <v>1.32</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1742,46 +1741,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-10.48</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H9">
-        <v>11.22</v>
+        <v>12.69</v>
       </c>
       <c r="I9">
-        <v>2.14</v>
+        <v>4.14</v>
       </c>
       <c r="J9">
-        <v>-2.34</v>
+        <v>-2.61</v>
       </c>
       <c r="K9">
-        <v>-1.69</v>
+        <v>-1.7</v>
       </c>
       <c r="L9">
-        <v>2.79</v>
+        <v>4.73</v>
       </c>
       <c r="M9">
-        <v>11.92</v>
+        <v>12.21</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>64</v>
       </c>
       <c r="P9">
-        <v>1178.84</v>
+        <v>1188.5</v>
       </c>
       <c r="Q9">
-        <v>1236.49</v>
+        <v>1234.63</v>
       </c>
       <c r="R9">
-        <v>1273.37</v>
+        <v>1271.1</v>
       </c>
       <c r="S9">
-        <v>1242.27</v>
+        <v>1242.89</v>
       </c>
       <c r="T9">
-        <v>-3.37</v>
+        <v>-2.14</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1796,34 +1795,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>40.93</v>
+        <v>45.25</v>
       </c>
       <c r="Z9">
-        <v>-27.34</v>
+        <v>-24.68</v>
       </c>
       <c r="AA9">
-        <v>-21.65</v>
+        <v>-22.26</v>
       </c>
       <c r="AB9">
-        <v>-5.69</v>
+        <v>-2.42</v>
       </c>
       <c r="AC9">
-        <v>27.74</v>
+        <v>52.66</v>
       </c>
       <c r="AD9">
-        <v>14.84</v>
+        <v>30.4</v>
       </c>
       <c r="AE9">
-        <v>28.39</v>
+        <v>28.98</v>
       </c>
       <c r="AF9">
-        <v>-3.31</v>
+        <v>60.58</v>
       </c>
       <c r="AG9">
-        <v>1321.66</v>
+        <v>1319.87</v>
       </c>
       <c r="AH9">
-        <v>1151.32</v>
+        <v>1149.4</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1832,7 +1831,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>43.52</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1842,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.47</v>
+        <v>80.87</v>
       </c>
       <c r="D10">
-        <v>-2.14</v>
+        <v>-0.74</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1855,46 +1854,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.91</v>
+        <v>-11.57</v>
       </c>
       <c r="H10">
-        <v>125.8</v>
+        <v>124.14</v>
       </c>
       <c r="I10">
-        <v>6.97</v>
+        <v>5.99</v>
       </c>
       <c r="J10">
-        <v>-0.39</v>
+        <v>-1.28</v>
       </c>
       <c r="K10">
-        <v>61.68</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="L10">
-        <v>0.7</v>
+        <v>-0.32</v>
       </c>
       <c r="M10">
-        <v>-3.31</v>
+        <v>-3.45</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="P10">
-        <v>80.25</v>
+        <v>81.16</v>
       </c>
       <c r="Q10">
-        <v>78.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="R10">
-        <v>81.65000000000001</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="S10">
-        <v>62.26</v>
+        <v>62.38</v>
       </c>
       <c r="T10">
-        <v>30.85</v>
+        <v>29.65</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1909,34 +1908,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>54.55</v>
+        <v>53.23</v>
       </c>
       <c r="Z10">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="AA10">
-        <v>-0.37</v>
+        <v>-0.24</v>
       </c>
       <c r="AB10">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AC10">
-        <v>93.36</v>
+        <v>84.52</v>
       </c>
       <c r="AD10">
-        <v>88.79000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="AE10">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="AF10">
-        <v>-53.42</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="AG10">
-        <v>83.29000000000001</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="AH10">
-        <v>73.78</v>
+        <v>73.77</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1945,7 +1944,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>30.51</v>
+        <v>28.7</v>
       </c>
     </row>
   </sheetData>
@@ -2126,7 +2125,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2146,22 +2145,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2198,13 +2197,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>8.19</v>
+        <v>-5.03</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.03</v>
+        <v>-5.88</v>
       </c>
       <c r="E8" s="7">
-        <v>-13.22</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2215,13 +2214,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.76</v>
+        <v>3.53</v>
       </c>
       <c r="D9" s="6">
-        <v>3.53</v>
+        <v>7.22</v>
       </c>
       <c r="E9" s="8">
-        <v>8.289999999999999</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2232,13 +2231,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.15</v>
+        <v>-5.94</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.94</v>
+        <v>-5.24</v>
       </c>
       <c r="E10" s="8">
-        <v>2.21</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2249,13 +2248,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.56</v>
+        <v>0.15</v>
       </c>
       <c r="D11" s="6">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="E11" s="8">
-        <v>5.71</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2266,13 +2265,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.87</v>
+        <v>-5.16</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.16</v>
+        <v>-4.38</v>
       </c>
       <c r="E12" s="8">
-        <v>1.71</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2283,13 +2282,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.09</v>
+        <v>2.33</v>
       </c>
       <c r="D13" s="6">
-        <v>2.33</v>
+        <v>3.48</v>
       </c>
       <c r="E13" s="8">
-        <v>3.42</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2300,13 +2299,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.39</v>
+        <v>2.7</v>
       </c>
       <c r="D14" s="6">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="E14" s="8">
-        <v>3.09</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2317,13 +2316,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.02</v>
+        <v>-2.34</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="E15" s="8">
-        <v>4.68</v>
+        <v>-2.61</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2334,13 +2333,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.89</v>
+        <v>-0.39</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.5</v>
+        <v>-1.28</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2351,13 +2350,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>11.18</v>
+        <v>10.35</v>
       </c>
       <c r="D17" s="6">
-        <v>10.35</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.83</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2368,13 +2367,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>5.39</v>
+        <v>10.73</v>
       </c>
       <c r="D18" s="6">
-        <v>10.73</v>
+        <v>11.85</v>
       </c>
       <c r="E18" s="8">
-        <v>5.34</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2385,13 +2384,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3</v>
+        <v>1.98</v>
       </c>
       <c r="D19" s="6">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="E19" s="8">
-        <v>4.98</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2402,13 +2401,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.47</v>
+        <v>2.7</v>
       </c>
       <c r="D20" s="6">
-        <v>2.7</v>
+        <v>3.88</v>
       </c>
       <c r="E20" s="8">
-        <v>5.17</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2419,13 +2418,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>1</v>
+        <v>2.59</v>
       </c>
       <c r="D21" s="6">
-        <v>2.59</v>
+        <v>4.39</v>
       </c>
       <c r="E21" s="8">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2436,13 +2435,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="D22" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.11</v>
+        <v>-0.26</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2453,13 +2452,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.42</v>
+        <v>0.27</v>
       </c>
       <c r="D23" s="6">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="8">
-        <v>3.69</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2470,13 +2469,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.37</v>
+        <v>2.14</v>
       </c>
       <c r="D24" s="6">
-        <v>2.14</v>
+        <v>4.14</v>
       </c>
       <c r="E24" s="8">
-        <v>6.51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2487,13 +2486,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>8</v>
+        <v>6.97</v>
       </c>
       <c r="D25" s="6">
-        <v>6.97</v>
+        <v>5.99</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.03</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2504,13 +2503,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>23.74</v>
+        <v>21.02</v>
       </c>
       <c r="D26" s="6">
-        <v>21.02</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.72</v>
+        <v>21.99</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2521,13 +2520,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>47.44</v>
+        <v>46.36</v>
       </c>
       <c r="D27" s="6">
-        <v>46.36</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.08</v>
+        <v>48.46</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2538,13 +2537,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.07</v>
+        <v>1.46</v>
       </c>
       <c r="D28" s="6">
-        <v>1.46</v>
+        <v>3.73</v>
       </c>
       <c r="E28" s="8">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2555,13 +2554,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-7.17</v>
+        <v>-6.1</v>
       </c>
       <c r="D29" s="6">
-        <v>-6.1</v>
+        <v>-4.72</v>
       </c>
       <c r="E29" s="8">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2572,13 +2571,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-9.359999999999999</v>
+        <v>-11.98</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.98</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.62</v>
+        <v>-11.06</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.92</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2589,13 +2588,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-30.66</v>
+        <v>-34.56</v>
       </c>
       <c r="D31" s="6">
-        <v>-34.56</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.9</v>
+        <v>-32.75</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.81</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2606,13 +2605,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>11.32</v>
+        <v>9.01</v>
       </c>
       <c r="D32" s="6">
-        <v>9.01</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.31</v>
+        <v>11.29</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.28</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2623,13 +2622,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>0.09</v>
+        <v>2.79</v>
       </c>
       <c r="D33" s="6">
-        <v>2.79</v>
+        <v>4.73</v>
       </c>
       <c r="E33" s="8">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2640,13 +2639,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="D34" s="6">
-        <v>0.7</v>
+        <v>-0.32</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.7</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2657,13 +2656,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>7.5</v>
+        <v>2.85</v>
       </c>
       <c r="D35" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-4.65</v>
+        <v>6.02</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.17</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2674,13 +2673,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>16.26</v>
+        <v>11.62</v>
       </c>
       <c r="D36" s="6">
-        <v>11.62</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-4.64</v>
+        <v>11.91</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2691,13 +2690,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.25</v>
+        <v>0.19</v>
       </c>
       <c r="D37" s="6">
-        <v>0.19</v>
+        <v>1.97</v>
       </c>
       <c r="E37" s="8">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2708,13 +2707,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.41</v>
+        <v>-1.74</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.33</v>
+        <v>-0.13</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2725,13 +2724,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-10.84</v>
+        <v>-11.86</v>
       </c>
       <c r="D39" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.02</v>
+        <v>-10.83</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.03</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2742,13 +2741,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>1.42</v>
+        <v>0.22</v>
       </c>
       <c r="D40" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.2</v>
+        <v>3.05</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.83</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2759,13 +2758,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>1.32</v>
+        <v>-1.37</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.69</v>
+        <v>-0.6</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2776,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-4.13</v>
+        <v>-1.69</v>
       </c>
       <c r="D42" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E42" s="8">
-        <v>2.44</v>
+        <v>-1.7</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2793,13 +2792,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>63.4</v>
+        <v>61.68</v>
       </c>
       <c r="D43" s="6">
-        <v>61.68</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.72</v>
+        <v>65.06999999999999</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3.39</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2810,13 +2809,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-27.92</v>
+        <v>-30.45</v>
       </c>
       <c r="D44" s="6">
-        <v>-30.45</v>
+        <v>-30.65</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.53</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2827,13 +2826,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-6.43</v>
+        <v>-5.76</v>
       </c>
       <c r="D45" s="6">
-        <v>-5.76</v>
+        <v>-5.02</v>
       </c>
       <c r="E45" s="8">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2844,13 +2843,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-20.14</v>
+        <v>-20.08</v>
       </c>
       <c r="D46" s="6">
-        <v>-20.08</v>
+        <v>-18.9</v>
       </c>
       <c r="E46" s="8">
-        <v>0.06</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2861,13 +2860,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-17.41</v>
+        <v>-16.18</v>
       </c>
       <c r="D47" s="6">
-        <v>-16.18</v>
+        <v>-14.81</v>
       </c>
       <c r="E47" s="8">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2878,13 +2877,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-18.28</v>
+        <v>-20.18</v>
       </c>
       <c r="D48" s="6">
-        <v>-20.18</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.9</v>
+        <v>-19.57</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2895,13 +2894,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-48.91</v>
+        <v>-49.37</v>
       </c>
       <c r="D49" s="6">
-        <v>-49.37</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.46</v>
+        <v>-48.95</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2912,13 +2911,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-7.02</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D50" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.94</v>
+        <v>-7.48</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2929,13 +2928,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-12.29</v>
+        <v>-10.48</v>
       </c>
       <c r="D51" s="6">
-        <v>-10.48</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E51" s="8">
-        <v>1.81</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2946,13 +2945,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-8.970000000000001</v>
+        <v>-10.91</v>
       </c>
       <c r="D52" s="6">
-        <v>-10.91</v>
+        <v>-11.57</v>
       </c>
       <c r="E52" s="7">
-        <v>-1.94</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2963,13 +2962,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>726.3</v>
+        <v>700.75</v>
       </c>
       <c r="D53" s="6">
-        <v>700.75</v>
+        <v>698.75</v>
       </c>
       <c r="E53" s="7">
-        <v>-25.55</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2980,13 +2979,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>297.1</v>
+        <v>299.2</v>
       </c>
       <c r="D54" s="6">
-        <v>299.2</v>
+        <v>301.55</v>
       </c>
       <c r="E54" s="8">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2997,13 +2996,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1029.2</v>
+        <v>1030</v>
       </c>
       <c r="D55" s="6">
-        <v>1030</v>
+        <v>1045.2</v>
       </c>
       <c r="E55" s="8">
-        <v>0.8</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3014,13 +3013,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>714.05</v>
+        <v>724.65</v>
       </c>
       <c r="D56" s="6">
-        <v>724.65</v>
+        <v>736.55</v>
       </c>
       <c r="E56" s="8">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3031,13 +3030,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>490.3</v>
+        <v>478.95</v>
       </c>
       <c r="D57" s="6">
-        <v>478.95</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-11.35</v>
+        <v>482.6</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.65</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3048,13 +3047,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>11324</v>
+        <v>11222</v>
       </c>
       <c r="D58" s="6">
-        <v>11222</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-102</v>
+        <v>11316</v>
+      </c>
+      <c r="E58" s="8">
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3065,13 +3064,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>341.8</v>
+        <v>334.65</v>
       </c>
       <c r="D59" s="6">
-        <v>334.65</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-7.15</v>
+        <v>340.1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.45</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3082,13 +3081,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1176.2</v>
+        <v>1200.4</v>
       </c>
       <c r="D60" s="6">
-        <v>1200.4</v>
+        <v>1216.3</v>
       </c>
       <c r="E60" s="8">
-        <v>24.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3099,13 +3098,13 @@
         <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>83.25</v>
+        <v>81.47</v>
       </c>
       <c r="D61" s="6">
-        <v>81.47</v>
+        <v>80.87</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.78</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3116,13 +3115,13 @@
         <v>13</v>
       </c>
       <c r="C62" s="6">
+        <v>45</v>
+      </c>
+      <c r="D62" s="6">
         <v>55</v>
       </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-10</v>
+      <c r="E62" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3133,13 +3132,13 @@
         <v>13</v>
       </c>
       <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
         <v>45</v>
       </c>
-      <c r="D63" s="6">
-        <v>55</v>
-      </c>
-      <c r="E63" s="8">
-        <v>10</v>
+      <c r="E63" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3150,13 +3149,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>62.5</v>
+        <v>55.82</v>
       </c>
       <c r="D64" s="6">
-        <v>55.82</v>
+        <v>55.32</v>
       </c>
       <c r="E64" s="7">
-        <v>-6.68</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3167,13 +3166,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>58.06</v>
+        <v>59.15</v>
       </c>
       <c r="D65" s="6">
-        <v>59.15</v>
+        <v>60.38</v>
       </c>
       <c r="E65" s="8">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3184,13 +3183,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>34.43</v>
+        <v>34.69</v>
       </c>
       <c r="D66" s="6">
-        <v>34.69</v>
+        <v>39.62</v>
       </c>
       <c r="E66" s="8">
-        <v>0.26</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3201,13 +3200,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>44.06</v>
+        <v>48.01</v>
       </c>
       <c r="D67" s="6">
-        <v>48.01</v>
+        <v>52.09</v>
       </c>
       <c r="E67" s="8">
-        <v>3.95</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3218,13 +3217,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>45.89</v>
+        <v>41.79</v>
       </c>
       <c r="D68" s="6">
-        <v>41.79</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-4.1</v>
+        <v>43.54</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1.75</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3235,13 +3234,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>50.71</v>
+        <v>47.28</v>
       </c>
       <c r="D69" s="6">
-        <v>47.28</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.43</v>
+        <v>50.6</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3.32</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3252,13 +3251,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>47.31</v>
+        <v>42.93</v>
       </c>
       <c r="D70" s="6">
-        <v>42.93</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-4.38</v>
+        <v>46.96</v>
+      </c>
+      <c r="E70" s="8">
+        <v>4.03</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3269,13 +3268,13 @@
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>33.52</v>
+        <v>40.93</v>
       </c>
       <c r="D71" s="6">
-        <v>40.93</v>
+        <v>45.25</v>
       </c>
       <c r="E71" s="8">
-        <v>7.41</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3286,13 +3285,13 @@
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>58.55</v>
+        <v>54.55</v>
       </c>
       <c r="D72" s="6">
-        <v>54.55</v>
+        <v>53.23</v>
       </c>
       <c r="E72" s="7">
-        <v>-4</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3303,13 +3302,13 @@
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>1162.56</v>
+        <v>107.69</v>
       </c>
       <c r="D73" s="6">
-        <v>107.69</v>
+        <v>-82</v>
       </c>
       <c r="E73" s="7">
-        <v>-1054.87</v>
+        <v>-189.69</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3320,13 +3319,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>103.49</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="D74" s="6">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-23.42</v>
+        <v>147.59</v>
+      </c>
+      <c r="E74" s="8">
+        <v>67.52</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3337,13 +3336,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-51.25</v>
+        <v>-12.3</v>
       </c>
       <c r="D75" s="6">
-        <v>-12.3</v>
+        <v>4.05</v>
       </c>
       <c r="E75" s="8">
-        <v>38.95</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3354,13 +3353,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-23.56</v>
+        <v>-43.95</v>
       </c>
       <c r="D76" s="6">
-        <v>-43.95</v>
+        <v>-49.98</v>
       </c>
       <c r="E76" s="7">
-        <v>-20.39</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3371,13 +3370,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>358.46</v>
+        <v>20.76</v>
       </c>
       <c r="D77" s="6">
-        <v>20.76</v>
+        <v>-45.36</v>
       </c>
       <c r="E77" s="7">
-        <v>-337.7</v>
+        <v>-66.12</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3388,13 +3387,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-90.27</v>
+        <v>-77.34</v>
       </c>
       <c r="D78" s="6">
-        <v>-77.34</v>
-      </c>
-      <c r="E78" s="8">
-        <v>12.93</v>
+        <v>-84.59999999999999</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-7.26</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3405,13 +3404,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-61.81</v>
+        <v>-44.91</v>
       </c>
       <c r="D79" s="6">
-        <v>-44.91</v>
-      </c>
-      <c r="E79" s="8">
-        <v>16.9</v>
+        <v>-58.35</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-13.44</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3422,13 +3421,13 @@
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>92.12</v>
+        <v>-3.31</v>
       </c>
       <c r="D80" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-95.43000000000001</v>
+        <v>60.58</v>
+      </c>
+      <c r="E80" s="8">
+        <v>63.89</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3439,13 +3438,13 @@
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>133.59</v>
+        <v>-53.42</v>
       </c>
       <c r="D81" s="6">
-        <v>-53.42</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-187.01</v>
+        <v>71.54000000000001</v>
+      </c>
+      <c r="E81" s="8">
+        <v>124.96</v>
       </c>
     </row>
   </sheetData>
@@ -3510,16 +3509,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>47.2</v>
+        <v>49.7</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="G2" s="11">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3656,31 +3655,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3858</v>
+        <v>0.3877</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3184</v>
+        <v>0.3225</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2843</v>
+        <v>0.2909</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1887</v>
+        <v>0.1905</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1827</v>
+        <v>0.1861</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1192</v>
+        <v>0.1221</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0464</v>
+        <v>0.048</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0331</v>
+        <v>-0.0345</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.0728</v>
+        <v>-0.0733</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.0 → 52.1</t>
+    <t>45.2 → 51.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>52.1</t>
-  </si>
-  <si>
-    <t>47.3 → 50.6</t>
-  </si>
-  <si>
-    <t>47.3</t>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>50.6 → 49.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.6</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,10 +427,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -798,7 +802,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -938,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>698.75</v>
+        <v>687.35</v>
       </c>
       <c r="D2">
-        <v>-0.29</v>
+        <v>-1.63</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -950,25 +955,25 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-30.65</v>
+        <v>-31.78</v>
       </c>
       <c r="H2">
-        <v>90.29000000000001</v>
+        <v>87.19</v>
       </c>
       <c r="I2">
-        <v>8.029999999999999</v>
+        <v>6.58</v>
       </c>
       <c r="J2">
-        <v>-5.88</v>
+        <v>-5.32</v>
       </c>
       <c r="K2">
-        <v>6.02</v>
+        <v>3.17</v>
       </c>
       <c r="L2">
-        <v>21.99</v>
+        <v>21.39</v>
       </c>
       <c r="M2">
-        <v>-7.33</v>
+        <v>-6.94</v>
       </c>
       <c r="N2">
         <v>77</v>
@@ -977,19 +982,19 @@
         <v>77</v>
       </c>
       <c r="P2">
-        <v>682.91</v>
+        <v>691.4</v>
       </c>
       <c r="Q2">
-        <v>681.09</v>
+        <v>679.53</v>
       </c>
       <c r="R2">
-        <v>669.84</v>
+        <v>670.9299999999999</v>
       </c>
       <c r="S2">
-        <v>649.04</v>
+        <v>650.08</v>
       </c>
       <c r="T2">
-        <v>7.66</v>
+        <v>5.73</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1004,34 +1009,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>55.32</v>
+        <v>52.44</v>
       </c>
       <c r="Z2">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="AA2">
-        <v>-2.26</v>
+        <v>-1.46</v>
       </c>
       <c r="AB2">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AC2">
-        <v>81.01000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="AD2">
-        <v>63.14</v>
+        <v>70.55</v>
       </c>
       <c r="AE2">
-        <v>34.14</v>
+        <v>33.59</v>
       </c>
       <c r="AF2">
-        <v>-82</v>
+        <v>-76.42</v>
       </c>
       <c r="AG2">
-        <v>747.3200000000001</v>
+        <v>743.49</v>
       </c>
       <c r="AH2">
-        <v>614.85</v>
+        <v>615.5700000000001</v>
       </c>
       <c r="AI2">
         <v>603.87</v>
@@ -1040,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>38.71</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1051,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>301.55</v>
+        <v>295.6</v>
       </c>
       <c r="D3">
-        <v>0.79</v>
+        <v>-1.97</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1063,46 +1068,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-5.02</v>
+        <v>-6.9</v>
       </c>
       <c r="H3">
-        <v>96.8</v>
+        <v>92.91</v>
       </c>
       <c r="I3">
-        <v>11.85</v>
+        <v>5.16</v>
       </c>
       <c r="J3">
-        <v>7.22</v>
+        <v>1.51</v>
       </c>
       <c r="K3">
-        <v>11.91</v>
+        <v>11.15</v>
       </c>
       <c r="L3">
-        <v>48.46</v>
+        <v>49.73</v>
       </c>
       <c r="M3">
-        <v>38.77</v>
+        <v>39.61</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>88</v>
       </c>
       <c r="P3">
-        <v>292.4</v>
+        <v>295.3</v>
       </c>
       <c r="Q3">
-        <v>283.66</v>
+        <v>283.96</v>
       </c>
       <c r="R3">
-        <v>287.68</v>
+        <v>288.29</v>
       </c>
       <c r="S3">
-        <v>233.52</v>
+        <v>234.18</v>
       </c>
       <c r="T3">
-        <v>29.13</v>
+        <v>26.23</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1117,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>60.38</v>
+        <v>55.79</v>
       </c>
       <c r="Z3">
-        <v>0.9399999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="AA3">
-        <v>-1.7</v>
+        <v>-1.06</v>
       </c>
       <c r="AB3">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AD3">
-        <v>97.77</v>
+        <v>97.36</v>
       </c>
       <c r="AE3">
-        <v>11.48</v>
+        <v>12.29</v>
       </c>
       <c r="AF3">
-        <v>147.59</v>
+        <v>132.75</v>
       </c>
       <c r="AG3">
-        <v>302.73</v>
+        <v>303.61</v>
       </c>
       <c r="AH3">
-        <v>264.59</v>
+        <v>264.31</v>
       </c>
       <c r="AI3">
         <v>268.82</v>
@@ -1153,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>36.68</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1164,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1045.2</v>
+        <v>1041.8</v>
       </c>
       <c r="D4">
-        <v>1.48</v>
+        <v>-0.33</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1176,46 +1181,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-18.9</v>
+        <v>-19.17</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.66</v>
       </c>
       <c r="I4">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="J4">
-        <v>-5.24</v>
+        <v>-7.67</v>
       </c>
       <c r="K4">
-        <v>1.97</v>
+        <v>0.82</v>
       </c>
       <c r="L4">
-        <v>3.73</v>
+        <v>4.6</v>
       </c>
       <c r="M4">
-        <v>18.61</v>
+        <v>19.16</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1029.72</v>
+        <v>1035.58</v>
       </c>
       <c r="Q4">
-        <v>1090.68</v>
+        <v>1086.79</v>
       </c>
       <c r="R4">
-        <v>1115.2</v>
+        <v>1114.02</v>
       </c>
       <c r="S4">
-        <v>1139.97</v>
+        <v>1140.07</v>
       </c>
       <c r="T4">
-        <v>-8.31</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1230,34 +1235,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.62</v>
+        <v>38.91</v>
       </c>
       <c r="Z4">
-        <v>-28.1</v>
+        <v>-27.05</v>
       </c>
       <c r="AA4">
-        <v>-21.73</v>
+        <v>-22.79</v>
       </c>
       <c r="AB4">
-        <v>-6.37</v>
+        <v>-4.26</v>
       </c>
       <c r="AC4">
-        <v>33.42</v>
+        <v>42.86</v>
       </c>
       <c r="AD4">
-        <v>24.49</v>
+        <v>33.2</v>
       </c>
       <c r="AE4">
-        <v>31.27</v>
+        <v>30.54</v>
       </c>
       <c r="AF4">
-        <v>4.05</v>
+        <v>-14.32</v>
       </c>
       <c r="AG4">
-        <v>1203.21</v>
+        <v>1200.5</v>
       </c>
       <c r="AH4">
-        <v>978.14</v>
+        <v>973.08</v>
       </c>
       <c r="AI4">
         <v>1118.75</v>
@@ -1266,7 +1271,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>50.71</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1277,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>736.55</v>
+        <v>734.9</v>
       </c>
       <c r="D5">
-        <v>1.64</v>
+        <v>-0.22</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1289,46 +1294,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-14.81</v>
+        <v>-15</v>
       </c>
       <c r="H5">
-        <v>11.28</v>
+        <v>11.03</v>
       </c>
       <c r="I5">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="J5">
-        <v>0.78</v>
+        <v>1.44</v>
       </c>
       <c r="K5">
-        <v>-0.13</v>
+        <v>0.57</v>
       </c>
       <c r="L5">
-        <v>-4.72</v>
+        <v>-5.12</v>
       </c>
       <c r="M5">
-        <v>32.25</v>
+        <v>33.29</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>720.54</v>
+        <v>726.14</v>
       </c>
       <c r="Q5">
-        <v>734.91</v>
+        <v>734.11</v>
       </c>
       <c r="R5">
-        <v>731.5700000000001</v>
+        <v>731.62</v>
       </c>
       <c r="S5">
-        <v>743.78</v>
+        <v>743.28</v>
       </c>
       <c r="T5">
-        <v>-0.97</v>
+        <v>-1.13</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1343,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>52.09</v>
+        <v>51.49</v>
       </c>
       <c r="Z5">
-        <v>-3.85</v>
+        <v>-2.91</v>
       </c>
       <c r="AA5">
-        <v>-2.6</v>
+        <v>-2.66</v>
       </c>
       <c r="AB5">
-        <v>-1.25</v>
+        <v>-0.25</v>
       </c>
       <c r="AC5">
-        <v>56.51</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="AD5">
-        <v>39.22</v>
+        <v>56.67</v>
       </c>
       <c r="AE5">
-        <v>21.05</v>
+        <v>20.91</v>
       </c>
       <c r="AF5">
-        <v>-49.98</v>
+        <v>5.24</v>
       </c>
       <c r="AG5">
-        <v>767.42</v>
+        <v>765.74</v>
       </c>
       <c r="AH5">
-        <v>702.39</v>
+        <v>702.47</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1379,7 +1384,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>18.91</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1390,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>482.6</v>
+        <v>482.2</v>
       </c>
       <c r="D6">
-        <v>0.76</v>
+        <v>-0.08</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1402,46 +1407,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-19.57</v>
+        <v>-19.63</v>
       </c>
       <c r="H6">
-        <v>10.04</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I6">
-        <v>4.39</v>
+        <v>3.18</v>
       </c>
       <c r="J6">
-        <v>-4.38</v>
+        <v>-5.82</v>
       </c>
       <c r="K6">
-        <v>-10.83</v>
+        <v>-15.06</v>
       </c>
       <c r="L6">
-        <v>-11.06</v>
+        <v>-10.57</v>
       </c>
       <c r="M6">
-        <v>4.8</v>
+        <v>5.46</v>
       </c>
       <c r="N6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P6">
-        <v>475.94</v>
+        <v>478.91</v>
       </c>
       <c r="Q6">
-        <v>492.77</v>
+        <v>490.58</v>
       </c>
       <c r="R6">
-        <v>521.51</v>
+        <v>519.9299999999999</v>
       </c>
       <c r="S6">
-        <v>523.64</v>
+        <v>523.71</v>
       </c>
       <c r="T6">
-        <v>-7.84</v>
+        <v>-7.93</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1456,34 +1461,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.54</v>
+        <v>43.38</v>
       </c>
       <c r="Z6">
-        <v>-13.54</v>
+        <v>-12.59</v>
       </c>
       <c r="AA6">
-        <v>-14.28</v>
+        <v>-13.94</v>
       </c>
       <c r="AB6">
-        <v>0.73</v>
+        <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>88.37</v>
+        <v>83.86</v>
       </c>
       <c r="AD6">
-        <v>64.64</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AE6">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="AF6">
-        <v>-45.36</v>
+        <v>-34.59</v>
       </c>
       <c r="AG6">
-        <v>532.24</v>
+        <v>527.03</v>
       </c>
       <c r="AH6">
-        <v>453.3</v>
+        <v>454.13</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
@@ -1492,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>26.15</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1503,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11316</v>
+        <v>11273</v>
       </c>
       <c r="D7">
-        <v>0.84</v>
+        <v>-0.38</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1515,46 +1520,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.95</v>
+        <v>-49.14</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="J7">
-        <v>3.48</v>
+        <v>1.14</v>
       </c>
       <c r="K7">
-        <v>3.05</v>
+        <v>2.01</v>
       </c>
       <c r="L7">
-        <v>-32.75</v>
+        <v>-32.46</v>
       </c>
       <c r="M7">
-        <v>19.05</v>
+        <v>19.08</v>
       </c>
       <c r="N7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P7">
-        <v>11299.2</v>
+        <v>11291</v>
       </c>
       <c r="Q7">
-        <v>11239.1</v>
+        <v>11238.65</v>
       </c>
       <c r="R7">
-        <v>11427.3</v>
+        <v>11411.12</v>
       </c>
       <c r="S7">
-        <v>13534.7</v>
+        <v>13492.06</v>
       </c>
       <c r="T7">
-        <v>-16.39</v>
+        <v>-16.45</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1569,34 +1574,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>50.6</v>
+        <v>49.07</v>
       </c>
       <c r="Z7">
-        <v>-20.17</v>
+        <v>-18.92</v>
       </c>
       <c r="AA7">
-        <v>-41.47</v>
+        <v>-36.96</v>
       </c>
       <c r="AB7">
-        <v>21.3</v>
+        <v>18.04</v>
       </c>
       <c r="AC7">
-        <v>81.98</v>
+        <v>76.55</v>
       </c>
       <c r="AD7">
-        <v>85.39</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="AE7">
-        <v>287.5</v>
+        <v>276.75</v>
       </c>
       <c r="AF7">
-        <v>-84.59999999999999</v>
+        <v>-78.77</v>
       </c>
       <c r="AG7">
-        <v>11461.77</v>
+        <v>11461</v>
       </c>
       <c r="AH7">
-        <v>11016.43</v>
+        <v>11016.3</v>
       </c>
       <c r="AI7">
         <v>12115.85</v>
@@ -1605,7 +1610,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>10.87</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1616,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>340.1</v>
+        <v>328.95</v>
       </c>
       <c r="D8">
-        <v>1.63</v>
+        <v>-3.28</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1628,46 +1633,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-7.48</v>
+        <v>-10.51</v>
       </c>
       <c r="H8">
-        <v>45.15</v>
+        <v>40.39</v>
       </c>
       <c r="I8">
-        <v>0.4</v>
+        <v>-3.06</v>
       </c>
       <c r="J8">
-        <v>4.47</v>
+        <v>0.7</v>
       </c>
       <c r="K8">
-        <v>-0.6</v>
+        <v>-5.6</v>
       </c>
       <c r="L8">
-        <v>11.29</v>
+        <v>6.51</v>
       </c>
       <c r="M8">
-        <v>29.09</v>
+        <v>27.6</v>
       </c>
       <c r="N8">
+        <v>44</v>
+      </c>
+      <c r="O8">
         <v>66</v>
       </c>
-      <c r="O8">
-        <v>70</v>
-      </c>
       <c r="P8">
-        <v>339.84</v>
+        <v>337.76</v>
       </c>
       <c r="Q8">
-        <v>350.63</v>
+        <v>349.67</v>
       </c>
       <c r="R8">
-        <v>341.97</v>
+        <v>341.99</v>
       </c>
       <c r="S8">
-        <v>295.86</v>
+        <v>296.07</v>
       </c>
       <c r="T8">
-        <v>14.95</v>
+        <v>11.11</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1682,43 +1687,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>46.96</v>
+        <v>40.63</v>
       </c>
       <c r="Z8">
-        <v>-0.71</v>
+        <v>-1.85</v>
       </c>
       <c r="AA8">
-        <v>1.66</v>
+        <v>0.96</v>
       </c>
       <c r="AB8">
-        <v>-2.37</v>
+        <v>-2.81</v>
       </c>
       <c r="AC8">
-        <v>18.49</v>
+        <v>10.2</v>
       </c>
       <c r="AD8">
-        <v>19.79</v>
+        <v>15.89</v>
       </c>
       <c r="AE8">
-        <v>11.39</v>
+        <v>11.46</v>
       </c>
       <c r="AF8">
-        <v>-58.35</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="AG8">
-        <v>371.53</v>
+        <v>372.7</v>
       </c>
       <c r="AH8">
-        <v>329.74</v>
+        <v>326.64</v>
       </c>
       <c r="AI8">
-        <v>331.1</v>
+        <v>368.68</v>
       </c>
       <c r="AJ8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.65</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1729,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1216.3</v>
+        <v>1241.3</v>
       </c>
       <c r="D9">
-        <v>1.32</v>
+        <v>2.06</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1741,46 +1746,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-9.300000000000001</v>
+        <v>-7.43</v>
       </c>
       <c r="H9">
-        <v>12.69</v>
+        <v>15.01</v>
       </c>
       <c r="I9">
-        <v>4.14</v>
+        <v>5.82</v>
       </c>
       <c r="J9">
-        <v>-2.61</v>
+        <v>-0.97</v>
       </c>
       <c r="K9">
-        <v>-1.7</v>
+        <v>-1.25</v>
       </c>
       <c r="L9">
-        <v>4.73</v>
+        <v>8.15</v>
       </c>
       <c r="M9">
-        <v>12.21</v>
+        <v>13.43</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O9">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P9">
-        <v>1188.5</v>
+        <v>1202.16</v>
       </c>
       <c r="Q9">
-        <v>1234.63</v>
+        <v>1232.92</v>
       </c>
       <c r="R9">
-        <v>1271.1</v>
+        <v>1269.77</v>
       </c>
       <c r="S9">
-        <v>1242.89</v>
+        <v>1243.54</v>
       </c>
       <c r="T9">
-        <v>-2.14</v>
+        <v>-0.18</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1795,34 +1800,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>45.25</v>
+        <v>51.28</v>
       </c>
       <c r="Z9">
-        <v>-24.68</v>
+        <v>-20.32</v>
       </c>
       <c r="AA9">
-        <v>-22.26</v>
+        <v>-21.87</v>
       </c>
       <c r="AB9">
-        <v>-2.42</v>
+        <v>1.55</v>
       </c>
       <c r="AC9">
-        <v>52.66</v>
+        <v>81.2</v>
       </c>
       <c r="AD9">
-        <v>30.4</v>
+        <v>53.87</v>
       </c>
       <c r="AE9">
-        <v>28.98</v>
+        <v>29.48</v>
       </c>
       <c r="AF9">
-        <v>60.58</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="AG9">
-        <v>1319.87</v>
+        <v>1316.04</v>
       </c>
       <c r="AH9">
-        <v>1149.4</v>
+        <v>1149.8</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1831,7 +1836,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>37.8</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1842,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>80.87</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.74</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1854,46 +1859,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.57</v>
+        <v>-10.68</v>
       </c>
       <c r="H10">
-        <v>124.14</v>
+        <v>126.39</v>
       </c>
       <c r="I10">
-        <v>5.99</v>
+        <v>3.92</v>
       </c>
       <c r="J10">
-        <v>-1.28</v>
+        <v>1.24</v>
       </c>
       <c r="K10">
-        <v>65.06999999999999</v>
+        <v>38.96</v>
       </c>
       <c r="L10">
-        <v>-0.32</v>
+        <v>2.76</v>
       </c>
       <c r="M10">
-        <v>-3.45</v>
+        <v>-2.77</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P10">
-        <v>81.16</v>
+        <v>81.78</v>
       </c>
       <c r="Q10">
-        <v>78.55</v>
+        <v>78.58</v>
       </c>
       <c r="R10">
-        <v>81.54000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="S10">
-        <v>62.38</v>
+        <v>62.48</v>
       </c>
       <c r="T10">
-        <v>29.65</v>
+        <v>30.72</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1908,34 +1913,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>53.23</v>
+        <v>54.82</v>
       </c>
       <c r="Z10">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="AA10">
-        <v>-0.24</v>
+        <v>-0.12</v>
       </c>
       <c r="AB10">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AC10">
-        <v>84.52</v>
+        <v>76.81</v>
       </c>
       <c r="AD10">
-        <v>90.98999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AE10">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="AF10">
-        <v>71.54000000000001</v>
+        <v>7.27</v>
       </c>
       <c r="AG10">
-        <v>83.31999999999999</v>
+        <v>83.45</v>
       </c>
       <c r="AH10">
-        <v>73.77</v>
+        <v>73.72</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1944,12 +1949,72 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>28.7</v>
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK10"/>
   <conditionalFormatting sqref="AF2:AF10">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J10">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K10">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1961,8 +2026,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N10">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1971,72 +2042,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T10">
@@ -2048,26 +2053,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U10">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V10">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W10">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2085,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2125,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2144,28 +2149,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2177,1274 +2182,1359 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-5.88</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-5.32</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>7.22</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-5.24</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-7.67</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.78</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-4.38</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-5.82</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3.48</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.14</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>4.47</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-2.61</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.97</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.28</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.24</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="D17" s="7">
+        <v>6.58</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>11.85</v>
+      </c>
+      <c r="D18" s="7">
+        <v>5.16</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-6.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2.89</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>3.88</v>
+      </c>
+      <c r="D20" s="7">
+        <v>3.96</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>4.39</v>
+      </c>
+      <c r="D21" s="7">
+        <v>3.18</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-3.06</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4.14</v>
+      </c>
+      <c r="D24" s="7">
+        <v>5.82</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>5.99</v>
+      </c>
+      <c r="D25" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>21.99</v>
+      </c>
+      <c r="D26" s="7">
+        <v>21.39</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>48.46</v>
+      </c>
+      <c r="D27" s="7">
+        <v>49.73</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>3.73</v>
+      </c>
+      <c r="D28" s="7">
+        <v>4.6</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-4.72</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-5.12</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-11.06</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-10.57</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-32.75</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-32.46</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>11.29</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6.51</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-4.78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>4.73</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8.15</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-0.32</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2.76</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>6.02</v>
+      </c>
+      <c r="D35" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>11.91</v>
+      </c>
+      <c r="D36" s="7">
+        <v>11.15</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>1.97</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-0.13</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.57</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-10.83</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-15.06</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-4.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="D40" s="7">
+        <v>2.01</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-5.6</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-1.7</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-1.25</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="D43" s="7">
+        <v>38.96</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-26.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-30.65</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-31.78</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-5.02</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-6.9</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-18.9</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-19.17</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-14.81</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-15</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-19.57</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-19.63</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-48.95</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-49.14</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-7.48</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-10.51</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-7.43</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-11.57</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-10.68</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>698.75</v>
+      </c>
+      <c r="D53" s="7">
+        <v>687.35</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>301.55</v>
+      </c>
+      <c r="D54" s="7">
+        <v>295.6</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1045.2</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1041.8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>736.55</v>
+      </c>
+      <c r="D56" s="7">
+        <v>734.9</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>482.6</v>
+      </c>
+      <c r="D57" s="7">
+        <v>482.2</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11316</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11273</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>340.1</v>
+      </c>
+      <c r="D59" s="7">
+        <v>328.95</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-11.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1216.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1241.3</v>
+      </c>
+      <c r="E60" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>80.87</v>
+      </c>
+      <c r="D61" s="7">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>88</v>
+      </c>
+      <c r="D62" s="7">
+        <v>99</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>34</v>
+      </c>
+      <c r="D63" s="7">
+        <v>33</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>22</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>12</v>
+      </c>
+      <c r="D65" s="7">
+        <v>11</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
         <v>66</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D66" s="7">
+        <v>44</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>45</v>
+      </c>
+      <c r="D67" s="7">
+        <v>66</v>
+      </c>
+      <c r="E67" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="7">
+        <v>99</v>
+      </c>
+      <c r="D68" s="7">
+        <v>88</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.03</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>55.32</v>
+      </c>
+      <c r="D69" s="7">
+        <v>52.44</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3.53</v>
-      </c>
-      <c r="D9" s="6">
-        <v>7.22</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>60.38</v>
+      </c>
+      <c r="D70" s="7">
+        <v>55.79</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-4.59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.24</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>39.62</v>
+      </c>
+      <c r="D71" s="7">
+        <v>38.91</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>52.09</v>
+      </c>
+      <c r="D72" s="7">
+        <v>51.49</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.38</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>43.54</v>
+      </c>
+      <c r="D73" s="7">
+        <v>43.38</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2.33</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3.48</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>50.6</v>
+      </c>
+      <c r="D74" s="7">
+        <v>49.07</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="D14" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46.96</v>
+      </c>
+      <c r="D75" s="7">
+        <v>40.63</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-6.33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>45.25</v>
+      </c>
+      <c r="D76" s="7">
+        <v>51.28</v>
+      </c>
+      <c r="E76" s="8">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="7">
+        <v>53.23</v>
+      </c>
+      <c r="D77" s="7">
+        <v>54.82</v>
+      </c>
+      <c r="E77" s="8">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="D17" s="6">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-82</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-76.42</v>
+      </c>
+      <c r="E78" s="8">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>10.73</v>
-      </c>
-      <c r="D18" s="6">
-        <v>11.85</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>147.59</v>
+      </c>
+      <c r="D79" s="7">
+        <v>132.75</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-14.84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.98</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>4.05</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-14.32</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-18.37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.88</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-49.98</v>
+      </c>
+      <c r="D81" s="7">
+        <v>5.24</v>
+      </c>
+      <c r="E81" s="8">
+        <v>55.22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2.59</v>
-      </c>
-      <c r="D21" s="6">
-        <v>4.39</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-45.36</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-34.59</v>
+      </c>
+      <c r="E82" s="8">
+        <v>10.77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-84.59999999999999</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-78.77</v>
+      </c>
+      <c r="E83" s="8">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.27</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-58.35</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-81.59999999999999</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-23.25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2.14</v>
-      </c>
-      <c r="D24" s="6">
-        <v>4.14</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B85" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="7">
+        <v>60.58</v>
+      </c>
+      <c r="D85" s="7">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="E85" s="8">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>6.97</v>
-      </c>
-      <c r="D25" s="6">
-        <v>5.99</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>21.02</v>
-      </c>
-      <c r="D26" s="6">
-        <v>21.99</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>46.36</v>
-      </c>
-      <c r="D27" s="6">
-        <v>48.46</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>1.46</v>
-      </c>
-      <c r="D28" s="6">
-        <v>3.73</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-6.1</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-4.72</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.98</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-11.06</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-34.56</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-32.75</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>9.01</v>
-      </c>
-      <c r="D32" s="6">
-        <v>11.29</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="D33" s="6">
-        <v>4.73</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-0.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="D35" s="6">
-        <v>6.02</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>11.62</v>
-      </c>
-      <c r="D36" s="6">
-        <v>11.91</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1.97</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="D40" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-1.7</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>61.68</v>
-      </c>
-      <c r="D43" s="6">
-        <v>65.06999999999999</v>
-      </c>
-      <c r="E43" s="8">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-30.45</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-30.65</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-20.08</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.9</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.18</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-14.81</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-20.18</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-19.57</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-49.37</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-48.95</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-7.48</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-10.48</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-10.91</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-11.57</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>700.75</v>
-      </c>
-      <c r="D53" s="6">
-        <v>698.75</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>299.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>301.55</v>
-      </c>
-      <c r="E54" s="8">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1030</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1045.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>724.65</v>
-      </c>
-      <c r="D56" s="6">
-        <v>736.55</v>
-      </c>
-      <c r="E56" s="8">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>478.95</v>
-      </c>
-      <c r="D57" s="6">
-        <v>482.6</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>11222</v>
-      </c>
-      <c r="D58" s="6">
-        <v>11316</v>
-      </c>
-      <c r="E58" s="8">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>334.65</v>
-      </c>
-      <c r="D59" s="6">
-        <v>340.1</v>
-      </c>
-      <c r="E59" s="8">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1200.4</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1216.3</v>
-      </c>
-      <c r="E60" s="8">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>81.47</v>
-      </c>
-      <c r="D61" s="6">
-        <v>80.87</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>55.82</v>
-      </c>
-      <c r="D64" s="6">
-        <v>55.32</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>59.15</v>
-      </c>
-      <c r="D65" s="6">
-        <v>60.38</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>34.69</v>
-      </c>
-      <c r="D66" s="6">
-        <v>39.62</v>
-      </c>
-      <c r="E66" s="8">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>48.01</v>
-      </c>
-      <c r="D67" s="6">
-        <v>52.09</v>
-      </c>
-      <c r="E67" s="8">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.79</v>
-      </c>
-      <c r="D68" s="6">
-        <v>43.54</v>
-      </c>
-      <c r="E68" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>47.28</v>
-      </c>
-      <c r="D69" s="6">
-        <v>50.6</v>
-      </c>
-      <c r="E69" s="8">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>42.93</v>
-      </c>
-      <c r="D70" s="6">
-        <v>46.96</v>
-      </c>
-      <c r="E70" s="8">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>40.93</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45.25</v>
-      </c>
-      <c r="E71" s="8">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>54.55</v>
-      </c>
-      <c r="D72" s="6">
-        <v>53.23</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>107.69</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-82</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-189.69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>80.06999999999999</v>
-      </c>
-      <c r="D74" s="6">
-        <v>147.59</v>
-      </c>
-      <c r="E74" s="8">
-        <v>67.52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-12.3</v>
-      </c>
-      <c r="D75" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="E75" s="8">
-        <v>16.35</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-43.95</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-49.98</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>20.76</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-45.36</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-66.12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-77.34</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-84.59999999999999</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-7.26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-44.91</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-58.35</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-13.44</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="D80" s="6">
-        <v>60.58</v>
-      </c>
-      <c r="E80" s="8">
-        <v>63.89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-53.42</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C86" s="7">
         <v>71.54000000000001</v>
       </c>
-      <c r="E81" s="8">
-        <v>124.96</v>
+      <c r="D86" s="7">
+        <v>7.27</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-64.27</v>
       </c>
     </row>
   </sheetData>
@@ -3470,61 +3560,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>77</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>49.76000000000001</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>49.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-0.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H2" s="11">
-        <v>55.4</v>
-      </c>
-      <c r="I2" s="11">
-        <v>20</v>
+      <c r="D2" s="12">
+        <v>48.6</v>
+      </c>
+      <c r="E2" s="12">
+        <v>44.4</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-1.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H2" s="12">
+        <v>55</v>
+      </c>
+      <c r="I2" s="12">
+        <v>22.2</v>
       </c>
     </row>
   </sheetData>
@@ -3625,61 +3715,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3877</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3225</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2909</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1905</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1861</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1221</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.048</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0345</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0733</v>
+      <c r="A2" s="15">
+        <v>0.3961</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3329</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.276</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1916</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1908</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1343</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0546</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0277</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0694</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,28 +196,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.2 → 51.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.2</t>
+    <t>52.4 → 48.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.4</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>55.8 → 41.4</t>
+  </si>
+  <si>
+    <t>55.8</t>
+  </si>
+  <si>
+    <t>41.4</t>
+  </si>
+  <si>
+    <t>51.3 → 47.2</t>
   </si>
   <si>
     <t>51.3</t>
   </si>
   <si>
-    <t>50.6 → 49.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>47.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,7 +433,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -943,10 +948,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>687.35</v>
+        <v>668.9</v>
       </c>
       <c r="D2">
-        <v>-1.63</v>
+        <v>-2.68</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -955,46 +960,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-31.78</v>
+        <v>-33.61</v>
       </c>
       <c r="H2">
-        <v>87.19</v>
+        <v>82.16</v>
       </c>
       <c r="I2">
-        <v>6.58</v>
+        <v>3.89</v>
       </c>
       <c r="J2">
-        <v>-5.32</v>
+        <v>-6.9</v>
       </c>
       <c r="K2">
-        <v>3.17</v>
+        <v>-0.14</v>
       </c>
       <c r="L2">
-        <v>21.39</v>
+        <v>17.16</v>
       </c>
       <c r="M2">
-        <v>-6.94</v>
+        <v>-7.16</v>
       </c>
       <c r="N2">
         <v>77</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>691.4</v>
+        <v>696.41</v>
       </c>
       <c r="Q2">
-        <v>679.53</v>
+        <v>675.9</v>
       </c>
       <c r="R2">
-        <v>670.9299999999999</v>
+        <v>671.91</v>
       </c>
       <c r="S2">
-        <v>650.08</v>
+        <v>650.98</v>
       </c>
       <c r="T2">
-        <v>5.73</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +1014,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.44</v>
+        <v>48.09</v>
       </c>
       <c r="Z2">
-        <v>1.73</v>
+        <v>0.77</v>
       </c>
       <c r="AA2">
-        <v>-1.46</v>
+        <v>-1.01</v>
       </c>
       <c r="AB2">
-        <v>3.19</v>
+        <v>1.79</v>
       </c>
       <c r="AC2">
-        <v>67.23</v>
+        <v>56.63</v>
       </c>
       <c r="AD2">
-        <v>70.55</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="AE2">
-        <v>33.59</v>
+        <v>33.29</v>
       </c>
       <c r="AF2">
-        <v>-76.42</v>
+        <v>-74.27</v>
       </c>
       <c r="AG2">
-        <v>743.49</v>
+        <v>732.92</v>
       </c>
       <c r="AH2">
-        <v>615.5700000000001</v>
+        <v>618.88</v>
       </c>
       <c r="AI2">
         <v>603.87</v>
@@ -1045,7 +1050,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>40.15</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1061,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>295.6</v>
+        <v>270.4</v>
       </c>
       <c r="D3">
-        <v>-1.97</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1068,46 +1073,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-6.9</v>
+        <v>-14.83</v>
       </c>
       <c r="H3">
-        <v>92.91</v>
+        <v>76.47</v>
       </c>
       <c r="I3">
-        <v>5.16</v>
+        <v>-4.47</v>
       </c>
       <c r="J3">
-        <v>1.51</v>
+        <v>-6.6</v>
       </c>
       <c r="K3">
-        <v>11.15</v>
+        <v>3.11</v>
       </c>
       <c r="L3">
-        <v>49.73</v>
+        <v>34.75</v>
       </c>
       <c r="M3">
-        <v>39.61</v>
+        <v>38.16</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>295.3</v>
+        <v>292.77</v>
       </c>
       <c r="Q3">
-        <v>283.96</v>
+        <v>282.83</v>
       </c>
       <c r="R3">
-        <v>288.29</v>
+        <v>288.27</v>
       </c>
       <c r="S3">
-        <v>234.18</v>
+        <v>234.7</v>
       </c>
       <c r="T3">
-        <v>26.23</v>
+        <v>15.21</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1122,34 +1127,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>55.79</v>
+        <v>41.42</v>
       </c>
       <c r="Z3">
-        <v>1.52</v>
+        <v>-0.06</v>
       </c>
       <c r="AA3">
-        <v>-1.06</v>
+        <v>-0.86</v>
       </c>
       <c r="AB3">
-        <v>2.58</v>
+        <v>0.8</v>
       </c>
       <c r="AC3">
-        <v>93.09999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="AD3">
-        <v>97.36</v>
+        <v>85.91</v>
       </c>
       <c r="AE3">
-        <v>12.29</v>
+        <v>13.45</v>
       </c>
       <c r="AF3">
-        <v>132.75</v>
+        <v>100.36</v>
       </c>
       <c r="AG3">
-        <v>303.61</v>
+        <v>302.88</v>
       </c>
       <c r="AH3">
-        <v>264.31</v>
+        <v>262.78</v>
       </c>
       <c r="AI3">
         <v>268.82</v>
@@ -1158,7 +1163,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>32.6</v>
+        <v>29.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1174,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1041.8</v>
+        <v>1028</v>
       </c>
       <c r="D4">
-        <v>-0.33</v>
+        <v>-1.32</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1181,46 +1186,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-19.17</v>
+        <v>-20.24</v>
       </c>
       <c r="H4">
-        <v>5.66</v>
+        <v>4.26</v>
       </c>
       <c r="I4">
-        <v>2.89</v>
+        <v>-0.36</v>
       </c>
       <c r="J4">
-        <v>-7.67</v>
+        <v>-8.17</v>
       </c>
       <c r="K4">
-        <v>0.82</v>
+        <v>-1.6</v>
       </c>
       <c r="L4">
-        <v>4.6</v>
+        <v>2.66</v>
       </c>
       <c r="M4">
-        <v>19.16</v>
+        <v>19.17</v>
       </c>
       <c r="N4">
         <v>55</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>1035.58</v>
+        <v>1034.84</v>
       </c>
       <c r="Q4">
-        <v>1086.79</v>
+        <v>1081.66</v>
       </c>
       <c r="R4">
-        <v>1114.02</v>
+        <v>1112.52</v>
       </c>
       <c r="S4">
-        <v>1140.07</v>
+        <v>1139.94</v>
       </c>
       <c r="T4">
-        <v>-8.619999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1235,34 +1240,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.91</v>
+        <v>36.09</v>
       </c>
       <c r="Z4">
-        <v>-27.05</v>
+        <v>-27.01</v>
       </c>
       <c r="AA4">
-        <v>-22.79</v>
+        <v>-23.64</v>
       </c>
       <c r="AB4">
-        <v>-4.26</v>
+        <v>-3.38</v>
       </c>
       <c r="AC4">
-        <v>42.86</v>
+        <v>47.79</v>
       </c>
       <c r="AD4">
-        <v>33.2</v>
+        <v>41.35</v>
       </c>
       <c r="AE4">
-        <v>30.54</v>
+        <v>30.45</v>
       </c>
       <c r="AF4">
-        <v>-14.32</v>
+        <v>5.42</v>
       </c>
       <c r="AG4">
-        <v>1200.5</v>
+        <v>1196.3</v>
       </c>
       <c r="AH4">
-        <v>973.08</v>
+        <v>967.02</v>
       </c>
       <c r="AI4">
         <v>1118.75</v>
@@ -1271,7 +1276,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>48.35</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1287,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>734.9</v>
+        <v>733.75</v>
       </c>
       <c r="D5">
-        <v>-0.22</v>
+        <v>-0.16</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1294,46 +1299,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15</v>
+        <v>-15.13</v>
       </c>
       <c r="H5">
-        <v>11.03</v>
+        <v>10.86</v>
       </c>
       <c r="I5">
-        <v>3.96</v>
+        <v>1.83</v>
       </c>
       <c r="J5">
-        <v>1.44</v>
+        <v>-2.29</v>
       </c>
       <c r="K5">
-        <v>0.57</v>
+        <v>-0.72</v>
       </c>
       <c r="L5">
-        <v>-5.12</v>
+        <v>-6.28</v>
       </c>
       <c r="M5">
-        <v>33.29</v>
+        <v>33.95</v>
       </c>
       <c r="N5">
         <v>33</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>726.14</v>
+        <v>728.78</v>
       </c>
       <c r="Q5">
-        <v>734.11</v>
+        <v>733.22</v>
       </c>
       <c r="R5">
-        <v>731.62</v>
+        <v>731.6</v>
       </c>
       <c r="S5">
-        <v>743.28</v>
+        <v>742.76</v>
       </c>
       <c r="T5">
-        <v>-1.13</v>
+        <v>-1.21</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,34 +1353,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>51.49</v>
+        <v>51.05</v>
       </c>
       <c r="Z5">
-        <v>-2.91</v>
+        <v>-2.24</v>
       </c>
       <c r="AA5">
-        <v>-2.66</v>
+        <v>-2.57</v>
       </c>
       <c r="AB5">
-        <v>-0.25</v>
+        <v>0.34</v>
       </c>
       <c r="AC5">
-        <v>74.20999999999999</v>
+        <v>81.45</v>
       </c>
       <c r="AD5">
-        <v>56.67</v>
+        <v>70.72</v>
       </c>
       <c r="AE5">
-        <v>20.91</v>
+        <v>21.2</v>
       </c>
       <c r="AF5">
-        <v>5.24</v>
+        <v>-45.08</v>
       </c>
       <c r="AG5">
-        <v>765.74</v>
+        <v>763.78</v>
       </c>
       <c r="AH5">
-        <v>702.47</v>
+        <v>702.66</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1384,7 +1389,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>19.14</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1400,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>482.2</v>
+        <v>474.95</v>
       </c>
       <c r="D6">
-        <v>-0.08</v>
+        <v>-1.5</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1407,46 +1412,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-19.63</v>
+        <v>-20.84</v>
       </c>
       <c r="H6">
-        <v>9.949999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="J6">
-        <v>-5.82</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K6">
-        <v>-15.06</v>
+        <v>-16.12</v>
       </c>
       <c r="L6">
-        <v>-10.57</v>
+        <v>-12.68</v>
       </c>
       <c r="M6">
-        <v>5.46</v>
+        <v>5.61</v>
       </c>
       <c r="N6">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="O6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P6">
-        <v>478.91</v>
+        <v>481.8</v>
       </c>
       <c r="Q6">
-        <v>490.58</v>
+        <v>488.48</v>
       </c>
       <c r="R6">
-        <v>519.9299999999999</v>
+        <v>518.14</v>
       </c>
       <c r="S6">
-        <v>523.71</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="T6">
-        <v>-7.93</v>
+        <v>-9.31</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1461,34 +1466,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.38</v>
+        <v>40.59</v>
       </c>
       <c r="Z6">
-        <v>-12.59</v>
+        <v>-12.27</v>
       </c>
       <c r="AA6">
-        <v>-13.94</v>
+        <v>-13.61</v>
       </c>
       <c r="AB6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC6">
-        <v>83.86</v>
+        <v>81.69</v>
       </c>
       <c r="AD6">
-        <v>78.15000000000001</v>
+        <v>84.64</v>
       </c>
       <c r="AE6">
-        <v>13.2</v>
+        <v>13.45</v>
       </c>
       <c r="AF6">
-        <v>-34.59</v>
+        <v>-58.96</v>
       </c>
       <c r="AG6">
-        <v>527.03</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="AH6">
-        <v>454.13</v>
+        <v>453.63</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
@@ -1497,7 +1502,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.97</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1513,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11273</v>
+        <v>11297</v>
       </c>
       <c r="D7">
-        <v>-0.38</v>
+        <v>0.21</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1520,46 +1525,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.14</v>
+        <v>-49.03</v>
       </c>
       <c r="H7">
-        <v>5.8</v>
+        <v>6.03</v>
       </c>
       <c r="I7">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="J7">
-        <v>1.14</v>
+        <v>0.13</v>
       </c>
       <c r="K7">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="L7">
-        <v>-32.46</v>
+        <v>-31.89</v>
       </c>
       <c r="M7">
-        <v>19.08</v>
+        <v>19.45</v>
       </c>
       <c r="N7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>11291</v>
+        <v>11286.4</v>
       </c>
       <c r="Q7">
-        <v>11238.65</v>
+        <v>11243.25</v>
       </c>
       <c r="R7">
-        <v>11411.12</v>
+        <v>11396.56</v>
       </c>
       <c r="S7">
-        <v>13492.06</v>
+        <v>13447.15</v>
       </c>
       <c r="T7">
-        <v>-16.45</v>
+        <v>-15.99</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1574,43 +1579,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>49.07</v>
+        <v>49.98</v>
       </c>
       <c r="Z7">
-        <v>-18.92</v>
+        <v>-15.81</v>
       </c>
       <c r="AA7">
-        <v>-36.96</v>
+        <v>-32.73</v>
       </c>
       <c r="AB7">
-        <v>18.04</v>
+        <v>16.92</v>
       </c>
       <c r="AC7">
-        <v>76.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AD7">
-        <v>80.15000000000001</v>
+        <v>80.12</v>
       </c>
       <c r="AE7">
-        <v>276.75</v>
+        <v>266.63</v>
       </c>
       <c r="AF7">
-        <v>-78.77</v>
+        <v>-59.69</v>
       </c>
       <c r="AG7">
-        <v>11461</v>
+        <v>11466.47</v>
       </c>
       <c r="AH7">
-        <v>11016.3</v>
+        <v>11020.03</v>
       </c>
       <c r="AI7">
-        <v>12115.85</v>
+        <v>12101.38</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>11.13</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>328.95</v>
+        <v>320.55</v>
       </c>
       <c r="D8">
-        <v>-3.28</v>
+        <v>-2.55</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1633,46 +1638,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-10.51</v>
+        <v>-12.8</v>
       </c>
       <c r="H8">
-        <v>40.39</v>
+        <v>36.81</v>
       </c>
       <c r="I8">
-        <v>-3.06</v>
+        <v>-6.63</v>
       </c>
       <c r="J8">
-        <v>0.7</v>
+        <v>-7.95</v>
       </c>
       <c r="K8">
-        <v>-5.6</v>
+        <v>-6.97</v>
       </c>
       <c r="L8">
-        <v>6.51</v>
+        <v>3.64</v>
       </c>
       <c r="M8">
-        <v>27.6</v>
+        <v>26.46</v>
       </c>
       <c r="N8">
         <v>44</v>
       </c>
       <c r="O8">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P8">
-        <v>337.76</v>
+        <v>333.21</v>
       </c>
       <c r="Q8">
-        <v>349.67</v>
+        <v>348.21</v>
       </c>
       <c r="R8">
-        <v>341.99</v>
+        <v>341.69</v>
       </c>
       <c r="S8">
-        <v>296.07</v>
+        <v>296.25</v>
       </c>
       <c r="T8">
-        <v>11.11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,43 +1692,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.63</v>
+        <v>36.63</v>
       </c>
       <c r="Z8">
-        <v>-1.85</v>
+        <v>-3.38</v>
       </c>
       <c r="AA8">
-        <v>0.96</v>
+        <v>0.09</v>
       </c>
       <c r="AB8">
-        <v>-2.81</v>
+        <v>-3.48</v>
       </c>
       <c r="AC8">
-        <v>10.2</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AD8">
-        <v>15.89</v>
+        <v>12.41</v>
       </c>
       <c r="AE8">
-        <v>11.46</v>
+        <v>11.8</v>
       </c>
       <c r="AF8">
-        <v>-81.59999999999999</v>
+        <v>-43.02</v>
       </c>
       <c r="AG8">
-        <v>372.7</v>
+        <v>374.67</v>
       </c>
       <c r="AH8">
-        <v>326.64</v>
+        <v>321.76</v>
       </c>
       <c r="AI8">
-        <v>368.68</v>
+        <v>361.71</v>
       </c>
       <c r="AJ8" t="s">
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>29.12</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1739,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1241.3</v>
+        <v>1222.9</v>
       </c>
       <c r="D9">
-        <v>2.06</v>
+        <v>-1.48</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1746,25 +1751,25 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-7.43</v>
+        <v>-8.81</v>
       </c>
       <c r="H9">
-        <v>15.01</v>
+        <v>13.3</v>
       </c>
       <c r="I9">
-        <v>5.82</v>
+        <v>3.94</v>
       </c>
       <c r="J9">
-        <v>-0.97</v>
+        <v>-4.13</v>
       </c>
       <c r="K9">
-        <v>-1.25</v>
+        <v>-3.51</v>
       </c>
       <c r="L9">
-        <v>8.15</v>
+        <v>5.35</v>
       </c>
       <c r="M9">
-        <v>13.43</v>
+        <v>13.67</v>
       </c>
       <c r="N9">
         <v>66</v>
@@ -1773,19 +1778,19 @@
         <v>69</v>
       </c>
       <c r="P9">
-        <v>1202.16</v>
+        <v>1211.42</v>
       </c>
       <c r="Q9">
-        <v>1232.92</v>
+        <v>1230.64</v>
       </c>
       <c r="R9">
-        <v>1269.77</v>
+        <v>1268.23</v>
       </c>
       <c r="S9">
-        <v>1243.54</v>
+        <v>1243.83</v>
       </c>
       <c r="T9">
-        <v>-0.18</v>
+        <v>-1.68</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1800,34 +1805,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>51.28</v>
+        <v>47.16</v>
       </c>
       <c r="Z9">
-        <v>-20.32</v>
+        <v>-18.14</v>
       </c>
       <c r="AA9">
-        <v>-21.87</v>
+        <v>-21.12</v>
       </c>
       <c r="AB9">
-        <v>1.55</v>
+        <v>2.98</v>
       </c>
       <c r="AC9">
-        <v>81.2</v>
+        <v>88.62</v>
       </c>
       <c r="AD9">
-        <v>53.87</v>
+        <v>74.16</v>
       </c>
       <c r="AE9">
-        <v>29.48</v>
+        <v>30.57</v>
       </c>
       <c r="AF9">
-        <v>99.56999999999999</v>
+        <v>-28.8</v>
       </c>
       <c r="AG9">
-        <v>1316.04</v>
+        <v>1312.12</v>
       </c>
       <c r="AH9">
-        <v>1149.8</v>
+        <v>1149.15</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1836,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>34.87</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1852,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.68000000000001</v>
+        <v>81.16</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>-0.64</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1859,46 +1864,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-10.68</v>
+        <v>-11.25</v>
       </c>
       <c r="H10">
-        <v>126.39</v>
+        <v>124.94</v>
       </c>
       <c r="I10">
-        <v>3.92</v>
+        <v>-0.58</v>
       </c>
       <c r="J10">
-        <v>1.24</v>
+        <v>0.32</v>
       </c>
       <c r="K10">
-        <v>38.96</v>
+        <v>17.54</v>
       </c>
       <c r="L10">
-        <v>2.76</v>
+        <v>1.29</v>
       </c>
       <c r="M10">
-        <v>-2.77</v>
+        <v>-2.54</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P10">
-        <v>81.78</v>
+        <v>81.69</v>
       </c>
       <c r="Q10">
-        <v>78.58</v>
+        <v>78.63</v>
       </c>
       <c r="R10">
-        <v>81.42</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="S10">
-        <v>62.48</v>
+        <v>62.58</v>
       </c>
       <c r="T10">
-        <v>30.72</v>
+        <v>29.69</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1913,34 +1918,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>54.82</v>
+        <v>53.56</v>
       </c>
       <c r="Z10">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="AA10">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="AC10">
-        <v>76.81</v>
+        <v>73.14</v>
       </c>
       <c r="AD10">
-        <v>84.90000000000001</v>
+        <v>78.16</v>
       </c>
       <c r="AE10">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="AF10">
-        <v>7.27</v>
+        <v>2.7</v>
       </c>
       <c r="AG10">
-        <v>83.45</v>
+        <v>83.59</v>
       </c>
       <c r="AH10">
-        <v>73.72</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1949,7 +1954,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>28.24</v>
+        <v>25.08</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2130,7 +2135,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2149,1398 +2154,1333 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.32</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.6</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-8.109999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-7.67</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-8.17</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-2.29</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.82</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.14</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-7.95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-8.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.97</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-5.88</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3.89</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>7.22</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.51</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-5.71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>5.16</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.47</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-9.630000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.24</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-7.67</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2.89</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.78</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3.96</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.83</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-4.38</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-5.82</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3.18</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3.14</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>3.48</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.14</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.2</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>4.47</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-6.63</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.97</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>5.82</v>
+      </c>
+      <c r="D25" s="6">
+        <v>3.94</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.28</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.24</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3.92</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="D17" s="7">
-        <v>6.58</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>21.39</v>
+      </c>
+      <c r="D27" s="6">
+        <v>17.16</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-4.23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>11.85</v>
-      </c>
-      <c r="D18" s="7">
-        <v>5.16</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-6.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>49.73</v>
+      </c>
+      <c r="D28" s="6">
+        <v>34.75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-14.98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2.89</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>4.6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2.66</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>3.88</v>
-      </c>
-      <c r="D20" s="7">
-        <v>3.96</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.28</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4.39</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3.18</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-10.57</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-12.68</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-32.46</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-31.89</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>6.51</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.64</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>8.15</v>
+      </c>
+      <c r="D34" s="6">
+        <v>5.35</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-0.14</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>11.15</v>
+      </c>
+      <c r="D37" s="6">
+        <v>3.11</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-8.039999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.82</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.57</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-0.72</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-15.06</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-16.12</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>2.01</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-5.6</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-6.97</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-1.25</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>38.96</v>
+      </c>
+      <c r="D44" s="6">
+        <v>17.54</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-21.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-31.78</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-33.61</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-6.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-14.83</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-7.93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-19.17</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-20.24</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-15</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-15.13</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-19.63</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-20.84</v>
+      </c>
+      <c r="E49" s="7">
         <v>-1.21</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.26</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-49.14</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-49.03</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-3.06</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-12.8</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>4.14</v>
-      </c>
-      <c r="D24" s="7">
-        <v>5.82</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-7.43</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-8.81</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>5.99</v>
-      </c>
-      <c r="D25" s="7">
-        <v>3.92</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-11.25</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>687.35</v>
+      </c>
+      <c r="D54" s="6">
+        <v>668.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-18.45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>295.6</v>
+      </c>
+      <c r="D55" s="6">
+        <v>270.4</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1041.8</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1028</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-13.8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>734.9</v>
+      </c>
+      <c r="D57" s="6">
+        <v>733.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>482.2</v>
+      </c>
+      <c r="D58" s="6">
+        <v>474.95</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-7.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>11273</v>
+      </c>
+      <c r="D59" s="6">
+        <v>11297</v>
+      </c>
+      <c r="E59" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>328.95</v>
+      </c>
+      <c r="D60" s="6">
+        <v>320.55</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1241.3</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1222.9</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-18.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>81.68000000000001</v>
+      </c>
+      <c r="D62" s="6">
+        <v>81.16</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>22</v>
+      </c>
+      <c r="D63" s="6">
         <v>11</v>
       </c>
-      <c r="C26" s="7">
-        <v>21.99</v>
-      </c>
-      <c r="D26" s="7">
-        <v>21.39</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="E63" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>11</v>
+      </c>
+      <c r="D64" s="6">
+        <v>22</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>52.44</v>
+      </c>
+      <c r="D65" s="6">
+        <v>48.09</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>48.46</v>
-      </c>
-      <c r="D27" s="7">
-        <v>49.73</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>55.79</v>
+      </c>
+      <c r="D66" s="6">
+        <v>41.42</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-14.37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>3.73</v>
-      </c>
-      <c r="D28" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>38.91</v>
+      </c>
+      <c r="D67" s="6">
+        <v>36.09</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-4.72</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-5.12</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>51.49</v>
+      </c>
+      <c r="D68" s="6">
+        <v>51.05</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-11.06</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-10.57</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>43.38</v>
+      </c>
+      <c r="D69" s="6">
+        <v>40.59</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-32.75</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-32.46</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>49.07</v>
+      </c>
+      <c r="D70" s="6">
+        <v>49.98</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>11.29</v>
-      </c>
-      <c r="D32" s="7">
-        <v>6.51</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>40.63</v>
+      </c>
+      <c r="D71" s="6">
+        <v>36.63</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>4.73</v>
-      </c>
-      <c r="D33" s="7">
-        <v>8.15</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>51.28</v>
+      </c>
+      <c r="D72" s="6">
+        <v>47.16</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="D34" s="7">
-        <v>2.76</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>54.82</v>
+      </c>
+      <c r="D73" s="6">
+        <v>53.56</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>6.02</v>
-      </c>
-      <c r="D35" s="7">
-        <v>3.17</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-76.42</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-74.27</v>
+      </c>
+      <c r="E74" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>11.91</v>
-      </c>
-      <c r="D36" s="7">
-        <v>11.15</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>132.75</v>
+      </c>
+      <c r="D75" s="6">
+        <v>100.36</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-32.39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>1.97</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0.82</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-14.32</v>
+      </c>
+      <c r="D76" s="6">
+        <v>5.42</v>
+      </c>
+      <c r="E76" s="8">
+        <v>19.74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-0.13</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0.57</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>5.24</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-45.08</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-50.32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-10.83</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-15.06</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-4.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-34.59</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-58.96</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-24.37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>3.05</v>
-      </c>
-      <c r="D40" s="7">
-        <v>2.01</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-78.77</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-59.69</v>
+      </c>
+      <c r="E79" s="8">
+        <v>19.08</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-5.6</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-81.59999999999999</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-43.02</v>
+      </c>
+      <c r="E80" s="8">
+        <v>38.58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-1.7</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-1.25</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-28.8</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-128.37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>65.06999999999999</v>
-      </c>
-      <c r="D43" s="7">
-        <v>38.96</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-26.11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-30.65</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-31.78</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-5.02</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-6.9</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-18.9</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-19.17</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-14.81</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-15</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-19.57</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-19.63</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-48.95</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-49.14</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-7.48</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-10.51</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-7.43</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-11.57</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-10.68</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>698.75</v>
-      </c>
-      <c r="D53" s="7">
-        <v>687.35</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>301.55</v>
-      </c>
-      <c r="D54" s="7">
-        <v>295.6</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-5.95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1045.2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1041.8</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>736.55</v>
-      </c>
-      <c r="D56" s="7">
-        <v>734.9</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>482.6</v>
-      </c>
-      <c r="D57" s="7">
-        <v>482.2</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>11316</v>
-      </c>
-      <c r="D58" s="7">
-        <v>11273</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>340.1</v>
-      </c>
-      <c r="D59" s="7">
-        <v>328.95</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-11.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1216.3</v>
-      </c>
-      <c r="D60" s="7">
-        <v>1241.3</v>
-      </c>
-      <c r="E60" s="8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>80.87</v>
-      </c>
-      <c r="D61" s="7">
-        <v>81.68000000000001</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>88</v>
-      </c>
-      <c r="D62" s="7">
-        <v>99</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>34</v>
-      </c>
-      <c r="D63" s="7">
-        <v>33</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>23</v>
-      </c>
-      <c r="D64" s="7">
-        <v>22</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>12</v>
-      </c>
-      <c r="D65" s="7">
-        <v>11</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>66</v>
-      </c>
-      <c r="D66" s="7">
-        <v>44</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>45</v>
-      </c>
-      <c r="D67" s="7">
-        <v>66</v>
-      </c>
-      <c r="E67" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="7">
-        <v>99</v>
-      </c>
-      <c r="D68" s="7">
-        <v>88</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>55.32</v>
-      </c>
-      <c r="D69" s="7">
-        <v>52.44</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>60.38</v>
-      </c>
-      <c r="D70" s="7">
-        <v>55.79</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-4.59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>39.62</v>
-      </c>
-      <c r="D71" s="7">
-        <v>38.91</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>52.09</v>
-      </c>
-      <c r="D72" s="7">
-        <v>51.49</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>43.54</v>
-      </c>
-      <c r="D73" s="7">
-        <v>43.38</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>50.6</v>
-      </c>
-      <c r="D74" s="7">
-        <v>49.07</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>46.96</v>
-      </c>
-      <c r="D75" s="7">
-        <v>40.63</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-6.33</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>45.25</v>
-      </c>
-      <c r="D76" s="7">
-        <v>51.28</v>
-      </c>
-      <c r="E76" s="8">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" s="7">
-        <v>53.23</v>
-      </c>
-      <c r="D77" s="7">
-        <v>54.82</v>
-      </c>
-      <c r="E77" s="8">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="7">
-        <v>-82</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-76.42</v>
-      </c>
-      <c r="E78" s="8">
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>147.59</v>
-      </c>
-      <c r="D79" s="7">
-        <v>132.75</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-14.84</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>4.05</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-14.32</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-18.37</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-49.98</v>
-      </c>
-      <c r="D81" s="7">
-        <v>5.24</v>
-      </c>
-      <c r="E81" s="8">
-        <v>55.22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-45.36</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-34.59</v>
-      </c>
-      <c r="E82" s="8">
-        <v>10.77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-84.59999999999999</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-78.77</v>
-      </c>
-      <c r="E83" s="8">
-        <v>5.83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-58.35</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-81.59999999999999</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-23.25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>60.58</v>
-      </c>
-      <c r="D85" s="7">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="E85" s="8">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="7">
-        <v>71.54000000000001</v>
-      </c>
-      <c r="D86" s="7">
+      <c r="C82" s="6">
         <v>7.27</v>
       </c>
-      <c r="E86" s="9">
-        <v>-64.27</v>
+      <c r="D82" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-4.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3560,60 +3500,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>78</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>49.76000000000001</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>48.6</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11">
         <v>44.4</v>
       </c>
-      <c r="F2" s="12">
-        <v>-1.5</v>
-      </c>
-      <c r="G2" s="12">
-        <v>3.9</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>55</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>22.2</v>
       </c>
     </row>
@@ -3715,61 +3655,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3961</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3329</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.276</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1916</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1908</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1343</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0546</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0277</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0694</v>
+      <c r="A2" s="14">
+        <v>0.3815999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3395</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2646</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1945</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1917</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1367</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0561</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0254</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.0716</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,34 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.4 → 48.1</t>
+    <t>50.0 → 51.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>51.0 → 42.7</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>55.8 → 41.4</t>
-  </si>
-  <si>
-    <t>55.8</t>
-  </si>
-  <si>
-    <t>41.4</t>
-  </si>
-  <si>
-    <t>51.3 → 47.2</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>47.2</t>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>42.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +303,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -433,10 +427,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -807,8 +802,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -948,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>668.9</v>
+        <v>664.7</v>
       </c>
       <c r="D2">
-        <v>-2.68</v>
+        <v>-0.63</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -960,46 +954,46 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-33.61</v>
+        <v>-34.03</v>
       </c>
       <c r="H2">
-        <v>82.16</v>
+        <v>81.02</v>
       </c>
       <c r="I2">
-        <v>3.89</v>
+        <v>-8.48</v>
       </c>
       <c r="J2">
-        <v>-6.9</v>
+        <v>-10.36</v>
       </c>
       <c r="K2">
-        <v>-0.14</v>
+        <v>2.63</v>
       </c>
       <c r="L2">
-        <v>17.16</v>
+        <v>17.71</v>
       </c>
       <c r="M2">
-        <v>-7.16</v>
+        <v>-6.56</v>
       </c>
       <c r="N2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>696.41</v>
+        <v>684.09</v>
       </c>
       <c r="Q2">
-        <v>675.9</v>
+        <v>673.04</v>
       </c>
       <c r="R2">
-        <v>671.91</v>
+        <v>672.63</v>
       </c>
       <c r="S2">
-        <v>650.98</v>
+        <v>651.9</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1014,34 +1008,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.09</v>
+        <v>47.13</v>
       </c>
       <c r="Z2">
-        <v>0.77</v>
+        <v>-0.32</v>
       </c>
       <c r="AA2">
-        <v>-1.01</v>
+        <v>-0.88</v>
       </c>
       <c r="AB2">
-        <v>1.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC2">
-        <v>56.63</v>
+        <v>45.41</v>
       </c>
       <c r="AD2">
-        <v>68.29000000000001</v>
+        <v>56.42</v>
       </c>
       <c r="AE2">
-        <v>33.29</v>
+        <v>33.54</v>
       </c>
       <c r="AF2">
-        <v>-74.27</v>
+        <v>-74.51000000000001</v>
       </c>
       <c r="AG2">
-        <v>732.92</v>
+        <v>725.9400000000001</v>
       </c>
       <c r="AH2">
-        <v>618.88</v>
+        <v>620.15</v>
       </c>
       <c r="AI2">
         <v>603.87</v>
@@ -1050,7 +1044,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.57</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1061,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>270.4</v>
+        <v>249.6</v>
       </c>
       <c r="D3">
-        <v>-8.529999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1073,46 +1067,46 @@
         <v>153.23</v>
       </c>
       <c r="G3">
+        <v>-21.39</v>
+      </c>
+      <c r="H3">
+        <v>62.89</v>
+      </c>
+      <c r="I3">
+        <v>-15.99</v>
+      </c>
+      <c r="J3">
         <v>-14.83</v>
       </c>
-      <c r="H3">
-        <v>76.47</v>
-      </c>
-      <c r="I3">
-        <v>-4.47</v>
-      </c>
-      <c r="J3">
-        <v>-6.6</v>
-      </c>
       <c r="K3">
-        <v>3.11</v>
+        <v>-5.86</v>
       </c>
       <c r="L3">
-        <v>34.75</v>
+        <v>25.15</v>
       </c>
       <c r="M3">
-        <v>38.16</v>
+        <v>36.16</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="O3">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>292.77</v>
+        <v>283.27</v>
       </c>
       <c r="Q3">
-        <v>282.83</v>
+        <v>280.99</v>
       </c>
       <c r="R3">
-        <v>288.27</v>
+        <v>287.68</v>
       </c>
       <c r="S3">
-        <v>234.7</v>
+        <v>235.12</v>
       </c>
       <c r="T3">
-        <v>15.21</v>
+        <v>6.16</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1127,43 +1121,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.42</v>
+        <v>33.71</v>
       </c>
       <c r="Z3">
-        <v>-0.06</v>
+        <v>-2.96</v>
       </c>
       <c r="AA3">
-        <v>-0.86</v>
+        <v>-1.28</v>
       </c>
       <c r="AB3">
-        <v>0.8</v>
+        <v>-1.68</v>
       </c>
       <c r="AC3">
-        <v>64.63</v>
+        <v>31.3</v>
       </c>
       <c r="AD3">
-        <v>85.91</v>
+        <v>63.01</v>
       </c>
       <c r="AE3">
-        <v>13.45</v>
+        <v>14.15</v>
       </c>
       <c r="AF3">
-        <v>100.36</v>
+        <v>94.28</v>
       </c>
       <c r="AG3">
-        <v>302.88</v>
+        <v>305.84</v>
       </c>
       <c r="AH3">
-        <v>262.78</v>
+        <v>256.14</v>
       </c>
       <c r="AI3">
-        <v>268.82</v>
+        <v>299.27</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>29.68</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1174,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="D4">
-        <v>-1.32</v>
+        <v>0.88</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1186,46 +1180,46 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-20.24</v>
+        <v>-19.54</v>
       </c>
       <c r="H4">
-        <v>4.26</v>
+        <v>5.17</v>
       </c>
       <c r="I4">
-        <v>-0.36</v>
+        <v>0.76</v>
       </c>
       <c r="J4">
-        <v>-8.17</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K4">
-        <v>-1.6</v>
+        <v>-0.77</v>
       </c>
       <c r="L4">
-        <v>2.66</v>
+        <v>1.39</v>
       </c>
       <c r="M4">
-        <v>19.17</v>
+        <v>19.86</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1034.84</v>
+        <v>1036.4</v>
       </c>
       <c r="Q4">
-        <v>1081.66</v>
+        <v>1076.46</v>
       </c>
       <c r="R4">
-        <v>1112.52</v>
+        <v>1110.76</v>
       </c>
       <c r="S4">
-        <v>1139.94</v>
+        <v>1139.79</v>
       </c>
       <c r="T4">
-        <v>-9.82</v>
+        <v>-9.02</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1240,43 +1234,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.09</v>
+        <v>39.19</v>
       </c>
       <c r="Z4">
-        <v>-27.01</v>
+        <v>-25.96</v>
       </c>
       <c r="AA4">
-        <v>-23.64</v>
+        <v>-24.1</v>
       </c>
       <c r="AB4">
-        <v>-3.38</v>
+        <v>-1.86</v>
       </c>
       <c r="AC4">
-        <v>47.79</v>
+        <v>57.45</v>
       </c>
       <c r="AD4">
-        <v>41.35</v>
+        <v>49.37</v>
       </c>
       <c r="AE4">
-        <v>30.45</v>
+        <v>31.08</v>
       </c>
       <c r="AF4">
-        <v>5.42</v>
+        <v>-24.22</v>
       </c>
       <c r="AG4">
-        <v>1196.3</v>
+        <v>1189.18</v>
       </c>
       <c r="AH4">
-        <v>967.02</v>
+        <v>963.74</v>
       </c>
       <c r="AI4">
-        <v>1118.75</v>
+        <v>1113.63</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>47.78</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1287,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>733.75</v>
+        <v>709.65</v>
       </c>
       <c r="D5">
-        <v>-0.16</v>
+        <v>-3.28</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1299,46 +1293,46 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-15.13</v>
+        <v>-17.92</v>
       </c>
       <c r="H5">
-        <v>10.86</v>
+        <v>7.21</v>
       </c>
       <c r="I5">
-        <v>1.83</v>
+        <v>-0.62</v>
       </c>
       <c r="J5">
-        <v>-2.29</v>
+        <v>-5.56</v>
       </c>
       <c r="K5">
-        <v>-0.72</v>
+        <v>-3.89</v>
       </c>
       <c r="L5">
-        <v>-6.28</v>
+        <v>-12.16</v>
       </c>
       <c r="M5">
-        <v>33.95</v>
+        <v>33.85</v>
       </c>
       <c r="N5">
         <v>33</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>728.78</v>
+        <v>727.9</v>
       </c>
       <c r="Q5">
-        <v>733.22</v>
+        <v>731.53</v>
       </c>
       <c r="R5">
-        <v>731.6</v>
+        <v>731.14</v>
       </c>
       <c r="S5">
-        <v>742.76</v>
+        <v>742.04</v>
       </c>
       <c r="T5">
-        <v>-1.21</v>
+        <v>-4.37</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1353,34 +1347,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>51.05</v>
+        <v>42.73</v>
       </c>
       <c r="Z5">
-        <v>-2.24</v>
+        <v>-3.6</v>
       </c>
       <c r="AA5">
-        <v>-2.57</v>
+        <v>-2.78</v>
       </c>
       <c r="AB5">
-        <v>0.34</v>
+        <v>-0.82</v>
       </c>
       <c r="AC5">
-        <v>81.45</v>
+        <v>59.12</v>
       </c>
       <c r="AD5">
-        <v>70.72</v>
+        <v>71.59</v>
       </c>
       <c r="AE5">
-        <v>21.2</v>
+        <v>21.94</v>
       </c>
       <c r="AF5">
-        <v>-45.08</v>
+        <v>-46.31</v>
       </c>
       <c r="AG5">
-        <v>763.78</v>
+        <v>763.42</v>
       </c>
       <c r="AH5">
-        <v>702.66</v>
+        <v>699.64</v>
       </c>
       <c r="AI5">
         <v>771.61</v>
@@ -1389,7 +1383,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>17.93</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1400,10 +1394,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>474.95</v>
+        <v>463.9</v>
       </c>
       <c r="D6">
-        <v>-1.5</v>
+        <v>-2.33</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1412,46 +1406,46 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-20.84</v>
+        <v>-22.68</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>5.78</v>
       </c>
       <c r="I6">
-        <v>3.14</v>
+        <v>-5.38</v>
       </c>
       <c r="J6">
-        <v>-9.710000000000001</v>
+        <v>-10.27</v>
       </c>
       <c r="K6">
-        <v>-16.12</v>
+        <v>-17.41</v>
       </c>
       <c r="L6">
-        <v>-12.68</v>
+        <v>-15.15</v>
       </c>
       <c r="M6">
-        <v>5.61</v>
+        <v>4.56</v>
       </c>
       <c r="N6">
         <v>11</v>
       </c>
       <c r="O6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P6">
-        <v>481.8</v>
+        <v>476.52</v>
       </c>
       <c r="Q6">
-        <v>488.48</v>
+        <v>485.77</v>
       </c>
       <c r="R6">
-        <v>518.14</v>
+        <v>515.86</v>
       </c>
       <c r="S6">
-        <v>523.6799999999999</v>
+        <v>523.5</v>
       </c>
       <c r="T6">
-        <v>-9.31</v>
+        <v>-11.38</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1466,34 +1460,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>40.59</v>
+        <v>36.71</v>
       </c>
       <c r="Z6">
-        <v>-12.27</v>
+        <v>-12.77</v>
       </c>
       <c r="AA6">
-        <v>-13.61</v>
+        <v>-13.44</v>
       </c>
       <c r="AB6">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AC6">
-        <v>81.69</v>
+        <v>69.38</v>
       </c>
       <c r="AD6">
-        <v>84.64</v>
+        <v>78.31</v>
       </c>
       <c r="AE6">
-        <v>13.45</v>
+        <v>13.36</v>
       </c>
       <c r="AF6">
-        <v>-58.96</v>
+        <v>-55.52</v>
       </c>
       <c r="AG6">
-        <v>523.3200000000001</v>
+        <v>519.35</v>
       </c>
       <c r="AH6">
-        <v>453.63</v>
+        <v>452.2</v>
       </c>
       <c r="AI6">
         <v>500.78</v>
@@ -1502,7 +1496,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.06</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11297</v>
+        <v>11344</v>
       </c>
       <c r="D7">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1525,46 +1519,46 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-49.03</v>
+        <v>-48.82</v>
       </c>
       <c r="H7">
-        <v>6.03</v>
+        <v>6.47</v>
       </c>
       <c r="I7">
-        <v>-0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J7">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="K7">
-        <v>2.88</v>
+        <v>3.93</v>
       </c>
       <c r="L7">
-        <v>-31.89</v>
+        <v>-32.96</v>
       </c>
       <c r="M7">
-        <v>19.45</v>
+        <v>19.6</v>
       </c>
       <c r="N7">
         <v>22</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>11286.4</v>
+        <v>11290.4</v>
       </c>
       <c r="Q7">
-        <v>11243.25</v>
+        <v>11249.5</v>
       </c>
       <c r="R7">
-        <v>11396.56</v>
+        <v>11386.4</v>
       </c>
       <c r="S7">
-        <v>13447.15</v>
+        <v>13405</v>
       </c>
       <c r="T7">
-        <v>-15.99</v>
+        <v>-15.37</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1579,34 +1573,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>49.98</v>
+        <v>51.79</v>
       </c>
       <c r="Z7">
-        <v>-15.81</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="AA7">
-        <v>-32.73</v>
+        <v>-28.07</v>
       </c>
       <c r="AB7">
-        <v>16.92</v>
+        <v>18.62</v>
       </c>
       <c r="AC7">
-        <v>81.81999999999999</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="AD7">
-        <v>80.12</v>
+        <v>80.89</v>
       </c>
       <c r="AE7">
-        <v>266.63</v>
+        <v>311.87</v>
       </c>
       <c r="AF7">
-        <v>-59.69</v>
+        <v>-74.19</v>
       </c>
       <c r="AG7">
-        <v>11466.47</v>
+        <v>11476.82</v>
       </c>
       <c r="AH7">
-        <v>11020.03</v>
+        <v>11022.18</v>
       </c>
       <c r="AI7">
         <v>12101.38</v>
@@ -1615,7 +1609,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>11.78</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1626,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>320.55</v>
+        <v>321.6</v>
       </c>
       <c r="D8">
-        <v>-2.55</v>
+        <v>0.33</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1638,46 +1632,46 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-12.8</v>
+        <v>-12.51</v>
       </c>
       <c r="H8">
-        <v>36.81</v>
+        <v>37.25</v>
       </c>
       <c r="I8">
-        <v>-6.63</v>
+        <v>-5.91</v>
       </c>
       <c r="J8">
-        <v>-7.95</v>
+        <v>-8.01</v>
       </c>
       <c r="K8">
-        <v>-6.97</v>
+        <v>-2.55</v>
       </c>
       <c r="L8">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="M8">
-        <v>26.46</v>
+        <v>26.57</v>
       </c>
       <c r="N8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P8">
-        <v>333.21</v>
+        <v>329.17</v>
       </c>
       <c r="Q8">
-        <v>348.21</v>
+        <v>345.91</v>
       </c>
       <c r="R8">
-        <v>341.69</v>
+        <v>341.28</v>
       </c>
       <c r="S8">
-        <v>296.25</v>
+        <v>296.44</v>
       </c>
       <c r="T8">
-        <v>8.199999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1692,43 +1686,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>36.63</v>
+        <v>37.46</v>
       </c>
       <c r="Z8">
-        <v>-3.38</v>
+        <v>-4.47</v>
       </c>
       <c r="AA8">
-        <v>0.09</v>
+        <v>-0.82</v>
       </c>
       <c r="AB8">
-        <v>-3.48</v>
+        <v>-3.65</v>
       </c>
       <c r="AC8">
-        <v>8.529999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="AD8">
-        <v>12.41</v>
+        <v>6.61</v>
       </c>
       <c r="AE8">
-        <v>11.8</v>
+        <v>11.99</v>
       </c>
       <c r="AF8">
-        <v>-43.02</v>
+        <v>-36.49</v>
       </c>
       <c r="AG8">
-        <v>374.67</v>
+        <v>373.26</v>
       </c>
       <c r="AH8">
-        <v>321.76</v>
+        <v>318.57</v>
       </c>
       <c r="AI8">
-        <v>361.71</v>
+        <v>354.52</v>
       </c>
       <c r="AJ8" t="s">
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>32.82</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1739,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1222.9</v>
+        <v>1220</v>
       </c>
       <c r="D9">
-        <v>-1.48</v>
+        <v>-0.24</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1751,46 +1745,46 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-8.81</v>
+        <v>-9.02</v>
       </c>
       <c r="H9">
-        <v>13.3</v>
+        <v>13.04</v>
       </c>
       <c r="I9">
-        <v>3.94</v>
+        <v>3.72</v>
       </c>
       <c r="J9">
-        <v>-4.13</v>
+        <v>-3.83</v>
       </c>
       <c r="K9">
-        <v>-3.51</v>
+        <v>-3.7</v>
       </c>
       <c r="L9">
-        <v>5.35</v>
+        <v>4.09</v>
       </c>
       <c r="M9">
-        <v>13.67</v>
+        <v>13.83</v>
       </c>
       <c r="N9">
         <v>66</v>
       </c>
       <c r="O9">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P9">
-        <v>1211.42</v>
+        <v>1220.18</v>
       </c>
       <c r="Q9">
-        <v>1230.64</v>
+        <v>1228.29</v>
       </c>
       <c r="R9">
-        <v>1268.23</v>
+        <v>1266.59</v>
       </c>
       <c r="S9">
-        <v>1243.83</v>
+        <v>1244.07</v>
       </c>
       <c r="T9">
-        <v>-1.68</v>
+        <v>-1.93</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1805,34 +1799,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>47.16</v>
+        <v>46.53</v>
       </c>
       <c r="Z9">
-        <v>-18.14</v>
+        <v>-16.46</v>
       </c>
       <c r="AA9">
-        <v>-21.12</v>
+        <v>-20.19</v>
       </c>
       <c r="AB9">
-        <v>2.98</v>
+        <v>3.73</v>
       </c>
       <c r="AC9">
-        <v>88.62</v>
+        <v>85.39</v>
       </c>
       <c r="AD9">
-        <v>74.16</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="AE9">
-        <v>30.57</v>
+        <v>30.35</v>
       </c>
       <c r="AF9">
-        <v>-28.8</v>
+        <v>-21.75</v>
       </c>
       <c r="AG9">
-        <v>1312.12</v>
+        <v>1308.05</v>
       </c>
       <c r="AH9">
-        <v>1149.15</v>
+        <v>1148.52</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1841,7 +1835,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>33.77</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1852,10 +1846,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.16</v>
+        <v>81.31</v>
       </c>
       <c r="D10">
-        <v>-0.64</v>
+        <v>0.18</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1864,46 +1858,46 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.25</v>
+        <v>-11.09</v>
       </c>
       <c r="H10">
-        <v>124.94</v>
+        <v>125.36</v>
       </c>
       <c r="I10">
-        <v>-0.58</v>
+        <v>-2.33</v>
       </c>
       <c r="J10">
-        <v>0.32</v>
+        <v>1.43</v>
       </c>
       <c r="K10">
-        <v>17.54</v>
+        <v>21.25</v>
       </c>
       <c r="L10">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="M10">
-        <v>-2.54</v>
+        <v>-2.37</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>81.69</v>
+        <v>81.3</v>
       </c>
       <c r="Q10">
-        <v>78.63</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="R10">
-        <v>81.34999999999999</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="S10">
-        <v>62.58</v>
+        <v>62.67</v>
       </c>
       <c r="T10">
-        <v>29.69</v>
+        <v>29.75</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1918,34 +1912,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>53.56</v>
+        <v>53.89</v>
       </c>
       <c r="Z10">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AB10">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="AC10">
-        <v>73.14</v>
+        <v>72.34</v>
       </c>
       <c r="AD10">
-        <v>78.16</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AE10">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="AF10">
-        <v>2.7</v>
+        <v>53.17</v>
       </c>
       <c r="AG10">
-        <v>83.59</v>
+        <v>83.89</v>
       </c>
       <c r="AH10">
-        <v>73.68000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1954,7 +1948,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>25.08</v>
+        <v>22.34</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2135,7 +2129,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2154,1333 +2148,1364 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-6.9</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-10.36</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-6.6</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-14.83</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-8.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-8.17</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-2.29</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5.56</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-10.27</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.24</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-7.95</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-8.01</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-4.13</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-3.83</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.43</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>3.89</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-8.48</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-12.37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-4.47</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-15.99</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-11.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.36</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-0.62</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>3.14</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-5.38</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-8.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.2</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-6.63</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-5.91</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>3.94</v>
+      </c>
+      <c r="D24" s="7">
+        <v>3.72</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.58</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.33</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>17.16</v>
+      </c>
+      <c r="D26" s="7">
+        <v>17.71</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>34.75</v>
+      </c>
+      <c r="D27" s="7">
+        <v>25.15</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>2.66</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1.39</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-6.28</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-12.16</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-5.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-12.68</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-15.15</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-31.89</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-32.96</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>3.64</v>
+      </c>
+      <c r="D32" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>5.35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2.3</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-0.14</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2.63</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3.11</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-5.86</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-8.970000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-0.77</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-0.72</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-3.89</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-16.12</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-17.41</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2.88</v>
+      </c>
+      <c r="D40" s="7">
+        <v>3.93</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-2.55</v>
+      </c>
+      <c r="E41" s="9">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-3.51</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>17.54</v>
+      </c>
+      <c r="D43" s="7">
+        <v>21.25</v>
+      </c>
+      <c r="E43" s="9">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-33.61</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-34.03</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-14.83</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-21.39</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-6.56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-20.24</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-19.54</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-15.13</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-17.92</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-20.84</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-22.68</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-49.03</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-48.82</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-12.8</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-12.51</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-8.81</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-9.02</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-11.25</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-11.09</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>668.9</v>
+      </c>
+      <c r="D53" s="7">
+        <v>664.7</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>270.4</v>
+      </c>
+      <c r="D54" s="7">
+        <v>249.6</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-20.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1028</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1037</v>
+      </c>
+      <c r="E55" s="9">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>733.75</v>
+      </c>
+      <c r="D56" s="7">
+        <v>709.65</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-24.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>474.95</v>
+      </c>
+      <c r="D57" s="7">
+        <v>463.9</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-11.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>11297</v>
+      </c>
+      <c r="D58" s="7">
+        <v>11344</v>
+      </c>
+      <c r="E58" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>320.55</v>
+      </c>
+      <c r="D59" s="7">
+        <v>321.6</v>
+      </c>
+      <c r="E59" s="9">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1222.9</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1220</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>81.16</v>
+      </c>
+      <c r="D61" s="7">
+        <v>81.31</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7">
+        <v>88</v>
+      </c>
+      <c r="E62" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.6</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-8.109999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>99</v>
+      </c>
+      <c r="D63" s="7">
+        <v>77</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-7.67</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-8.17</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>55</v>
+      </c>
+      <c r="D64" s="7">
+        <v>44</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>44</v>
+      </c>
+      <c r="D65" s="7">
+        <v>55</v>
+      </c>
+      <c r="E65" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>88</v>
+      </c>
+      <c r="D66" s="7">
+        <v>99</v>
+      </c>
+      <c r="E66" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>48.09</v>
+      </c>
+      <c r="D67" s="7">
+        <v>47.13</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>41.42</v>
+      </c>
+      <c r="D68" s="7">
+        <v>33.71</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-7.71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>36.09</v>
+      </c>
+      <c r="D69" s="7">
+        <v>39.19</v>
+      </c>
+      <c r="E69" s="9">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-2.29</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>51.05</v>
+      </c>
+      <c r="D70" s="7">
+        <v>42.73</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-8.32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.82</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>40.59</v>
+      </c>
+      <c r="D71" s="7">
+        <v>36.71</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-3.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.14</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>49.98</v>
+      </c>
+      <c r="D72" s="7">
+        <v>51.79</v>
+      </c>
+      <c r="E72" s="9">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-7.95</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-8.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>36.63</v>
+      </c>
+      <c r="D73" s="7">
+        <v>37.46</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>47.16</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46.53</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.24</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>53.56</v>
+      </c>
+      <c r="D75" s="7">
+        <v>53.89</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>6.58</v>
-      </c>
-      <c r="D18" s="6">
-        <v>3.89</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-74.27</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-74.51000000000001</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>5.16</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-4.47</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-9.630000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>100.36</v>
+      </c>
+      <c r="D77" s="7">
+        <v>94.28</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-6.08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2.89</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>5.42</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-24.22</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-29.64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3.96</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.83</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-45.08</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-46.31</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.18</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3.14</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-58.96</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-55.52</v>
+      </c>
+      <c r="E80" s="9">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-59.69</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-74.19</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-6.63</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-43.02</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-36.49</v>
+      </c>
+      <c r="E82" s="9">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>5.82</v>
-      </c>
-      <c r="D25" s="6">
-        <v>3.94</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-28.8</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-21.75</v>
+      </c>
+      <c r="E83" s="9">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>3.92</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>21.39</v>
-      </c>
-      <c r="D27" s="6">
-        <v>17.16</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>49.73</v>
-      </c>
-      <c r="D28" s="6">
-        <v>34.75</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-14.98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>4.6</v>
-      </c>
-      <c r="D29" s="6">
-        <v>2.66</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.28</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-10.57</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-12.68</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-32.46</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-31.89</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6.51</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.64</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>8.15</v>
-      </c>
-      <c r="D34" s="6">
-        <v>5.35</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>2.76</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>11.15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-8.039999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>0.82</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-0.72</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-15.06</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-16.12</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>2.01</v>
-      </c>
-      <c r="D41" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-5.6</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-6.97</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>38.96</v>
-      </c>
-      <c r="D44" s="6">
-        <v>17.54</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-21.42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-31.78</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-33.61</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.83</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-7.93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-19.17</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-20.24</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-15</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-15.13</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-19.63</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-20.84</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-49.14</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-49.03</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-12.8</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-7.43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-8.81</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-11.25</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>687.35</v>
-      </c>
-      <c r="D54" s="6">
-        <v>668.9</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-18.45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>295.6</v>
-      </c>
-      <c r="D55" s="6">
-        <v>270.4</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-25.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1041.8</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1028</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-13.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>734.9</v>
-      </c>
-      <c r="D57" s="6">
-        <v>733.75</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>482.2</v>
-      </c>
-      <c r="D58" s="6">
-        <v>474.95</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-7.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>11273</v>
-      </c>
-      <c r="D59" s="6">
-        <v>11297</v>
-      </c>
-      <c r="E59" s="8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>328.95</v>
-      </c>
-      <c r="D60" s="6">
-        <v>320.55</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-8.4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1241.3</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1222.9</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-18.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>81.68000000000001</v>
-      </c>
-      <c r="D62" s="6">
-        <v>81.16</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>22</v>
-      </c>
-      <c r="D63" s="6">
-        <v>11</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>11</v>
-      </c>
-      <c r="D64" s="6">
-        <v>22</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>52.44</v>
-      </c>
-      <c r="D65" s="6">
-        <v>48.09</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>55.79</v>
-      </c>
-      <c r="D66" s="6">
-        <v>41.42</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-14.37</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>38.91</v>
-      </c>
-      <c r="D67" s="6">
-        <v>36.09</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>51.49</v>
-      </c>
-      <c r="D68" s="6">
-        <v>51.05</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>43.38</v>
-      </c>
-      <c r="D69" s="6">
-        <v>40.59</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>49.07</v>
-      </c>
-      <c r="D70" s="6">
-        <v>49.98</v>
-      </c>
-      <c r="E70" s="8">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>40.63</v>
-      </c>
-      <c r="D71" s="6">
-        <v>36.63</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>51.28</v>
-      </c>
-      <c r="D72" s="6">
-        <v>47.16</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-4.12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>54.82</v>
-      </c>
-      <c r="D73" s="6">
-        <v>53.56</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="5" t="s">
+      <c r="B84" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="6">
-        <v>-76.42</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-74.27</v>
-      </c>
-      <c r="E74" s="8">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>132.75</v>
-      </c>
-      <c r="D75" s="6">
-        <v>100.36</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-32.39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-14.32</v>
-      </c>
-      <c r="D76" s="6">
-        <v>5.42</v>
-      </c>
-      <c r="E76" s="8">
-        <v>19.74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>5.24</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-45.08</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-50.32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-34.59</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-58.96</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-24.37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-78.77</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-59.69</v>
-      </c>
-      <c r="E79" s="8">
-        <v>19.08</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-81.59999999999999</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-43.02</v>
-      </c>
-      <c r="E80" s="8">
-        <v>38.58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-28.8</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-128.37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>7.27</v>
-      </c>
-      <c r="D82" s="6">
+      <c r="C84" s="7">
         <v>2.7</v>
       </c>
-      <c r="E82" s="7">
-        <v>-4.57</v>
+      <c r="D84" s="7">
+        <v>53.17</v>
+      </c>
+      <c r="E84" s="9">
+        <v>50.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3500,60 +3525,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>49.76000000000001</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>43.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>44.4</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-0.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>55</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>22.2</v>
       </c>
     </row>
@@ -3655,61 +3680,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3815999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3395</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2646</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1917</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1367</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0561</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0254</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0716</v>
+      <c r="A2" s="15">
+        <v>0.3616</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3385</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2657</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1986</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.196</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1383</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.04559999999999999</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0237</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.06559999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/JINDAL_GROUP_Technical_Metrics.xlsx
+++ b/JINDAL_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="84">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -196,28 +196,43 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 51.8</t>
+    <t>47.1 → 61.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>50.0</t>
+    <t>47.1</t>
+  </si>
+  <si>
+    <t>61.7</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>51.8 → 48.3</t>
   </si>
   <si>
     <t>51.8</t>
   </si>
   <si>
-    <t>51.0 → 42.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>42.7</t>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>53.9 → 44.9</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>44.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -430,8 +445,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -802,7 +817,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -942,10 +958,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>664.7</v>
+        <v>739.35</v>
       </c>
       <c r="D2">
-        <v>-0.63</v>
+        <v>11.23</v>
       </c>
       <c r="E2">
         <v>1007.6</v>
@@ -954,97 +970,97 @@
         <v>367.2</v>
       </c>
       <c r="G2">
-        <v>-34.03</v>
+        <v>-26.62</v>
       </c>
       <c r="H2">
-        <v>81.02</v>
+        <v>101.35</v>
       </c>
       <c r="I2">
-        <v>-8.48</v>
+        <v>5.51</v>
       </c>
       <c r="J2">
-        <v>-10.36</v>
+        <v>2.42</v>
       </c>
       <c r="K2">
-        <v>2.63</v>
+        <v>15.9</v>
       </c>
       <c r="L2">
-        <v>17.71</v>
+        <v>31.77</v>
       </c>
       <c r="M2">
-        <v>-6.56</v>
+        <v>-4.58</v>
       </c>
       <c r="N2">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="P2">
-        <v>684.09</v>
+        <v>691.8099999999999</v>
       </c>
       <c r="Q2">
-        <v>673.04</v>
+        <v>674.25</v>
       </c>
       <c r="R2">
-        <v>672.63</v>
+        <v>674.83</v>
       </c>
       <c r="S2">
-        <v>651.9</v>
+        <v>653.2</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>13.19</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
         <v>47</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.13</v>
+        <v>61.74</v>
       </c>
       <c r="Z2">
-        <v>-0.32</v>
+        <v>4.78</v>
       </c>
       <c r="AA2">
-        <v>-0.88</v>
+        <v>0.26</v>
       </c>
       <c r="AB2">
-        <v>0.5600000000000001</v>
+        <v>4.53</v>
       </c>
       <c r="AC2">
-        <v>45.41</v>
+        <v>58.15</v>
       </c>
       <c r="AD2">
-        <v>56.42</v>
+        <v>53.4</v>
       </c>
       <c r="AE2">
-        <v>33.54</v>
+        <v>40.53</v>
       </c>
       <c r="AF2">
-        <v>-74.51000000000001</v>
+        <v>17521.43</v>
       </c>
       <c r="AG2">
-        <v>725.9400000000001</v>
+        <v>732.0700000000001</v>
       </c>
       <c r="AH2">
-        <v>620.15</v>
+        <v>616.4299999999999</v>
       </c>
       <c r="AI2">
-        <v>603.87</v>
+        <v>609.45</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.38</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1071,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>249.6</v>
+        <v>232.15</v>
       </c>
       <c r="D3">
-        <v>-7.69</v>
+        <v>-6.99</v>
       </c>
       <c r="E3">
         <v>317.5</v>
@@ -1067,97 +1083,97 @@
         <v>153.23</v>
       </c>
       <c r="G3">
-        <v>-21.39</v>
+        <v>-26.88</v>
       </c>
       <c r="H3">
-        <v>62.89</v>
+        <v>51.5</v>
       </c>
       <c r="I3">
-        <v>-15.99</v>
+        <v>-22.41</v>
       </c>
       <c r="J3">
-        <v>-14.83</v>
+        <v>-18.96</v>
       </c>
       <c r="K3">
-        <v>-5.86</v>
+        <v>-11.04</v>
       </c>
       <c r="L3">
-        <v>25.15</v>
+        <v>22.9</v>
       </c>
       <c r="M3">
-        <v>36.16</v>
+        <v>34.93</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>283.27</v>
+        <v>269.86</v>
       </c>
       <c r="Q3">
-        <v>280.99</v>
+        <v>277.97</v>
       </c>
       <c r="R3">
-        <v>287.68</v>
+        <v>286.85</v>
       </c>
       <c r="S3">
-        <v>235.12</v>
+        <v>235.44</v>
       </c>
       <c r="T3">
-        <v>6.16</v>
+        <v>-1.4</v>
       </c>
       <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>47</v>
       </c>
-      <c r="W3" t="s">
-        <v>48</v>
-      </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>33.71</v>
+        <v>28.85</v>
       </c>
       <c r="Z3">
-        <v>-2.96</v>
+        <v>-6.58</v>
       </c>
       <c r="AA3">
-        <v>-1.28</v>
+        <v>-2.34</v>
       </c>
       <c r="AB3">
-        <v>-1.68</v>
+        <v>-4.24</v>
       </c>
       <c r="AC3">
-        <v>31.3</v>
+        <v>4.86</v>
       </c>
       <c r="AD3">
-        <v>63.01</v>
+        <v>33.6</v>
       </c>
       <c r="AE3">
-        <v>14.15</v>
+        <v>14.62</v>
       </c>
       <c r="AF3">
-        <v>94.28</v>
+        <v>66.89</v>
       </c>
       <c r="AG3">
-        <v>305.84</v>
+        <v>310.41</v>
       </c>
       <c r="AH3">
-        <v>256.14</v>
+        <v>245.52</v>
       </c>
       <c r="AI3">
-        <v>299.27</v>
+        <v>285.07</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>30.74</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1184,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1037</v>
+        <v>1015.9</v>
       </c>
       <c r="D4">
-        <v>0.88</v>
+        <v>-2.03</v>
       </c>
       <c r="E4">
         <v>1288.8</v>
@@ -1180,25 +1196,25 @@
         <v>986</v>
       </c>
       <c r="G4">
-        <v>-19.54</v>
+        <v>-21.17</v>
       </c>
       <c r="H4">
-        <v>5.17</v>
+        <v>3.03</v>
       </c>
       <c r="I4">
-        <v>0.76</v>
+        <v>-1.37</v>
       </c>
       <c r="J4">
-        <v>-8.279999999999999</v>
+        <v>-10.96</v>
       </c>
       <c r="K4">
-        <v>-0.77</v>
+        <v>-2.5</v>
       </c>
       <c r="L4">
-        <v>1.39</v>
+        <v>0.82</v>
       </c>
       <c r="M4">
-        <v>19.86</v>
+        <v>19.38</v>
       </c>
       <c r="N4">
         <v>44</v>
@@ -1207,70 +1223,70 @@
         <v>69</v>
       </c>
       <c r="P4">
-        <v>1036.4</v>
+        <v>1033.58</v>
       </c>
       <c r="Q4">
-        <v>1076.46</v>
+        <v>1068.49</v>
       </c>
       <c r="R4">
-        <v>1110.76</v>
+        <v>1109.18</v>
       </c>
       <c r="S4">
-        <v>1139.79</v>
+        <v>1139.46</v>
       </c>
       <c r="T4">
-        <v>-9.02</v>
+        <v>-10.84</v>
       </c>
       <c r="U4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.19</v>
+        <v>34.92</v>
       </c>
       <c r="Z4">
-        <v>-25.96</v>
+        <v>-26.53</v>
       </c>
       <c r="AA4">
-        <v>-24.1</v>
+        <v>-24.59</v>
       </c>
       <c r="AB4">
-        <v>-1.86</v>
+        <v>-1.94</v>
       </c>
       <c r="AC4">
-        <v>57.45</v>
+        <v>58.35</v>
       </c>
       <c r="AD4">
-        <v>49.37</v>
+        <v>54.53</v>
       </c>
       <c r="AE4">
-        <v>31.08</v>
+        <v>31.15</v>
       </c>
       <c r="AF4">
-        <v>-24.22</v>
+        <v>-36.23</v>
       </c>
       <c r="AG4">
-        <v>1189.18</v>
+        <v>1174.11</v>
       </c>
       <c r="AH4">
-        <v>963.74</v>
+        <v>962.87</v>
       </c>
       <c r="AI4">
-        <v>1113.63</v>
+        <v>1112.9</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>48.7</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>709.65</v>
+        <v>687.4</v>
       </c>
       <c r="D5">
-        <v>-3.28</v>
+        <v>-3.14</v>
       </c>
       <c r="E5">
         <v>864.58</v>
@@ -1293,25 +1309,25 @@
         <v>661.9</v>
       </c>
       <c r="G5">
-        <v>-17.92</v>
+        <v>-20.49</v>
       </c>
       <c r="H5">
-        <v>7.21</v>
+        <v>3.85</v>
       </c>
       <c r="I5">
-        <v>-0.62</v>
+        <v>-5.14</v>
       </c>
       <c r="J5">
-        <v>-5.56</v>
+        <v>-7.54</v>
       </c>
       <c r="K5">
-        <v>-3.89</v>
+        <v>-6.58</v>
       </c>
       <c r="L5">
-        <v>-12.16</v>
+        <v>-13.06</v>
       </c>
       <c r="M5">
-        <v>33.85</v>
+        <v>33.22</v>
       </c>
       <c r="N5">
         <v>33</v>
@@ -1320,70 +1336,70 @@
         <v>57</v>
       </c>
       <c r="P5">
-        <v>727.9</v>
+        <v>720.45</v>
       </c>
       <c r="Q5">
-        <v>731.53</v>
+        <v>727.97</v>
       </c>
       <c r="R5">
-        <v>731.14</v>
+        <v>730.38</v>
       </c>
       <c r="S5">
-        <v>742.04</v>
+        <v>741.21</v>
       </c>
       <c r="T5">
-        <v>-4.37</v>
+        <v>-7.26</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
       </c>
       <c r="V5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>42.73</v>
+        <v>36.77</v>
       </c>
       <c r="Z5">
-        <v>-3.6</v>
+        <v>-6.41</v>
       </c>
       <c r="AA5">
-        <v>-2.78</v>
+        <v>-3.51</v>
       </c>
       <c r="AB5">
-        <v>-0.82</v>
+        <v>-2.9</v>
       </c>
       <c r="AC5">
-        <v>59.12</v>
+        <v>32.1</v>
       </c>
       <c r="AD5">
-        <v>71.59</v>
+        <v>57.55</v>
       </c>
       <c r="AE5">
-        <v>21.94</v>
+        <v>22.8</v>
       </c>
       <c r="AF5">
-        <v>-46.31</v>
+        <v>34.82</v>
       </c>
       <c r="AG5">
-        <v>763.42</v>
+        <v>762.9</v>
       </c>
       <c r="AH5">
-        <v>699.64</v>
+        <v>693.05</v>
       </c>
       <c r="AI5">
-        <v>771.61</v>
+        <v>764.0599999999999</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>18.78</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>463.9</v>
+        <v>448.55</v>
       </c>
       <c r="D6">
-        <v>-2.33</v>
+        <v>-3.31</v>
       </c>
       <c r="E6">
         <v>600.01</v>
@@ -1406,97 +1422,97 @@
         <v>438.56</v>
       </c>
       <c r="G6">
-        <v>-22.68</v>
+        <v>-25.24</v>
       </c>
       <c r="H6">
-        <v>5.78</v>
+        <v>2.28</v>
       </c>
       <c r="I6">
-        <v>-5.38</v>
+        <v>-6.35</v>
       </c>
       <c r="J6">
-        <v>-10.27</v>
+        <v>-13.41</v>
       </c>
       <c r="K6">
-        <v>-17.41</v>
+        <v>-19.52</v>
       </c>
       <c r="L6">
-        <v>-15.15</v>
+        <v>-16.78</v>
       </c>
       <c r="M6">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="N6">
         <v>11</v>
       </c>
       <c r="O6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P6">
-        <v>476.52</v>
+        <v>470.44</v>
       </c>
       <c r="Q6">
-        <v>485.77</v>
+        <v>482.15</v>
       </c>
       <c r="R6">
-        <v>515.86</v>
+        <v>513.5700000000001</v>
       </c>
       <c r="S6">
-        <v>523.5</v>
+        <v>523.2</v>
       </c>
       <c r="T6">
-        <v>-11.38</v>
+        <v>-14.27</v>
       </c>
       <c r="U6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.71</v>
+        <v>32.12</v>
       </c>
       <c r="Z6">
-        <v>-12.77</v>
+        <v>-14.24</v>
       </c>
       <c r="AA6">
-        <v>-13.44</v>
+        <v>-13.6</v>
       </c>
       <c r="AB6">
-        <v>0.67</v>
+        <v>-0.64</v>
       </c>
       <c r="AC6">
-        <v>69.38</v>
+        <v>49.05</v>
       </c>
       <c r="AD6">
-        <v>78.31</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AE6">
-        <v>13.36</v>
+        <v>14.18</v>
       </c>
       <c r="AF6">
-        <v>-55.52</v>
+        <v>15.02</v>
       </c>
       <c r="AG6">
-        <v>519.35</v>
+        <v>515.35</v>
       </c>
       <c r="AH6">
-        <v>452.2</v>
+        <v>448.95</v>
       </c>
       <c r="AI6">
-        <v>500.78</v>
+        <v>495.09</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.34</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>11344</v>
+        <v>11258</v>
       </c>
       <c r="D7">
-        <v>0.42</v>
+        <v>-0.76</v>
       </c>
       <c r="E7">
         <v>22165</v>
@@ -1519,88 +1535,88 @@
         <v>10655</v>
       </c>
       <c r="G7">
-        <v>-48.82</v>
+        <v>-49.21</v>
       </c>
       <c r="H7">
-        <v>6.47</v>
+        <v>5.66</v>
       </c>
       <c r="I7">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="J7">
-        <v>1.24</v>
+        <v>0.35</v>
       </c>
       <c r="K7">
-        <v>3.93</v>
+        <v>5.66</v>
       </c>
       <c r="L7">
-        <v>-32.96</v>
+        <v>-34.38</v>
       </c>
       <c r="M7">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="N7">
         <v>22</v>
       </c>
       <c r="O7">
+        <v>52</v>
+      </c>
+      <c r="P7">
+        <v>11297.6</v>
+      </c>
+      <c r="Q7">
+        <v>11245.75</v>
+      </c>
+      <c r="R7">
+        <v>11372.74</v>
+      </c>
+      <c r="S7">
+        <v>13361.64</v>
+      </c>
+      <c r="T7">
+        <v>-15.74</v>
+      </c>
+      <c r="U7" t="s">
         <v>47</v>
       </c>
-      <c r="P7">
-        <v>11290.4</v>
-      </c>
-      <c r="Q7">
-        <v>11249.5</v>
-      </c>
-      <c r="R7">
-        <v>11386.4</v>
-      </c>
-      <c r="S7">
-        <v>13405</v>
-      </c>
-      <c r="T7">
-        <v>-15.37</v>
-      </c>
-      <c r="U7" t="s">
-        <v>48</v>
-      </c>
       <c r="V7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>51.79</v>
+        <v>48.34</v>
       </c>
       <c r="Z7">
-        <v>-9.449999999999999</v>
+        <v>-11.22</v>
       </c>
       <c r="AA7">
-        <v>-28.07</v>
+        <v>-24.7</v>
       </c>
       <c r="AB7">
-        <v>18.62</v>
+        <v>13.48</v>
       </c>
       <c r="AC7">
-        <v>84.29000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="AD7">
-        <v>80.89</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AE7">
-        <v>311.87</v>
+        <v>318.66</v>
       </c>
       <c r="AF7">
-        <v>-74.19</v>
+        <v>-55.22</v>
       </c>
       <c r="AG7">
-        <v>11476.82</v>
+        <v>11469.72</v>
       </c>
       <c r="AH7">
-        <v>11022.18</v>
+        <v>11021.78</v>
       </c>
       <c r="AI7">
         <v>12101.38</v>
@@ -1609,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>17.73</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,10 +1636,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>321.6</v>
+        <v>316</v>
       </c>
       <c r="D8">
-        <v>0.33</v>
+        <v>-1.74</v>
       </c>
       <c r="E8">
         <v>367.6</v>
@@ -1632,97 +1648,97 @@
         <v>234.31</v>
       </c>
       <c r="G8">
-        <v>-12.51</v>
+        <v>-14.04</v>
       </c>
       <c r="H8">
-        <v>37.25</v>
+        <v>34.86</v>
       </c>
       <c r="I8">
-        <v>-5.91</v>
+        <v>-5.57</v>
       </c>
       <c r="J8">
-        <v>-8.01</v>
+        <v>-14.04</v>
       </c>
       <c r="K8">
-        <v>-2.55</v>
+        <v>-2.62</v>
       </c>
       <c r="L8">
-        <v>4.09</v>
+        <v>6.33</v>
       </c>
       <c r="M8">
-        <v>26.57</v>
+        <v>25.82</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P8">
-        <v>329.17</v>
+        <v>325.44</v>
       </c>
       <c r="Q8">
-        <v>345.91</v>
+        <v>343.53</v>
       </c>
       <c r="R8">
-        <v>341.28</v>
+        <v>340.77</v>
       </c>
       <c r="S8">
-        <v>296.44</v>
+        <v>296.59</v>
       </c>
       <c r="T8">
-        <v>8.49</v>
+        <v>6.54</v>
       </c>
       <c r="U8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>37.46</v>
+        <v>34.84</v>
       </c>
       <c r="Z8">
-        <v>-4.47</v>
+        <v>-5.71</v>
       </c>
       <c r="AA8">
-        <v>-0.82</v>
+        <v>-1.8</v>
       </c>
       <c r="AB8">
-        <v>-3.65</v>
+        <v>-3.91</v>
       </c>
       <c r="AC8">
         <v>1.09</v>
       </c>
       <c r="AD8">
-        <v>6.61</v>
+        <v>3.57</v>
       </c>
       <c r="AE8">
-        <v>11.99</v>
+        <v>12.14</v>
       </c>
       <c r="AF8">
-        <v>-36.49</v>
+        <v>-19.42</v>
       </c>
       <c r="AG8">
-        <v>373.26</v>
+        <v>372.63</v>
       </c>
       <c r="AH8">
-        <v>318.57</v>
+        <v>314.44</v>
       </c>
       <c r="AI8">
-        <v>354.52</v>
+        <v>352.79</v>
       </c>
       <c r="AJ8" t="s">
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>36.86</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>1220</v>
+        <v>1185.5</v>
       </c>
       <c r="D9">
-        <v>-0.24</v>
+        <v>-2.83</v>
       </c>
       <c r="E9">
         <v>1341</v>
@@ -1745,88 +1761,88 @@
         <v>1079.3</v>
       </c>
       <c r="G9">
-        <v>-9.02</v>
+        <v>-11.6</v>
       </c>
       <c r="H9">
-        <v>13.04</v>
+        <v>9.84</v>
       </c>
       <c r="I9">
-        <v>3.72</v>
+        <v>-1.24</v>
       </c>
       <c r="J9">
-        <v>-3.83</v>
+        <v>-6.43</v>
       </c>
       <c r="K9">
-        <v>-3.7</v>
+        <v>-4.92</v>
       </c>
       <c r="L9">
-        <v>4.09</v>
+        <v>1.91</v>
       </c>
       <c r="M9">
-        <v>13.83</v>
+        <v>12.98</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P9">
-        <v>1220.18</v>
+        <v>1217.2</v>
       </c>
       <c r="Q9">
-        <v>1228.29</v>
+        <v>1222.67</v>
       </c>
       <c r="R9">
-        <v>1266.59</v>
+        <v>1264.64</v>
       </c>
       <c r="S9">
-        <v>1244.07</v>
+        <v>1244.09</v>
       </c>
       <c r="T9">
-        <v>-1.93</v>
+        <v>-4.71</v>
       </c>
       <c r="U9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V9" t="s">
         <v>48</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
         <v>47</v>
-      </c>
-      <c r="W9" t="s">
-        <v>48</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>46.53</v>
+        <v>39.69</v>
       </c>
       <c r="Z9">
-        <v>-16.46</v>
+        <v>-17.7</v>
       </c>
       <c r="AA9">
-        <v>-20.19</v>
+        <v>-19.69</v>
       </c>
       <c r="AB9">
-        <v>3.73</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>85.39</v>
+        <v>66.31</v>
       </c>
       <c r="AD9">
-        <v>85.06999999999999</v>
+        <v>80.11</v>
       </c>
       <c r="AE9">
-        <v>30.35</v>
+        <v>31.17</v>
       </c>
       <c r="AF9">
-        <v>-21.75</v>
+        <v>32.22</v>
       </c>
       <c r="AG9">
-        <v>1308.05</v>
+        <v>1297.48</v>
       </c>
       <c r="AH9">
-        <v>1148.52</v>
+        <v>1147.86</v>
       </c>
       <c r="AI9">
         <v>1253.62</v>
@@ -1835,7 +1851,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>30.35</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1846,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>81.31</v>
+        <v>77.36</v>
       </c>
       <c r="D10">
-        <v>0.18</v>
+        <v>-4.86</v>
       </c>
       <c r="E10">
         <v>91.45</v>
@@ -1858,88 +1874,88 @@
         <v>36.08</v>
       </c>
       <c r="G10">
-        <v>-11.09</v>
+        <v>-15.41</v>
       </c>
       <c r="H10">
-        <v>125.36</v>
+        <v>114.41</v>
       </c>
       <c r="I10">
-        <v>-2.33</v>
+        <v>-5.04</v>
       </c>
       <c r="J10">
-        <v>1.43</v>
+        <v>-0.36</v>
       </c>
       <c r="K10">
-        <v>21.25</v>
+        <v>23.48</v>
       </c>
       <c r="L10">
-        <v>2.3</v>
+        <v>-3.63</v>
       </c>
       <c r="M10">
-        <v>-2.37</v>
+        <v>-2.99</v>
       </c>
       <c r="N10">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="P10">
-        <v>81.3</v>
+        <v>80.48</v>
       </c>
       <c r="Q10">
-        <v>78.81999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="R10">
-        <v>81.29000000000001</v>
+        <v>81.16</v>
       </c>
       <c r="S10">
-        <v>62.67</v>
+        <v>62.68</v>
       </c>
       <c r="T10">
-        <v>29.75</v>
+        <v>23.43</v>
       </c>
       <c r="U10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V10" t="s">
         <v>48</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>47</v>
-      </c>
-      <c r="W10" t="s">
-        <v>48</v>
       </c>
       <c r="X10">
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>53.89</v>
+        <v>44.88</v>
       </c>
       <c r="Z10">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="AA10">
+        <v>0.13</v>
+      </c>
+      <c r="AB10">
         <v>0.11</v>
       </c>
-      <c r="AB10">
-        <v>0.42</v>
-      </c>
       <c r="AC10">
-        <v>72.34</v>
+        <v>51.79</v>
       </c>
       <c r="AD10">
-        <v>74.09999999999999</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="AE10">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="AF10">
-        <v>53.17</v>
+        <v>0.85</v>
       </c>
       <c r="AG10">
-        <v>83.89</v>
+        <v>83.84</v>
       </c>
       <c r="AH10">
-        <v>73.75</v>
+        <v>73.62</v>
       </c>
       <c r="AI10">
         <v>88.06999999999999</v>
@@ -1948,7 +1964,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>22.34</v>
+        <v>21.13</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2129,7 +2145,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2149,10 +2165,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>62</v>
@@ -2161,1027 +2177,1039 @@
         <v>63</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="F7" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-6.9</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-10.36</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-6.6</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-14.83</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-8.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-8.17</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.29</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-5.56</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.27</v>
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-9.710000000000001</v>
+        <v>-10.36</v>
       </c>
       <c r="D12" s="7">
-        <v>-10.27</v>
+        <v>2.42</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.5600000000000001</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>0.13</v>
+        <v>-14.83</v>
       </c>
       <c r="D13" s="7">
-        <v>1.24</v>
+        <v>-18.96</v>
       </c>
       <c r="E13" s="9">
-        <v>1.11</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-7.95</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D14" s="7">
-        <v>-8.01</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.06</v>
+        <v>-10.96</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-4.13</v>
+        <v>-5.56</v>
       </c>
       <c r="D15" s="7">
-        <v>-3.83</v>
+        <v>-7.54</v>
       </c>
       <c r="E15" s="9">
-        <v>0.3</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>0.32</v>
+        <v>-10.27</v>
       </c>
       <c r="D16" s="7">
-        <v>1.43</v>
+        <v>-13.41</v>
       </c>
       <c r="E16" s="9">
-        <v>1.11</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>3.89</v>
+        <v>1.24</v>
       </c>
       <c r="D17" s="7">
-        <v>-8.48</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-12.37</v>
+        <v>0.35</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.47</v>
+        <v>-8.01</v>
       </c>
       <c r="D18" s="7">
-        <v>-15.99</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-11.52</v>
+        <v>-14.04</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-6.03</v>
       </c>
     <